--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="1306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="1307">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333736181259155</t>
+    <t xml:space="preserve">0.333736151456833</t>
   </si>
   <si>
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327446281909943</t>
+    <t xml:space="preserve">0.327446311712265</t>
   </si>
   <si>
     <t xml:space="preserve">0.321156322956085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317678362131119</t>
+    <t xml:space="preserve">0.317678391933441</t>
   </si>
   <si>
     <t xml:space="preserve">0.307318478822708</t>
@@ -65,43 +65,43 @@
     <t xml:space="preserve">0.294368624687195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285636752843857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273796826601028</t>
+    <t xml:space="preserve">0.285636782646179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273796886205673</t>
   </si>
   <si>
     <t xml:space="preserve">0.258997052907944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25825709104538</t>
+    <t xml:space="preserve">0.258257061243057</t>
   </si>
   <si>
     <t xml:space="preserve">0.243605211377144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246417209506035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262696981430054</t>
+    <t xml:space="preserve">0.246417179703712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262696951627731</t>
   </si>
   <si>
     <t xml:space="preserve">0.256407082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.259811013936996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261512994766235</t>
+    <t xml:space="preserve">0.259811073541641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261513024568558</t>
   </si>
   <si>
     <t xml:space="preserve">0.253817081451416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25307708978653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286894708871841</t>
+    <t xml:space="preserve">0.253077119588852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286894738674164</t>
   </si>
   <si>
     <t xml:space="preserve">0.284600764513016</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">0.290742665529251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263806939125061</t>
+    <t xml:space="preserve">0.263806968927383</t>
   </si>
   <si>
     <t xml:space="preserve">0.256777077913284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250117152929306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277570843696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297994583845139</t>
+    <t xml:space="preserve">0.250117123126984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277570784091949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297994613647461</t>
   </si>
   <si>
     <t xml:space="preserve">0.310796439647675</t>
@@ -143,64 +143,64 @@
     <t xml:space="preserve">0.318122327327728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309686452150345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30162051320076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310352444648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323376297950745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320046365261078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316716402769089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315236359834671</t>
+    <t xml:space="preserve">0.309686481952667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301620543003082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31035241484642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323376327753067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320046335458755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316716372966766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315236389636993</t>
   </si>
   <si>
     <t xml:space="preserve">0.315606385469437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332996129989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332256197929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328852236270905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330480217933655</t>
+    <t xml:space="preserve">0.332996159791946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332256227731705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328852266073227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330480188131332</t>
   </si>
   <si>
     <t xml:space="preserve">0.311240434646606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312054455280304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299696534872055</t>
+    <t xml:space="preserve">0.312054425477982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299696564674377</t>
   </si>
   <si>
     <t xml:space="preserve">0.296884596347809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2994005382061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29747661948204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295996576547623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293702632188797</t>
+    <t xml:space="preserve">0.299400568008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297476559877396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295996636152267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293702661991119</t>
   </si>
   <si>
     <t xml:space="preserve">0.298216581344604</t>
@@ -212,34 +212,34 @@
     <t xml:space="preserve">0.276756852865219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274536818265915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2723169028759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268542915582657</t>
+    <t xml:space="preserve">0.274536848068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272316873073578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268542885780334</t>
   </si>
   <si>
     <t xml:space="preserve">0.270466893911362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265064984560013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268172919750214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268616914749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269208908081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275276869535446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28489676117897</t>
+    <t xml:space="preserve">0.26506495475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268172949552536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26861697435379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269208878278732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275276839733124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284896731376648</t>
   </si>
   <si>
     <t xml:space="preserve">0.290002673864365</t>
@@ -251,10 +251,10 @@
     <t xml:space="preserve">0.309168487787247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318196386098862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31693834066391</t>
+    <t xml:space="preserve">0.318196326494217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316938400268555</t>
   </si>
   <si>
     <t xml:space="preserve">0.308946460485458</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">0.314200401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321378320455551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319380313158035</t>
+    <t xml:space="preserve">0.321378350257874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319380342960358</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722440481186</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">0.30709645152092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30761444568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304950505495071</t>
+    <t xml:space="preserve">0.307614475488663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304950535297394</t>
   </si>
   <si>
     <t xml:space="preserve">0.305616497993469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299548596143723</t>
+    <t xml:space="preserve">0.2995485663414</t>
   </si>
   <si>
     <t xml:space="preserve">0.305320471525192</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">0.295626610517502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300954550504684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314400315284729</t>
+    <t xml:space="preserve">0.300954520702362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314400285482407</t>
   </si>
   <si>
     <t xml:space="preserve">0.318779796361923</t>
@@ -311,40 +311,40 @@
     <t xml:space="preserve">0.318856596946716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318395644426346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319932252168655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318088263273239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307331651449203</t>
+    <t xml:space="preserve">0.318395614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319932281970978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318088293075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307331711053848</t>
   </si>
   <si>
     <t xml:space="preserve">0.321776270866394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320393264293671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311557531356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305795043706894</t>
+    <t xml:space="preserve">0.320393294095993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311557501554489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305795013904572</t>
   </si>
   <si>
     <t xml:space="preserve">0.301569253206253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295806765556335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299648344516754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296575099229813</t>
+    <t xml:space="preserve">0.295806735754013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299648374319077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296575129032135</t>
   </si>
   <si>
     <t xml:space="preserve">0.303490042686462</t>
@@ -362,31 +362,31 @@
     <t xml:space="preserve">0.32116162776947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310020804405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311941623687744</t>
+    <t xml:space="preserve">0.310020834207535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311941653490067</t>
   </si>
   <si>
     <t xml:space="preserve">0.311173319816589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30725485086441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30671700835228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305564552545547</t>
+    <t xml:space="preserve">0.307254821062088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306716978549957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30556458234787</t>
   </si>
   <si>
     <t xml:space="preserve">0.304949879646301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306870698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297727555036545</t>
+    <t xml:space="preserve">0.306870669126511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297727584838867</t>
   </si>
   <si>
     <t xml:space="preserve">0.301799744367599</t>
@@ -395,19 +395,19 @@
     <t xml:space="preserve">0.304027855396271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300032556056976</t>
+    <t xml:space="preserve">0.300032585859299</t>
   </si>
   <si>
     <t xml:space="preserve">0.313478320837021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31255629658699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307869523763657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311480671167374</t>
+    <t xml:space="preserve">0.312556326389313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307869493961334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311480611562729</t>
   </si>
   <si>
     <t xml:space="preserve">0.298265427350998</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">0.295576244592667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295960396528244</t>
+    <t xml:space="preserve">0.295960366725922</t>
   </si>
   <si>
     <t xml:space="preserve">0.297650754451752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297881215810776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293732285499573</t>
+    <t xml:space="preserve">0.297881275415421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29373225569725</t>
   </si>
   <si>
     <t xml:space="preserve">0.298803210258484</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">0.300416707992554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300109416246414</t>
+    <t xml:space="preserve">0.300109386444092</t>
   </si>
   <si>
     <t xml:space="preserve">0.298880040645599</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">0.30548769235611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309559881687164</t>
+    <t xml:space="preserve">0.309559851884842</t>
   </si>
   <si>
     <t xml:space="preserve">0.303105890750885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303566843271255</t>
+    <t xml:space="preserve">0.303566873073578</t>
   </si>
   <si>
     <t xml:space="preserve">0.308253675699234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304873019456863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306563377380371</t>
+    <t xml:space="preserve">0.304873079061508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306563317775726</t>
   </si>
   <si>
     <t xml:space="preserve">0.300186216831207</t>
@@ -473,25 +473,25 @@
     <t xml:space="preserve">0.298649579286575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296421378850937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301415532827377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3006471991539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282975643873215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291965067386627</t>
+    <t xml:space="preserve">0.296421408653259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301415592432022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300647228956223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282975614070892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29196509718895</t>
   </si>
   <si>
     <t xml:space="preserve">0.289736956357956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293501764535904</t>
+    <t xml:space="preserve">0.293501734733582</t>
   </si>
   <si>
     <t xml:space="preserve">0.292656600475311</t>
@@ -500,16 +500,16 @@
     <t xml:space="preserve">0.292502909898758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289583295583725</t>
+    <t xml:space="preserve">0.289583265781403</t>
   </si>
   <si>
     <t xml:space="preserve">0.288123458623886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2842817902565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287892997264862</t>
+    <t xml:space="preserve">0.284281820058823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28789296746254</t>
   </si>
   <si>
     <t xml:space="preserve">0.290044277906418</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">0.293117612600327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291888266801834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289813756942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286586850881577</t>
+    <t xml:space="preserve">0.291888296604156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289813816547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286586791276932</t>
   </si>
   <si>
     <t xml:space="preserve">0.294270098209381</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">0.291811436414719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292579799890518</t>
+    <t xml:space="preserve">0.292579770088196</t>
   </si>
   <si>
     <t xml:space="preserve">0.295729905366898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298419088125229</t>
+    <t xml:space="preserve">0.298419058322906</t>
   </si>
   <si>
     <t xml:space="preserve">0.294731080532074</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">0.287355154752731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293809056282043</t>
+    <t xml:space="preserve">0.293809115886688</t>
   </si>
   <si>
     <t xml:space="preserve">0.292041927576065</t>
@@ -563,16 +563,16 @@
     <t xml:space="preserve">0.2846659719944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278903514146805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275599658489227</t>
+    <t xml:space="preserve">0.278903543949127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27559968829155</t>
   </si>
   <si>
     <t xml:space="preserve">0.270221412181854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272449553012848</t>
+    <t xml:space="preserve">0.272449523210526</t>
   </si>
   <si>
     <t xml:space="preserve">0.276675343513489</t>
@@ -596,16 +596,16 @@
     <t xml:space="preserve">0.27114337682724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274293512105942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270451873540878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268146932125092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267378598451614</t>
+    <t xml:space="preserve">0.274293571710587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270451903343201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268146902322769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267378568649292</t>
   </si>
   <si>
     <t xml:space="preserve">0.264612555503845</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">0.262384444475174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267532229423523</t>
+    <t xml:space="preserve">0.267532199621201</t>
   </si>
   <si>
     <t xml:space="preserve">0.265304088592529</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">0.272526353597641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283282935619354</t>
+    <t xml:space="preserve">0.283282965421677</t>
   </si>
   <si>
     <t xml:space="preserve">0.279902338981628</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.277059525251389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27844250202179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280517041683197</t>
+    <t xml:space="preserve">0.278442531824112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280517011880875</t>
   </si>
   <si>
     <t xml:space="preserve">0.278749823570251</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">0.278980314731598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278212010860443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284051328897476</t>
+    <t xml:space="preserve">0.278212040662766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284051299095154</t>
   </si>
   <si>
     <t xml:space="preserve">0.290812641382217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289660096168518</t>
+    <t xml:space="preserve">0.28966012597084</t>
   </si>
   <si>
     <t xml:space="preserve">0.290428429841995</t>
@@ -671,28 +671,28 @@
     <t xml:space="preserve">0.295422583818436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288507580757141</t>
+    <t xml:space="preserve">0.288507610559464</t>
   </si>
   <si>
     <t xml:space="preserve">0.284589141607285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291043132543564</t>
+    <t xml:space="preserve">0.291043102741241</t>
   </si>
   <si>
     <t xml:space="preserve">0.293885916471481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294884771108627</t>
+    <t xml:space="preserve">0.294884711503983</t>
   </si>
   <si>
     <t xml:space="preserve">0.289890617132187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286125779151917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284358620643616</t>
+    <t xml:space="preserve">0.286125808954239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284358590841293</t>
   </si>
   <si>
     <t xml:space="preserve">0.282745152711868</t>
@@ -704,28 +704,28 @@
     <t xml:space="preserve">0.281976819038391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276214361190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27360200881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269760370254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275061875581741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271834880113602</t>
+    <t xml:space="preserve">0.276214301586151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273602038621902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269760429859161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275061845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271834909915924</t>
   </si>
   <si>
     <t xml:space="preserve">0.273371547460556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275215536355972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276905864477158</t>
+    <t xml:space="preserve">0.27521550655365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276905834674835</t>
   </si>
   <si>
     <t xml:space="preserve">0.27483132481575</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">0.281208485364914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278673022985458</t>
+    <t xml:space="preserve">0.278672993183136</t>
   </si>
   <si>
     <t xml:space="preserve">0.282591491937637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279364496469498</t>
+    <t xml:space="preserve">0.279364466667175</t>
   </si>
   <si>
     <t xml:space="preserve">0.285587966442108</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">0.283897668123245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285280644893646</t>
+    <t xml:space="preserve">0.285280674695969</t>
   </si>
   <si>
     <t xml:space="preserve">0.285434275865555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295038431882858</t>
+    <t xml:space="preserve">0.295038402080536</t>
   </si>
   <si>
     <t xml:space="preserve">0.30425837635994</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">0.321929931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325617909431458</t>
+    <t xml:space="preserve">0.32561793923378</t>
   </si>
   <si>
     <t xml:space="preserve">0.33184140920639</t>
@@ -800,37 +800,37 @@
     <t xml:space="preserve">0.325387418270111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316935747861862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309790343046188</t>
+    <t xml:space="preserve">0.316935807466507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309790372848511</t>
   </si>
   <si>
     <t xml:space="preserve">0.309252500534058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311096489429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313094168901443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313017308712006</t>
+    <t xml:space="preserve">0.311096519231796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313094139099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313017338514328</t>
   </si>
   <si>
     <t xml:space="preserve">0.288891792297363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293040722608566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295192092657089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296805560588837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297266602516174</t>
+    <t xml:space="preserve">0.293040752410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295192062854767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296805590391159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297266572713852</t>
   </si>
   <si>
     <t xml:space="preserve">0.298111736774445</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">0.310251355171204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313555121421814</t>
+    <t xml:space="preserve">0.313555151224136</t>
   </si>
   <si>
     <t xml:space="preserve">0.300800889730453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30886834859848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299725234508514</t>
+    <t xml:space="preserve">0.308868318796158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299725204706192</t>
   </si>
   <si>
     <t xml:space="preserve">0.321853131055832</t>
@@ -857,37 +857,37 @@
     <t xml:space="preserve">0.327308237552643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318472474813461</t>
+    <t xml:space="preserve">0.318472445011139</t>
   </si>
   <si>
     <t xml:space="preserve">0.31209534406662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314016133546829</t>
+    <t xml:space="preserve">0.314016163349152</t>
   </si>
   <si>
     <t xml:space="preserve">0.315014988183975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312248975038528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313939332962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309636652469635</t>
+    <t xml:space="preserve">0.312249004840851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313939303159714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309636682271957</t>
   </si>
   <si>
     <t xml:space="preserve">0.307408511638641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308945208787918</t>
+    <t xml:space="preserve">0.308945178985596</t>
   </si>
   <si>
     <t xml:space="preserve">0.313631981611252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308023184537888</t>
+    <t xml:space="preserve">0.308023154735565</t>
   </si>
   <si>
     <t xml:space="preserve">0.307715833187103</t>
@@ -908,25 +908,25 @@
     <t xml:space="preserve">0.316474825143814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324388593435287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325003296136856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31831881403923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317704111337662</t>
+    <t xml:space="preserve">0.324388563632965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325003266334534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318318754434586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317704141139984</t>
   </si>
   <si>
     <t xml:space="preserve">0.32154580950737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320470124483109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621464729309</t>
+    <t xml:space="preserve">0.320470094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621434926987</t>
   </si>
   <si>
     <t xml:space="preserve">0.323697090148926</t>
@@ -944,16 +944,16 @@
     <t xml:space="preserve">0.339524686336517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34567129611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340446650981903</t>
+    <t xml:space="preserve">0.345671325922012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340446680784225</t>
   </si>
   <si>
     <t xml:space="preserve">0.333378046751022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334991544485092</t>
+    <t xml:space="preserve">0.334991484880447</t>
   </si>
   <si>
     <t xml:space="preserve">0.336144030094147</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">0.337757498025894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338910013437271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338141739368439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339678347110748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350358128547668</t>
+    <t xml:space="preserve">0.338910043239594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338141679763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339678317308426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350358098745346</t>
   </si>
   <si>
     <t xml:space="preserve">0.346593290567398</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">0.344211518764496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34067714214325</t>
+    <t xml:space="preserve">0.340677171945572</t>
   </si>
   <si>
     <t xml:space="preserve">0.334607362747192</t>
@@ -989,34 +989,34 @@
     <t xml:space="preserve">0.338218539953232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346900641918182</t>
+    <t xml:space="preserve">0.34690061211586</t>
   </si>
   <si>
     <t xml:space="preserve">0.346132308244705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33960148692131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340907663106918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3526631295681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369950532913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365417391061783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363035559654236</t>
+    <t xml:space="preserve">0.339601516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340907633304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352663099765778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369950503110886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36541736125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363035529851913</t>
   </si>
   <si>
     <t xml:space="preserve">0.374099493026733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371103048324585</t>
+    <t xml:space="preserve">0.371103018522263</t>
   </si>
   <si>
     <t xml:space="preserve">0.369566351175308</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">0.368798017501831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366108894348145</t>
+    <t xml:space="preserve">0.366108864545822</t>
   </si>
   <si>
     <t xml:space="preserve">0.363112390041351</t>
@@ -1037,25 +1037,25 @@
     <t xml:space="preserve">0.366877168416977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366262525320053</t>
+    <t xml:space="preserve">0.366262555122375</t>
   </si>
   <si>
     <t xml:space="preserve">0.361114740371704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359885424375534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359193921089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368567496538162</t>
+    <t xml:space="preserve">0.359885394573212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35919389128685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368567526340485</t>
   </si>
   <si>
     <t xml:space="preserve">0.372024983167648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37555930018425</t>
+    <t xml:space="preserve">0.375559329986572</t>
   </si>
   <si>
     <t xml:space="preserve">0.380246132612228</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">0.405677825212479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421044439077377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419507741928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39684209227562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413361072540283</t>
+    <t xml:space="preserve">0.421044379472733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419507771730423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396842062473297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413361102342606</t>
   </si>
   <si>
     <t xml:space="preserve">0.422581076622009</t>
@@ -1085,19 +1085,19 @@
     <t xml:space="preserve">0.417586892843246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426422715187073</t>
+    <t xml:space="preserve">0.426422744989395</t>
   </si>
   <si>
     <t xml:space="preserve">0.423349380493164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427959412336349</t>
+    <t xml:space="preserve">0.427959322929382</t>
   </si>
   <si>
     <t xml:space="preserve">0.436795145273209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432953476905823</t>
+    <t xml:space="preserve">0.432953506708145</t>
   </si>
   <si>
     <t xml:space="preserve">0.452930063009262</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">0.481358259916306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522463858127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515164792537689</t>
+    <t xml:space="preserve">0.522463798522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515164732933044</t>
   </si>
   <si>
     <t xml:space="preserve">0.505560576915741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50709730386734</t>
+    <t xml:space="preserve">0.507097244262695</t>
   </si>
   <si>
     <t xml:space="preserve">0.515548884868622</t>
@@ -1133,19 +1133,19 @@
     <t xml:space="preserve">0.503255605697632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489809840917587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480205774307251</t>
+    <t xml:space="preserve">0.489809900522232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480205714702606</t>
   </si>
   <si>
     <t xml:space="preserve">0.519006371498108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511323094367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499413937330246</t>
+    <t xml:space="preserve">0.511323034763336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499413996934891</t>
   </si>
   <si>
     <t xml:space="preserve">0.491730690002441</t>
@@ -1154,16 +1154,16 @@
     <t xml:space="preserve">0.484431564807892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483663201332092</t>
+    <t xml:space="preserve">0.483663141727448</t>
   </si>
   <si>
     <t xml:space="preserve">0.484815716743469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49518820643425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490194082260132</t>
+    <t xml:space="preserve">0.495188146829605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490194022655487</t>
   </si>
   <si>
     <t xml:space="preserve">0.553197085857391</t>
@@ -1172,55 +1172,55 @@
     <t xml:space="preserve">0.542056262493134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56280118227005</t>
+    <t xml:space="preserve">0.562801122665405</t>
   </si>
   <si>
     <t xml:space="preserve">0.586235225200653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600065112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582393527030945</t>
+    <t xml:space="preserve">0.600065171718597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58239358663559</t>
   </si>
   <si>
     <t xml:space="preserve">0.572021126747131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572789490222931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552428722381592</t>
+    <t xml:space="preserve">0.572789371013641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552428603172302</t>
   </si>
   <si>
     <t xml:space="preserve">0.55127614736557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545129537582397</t>
+    <t xml:space="preserve">0.545129597187042</t>
   </si>
   <si>
     <t xml:space="preserve">0.565874457359314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577015161514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596607506275177</t>
+    <t xml:space="preserve">0.577015221118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596607625484467</t>
   </si>
   <si>
     <t xml:space="preserve">0.584698498249054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608132541179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621962487697601</t>
+    <t xml:space="preserve">0.608132481575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621962428092957</t>
   </si>
   <si>
     <t xml:space="preserve">0.620425879955292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629645884037018</t>
+    <t xml:space="preserve">0.629645824432373</t>
   </si>
   <si>
     <t xml:space="preserve">0.614279210567474</t>
@@ -1244,25 +1244,25 @@
     <t xml:space="preserve">0.619657516479492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618120789527893</t>
+    <t xml:space="preserve">0.618120849132538</t>
   </si>
   <si>
     <t xml:space="preserve">0.601601779460907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586619257926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59545511007309</t>
+    <t xml:space="preserve">0.586619317531586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595455169677734</t>
   </si>
   <si>
     <t xml:space="preserve">0.587771832942963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584314405918121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577399432659149</t>
+    <t xml:space="preserve">0.584314346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577399373054504</t>
   </si>
   <si>
     <t xml:space="preserve">0.567026913166046</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">0.57432609796524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543592870235443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564721941947937</t>
+    <t xml:space="preserve">0.543592929840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564722061157227</t>
   </si>
   <si>
     <t xml:space="preserve">0.563185274600983</t>
@@ -1283,19 +1283,19 @@
     <t xml:space="preserve">0.576246917247772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583930134773254</t>
+    <t xml:space="preserve">0.583930194377899</t>
   </si>
   <si>
     <t xml:space="preserve">0.58085685968399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587003529071808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604675054550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629261612892151</t>
+    <t xml:space="preserve">0.587003469467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604675114154816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629261553287506</t>
   </si>
   <si>
     <t xml:space="preserve">0.618505001068115</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">0.612358391284943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611590087413788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59391850233078</t>
+    <t xml:space="preserve">0.611590027809143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593918442726135</t>
   </si>
   <si>
     <t xml:space="preserve">0.596991777420044</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">0.608516752719879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599296689033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589308440685272</t>
+    <t xml:space="preserve">0.599296748638153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589308500289917</t>
   </si>
   <si>
     <t xml:space="preserve">0.553965389728546</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">0.557038724422455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536293864250183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524000465869904</t>
+    <t xml:space="preserve">0.536293804645538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524000525474548</t>
   </si>
   <si>
     <t xml:space="preserve">0.537830471992493</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">0.547818720340729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53245210647583</t>
+    <t xml:space="preserve">0.532452166080475</t>
   </si>
   <si>
     <t xml:space="preserve">0.537062108516693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527073860168457</t>
+    <t xml:space="preserve">0.527073800563812</t>
   </si>
   <si>
     <t xml:space="preserve">0.52092719078064</t>
@@ -1364,16 +1364,16 @@
     <t xml:space="preserve">0.517853915691376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525537133216858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530147135257721</t>
+    <t xml:space="preserve">0.525537192821503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530147194862366</t>
   </si>
   <si>
     <t xml:space="preserve">0.523232221603394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51939058303833</t>
+    <t xml:space="preserve">0.519390523433685</t>
   </si>
   <si>
     <t xml:space="preserve">0.524768888950348</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">0.549355387687683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501718938350677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492499023675919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477900832891464</t>
+    <t xml:space="preserve">0.501718997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492499083280563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477900803089142</t>
   </si>
   <si>
     <t xml:space="preserve">0.476364135742188</t>
@@ -1400,43 +1400,43 @@
     <t xml:space="preserve">0.471754133701324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472522526979446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468680769205093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487120717763901</t>
+    <t xml:space="preserve">0.472522407770157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468680918216705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487120658159256</t>
   </si>
   <si>
     <t xml:space="preserve">0.481742382049561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480974107980728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48327910900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478669077157974</t>
+    <t xml:space="preserve">0.480974048376083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483279049396515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478669106960297</t>
   </si>
   <si>
     <t xml:space="preserve">0.47021746635437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467912584543228</t>
+    <t xml:space="preserve">0.467912554740906</t>
   </si>
   <si>
     <t xml:space="preserve">0.466375827789307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464839190244675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461765855550766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4878890812397</t>
+    <t xml:space="preserve">0.464839220046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461765915155411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487889051437378</t>
   </si>
   <si>
     <t xml:space="preserve">0.500182330608368</t>
@@ -1445,25 +1445,25 @@
     <t xml:space="preserve">0.469449132680893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437179356813431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444862633943558</t>
+    <t xml:space="preserve">0.437179327011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444862574338913</t>
   </si>
   <si>
     <t xml:space="preserve">0.431800991296768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444094240665436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424117654561996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415666133165359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382627934217453</t>
+    <t xml:space="preserve">0.444094330072403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424117684364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415666103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382627964019775</t>
   </si>
   <si>
     <t xml:space="preserve">0.379170447587967</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">0.388774573802948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391847878694534</t>
+    <t xml:space="preserve">0.391847908496857</t>
   </si>
   <si>
     <t xml:space="preserve">0.384164601564407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376481294631958</t>
+    <t xml:space="preserve">0.37648132443428</t>
   </si>
   <si>
     <t xml:space="preserve">0.367261350154877</t>
@@ -1493,16 +1493,16 @@
     <t xml:space="preserve">0.364956378936768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360346406698227</t>
+    <t xml:space="preserve">0.360346436500549</t>
   </si>
   <si>
     <t xml:space="preserve">0.352278918027878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356504708528519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37148717045784</t>
+    <t xml:space="preserve">0.356504768133163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371487140655518</t>
   </si>
   <si>
     <t xml:space="preserve">0.368029683828354</t>
@@ -1511,34 +1511,34 @@
     <t xml:space="preserve">0.372255504131317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365340501070023</t>
+    <t xml:space="preserve">0.365340530872345</t>
   </si>
   <si>
     <t xml:space="preserve">0.374944627285004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3664930164814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374560475349426</t>
+    <t xml:space="preserve">0.366492986679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374560505151749</t>
   </si>
   <si>
     <t xml:space="preserve">0.374176323413849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378786325454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362267255783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353815615177155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354583919048309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353047281503677</t>
+    <t xml:space="preserve">0.37878629565239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362267225980759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353815585374832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354583889245987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353047311306</t>
   </si>
   <si>
     <t xml:space="preserve">0.370718836784363</t>
@@ -1547,22 +1547,22 @@
     <t xml:space="preserve">0.354199767112732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39568954706192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411056160926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407982885837555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38493287563324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390311270952225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378017961978912</t>
+    <t xml:space="preserve">0.395689517259598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411056131124496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407982796430588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384932935237885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390311241149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378017991781235</t>
   </si>
   <si>
     <t xml:space="preserve">0.380707114934921</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">0.353431463241577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349589765071869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344979822635651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343059003353119</t>
+    <t xml:space="preserve">0.349589824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344979852437973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343058973550797</t>
   </si>
   <si>
     <t xml:space="preserve">0.354968100786209</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">0.364188075065613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357273072004318</t>
+    <t xml:space="preserve">0.357273101806641</t>
   </si>
   <si>
     <t xml:space="preserve">0.349973976612091</t>
@@ -1613,25 +1613,25 @@
     <t xml:space="preserve">0.389542937278748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404141128063202</t>
+    <t xml:space="preserve">0.404141157865524</t>
   </si>
   <si>
     <t xml:space="preserve">0.396457880735397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412592768669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404909461736679</t>
+    <t xml:space="preserve">0.412592798471451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404909521341324</t>
   </si>
   <si>
     <t xml:space="preserve">0.401836186647415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394152909517288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399531185626984</t>
+    <t xml:space="preserve">0.394152879714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399531155824661</t>
   </si>
   <si>
     <t xml:space="preserve">0.40260449051857</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">0.40106788277626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397994548082352</t>
+    <t xml:space="preserve">0.397994518280029</t>
   </si>
   <si>
     <t xml:space="preserve">0.375712960958481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364572197198868</t>
+    <t xml:space="preserve">0.36457222700119</t>
   </si>
   <si>
     <t xml:space="preserve">0.345748126506805</t>
@@ -1655,16 +1655,16 @@
     <t xml:space="preserve">0.336528211832047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335759878158569</t>
+    <t xml:space="preserve">0.335759907960892</t>
   </si>
   <si>
     <t xml:space="preserve">0.337296515703201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329613208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328076511621475</t>
+    <t xml:space="preserve">0.329613238573074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328076541423798</t>
   </si>
   <si>
     <t xml:space="preserve">0.331534057855606</t>
@@ -1679,28 +1679,28 @@
     <t xml:space="preserve">0.312709987163544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341138184070587</t>
+    <t xml:space="preserve">0.34113821387291</t>
   </si>
   <si>
     <t xml:space="preserve">0.322698265314102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326155751943588</t>
+    <t xml:space="preserve">0.326155722141266</t>
   </si>
   <si>
     <t xml:space="preserve">0.324619084596634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325771570205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330381572246552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329997420310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324234962463379</t>
+    <t xml:space="preserve">0.325771600008011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330381542444229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329997390508652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324234932661057</t>
   </si>
   <si>
     <t xml:space="preserve">0.313862472772598</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">0.30387419462204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29695925116539</t>
+    <t xml:space="preserve">0.296959221363068</t>
   </si>
   <si>
     <t xml:space="preserve">0.302721709012985</t>
@@ -1724,31 +1724,31 @@
     <t xml:space="preserve">0.308100014925003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310405015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306947499513626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314630806446075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305410891771317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30848416686058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304642528295517</t>
+    <t xml:space="preserve">0.310404986143112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306947529315948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314630776643753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305410832166672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308484196662903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304642498493195</t>
   </si>
   <si>
     <t xml:space="preserve">0.32077744603157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356888920068741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358041405677795</t>
+    <t xml:space="preserve">0.356888949871063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358041375875473</t>
   </si>
   <si>
     <t xml:space="preserve">0.356120586395264</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">0.360730588436127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358809769153595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351126462221146</t>
+    <t xml:space="preserve">0.358809739351273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351126432418823</t>
   </si>
   <si>
     <t xml:space="preserve">0.355736404657364</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">0.376097172498703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376865476369858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377249628305435</t>
+    <t xml:space="preserve">0.37686550617218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377249658107758</t>
   </si>
   <si>
     <t xml:space="preserve">0.398762881755829</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">0.381475448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407214492559433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387237936258316</t>
+    <t xml:space="preserve">0.407214462757111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387237906455994</t>
   </si>
   <si>
     <t xml:space="preserve">0.394921183586121</t>
@@ -1817,37 +1817,37 @@
     <t xml:space="preserve">0.411824464797974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414897799491882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417202770709991</t>
+    <t xml:space="preserve">0.41489776968956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417202711105347</t>
   </si>
   <si>
     <t xml:space="preserve">0.397226184606552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408751159906387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410287797451019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414129376411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416434407234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418739408254623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420276075601578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421812742948532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430264353752136</t>
+    <t xml:space="preserve">0.40875118970871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410287767648697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41412940621376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416434466838837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418739438056946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4202761054039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421812772750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430264383554459</t>
   </si>
   <si>
     <t xml:space="preserve">0.473290801048279</t>
@@ -1856,91 +1856,91 @@
     <t xml:space="preserve">0.49480402469635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484047323465347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267416954041</t>
+    <t xml:space="preserve">0.484047442674637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267357349396</t>
   </si>
   <si>
     <t xml:space="preserve">0.506328940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479437440633774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482510775327682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47559580206871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465607523918152</t>
+    <t xml:space="preserve">0.479437381029129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482510715723038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595921278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070856571198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465607434511185</t>
   </si>
   <si>
     <t xml:space="preserve">0.460997521877289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434105962514877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789299249649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445630967617035</t>
+    <t xml:space="preserve">0.453314214944839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4341059923172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789239645004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44563090801239</t>
   </si>
   <si>
     <t xml:space="preserve">0.449472546577454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451009213924408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460229188203812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454082578420639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45715594291687</t>
+    <t xml:space="preserve">0.451009303331375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460229218006134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454082548618317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457155913114548</t>
   </si>
   <si>
     <t xml:space="preserve">0.451777577400208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456387519836426</t>
+    <t xml:space="preserve">0.456387490034103</t>
   </si>
   <si>
     <t xml:space="preserve">0.463302463293076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470985740423203</t>
+    <t xml:space="preserve">0.470985800027847</t>
   </si>
   <si>
     <t xml:space="preserve">0.467144161462784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457924216985703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447167664766312</t>
+    <t xml:space="preserve">0.457924246788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447167634963989</t>
   </si>
   <si>
     <t xml:space="preserve">0.432569354772568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437947690486908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433337658643723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434874355792999</t>
+    <t xml:space="preserve">0.437947660684586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433337688446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434874325990677</t>
   </si>
   <si>
     <t xml:space="preserve">0.436411023139954</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">0.43948432803154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441020935773849</t>
+    <t xml:space="preserve">0.441020965576172</t>
   </si>
   <si>
     <t xml:space="preserve">0.440252661705017</t>
@@ -1958,64 +1958,64 @@
     <t xml:space="preserve">0.43871596455574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442557573318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485584050416946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455619245767593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443325966596603</t>
+    <t xml:space="preserve">0.442557543516159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485584169626236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455619215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443326026201248</t>
   </si>
   <si>
     <t xml:space="preserve">0.429496049880981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435642629861832</t>
+    <t xml:space="preserve">0.435642689466476</t>
   </si>
   <si>
     <t xml:space="preserve">0.450240910053253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427191019058228</t>
+    <t xml:space="preserve">0.427191078662872</t>
   </si>
   <si>
     <t xml:space="preserve">0.375328809022903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386469632387161</t>
+    <t xml:space="preserve">0.386469602584839</t>
   </si>
   <si>
     <t xml:space="preserve">0.393384575843811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365724712610245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372639685869217</t>
+    <t xml:space="preserve">0.365724682807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372639715671539</t>
   </si>
   <si>
     <t xml:space="preserve">0.351510614156723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342674851417542</t>
+    <t xml:space="preserve">0.342674821615219</t>
   </si>
   <si>
     <t xml:space="preserve">0.317319959402084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26507356762886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259695291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.239334538578987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242023661732674</t>
+    <t xml:space="preserve">0.265073597431183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259695261716843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239334553480148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242023721337318</t>
   </si>
   <si>
     <t xml:space="preserve">0.234724566340446</t>
@@ -2048,28 +2048,28 @@
     <t xml:space="preserve">0.242407858371735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245097041130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254701137542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262000232934952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254316955804825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261231929063797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262768566608429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264689445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27198851108551</t>
+    <t xml:space="preserve">0.245097011327744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254701167345047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262000262737274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254316985607147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261231899261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262768596410751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264689415693283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271988540887833</t>
   </si>
   <si>
     <t xml:space="preserve">0.273909360170364</t>
@@ -2081,22 +2081,22 @@
     <t xml:space="preserve">0.272756844758987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275445997714996</t>
+    <t xml:space="preserve">0.275446027517319</t>
   </si>
   <si>
     <t xml:space="preserve">0.268915235996246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26584193110466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258542776107788</t>
+    <t xml:space="preserve">0.265841871500015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25854280591011</t>
   </si>
   <si>
     <t xml:space="preserve">0.26545774936676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263152778148651</t>
+    <t xml:space="preserve">0.263152748346329</t>
   </si>
   <si>
     <t xml:space="preserve">0.292733430862427</t>
@@ -2105,61 +2105,61 @@
     <t xml:space="preserve">0.327692419290543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302337527275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30195340514183</t>
+    <t xml:space="preserve">0.302337557077408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301953375339508</t>
   </si>
   <si>
     <t xml:space="preserve">0.332302391529083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332686573266983</t>
+    <t xml:space="preserve">0.332686543464661</t>
   </si>
   <si>
     <t xml:space="preserve">0.306179195642471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305026710033417</t>
+    <t xml:space="preserve">0.305026739835739</t>
   </si>
   <si>
     <t xml:space="preserve">0.312325835227966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331918209791183</t>
+    <t xml:space="preserve">0.331918239593506</t>
   </si>
   <si>
     <t xml:space="preserve">0.315399140119553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326539933681488</t>
+    <t xml:space="preserve">0.326539903879166</t>
   </si>
   <si>
     <t xml:space="preserve">0.292349249124527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289275914430618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291196763515472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286970943212509</t>
+    <t xml:space="preserve">0.289275944232941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291196793317795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286970913410187</t>
   </si>
   <si>
     <t xml:space="preserve">0.285050123929977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273525238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26084777712822</t>
+    <t xml:space="preserve">0.273525208234787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260847747325897</t>
   </si>
   <si>
     <t xml:space="preserve">0.261616110801697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270067691802979</t>
+    <t xml:space="preserve">0.270067721605301</t>
   </si>
   <si>
     <t xml:space="preserve">0.278519362211227</t>
@@ -2180,19 +2180,19 @@
     <t xml:space="preserve">0.256621956825256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256237804889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.249322831630707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236261263489723</t>
+    <t xml:space="preserve">0.256237775087357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.249322801828384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.236261203885078</t>
   </si>
   <si>
     <t xml:space="preserve">0.238182067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25354865193367</t>
+    <t xml:space="preserve">0.253548622131348</t>
   </si>
   <si>
     <t xml:space="preserve">0.267762720584869</t>
@@ -2201,61 +2201,61 @@
     <t xml:space="preserve">0.283513456583023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277750998735428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294654220342636</t>
+    <t xml:space="preserve">0.27775102853775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294654250144958</t>
   </si>
   <si>
     <t xml:space="preserve">0.319624930620193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343827337026596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338449001312256</t>
+    <t xml:space="preserve">0.343827307224274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338448971509933</t>
   </si>
   <si>
     <t xml:space="preserve">0.34075403213501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338833212852478</t>
+    <t xml:space="preserve">0.338833183050156</t>
   </si>
   <si>
     <t xml:space="preserve">0.338064819574356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336912304162979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33383908867836</t>
+    <t xml:space="preserve">0.336912363767624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333839029073715</t>
   </si>
   <si>
     <t xml:space="preserve">0.330765724182129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32884493470192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339985698461533</t>
+    <t xml:space="preserve">0.328844904899597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339985728263855</t>
   </si>
   <si>
     <t xml:space="preserve">0.34766897559166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359962224960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351894795894623</t>
+    <t xml:space="preserve">0.35996225476265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351894825696945</t>
   </si>
   <si>
     <t xml:space="preserve">0.369182199239731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357657223939896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355352252721786</t>
+    <t xml:space="preserve">0.357657253742218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355352282524109</t>
   </si>
   <si>
     <t xml:space="preserve">0.348053127527237</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">0.346516460180283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347284764051437</t>
+    <t xml:space="preserve">0.34728479385376</t>
   </si>
   <si>
     <t xml:space="preserve">0.363419711589813</t>
@@ -2273,19 +2273,19 @@
     <t xml:space="preserve">0.373792141675949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373023808002472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379554629325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425654411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417971163988113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381859630346298</t>
+    <t xml:space="preserve">0.373023837804794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379554599523544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425654381513596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417971104383469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381859600543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.38301208615303</t>
@@ -2294,31 +2294,31 @@
     <t xml:space="preserve">0.377633810043335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378402173519135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381091296672821</t>
+    <t xml:space="preserve">0.37840211391449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381091326475143</t>
   </si>
   <si>
     <t xml:space="preserve">0.380322992801666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348437309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400299549102783</t>
+    <t xml:space="preserve">0.348437339067459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400299578905106</t>
   </si>
   <si>
     <t xml:space="preserve">0.383396297693253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379938781261444</t>
+    <t xml:space="preserve">0.379938811063766</t>
   </si>
   <si>
     <t xml:space="preserve">0.388006269931793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428727716207504</t>
+    <t xml:space="preserve">0.428727746009827</t>
   </si>
   <si>
     <t xml:space="preserve">0.368413895368576</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">0.334223210811615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34190645813942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323466628789902</t>
+    <t xml:space="preserve">0.341906487941742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323466598987579</t>
   </si>
   <si>
     <t xml:space="preserve">0.340369820594788</t>
@@ -2348,43 +2348,43 @@
     <t xml:space="preserve">0.322314113378525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285818487405777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337680697441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345363944768906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341522365808487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329229056835175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353653132915497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351594567298889</t>
+    <t xml:space="preserve">0.285818457603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337680727243423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345363974571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341522336006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329229086637497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353653103113174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351594597101212</t>
   </si>
   <si>
     <t xml:space="preserve">0.354064851999283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352829694747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347477585077286</t>
+    <t xml:space="preserve">0.352829724550247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347477555274963</t>
   </si>
   <si>
     <t xml:space="preserve">0.345830768346786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341713726520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342537134885788</t>
+    <t xml:space="preserve">0.341713696718216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342537194490433</t>
   </si>
   <si>
     <t xml:space="preserve">0.348300993442535</t>
@@ -2399,19 +2399,19 @@
     <t xml:space="preserve">0.354888260364532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350359499454498</t>
+    <t xml:space="preserve">0.350359529256821</t>
   </si>
   <si>
     <t xml:space="preserve">0.345007359981537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339655190706253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342948853969574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341302037239075</t>
+    <t xml:space="preserve">0.339655220508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342948824167252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341302007436752</t>
   </si>
   <si>
     <t xml:space="preserve">0.333479672670364</t>
@@ -2420,49 +2420,49 @@
     <t xml:space="preserve">0.320716857910156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319070041179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321540266275406</t>
+    <t xml:space="preserve">0.319070070981979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321540236473083</t>
   </si>
   <si>
     <t xml:space="preserve">0.310835987329483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315776407718658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314129620790482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312894463539124</t>
+    <t xml:space="preserve">0.315776437520981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314129650592804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312894493341446</t>
   </si>
   <si>
     <t xml:space="preserve">0.318246632814407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317834973335266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319481790065765</t>
+    <t xml:space="preserve">0.317834943532944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319481760263443</t>
   </si>
   <si>
     <t xml:space="preserve">0.312071084976196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308365762233734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310012549161911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314541310071945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318658322095871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320305168628693</t>
+    <t xml:space="preserve">0.308365792036057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310012578964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314541280269623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318658351898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32030513882637</t>
   </si>
   <si>
     <t xml:space="preserve">0.322775393724442</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">0.30960088968277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309189140796661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321128517389297</t>
+    <t xml:space="preserve">0.309189170598984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321128576993942</t>
   </si>
   <si>
     <t xml:space="preserve">0.321951985359192</t>
@@ -2483,19 +2483,19 @@
     <t xml:space="preserve">0.325245589017868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326892405748367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323187112808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323598802089691</t>
+    <t xml:space="preserve">0.32689243555069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323187083005905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323598772287369</t>
   </si>
   <si>
     <t xml:space="preserve">0.315364718437195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31330618262291</t>
+    <t xml:space="preserve">0.313306212425232</t>
   </si>
   <si>
     <t xml:space="preserve">0.310424298048019</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">0.31742325425148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311659425497055</t>
+    <t xml:space="preserve">0.311659395694733</t>
   </si>
   <si>
     <t xml:space="preserve">0.316188126802444</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">0.319893449544907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30466040968895</t>
+    <t xml:space="preserve">0.304660439491272</t>
   </si>
   <si>
     <t xml:space="preserve">0.30877748131752</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">0.307542324066162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302601903676987</t>
+    <t xml:space="preserve">0.302601933479309</t>
   </si>
   <si>
     <t xml:space="preserve">0.307954072952271</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">0.30095511674881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301366806030273</t>
+    <t xml:space="preserve">0.301366835832596</t>
   </si>
   <si>
     <t xml:space="preserve">0.302190214395523</t>
@@ -2567,10 +2567,7 @@
     <t xml:space="preserve">0.328539222478867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344595670700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340890318155289</t>
+    <t xml:space="preserve">0.340890347957611</t>
   </si>
   <si>
     <t xml:space="preserve">0.356535077095032</t>
@@ -2582,13 +2579,13 @@
     <t xml:space="preserve">0.336361587047577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339243531227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335126459598541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358181834220886</t>
+    <t xml:space="preserve">0.339243501424789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335126489400864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358181864023209</t>
   </si>
   <si>
     <t xml:space="preserve">0.347065895795822</t>
@@ -2603,13 +2600,13 @@
     <t xml:space="preserve">0.345419049263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349124372005463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338008403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335949867963791</t>
+    <t xml:space="preserve">0.349124401807785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338008373975754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335949838161469</t>
   </si>
   <si>
     <t xml:space="preserve">0.343772232532501</t>
@@ -2627,7 +2624,7 @@
     <t xml:space="preserve">0.332244515419006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329362601041794</t>
+    <t xml:space="preserve">0.329362630844116</t>
   </si>
   <si>
     <t xml:space="preserve">0.325657308101654</t>
@@ -2636,19 +2633,19 @@
     <t xml:space="preserve">0.338420122861862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346654176712036</t>
+    <t xml:space="preserve">0.346654146909714</t>
   </si>
   <si>
     <t xml:space="preserve">0.35571163892746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359005242586136</t>
+    <t xml:space="preserve">0.359005272388458</t>
   </si>
   <si>
     <t xml:space="preserve">0.370121240615845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377943634986877</t>
+    <t xml:space="preserve">0.377943605184555</t>
   </si>
   <si>
     <t xml:space="preserve">0.38164895772934</t>
@@ -2660,28 +2657,28 @@
     <t xml:space="preserve">0.395235151052475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399763882160187</t>
+    <t xml:space="preserve">0.399763911962509</t>
   </si>
   <si>
     <t xml:space="preserve">0.38947132229805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401822417974472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411703288555145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402234107255936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403469204902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409644782543182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408409655094147</t>
+    <t xml:space="preserve">0.401822447776794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411703318357468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402234137058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403469234704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40964475274086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408409684896469</t>
   </si>
   <si>
     <t xml:space="preserve">0.40593945980072</t>
@@ -2699,16 +2696,16 @@
     <t xml:space="preserve">0.403880923986435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403057545423508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394823491573334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417467147111893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433111846446991</t>
+    <t xml:space="preserve">0.403057515621185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394823431968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417467176914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433111906051636</t>
   </si>
   <si>
     <t xml:space="preserve">0.430641651153564</t>
@@ -2717,10 +2714,10 @@
     <t xml:space="preserve">0.441345930099487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454520374536514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442992717027664</t>
+    <t xml:space="preserve">0.454520463943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442992746829987</t>
   </si>
   <si>
     <t xml:space="preserve">0.488280117511749</t>
@@ -2729,37 +2726,37 @@
     <t xml:space="preserve">0.50392484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534390866756439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518746078014374</t>
+    <t xml:space="preserve">0.534390926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518746137619019</t>
   </si>
   <si>
     <t xml:space="preserve">0.522039771080017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500631213188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517922818660736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469341784715652</t>
+    <t xml:space="preserve">0.500631153583527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517922759056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469341725111008</t>
   </si>
   <si>
     <t xml:space="preserve">0.485809832811356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462754487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472635328769684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493220567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573691368103</t>
+    <t xml:space="preserve">0.462754458189011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472635388374329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493220508098602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491573810577393</t>
   </si>
   <si>
     <t xml:space="preserve">0.48169282078743</t>
@@ -2768,13 +2765,16 @@
     <t xml:space="preserve">0.467694967985153</t>
   </si>
   <si>
+    <t xml:space="preserve">0.459460943937302</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.461107671260834</t>
   </si>
   <si>
     <t xml:space="preserve">0.476752430200577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47922271490097</t>
+    <t xml:space="preserve">0.479222655296326</t>
   </si>
   <si>
     <t xml:space="preserve">0.477575838565826</t>
@@ -2786,10 +2786,10 @@
     <t xml:space="preserve">0.504748165607452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501454710960388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498984396457672</t>
+    <t xml:space="preserve">0.501454591751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498984456062317</t>
   </si>
   <si>
     <t xml:space="preserve">0.494043946266174</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">0.470988571643829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470165133476257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46522468328476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284292697906</t>
+    <t xml:space="preserve">0.470165193080902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465224713087082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284262895584</t>
   </si>
   <si>
     <t xml:space="preserve">0.468518376350403</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">0.457910388708115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461446404457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464098364114761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454374372959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441114455461502</t>
+    <t xml:space="preserve">0.46144637465477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464098334312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454374402761459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44111442565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.420782536268234</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">0.435810476541519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438462436199188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427412480115891</t>
+    <t xml:space="preserve">0.438462466001511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427412509918213</t>
   </si>
   <si>
     <t xml:space="preserve">0.426528483629227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433158457279205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448186427354813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441998422145844</t>
+    <t xml:space="preserve">0.433158487081528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448186457157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441998451948166</t>
   </si>
   <si>
     <t xml:space="preserve">0.434484452009201</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">0.449070423841476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437578469514847</t>
+    <t xml:space="preserve">0.437578439712524</t>
   </si>
   <si>
     <t xml:space="preserve">0.433600455522537</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">0.430948466062546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431390464305878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434926450252533</t>
+    <t xml:space="preserve">0.4313904941082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434926480054855</t>
   </si>
   <si>
     <t xml:space="preserve">0.429622501134872</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">0.419456511735916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417246490716934</t>
+    <t xml:space="preserve">0.417246520519257</t>
   </si>
   <si>
     <t xml:space="preserve">0.411942541599274</t>
@@ -2936,22 +2936,22 @@
     <t xml:space="preserve">0.41813051700592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42255049943924</t>
+    <t xml:space="preserve">0.422550469636917</t>
   </si>
   <si>
     <t xml:space="preserve">0.413710534572601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425202488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423876523971558</t>
+    <t xml:space="preserve">0.425202518701553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423876464366913</t>
   </si>
   <si>
     <t xml:space="preserve">0.414594531059265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422992497682571</t>
+    <t xml:space="preserve">0.422992527484894</t>
   </si>
   <si>
     <t xml:space="preserve">0.421224534511566</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">0.408406555652618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412384569644928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41105854511261</t>
+    <t xml:space="preserve">0.412384539842606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411058515310287</t>
   </si>
   <si>
     <t xml:space="preserve">0.409732550382614</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">0.407964557409286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423434495925903</t>
+    <t xml:space="preserve">0.423434525728226</t>
   </si>
   <si>
     <t xml:space="preserve">0.420340478420258</t>
@@ -2993,16 +2993,16 @@
     <t xml:space="preserve">0.428296476602554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424760520458221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422108471393585</t>
+    <t xml:space="preserve">0.424760490655899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422108501195908</t>
   </si>
   <si>
     <t xml:space="preserve">0.415478527545929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402218550443649</t>
+    <t xml:space="preserve">0.402218610048294</t>
   </si>
   <si>
     <t xml:space="preserve">0.394262611865997</t>
@@ -3017,40 +3017,40 @@
     <t xml:space="preserve">0.39249461889267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396030634641647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405754566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403544574975967</t>
+    <t xml:space="preserve">0.396030604839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405754536390305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403544545173645</t>
   </si>
   <si>
     <t xml:space="preserve">0.400450587272644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389842659235001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388958603143692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395146608352661</t>
+    <t xml:space="preserve">0.389842629432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388958632946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395146578550339</t>
   </si>
   <si>
     <t xml:space="preserve">0.386748641729355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393378555774689</t>
+    <t xml:space="preserve">0.393378585577011</t>
   </si>
   <si>
     <t xml:space="preserve">0.403102576732635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396914601325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39779856801033</t>
+    <t xml:space="preserve">0.396914571523666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397798597812653</t>
   </si>
   <si>
     <t xml:space="preserve">0.40177658200264</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660578489304</t>
+    <t xml:space="preserve">0.402660548686981</t>
   </si>
   <si>
     <t xml:space="preserve">0.419898509979248</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">0.436694443225861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443766415119171</t>
+    <t xml:space="preserve">0.443766385316849</t>
   </si>
   <si>
     <t xml:space="preserve">0.453789889812469</t>
@@ -3098,10 +3098,10 @@
     <t xml:space="preserve">0.468369513750076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480215430259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482949048280716</t>
+    <t xml:space="preserve">0.480215400457382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482949018478394</t>
   </si>
   <si>
     <t xml:space="preserve">0.481126666069031</t>
@@ -3125,10 +3125,10 @@
     <t xml:space="preserve">0.523042976856232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529421448707581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525776624679565</t>
+    <t xml:space="preserve">0.529421508312225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52577668428421</t>
   </si>
   <si>
     <t xml:space="preserve">0.523954212665558</t>
@@ -3143,40 +3143,40 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753149986267</t>
+    <t xml:space="preserve">0.515753209590912</t>
   </si>
   <si>
     <t xml:space="preserve">0.507552146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511197030544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514841973781586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519398093223572</t>
+    <t xml:space="preserve">0.511197090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514841914176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519398033618927</t>
   </si>
   <si>
     <t xml:space="preserve">0.513930678367615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524865448474884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509374618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526687860488892</t>
+    <t xml:space="preserve">0.524865388870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509374558925629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526687920093536</t>
   </si>
   <si>
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546734809875488</t>
+    <t xml:space="preserve">0.541267454624176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546734869480133</t>
   </si>
   <si>
     <t xml:space="preserve">0.537622511386871</t>
@@ -3197,10 +3197,10 @@
     <t xml:space="preserve">0.569515407085419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562225580215454</t>
+    <t xml:space="preserve">0.565870463848114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562225639820099</t>
   </si>
   <si>
     <t xml:space="preserve">0.551290929317474</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">0.548557281494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550379693508148</t>
+    <t xml:space="preserve">0.550379633903503</t>
   </si>
   <si>
     <t xml:space="preserve">0.547646045684814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555847108364105</t>
+    <t xml:space="preserve">0.55584704875946</t>
   </si>
   <si>
     <t xml:space="preserve">0.553113341331482</t>
@@ -3227,22 +3227,22 @@
     <t xml:space="preserve">0.559491991996765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561314404010773</t>
+    <t xml:space="preserve">0.561314344406128</t>
   </si>
   <si>
     <t xml:space="preserve">0.558580696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556758224964142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542178690433502</t>
+    <t xml:space="preserve">0.556758284568787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542178750038147</t>
   </si>
   <si>
     <t xml:space="preserve">0.557669520378113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534888923168182</t>
+    <t xml:space="preserve">0.534888863563538</t>
   </si>
   <si>
     <t xml:space="preserve">0.528510332107544</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">0.535800099372864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530332803726196</t>
+    <t xml:space="preserve">0.530332744121552</t>
   </si>
   <si>
     <t xml:space="preserve">0.527599096298218</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617466211319</t>
+    <t xml:space="preserve">0.496617496013641</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">0.505729734897614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494794964790344</t>
+    <t xml:space="preserve">0.494794994592667</t>
   </si>
   <si>
     <t xml:space="preserve">0.499351114034653</t>
@@ -3284,16 +3284,16 @@
     <t xml:space="preserve">0.492061376571655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488416492938995</t>
+    <t xml:space="preserve">0.488416433334351</t>
   </si>
   <si>
     <t xml:space="preserve">0.483860343694687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487505227327347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495706290006638</t>
+    <t xml:space="preserve">0.487505257129669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495706230401993</t>
   </si>
   <si>
     <t xml:space="preserve">0.49388375878334</t>
@@ -3930,6 +3930,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.640999972820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621999979019165</t>
   </si>
 </sst>
 </file>
@@ -49630,7 +49633,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1745" t="s">
-        <v>851</v>
+        <v>770</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49656,7 +49659,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1746" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49682,7 +49685,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1747" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49760,7 +49763,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1750" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49786,7 +49789,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G1751" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49812,7 +49815,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1752" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49838,7 +49841,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1753" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49864,7 +49867,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1754" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49890,7 +49893,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1755" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49916,7 +49919,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1756" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49942,7 +49945,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1757" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49968,7 +49971,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1758" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -50020,7 +50023,7 @@
         <v>0.41949999332428</v>
       </c>
       <c r="G1760" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50046,7 +50049,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1761" t="s">
-        <v>851</v>
+        <v>770</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50072,7 +50075,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1762" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50124,7 +50127,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1764" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -50150,7 +50153,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1765" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50176,7 +50179,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1766" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -50202,7 +50205,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1767" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50228,7 +50231,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1768" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -50254,7 +50257,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1769" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -50280,7 +50283,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1770" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50306,7 +50309,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1771" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50358,7 +50361,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1773" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50384,7 +50387,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1774" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50410,7 +50413,7 @@
         <v>0.403499990701675</v>
       </c>
       <c r="G1775" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50462,7 +50465,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1777" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50488,7 +50491,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1778" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50540,7 +50543,7 @@
         <v>0.395500004291534</v>
       </c>
       <c r="G1780" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50592,7 +50595,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1782" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50618,7 +50621,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1783" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50644,7 +50647,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1784" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50670,7 +50673,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1785" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50696,7 +50699,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1786" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50722,7 +50725,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1787" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50774,7 +50777,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1789" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50800,7 +50803,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1790" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50826,7 +50829,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1791" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50852,7 +50855,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1792" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50904,7 +50907,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50930,7 +50933,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1795" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50956,7 +50959,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1796" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50982,7 +50985,7 @@
         <v>0.449499994516373</v>
       </c>
       <c r="G1797" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51008,7 +51011,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G1798" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51034,7 +51037,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1799" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51060,7 +51063,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G1800" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -51086,7 +51089,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1801" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -51112,7 +51115,7 @@
         <v>0.485500007867813</v>
       </c>
       <c r="G1802" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -51138,7 +51141,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1803" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51164,7 +51167,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1804" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -51190,7 +51193,7 @@
         <v>0.5</v>
       </c>
       <c r="G1805" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -51216,7 +51219,7 @@
         <v>0.488499999046326</v>
       </c>
       <c r="G1806" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51242,7 +51245,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -51268,7 +51271,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G1808" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51294,7 +51297,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1809" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51320,7 +51323,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1810" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51346,7 +51349,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1811" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51372,7 +51375,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1812" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51398,7 +51401,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1813" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51424,7 +51427,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1814" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51450,7 +51453,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1815" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51476,7 +51479,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1816" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51502,7 +51505,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1817" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51528,7 +51531,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1818" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51554,7 +51557,7 @@
         <v>0.489499986171722</v>
       </c>
       <c r="G1819" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51580,7 +51583,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1820" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51606,7 +51609,7 @@
         <v>0.5</v>
       </c>
       <c r="G1821" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51632,7 +51635,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1822" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51658,7 +51661,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1823" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51684,7 +51687,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1824" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51710,7 +51713,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1825" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51736,7 +51739,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1826" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51762,7 +51765,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1827" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51788,7 +51791,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G1828" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51814,7 +51817,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1829" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51840,7 +51843,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G1830" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51866,7 +51869,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1831" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51892,7 +51895,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1832" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51918,7 +51921,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1833" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51944,7 +51947,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G1834" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51970,7 +51973,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1835" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51996,7 +51999,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1836" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52022,7 +52025,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1837" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52048,7 +52051,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1838" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -52074,7 +52077,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1839" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -52100,7 +52103,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1840" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52126,7 +52129,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G1841" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52152,7 +52155,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1842" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52178,7 +52181,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1843" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52204,7 +52207,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1844" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52230,7 +52233,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1845" t="s">
-        <v>363</v>
+        <v>917</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52308,7 +52311,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1848" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52412,7 +52415,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1852" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52802,7 +52805,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1867" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52854,7 +52857,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1869" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52906,7 +52909,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1871" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52958,7 +52961,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1873" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53036,7 +53039,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>363</v>
+        <v>917</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -68904,7 +68907,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6496875</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>1522410</v>
@@ -68925,6 +68928,32 @@
         <v>1305</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6494907407</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>1605501</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>0.621999979019165</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>0.640999972820282</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>0.621999979019165</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="1309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="1310">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,76 +38,76 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333736211061478</t>
+    <t xml:space="preserve">0.333736151456833</t>
   </si>
   <si>
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327446222305298</t>
+    <t xml:space="preserve">0.32744625210762</t>
   </si>
   <si>
     <t xml:space="preserve">0.321156322956085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317678391933441</t>
+    <t xml:space="preserve">0.317678332328796</t>
   </si>
   <si>
     <t xml:space="preserve">0.307318478822708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288448691368103</t>
+    <t xml:space="preserve">0.288448721170425</t>
   </si>
   <si>
     <t xml:space="preserve">0.289336711168289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294368624687195</t>
+    <t xml:space="preserve">0.294368594884872</t>
   </si>
   <si>
     <t xml:space="preserve">0.285636752843857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796856403351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258996993303299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258257061243057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243605211377144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246417179703712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262697011232376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256407111883163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259811013936996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261513024568558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253817051649094</t>
+    <t xml:space="preserve">0.273796886205673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258997023105621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258257031440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243605226278305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246417194604874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262696951627731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256407052278519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259811043739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261512964963913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253817111253738</t>
   </si>
   <si>
     <t xml:space="preserve">0.25307708978653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286894738674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284600764513016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277496844530106</t>
+    <t xml:space="preserve">0.286894679069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284600734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277496814727783</t>
   </si>
   <si>
     <t xml:space="preserve">0.287116706371307</t>
@@ -119,31 +119,31 @@
     <t xml:space="preserve">0.263806998729706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256777077913284</t>
+    <t xml:space="preserve">0.256777048110962</t>
   </si>
   <si>
     <t xml:space="preserve">0.250117152929306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277570843696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297994643449783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310796439647675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303544521331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304358512163162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318122357130051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309686452150345</t>
+    <t xml:space="preserve">0.277570784091949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297994583845139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310796409845352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303544491529465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304358541965485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318122386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309686481952667</t>
   </si>
   <si>
     <t xml:space="preserve">0.301620543003082</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">0.316716372966766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315236419439316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315606385469437</t>
+    <t xml:space="preserve">0.315236389636993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315606415271759</t>
   </si>
   <si>
     <t xml:space="preserve">0.332996189594269</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">0.330480217933655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311240404844284</t>
+    <t xml:space="preserve">0.311240434646606</t>
   </si>
   <si>
     <t xml:space="preserve">0.312054425477982</t>
@@ -194,22 +194,22 @@
     <t xml:space="preserve">0.299400568008423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297476559877396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295996636152267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293702661991119</t>
+    <t xml:space="preserve">0.297476589679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295996606349945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293702632188797</t>
   </si>
   <si>
     <t xml:space="preserve">0.298216581344604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286376714706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276756852865219</t>
+    <t xml:space="preserve">0.286376684904099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276756793260574</t>
   </si>
   <si>
     <t xml:space="preserve">0.274536848068237</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">0.268542915582657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270466893911362</t>
+    <t xml:space="preserve">0.270466923713684</t>
   </si>
   <si>
     <t xml:space="preserve">0.265064984560013</t>
@@ -230,31 +230,31 @@
     <t xml:space="preserve">0.268172949552536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268616944551468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269208878278732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275276839733124</t>
+    <t xml:space="preserve">0.268616914749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269208908081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275276869535446</t>
   </si>
   <si>
     <t xml:space="preserve">0.284896731376648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290002644062042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308206498622894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309168487787247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318196326494217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316938370466232</t>
+    <t xml:space="preserve">0.290002703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308206468820572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309168457984924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318196386098862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31693834066391</t>
   </si>
   <si>
     <t xml:space="preserve">0.308946460485458</t>
@@ -263,28 +263,28 @@
     <t xml:space="preserve">0.314200401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321378320455551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319380313158035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722410678864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313682377338409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313312411308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307096511125565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30761444568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304950505495071</t>
+    <t xml:space="preserve">0.321378290653229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31938037276268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722440481186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313682436943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313312441110611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307096481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307614475488663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304950475692749</t>
   </si>
   <si>
     <t xml:space="preserve">0.305616468191147</t>
@@ -293,16 +293,16 @@
     <t xml:space="preserve">0.2995485663414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305320531129837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295626640319824</t>
+    <t xml:space="preserve">0.305320501327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295626610517502</t>
   </si>
   <si>
     <t xml:space="preserve">0.300954550504684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314400345087051</t>
+    <t xml:space="preserve">0.314400315284729</t>
   </si>
   <si>
     <t xml:space="preserve">0.318779796361923</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.319932252168655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318088322877884</t>
+    <t xml:space="preserve">0.318088293075562</t>
   </si>
   <si>
     <t xml:space="preserve">0.307331681251526</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">0.305795013904572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301569253206253</t>
+    <t xml:space="preserve">0.301569223403931</t>
   </si>
   <si>
     <t xml:space="preserve">0.295806735754013</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">0.299648344516754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296575099229813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303490042686462</t>
+    <t xml:space="preserve">0.29657506942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303490072488785</t>
   </si>
   <si>
     <t xml:space="preserve">0.314246654510498</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">0.310020834207535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311941683292389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311173319816589</t>
+    <t xml:space="preserve">0.311941653490067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311173349618912</t>
   </si>
   <si>
     <t xml:space="preserve">0.30725485086441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306716978549957</t>
+    <t xml:space="preserve">0.30671700835228</t>
   </si>
   <si>
     <t xml:space="preserve">0.305564522743225</t>
@@ -386,31 +386,31 @@
     <t xml:space="preserve">0.306870669126511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297727555036545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301799714565277</t>
+    <t xml:space="preserve">0.297727584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301799684762955</t>
   </si>
   <si>
     <t xml:space="preserve">0.304027885198593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300032556056976</t>
+    <t xml:space="preserve">0.300032585859299</t>
   </si>
   <si>
     <t xml:space="preserve">0.313478320837021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31255629658699</t>
+    <t xml:space="preserve">0.312556326389313</t>
   </si>
   <si>
     <t xml:space="preserve">0.307869523763657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311480700969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298265397548676</t>
+    <t xml:space="preserve">0.311480671167374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298265367746353</t>
   </si>
   <si>
     <t xml:space="preserve">0.299110531806946</t>
@@ -425,37 +425,37 @@
     <t xml:space="preserve">0.295960396528244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297650694847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297881245613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29373225569725</t>
+    <t xml:space="preserve">0.297650724649429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297881215810776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293732225894928</t>
   </si>
   <si>
     <t xml:space="preserve">0.298803240060806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300416767597198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300109416246414</t>
+    <t xml:space="preserve">0.300416737794876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300109386444092</t>
   </si>
   <si>
     <t xml:space="preserve">0.298880040645599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30548769235611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30955982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303105860948563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303566843271255</t>
+    <t xml:space="preserve">0.305487662553787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309559881687164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303105890750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303566873073578</t>
   </si>
   <si>
     <t xml:space="preserve">0.308253675699234</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.306563347578049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300186216831207</t>
+    <t xml:space="preserve">0.30018624663353</t>
   </si>
   <si>
     <t xml:space="preserve">0.298649579286575</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">0.29196509718895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289736956357956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293501734733582</t>
+    <t xml:space="preserve">0.289736926555634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293501704931259</t>
   </si>
   <si>
     <t xml:space="preserve">0.292656600475311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29250293970108</t>
+    <t xml:space="preserve">0.292502909898758</t>
   </si>
   <si>
     <t xml:space="preserve">0.289583265781403</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">0.288123458623886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284281820058823</t>
+    <t xml:space="preserve">0.284281849861145</t>
   </si>
   <si>
     <t xml:space="preserve">0.287892997264862</t>
@@ -515,28 +515,28 @@
     <t xml:space="preserve">0.290044277906418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292887091636658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293117582798004</t>
+    <t xml:space="preserve">0.292887061834335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293117612600327</t>
   </si>
   <si>
     <t xml:space="preserve">0.291888266801834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289813786745071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286586791276932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294270098209381</t>
+    <t xml:space="preserve">0.289813756942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286586850881577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294270068407059</t>
   </si>
   <si>
     <t xml:space="preserve">0.291811406612396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292579799890518</t>
+    <t xml:space="preserve">0.292579770088196</t>
   </si>
   <si>
     <t xml:space="preserve">0.29572993516922</t>
@@ -545,34 +545,34 @@
     <t xml:space="preserve">0.298419058322906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294731080532074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287355154752731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293809115886688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292041927576065</t>
+    <t xml:space="preserve">0.294731050729752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287355124950409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293809086084366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292041957378387</t>
   </si>
   <si>
     <t xml:space="preserve">0.286740452051163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2846659719944</t>
+    <t xml:space="preserve">0.284665942192078</t>
   </si>
   <si>
     <t xml:space="preserve">0.278903514146805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275599658489227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270221412181854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27244958281517</t>
+    <t xml:space="preserve">0.27559968829155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270221382379532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272449553012848</t>
   </si>
   <si>
     <t xml:space="preserve">0.276675343513489</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">0.27398619055748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275676518678665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275522857904434</t>
+    <t xml:space="preserve">0.275676548480988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275522828102112</t>
   </si>
   <si>
     <t xml:space="preserve">0.276598513126373</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">0.270989686250687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271143406629562</t>
+    <t xml:space="preserve">0.27114337682724</t>
   </si>
   <si>
     <t xml:space="preserve">0.274293512105942</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">0.267378568649292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264612585306168</t>
+    <t xml:space="preserve">0.264612555503845</t>
   </si>
   <si>
     <t xml:space="preserve">0.265765100717545</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">0.265304088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271911710500717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272526353597641</t>
+    <t xml:space="preserve">0.271911680698395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272526383399963</t>
   </si>
   <si>
     <t xml:space="preserve">0.283282995223999</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">0.279902338981628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277059525251389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27844250202179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280517041683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278749823570251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27898034453392</t>
+    <t xml:space="preserve">0.277059555053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278442531824112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280517011880875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278749853372574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278980314731598</t>
   </si>
   <si>
     <t xml:space="preserve">0.278212010860443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284051328897476</t>
+    <t xml:space="preserve">0.284051299095154</t>
   </si>
   <si>
     <t xml:space="preserve">0.290812611579895</t>
@@ -662,25 +662,25 @@
     <t xml:space="preserve">0.28966012597084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290428459644318</t>
+    <t xml:space="preserve">0.290428429841995</t>
   </si>
   <si>
     <t xml:space="preserve">0.294807940721512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295422613620758</t>
+    <t xml:space="preserve">0.295422583818436</t>
   </si>
   <si>
     <t xml:space="preserve">0.288507610559464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284589141607285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291043132543564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293885916471481</t>
+    <t xml:space="preserve">0.284589171409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291043072938919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293885946273804</t>
   </si>
   <si>
     <t xml:space="preserve">0.294884741306305</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">0.289890617132187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286125779151917</t>
+    <t xml:space="preserve">0.286125808954239</t>
   </si>
   <si>
     <t xml:space="preserve">0.284358650445938</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">0.282745122909546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277290046215057</t>
+    <t xml:space="preserve">0.277290016412735</t>
   </si>
   <si>
     <t xml:space="preserve">0.281976819038391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276214301586151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273602038621902</t>
+    <t xml:space="preserve">0.276214331388474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27360200881958</t>
   </si>
   <si>
     <t xml:space="preserve">0.269760370254517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275061845779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271834880113602</t>
+    <t xml:space="preserve">0.275061875581741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271834850311279</t>
   </si>
   <si>
     <t xml:space="preserve">0.273371547460556</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">0.275215566158295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276905834674835</t>
+    <t xml:space="preserve">0.276905864477158</t>
   </si>
   <si>
     <t xml:space="preserve">0.274831354618073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282668322324753</t>
+    <t xml:space="preserve">0.28266829252243</t>
   </si>
   <si>
     <t xml:space="preserve">0.280440181493759</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">0.279595017433167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27736684679985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278135150671005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281208485364914</t>
+    <t xml:space="preserve">0.277366816997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278135180473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281208515167236</t>
   </si>
   <si>
     <t xml:space="preserve">0.278672963380814</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">0.282591491937637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279364496469498</t>
+    <t xml:space="preserve">0.27936452627182</t>
   </si>
   <si>
     <t xml:space="preserve">0.285587936639786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27967181801796</t>
+    <t xml:space="preserve">0.279671847820282</t>
   </si>
   <si>
     <t xml:space="preserve">0.286663681268692</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">0.281899988651276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283897697925568</t>
+    <t xml:space="preserve">0.283897668123245</t>
   </si>
   <si>
     <t xml:space="preserve">0.285280615091324</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">0.304258346557617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321929901838303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325617909431458</t>
+    <t xml:space="preserve">0.321929931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32561793923378</t>
   </si>
   <si>
     <t xml:space="preserve">0.331841379404068</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">0.325387448072433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316935777664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309790313243866</t>
+    <t xml:space="preserve">0.316935807466507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309790343046188</t>
   </si>
   <si>
     <t xml:space="preserve">0.309252500534058</t>
@@ -812,25 +812,25 @@
     <t xml:space="preserve">0.311096489429474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313094168901443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313017308712006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288891762495041</t>
+    <t xml:space="preserve">0.313094139099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313017338514328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288891792297363</t>
   </si>
   <si>
     <t xml:space="preserve">0.293040752410889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295192062854767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296805530786514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297266602516174</t>
+    <t xml:space="preserve">0.295192092657089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296805560588837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297266572713852</t>
   </si>
   <si>
     <t xml:space="preserve">0.298111736774445</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">0.310251325368881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313555181026459</t>
+    <t xml:space="preserve">0.313555151224136</t>
   </si>
   <si>
     <t xml:space="preserve">0.300800889730453</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">0.299725204706192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321853131055832</t>
+    <t xml:space="preserve">0.32185310125351</t>
   </si>
   <si>
     <t xml:space="preserve">0.327308237552643</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">0.314016133546829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315014988183975</t>
+    <t xml:space="preserve">0.315014958381653</t>
   </si>
   <si>
     <t xml:space="preserve">0.312249004840851</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">0.313939332962036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309636622667313</t>
+    <t xml:space="preserve">0.309636652469635</t>
   </si>
   <si>
     <t xml:space="preserve">0.307408541440964</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">0.308945178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313631951808929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308023184537888</t>
+    <t xml:space="preserve">0.313631981611252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30802321434021</t>
   </si>
   <si>
     <t xml:space="preserve">0.307715862989426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309022039175034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309943974018097</t>
+    <t xml:space="preserve">0.309021979570389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309944003820419</t>
   </si>
   <si>
     <t xml:space="preserve">0.3177809715271</t>
@@ -905,28 +905,28 @@
     <t xml:space="preserve">0.316551625728607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316474825143814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324388563632965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325003236532211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318318784236908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317704141139984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32154580950737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320470094680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621464729309</t>
+    <t xml:space="preserve">0.316474765539169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324388593435287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325003266334534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318318754434586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317704111337662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321545779705048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320470124483109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621405124664</t>
   </si>
   <si>
     <t xml:space="preserve">0.323697060346603</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">0.333454877138138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327385067939758</t>
+    <t xml:space="preserve">0.327385038137436</t>
   </si>
   <si>
     <t xml:space="preserve">0.331764549016953</t>
@@ -950,16 +950,16 @@
     <t xml:space="preserve">0.340446710586548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333378046751022</t>
+    <t xml:space="preserve">0.3333780169487</t>
   </si>
   <si>
     <t xml:space="preserve">0.334991544485092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336144059896469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337757498025894</t>
+    <t xml:space="preserve">0.336144030094147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337757527828217</t>
   </si>
   <si>
     <t xml:space="preserve">0.338910013437271</t>
@@ -980,19 +980,19 @@
     <t xml:space="preserve">0.344211488962173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340677171945572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334607362747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338218539953232</t>
+    <t xml:space="preserve">0.34067714214325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33460733294487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338218510150909</t>
   </si>
   <si>
     <t xml:space="preserve">0.346900641918182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346132308244705</t>
+    <t xml:space="preserve">0.346132338047028</t>
   </si>
   <si>
     <t xml:space="preserve">0.33960148692131</t>
@@ -1004,25 +1004,25 @@
     <t xml:space="preserve">0.352663099765778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369950532913208</t>
+    <t xml:space="preserve">0.369950503110886</t>
   </si>
   <si>
     <t xml:space="preserve">0.36541736125946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363035529851913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374099463224411</t>
+    <t xml:space="preserve">0.363035559654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374099493026733</t>
   </si>
   <si>
     <t xml:space="preserve">0.371103048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369566321372986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368797987699509</t>
+    <t xml:space="preserve">0.369566380977631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368798017501831</t>
   </si>
   <si>
     <t xml:space="preserve">0.366108864545822</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">0.366262525320053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361114740371704</t>
+    <t xml:space="preserve">0.361114770174026</t>
   </si>
   <si>
     <t xml:space="preserve">0.359885424375534</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">0.35919389128685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368567496538162</t>
+    <t xml:space="preserve">0.368567526340485</t>
   </si>
   <si>
     <t xml:space="preserve">0.372025012969971</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">0.380246102809906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392616212368011</t>
+    <t xml:space="preserve">0.392616182565689</t>
   </si>
   <si>
     <t xml:space="preserve">0.405677825212479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421044409275055</t>
+    <t xml:space="preserve">0.4210444688797</t>
   </si>
   <si>
     <t xml:space="preserve">0.419507741928101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396842032670975</t>
+    <t xml:space="preserve">0.39684209227562</t>
   </si>
   <si>
     <t xml:space="preserve">0.413361132144928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422581106424332</t>
+    <t xml:space="preserve">0.422581076622009</t>
   </si>
   <si>
     <t xml:space="preserve">0.417586922645569</t>
@@ -1088,37 +1088,37 @@
     <t xml:space="preserve">0.42642268538475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423349410295486</t>
+    <t xml:space="preserve">0.423349380493164</t>
   </si>
   <si>
     <t xml:space="preserve">0.427959352731705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436795175075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4329534471035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452930122613907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460824728012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465223282575607</t>
+    <t xml:space="preserve">0.436795204877853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432953476905823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452930092811584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460854530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46522331237793</t>
   </si>
   <si>
     <t xml:space="preserve">0.468296617269516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481358289718628</t>
+    <t xml:space="preserve">0.481358259916306</t>
   </si>
   <si>
     <t xml:space="preserve">0.522463917732239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515164732933044</t>
+    <t xml:space="preserve">0.5151646733284</t>
   </si>
   <si>
     <t xml:space="preserve">0.505560576915741</t>
@@ -1127,31 +1127,31 @@
     <t xml:space="preserve">0.50709730386734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515548884868622</t>
+    <t xml:space="preserve">0.515548944473267</t>
   </si>
   <si>
     <t xml:space="preserve">0.503255605697632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48980987071991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480205774307251</t>
+    <t xml:space="preserve">0.489809811115265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480205744504929</t>
   </si>
   <si>
     <t xml:space="preserve">0.519006371498108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511323034763336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499414056539536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491730690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484431535005569</t>
+    <t xml:space="preserve">0.511323094367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499413967132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491730660200119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484431564807892</t>
   </si>
   <si>
     <t xml:space="preserve">0.483663260936737</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">0.484815716743469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49518820643425</t>
+    <t xml:space="preserve">0.495188176631927</t>
   </si>
   <si>
     <t xml:space="preserve">0.490194022655487</t>
@@ -1175,31 +1175,31 @@
     <t xml:space="preserve">0.56280118227005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586235165596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600065112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58239358663559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572021126747131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572789490222931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552428603172302</t>
+    <t xml:space="preserve">0.586235225200653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600065171718597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582393527030945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572021067142487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572789430618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552428662776947</t>
   </si>
   <si>
     <t xml:space="preserve">0.55127626657486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545129597187042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565874457359314</t>
+    <t xml:space="preserve">0.545129656791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565874516963959</t>
   </si>
   <si>
     <t xml:space="preserve">0.577015221118927</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">0.584698498249054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608132541179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621962487697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620425879955292</t>
+    <t xml:space="preserve">0.608132481575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621962547302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620425820350647</t>
   </si>
   <si>
     <t xml:space="preserve">0.629645824432373</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">0.614279210567474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60774838924408</t>
+    <t xml:space="preserve">0.607748448848724</t>
   </si>
   <si>
     <t xml:space="preserve">0.58162522315979</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">0.560880362987518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598528385162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598144292831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619657635688782</t>
+    <t xml:space="preserve">0.598528444766998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598144352436066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619657576084137</t>
   </si>
   <si>
     <t xml:space="preserve">0.618120849132538</t>
@@ -1250,19 +1250,19 @@
     <t xml:space="preserve">0.601601779460907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58661937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59545511007309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587771832942963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584314465522766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577399432659149</t>
+    <t xml:space="preserve">0.586619257926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595455169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587771892547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584314405918121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577399373054504</t>
   </si>
   <si>
     <t xml:space="preserve">0.567026913166046</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">0.564721941947937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.563185214996338</t>
+    <t xml:space="preserve">0.563185274600983</t>
   </si>
   <si>
     <t xml:space="preserve">0.576246917247772</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">0.583930194377899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580856919288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587003469467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604674994945526</t>
+    <t xml:space="preserve">0.58085685968399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587003409862518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604675114154816</t>
   </si>
   <si>
     <t xml:space="preserve">0.629261612892151</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">0.618505001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606980085372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603138506412506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612358391284943</t>
+    <t xml:space="preserve">0.60698014497757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603138446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612358450889587</t>
   </si>
   <si>
     <t xml:space="preserve">0.611590027809143</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">0.59391850233078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596991837024689</t>
+    <t xml:space="preserve">0.596991777420044</t>
   </si>
   <si>
     <t xml:space="preserve">0.608516693115234</t>
@@ -1325,16 +1325,16 @@
     <t xml:space="preserve">0.599296689033508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589308559894562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553965449333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538598716259003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557038724422455</t>
+    <t xml:space="preserve">0.589308500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553965389728546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538598656654358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5570387840271</t>
   </si>
   <si>
     <t xml:space="preserve">0.536293745040894</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">0.537830412387848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547818779945374</t>
+    <t xml:space="preserve">0.547818720340729</t>
   </si>
   <si>
     <t xml:space="preserve">0.532452166080475</t>
@@ -1361,19 +1361,19 @@
     <t xml:space="preserve">0.52092719078064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517853856086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525537192821503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530147135257721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523232161998749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519390642642975</t>
+    <t xml:space="preserve">0.517853915691376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525537133216858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530147194862366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523232221603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51939058303833</t>
   </si>
   <si>
     <t xml:space="preserve">0.524768948554993</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">0.501718997955322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492498993873596</t>
+    <t xml:space="preserve">0.492499023675919</t>
   </si>
   <si>
     <t xml:space="preserve">0.477900803089142</t>
@@ -1394,43 +1394,43 @@
     <t xml:space="preserve">0.476364135742188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488657385110855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471754103899002</t>
+    <t xml:space="preserve">0.488657414913177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471754163503647</t>
   </si>
   <si>
     <t xml:space="preserve">0.472522437572479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468680769205093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487120717763901</t>
+    <t xml:space="preserve">0.468680799007416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487120777368546</t>
   </si>
   <si>
     <t xml:space="preserve">0.481742411851883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480974018573761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48327910900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478669077157974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470217496156693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467912524938583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466375797986984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839190244675</t>
+    <t xml:space="preserve">0.480974107980728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483279049396515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478669106960297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47021746635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467912554740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466375827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839220046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.461765885353088</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">0.500182330608368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469449192285538</t>
+    <t xml:space="preserve">0.469449132680893</t>
   </si>
   <si>
     <t xml:space="preserve">0.437179356813431</t>
@@ -1457,10 +1457,10 @@
     <t xml:space="preserve">0.444094270467758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424117714166641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415666133165359</t>
+    <t xml:space="preserve">0.424117684364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415666162967682</t>
   </si>
   <si>
     <t xml:space="preserve">0.382627934217453</t>
@@ -1481,25 +1481,25 @@
     <t xml:space="preserve">0.391847878694534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38416463136673</t>
+    <t xml:space="preserve">0.384164601564407</t>
   </si>
   <si>
     <t xml:space="preserve">0.37648132443428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367261379957199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36495640873909</t>
+    <t xml:space="preserve">0.367261350154877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364956378936768</t>
   </si>
   <si>
     <t xml:space="preserve">0.360346406698227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3522789478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356504738330841</t>
+    <t xml:space="preserve">0.352278977632523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356504708528519</t>
   </si>
   <si>
     <t xml:space="preserve">0.37148717045784</t>
@@ -1508,22 +1508,22 @@
     <t xml:space="preserve">0.368029713630676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372255474328995</t>
+    <t xml:space="preserve">0.372255504131317</t>
   </si>
   <si>
     <t xml:space="preserve">0.365340530872345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374944657087326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3664930164814</t>
+    <t xml:space="preserve">0.374944686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366493046283722</t>
   </si>
   <si>
     <t xml:space="preserve">0.374560505151749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374176293611526</t>
+    <t xml:space="preserve">0.374176323413849</t>
   </si>
   <si>
     <t xml:space="preserve">0.37878629565239</t>
@@ -1535,34 +1535,34 @@
     <t xml:space="preserve">0.353815644979477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354583919048309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353047281503677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370718866586685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354199796915054</t>
+    <t xml:space="preserve">0.354583948850632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353047311306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370718836784363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35419973731041</t>
   </si>
   <si>
     <t xml:space="preserve">0.39568954706192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411056190729141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40798282623291</t>
+    <t xml:space="preserve">0.411056160926819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407982856035233</t>
   </si>
   <si>
     <t xml:space="preserve">0.384932905435562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39031121134758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378018021583557</t>
+    <t xml:space="preserve">0.390311241149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378017961978912</t>
   </si>
   <si>
     <t xml:space="preserve">0.380707114934921</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">0.35957807302475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353431463241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349589794874191</t>
+    <t xml:space="preserve">0.353431433439255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349589824676514</t>
   </si>
   <si>
     <t xml:space="preserve">0.344979822635651</t>
@@ -1586,16 +1586,16 @@
     <t xml:space="preserve">0.343059003353119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354968100786209</t>
+    <t xml:space="preserve">0.354968130588531</t>
   </si>
   <si>
     <t xml:space="preserve">0.36418804526329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357273101806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349973946809769</t>
+    <t xml:space="preserve">0.357273072004318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349973976612091</t>
   </si>
   <si>
     <t xml:space="preserve">0.339217334985733</t>
@@ -1610,13 +1610,13 @@
     <t xml:space="preserve">0.350742280483246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389542937278748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404141157865524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396457880735397</t>
+    <t xml:space="preserve">0.389542907476425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404141187667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396457850933075</t>
   </si>
   <si>
     <t xml:space="preserve">0.412592798471451</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">0.397994548082352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375712960958481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.364572256803513</t>
+    <t xml:space="preserve">0.375712990760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364572197198868</t>
   </si>
   <si>
     <t xml:space="preserve">0.345748126506805</t>
@@ -1655,25 +1655,25 @@
     <t xml:space="preserve">0.336528182029724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335759907960892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337296515703201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329613268375397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328076541423798</t>
+    <t xml:space="preserve">0.335759878158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337296485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329613238573074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32807657122612</t>
   </si>
   <si>
     <t xml:space="preserve">0.331534057855606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319240808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326924055814743</t>
+    <t xml:space="preserve">0.319240778684616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326924085617065</t>
   </si>
   <si>
     <t xml:space="preserve">0.312709987163544</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">0.322698265314102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326155751943588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324619114398956</t>
+    <t xml:space="preserve">0.326155722141266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324619084596634</t>
   </si>
   <si>
     <t xml:space="preserve">0.325771570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330381572246552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329997420310974</t>
+    <t xml:space="preserve">0.330381602048874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329997390508652</t>
   </si>
   <si>
     <t xml:space="preserve">0.324234962463379</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">0.301185041666031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30387419462204</t>
+    <t xml:space="preserve">0.303874224424362</t>
   </si>
   <si>
     <t xml:space="preserve">0.29695925116539</t>
@@ -1721,22 +1721,22 @@
     <t xml:space="preserve">0.32308241724968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308100044727325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310404986143112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306947529315948</t>
+    <t xml:space="preserve">0.308100014925003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310405015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306947499513626</t>
   </si>
   <si>
     <t xml:space="preserve">0.314630806446075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305410861968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30848416686058</t>
+    <t xml:space="preserve">0.305410891771317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308484196662903</t>
   </si>
   <si>
     <t xml:space="preserve">0.304642528295517</t>
@@ -1748,37 +1748,37 @@
     <t xml:space="preserve">0.356888920068741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358041375875473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356120556592941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360730588436127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358809769153595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351126432418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355736434459686</t>
+    <t xml:space="preserve">0.358041405677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356120586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360730558633804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358809739351273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351126462221146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355736464262009</t>
   </si>
   <si>
     <t xml:space="preserve">0.342290669679642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371871381998062</t>
+    <t xml:space="preserve">0.37187135219574</t>
   </si>
   <si>
     <t xml:space="preserve">0.370334684848785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383780419826508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376097172498703</t>
+    <t xml:space="preserve">0.38378044962883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376097142696381</t>
   </si>
   <si>
     <t xml:space="preserve">0.376865476369858</t>
@@ -1799,28 +1799,28 @@
     <t xml:space="preserve">0.409519463777542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391079545021057</t>
+    <t xml:space="preserve">0.39107957482338</t>
   </si>
   <si>
     <t xml:space="preserve">0.381475448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407214462757111</t>
+    <t xml:space="preserve">0.407214432954788</t>
   </si>
   <si>
     <t xml:space="preserve">0.387237936258316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394921243190765</t>
+    <t xml:space="preserve">0.394921213388443</t>
   </si>
   <si>
     <t xml:space="preserve">0.411824434995651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41489776968956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417202740907669</t>
+    <t xml:space="preserve">0.414897799491882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417202711105347</t>
   </si>
   <si>
     <t xml:space="preserve">0.397226184606552</t>
@@ -1829,88 +1829,88 @@
     <t xml:space="preserve">0.408751159906387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410287797451019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414129436016083</t>
+    <t xml:space="preserve">0.410287827253342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41412940621376</t>
   </si>
   <si>
     <t xml:space="preserve">0.416434437036514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418739408254623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420276075601578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42181271314621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430264383554459</t>
+    <t xml:space="preserve">0.418739438056946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4202761054039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421812742948532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430264353752136</t>
   </si>
   <si>
     <t xml:space="preserve">0.473290771245956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494803994894028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484047383069992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267327547073</t>
+    <t xml:space="preserve">0.494803965091705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484047412872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267387151718</t>
   </si>
   <si>
     <t xml:space="preserve">0.506328940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479437410831451</t>
+    <t xml:space="preserve">0.479437470436096</t>
   </si>
   <si>
     <t xml:space="preserve">0.482510805130005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475595772266388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070856571198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465607523918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460997521877289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453314244747162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434106022119522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789269447327</t>
+    <t xml:space="preserve">0.475595742464066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465607553720474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460997551679611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453314274549484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434105962514877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789239645004</t>
   </si>
   <si>
     <t xml:space="preserve">0.445630967617035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449472606182098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451009213924408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460229188203812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454082548618317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457155913114548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451777577400208</t>
+    <t xml:space="preserve">0.449472576379776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45100924372673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460229218006134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454082578420639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45715594291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45177760720253</t>
   </si>
   <si>
     <t xml:space="preserve">0.456387549638748</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">0.463302493095398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470985800027847</t>
+    <t xml:space="preserve">0.470985740423203</t>
   </si>
   <si>
     <t xml:space="preserve">0.467144161462784</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">0.447167575359344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432569324970245</t>
+    <t xml:space="preserve">0.432569354772568</t>
   </si>
   <si>
     <t xml:space="preserve">0.437947660684586</t>
@@ -1943,22 +1943,22 @@
     <t xml:space="preserve">0.434874355792999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436410963535309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439484298229218</t>
+    <t xml:space="preserve">0.436410933732986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43948432803154</t>
   </si>
   <si>
     <t xml:space="preserve">0.441020965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440252721309662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438715934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442557603120804</t>
+    <t xml:space="preserve">0.440252661705017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43871596455574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442557632923126</t>
   </si>
   <si>
     <t xml:space="preserve">0.485584050416946</t>
@@ -1976,55 +1976,55 @@
     <t xml:space="preserve">0.435642659664154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450240939855576</t>
+    <t xml:space="preserve">0.450240969657898</t>
   </si>
   <si>
     <t xml:space="preserve">0.427191019058228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375328838825226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386469602584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393384575843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365724712610245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372639656066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351510584354401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342674851417542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317319929599762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26507356762886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259695321321487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.239334538578987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242023691534996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234724596142769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245865345001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258926928043365</t>
+    <t xml:space="preserve">0.375328809022903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386469572782516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393384605646133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365724742412567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372639685869217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351510614156723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342674821615219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317319959402084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265073597431183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259695291519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239334553480148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242023706436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234724566340446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24586533010006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258926957845688</t>
   </si>
   <si>
     <t xml:space="preserve">0.251627802848816</t>
@@ -2033,16 +2033,16 @@
     <t xml:space="preserve">0.266610234975815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269299358129501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258158624172211</t>
+    <t xml:space="preserve">0.269299328327179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258158594369888</t>
   </si>
   <si>
     <t xml:space="preserve">0.251243650913239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252011984586716</t>
+    <t xml:space="preserve">0.252011954784393</t>
   </si>
   <si>
     <t xml:space="preserve">0.242407858371735</t>
@@ -2051,34 +2051,34 @@
     <t xml:space="preserve">0.245097011327744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254701137542725</t>
+    <t xml:space="preserve">0.254701107740402</t>
   </si>
   <si>
     <t xml:space="preserve">0.262000232934952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254316985607147</t>
+    <t xml:space="preserve">0.254316955804825</t>
   </si>
   <si>
     <t xml:space="preserve">0.261231958866119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262768596410751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264689385890961</t>
+    <t xml:space="preserve">0.262768566608429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264689445495605</t>
   </si>
   <si>
     <t xml:space="preserve">0.271988540887833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273909389972687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276982724666595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27275687456131</t>
+    <t xml:space="preserve">0.273909360170364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276982694864273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272756844758987</t>
   </si>
   <si>
     <t xml:space="preserve">0.275445997714996</t>
@@ -2087,28 +2087,28 @@
     <t xml:space="preserve">0.268915206193924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26584193110466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258542746305466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26545774936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263152748346329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292733401060104</t>
+    <t xml:space="preserve">0.265841901302338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258542776107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265457719564438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263152778148651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292733430862427</t>
   </si>
   <si>
     <t xml:space="preserve">0.327692419290543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302337497472763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301953434944153</t>
+    <t xml:space="preserve">0.302337557077408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301953375339508</t>
   </si>
   <si>
     <t xml:space="preserve">0.332302391529083</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">0.332686573266983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306179195642471</t>
+    <t xml:space="preserve">0.306179225444794</t>
   </si>
   <si>
     <t xml:space="preserve">0.305026710033417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312325835227966</t>
+    <t xml:space="preserve">0.312325805425644</t>
   </si>
   <si>
     <t xml:space="preserve">0.331918209791183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315399140119553</t>
+    <t xml:space="preserve">0.31539911031723</t>
   </si>
   <si>
     <t xml:space="preserve">0.326539933681488</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">0.289275974035263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291196793317795</t>
+    <t xml:space="preserve">0.291196763515472</t>
   </si>
   <si>
     <t xml:space="preserve">0.286970973014832</t>
@@ -2150,19 +2150,19 @@
     <t xml:space="preserve">0.285050123929977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273525238037109</t>
+    <t xml:space="preserve">0.273525208234787</t>
   </si>
   <si>
     <t xml:space="preserve">0.26084777712822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261616080999374</t>
+    <t xml:space="preserve">0.261616110801697</t>
   </si>
   <si>
     <t xml:space="preserve">0.270067691802979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278519362211227</t>
+    <t xml:space="preserve">0.27851939201355</t>
   </si>
   <si>
     <t xml:space="preserve">0.27314105629921</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">0.25316447019577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256621927022934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256237834692001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.249322831630707</t>
+    <t xml:space="preserve">0.256621956825256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256237804889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.249322816729546</t>
   </si>
   <si>
     <t xml:space="preserve">0.23626121878624</t>
@@ -2201,22 +2201,22 @@
     <t xml:space="preserve">0.283513456583023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27775102853775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294654279947281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319624960422516</t>
+    <t xml:space="preserve">0.277750998735428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294654250144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319624990224838</t>
   </si>
   <si>
     <t xml:space="preserve">0.343827366828918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338449001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34075403213501</t>
+    <t xml:space="preserve">0.338449031114578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340754002332687</t>
   </si>
   <si>
     <t xml:space="preserve">0.338833212852478</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">0.338064819574356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336912363767624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333839029073715</t>
+    <t xml:space="preserve">0.336912333965302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333839058876038</t>
   </si>
   <si>
     <t xml:space="preserve">0.330765724182129</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">0.34766897559166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35996225476265</t>
+    <t xml:space="preserve">0.359962224960327</t>
   </si>
   <si>
     <t xml:space="preserve">0.3518947660923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369182169437408</t>
+    <t xml:space="preserve">0.369182199239731</t>
   </si>
   <si>
     <t xml:space="preserve">0.357657223939896</t>
@@ -2258,16 +2258,16 @@
     <t xml:space="preserve">0.355352252721786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348053127527237</t>
+    <t xml:space="preserve">0.348053097724915</t>
   </si>
   <si>
     <t xml:space="preserve">0.346516460180283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347284823656082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363419681787491</t>
+    <t xml:space="preserve">0.34728479385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363419711589813</t>
   </si>
   <si>
     <t xml:space="preserve">0.373792171478271</t>
@@ -2279,22 +2279,22 @@
     <t xml:space="preserve">0.379554599523544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425654411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417971104383469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381859660148621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38301208615303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377633780241013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378402173519135</t>
+    <t xml:space="preserve">0.425654381513596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417971134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381859600543976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383012115955353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377633810043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378402143716812</t>
   </si>
   <si>
     <t xml:space="preserve">0.381091266870499</t>
@@ -2303,34 +2303,34 @@
     <t xml:space="preserve">0.380322962999344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348437309265137</t>
+    <t xml:space="preserve">0.348437339067459</t>
   </si>
   <si>
     <t xml:space="preserve">0.400299519300461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383396327495575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379938781261444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388006269931793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428727716207504</t>
+    <t xml:space="preserve">0.383396297693253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379938811063766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388006240129471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428727686405182</t>
   </si>
   <si>
     <t xml:space="preserve">0.368413865566254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344595611095428</t>
+    <t xml:space="preserve">0.344595640897751</t>
   </si>
   <si>
     <t xml:space="preserve">0.334223181009293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341906487941742</t>
+    <t xml:space="preserve">0.34190645813942</t>
   </si>
   <si>
     <t xml:space="preserve">0.323466598987579</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">0.340369820594788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331149876117706</t>
+    <t xml:space="preserve">0.331149905920029</t>
   </si>
   <si>
     <t xml:space="preserve">0.348821461200714</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">0.322314113378525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285818457603455</t>
+    <t xml:space="preserve">0.285818517208099</t>
   </si>
   <si>
     <t xml:space="preserve">0.337680727243423</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">0.345363944768906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341522336006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329229056835175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353653162717819</t>
+    <t xml:space="preserve">0.341522365808487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329229027032852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353653132915497</t>
   </si>
   <si>
     <t xml:space="preserve">0.351594597101212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35406482219696</t>
+    <t xml:space="preserve">0.354064851999283</t>
   </si>
   <si>
     <t xml:space="preserve">0.352829694747925</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">0.341713756322861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342537134885788</t>
+    <t xml:space="preserve">0.34253716468811</t>
   </si>
   <si>
     <t xml:space="preserve">0.348300993442535</t>
@@ -2393,25 +2393,25 @@
     <t xml:space="preserve">0.35982871055603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241443634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354888200759888</t>
+    <t xml:space="preserve">0.353241413831711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35488823056221</t>
   </si>
   <si>
     <t xml:space="preserve">0.350359499454498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345007359981537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339655190706253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342948853969574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341302007436752</t>
+    <t xml:space="preserve">0.345007330179214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339655220508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342948824167252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341302037239075</t>
   </si>
   <si>
     <t xml:space="preserve">0.333479672670364</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">0.319070041179657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321540296077728</t>
+    <t xml:space="preserve">0.321540266275406</t>
   </si>
   <si>
     <t xml:space="preserve">0.310835987329483</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">0.312894523143768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31824666261673</t>
+    <t xml:space="preserve">0.318246632814407</t>
   </si>
   <si>
     <t xml:space="preserve">0.317834943532944</t>
@@ -2447,34 +2447,34 @@
     <t xml:space="preserve">0.319481760263443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312071114778519</t>
+    <t xml:space="preserve">0.312071084976196</t>
   </si>
   <si>
     <t xml:space="preserve">0.308365762233734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310012608766556</t>
+    <t xml:space="preserve">0.310012578964233</t>
   </si>
   <si>
     <t xml:space="preserve">0.314541280269623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318658351898193</t>
+    <t xml:space="preserve">0.318658322095871</t>
   </si>
   <si>
     <t xml:space="preserve">0.32030513882637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322775363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309600830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309189140796661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321128517389297</t>
+    <t xml:space="preserve">0.322775393724442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309600859880447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309189170598984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32112854719162</t>
   </si>
   <si>
     <t xml:space="preserve">0.321951985359192</t>
@@ -2483,16 +2483,16 @@
     <t xml:space="preserve">0.32524561882019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326892405748367</t>
+    <t xml:space="preserve">0.32689243555069</t>
   </si>
   <si>
     <t xml:space="preserve">0.323187112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323598831892014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315364718437195</t>
+    <t xml:space="preserve">0.323598802089691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315364688634872</t>
   </si>
   <si>
     <t xml:space="preserve">0.31330618262291</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">0.311247676610947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317011535167694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31742325425148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311659425497055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316188156604767</t>
+    <t xml:space="preserve">0.317011564970016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317423224449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311659395694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316188126802444</t>
   </si>
   <si>
     <t xml:space="preserve">0.319893479347229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304660469293594</t>
+    <t xml:space="preserve">0.304660439491272</t>
   </si>
   <si>
     <t xml:space="preserve">0.30877748131752</t>
@@ -2534,25 +2534,25 @@
     <t xml:space="preserve">0.307542353868484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302601903676987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307954102754593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306307256221771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301778495311737</t>
+    <t xml:space="preserve">0.302601933479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307954072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306307286024094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301778525114059</t>
   </si>
   <si>
     <t xml:space="preserve">0.3038370013237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30095511674881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301366835832596</t>
+    <t xml:space="preserve">0.300955086946487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301366806030273</t>
   </si>
   <si>
     <t xml:space="preserve">0.302190214395523</t>
@@ -2561,64 +2561,64 @@
     <t xml:space="preserve">0.313717901706696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326480716466904</t>
+    <t xml:space="preserve">0.326480686664581</t>
   </si>
   <si>
     <t xml:space="preserve">0.328539222478867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344595670700073</t>
+    <t xml:space="preserve">0.344595700502396</t>
   </si>
   <si>
     <t xml:space="preserve">0.340890318155289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356535077095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343360513448715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336361557245255</t>
+    <t xml:space="preserve">0.356535047292709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343360543251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336361587047577</t>
   </si>
   <si>
     <t xml:space="preserve">0.339243501424789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335126459598541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358181834220886</t>
+    <t xml:space="preserve">0.335126489400864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358181864023209</t>
   </si>
   <si>
     <t xml:space="preserve">0.3470658659935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34418398141861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336773306131363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345419049263</t>
+    <t xml:space="preserve">0.344183951616287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336773276329041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345419079065323</t>
   </si>
   <si>
     <t xml:space="preserve">0.349124372005463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338008433580399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335949897766113</t>
+    <t xml:space="preserve">0.338008403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335949867963791</t>
   </si>
   <si>
     <t xml:space="preserve">0.343772232532501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33759668469429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340066909790039</t>
+    <t xml:space="preserve">0.337596714496613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340066879987717</t>
   </si>
   <si>
     <t xml:space="preserve">0.340478628873825</t>
@@ -2630,19 +2630,19 @@
     <t xml:space="preserve">0.329362630844116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325657337903976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33842009305954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346654146909714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355711668729782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359005272388458</t>
+    <t xml:space="preserve">0.325657308101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338420122861862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346654176712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35571163892746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359005302190781</t>
   </si>
   <si>
     <t xml:space="preserve">0.370121240615845</t>
@@ -2651,16 +2651,16 @@
     <t xml:space="preserve">0.377943605184555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381648927927017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3902947306633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39523509144783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399763882160187</t>
+    <t xml:space="preserve">0.38164895772934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390294700860977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395235121250153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399763911962509</t>
   </si>
   <si>
     <t xml:space="preserve">0.389471292495728</t>
@@ -2705,16 +2705,16 @@
     <t xml:space="preserve">0.394823491573334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417467147111893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433111876249313</t>
+    <t xml:space="preserve">0.417467176914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433111846446991</t>
   </si>
   <si>
     <t xml:space="preserve">0.430641621351242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441345930099487</t>
+    <t xml:space="preserve">0.441345900297165</t>
   </si>
   <si>
     <t xml:space="preserve">0.454520404338837</t>
@@ -2729,10 +2729,10 @@
     <t xml:space="preserve">0.50392484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534390866756439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518746197223663</t>
+    <t xml:space="preserve">0.534390807151794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518746137619019</t>
   </si>
   <si>
     <t xml:space="preserve">0.522039771080017</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">0.46934175491333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485809892416</t>
+    <t xml:space="preserve">0.485809922218323</t>
   </si>
   <si>
     <t xml:space="preserve">0.462754458189011</t>
@@ -2756,34 +2756,34 @@
     <t xml:space="preserve">0.472635388374329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493220567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573721170425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481692880392075</t>
+    <t xml:space="preserve">0.493220508098602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491573691368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48169282078743</t>
   </si>
   <si>
     <t xml:space="preserve">0.467694908380508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459460854530334</t>
+    <t xml:space="preserve">0.459460884332657</t>
   </si>
   <si>
     <t xml:space="preserve">0.461107701063156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476752430200577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479222625494003</t>
+    <t xml:space="preserve">0.476752400398254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479222595691681</t>
   </si>
   <si>
     <t xml:space="preserve">0.477575838565826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515452444553375</t>
+    <t xml:space="preserve">0.51545250415802</t>
   </si>
   <si>
     <t xml:space="preserve">0.504748225212097</t>
@@ -2792,40 +2792,40 @@
     <t xml:space="preserve">0.501454651355743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498984396457672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494043916463852</t>
+    <t xml:space="preserve">0.498984456062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494043976068497</t>
   </si>
   <si>
     <t xml:space="preserve">0.505571663379669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490750312805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484986454248428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492397099733353</t>
+    <t xml:space="preserve">0.490750372409821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484986424446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492397129535675</t>
   </si>
   <si>
     <t xml:space="preserve">0.482516318559647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478399187326431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473458766937256</t>
+    <t xml:space="preserve">0.478399217128754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473458737134933</t>
   </si>
   <si>
     <t xml:space="preserve">0.470988571643829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470165133476257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465224713087082</t>
+    <t xml:space="preserve">0.47016516327858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46522468328476</t>
   </si>
   <si>
     <t xml:space="preserve">0.460284322500229</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">0.473822295665741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457910358905792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461446434259415</t>
+    <t xml:space="preserve">0.457910388708115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461446404457092</t>
   </si>
   <si>
     <t xml:space="preserve">0.464098334312439</t>
@@ -2870,16 +2870,16 @@
     <t xml:space="preserve">0.426528483629227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433158457279205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448186427354813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441998422145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434484452009201</t>
+    <t xml:space="preserve">0.433158487081528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448186457157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441998451948166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434484422206879</t>
   </si>
   <si>
     <t xml:space="preserve">0.444650441408157</t>
@@ -2891,16 +2891,16 @@
     <t xml:space="preserve">0.437578469514847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43360048532486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430948466062546</t>
+    <t xml:space="preserve">0.433600455522537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430948495864868</t>
   </si>
   <si>
     <t xml:space="preserve">0.431390464305878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434926450252533</t>
+    <t xml:space="preserve">0.434926480054855</t>
   </si>
   <si>
     <t xml:space="preserve">0.429622501134872</t>
@@ -2912,16 +2912,16 @@
     <t xml:space="preserve">0.424318462610245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434042453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421666502952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430506467819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427854478359222</t>
+    <t xml:space="preserve">0.434042483568192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421666473150253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430506438016891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427854508161545</t>
   </si>
   <si>
     <t xml:space="preserve">0.419456511735916</t>
@@ -2942,37 +2942,37 @@
     <t xml:space="preserve">0.42255049943924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413710564374924</t>
+    <t xml:space="preserve">0.413710504770279</t>
   </si>
   <si>
     <t xml:space="preserve">0.425202518701553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423876523971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414594531059265</t>
+    <t xml:space="preserve">0.423876494169235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414594560861588</t>
   </si>
   <si>
     <t xml:space="preserve">0.422992497682571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421224504709244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413268506526947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415920525789261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408406555652618</t>
+    <t xml:space="preserve">0.421224534511566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413268536329269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415920495986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408406585454941</t>
   </si>
   <si>
     <t xml:space="preserve">0.412384569644928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411058574914932</t>
+    <t xml:space="preserve">0.41105854511261</t>
   </si>
   <si>
     <t xml:space="preserve">0.409732550382614</t>
@@ -2984,10 +2984,10 @@
     <t xml:space="preserve">0.407964557409286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423434495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42034050822258</t>
+    <t xml:space="preserve">0.423434525728226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420340478420258</t>
   </si>
   <si>
     <t xml:space="preserve">0.426086455583572</t>
@@ -3002,10 +3002,10 @@
     <t xml:space="preserve">0.422108501195908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415478557348251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402218580245972</t>
+    <t xml:space="preserve">0.415478527545929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402218610048294</t>
   </si>
   <si>
     <t xml:space="preserve">0.394262611865997</t>
@@ -3023,22 +3023,22 @@
     <t xml:space="preserve">0.396030604839325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405754595994949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403544545173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400450557470322</t>
+    <t xml:space="preserve">0.405754566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403544574975967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400450587272644</t>
   </si>
   <si>
     <t xml:space="preserve">0.389842629432678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388958632946014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395146608352661</t>
+    <t xml:space="preserve">0.388958603143692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395146578550339</t>
   </si>
   <si>
     <t xml:space="preserve">0.386748641729355</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">0.393378585577011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403102576732635</t>
+    <t xml:space="preserve">0.403102546930313</t>
   </si>
   <si>
     <t xml:space="preserve">0.396914601325989</t>
@@ -3062,13 +3062,13 @@
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660608291626</t>
+    <t xml:space="preserve">0.402660578489304</t>
   </si>
   <si>
     <t xml:space="preserve">0.419898509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436694473028183</t>
+    <t xml:space="preserve">0.436694413423538</t>
   </si>
   <si>
     <t xml:space="preserve">0.443766415119171</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">0.452878683805466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453334301710129</t>
+    <t xml:space="preserve">0.453334271907806</t>
   </si>
   <si>
     <t xml:space="preserve">0.462902158498764</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">0.459257245063782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456523537635803</t>
+    <t xml:space="preserve">0.456523567438126</t>
   </si>
   <si>
     <t xml:space="preserve">0.465635806322098</t>
@@ -3098,22 +3098,22 @@
     <t xml:space="preserve">0.464724570512772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468369483947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480215430259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482949078083038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481126606464386</t>
+    <t xml:space="preserve">0.468369513750076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480215460062027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482949018478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481126666069031</t>
   </si>
   <si>
     <t xml:space="preserve">0.482037842273712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479304194450378</t>
+    <t xml:space="preserve">0.479304224252701</t>
   </si>
   <si>
     <t xml:space="preserve">0.474748075008392</t>
@@ -3122,13 +3122,13 @@
     <t xml:space="preserve">0.486593961715698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501173555850983</t>
+    <t xml:space="preserve">0.501173615455627</t>
   </si>
   <si>
     <t xml:space="preserve">0.523042976856232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529421448707581</t>
+    <t xml:space="preserve">0.529421508312225</t>
   </si>
   <si>
     <t xml:space="preserve">0.52577668428421</t>
@@ -3146,19 +3146,19 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753149986267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507552087306976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511197030544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514841973781586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519398093223572</t>
+    <t xml:space="preserve">0.515753209590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507552146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511197090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514841914176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519398033618927</t>
   </si>
   <si>
     <t xml:space="preserve">0.51393073797226</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546734809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537622511386871</t>
+    <t xml:space="preserve">0.541267514228821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546734869480133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537622570991516</t>
   </si>
   <si>
     <t xml:space="preserve">0.549468457698822</t>
@@ -3194,10 +3194,10 @@
     <t xml:space="preserve">0.554024577140808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564959347248077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569515407085419</t>
+    <t xml:space="preserve">0.564959287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569515466690063</t>
   </si>
   <si>
     <t xml:space="preserve">0.565870463848114</t>
@@ -3212,10 +3212,10 @@
     <t xml:space="preserve">0.548557281494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550379693508148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547646045684814</t>
+    <t xml:space="preserve">0.550379633903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547646105289459</t>
   </si>
   <si>
     <t xml:space="preserve">0.55584704875946</t>
@@ -3236,25 +3236,25 @@
     <t xml:space="preserve">0.558580696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556758284568787</t>
+    <t xml:space="preserve">0.556758344173431</t>
   </si>
   <si>
     <t xml:space="preserve">0.542178690433502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557669520378113</t>
+    <t xml:space="preserve">0.557669460773468</t>
   </si>
   <si>
     <t xml:space="preserve">0.534888863563538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528510332107544</t>
+    <t xml:space="preserve">0.528510272502899</t>
   </si>
   <si>
     <t xml:space="preserve">0.535800099372864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530332803726196</t>
+    <t xml:space="preserve">0.530332744121552</t>
   </si>
   <si>
     <t xml:space="preserve">0.527599096298218</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617466211319</t>
+    <t xml:space="preserve">0.496617436408997</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">0.505729734897614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494795024394989</t>
+    <t xml:space="preserve">0.494794994592667</t>
   </si>
   <si>
     <t xml:space="preserve">0.499351114034653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497528731822968</t>
+    <t xml:space="preserve">0.497528672218323</t>
   </si>
   <si>
     <t xml:space="preserve">0.492061376571655</t>
@@ -3290,25 +3290,25 @@
     <t xml:space="preserve">0.488416433334351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483860313892365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487505227327347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495706230401993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49388375878334</t>
+    <t xml:space="preserve">0.483860343694687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487505257129669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495706290006638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493883818387985</t>
   </si>
   <si>
     <t xml:space="preserve">0.491150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517575621604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489643424749374</t>
+    <t xml:space="preserve">0.517575681209564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489643454551697</t>
   </si>
   <si>
     <t xml:space="preserve">0.48199275135994</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">0.475776553153992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476732909679413</t>
+    <t xml:space="preserve">0.47673287987709</t>
   </si>
   <si>
     <t xml:space="preserve">0.480080038309097</t>
@@ -3332,31 +3332,31 @@
     <t xml:space="preserve">0.46477872133255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473385721445084</t>
+    <t xml:space="preserve">0.473385751247406</t>
   </si>
   <si>
     <t xml:space="preserve">0.469560384750366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470994889736176</t>
+    <t xml:space="preserve">0.470994919538498</t>
   </si>
   <si>
     <t xml:space="preserve">0.459040701389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453780889511108</t>
+    <t xml:space="preserve">0.453780859708786</t>
   </si>
   <si>
     <t xml:space="preserve">0.451390027999878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447564691305161</t>
+    <t xml:space="preserve">0.447564661502838</t>
   </si>
   <si>
     <t xml:space="preserve">0.45091187953949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441826671361923</t>
+    <t xml:space="preserve">0.441826701164246</t>
   </si>
   <si>
     <t xml:space="preserve">0.438479512929916</t>
@@ -3365,13 +3365,13 @@
     <t xml:space="preserve">0.432741492986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436088681221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438001334667206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441348522901535</t>
+    <t xml:space="preserve">0.436088651418686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438001364469528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441348493099213</t>
   </si>
   <si>
     <t xml:space="preserve">0.446608364582062</t>
@@ -3386,16 +3386,16 @@
     <t xml:space="preserve">0.436566829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438957661390305</t>
+    <t xml:space="preserve">0.438957691192627</t>
   </si>
   <si>
     <t xml:space="preserve">0.444695681333542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439435869455338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433697819709778</t>
+    <t xml:space="preserve">0.439435839653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4336978495121</t>
   </si>
   <si>
     <t xml:space="preserve">0.434654176235199</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">0.46669140458107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454737186431885</t>
+    <t xml:space="preserve">0.454737216234207</t>
   </si>
   <si>
     <t xml:space="preserve">0.455693542957306</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">0.561368525028229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538416564464569</t>
+    <t xml:space="preserve">0.538416504859924</t>
   </si>
   <si>
     <t xml:space="preserve">0.544154524803162</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">0.540329158306122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525984108448029</t>
+    <t xml:space="preserve">0.525984168052673</t>
   </si>
   <si>
     <t xml:space="preserve">0.517377138137817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525027871131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521202504634857</t>
+    <t xml:space="preserve">0.525027811527252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521202445030212</t>
   </si>
   <si>
     <t xml:space="preserve">0.519289791584015</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">0.531722128391266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518333435058594</t>
+    <t xml:space="preserve">0.518333494663239</t>
   </si>
   <si>
     <t xml:space="preserve">0.514508128166199</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">0.527896821498871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52694046497345</t>
+    <t xml:space="preserve">0.526940524578094</t>
   </si>
   <si>
     <t xml:space="preserve">0.535547494888306</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">0.553717851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568062841892242</t>
+    <t xml:space="preserve">0.568062901496887</t>
   </si>
   <si>
     <t xml:space="preserve">0.55849951505661</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">0.555630505084991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554674208164215</t>
+    <t xml:space="preserve">0.55467414855957</t>
   </si>
   <si>
     <t xml:space="preserve">0.557543218135834</t>
@@ -3494,16 +3494,16 @@
     <t xml:space="preserve">0.54702353477478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537460148334503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551805198192596</t>
+    <t xml:space="preserve">0.537460088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551805257797241</t>
   </si>
   <si>
     <t xml:space="preserve">0.524071455001831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533634901046753</t>
+    <t xml:space="preserve">0.533634841442108</t>
   </si>
   <si>
     <t xml:space="preserve">0.536503851413727</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">0.522158801555634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529809534549713</t>
+    <t xml:space="preserve">0.529809474945068</t>
   </si>
   <si>
     <t xml:space="preserve">0.532678484916687</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">0.499206781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49633777141571</t>
+    <t xml:space="preserve">0.496337741613388</t>
   </si>
   <si>
     <t xml:space="preserve">0.506857395172119</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">0.487730741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483905404806137</t>
+    <t xml:space="preserve">0.483905375003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.461909741163254</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">0.478167414665222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46860408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471473067998886</t>
+    <t xml:space="preserve">0.468604058027267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471473038196564</t>
   </si>
   <si>
     <t xml:space="preserve">0.48260822892189</t>
@@ -3939,6 +3939,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.633000016212463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615000009536743</t>
   </si>
 </sst>
 </file>
@@ -68965,7 +68968,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6494907407</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>1226397</v>
@@ -68986,6 +68989,32 @@
         <v>1308</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6494675926</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>560859</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>0.638999998569489</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>0.614000022411346</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>0.637000024318695</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1309</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="1310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="1311">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333736211061478</t>
+    <t xml:space="preserve">0.333736181259155</t>
   </si>
   <si>
     <t xml:space="preserve">IMS.MI</t>
@@ -56,46 +56,46 @@
     <t xml:space="preserve">0.307318478822708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288448721170425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289336651563644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294368624687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285636752843857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273796856403351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258997052907944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258257061243057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243605241179466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246417179703712</t>
+    <t xml:space="preserve">0.288448691368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289336681365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294368654489517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285636723041534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273796826601028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258997023105621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258257031440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243605226278305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246417164802551</t>
   </si>
   <si>
     <t xml:space="preserve">0.262696981430054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256407052278519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259810984134674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261513024568558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253817111253738</t>
+    <t xml:space="preserve">0.256407082080841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259811013936996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261512964963913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253817081451416</t>
   </si>
   <si>
     <t xml:space="preserve">0.253077119588852</t>
@@ -107,37 +107,37 @@
     <t xml:space="preserve">0.284600764513016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277496755123138</t>
+    <t xml:space="preserve">0.277496814727783</t>
   </si>
   <si>
     <t xml:space="preserve">0.28711673617363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290742665529251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263806939125061</t>
+    <t xml:space="preserve">0.290742635726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263806998729706</t>
   </si>
   <si>
     <t xml:space="preserve">0.256777077913284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250117123126984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277570813894272</t>
+    <t xml:space="preserve">0.250117152929306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277570843696594</t>
   </si>
   <si>
     <t xml:space="preserve">0.297994613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310796409845352</t>
+    <t xml:space="preserve">0.310796469449997</t>
   </si>
   <si>
     <t xml:space="preserve">0.303544521331787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304358541965485</t>
+    <t xml:space="preserve">0.304358512163162</t>
   </si>
   <si>
     <t xml:space="preserve">0.318122357130051</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">0.309686452150345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301620543003082</t>
+    <t xml:space="preserve">0.301620572805405</t>
   </si>
   <si>
     <t xml:space="preserve">0.310352444648743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323376327753067</t>
+    <t xml:space="preserve">0.323376268148422</t>
   </si>
   <si>
     <t xml:space="preserve">0.320046305656433</t>
@@ -164,58 +164,58 @@
     <t xml:space="preserve">0.315236389636993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315606385469437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332996159791946</t>
+    <t xml:space="preserve">0.315606415271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332996189594269</t>
   </si>
   <si>
     <t xml:space="preserve">0.332256197929382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328852266073227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330480217933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311240464448929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312054395675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299696534872055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296884626150131</t>
+    <t xml:space="preserve">0.328852236270905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330480247735977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311240434646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312054425477982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299696564674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296884596347809</t>
   </si>
   <si>
     <t xml:space="preserve">0.299400568008423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297476559877396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295996606349945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293702661991119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298216640949249</t>
+    <t xml:space="preserve">0.297476589679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295996576547623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293702632188797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298216581344604</t>
   </si>
   <si>
     <t xml:space="preserve">0.286376714706421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276756882667542</t>
+    <t xml:space="preserve">0.276756852865219</t>
   </si>
   <si>
     <t xml:space="preserve">0.27453687787056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272316873073578</t>
+    <t xml:space="preserve">0.2723169028759</t>
   </si>
   <si>
     <t xml:space="preserve">0.268542915582657</t>
@@ -224,31 +224,31 @@
     <t xml:space="preserve">0.270466893911362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26506495475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268172979354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268616944551468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269208878278732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275276839733124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28489676117897</t>
+    <t xml:space="preserve">0.265064984560013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268172919750214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268616914749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269208908081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275276809930801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284896731376648</t>
   </si>
   <si>
     <t xml:space="preserve">0.290002644062042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308206498622894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309168487787247</t>
+    <t xml:space="preserve">0.308206468820572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309168457984924</t>
   </si>
   <si>
     <t xml:space="preserve">0.318196386098862</t>
@@ -260,28 +260,28 @@
     <t xml:space="preserve">0.308946460485458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314200401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321378350257874</t>
+    <t xml:space="preserve">0.314200431108475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321378290653229</t>
   </si>
   <si>
     <t xml:space="preserve">0.319380342960358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310722470283508</t>
+    <t xml:space="preserve">0.310722440481186</t>
   </si>
   <si>
     <t xml:space="preserve">0.313682407140732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313312441110611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30709645152092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30761444568634</t>
+    <t xml:space="preserve">0.313312411308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307096481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307614415884018</t>
   </si>
   <si>
     <t xml:space="preserve">0.304950475692749</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">0.305320501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295626640319824</t>
+    <t xml:space="preserve">0.295626610517502</t>
   </si>
   <si>
     <t xml:space="preserve">0.300954550504684</t>
@@ -305,16 +305,16 @@
     <t xml:space="preserve">0.314400315284729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318779766559601</t>
+    <t xml:space="preserve">0.318779796361923</t>
   </si>
   <si>
     <t xml:space="preserve">0.318856626749039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318395644426346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319932252168655</t>
+    <t xml:space="preserve">0.318395614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319932281970978</t>
   </si>
   <si>
     <t xml:space="preserve">0.318088293075562</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">0.321776270866394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320393294095993</t>
+    <t xml:space="preserve">0.320393264293671</t>
   </si>
   <si>
     <t xml:space="preserve">0.311557501554489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305795043706894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301569193601608</t>
+    <t xml:space="preserve">0.305795013904572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301569223403931</t>
   </si>
   <si>
     <t xml:space="preserve">0.295806765556335</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">0.299648374319077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296575099229813</t>
+    <t xml:space="preserve">0.296575129032135</t>
   </si>
   <si>
     <t xml:space="preserve">0.303490042686462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31424668431282</t>
+    <t xml:space="preserve">0.314246624708176</t>
   </si>
   <si>
     <t xml:space="preserve">0.318011462688446</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">0.310020834207535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311941653490067</t>
+    <t xml:space="preserve">0.311941683292389</t>
   </si>
   <si>
     <t xml:space="preserve">0.311173319816589</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">0.30671700835228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305564522743225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304949879646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306870669126511</t>
+    <t xml:space="preserve">0.305564552545547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304949849843979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306870639324188</t>
   </si>
   <si>
     <t xml:space="preserve">0.297727555036545</t>
@@ -401,19 +401,19 @@
     <t xml:space="preserve">0.313478320837021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312556356191635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307869523763657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311480671167374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298265397548676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299110591411591</t>
+    <t xml:space="preserve">0.312556326389313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307869493961334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311480641365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298265427350998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299110561609268</t>
   </si>
   <si>
     <t xml:space="preserve">0.305257201194763</t>
@@ -425,22 +425,22 @@
     <t xml:space="preserve">0.295960426330566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297650694847107</t>
+    <t xml:space="preserve">0.297650724649429</t>
   </si>
   <si>
     <t xml:space="preserve">0.297881245613098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293732285499573</t>
+    <t xml:space="preserve">0.29373225569725</t>
   </si>
   <si>
     <t xml:space="preserve">0.298803240060806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300416707992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300109386444092</t>
+    <t xml:space="preserve">0.300416737794876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300109416246414</t>
   </si>
   <si>
     <t xml:space="preserve">0.298880070447922</t>
@@ -452,31 +452,31 @@
     <t xml:space="preserve">0.309559851884842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303105890750885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303566843271255</t>
+    <t xml:space="preserve">0.303105860948563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3035669028759</t>
   </si>
   <si>
     <t xml:space="preserve">0.308253675699234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304872989654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306563317775726</t>
+    <t xml:space="preserve">0.304873079061508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306563347578049</t>
   </si>
   <si>
     <t xml:space="preserve">0.300186216831207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298649609088898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296421468257904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301415592432022</t>
+    <t xml:space="preserve">0.298649579286575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296421378850937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3014155626297</t>
   </si>
   <si>
     <t xml:space="preserve">0.300647228956223</t>
@@ -485,28 +485,28 @@
     <t xml:space="preserve">0.282975643873215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291965126991272</t>
+    <t xml:space="preserve">0.29196509718895</t>
   </si>
   <si>
     <t xml:space="preserve">0.289736956357956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293501764535904</t>
+    <t xml:space="preserve">0.293501734733582</t>
   </si>
   <si>
     <t xml:space="preserve">0.292656570672989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29250293970108</t>
+    <t xml:space="preserve">0.292502880096436</t>
   </si>
   <si>
     <t xml:space="preserve">0.289583265781403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288123428821564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2842817902565</t>
+    <t xml:space="preserve">0.288123458623886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284281820058823</t>
   </si>
   <si>
     <t xml:space="preserve">0.28789296746254</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">0.290044248104095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292887061834335</t>
+    <t xml:space="preserve">0.292887091636658</t>
   </si>
   <si>
     <t xml:space="preserve">0.293117612600327</t>
@@ -527,64 +527,64 @@
     <t xml:space="preserve">0.289813816547394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286586791276932</t>
+    <t xml:space="preserve">0.286586821079254</t>
   </si>
   <si>
     <t xml:space="preserve">0.294270098209381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291811436414719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292579770088196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29572993516922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298419088125229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294731080532074</t>
+    <t xml:space="preserve">0.291811406612396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292579799890518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295729905366898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298419058322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294731050729752</t>
   </si>
   <si>
     <t xml:space="preserve">0.287355124950409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293809115886688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292041957378387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286740452051163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2846659719944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278903514146805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27559968829155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270221412181854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272449553012848</t>
+    <t xml:space="preserve">0.293809086084366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29204198718071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286740481853485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284666001796722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278903543949127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275599718093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270221382379532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272449523210526</t>
   </si>
   <si>
     <t xml:space="preserve">0.276675373315811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27398619055748</t>
+    <t xml:space="preserve">0.273986160755157</t>
   </si>
   <si>
     <t xml:space="preserve">0.275676518678665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275522857904434</t>
+    <t xml:space="preserve">0.275522828102112</t>
   </si>
   <si>
     <t xml:space="preserve">0.276598513126373</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">0.270989716053009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271143347024918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274293482303619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270451873540878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268146902322769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267378568649292</t>
+    <t xml:space="preserve">0.271143406629562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274293571710587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270451903343201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268146872520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267378598451614</t>
   </si>
   <si>
     <t xml:space="preserve">0.264612555503845</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">0.265765070915222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262384444475174</t>
+    <t xml:space="preserve">0.262384414672852</t>
   </si>
   <si>
     <t xml:space="preserve">0.267532229423523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265304088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27191174030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272526353597641</t>
+    <t xml:space="preserve">0.265304058790207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271911710500717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272526383399963</t>
   </si>
   <si>
     <t xml:space="preserve">0.283282965421677</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">0.279902368783951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277059465646744</t>
+    <t xml:space="preserve">0.277059495449066</t>
   </si>
   <si>
     <t xml:space="preserve">0.27844250202179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280516982078552</t>
+    <t xml:space="preserve">0.280517011880875</t>
   </si>
   <si>
     <t xml:space="preserve">0.278749823570251</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.278980314731598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278211981058121</t>
+    <t xml:space="preserve">0.278212040662766</t>
   </si>
   <si>
     <t xml:space="preserve">0.284051328897476</t>
@@ -659,49 +659,49 @@
     <t xml:space="preserve">0.290812611579895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289660096168518</t>
+    <t xml:space="preserve">0.28966012597084</t>
   </si>
   <si>
     <t xml:space="preserve">0.290428429841995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294807910919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295422554016113</t>
+    <t xml:space="preserve">0.294807940721512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295422583818436</t>
   </si>
   <si>
     <t xml:space="preserve">0.288507610559464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284589171409607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291043102741241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293885946273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294884711503983</t>
+    <t xml:space="preserve">0.284589141607285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291043132543564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293885886669159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294884741306305</t>
   </si>
   <si>
     <t xml:space="preserve">0.289890587329865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286125808954239</t>
+    <t xml:space="preserve">0.286125779151917</t>
   </si>
   <si>
     <t xml:space="preserve">0.284358620643616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282745152711868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277290046215057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281976848840714</t>
+    <t xml:space="preserve">0.282745182514191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277290016412735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281976819038391</t>
   </si>
   <si>
     <t xml:space="preserve">0.276214331388474</t>
@@ -710,91 +710,91 @@
     <t xml:space="preserve">0.273602038621902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269760370254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275061845779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271834880113602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273371547460556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275215536355972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276905864477158</t>
+    <t xml:space="preserve">0.269760400056839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275061875581741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271834939718246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273371577262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27521550655365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276905834674835</t>
   </si>
   <si>
     <t xml:space="preserve">0.27483132481575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282668352127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280440151691437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279595017433167</t>
+    <t xml:space="preserve">0.282668322324753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280440181493759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279595047235489</t>
   </si>
   <si>
     <t xml:space="preserve">0.27736684679985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278135180473328</t>
+    <t xml:space="preserve">0.278135120868683</t>
   </si>
   <si>
     <t xml:space="preserve">0.281208485364914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278672993183136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28259152173996</t>
+    <t xml:space="preserve">0.278672963380814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282591491937637</t>
   </si>
   <si>
     <t xml:space="preserve">0.279364496469498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285587936639786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27967181801796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28666365146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284435480833054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281900018453598</t>
+    <t xml:space="preserve">0.285587966442108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279671788215637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286663621664047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284435451030731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281899958848953</t>
   </si>
   <si>
     <t xml:space="preserve">0.283897668123245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285280674695969</t>
+    <t xml:space="preserve">0.285280644893646</t>
   </si>
   <si>
     <t xml:space="preserve">0.285434275865555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295038431882858</t>
+    <t xml:space="preserve">0.295038402080536</t>
   </si>
   <si>
     <t xml:space="preserve">0.30425837635994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321929931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325617909431458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331841379404068</t>
+    <t xml:space="preserve">0.321929901838303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32561793923378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33184140920639</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387418270111</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">0.309790343046188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30925253033638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311096489429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313094198703766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31301736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288891792297363</t>
+    <t xml:space="preserve">0.309252470731735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311096519231796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313094168901443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313017308712006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288891762495041</t>
   </si>
   <si>
     <t xml:space="preserve">0.293040752410889</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">0.298111736774445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310251355171204</t>
+    <t xml:space="preserve">0.310251325368881</t>
   </si>
   <si>
     <t xml:space="preserve">0.313555151224136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300800889730453</t>
+    <t xml:space="preserve">0.300800859928131</t>
   </si>
   <si>
     <t xml:space="preserve">0.308868318796158</t>
@@ -851,13 +851,13 @@
     <t xml:space="preserve">0.299725234508514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32185310125351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327308237552643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318472474813461</t>
+    <t xml:space="preserve">0.321853131055832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327308297157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318472445011139</t>
   </si>
   <si>
     <t xml:space="preserve">0.312095314264297</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">0.315014988183975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312249004840851</t>
+    <t xml:space="preserve">0.312249034643173</t>
   </si>
   <si>
     <t xml:space="preserve">0.313939303159714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309636682271957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307408481836319</t>
+    <t xml:space="preserve">0.309636652469635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307408511638641</t>
   </si>
   <si>
     <t xml:space="preserve">0.308945149183273</t>
@@ -899,34 +899,34 @@
     <t xml:space="preserve">0.309944003820419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3177809715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316551625728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316474825143814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324388563632965</t>
+    <t xml:space="preserve">0.317780941724777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31655165553093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316474795341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324388593435287</t>
   </si>
   <si>
     <t xml:space="preserve">0.325003266334534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318318754434586</t>
+    <t xml:space="preserve">0.318318784236908</t>
   </si>
   <si>
     <t xml:space="preserve">0.317704141139984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32154580950737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320470094680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621464729309</t>
+    <t xml:space="preserve">0.321545779705048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320470124483109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621434926987</t>
   </si>
   <si>
     <t xml:space="preserve">0.323697090148926</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">0.333454877138138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327385067939758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331764549016953</t>
+    <t xml:space="preserve">0.327385038137436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331764578819275</t>
   </si>
   <si>
     <t xml:space="preserve">0.339524686336517</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">0.34567129611969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340446710586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333378046751022</t>
+    <t xml:space="preserve">0.340446680784225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333378076553345</t>
   </si>
   <si>
     <t xml:space="preserve">0.33499151468277</t>
@@ -965,22 +965,22 @@
     <t xml:space="preserve">0.338910013437271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338141739368439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339678347110748</t>
+    <t xml:space="preserve">0.338141679763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339678317308426</t>
   </si>
   <si>
     <t xml:space="preserve">0.350358128547668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34659332036972</t>
+    <t xml:space="preserve">0.346593290567398</t>
   </si>
   <si>
     <t xml:space="preserve">0.344211488962173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340677171945572</t>
+    <t xml:space="preserve">0.340677201747894</t>
   </si>
   <si>
     <t xml:space="preserve">0.334607362747192</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">0.339601516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340907692909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3526631295681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369950503110886</t>
+    <t xml:space="preserve">0.340907633304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352663099765778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369950532913208</t>
   </si>
   <si>
     <t xml:space="preserve">0.36541736125946</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">0.363035529851913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374099493026733</t>
+    <t xml:space="preserve">0.374099522829056</t>
   </si>
   <si>
     <t xml:space="preserve">0.371103018522263</t>
@@ -1028,25 +1028,25 @@
     <t xml:space="preserve">0.366108864545822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363112390041351</t>
+    <t xml:space="preserve">0.363112419843674</t>
   </si>
   <si>
     <t xml:space="preserve">0.3686443567276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366877198219299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366262525320053</t>
+    <t xml:space="preserve">0.366877168416977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366262555122375</t>
   </si>
   <si>
     <t xml:space="preserve">0.361114740371704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359885424375534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359193921089172</t>
+    <t xml:space="preserve">0.359885394573212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35919389128685</t>
   </si>
   <si>
     <t xml:space="preserve">0.368567526340485</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">0.372025012969971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375559329986572</t>
+    <t xml:space="preserve">0.37555930018425</t>
   </si>
   <si>
     <t xml:space="preserve">0.380246102809906</t>
@@ -1064,55 +1064,55 @@
     <t xml:space="preserve">0.392616212368011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405677795410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421044409275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419507801532745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396842032670975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41336116194725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422581106424332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417586952447891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42642268538475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423349440097809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427959382534027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436795145273209</t>
+    <t xml:space="preserve">0.405677855014801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42104434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419507741928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396842062473297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413361132144928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422581076622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417586922645569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426422744989395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423349410295486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427959322929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436795175075531</t>
   </si>
   <si>
     <t xml:space="preserve">0.432953536510468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452930092811584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460824728012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465223371982574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296647071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481358259916306</t>
+    <t xml:space="preserve">0.45293003320694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460884332657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465223401784897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296676874161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481358230113983</t>
   </si>
   <si>
     <t xml:space="preserve">0.522463858127594</t>
@@ -1127,19 +1127,19 @@
     <t xml:space="preserve">0.50709730386734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515548825263977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503255605697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48980987071991</t>
+    <t xml:space="preserve">0.515548884868622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503255665302277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489809811115265</t>
   </si>
   <si>
     <t xml:space="preserve">0.480205804109573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519006311893463</t>
+    <t xml:space="preserve">0.519006431102753</t>
   </si>
   <si>
     <t xml:space="preserve">0.511323034763336</t>
@@ -1148,28 +1148,28 @@
     <t xml:space="preserve">0.499413967132568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491730630397797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484431535005569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483663201332092</t>
+    <t xml:space="preserve">0.491730719804764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484431594610214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48366317152977</t>
   </si>
   <si>
     <t xml:space="preserve">0.484815716743469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495188176631927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490194082260132</t>
+    <t xml:space="preserve">0.495188146829605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490193992853165</t>
   </si>
   <si>
     <t xml:space="preserve">0.553197026252747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542056262493134</t>
+    <t xml:space="preserve">0.542056202888489</t>
   </si>
   <si>
     <t xml:space="preserve">0.56280118227005</t>
@@ -1193,31 +1193,31 @@
     <t xml:space="preserve">0.552428662776947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551276206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545129537582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565874457359314</t>
+    <t xml:space="preserve">0.55127614736557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545129597187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565874397754669</t>
   </si>
   <si>
     <t xml:space="preserve">0.577015221118927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596607625484467</t>
+    <t xml:space="preserve">0.596607685089111</t>
   </si>
   <si>
     <t xml:space="preserve">0.584698498249054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608132541179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621962487697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620425820350647</t>
+    <t xml:space="preserve">0.608132481575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621962428092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620425879955292</t>
   </si>
   <si>
     <t xml:space="preserve">0.629645824432373</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">0.58162522315979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560880303382874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598528504371643</t>
+    <t xml:space="preserve">0.560880362987518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598528444766998</t>
   </si>
   <si>
     <t xml:space="preserve">0.598144292831421</t>
@@ -1244,25 +1244,25 @@
     <t xml:space="preserve">0.619657516479492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618120789527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601601779460907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58661937713623</t>
+    <t xml:space="preserve">0.618120849132538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601601719856262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586619317531586</t>
   </si>
   <si>
     <t xml:space="preserve">0.59545511007309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587771892547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584314405918121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577399373054504</t>
+    <t xml:space="preserve">0.587771773338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584314346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577399432659149</t>
   </si>
   <si>
     <t xml:space="preserve">0.567026913166046</t>
@@ -1271,52 +1271,52 @@
     <t xml:space="preserve">0.574326038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543592870235443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564721941947937</t>
+    <t xml:space="preserve">0.543592810630798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564722001552582</t>
   </si>
   <si>
     <t xml:space="preserve">0.563185274600983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576246857643127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583930253982544</t>
+    <t xml:space="preserve">0.576246917247772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583930194377899</t>
   </si>
   <si>
     <t xml:space="preserve">0.58085685968399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587003529071808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60467517375946</t>
+    <t xml:space="preserve">0.587003469467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604675114154816</t>
   </si>
   <si>
     <t xml:space="preserve">0.629261612892151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61850506067276</t>
+    <t xml:space="preserve">0.61850494146347</t>
   </si>
   <si>
     <t xml:space="preserve">0.606980085372925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603138387203217</t>
+    <t xml:space="preserve">0.603138446807861</t>
   </si>
   <si>
     <t xml:space="preserve">0.612358391284943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611590087413788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59391850233078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596991837024689</t>
+    <t xml:space="preserve">0.611590027809143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593918442726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596991717815399</t>
   </si>
   <si>
     <t xml:space="preserve">0.608516752719879</t>
@@ -1325,10 +1325,10 @@
     <t xml:space="preserve">0.599296748638153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589308559894562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553965330123901</t>
+    <t xml:space="preserve">0.589308619499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553965389728546</t>
   </si>
   <si>
     <t xml:space="preserve">0.538598716259003</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">0.557038724422455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536293804645538</t>
+    <t xml:space="preserve">0.536293745040894</t>
   </si>
   <si>
     <t xml:space="preserve">0.524000525474548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537830352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547818660736084</t>
+    <t xml:space="preserve">0.537830471992493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547818720340729</t>
   </si>
   <si>
     <t xml:space="preserve">0.532452166080475</t>
@@ -1358,37 +1358,37 @@
     <t xml:space="preserve">0.527073860168457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520927131175995</t>
+    <t xml:space="preserve">0.52092719078064</t>
   </si>
   <si>
     <t xml:space="preserve">0.517853915691376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525537192821503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530147135257721</t>
+    <t xml:space="preserve">0.525537252426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530147194862366</t>
   </si>
   <si>
     <t xml:space="preserve">0.523232221603394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519390523433685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524768888950348</t>
+    <t xml:space="preserve">0.51939058303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524768829345703</t>
   </si>
   <si>
     <t xml:space="preserve">0.549355387687683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501718938350677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492499023675919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477900743484497</t>
+    <t xml:space="preserve">0.501718997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492499053478241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477900773286819</t>
   </si>
   <si>
     <t xml:space="preserve">0.476364135742188</t>
@@ -1397,70 +1397,70 @@
     <t xml:space="preserve">0.488657385110855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471754133701324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472522526979446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468680769205093</t>
+    <t xml:space="preserve">0.471754163503647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472522437572479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468680918216705</t>
   </si>
   <si>
     <t xml:space="preserve">0.487120717763901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481742352247238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480974078178406</t>
+    <t xml:space="preserve">0.481742382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480974107980728</t>
   </si>
   <si>
     <t xml:space="preserve">0.483279049396515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478669077157974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470217525959015</t>
+    <t xml:space="preserve">0.478669136762619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470217436552048</t>
   </si>
   <si>
     <t xml:space="preserve">0.467912554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466375827789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839190244675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461765855550766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487889021635056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500182271003723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469449102878571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437179327011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444862604141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431801021099091</t>
+    <t xml:space="preserve">0.466375797986984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839220046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461765885353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4878890812397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500182390213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469449192285538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437179356813431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444862574338913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431800991296768</t>
   </si>
   <si>
     <t xml:space="preserve">0.444094330072403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424117684364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415666103363037</t>
+    <t xml:space="preserve">0.424117714166641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415666133165359</t>
   </si>
   <si>
     <t xml:space="preserve">0.382627964019775</t>
@@ -1472,19 +1472,19 @@
     <t xml:space="preserve">0.382243782281876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385701268911362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388774514198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391847848892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384164571762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376481354236603</t>
+    <t xml:space="preserve">0.385701239109039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388774573802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391847908496857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384164601564407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37648132443428</t>
   </si>
   <si>
     <t xml:space="preserve">0.367261350154877</t>
@@ -1493,13 +1493,13 @@
     <t xml:space="preserve">0.364956349134445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360346376895905</t>
+    <t xml:space="preserve">0.360346436500549</t>
   </si>
   <si>
     <t xml:space="preserve">0.352278918027878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356504738330841</t>
+    <t xml:space="preserve">0.356504768133163</t>
   </si>
   <si>
     <t xml:space="preserve">0.37148717045784</t>
@@ -1508,28 +1508,28 @@
     <t xml:space="preserve">0.368029683828354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372255474328995</t>
+    <t xml:space="preserve">0.372255504131317</t>
   </si>
   <si>
     <t xml:space="preserve">0.365340530872345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374944657087326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366493046283722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374560475349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374176323413849</t>
+    <t xml:space="preserve">0.374944627285004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3664930164814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374560505151749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374176293611526</t>
   </si>
   <si>
     <t xml:space="preserve">0.37878629565239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362267225980759</t>
+    <t xml:space="preserve">0.362267255783081</t>
   </si>
   <si>
     <t xml:space="preserve">0.353815585374832</t>
@@ -1538,19 +1538,19 @@
     <t xml:space="preserve">0.354583919048309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353047311306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37071880698204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35419973731041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395689517259598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411056160926819</t>
+    <t xml:space="preserve">0.353047281503677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370718836784363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354199767112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395689487457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411056131124496</t>
   </si>
   <si>
     <t xml:space="preserve">0.407982796430588</t>
@@ -1559,88 +1559,88 @@
     <t xml:space="preserve">0.384932935237885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390311270952225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378017961978912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380707085132599</t>
+    <t xml:space="preserve">0.390311241149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378017991781235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380707114934921</t>
   </si>
   <si>
     <t xml:space="preserve">0.362651377916336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359578043222427</t>
+    <t xml:space="preserve">0.35957807302475</t>
   </si>
   <si>
     <t xml:space="preserve">0.353431433439255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349589794874191</t>
+    <t xml:space="preserve">0.349589824676514</t>
   </si>
   <si>
     <t xml:space="preserve">0.344979822635651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343058973550797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354968100786209</t>
+    <t xml:space="preserve">0.343059003353119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354968070983887</t>
   </si>
   <si>
     <t xml:space="preserve">0.364188075065613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357273072004318</t>
+    <t xml:space="preserve">0.357273101806641</t>
   </si>
   <si>
     <t xml:space="preserve">0.349973976612091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339217334985733</t>
+    <t xml:space="preserve">0.339217364788055</t>
   </si>
   <si>
     <t xml:space="preserve">0.323850750923157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361883044242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350742310285568</t>
+    <t xml:space="preserve">0.361883074045181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350742280483246</t>
   </si>
   <si>
     <t xml:space="preserve">0.389542937278748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404141187667847</t>
+    <t xml:space="preserve">0.404141157865524</t>
   </si>
   <si>
     <t xml:space="preserve">0.396457850933075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412592768669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404909491539001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401836156845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394152879714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399531185626984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402604460716248</t>
+    <t xml:space="preserve">0.412592828273773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404909521341324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401836186647415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394152909517288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399531155824661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40260449051857</t>
   </si>
   <si>
     <t xml:space="preserve">0.401067852973938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397994488477707</t>
+    <t xml:space="preserve">0.397994518280029</t>
   </si>
   <si>
     <t xml:space="preserve">0.375712960958481</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">0.364572197198868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345748126506805</t>
+    <t xml:space="preserve">0.345748096704483</t>
   </si>
   <si>
     <t xml:space="preserve">0.336528211832047</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">0.337296515703201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329613268375397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32807657122612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331534087657928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319240778684616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326924115419388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312709987163544</t>
+    <t xml:space="preserve">0.329613238573074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328076541423798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331534028053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319240808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326924055814743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312709957361221</t>
   </si>
   <si>
     <t xml:space="preserve">0.341138154268265</t>
@@ -1688,31 +1688,31 @@
     <t xml:space="preserve">0.326155751943588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324619114398956</t>
+    <t xml:space="preserve">0.324619084596634</t>
   </si>
   <si>
     <t xml:space="preserve">0.325771570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330381572246552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329997360706329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324234962463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313862442970276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301185071468353</t>
+    <t xml:space="preserve">0.330381542444229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329997390508652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324234932661057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313862472772598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301185041666031</t>
   </si>
   <si>
     <t xml:space="preserve">0.303874224424362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29695925116539</t>
+    <t xml:space="preserve">0.296959221363068</t>
   </si>
   <si>
     <t xml:space="preserve">0.302721709012985</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">0.323082447052002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308100044727325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310405045747757</t>
+    <t xml:space="preserve">0.308100014925003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310404986143112</t>
   </si>
   <si>
     <t xml:space="preserve">0.306947559118271</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">0.314630806446075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305410891771317</t>
+    <t xml:space="preserve">0.305410861968994</t>
   </si>
   <si>
     <t xml:space="preserve">0.30848416686058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304642528295517</t>
+    <t xml:space="preserve">0.304642498493195</t>
   </si>
   <si>
     <t xml:space="preserve">0.320777416229248</t>
@@ -1754,22 +1754,22 @@
     <t xml:space="preserve">0.356120586395264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360730558633804</t>
+    <t xml:space="preserve">0.360730588436127</t>
   </si>
   <si>
     <t xml:space="preserve">0.358809769153595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351126402616501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355736404657364</t>
+    <t xml:space="preserve">0.351126432418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355736434459686</t>
   </si>
   <si>
     <t xml:space="preserve">0.342290639877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37187135219574</t>
+    <t xml:space="preserve">0.371871381998062</t>
   </si>
   <si>
     <t xml:space="preserve">0.370334655046463</t>
@@ -1781,31 +1781,31 @@
     <t xml:space="preserve">0.376097142696381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376865446567535</t>
+    <t xml:space="preserve">0.376865476369858</t>
   </si>
   <si>
     <t xml:space="preserve">0.377249628305435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398762851953506</t>
+    <t xml:space="preserve">0.398762881755829</t>
   </si>
   <si>
     <t xml:space="preserve">0.403372824192047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406446158885956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409519493579865</t>
+    <t xml:space="preserve">0.406446129083633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409519463777542</t>
   </si>
   <si>
     <t xml:space="preserve">0.39107957482338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381475418806076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407214462757111</t>
+    <t xml:space="preserve">0.381475478410721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407214432954788</t>
   </si>
   <si>
     <t xml:space="preserve">0.387237936258316</t>
@@ -1817,16 +1817,16 @@
     <t xml:space="preserve">0.411824464797974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414897799491882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417202770709991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397226214408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408751159906387</t>
+    <t xml:space="preserve">0.41489776968956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417202711105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397226184606552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408751130104065</t>
   </si>
   <si>
     <t xml:space="preserve">0.410287767648697</t>
@@ -1835,91 +1835,91 @@
     <t xml:space="preserve">0.414129436016083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416434437036514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418739467859268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420276075601578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42181271314621</t>
+    <t xml:space="preserve">0.416434466838837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418739438056946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4202761054039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421812772750854</t>
   </si>
   <si>
     <t xml:space="preserve">0.430264353752136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473290771245956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494804054498672</t>
+    <t xml:space="preserve">0.473290801048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49480402469635</t>
   </si>
   <si>
     <t xml:space="preserve">0.484047412872314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493267387151718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506328880786896</t>
+    <t xml:space="preserve">0.493267297744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506328999996185</t>
   </si>
   <si>
     <t xml:space="preserve">0.479437410831451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482510775327682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47559580206871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465607553720474</t>
+    <t xml:space="preserve">0.482510715723038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595861673355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070826768875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465607464313507</t>
   </si>
   <si>
     <t xml:space="preserve">0.460997551679611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453314214944839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434105962514877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789329051971</t>
+    <t xml:space="preserve">0.453314244747162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4341059923172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789239645004</t>
   </si>
   <si>
     <t xml:space="preserve">0.445630937814713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449472576379776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451009273529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460229218006134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454082578420639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457155883312225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451777577400208</t>
+    <t xml:space="preserve">0.449472546577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451009303331375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460229188203812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454082608222961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45715594291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451777547597885</t>
   </si>
   <si>
     <t xml:space="preserve">0.456387519836426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463302493095398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470985770225525</t>
+    <t xml:space="preserve">0.463302463293076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470985800027847</t>
   </si>
   <si>
     <t xml:space="preserve">0.467144161462784</t>
@@ -1928,55 +1928,55 @@
     <t xml:space="preserve">0.457924246788025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447167605161667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43256938457489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437947690486908</t>
+    <t xml:space="preserve">0.447167634963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432569324970245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437947660684586</t>
   </si>
   <si>
     <t xml:space="preserve">0.433337718248367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434874355792999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436410993337631</t>
+    <t xml:space="preserve">0.434874325990677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436411052942276</t>
   </si>
   <si>
     <t xml:space="preserve">0.43948432803154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441020965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440252631902695</t>
+    <t xml:space="preserve">0.441020995378494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440252602100372</t>
   </si>
   <si>
     <t xml:space="preserve">0.43871596455574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442557603120804</t>
+    <t xml:space="preserve">0.442557543516159</t>
   </si>
   <si>
     <t xml:space="preserve">0.485584110021591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455619245767593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443325996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429496079683304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435642659664154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450240910053253</t>
+    <t xml:space="preserve">0.455619186162949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443326026201248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429496049880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435642689466476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450240939855576</t>
   </si>
   <si>
     <t xml:space="preserve">0.427191078662872</t>
@@ -1988,46 +1988,46 @@
     <t xml:space="preserve">0.386469602584839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393384546041489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365724682807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372639656066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351510614156723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342674881219864</t>
+    <t xml:space="preserve">0.393384575843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365724712610245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372639685869217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351510643959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342674821615219</t>
   </si>
   <si>
     <t xml:space="preserve">0.317319959402084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26507356762886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259695261716843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.239334538578987</t>
+    <t xml:space="preserve">0.265073597431183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259695291519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23933456838131</t>
   </si>
   <si>
     <t xml:space="preserve">0.242023706436157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234724551439285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245865315198898</t>
+    <t xml:space="preserve">0.234724596142769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245865359902382</t>
   </si>
   <si>
     <t xml:space="preserve">0.258926957845688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251627802848816</t>
+    <t xml:space="preserve">0.251627832651138</t>
   </si>
   <si>
     <t xml:space="preserve">0.266610234975815</t>
@@ -2036,22 +2036,22 @@
     <t xml:space="preserve">0.269299358129501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258158594369888</t>
+    <t xml:space="preserve">0.258158624172211</t>
   </si>
   <si>
     <t xml:space="preserve">0.251243650913239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252011984586716</t>
+    <t xml:space="preserve">0.252012014389038</t>
   </si>
   <si>
     <t xml:space="preserve">0.242407858371735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245097041130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254701107740402</t>
+    <t xml:space="preserve">0.245096996426582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254701137542725</t>
   </si>
   <si>
     <t xml:space="preserve">0.262000262737274</t>
@@ -2063,28 +2063,28 @@
     <t xml:space="preserve">0.261231929063797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262768596410751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264689445495605</t>
+    <t xml:space="preserve">0.262768626213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264689415693283</t>
   </si>
   <si>
     <t xml:space="preserve">0.271988540887833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273909330368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276982665061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27275687456131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275446027517319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268915176391602</t>
+    <t xml:space="preserve">0.273909360170364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276982694864273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272756844758987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275446057319641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268915235996246</t>
   </si>
   <si>
     <t xml:space="preserve">0.265841871500015</t>
@@ -2093,22 +2093,22 @@
     <t xml:space="preserve">0.258542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26545774936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263152718544006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292733430862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32769238948822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30233758687973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30195340514183</t>
+    <t xml:space="preserve">0.265457719564438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263152778148651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292733460664749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327692419290543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302337557077408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301953375339508</t>
   </si>
   <si>
     <t xml:space="preserve">0.332302391529083</t>
@@ -2120,25 +2120,25 @@
     <t xml:space="preserve">0.306179195642471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305026739835739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312325865030289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331918239593506</t>
+    <t xml:space="preserve">0.305026710033417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312325805425644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331918209791183</t>
   </si>
   <si>
     <t xml:space="preserve">0.315399169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32653996348381</t>
+    <t xml:space="preserve">0.326539903879166</t>
   </si>
   <si>
     <t xml:space="preserve">0.292349249124527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289275974035263</t>
+    <t xml:space="preserve">0.289275914430618</t>
   </si>
   <si>
     <t xml:space="preserve">0.291196793317795</t>
@@ -2147,25 +2147,25 @@
     <t xml:space="preserve">0.286970943212509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285050123929977</t>
+    <t xml:space="preserve">0.2850501537323</t>
   </si>
   <si>
     <t xml:space="preserve">0.273525208234787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26084777712822</t>
+    <t xml:space="preserve">0.260847747325897</t>
   </si>
   <si>
     <t xml:space="preserve">0.261616110801697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270067721605301</t>
+    <t xml:space="preserve">0.270067691802979</t>
   </si>
   <si>
     <t xml:space="preserve">0.278519362211227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273141026496887</t>
+    <t xml:space="preserve">0.27314105629921</t>
   </si>
   <si>
     <t xml:space="preserve">0.266994386911392</t>
@@ -2174,19 +2174,19 @@
     <t xml:space="preserve">0.255469471216202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253164440393448</t>
+    <t xml:space="preserve">0.253164499998093</t>
   </si>
   <si>
     <t xml:space="preserve">0.256621956825256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256237804889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.249322846531868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236261263489723</t>
+    <t xml:space="preserve">0.256237775087357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.249322801828384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23626121878624</t>
   </si>
   <si>
     <t xml:space="preserve">0.238182067871094</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">0.25354865193367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267762750387192</t>
+    <t xml:space="preserve">0.267762720584869</t>
   </si>
   <si>
     <t xml:space="preserve">0.283513456583023</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">0.277750998735428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294654279947281</t>
+    <t xml:space="preserve">0.294654309749603</t>
   </si>
   <si>
     <t xml:space="preserve">0.319624960422516</t>
@@ -2228,16 +2228,16 @@
     <t xml:space="preserve">0.336912363767624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333839058876038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330765753984451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328844904899597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33998566865921</t>
+    <t xml:space="preserve">0.333839029073715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330765724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32884493470192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339985728263855</t>
   </si>
   <si>
     <t xml:space="preserve">0.34766897559166</t>
@@ -2249,37 +2249,37 @@
     <t xml:space="preserve">0.351894795894623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369182229042053</t>
+    <t xml:space="preserve">0.369182199239731</t>
   </si>
   <si>
     <t xml:space="preserve">0.357657253742218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355352282524109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348053187131882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346516460180283</t>
+    <t xml:space="preserve">0.355352252721786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348053157329559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346516489982605</t>
   </si>
   <si>
     <t xml:space="preserve">0.34728479385376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363419681787491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373792171478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373023837804794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379554599523544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42565444111824</t>
+    <t xml:space="preserve">0.363419711589813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373792141675949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373023867607117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379554629325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425654411315918</t>
   </si>
   <si>
     <t xml:space="preserve">0.417971104383469</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">0.377633810043335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378402143716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381091296672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380322992801666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348437279462814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400299519300461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38339626789093</t>
+    <t xml:space="preserve">0.37840211391449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381091326475143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380322962999344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348437339067459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400299578905106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383396297693253</t>
   </si>
   <si>
     <t xml:space="preserve">0.379938811063766</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">0.388006240129471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428727716207504</t>
+    <t xml:space="preserve">0.428727746009827</t>
   </si>
   <si>
     <t xml:space="preserve">0.368413865566254</t>
@@ -2327,34 +2327,34 @@
     <t xml:space="preserve">0.344595670700073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334223240613937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341906487941742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323466628789902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340369820594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331149876117706</t>
+    <t xml:space="preserve">0.334223210811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34190645813942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323466598987579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34036985039711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331149905920029</t>
   </si>
   <si>
     <t xml:space="preserve">0.348821461200714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322314113378525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285818487405777</t>
+    <t xml:space="preserve">0.322314083576202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285818457603455</t>
   </si>
   <si>
     <t xml:space="preserve">0.337680697441101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34536400437355</t>
+    <t xml:space="preserve">0.345363944768906</t>
   </si>
   <si>
     <t xml:space="preserve">0.341522336006165</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">0.353653132915497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351594567298889</t>
+    <t xml:space="preserve">0.351594626903534</t>
   </si>
   <si>
     <t xml:space="preserve">0.354064851999283</t>
@@ -2378,25 +2378,25 @@
     <t xml:space="preserve">0.347477585077286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345830738544464</t>
+    <t xml:space="preserve">0.345830768346786</t>
   </si>
   <si>
     <t xml:space="preserve">0.341713726520538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342537134885788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348300963640213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35982871055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353241443634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354888200759888</t>
+    <t xml:space="preserve">0.342537194490433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348300993442535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359828680753708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353241413831711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35488823056221</t>
   </si>
   <si>
     <t xml:space="preserve">0.350359499454498</t>
@@ -2405,22 +2405,22 @@
     <t xml:space="preserve">0.345007359981537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339655190706253</t>
+    <t xml:space="preserve">0.339655220508575</t>
   </si>
   <si>
     <t xml:space="preserve">0.342948824167252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341302037239075</t>
+    <t xml:space="preserve">0.341302007436752</t>
   </si>
   <si>
     <t xml:space="preserve">0.333479672670364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320716887712479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319070041179657</t>
+    <t xml:space="preserve">0.320716857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319070070981979</t>
   </si>
   <si>
     <t xml:space="preserve">0.321540266275406</t>
@@ -2444,25 +2444,25 @@
     <t xml:space="preserve">0.317834943532944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319481790065765</t>
+    <t xml:space="preserve">0.319481760263443</t>
   </si>
   <si>
     <t xml:space="preserve">0.312071084976196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308365762233734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310012578964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314541339874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318658322095871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320305168628693</t>
+    <t xml:space="preserve">0.308365792036057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310012608766556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314541280269623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318658351898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32030513882637</t>
   </si>
   <si>
     <t xml:space="preserve">0.322775363922119</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">0.309600859880447</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309189200401306</t>
+    <t xml:space="preserve">0.309189140796661</t>
   </si>
   <si>
     <t xml:space="preserve">0.321128576993942</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">0.32195195555687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32524561882019</t>
+    <t xml:space="preserve">0.325245589017868</t>
   </si>
   <si>
     <t xml:space="preserve">0.32689243555069</t>
@@ -2501,13 +2501,13 @@
     <t xml:space="preserve">0.310424298048019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314952999353409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311247676610947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317011535167694</t>
+    <t xml:space="preserve">0.314953029155731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311247646808624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317011505365372</t>
   </si>
   <si>
     <t xml:space="preserve">0.31742325425148</t>
@@ -2516,16 +2516,16 @@
     <t xml:space="preserve">0.311659395694733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316188126802444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319893479347229</t>
+    <t xml:space="preserve">0.316188097000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319893449544907</t>
   </si>
   <si>
     <t xml:space="preserve">0.304660439491272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30877748131752</t>
+    <t xml:space="preserve">0.308777451515198</t>
   </si>
   <si>
     <t xml:space="preserve">0.303013622760773</t>
@@ -2534,19 +2534,19 @@
     <t xml:space="preserve">0.307542353868484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302601933479309</t>
+    <t xml:space="preserve">0.302601963281631</t>
   </si>
   <si>
     <t xml:space="preserve">0.307954072952271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306307256221771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301778465509415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303837031126022</t>
+    <t xml:space="preserve">0.306307226419449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301778495311737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3038370013237</t>
   </si>
   <si>
     <t xml:space="preserve">0.30095511674881</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">0.301366806030273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302190244197845</t>
+    <t xml:space="preserve">0.302190214395523</t>
   </si>
   <si>
     <t xml:space="preserve">0.313717901706696</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">0.326480716466904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328539192676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340890318155289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356535047292709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34336057305336</t>
+    <t xml:space="preserve">0.328539252281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340890347957611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356535077095032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343360543251038</t>
   </si>
   <si>
     <t xml:space="preserve">0.336361587047577</t>
@@ -2582,49 +2582,49 @@
     <t xml:space="preserve">0.339243501424789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335126459598541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358181864023209</t>
+    <t xml:space="preserve">0.335126519203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358181893825531</t>
   </si>
   <si>
     <t xml:space="preserve">0.3470658659935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344183951616287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336773335933685</t>
+    <t xml:space="preserve">0.34418398141861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336773306131363</t>
   </si>
   <si>
     <t xml:space="preserve">0.345419049263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349124372005463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338008403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335949897766113</t>
+    <t xml:space="preserve">0.349124401807785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338008373975754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335949867963791</t>
   </si>
   <si>
     <t xml:space="preserve">0.343772232532501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33759668469429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340066909790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340478599071503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332244545221329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329362630844116</t>
+    <t xml:space="preserve">0.337596714496613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340066939592361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340478628873825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332244515419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329362660646439</t>
   </si>
   <si>
     <t xml:space="preserve">0.325657308101654</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">0.338420122861862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346654206514359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35571163892746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359005242586136</t>
+    <t xml:space="preserve">0.346654176712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355711668729782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359005272388458</t>
   </si>
   <si>
     <t xml:space="preserve">0.370121240615845</t>
@@ -2648,37 +2648,37 @@
     <t xml:space="preserve">0.377943605184555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38164895772934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390294760465622</t>
+    <t xml:space="preserve">0.381648927927017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3902947306633</t>
   </si>
   <si>
     <t xml:space="preserve">0.395235151052475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399763882160187</t>
+    <t xml:space="preserve">0.399763911962509</t>
   </si>
   <si>
     <t xml:space="preserve">0.389471292495728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401822447776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411703288555145</t>
+    <t xml:space="preserve">0.401822417974472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411703318357468</t>
   </si>
   <si>
     <t xml:space="preserve">0.402234137058258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403469264507294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409644812345505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408409684896469</t>
+    <t xml:space="preserve">0.403469234704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409644782543182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408409655094147</t>
   </si>
   <si>
     <t xml:space="preserve">0.405939429998398</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">0.400175601243973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397705376148224</t>
+    <t xml:space="preserve">0.397705405950546</t>
   </si>
   <si>
     <t xml:space="preserve">0.403880923986435</t>
@@ -2699,52 +2699,52 @@
     <t xml:space="preserve">0.403057515621185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394823461771011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417467147111893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433111846446991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430641621351242</t>
+    <t xml:space="preserve">0.394823431968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417467176914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433111876249313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430641680955887</t>
   </si>
   <si>
     <t xml:space="preserve">0.441345930099487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454520374536514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442992746829987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488280117511749</t>
+    <t xml:space="preserve">0.454520434141159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442992717027664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488280087709427</t>
   </si>
   <si>
     <t xml:space="preserve">0.50392484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534390866756439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518746197223663</t>
+    <t xml:space="preserve">0.534390926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518746137619019</t>
   </si>
   <si>
     <t xml:space="preserve">0.522039771080017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500631213188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517922699451447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469341784715652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485809892416</t>
+    <t xml:space="preserve">0.500631153583527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517922759056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469341725111008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485809862613678</t>
   </si>
   <si>
     <t xml:space="preserve">0.462754517793655</t>
@@ -2753,19 +2753,19 @@
     <t xml:space="preserve">0.472635388374329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493220537900925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573691368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481692790985107</t>
+    <t xml:space="preserve">0.49322047829628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49157378077507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48169282078743</t>
   </si>
   <si>
     <t xml:space="preserve">0.467694938182831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459460884332657</t>
+    <t xml:space="preserve">0.459460914134979</t>
   </si>
   <si>
     <t xml:space="preserve">0.461107671260834</t>
@@ -2780,79 +2780,79 @@
     <t xml:space="preserve">0.477575838565826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515452444553375</t>
+    <t xml:space="preserve">0.51545250415802</t>
   </si>
   <si>
     <t xml:space="preserve">0.504748165607452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501454710960388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498984426259995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494043946266174</t>
+    <t xml:space="preserve">0.501454591751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498984456062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494044005870819</t>
   </si>
   <si>
     <t xml:space="preserve">0.505571663379669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490750342607498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484986424446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492397099733353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482516258955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478399157524109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473458796739578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470988571643829</t>
+    <t xml:space="preserve">0.490750372409821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484986543655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492397129535675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482516288757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478399217128754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473458826541901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470988631248474</t>
   </si>
   <si>
     <t xml:space="preserve">0.470165133476257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46522468328476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284322500229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46851834654808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46675032377243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473822295665741</t>
+    <t xml:space="preserve">0.465224713087082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284262895584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468518376350403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466750383377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473822325468063</t>
   </si>
   <si>
     <t xml:space="preserve">0.457910388708115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461446404457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464098364114761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454374372959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441114455461502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420782506465912</t>
+    <t xml:space="preserve">0.46144637465477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464098334312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454374402761459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44111442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420782536268234</t>
   </si>
   <si>
     <t xml:space="preserve">0.435810446739197</t>
@@ -2861,25 +2861,25 @@
     <t xml:space="preserve">0.438462436199188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427412480115891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426528483629227</t>
+    <t xml:space="preserve">0.427412509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426528453826904</t>
   </si>
   <si>
     <t xml:space="preserve">0.433158487081528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448186427354813</t>
+    <t xml:space="preserve">0.448186457157135</t>
   </si>
   <si>
     <t xml:space="preserve">0.441998451948166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434484452009201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444650441408157</t>
+    <t xml:space="preserve">0.434484481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44465047121048</t>
   </si>
   <si>
     <t xml:space="preserve">0.449070423841476</t>
@@ -2888,19 +2888,19 @@
     <t xml:space="preserve">0.437578439712524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433600455522537</t>
+    <t xml:space="preserve">0.433600425720215</t>
   </si>
   <si>
     <t xml:space="preserve">0.430948466062546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4313904941082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434926450252533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42962247133255</t>
+    <t xml:space="preserve">0.431390464305878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434926480054855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429622501134872</t>
   </si>
   <si>
     <t xml:space="preserve">0.428738474845886</t>
@@ -2909,25 +2909,25 @@
     <t xml:space="preserve">0.424318492412567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434042483568192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421666473150253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430506497621536</t>
+    <t xml:space="preserve">0.434042453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421666502952576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430506467819214</t>
   </si>
   <si>
     <t xml:space="preserve">0.427854478359222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419456511735916</t>
+    <t xml:space="preserve">0.419456541538239</t>
   </si>
   <si>
     <t xml:space="preserve">0.417246520519257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411942541599274</t>
+    <t xml:space="preserve">0.411942571401596</t>
   </si>
   <si>
     <t xml:space="preserve">0.414152532815933</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">0.42255049943924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413710504770279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425202488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423876523971558</t>
+    <t xml:space="preserve">0.413710534572601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425202518701553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423876464366913</t>
   </si>
   <si>
     <t xml:space="preserve">0.414594531059265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422992497682571</t>
+    <t xml:space="preserve">0.422992527484894</t>
   </si>
   <si>
     <t xml:space="preserve">0.421224504709244</t>
@@ -2963,31 +2963,31 @@
     <t xml:space="preserve">0.415920525789261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408406585454941</t>
+    <t xml:space="preserve">0.408406525850296</t>
   </si>
   <si>
     <t xml:space="preserve">0.412384539842606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411058515310287</t>
+    <t xml:space="preserve">0.41105854511261</t>
   </si>
   <si>
     <t xml:space="preserve">0.409732550382614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409290552139282</t>
+    <t xml:space="preserve">0.409290581941605</t>
   </si>
   <si>
     <t xml:space="preserve">0.407964557409286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423434525728226</t>
+    <t xml:space="preserve">0.423434495925903</t>
   </si>
   <si>
     <t xml:space="preserve">0.42034050822258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426086515188217</t>
+    <t xml:space="preserve">0.426086455583572</t>
   </si>
   <si>
     <t xml:space="preserve">0.428296476602554</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">0.422108501195908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415478557348251</t>
+    <t xml:space="preserve">0.415478527545929</t>
   </si>
   <si>
     <t xml:space="preserve">0.402218610048294</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">0.400008589029312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401334583759308</t>
+    <t xml:space="preserve">0.401334553956985</t>
   </si>
   <si>
     <t xml:space="preserve">0.39249461889267</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">0.405754536390305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403544574975967</t>
+    <t xml:space="preserve">0.403544545173645</t>
   </si>
   <si>
     <t xml:space="preserve">0.400450617074966</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">0.389842629432678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388958603143692</t>
+    <t xml:space="preserve">0.388958632946014</t>
   </si>
   <si>
     <t xml:space="preserve">0.395146608352661</t>
@@ -3041,16 +3041,16 @@
     <t xml:space="preserve">0.386748641729355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393378615379333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403102546930313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396914601325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39779856801033</t>
+    <t xml:space="preserve">0.393378585577011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403102576732635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396914571523666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397798597812653</t>
   </si>
   <si>
     <t xml:space="preserve">0.401776552200317</t>
@@ -3059,19 +3059,19 @@
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660608291626</t>
+    <t xml:space="preserve">0.402660578489304</t>
   </si>
   <si>
     <t xml:space="preserve">0.419898509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436694443225861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443766415119171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453789919614792</t>
+    <t xml:space="preserve">0.436694473028183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443766385316849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453789889812469</t>
   </si>
   <si>
     <t xml:space="preserve">0.452878683805466</t>
@@ -3086,31 +3086,31 @@
     <t xml:space="preserve">0.459257245063782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456523537635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465635806322098</t>
+    <t xml:space="preserve">0.456523567438126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465635776519775</t>
   </si>
   <si>
     <t xml:space="preserve">0.464724570512772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468369483947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480215430259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482949078083038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481126606464386</t>
+    <t xml:space="preserve">0.468369513750076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480215400457382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482949018478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481126666069031</t>
   </si>
   <si>
     <t xml:space="preserve">0.482037842273712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479304194450378</t>
+    <t xml:space="preserve">0.479304224252701</t>
   </si>
   <si>
     <t xml:space="preserve">0.474748075008392</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">0.52577668428421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523954153060913</t>
+    <t xml:space="preserve">0.523954212665558</t>
   </si>
   <si>
     <t xml:space="preserve">0.510285794734955</t>
@@ -3143,28 +3143,28 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753149986267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507552087306976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511197030544281</t>
+    <t xml:space="preserve">0.515753209590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507552146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511197090148926</t>
   </si>
   <si>
     <t xml:space="preserve">0.514841914176941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519398093223572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51393073797226</t>
+    <t xml:space="preserve">0.519398033618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513930678367615</t>
   </si>
   <si>
     <t xml:space="preserve">0.524865388870239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509374618530273</t>
+    <t xml:space="preserve">0.509374558925629</t>
   </si>
   <si>
     <t xml:space="preserve">0.526687920093536</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267395019531</t>
+    <t xml:space="preserve">0.541267454624176</t>
   </si>
   <si>
     <t xml:space="preserve">0.546734869480133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537622570991516</t>
+    <t xml:space="preserve">0.537622511386871</t>
   </si>
   <si>
     <t xml:space="preserve">0.549468457698822</t>
@@ -3191,25 +3191,25 @@
     <t xml:space="preserve">0.554024577140808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564959347248077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569515466690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562225580215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551290988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548557221889496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550379693508148</t>
+    <t xml:space="preserve">0.564959287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569515407085419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565870463848114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562225639820099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551290929317474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548557281494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550379633903503</t>
   </si>
   <si>
     <t xml:space="preserve">0.547646045684814</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">0.55584704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553113400936127</t>
+    <t xml:space="preserve">0.553113341331482</t>
   </si>
   <si>
     <t xml:space="preserve">0.564048111438751</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">0.559491991996765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561314404010773</t>
+    <t xml:space="preserve">0.561314344406128</t>
   </si>
   <si>
     <t xml:space="preserve">0.558580696582794</t>
@@ -3245,10 +3245,10 @@
     <t xml:space="preserve">0.534888863563538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528510272502899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535800158977509</t>
+    <t xml:space="preserve">0.528510332107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535800099372864</t>
   </si>
   <si>
     <t xml:space="preserve">0.530332744121552</t>
@@ -3263,13 +3263,13 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617466211319</t>
+    <t xml:space="preserve">0.496617496013641</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505729675292969</t>
+    <t xml:space="preserve">0.505729734897614</t>
   </si>
   <si>
     <t xml:space="preserve">0.494794994592667</t>
@@ -3278,25 +3278,25 @@
     <t xml:space="preserve">0.499351114034653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497528702020645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492061346769333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488416403532028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483860313892365</t>
+    <t xml:space="preserve">0.497528672218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492061376571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488416433334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483860343694687</t>
   </si>
   <si>
     <t xml:space="preserve">0.487505257129669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495706260204315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493883788585663</t>
+    <t xml:space="preserve">0.495706230401993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49388375878334</t>
   </si>
   <si>
     <t xml:space="preserve">0.491150081157684</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">0.517575621604919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489643454551697</t>
+    <t xml:space="preserve">0.489643424749374</t>
   </si>
   <si>
     <t xml:space="preserve">0.48199275135994</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">0.475776553153992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47673287987709</t>
+    <t xml:space="preserve">0.476732909679413</t>
   </si>
   <si>
     <t xml:space="preserve">0.480080038309097</t>
@@ -3329,31 +3329,31 @@
     <t xml:space="preserve">0.46477872133255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473385751247406</t>
+    <t xml:space="preserve">0.473385721445084</t>
   </si>
   <si>
     <t xml:space="preserve">0.469560384750366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470994919538498</t>
+    <t xml:space="preserve">0.470994889736176</t>
   </si>
   <si>
     <t xml:space="preserve">0.459040701389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453780859708786</t>
+    <t xml:space="preserve">0.453780889511108</t>
   </si>
   <si>
     <t xml:space="preserve">0.451390027999878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447564661502838</t>
+    <t xml:space="preserve">0.447564691305161</t>
   </si>
   <si>
     <t xml:space="preserve">0.45091187953949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441826701164246</t>
+    <t xml:space="preserve">0.441826671361923</t>
   </si>
   <si>
     <t xml:space="preserve">0.438479512929916</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">0.432741492986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436088651418686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438001364469528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441348493099213</t>
+    <t xml:space="preserve">0.436088681221008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438001334667206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441348522901535</t>
   </si>
   <si>
     <t xml:space="preserve">0.446608364582062</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">0.436566829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438957691192627</t>
+    <t xml:space="preserve">0.438957661390305</t>
   </si>
   <si>
     <t xml:space="preserve">0.444695681333542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439435839653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4336978495121</t>
+    <t xml:space="preserve">0.439435869455338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433697819709778</t>
   </si>
   <si>
     <t xml:space="preserve">0.434654176235199</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">0.46669140458107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454737216234207</t>
+    <t xml:space="preserve">0.454737186431885</t>
   </si>
   <si>
     <t xml:space="preserve">0.455693542957306</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">0.561368525028229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538416504859924</t>
+    <t xml:space="preserve">0.538416564464569</t>
   </si>
   <si>
     <t xml:space="preserve">0.544154524803162</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">0.540329158306122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525984168052673</t>
+    <t xml:space="preserve">0.525984108448029</t>
   </si>
   <si>
     <t xml:space="preserve">0.517377138137817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525027811527252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521202445030212</t>
+    <t xml:space="preserve">0.525027871131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521202504634857</t>
   </si>
   <si>
     <t xml:space="preserve">0.519289791584015</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">0.531722128391266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518333494663239</t>
+    <t xml:space="preserve">0.518333435058594</t>
   </si>
   <si>
     <t xml:space="preserve">0.514508128166199</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">0.527896821498871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526940524578094</t>
+    <t xml:space="preserve">0.52694046497345</t>
   </si>
   <si>
     <t xml:space="preserve">0.535547494888306</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">0.553717851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568062901496887</t>
+    <t xml:space="preserve">0.568062841892242</t>
   </si>
   <si>
     <t xml:space="preserve">0.55849951505661</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">0.555630505084991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55467414855957</t>
+    <t xml:space="preserve">0.554674208164215</t>
   </si>
   <si>
     <t xml:space="preserve">0.557543218135834</t>
@@ -3491,16 +3491,16 @@
     <t xml:space="preserve">0.54702353477478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537460088729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551805257797241</t>
+    <t xml:space="preserve">0.537460148334503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551805198192596</t>
   </si>
   <si>
     <t xml:space="preserve">0.524071455001831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533634841442108</t>
+    <t xml:space="preserve">0.533634901046753</t>
   </si>
   <si>
     <t xml:space="preserve">0.536503851413727</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">0.522158801555634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529809474945068</t>
+    <t xml:space="preserve">0.529809534549713</t>
   </si>
   <si>
     <t xml:space="preserve">0.532678484916687</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">0.499206781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496337741613388</t>
+    <t xml:space="preserve">0.49633777141571</t>
   </si>
   <si>
     <t xml:space="preserve">0.506857395172119</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">0.487730741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483905375003815</t>
+    <t xml:space="preserve">0.483905404806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.461909741163254</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">0.478167414665222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468604058027267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471473038196564</t>
+    <t xml:space="preserve">0.46860408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471473067998886</t>
   </si>
   <si>
     <t xml:space="preserve">0.48260822892189</t>
@@ -3942,6 +3942,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.601999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602999985218048</t>
   </si>
 </sst>
 </file>
@@ -69020,7 +69023,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6497685185</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>502589</v>
@@ -69041,6 +69044,32 @@
         <v>1309</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6495023148</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>785187</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>0.603999972343445</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>0.583999991416931</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>0.597000002861023</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>0.602999985218048</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1310</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="1316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="1317">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,22 +44,22 @@
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327446222305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321156322956085</t>
+    <t xml:space="preserve">0.327446281909943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321156293153763</t>
   </si>
   <si>
     <t xml:space="preserve">0.317678362131119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307318449020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288448750972748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289336681365967</t>
+    <t xml:space="preserve">0.307318478822708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288448721170425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289336711168289</t>
   </si>
   <si>
     <t xml:space="preserve">0.294368624687195</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">0.285636752843857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796856403351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258997023105621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258257061243057</t>
+    <t xml:space="preserve">0.273796886205673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258997052907944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258257031440735</t>
   </si>
   <si>
     <t xml:space="preserve">0.243605211377144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246417209506035</t>
+    <t xml:space="preserve">0.246417179703712</t>
   </si>
   <si>
     <t xml:space="preserve">0.262696951627731</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">0.256407082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.259811013936996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261512994766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253817111253738</t>
+    <t xml:space="preserve">0.259811043739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261513024568558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253817081451416</t>
   </si>
   <si>
     <t xml:space="preserve">0.253077119588852</t>
@@ -104,19 +104,19 @@
     <t xml:space="preserve">0.286894708871841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284600734710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277496844530106</t>
+    <t xml:space="preserve">0.284600764513016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277496814727783</t>
   </si>
   <si>
     <t xml:space="preserve">0.28711673617363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290742665529251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263806998729706</t>
+    <t xml:space="preserve">0.290742635726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263806968927383</t>
   </si>
   <si>
     <t xml:space="preserve">0.256777077913284</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">0.277570813894272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297994583845139</t>
+    <t xml:space="preserve">0.297994613647461</t>
   </si>
   <si>
     <t xml:space="preserve">0.310796469449997</t>
@@ -137,19 +137,19 @@
     <t xml:space="preserve">0.303544491529465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304358512163162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318122357130051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309686422348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301620572805405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310352444648743</t>
+    <t xml:space="preserve">0.30435848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318122327327728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309686452150345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301620543003082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31035241484642</t>
   </si>
   <si>
     <t xml:space="preserve">0.323376297950745</t>
@@ -158,85 +158,85 @@
     <t xml:space="preserve">0.320046335458755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316716343164444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315236389636993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315606415271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332996189594269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332256227731705</t>
+    <t xml:space="preserve">0.316716372966766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315236419439316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315606385469437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332996129989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332256197929382</t>
   </si>
   <si>
     <t xml:space="preserve">0.328852236270905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330480188131332</t>
+    <t xml:space="preserve">0.330480217933655</t>
   </si>
   <si>
     <t xml:space="preserve">0.311240434646606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312054395675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299696534872055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296884626150131</t>
+    <t xml:space="preserve">0.312054425477982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2996965944767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296884596347809</t>
   </si>
   <si>
     <t xml:space="preserve">0.299400568008423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297476559877396</t>
+    <t xml:space="preserve">0.297476589679718</t>
   </si>
   <si>
     <t xml:space="preserve">0.295996606349945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293702632188797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298216611146927</t>
+    <t xml:space="preserve">0.293702661991119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298216551542282</t>
   </si>
   <si>
     <t xml:space="preserve">0.286376684904099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276756882667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274536818265915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272316873073578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268542945384979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270466923713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26506495475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268172979354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268616944551468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269208878278732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275276869535446</t>
+    <t xml:space="preserve">0.276756823062897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274536848068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2723169028759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268542885780334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270466893911362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265064984560013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268172919750214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26861697435379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269208908081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275276839733124</t>
   </si>
   <si>
     <t xml:space="preserve">0.284896731376648</t>
@@ -245,28 +245,28 @@
     <t xml:space="preserve">0.290002673864365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308206468820572</t>
+    <t xml:space="preserve">0.308206528425217</t>
   </si>
   <si>
     <t xml:space="preserve">0.309168457984924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318196356296539</t>
+    <t xml:space="preserve">0.318196326494217</t>
   </si>
   <si>
     <t xml:space="preserve">0.316938370466232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308946490287781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314200401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321378290653229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319380313158035</t>
+    <t xml:space="preserve">0.308946430683136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314200431108475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321378320455551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31938037276268</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722440481186</t>
@@ -275,31 +275,31 @@
     <t xml:space="preserve">0.313682407140732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313312381505966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307096511125565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30761444568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304950475692749</t>
+    <t xml:space="preserve">0.313312411308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307096481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307614475488663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304950535297394</t>
   </si>
   <si>
     <t xml:space="preserve">0.305616497993469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299548536539078</t>
+    <t xml:space="preserve">0.2995485663414</t>
   </si>
   <si>
     <t xml:space="preserve">0.305320501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295626670122147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300954550504684</t>
+    <t xml:space="preserve">0.295626610517502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300954520702362</t>
   </si>
   <si>
     <t xml:space="preserve">0.314400315284729</t>
@@ -308,16 +308,16 @@
     <t xml:space="preserve">0.318779796361923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318856596946716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318395614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3199323117733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318088293075562</t>
+    <t xml:space="preserve">0.318856626749039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318395644426346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319932281970978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318088263273239</t>
   </si>
   <si>
     <t xml:space="preserve">0.307331681251526</t>
@@ -326,13 +326,13 @@
     <t xml:space="preserve">0.321776270866394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320393294095993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311557471752167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305795043706894</t>
+    <t xml:space="preserve">0.320393264293671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311557501554489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305795013904572</t>
   </si>
   <si>
     <t xml:space="preserve">0.301569223403931</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">0.295806735754013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299648344516754</t>
+    <t xml:space="preserve">0.299648374319077</t>
   </si>
   <si>
     <t xml:space="preserve">0.296575099229813</t>
@@ -365,67 +365,67 @@
     <t xml:space="preserve">0.310020834207535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311941683292389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311173290014267</t>
+    <t xml:space="preserve">0.311941653490067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311173349618912</t>
   </si>
   <si>
     <t xml:space="preserve">0.30725485086441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306716978549957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305564522743225</t>
+    <t xml:space="preserve">0.30671700835228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305564552545547</t>
   </si>
   <si>
     <t xml:space="preserve">0.304949879646301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306870669126511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297727555036545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301799684762955</t>
+    <t xml:space="preserve">0.306870639324188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297727584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301799714565277</t>
   </si>
   <si>
     <t xml:space="preserve">0.304027855396271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300032556056976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313478320837021</t>
+    <t xml:space="preserve">0.300032615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313478291034698</t>
   </si>
   <si>
     <t xml:space="preserve">0.312556326389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307869523763657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311480641365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298265427350998</t>
+    <t xml:space="preserve">0.307869493961334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311480611562729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298265397548676</t>
   </si>
   <si>
     <t xml:space="preserve">0.299110561609268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305257171392441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295576244592667</t>
+    <t xml:space="preserve">0.305257201194763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295576214790344</t>
   </si>
   <si>
     <t xml:space="preserve">0.295960396528244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297650694847107</t>
+    <t xml:space="preserve">0.297650724649429</t>
   </si>
   <si>
     <t xml:space="preserve">0.297881215810776</t>
@@ -434,34 +434,34 @@
     <t xml:space="preserve">0.293732225894928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298803269863129</t>
+    <t xml:space="preserve">0.298803240060806</t>
   </si>
   <si>
     <t xml:space="preserve">0.300416737794876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300109356641769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298880040645599</t>
+    <t xml:space="preserve">0.300109386444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298880070447922</t>
   </si>
   <si>
     <t xml:space="preserve">0.30548769235611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30955982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303105860948563</t>
+    <t xml:space="preserve">0.309559851884842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303105890750885</t>
   </si>
   <si>
     <t xml:space="preserve">0.303566873073578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308253705501556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304873079061508</t>
+    <t xml:space="preserve">0.308253675699234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304873049259186</t>
   </si>
   <si>
     <t xml:space="preserve">0.306563347578049</t>
@@ -470,34 +470,34 @@
     <t xml:space="preserve">0.30018624663353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298649609088898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296421408653259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301415592432022</t>
+    <t xml:space="preserve">0.298649579286575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296421378850937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3014155626297</t>
   </si>
   <si>
     <t xml:space="preserve">0.300647228956223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282975614070892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291965067386627</t>
+    <t xml:space="preserve">0.282975643873215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29196509718895</t>
   </si>
   <si>
     <t xml:space="preserve">0.289736956357956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293501764535904</t>
+    <t xml:space="preserve">0.293501734733582</t>
   </si>
   <si>
     <t xml:space="preserve">0.292656570672989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29250293970108</t>
+    <t xml:space="preserve">0.292502909898758</t>
   </si>
   <si>
     <t xml:space="preserve">0.289583295583725</t>
@@ -518,106 +518,106 @@
     <t xml:space="preserve">0.292887091636658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293117582798004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291888296604156</t>
+    <t xml:space="preserve">0.293117612600327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291888266801834</t>
   </si>
   <si>
     <t xml:space="preserve">0.289813786745071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286586791276932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294270128011703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291811406612396</t>
+    <t xml:space="preserve">0.286586821079254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294270068407059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291811436414719</t>
   </si>
   <si>
     <t xml:space="preserve">0.292579770088196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29572993516922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298419028520584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294731050729752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287355154752731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293809145689011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29204198718071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286740481853485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284666001796722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278903514146805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27559968829155</t>
+    <t xml:space="preserve">0.295729905366898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298419058322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294731080532074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287355124950409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293809115886688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292041957378387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286740452051163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284665942192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278903543949127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275599718093872</t>
   </si>
   <si>
     <t xml:space="preserve">0.270221382379532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272449553012848</t>
+    <t xml:space="preserve">0.272449523210526</t>
   </si>
   <si>
     <t xml:space="preserve">0.276675343513489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273986160755157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275676548480988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275522857904434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276598513126373</t>
+    <t xml:space="preserve">0.27398619055748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275676518678665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275522828102112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276598542928696</t>
   </si>
   <si>
     <t xml:space="preserve">0.270989716053009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27114337682724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274293541908264</t>
+    <t xml:space="preserve">0.271143406629562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274293571710587</t>
   </si>
   <si>
     <t xml:space="preserve">0.270451903343201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268146902322769</t>
+    <t xml:space="preserve">0.268146872520447</t>
   </si>
   <si>
     <t xml:space="preserve">0.267378598451614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264612585306168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265765100717545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262384414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267532259225845</t>
+    <t xml:space="preserve">0.264612555503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2657650411129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262384444475174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267532229423523</t>
   </si>
   <si>
     <t xml:space="preserve">0.265304088592529</t>
@@ -629,43 +629,43 @@
     <t xml:space="preserve">0.272526383399963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283282965421677</t>
+    <t xml:space="preserve">0.283282995223999</t>
   </si>
   <si>
     <t xml:space="preserve">0.279902338981628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277059495449066</t>
+    <t xml:space="preserve">0.277059525251389</t>
   </si>
   <si>
     <t xml:space="preserve">0.27844250202179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280517011880875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278749853372574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278980314731598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278212010860443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284051328897476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290812611579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289660155773163</t>
+    <t xml:space="preserve">0.280516982078552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278749823570251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27898034453392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278212040662766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284051299095154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290812641382217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28966012597084</t>
   </si>
   <si>
     <t xml:space="preserve">0.290428429841995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294807910919189</t>
+    <t xml:space="preserve">0.294807940721512</t>
   </si>
   <si>
     <t xml:space="preserve">0.295422583818436</t>
@@ -674,25 +674,25 @@
     <t xml:space="preserve">0.288507610559464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284589141607285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291043132543564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293885886669159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294884711503983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289890587329865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286125779151917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284358650445938</t>
+    <t xml:space="preserve">0.284589171409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291043102741241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293885916471481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294884741306305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289890617132187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286125808954239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284358620643616</t>
   </si>
   <si>
     <t xml:space="preserve">0.282745182514191</t>
@@ -701,22 +701,22 @@
     <t xml:space="preserve">0.277290046215057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281976848840714</t>
+    <t xml:space="preserve">0.281976789236069</t>
   </si>
   <si>
     <t xml:space="preserve">0.276214331388474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273602038621902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269760370254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275061875581741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271834880113602</t>
+    <t xml:space="preserve">0.273602068424225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269760400056839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275061845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271834909915924</t>
   </si>
   <si>
     <t xml:space="preserve">0.273371547460556</t>
@@ -725,31 +725,31 @@
     <t xml:space="preserve">0.275215536355972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276905804872513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274831354618073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282668352127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280440151691437</t>
+    <t xml:space="preserve">0.276905834674835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27483132481575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282668322324753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280440181493759</t>
   </si>
   <si>
     <t xml:space="preserve">0.279595017433167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27736684679985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278135180473328</t>
+    <t xml:space="preserve">0.277366816997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278135150671005</t>
   </si>
   <si>
     <t xml:space="preserve">0.281208485364914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278672933578491</t>
+    <t xml:space="preserve">0.278672993183136</t>
   </si>
   <si>
     <t xml:space="preserve">0.282591491937637</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">0.279364496469498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285587936639786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27967181801796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28666365146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284435480833054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281900018453598</t>
+    <t xml:space="preserve">0.285587966442108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279671788215637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286663621664047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284435451030731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281899988651276</t>
   </si>
   <si>
     <t xml:space="preserve">0.283897697925568</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">0.285434275865555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295038402080536</t>
+    <t xml:space="preserve">0.295038431882858</t>
   </si>
   <si>
     <t xml:space="preserve">0.304258346557617</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">0.321929931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325617909431458</t>
+    <t xml:space="preserve">0.32561793923378</t>
   </si>
   <si>
     <t xml:space="preserve">0.33184140920639</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">0.309790343046188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309252470731735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311096519231796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313094168901443</t>
+    <t xml:space="preserve">0.309252500534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311096489429474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313094139099121</t>
   </si>
   <si>
     <t xml:space="preserve">0.313017338514328</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">0.288891792297363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293040782213211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295192062854767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296805560588837</t>
+    <t xml:space="preserve">0.293040752410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295192092657089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296805590391159</t>
   </si>
   <si>
     <t xml:space="preserve">0.297266572713852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298111736774445</t>
+    <t xml:space="preserve">0.298111766576767</t>
   </si>
   <si>
     <t xml:space="preserve">0.310251325368881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313555151224136</t>
+    <t xml:space="preserve">0.313555121421814</t>
   </si>
   <si>
     <t xml:space="preserve">0.300800889730453</t>
@@ -857,10 +857,10 @@
     <t xml:space="preserve">0.327308267354965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318472474813461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31209534406662</t>
+    <t xml:space="preserve">0.318472415208817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312095314264297</t>
   </si>
   <si>
     <t xml:space="preserve">0.314016163349152</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">0.315014988183975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312249034643173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313939303159714</t>
+    <t xml:space="preserve">0.312249004840851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313939273357391</t>
   </si>
   <si>
     <t xml:space="preserve">0.309636652469635</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">0.308945149183273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313631951808929</t>
+    <t xml:space="preserve">0.313632011413574</t>
   </si>
   <si>
     <t xml:space="preserve">0.308023184537888</t>
@@ -893,25 +893,25 @@
     <t xml:space="preserve">0.307715862989426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309022039175034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309943974018097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3177809715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316551625728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316474825143814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32438862323761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325003266334534</t>
+    <t xml:space="preserve">0.309022009372711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309944003820419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317780941724777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31655165553093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316474795341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324388563632965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325003296136856</t>
   </si>
   <si>
     <t xml:space="preserve">0.318318784236908</t>
@@ -923,46 +923,46 @@
     <t xml:space="preserve">0.321545779705048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320470094680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621494531631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323697090148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333454877138138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327385067939758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331764578819275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339524656534195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345671355724335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340446680784225</t>
+    <t xml:space="preserve">0.320470124483109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621434926987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323697060346603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333454847335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327385038137436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331764549016953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339524686336517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345671325922012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340446710586548</t>
   </si>
   <si>
     <t xml:space="preserve">0.333378046751022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334991544485092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336144030094147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337757498025894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338910043239594</t>
+    <t xml:space="preserve">0.334991484880447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336144059896469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337757527828217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338910013437271</t>
   </si>
   <si>
     <t xml:space="preserve">0.338141679763794</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">0.339678317308426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350358158349991</t>
+    <t xml:space="preserve">0.350358128547668</t>
   </si>
   <si>
     <t xml:space="preserve">0.346593290567398</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">0.338218539953232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346900641918182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346132308244705</t>
+    <t xml:space="preserve">0.34690061211586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346132338047028</t>
   </si>
   <si>
     <t xml:space="preserve">0.33960148692131</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">0.36541736125946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363035500049591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374099463224411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371103048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369566351175308</t>
+    <t xml:space="preserve">0.363035529851913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374099493026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371103018522263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369566380977631</t>
   </si>
   <si>
     <t xml:space="preserve">0.368798017501831</t>
@@ -1028,106 +1028,106 @@
     <t xml:space="preserve">0.366108864545822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363112419843674</t>
+    <t xml:space="preserve">0.363112390041351</t>
   </si>
   <si>
     <t xml:space="preserve">0.3686443567276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366877198219299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366262525320053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361114710569382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359885424375534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35919389128685</t>
+    <t xml:space="preserve">0.366877168416977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366262555122375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361114740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359885394573212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359193861484528</t>
   </si>
   <si>
     <t xml:space="preserve">0.368567526340485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372024983167648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37555930018425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380246102809906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392616212368011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405677825212479</t>
+    <t xml:space="preserve">0.372025012969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375559329986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380246132612228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392616182565689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405677855014801</t>
   </si>
   <si>
     <t xml:space="preserve">0.421044379472733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419507771730423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396842032670975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413361132144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422581106424332</t>
+    <t xml:space="preserve">0.419507741928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396842062473297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41336116194725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422581076622009</t>
   </si>
   <si>
     <t xml:space="preserve">0.417586922645569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42642268538475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423349440097809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427959352731705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436795145273209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432953506708145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452930092811584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460824728012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465223371982574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296617269516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481358289718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522463917732239</t>
+    <t xml:space="preserve">0.426422744989395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423349410295486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427959322929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436795175075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432953536510468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45293003320694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460884332657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465223401784897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296647071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481358259916306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522463798522949</t>
   </si>
   <si>
     <t xml:space="preserve">0.515164732933044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505560576915741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50709730386734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515548884868622</t>
+    <t xml:space="preserve">0.505560636520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507097244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515548944473267</t>
   </si>
   <si>
     <t xml:space="preserve">0.503255605697632</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">0.48980987071991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480205714702606</t>
+    <t xml:space="preserve">0.480205744504929</t>
   </si>
   <si>
     <t xml:space="preserve">0.519006371498108</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">0.511323034763336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499413996934891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491730630397797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484431594610214</t>
+    <t xml:space="preserve">0.499413967132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491730719804764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484431564807892</t>
   </si>
   <si>
     <t xml:space="preserve">0.483663141727448</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">0.484815716743469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495188146829605</t>
+    <t xml:space="preserve">0.495188176631927</t>
   </si>
   <si>
     <t xml:space="preserve">0.490194022655487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553197026252747</t>
+    <t xml:space="preserve">0.553197085857391</t>
   </si>
   <si>
     <t xml:space="preserve">0.542056202888489</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">0.56280118227005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586235165596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600065112113953</t>
+    <t xml:space="preserve">0.586235225200653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600065231323242</t>
   </si>
   <si>
     <t xml:space="preserve">0.58239358663559</t>
@@ -1193,76 +1193,76 @@
     <t xml:space="preserve">0.552428662776947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551276206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545129537582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565874516963959</t>
+    <t xml:space="preserve">0.55127614736557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545129597187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565874397754669</t>
   </si>
   <si>
     <t xml:space="preserve">0.577015221118927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596607625484467</t>
+    <t xml:space="preserve">0.596607685089111</t>
   </si>
   <si>
     <t xml:space="preserve">0.584698498249054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608132541179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621962487697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620425820350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629645764827728</t>
+    <t xml:space="preserve">0.608132421970367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621962428092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620425879955292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629645824432373</t>
   </si>
   <si>
     <t xml:space="preserve">0.614279210567474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607748448848724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58162522315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560880303382874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598528385162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598144292831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619657576084137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618120908737183</t>
+    <t xml:space="preserve">0.60774838924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581625282764435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560880362987518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598528444766998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598144233226776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619657516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618120849132538</t>
   </si>
   <si>
     <t xml:space="preserve">0.601601779460907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586619436740875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59545511007309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587771773338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584314405918121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577399373054504</t>
+    <t xml:space="preserve">0.58661937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595455169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587771832942963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584314346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577399432659149</t>
   </si>
   <si>
     <t xml:space="preserve">0.567026913166046</t>
@@ -1271,25 +1271,25 @@
     <t xml:space="preserve">0.57432609796524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543592929840088</t>
+    <t xml:space="preserve">0.543592870235443</t>
   </si>
   <si>
     <t xml:space="preserve">0.564721941947937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.563185214996338</t>
+    <t xml:space="preserve">0.563185334205627</t>
   </si>
   <si>
     <t xml:space="preserve">0.576246917247772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583930134773254</t>
+    <t xml:space="preserve">0.583930194377899</t>
   </si>
   <si>
     <t xml:space="preserve">0.58085685968399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587003529071808</t>
+    <t xml:space="preserve">0.587003469467163</t>
   </si>
   <si>
     <t xml:space="preserve">0.604675054550171</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">0.629261612892151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61850494146347</t>
+    <t xml:space="preserve">0.618505001068115</t>
   </si>
   <si>
     <t xml:space="preserve">0.606980085372925</t>
@@ -1307,43 +1307,43 @@
     <t xml:space="preserve">0.603138446807861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612358450889587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611590087413788</t>
+    <t xml:space="preserve">0.612358391284943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611590027809143</t>
   </si>
   <si>
     <t xml:space="preserve">0.593918442726135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596991837024689</t>
+    <t xml:space="preserve">0.596991717815399</t>
   </si>
   <si>
     <t xml:space="preserve">0.608516693115234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599296689033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589308500289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553965449333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538598656654358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55703866481781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536293804645538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524000465869904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537830412387848</t>
+    <t xml:space="preserve">0.599296748638153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589308559894562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553965389728546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538598716259003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557038724422455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536293745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524000585079193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537830471992493</t>
   </si>
   <si>
     <t xml:space="preserve">0.547818720340729</t>
@@ -1352,22 +1352,22 @@
     <t xml:space="preserve">0.532452166080475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537062168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527073860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520927250385284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517853856086731</t>
+    <t xml:space="preserve">0.537062108516693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527073800563812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52092719078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517853915691376</t>
   </si>
   <si>
     <t xml:space="preserve">0.525537192821503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530147135257721</t>
+    <t xml:space="preserve">0.530147194862366</t>
   </si>
   <si>
     <t xml:space="preserve">0.523232221603394</t>
@@ -1376,49 +1376,49 @@
     <t xml:space="preserve">0.51939058303833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524768829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549355328083038</t>
+    <t xml:space="preserve">0.524768888950348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549355387687683</t>
   </si>
   <si>
     <t xml:space="preserve">0.501718997955322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492498993873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477900683879852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476364076137543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488657385110855</t>
+    <t xml:space="preserve">0.492499023675919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477900743484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476364135742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488657355308533</t>
   </si>
   <si>
     <t xml:space="preserve">0.471754193305969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472522467374802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468680828809738</t>
+    <t xml:space="preserve">0.472522437572479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468680858612061</t>
   </si>
   <si>
     <t xml:space="preserve">0.487120717763901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481742352247238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480974137783051</t>
+    <t xml:space="preserve">0.481742411851883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480974107980728</t>
   </si>
   <si>
     <t xml:space="preserve">0.483279049396515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478669136762619</t>
+    <t xml:space="preserve">0.478669166564941</t>
   </si>
   <si>
     <t xml:space="preserve">0.47021746635437</t>
@@ -1427,16 +1427,16 @@
     <t xml:space="preserve">0.467912524938583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466375768184662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839220046997</t>
+    <t xml:space="preserve">0.466375797986984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839190244675</t>
   </si>
   <si>
     <t xml:space="preserve">0.461765915155411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487889051437378</t>
+    <t xml:space="preserve">0.487889021635056</t>
   </si>
   <si>
     <t xml:space="preserve">0.500182330608368</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">0.382627964019775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379170477390289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382243782281876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385701239109039</t>
+    <t xml:space="preserve">0.379170447587967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382243812084198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385701268911362</t>
   </si>
   <si>
     <t xml:space="preserve">0.388774573802948</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">0.364956378936768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360346406698227</t>
+    <t xml:space="preserve">0.360346436500549</t>
   </si>
   <si>
     <t xml:space="preserve">0.3522789478302</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">0.356504738330841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371487200260162</t>
+    <t xml:space="preserve">0.371487140655518</t>
   </si>
   <si>
     <t xml:space="preserve">0.368029683828354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372255504131317</t>
+    <t xml:space="preserve">0.37225553393364</t>
   </si>
   <si>
     <t xml:space="preserve">0.365340530872345</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">0.3664930164814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374560475349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374176353216171</t>
+    <t xml:space="preserve">0.374560534954071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374176323413849</t>
   </si>
   <si>
     <t xml:space="preserve">0.37878629565239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362267225980759</t>
+    <t xml:space="preserve">0.362267255783081</t>
   </si>
   <si>
     <t xml:space="preserve">0.353815615177155</t>
@@ -1541,28 +1541,28 @@
     <t xml:space="preserve">0.353047311306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370718866586685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354199796915054</t>
+    <t xml:space="preserve">0.37071880698204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35419973731041</t>
   </si>
   <si>
     <t xml:space="preserve">0.395689517259598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411056160926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407982856035233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384932935237885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390311241149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378018021583557</t>
+    <t xml:space="preserve">0.411056131124496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407982796430588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384932965040207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39031121134758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378017961978912</t>
   </si>
   <si>
     <t xml:space="preserve">0.380707114934921</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">0.35957807302475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353431433439255</t>
+    <t xml:space="preserve">0.353431463241577</t>
   </si>
   <si>
     <t xml:space="preserve">0.349589794874191</t>
@@ -1583,40 +1583,40 @@
     <t xml:space="preserve">0.344979822635651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343059003353119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354968130588531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.364188075065613</t>
+    <t xml:space="preserve">0.343058973550797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354968100786209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36418804526329</t>
   </si>
   <si>
     <t xml:space="preserve">0.357273101806641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349973946809769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339217334985733</t>
+    <t xml:space="preserve">0.349973976612091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339217394590378</t>
   </si>
   <si>
     <t xml:space="preserve">0.323850780725479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361883074045181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350742280483246</t>
+    <t xml:space="preserve">0.361883014440536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350742250680923</t>
   </si>
   <si>
     <t xml:space="preserve">0.38954296708107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404141187667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396457850933075</t>
+    <t xml:space="preserve">0.404141157865524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396457880735397</t>
   </si>
   <si>
     <t xml:space="preserve">0.412592798471451</t>
@@ -1625,55 +1625,55 @@
     <t xml:space="preserve">0.404909521341324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401836216449738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394152879714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399531155824661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402604460716248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401067852973938</t>
+    <t xml:space="preserve">0.401836186647415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394152909517288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399531185626984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40260449051857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40106788277626</t>
   </si>
   <si>
     <t xml:space="preserve">0.397994518280029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375712990760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.364572256803513</t>
+    <t xml:space="preserve">0.375712960958481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36457222700119</t>
   </si>
   <si>
     <t xml:space="preserve">0.345748096704483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336528211832047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335759907960892</t>
+    <t xml:space="preserve">0.336528241634369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335759878158569</t>
   </si>
   <si>
     <t xml:space="preserve">0.337296515703201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329613268375397</t>
+    <t xml:space="preserve">0.329613238573074</t>
   </si>
   <si>
     <t xml:space="preserve">0.328076541423798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331534057855606</t>
+    <t xml:space="preserve">0.331534028053284</t>
   </si>
   <si>
     <t xml:space="preserve">0.319240808486938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326924085617065</t>
+    <t xml:space="preserve">0.326924055814743</t>
   </si>
   <si>
     <t xml:space="preserve">0.312709987163544</t>
@@ -1682,43 +1682,43 @@
     <t xml:space="preserve">0.34113821387291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322698265314102</t>
+    <t xml:space="preserve">0.322698295116425</t>
   </si>
   <si>
     <t xml:space="preserve">0.326155751943588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324619114398956</t>
+    <t xml:space="preserve">0.324619084596634</t>
   </si>
   <si>
     <t xml:space="preserve">0.325771570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330381572246552</t>
+    <t xml:space="preserve">0.330381542444229</t>
   </si>
   <si>
     <t xml:space="preserve">0.329997390508652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324234962463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313862502574921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301185071468353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303874224424362</t>
+    <t xml:space="preserve">0.324234932661057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313862472772598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301185011863708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30387419462204</t>
   </si>
   <si>
     <t xml:space="preserve">0.296959221363068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302721709012985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082387447357</t>
+    <t xml:space="preserve">0.302721738815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32308241724968</t>
   </si>
   <si>
     <t xml:space="preserve">0.308100014925003</t>
@@ -1727,19 +1727,19 @@
     <t xml:space="preserve">0.310405015945435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306947559118271</t>
+    <t xml:space="preserve">0.306947529315948</t>
   </si>
   <si>
     <t xml:space="preserve">0.314630806446075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305410832166672</t>
+    <t xml:space="preserve">0.305410861968994</t>
   </si>
   <si>
     <t xml:space="preserve">0.30848416686058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304642528295517</t>
+    <t xml:space="preserve">0.304642498493195</t>
   </si>
   <si>
     <t xml:space="preserve">0.320777416229248</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">0.356888920068741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358041375875473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356120556592941</t>
+    <t xml:space="preserve">0.358041405677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356120586395264</t>
   </si>
   <si>
     <t xml:space="preserve">0.360730588436127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358809769153595</t>
+    <t xml:space="preserve">0.358809739351273</t>
   </si>
   <si>
     <t xml:space="preserve">0.351126432418823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355736404657364</t>
+    <t xml:space="preserve">0.355736434459686</t>
   </si>
   <si>
     <t xml:space="preserve">0.342290639877319</t>
@@ -1772,25 +1772,25 @@
     <t xml:space="preserve">0.37187135219574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370334684848785</t>
+    <t xml:space="preserve">0.370334655046463</t>
   </si>
   <si>
     <t xml:space="preserve">0.383780419826508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376097172498703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376865446567535</t>
+    <t xml:space="preserve">0.376097142696381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376865476369858</t>
   </si>
   <si>
     <t xml:space="preserve">0.377249658107758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398762851953506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403372794389725</t>
+    <t xml:space="preserve">0.398762881755829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403372824192047</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446129083633</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">0.409519463777542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391079545021057</t>
+    <t xml:space="preserve">0.39107957482338</t>
   </si>
   <si>
     <t xml:space="preserve">0.381475448608398</t>
@@ -1808,22 +1808,22 @@
     <t xml:space="preserve">0.407214462757111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387237906455994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394921243190765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411824494600296</t>
+    <t xml:space="preserve">0.387237936258316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394921183586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411824464797974</t>
   </si>
   <si>
     <t xml:space="preserve">0.41489776968956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417202740907669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397226214408875</t>
+    <t xml:space="preserve">0.417202711105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397226184606552</t>
   </si>
   <si>
     <t xml:space="preserve">0.408751159906387</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">0.410287767648697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414129436016083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416434466838837</t>
+    <t xml:space="preserve">0.414129376411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416434437036514</t>
   </si>
   <si>
     <t xml:space="preserve">0.418739438056946</t>
@@ -1844,40 +1844,40 @@
     <t xml:space="preserve">0.420276075601578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421812742948532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430264383554459</t>
+    <t xml:space="preserve">0.421812772750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430264353752136</t>
   </si>
   <si>
     <t xml:space="preserve">0.473290771245956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494804054498672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484047383069992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267327547073</t>
+    <t xml:space="preserve">0.49480402469635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484047412872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267387151718</t>
   </si>
   <si>
     <t xml:space="preserve">0.506328940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479437470436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482510805130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595861673355</t>
+    <t xml:space="preserve">0.479437410831451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482510715723038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595891475677</t>
   </si>
   <si>
     <t xml:space="preserve">0.464070826768875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465607523918152</t>
+    <t xml:space="preserve">0.465607464313507</t>
   </si>
   <si>
     <t xml:space="preserve">0.460997551679611</t>
@@ -1886,79 +1886,79 @@
     <t xml:space="preserve">0.453314214944839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434106051921844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789269447327</t>
+    <t xml:space="preserve">0.4341059923172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789239645004</t>
   </si>
   <si>
     <t xml:space="preserve">0.445630937814713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449472576379776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451009273529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460229188203812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454082578420639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457155853509903</t>
+    <t xml:space="preserve">0.449472546577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451009303331375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460229218006134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454082608222961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457155913114548</t>
   </si>
   <si>
     <t xml:space="preserve">0.451777577400208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456387519836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46330252289772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470985770225525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467144161462784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457924276590347</t>
+    <t xml:space="preserve">0.456387490034103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463302463293076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47098582983017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467144191265106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457924216985703</t>
   </si>
   <si>
     <t xml:space="preserve">0.447167605161667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43256938457489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437947630882263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433337658643723</t>
+    <t xml:space="preserve">0.432569354772568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437947660684586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433337688446045</t>
   </si>
   <si>
     <t xml:space="preserve">0.434874325990677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436410993337631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439484357833862</t>
+    <t xml:space="preserve">0.436411023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43948432803154</t>
   </si>
   <si>
     <t xml:space="preserve">0.441020995378494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440252661705017</t>
+    <t xml:space="preserve">0.440252631902695</t>
   </si>
   <si>
     <t xml:space="preserve">0.438715934753418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442557603120804</t>
+    <t xml:space="preserve">0.442557543516159</t>
   </si>
   <si>
     <t xml:space="preserve">0.485584110021591</t>
@@ -1967,19 +1967,19 @@
     <t xml:space="preserve">0.455619186162949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443325966596603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429496049880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435642629861832</t>
+    <t xml:space="preserve">0.443326026201248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429496079683304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435642659664154</t>
   </si>
   <si>
     <t xml:space="preserve">0.450240910053253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42719104886055</t>
+    <t xml:space="preserve">0.427191078662872</t>
   </si>
   <si>
     <t xml:space="preserve">0.375328809022903</t>
@@ -1988,43 +1988,43 @@
     <t xml:space="preserve">0.386469602584839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393384575843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365724742412567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372639656066895</t>
+    <t xml:space="preserve">0.393384605646133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365724712610245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372639685869217</t>
   </si>
   <si>
     <t xml:space="preserve">0.351510614156723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342674851417542</t>
+    <t xml:space="preserve">0.342674821615219</t>
   </si>
   <si>
     <t xml:space="preserve">0.317319959402084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26507356762886</t>
+    <t xml:space="preserve">0.265073597431183</t>
   </si>
   <si>
     <t xml:space="preserve">0.259695291519165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23933456838131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242023691534996</t>
+    <t xml:space="preserve">0.239334583282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242023706436157</t>
   </si>
   <si>
     <t xml:space="preserve">0.234724566340446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245865315198898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258926928043365</t>
+    <t xml:space="preserve">0.245865359902382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258926957845688</t>
   </si>
   <si>
     <t xml:space="preserve">0.251627802848816</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">0.266610264778137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269299328327179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258158594369888</t>
+    <t xml:space="preserve">0.269299358129501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258158624172211</t>
   </si>
   <si>
     <t xml:space="preserve">0.251243650913239</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">0.245097011327744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254701107740402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262000232934952</t>
+    <t xml:space="preserve">0.254701137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262000292539597</t>
   </si>
   <si>
     <t xml:space="preserve">0.254316985607147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261231958866119</t>
+    <t xml:space="preserve">0.261231899261475</t>
   </si>
   <si>
     <t xml:space="preserve">0.262768596410751</t>
@@ -2069,61 +2069,61 @@
     <t xml:space="preserve">0.264689415693283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271988540887833</t>
+    <t xml:space="preserve">0.271988570690155</t>
   </si>
   <si>
     <t xml:space="preserve">0.273909360170364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276982724666595</t>
+    <t xml:space="preserve">0.276982694864273</t>
   </si>
   <si>
     <t xml:space="preserve">0.272756844758987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275445997714996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268915206193924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265841901302338</t>
+    <t xml:space="preserve">0.275446057319641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268915235996246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265841841697693</t>
   </si>
   <si>
     <t xml:space="preserve">0.258542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265457779169083</t>
+    <t xml:space="preserve">0.265457719564438</t>
   </si>
   <si>
     <t xml:space="preserve">0.263152748346329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292733401060104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32769238948822</t>
+    <t xml:space="preserve">0.292733430862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327692419290543</t>
   </si>
   <si>
     <t xml:space="preserve">0.302337527275085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301953375339508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332302361726761</t>
+    <t xml:space="preserve">0.301953345537186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332302391529083</t>
   </si>
   <si>
     <t xml:space="preserve">0.332686543464661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306179225444794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305026710033417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312325835227966</t>
+    <t xml:space="preserve">0.306179195642471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305026739835739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312325805425644</t>
   </si>
   <si>
     <t xml:space="preserve">0.331918239593506</t>
@@ -2138,73 +2138,73 @@
     <t xml:space="preserve">0.292349249124527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289275974035263</t>
+    <t xml:space="preserve">0.289275944232941</t>
   </si>
   <si>
     <t xml:space="preserve">0.291196793317795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286970973014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2850501537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273525208234787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26084777712822</t>
+    <t xml:space="preserve">0.286970943212509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285050123929977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273525178432465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260847747325897</t>
   </si>
   <si>
     <t xml:space="preserve">0.261616110801697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270067721605301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278519332408905</t>
+    <t xml:space="preserve">0.270067691802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278519362211227</t>
   </si>
   <si>
     <t xml:space="preserve">0.27314105629921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266994386911392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.255469441413879</t>
+    <t xml:space="preserve">0.266994416713715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.255469471216202</t>
   </si>
   <si>
     <t xml:space="preserve">0.25316447019577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256621956825256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256237804889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.249322831630707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236261233687401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238182038068771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25354865193367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267762720584869</t>
+    <t xml:space="preserve">0.256621986627579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256237775087357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.249322816729546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23626121878624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238182067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253548622131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267762750387192</t>
   </si>
   <si>
     <t xml:space="preserve">0.283513456583023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277751058340073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294654250144958</t>
+    <t xml:space="preserve">0.27775102853775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294654279947281</t>
   </si>
   <si>
     <t xml:space="preserve">0.319624960422516</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">0.338449001312256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34075403213501</t>
+    <t xml:space="preserve">0.340754002332687</t>
   </si>
   <si>
     <t xml:space="preserve">0.338833212852478</t>
@@ -2225,28 +2225,28 @@
     <t xml:space="preserve">0.338064849376678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336912363767624</t>
+    <t xml:space="preserve">0.336912333965302</t>
   </si>
   <si>
     <t xml:space="preserve">0.333839058876038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330765753984451</t>
+    <t xml:space="preserve">0.330765724182129</t>
   </si>
   <si>
     <t xml:space="preserve">0.328844904899597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33998566865921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347668945789337</t>
+    <t xml:space="preserve">0.339985698461533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34766897559166</t>
   </si>
   <si>
     <t xml:space="preserve">0.35996225476265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3518947660923</t>
+    <t xml:space="preserve">0.351894795894623</t>
   </si>
   <si>
     <t xml:space="preserve">0.369182199239731</t>
@@ -2258,25 +2258,25 @@
     <t xml:space="preserve">0.355352282524109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348053187131882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346516460180283</t>
+    <t xml:space="preserve">0.348053127527237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346516489982605</t>
   </si>
   <si>
     <t xml:space="preserve">0.347284823656082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363419681787491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373792171478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373023837804794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379554599523544</t>
+    <t xml:space="preserve">0.363419741392136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373792141675949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373023808002472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379554629325867</t>
   </si>
   <si>
     <t xml:space="preserve">0.425654411315918</t>
@@ -2285,25 +2285,25 @@
     <t xml:space="preserve">0.417971104383469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381859630346298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383012115955353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377633810043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378402143716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381091326475143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380322933197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348437339067459</t>
+    <t xml:space="preserve">0.381859600543976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38301208615303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377633839845657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37840211391449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381091296672821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380322962999344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348437309265137</t>
   </si>
   <si>
     <t xml:space="preserve">0.400299549102783</t>
@@ -2312,16 +2312,16 @@
     <t xml:space="preserve">0.383396297693253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379938781261444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388006269931793</t>
+    <t xml:space="preserve">0.379938840866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388006240129471</t>
   </si>
   <si>
     <t xml:space="preserve">0.428727746009827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368413835763931</t>
+    <t xml:space="preserve">0.368413865566254</t>
   </si>
   <si>
     <t xml:space="preserve">0.344595640897751</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">0.341906487941742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323466628789902</t>
+    <t xml:space="preserve">0.323466569185257</t>
   </si>
   <si>
     <t xml:space="preserve">0.340369820594788</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">0.331149905920029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348821431398392</t>
+    <t xml:space="preserve">0.348821461200714</t>
   </si>
   <si>
     <t xml:space="preserve">0.322314113378525</t>
@@ -2351,22 +2351,22 @@
     <t xml:space="preserve">0.285818457603455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337680727243423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345363974571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341522336006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329229086637497</t>
+    <t xml:space="preserve">0.337680697441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345363944768906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341522365808487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329229056835175</t>
   </si>
   <si>
     <t xml:space="preserve">0.353653132915497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351594597101212</t>
+    <t xml:space="preserve">0.351594626903534</t>
   </si>
   <si>
     <t xml:space="preserve">0.354064851999283</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">0.352829724550247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347477585077286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345830738544464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341713726520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342537134885788</t>
+    <t xml:space="preserve">0.347477555274963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345830768346786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341713696718216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34253716468811</t>
   </si>
   <si>
     <t xml:space="preserve">0.348300993442535</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">0.35982871055603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241443634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354888200759888</t>
+    <t xml:space="preserve">0.353241413831711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35488823056221</t>
   </si>
   <si>
     <t xml:space="preserve">0.350359499454498</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">0.339655190706253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342948853969574</t>
+    <t xml:space="preserve">0.342948824167252</t>
   </si>
   <si>
     <t xml:space="preserve">0.341302037239075</t>
@@ -2417,16 +2417,16 @@
     <t xml:space="preserve">0.333479672670364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320716887712479</t>
+    <t xml:space="preserve">0.320716857910156</t>
   </si>
   <si>
     <t xml:space="preserve">0.319070041179657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321540296077728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310835987329483</t>
+    <t xml:space="preserve">0.321540266275406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310835957527161</t>
   </si>
   <si>
     <t xml:space="preserve">0.315776437520981</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">0.312894523143768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31824666261673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317834913730621</t>
+    <t xml:space="preserve">0.318246603012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317834943532944</t>
   </si>
   <si>
     <t xml:space="preserve">0.319481790065765</t>
@@ -2450,25 +2450,25 @@
     <t xml:space="preserve">0.312071084976196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308365762233734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310012578964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314541310071945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318658322095871</t>
+    <t xml:space="preserve">0.308365792036057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310012608766556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314541280269623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318658351898193</t>
   </si>
   <si>
     <t xml:space="preserve">0.320305168628693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322775363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309600859880447</t>
+    <t xml:space="preserve">0.322775393724442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30960088968277</t>
   </si>
   <si>
     <t xml:space="preserve">0.309189170598984</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">0.32195195555687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326892405748367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323187083005905</t>
+    <t xml:space="preserve">0.325245589017868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32689243555069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323187112808228</t>
   </si>
   <si>
     <t xml:space="preserve">0.323598802089691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315364718437195</t>
+    <t xml:space="preserve">0.315364688634872</t>
   </si>
   <si>
     <t xml:space="preserve">0.31330618262291</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">0.310424298048019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314953029155731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311247646808624</t>
+    <t xml:space="preserve">0.314952999353409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311247676610947</t>
   </si>
   <si>
     <t xml:space="preserve">0.317011535167694</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">0.31742325425148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311659425497055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316188156604767</t>
+    <t xml:space="preserve">0.311659395694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316188126802444</t>
   </si>
   <si>
     <t xml:space="preserve">0.319893479347229</t>
@@ -2531,13 +2531,13 @@
     <t xml:space="preserve">0.303013622760773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307542353868484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302601903676987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307954072952271</t>
+    <t xml:space="preserve">0.307542324066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302601963281631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307954043149948</t>
   </si>
   <si>
     <t xml:space="preserve">0.306307256221771</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">0.301366806030273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302190244197845</t>
+    <t xml:space="preserve">0.302190214395523</t>
   </si>
   <si>
     <t xml:space="preserve">0.313717901706696</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">0.328539192676544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340890318155289</t>
+    <t xml:space="preserve">0.340890347957611</t>
   </si>
   <si>
     <t xml:space="preserve">0.356535047292709</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">0.343360543251038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336361557245255</t>
+    <t xml:space="preserve">0.336361587047577</t>
   </si>
   <si>
     <t xml:space="preserve">0.339243501424789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335126429796219</t>
+    <t xml:space="preserve">0.335126489400864</t>
   </si>
   <si>
     <t xml:space="preserve">0.358181864023209</t>
@@ -2591,55 +2591,55 @@
     <t xml:space="preserve">0.3470658659935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34418398141861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336773335933685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345419019460678</t>
+    <t xml:space="preserve">0.344183951616287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336773276329041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345419049263</t>
   </si>
   <si>
     <t xml:space="preserve">0.349124372005463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338008433580399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335949927568436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343772232532501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33759668469429</t>
+    <t xml:space="preserve">0.338008373975754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335949867963791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343772262334824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337596714496613</t>
   </si>
   <si>
     <t xml:space="preserve">0.340066909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340478599071503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332244545221329</t>
+    <t xml:space="preserve">0.340478628873825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332244515419006</t>
   </si>
   <si>
     <t xml:space="preserve">0.329362630844116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325657337903976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33842009305954</t>
+    <t xml:space="preserve">0.325657278299332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338420122861862</t>
   </si>
   <si>
     <t xml:space="preserve">0.346654176712036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355711668729782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359005242586136</t>
+    <t xml:space="preserve">0.35571163892746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359005272388458</t>
   </si>
   <si>
     <t xml:space="preserve">0.370121270418167</t>
@@ -2648,25 +2648,25 @@
     <t xml:space="preserve">0.377943605184555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381648927927017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390294760465622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395235121250153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399763882160187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389471262693405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401822447776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411703258752823</t>
+    <t xml:space="preserve">0.38164895772934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390294700860977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395235151052475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399763911962509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389471292495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401822417974472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411703288555145</t>
   </si>
   <si>
     <t xml:space="preserve">0.402234137058258</t>
@@ -2681,82 +2681,82 @@
     <t xml:space="preserve">0.408409684896469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405939429998398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406351149082184</t>
+    <t xml:space="preserve">0.40593945980072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406351119279861</t>
   </si>
   <si>
     <t xml:space="preserve">0.400175601243973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397705376148224</t>
+    <t xml:space="preserve">0.397705405950546</t>
   </si>
   <si>
     <t xml:space="preserve">0.403880923986435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403057545423508</t>
+    <t xml:space="preserve">0.403057515621185</t>
   </si>
   <si>
     <t xml:space="preserve">0.394823461771011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417467147111893</t>
+    <t xml:space="preserve">0.417467176914215</t>
   </si>
   <si>
     <t xml:space="preserve">0.433111876249313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430641651153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441345930099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454520374536514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442992746829987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488280147314072</t>
+    <t xml:space="preserve">0.430641680955887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44134595990181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454520434141159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442992717027664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488280087709427</t>
   </si>
   <si>
     <t xml:space="preserve">0.50392484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534390866756439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518746197223663</t>
+    <t xml:space="preserve">0.534390926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518746137619019</t>
   </si>
   <si>
     <t xml:space="preserve">0.522039771080017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500631213188171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517922699451447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469341784715652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485809892416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462754517793655</t>
+    <t xml:space="preserve">0.500631153583527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517922759056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46934175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485809803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462754458189011</t>
   </si>
   <si>
     <t xml:space="preserve">0.472635388374329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493220567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573721170425</t>
+    <t xml:space="preserve">0.493220508098602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491573750972748</t>
   </si>
   <si>
     <t xml:space="preserve">0.48169282078743</t>
@@ -2765,103 +2765,103 @@
     <t xml:space="preserve">0.467694938182831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459460884332657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461107671260834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476752430200577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479222625494003</t>
+    <t xml:space="preserve">0.459460943937302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461107701063156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476752400398254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479222595691681</t>
   </si>
   <si>
     <t xml:space="preserve">0.477575838565826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515452444553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504748165607452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501454651355743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498984396457672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494043916463852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505571663379669</t>
+    <t xml:space="preserve">0.51545250415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504748225212097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501454591751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498984456062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494043976068497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505571722984314</t>
   </si>
   <si>
     <t xml:space="preserve">0.490750372409821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484986454248428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492397099733353</t>
+    <t xml:space="preserve">0.484986543655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492397129535675</t>
   </si>
   <si>
     <t xml:space="preserve">0.482516258955002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478399187326431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473458796739578</t>
+    <t xml:space="preserve">0.478399217128754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473458826541901</t>
   </si>
   <si>
     <t xml:space="preserve">0.470988571643829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470165133476257</t>
+    <t xml:space="preserve">0.47016516327858</t>
   </si>
   <si>
     <t xml:space="preserve">0.46522468328476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460284322500229</t>
+    <t xml:space="preserve">0.460284262895584</t>
   </si>
   <si>
     <t xml:space="preserve">0.46851834654808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46675032377243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473822295665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457910358905792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461446404457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464098364114761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454374372959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441114455461502</t>
+    <t xml:space="preserve">0.466750353574753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473822325468063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457910388708115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46144637465477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464098334312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454374402761459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44111442565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.420782536268234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435810446739197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438462436199188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427412480115891</t>
+    <t xml:space="preserve">0.435810476541519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438462466001511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427412509918213</t>
   </si>
   <si>
     <t xml:space="preserve">0.426528483629227</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">0.433158487081528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448186427354813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441998422145844</t>
+    <t xml:space="preserve">0.448186457157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441998451948166</t>
   </si>
   <si>
     <t xml:space="preserve">0.434484452009201</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">0.449070423841476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437578469514847</t>
+    <t xml:space="preserve">0.437578439712524</t>
   </si>
   <si>
     <t xml:space="preserve">0.433600455522537</t>
@@ -2897,16 +2897,16 @@
     <t xml:space="preserve">0.4313904941082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434926450252533</t>
+    <t xml:space="preserve">0.434926480054855</t>
   </si>
   <si>
     <t xml:space="preserve">0.429622501134872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428738504648209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424318462610245</t>
+    <t xml:space="preserve">0.428738474845886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424318492412567</t>
   </si>
   <si>
     <t xml:space="preserve">0.434042453765869</t>
@@ -2930,31 +2930,31 @@
     <t xml:space="preserve">0.411942541599274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414152532815933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418130487203598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42255049943924</t>
+    <t xml:space="preserve">0.414152503013611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41813051700592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422550469636917</t>
   </si>
   <si>
     <t xml:space="preserve">0.413710534572601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425202488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423876523971558</t>
+    <t xml:space="preserve">0.425202518701553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423876464366913</t>
   </si>
   <si>
     <t xml:space="preserve">0.414594531059265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422992497682571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421224504709244</t>
+    <t xml:space="preserve">0.422992527484894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421224534511566</t>
   </si>
   <si>
     <t xml:space="preserve">0.413268536329269</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">0.412384539842606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41105854511261</t>
+    <t xml:space="preserve">0.411058515310287</t>
   </si>
   <si>
     <t xml:space="preserve">0.409732550382614</t>
@@ -2984,28 +2984,28 @@
     <t xml:space="preserve">0.423434525728226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42034050822258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426086485385895</t>
+    <t xml:space="preserve">0.420340478420258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426086455583572</t>
   </si>
   <si>
     <t xml:space="preserve">0.428296476602554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424760520458221</t>
+    <t xml:space="preserve">0.424760490655899</t>
   </si>
   <si>
     <t xml:space="preserve">0.422108501195908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415478557348251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402218580245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394262582063675</t>
+    <t xml:space="preserve">0.415478527545929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402218610048294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394262611865997</t>
   </si>
   <si>
     <t xml:space="preserve">0.400008589029312</t>
@@ -3014,16 +3014,16 @@
     <t xml:space="preserve">0.401334583759308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392494589090347</t>
+    <t xml:space="preserve">0.39249461889267</t>
   </si>
   <si>
     <t xml:space="preserve">0.396030604839325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405754566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403544574975967</t>
+    <t xml:space="preserve">0.405754536390305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403544545173645</t>
   </si>
   <si>
     <t xml:space="preserve">0.400450587272644</t>
@@ -3032,43 +3032,43 @@
     <t xml:space="preserve">0.389842629432678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388958603143692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395146608352661</t>
+    <t xml:space="preserve">0.388958632946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395146578550339</t>
   </si>
   <si>
     <t xml:space="preserve">0.386748641729355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393378615379333</t>
+    <t xml:space="preserve">0.393378585577011</t>
   </si>
   <si>
     <t xml:space="preserve">0.403102576732635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396914601325989</t>
+    <t xml:space="preserve">0.396914571523666</t>
   </si>
   <si>
     <t xml:space="preserve">0.397798597812653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401776552200317</t>
+    <t xml:space="preserve">0.40177658200264</t>
   </si>
   <si>
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660608291626</t>
+    <t xml:space="preserve">0.402660548686981</t>
   </si>
   <si>
     <t xml:space="preserve">0.419898509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436694473028183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443766415119171</t>
+    <t xml:space="preserve">0.436694443225861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443766385316849</t>
   </si>
   <si>
     <t xml:space="preserve">0.453789889812469</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">0.452878683805466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453334301710129</t>
+    <t xml:space="preserve">0.453334271907806</t>
   </si>
   <si>
     <t xml:space="preserve">0.462902158498764</t>
@@ -3086,31 +3086,31 @@
     <t xml:space="preserve">0.459257245063782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456523537635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465635806322098</t>
+    <t xml:space="preserve">0.456523567438126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465635776519775</t>
   </si>
   <si>
     <t xml:space="preserve">0.464724570512772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468369483947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480215430259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482949078083038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481126606464386</t>
+    <t xml:space="preserve">0.468369513750076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480215400457382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482949018478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481126666069031</t>
   </si>
   <si>
     <t xml:space="preserve">0.482037842273712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479304194450378</t>
+    <t xml:space="preserve">0.479304224252701</t>
   </si>
   <si>
     <t xml:space="preserve">0.474748075008392</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">0.523042976856232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529421448707581</t>
+    <t xml:space="preserve">0.529421508312225</t>
   </si>
   <si>
     <t xml:space="preserve">0.52577668428421</t>
@@ -3143,40 +3143,40 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753149986267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507552087306976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511197030544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514841973781586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519398093223572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51393073797226</t>
+    <t xml:space="preserve">0.515753209590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507552146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511197090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514841914176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519398033618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513930678367615</t>
   </si>
   <si>
     <t xml:space="preserve">0.524865388870239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509374618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526687860488892</t>
+    <t xml:space="preserve">0.509374558925629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526687920093536</t>
   </si>
   <si>
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546734809875488</t>
+    <t xml:space="preserve">0.541267454624176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546734869480133</t>
   </si>
   <si>
     <t xml:space="preserve">0.537622511386871</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">0.554024577140808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564959347248077</t>
+    <t xml:space="preserve">0.564959287643433</t>
   </si>
   <si>
     <t xml:space="preserve">0.569515407085419</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">0.548557281494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550379693508148</t>
+    <t xml:space="preserve">0.550379633903503</t>
   </si>
   <si>
     <t xml:space="preserve">0.547646045684814</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">0.55584704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553113400936127</t>
+    <t xml:space="preserve">0.553113341331482</t>
   </si>
   <si>
     <t xml:space="preserve">0.564048111438751</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">0.559491991996765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561314404010773</t>
+    <t xml:space="preserve">0.561314344406128</t>
   </si>
   <si>
     <t xml:space="preserve">0.558580696582794</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">0.556758284568787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542178690433502</t>
+    <t xml:space="preserve">0.542178750038147</t>
   </si>
   <si>
     <t xml:space="preserve">0.557669520378113</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">0.535800099372864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530332803726196</t>
+    <t xml:space="preserve">0.530332744121552</t>
   </si>
   <si>
     <t xml:space="preserve">0.527599096298218</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617466211319</t>
+    <t xml:space="preserve">0.496617496013641</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">0.505729734897614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494795024394989</t>
+    <t xml:space="preserve">0.494794994592667</t>
   </si>
   <si>
     <t xml:space="preserve">0.499351114034653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497528731822968</t>
+    <t xml:space="preserve">0.497528672218323</t>
   </si>
   <si>
     <t xml:space="preserve">0.492061376571655</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">0.488416433334351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483860313892365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487505227327347</t>
+    <t xml:space="preserve">0.483860343694687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487505257129669</t>
   </si>
   <si>
     <t xml:space="preserve">0.495706230401993</t>
@@ -3960,6 +3960,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.591000020503998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584999978542328</t>
   </si>
 </sst>
 </file>
@@ -69220,7 +69223,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912268518</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>170550</v>
@@ -69241,6 +69244,32 @@
         <v>1315</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6909837963</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>115702</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>0.592000007629395</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>0.583000004291534</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>0.591000020503998</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="1317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="1318">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333736181259155</t>
+    <t xml:space="preserve">0.333736211061478</t>
   </si>
   <si>
     <t xml:space="preserve">IMS.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">0.327446281909943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321156293153763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317678362131119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307318478822708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288448721170425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289336711168289</t>
+    <t xml:space="preserve">0.321156322956085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317678391933441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307318449020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288448661565781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289336681365967</t>
   </si>
   <si>
     <t xml:space="preserve">0.294368624687195</t>
@@ -68,49 +68,49 @@
     <t xml:space="preserve">0.285636752843857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796886205673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258997052907944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258257031440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243605211377144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246417179703712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262696951627731</t>
+    <t xml:space="preserve">0.273796856403351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258997023105621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258257061243057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243605226278305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246417194604874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262696981430054</t>
   </si>
   <si>
     <t xml:space="preserve">0.256407082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.259811043739319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261513024568558</t>
+    <t xml:space="preserve">0.259811013936996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261512994766235</t>
   </si>
   <si>
     <t xml:space="preserve">0.253817081451416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253077119588852</t>
+    <t xml:space="preserve">0.25307708978653</t>
   </si>
   <si>
     <t xml:space="preserve">0.286894708871841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284600764513016</t>
+    <t xml:space="preserve">0.284600734710693</t>
   </si>
   <si>
     <t xml:space="preserve">0.277496814727783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28711673617363</t>
+    <t xml:space="preserve">0.287116706371307</t>
   </si>
   <si>
     <t xml:space="preserve">0.290742635726929</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">0.263806968927383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256777077913284</t>
+    <t xml:space="preserve">0.256777107715607</t>
   </si>
   <si>
     <t xml:space="preserve">0.250117152929306</t>
@@ -131,34 +131,34 @@
     <t xml:space="preserve">0.297994613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310796469449997</t>
+    <t xml:space="preserve">0.310796409845352</t>
   </si>
   <si>
     <t xml:space="preserve">0.303544491529465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30435848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318122327327728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309686452150345</t>
+    <t xml:space="preserve">0.304358541965485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318122357130051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309686481952667</t>
   </si>
   <si>
     <t xml:space="preserve">0.301620543003082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31035241484642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323376297950745</t>
+    <t xml:space="preserve">0.310352444648743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323376268148422</t>
   </si>
   <si>
     <t xml:space="preserve">0.320046335458755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316716372966766</t>
+    <t xml:space="preserve">0.316716343164444</t>
   </si>
   <si>
     <t xml:space="preserve">0.315236419439316</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">0.315606385469437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332996129989624</t>
+    <t xml:space="preserve">0.332996189594269</t>
   </si>
   <si>
     <t xml:space="preserve">0.332256197929382</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">0.311240434646606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312054425477982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2996965944767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296884596347809</t>
+    <t xml:space="preserve">0.312054395675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299696564674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296884566545486</t>
   </si>
   <si>
     <t xml:space="preserve">0.299400568008423</t>
@@ -206,67 +206,67 @@
     <t xml:space="preserve">0.298216551542282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286376684904099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276756823062897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274536848068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2723169028759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268542885780334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270466893911362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265064984560013</t>
+    <t xml:space="preserve">0.286376744508743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276756852865219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27453687787056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272316873073578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268542915582657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270466953516006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26506495475769</t>
   </si>
   <si>
     <t xml:space="preserve">0.268172919750214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26861697435379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269208908081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275276839733124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284896731376648</t>
+    <t xml:space="preserve">0.268616944551468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269208878278732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275276869535446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284896701574326</t>
   </si>
   <si>
     <t xml:space="preserve">0.290002673864365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308206528425217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309168457984924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318196326494217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316938370466232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308946430683136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314200431108475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321378320455551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31938037276268</t>
+    <t xml:space="preserve">0.308206468820572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309168487787247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318196356296539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31693834066391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308946460485458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314200401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321378290653229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319380342960358</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722440481186</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">0.307096481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307614475488663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304950535297394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305616497993469</t>
+    <t xml:space="preserve">0.30761444568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304950505495071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305616468191147</t>
   </si>
   <si>
     <t xml:space="preserve">0.2995485663414</t>
@@ -296,10 +296,10 @@
     <t xml:space="preserve">0.305320501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295626610517502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300954520702362</t>
+    <t xml:space="preserve">0.295626640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300954550504684</t>
   </si>
   <si>
     <t xml:space="preserve">0.314400315284729</t>
@@ -308,16 +308,16 @@
     <t xml:space="preserve">0.318779796361923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318856626749039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318395644426346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319932281970978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318088263273239</t>
+    <t xml:space="preserve">0.318856596946716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318395614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319932252168655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318088293075562</t>
   </si>
   <si>
     <t xml:space="preserve">0.307331681251526</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">0.321776270866394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320393264293671</t>
+    <t xml:space="preserve">0.320393294095993</t>
   </si>
   <si>
     <t xml:space="preserve">0.311557501554489</t>
@@ -338,10 +338,10 @@
     <t xml:space="preserve">0.301569223403931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295806735754013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299648374319077</t>
+    <t xml:space="preserve">0.295806705951691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299648404121399</t>
   </si>
   <si>
     <t xml:space="preserve">0.296575099229813</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">0.318011462688446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318702936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32116162776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310020834207535</t>
+    <t xml:space="preserve">0.318702965974808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321161597967148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310020804405212</t>
   </si>
   <si>
     <t xml:space="preserve">0.311941653490067</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311173349618912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30725485086441</t>
+    <t xml:space="preserve">0.311173319816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307254880666733</t>
   </si>
   <si>
     <t xml:space="preserve">0.30671700835228</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">0.304949879646301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306870639324188</t>
+    <t xml:space="preserve">0.306870698928833</t>
   </si>
   <si>
     <t xml:space="preserve">0.297727584838867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301799714565277</t>
+    <t xml:space="preserve">0.301799684762955</t>
   </si>
   <si>
     <t xml:space="preserve">0.304027855396271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300032615661621</t>
+    <t xml:space="preserve">0.300032585859299</t>
   </si>
   <si>
     <t xml:space="preserve">0.313478291034698</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">0.312556326389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307869493961334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311480611562729</t>
+    <t xml:space="preserve">0.307869523763657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311480671167374</t>
   </si>
   <si>
     <t xml:space="preserve">0.298265397548676</t>
@@ -422,25 +422,25 @@
     <t xml:space="preserve">0.295576214790344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295960396528244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297650724649429</t>
+    <t xml:space="preserve">0.295960366725922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297650694847107</t>
   </si>
   <si>
     <t xml:space="preserve">0.297881215810776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293732225894928</t>
+    <t xml:space="preserve">0.29373225569725</t>
   </si>
   <si>
     <t xml:space="preserve">0.298803240060806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300416737794876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300109386444092</t>
+    <t xml:space="preserve">0.300416707992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300109356641769</t>
   </si>
   <si>
     <t xml:space="preserve">0.298880070447922</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">0.30548769235611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309559851884842</t>
+    <t xml:space="preserve">0.30955982208252</t>
   </si>
   <si>
     <t xml:space="preserve">0.303105890750885</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">0.3014155626297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300647228956223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282975643873215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29196509718895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289736956357956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293501734733582</t>
+    <t xml:space="preserve">0.3006471991539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28297558426857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291965126991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289736926555634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293501764535904</t>
   </si>
   <si>
     <t xml:space="preserve">0.292656570672989</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">0.292502909898758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289583295583725</t>
+    <t xml:space="preserve">0.289583265781403</t>
   </si>
   <si>
     <t xml:space="preserve">0.288123458623886</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">0.284281820058823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28789296746254</t>
+    <t xml:space="preserve">0.287892997264862</t>
   </si>
   <si>
     <t xml:space="preserve">0.290044277906418</t>
@@ -524,28 +524,28 @@
     <t xml:space="preserve">0.291888266801834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289813786745071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286586821079254</t>
+    <t xml:space="preserve">0.289813816547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286586791276932</t>
   </si>
   <si>
     <t xml:space="preserve">0.294270068407059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291811436414719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292579770088196</t>
+    <t xml:space="preserve">0.291811406612396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292579799890518</t>
   </si>
   <si>
     <t xml:space="preserve">0.295729905366898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298419058322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294731080532074</t>
+    <t xml:space="preserve">0.298419088125229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294731050729752</t>
   </si>
   <si>
     <t xml:space="preserve">0.287355124950409</t>
@@ -554,16 +554,16 @@
     <t xml:space="preserve">0.293809115886688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292041957378387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286740452051163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284665942192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278903543949127</t>
+    <t xml:space="preserve">0.292041927576065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286740481853485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2846659719944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278903514146805</t>
   </si>
   <si>
     <t xml:space="preserve">0.275599718093872</t>
@@ -575,82 +575,82 @@
     <t xml:space="preserve">0.272449523210526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276675343513489</t>
+    <t xml:space="preserve">0.276675373315811</t>
   </si>
   <si>
     <t xml:space="preserve">0.27398619055748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275676518678665</t>
+    <t xml:space="preserve">0.275676548480988</t>
   </si>
   <si>
     <t xml:space="preserve">0.275522828102112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276598542928696</t>
+    <t xml:space="preserve">0.276598483324051</t>
   </si>
   <si>
     <t xml:space="preserve">0.270989716053009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271143406629562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274293571710587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270451903343201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268146872520447</t>
+    <t xml:space="preserve">0.27114337682724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274293541908264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270451933145523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268146902322769</t>
   </si>
   <si>
     <t xml:space="preserve">0.267378598451614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264612555503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2657650411129</t>
+    <t xml:space="preserve">0.264612585306168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265765070915222</t>
   </si>
   <si>
     <t xml:space="preserve">0.262384444475174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267532229423523</t>
+    <t xml:space="preserve">0.267532199621201</t>
   </si>
   <si>
     <t xml:space="preserve">0.265304088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271911710500717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272526383399963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283282995223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279902338981628</t>
+    <t xml:space="preserve">0.271911680698395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272526413202286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283283025026321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279902309179306</t>
   </si>
   <si>
     <t xml:space="preserve">0.277059525251389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27844250202179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280516982078552</t>
+    <t xml:space="preserve">0.278442531824112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280517011880875</t>
   </si>
   <si>
     <t xml:space="preserve">0.278749823570251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27898034453392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278212040662766</t>
+    <t xml:space="preserve">0.278980314731598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278212010860443</t>
   </si>
   <si>
     <t xml:space="preserve">0.284051299095154</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.290812641382217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28966012597084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290428429841995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294807940721512</t>
+    <t xml:space="preserve">0.289660155773163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290428400039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294807910919189</t>
   </si>
   <si>
     <t xml:space="preserve">0.295422583818436</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.288507610559464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284589171409607</t>
+    <t xml:space="preserve">0.284589141607285</t>
   </si>
   <si>
     <t xml:space="preserve">0.291043102741241</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">0.293885916471481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294884741306305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289890617132187</t>
+    <t xml:space="preserve">0.294884771108627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289890587329865</t>
   </si>
   <si>
     <t xml:space="preserve">0.286125808954239</t>
@@ -695,28 +695,28 @@
     <t xml:space="preserve">0.284358620643616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282745182514191</t>
+    <t xml:space="preserve">0.282745152711868</t>
   </si>
   <si>
     <t xml:space="preserve">0.277290046215057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281976789236069</t>
+    <t xml:space="preserve">0.281976819038391</t>
   </si>
   <si>
     <t xml:space="preserve">0.276214331388474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273602068424225</t>
+    <t xml:space="preserve">0.273602038621902</t>
   </si>
   <si>
     <t xml:space="preserve">0.269760400056839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275061845779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271834909915924</t>
+    <t xml:space="preserve">0.275061875581741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271834880113602</t>
   </si>
   <si>
     <t xml:space="preserve">0.273371547460556</t>
@@ -728,28 +728,28 @@
     <t xml:space="preserve">0.276905834674835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27483132481575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282668322324753</t>
+    <t xml:space="preserve">0.274831354618073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282668352127075</t>
   </si>
   <si>
     <t xml:space="preserve">0.280440181493759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279595017433167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277366816997528</t>
+    <t xml:space="preserve">0.279595047235489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27736684679985</t>
   </si>
   <si>
     <t xml:space="preserve">0.278135150671005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281208485364914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278672993183136</t>
+    <t xml:space="preserve">0.281208515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278672963380814</t>
   </si>
   <si>
     <t xml:space="preserve">0.282591491937637</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">0.285587966442108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279671788215637</t>
+    <t xml:space="preserve">0.27967181801796</t>
   </si>
   <si>
     <t xml:space="preserve">0.286663621664047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284435451030731</t>
+    <t xml:space="preserve">0.284435510635376</t>
   </si>
   <si>
     <t xml:space="preserve">0.281899988651276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283897697925568</t>
+    <t xml:space="preserve">0.283897668123245</t>
   </si>
   <si>
     <t xml:space="preserve">0.285280615091324</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">0.304258346557617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321929931640625</t>
+    <t xml:space="preserve">0.321929961442947</t>
   </si>
   <si>
     <t xml:space="preserve">0.32561793923378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33184140920639</t>
+    <t xml:space="preserve">0.331841379404068</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387418270111</t>
@@ -803,22 +803,22 @@
     <t xml:space="preserve">0.316935807466507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309790343046188</t>
+    <t xml:space="preserve">0.309790313243866</t>
   </si>
   <si>
     <t xml:space="preserve">0.309252500534058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311096489429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313094139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313017338514328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288891792297363</t>
+    <t xml:space="preserve">0.311096519231796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313094168901443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313017308712006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288891762495041</t>
   </si>
   <si>
     <t xml:space="preserve">0.293040752410889</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">0.296805590391159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297266572713852</t>
+    <t xml:space="preserve">0.297266602516174</t>
   </si>
   <si>
     <t xml:space="preserve">0.298111766576767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310251325368881</t>
+    <t xml:space="preserve">0.310251295566559</t>
   </si>
   <si>
     <t xml:space="preserve">0.313555121421814</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">0.300800889730453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30886834859848</t>
+    <t xml:space="preserve">0.308868318796158</t>
   </si>
   <si>
     <t xml:space="preserve">0.299725204706192</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">0.32185310125351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327308267354965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318472415208817</t>
+    <t xml:space="preserve">0.327308297157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318472474813461</t>
   </si>
   <si>
     <t xml:space="preserve">0.312095314264297</t>
@@ -872,28 +872,28 @@
     <t xml:space="preserve">0.312249004840851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313939273357391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309636652469635</t>
+    <t xml:space="preserve">0.313939303159714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309636682271957</t>
   </si>
   <si>
     <t xml:space="preserve">0.307408541440964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308945149183273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313632011413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308023184537888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307715862989426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309022009372711</t>
+    <t xml:space="preserve">0.308945178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313631981611252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30802321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307715833187103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309022039175034</t>
   </si>
   <si>
     <t xml:space="preserve">0.309944003820419</t>
@@ -902,40 +902,40 @@
     <t xml:space="preserve">0.317780941724777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31655165553093</t>
+    <t xml:space="preserve">0.316551625728607</t>
   </si>
   <si>
     <t xml:space="preserve">0.316474795341492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324388563632965</t>
+    <t xml:space="preserve">0.324388593435287</t>
   </si>
   <si>
     <t xml:space="preserve">0.325003296136856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318318784236908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317704141139984</t>
+    <t xml:space="preserve">0.318318754434586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317704111337662</t>
   </si>
   <si>
     <t xml:space="preserve">0.321545779705048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320470124483109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621434926987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323697060346603</t>
+    <t xml:space="preserve">0.320470094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621405124664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323697090148926</t>
   </si>
   <si>
     <t xml:space="preserve">0.333454847335815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327385038137436</t>
+    <t xml:space="preserve">0.327385067939758</t>
   </si>
   <si>
     <t xml:space="preserve">0.331764549016953</t>
@@ -944,22 +944,22 @@
     <t xml:space="preserve">0.339524686336517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345671325922012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340446710586548</t>
+    <t xml:space="preserve">0.34567129611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340446680784225</t>
   </si>
   <si>
     <t xml:space="preserve">0.333378046751022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334991484880447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336144059896469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337757527828217</t>
+    <t xml:space="preserve">0.33499151468277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336144030094147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337757498025894</t>
   </si>
   <si>
     <t xml:space="preserve">0.338910013437271</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">0.338141679763794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339678317308426</t>
+    <t xml:space="preserve">0.339678376913071</t>
   </si>
   <si>
     <t xml:space="preserve">0.350358128547668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346593290567398</t>
+    <t xml:space="preserve">0.346593260765076</t>
   </si>
   <si>
     <t xml:space="preserve">0.344211488962173</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">0.334607362747192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338218539953232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34690061211586</t>
+    <t xml:space="preserve">0.338218510150909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346900671720505</t>
   </si>
   <si>
     <t xml:space="preserve">0.346132338047028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33960148692131</t>
+    <t xml:space="preserve">0.339601516723633</t>
   </si>
   <si>
     <t xml:space="preserve">0.340907663106918</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">0.352663099765778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369950503110886</t>
+    <t xml:space="preserve">0.369950473308563</t>
   </si>
   <si>
     <t xml:space="preserve">0.36541736125946</t>
@@ -1022,19 +1022,19 @@
     <t xml:space="preserve">0.369566380977631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368798017501831</t>
+    <t xml:space="preserve">0.368797987699509</t>
   </si>
   <si>
     <t xml:space="preserve">0.366108864545822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363112390041351</t>
+    <t xml:space="preserve">0.363112419843674</t>
   </si>
   <si>
     <t xml:space="preserve">0.3686443567276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366877168416977</t>
+    <t xml:space="preserve">0.366877198219299</t>
   </si>
   <si>
     <t xml:space="preserve">0.366262555122375</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.368567526340485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372025012969971</t>
+    <t xml:space="preserve">0.372024983167648</t>
   </si>
   <si>
     <t xml:space="preserve">0.375559329986572</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">0.380246132612228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392616182565689</t>
+    <t xml:space="preserve">0.392616212368011</t>
   </si>
   <si>
     <t xml:space="preserve">0.405677855014801</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">0.396842062473297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41336116194725</t>
+    <t xml:space="preserve">0.413361132144928</t>
   </si>
   <si>
     <t xml:space="preserve">0.422581076622009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417586922645569</t>
+    <t xml:space="preserve">0.417586892843246</t>
   </si>
   <si>
     <t xml:space="preserve">0.426422744989395</t>
@@ -1097,25 +1097,25 @@
     <t xml:space="preserve">0.436795175075531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432953536510468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45293003320694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460884332657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465223401784897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296647071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481358259916306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522463798522949</t>
+    <t xml:space="preserve">0.432953506708145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452930063009262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460854530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465223342180252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296676874161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48135831952095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522463858127594</t>
   </si>
   <si>
     <t xml:space="preserve">0.515164732933044</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">0.507097244262695</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515548944473267</t>
+    <t xml:space="preserve">0.515548825263977</t>
   </si>
   <si>
     <t xml:space="preserve">0.503255605697632</t>
@@ -1142,31 +1142,31 @@
     <t xml:space="preserve">0.519006371498108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511323034763336</t>
+    <t xml:space="preserve">0.511323094367981</t>
   </si>
   <si>
     <t xml:space="preserve">0.499413967132568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491730719804764</t>
+    <t xml:space="preserve">0.491730660200119</t>
   </si>
   <si>
     <t xml:space="preserve">0.484431564807892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483663141727448</t>
+    <t xml:space="preserve">0.483663260936737</t>
   </si>
   <si>
     <t xml:space="preserve">0.484815716743469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495188176631927</t>
+    <t xml:space="preserve">0.495188236236572</t>
   </si>
   <si>
     <t xml:space="preserve">0.490194022655487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553197085857391</t>
+    <t xml:space="preserve">0.553196966648102</t>
   </si>
   <si>
     <t xml:space="preserve">0.542056202888489</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">0.586235225200653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600065231323242</t>
+    <t xml:space="preserve">0.600065171718597</t>
   </si>
   <si>
     <t xml:space="preserve">0.58239358663559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572021126747131</t>
+    <t xml:space="preserve">0.572021067142487</t>
   </si>
   <si>
     <t xml:space="preserve">0.572789430618286</t>
@@ -1193,40 +1193,40 @@
     <t xml:space="preserve">0.552428662776947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55127614736557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545129597187042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565874397754669</t>
+    <t xml:space="preserve">0.551276206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545129537582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565874516963959</t>
   </si>
   <si>
     <t xml:space="preserve">0.577015221118927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596607685089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584698498249054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608132421970367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621962428092957</t>
+    <t xml:space="preserve">0.596607625484467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584698557853699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608132541179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621962487697601</t>
   </si>
   <si>
     <t xml:space="preserve">0.620425879955292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629645824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614279210567474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60774838924408</t>
+    <t xml:space="preserve">0.629645764827728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614279270172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607748329639435</t>
   </si>
   <si>
     <t xml:space="preserve">0.581625282764435</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">0.598528444766998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598144233226776</t>
+    <t xml:space="preserve">0.598144292831421</t>
   </si>
   <si>
     <t xml:space="preserve">0.619657516479492</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">0.601601779460907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58661937713623</t>
+    <t xml:space="preserve">0.586619317531586</t>
   </si>
   <si>
     <t xml:space="preserve">0.595455169677734</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">0.584314346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577399432659149</t>
+    <t xml:space="preserve">0.577399373054504</t>
   </si>
   <si>
     <t xml:space="preserve">0.567026913166046</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">0.57432609796524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543592870235443</t>
+    <t xml:space="preserve">0.543592929840088</t>
   </si>
   <si>
     <t xml:space="preserve">0.564721941947937</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">0.576246917247772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583930194377899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58085685968399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587003469467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604675054550171</t>
+    <t xml:space="preserve">0.583930253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580856800079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587003529071808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604674994945526</t>
   </si>
   <si>
     <t xml:space="preserve">0.629261612892151</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">0.593918442726135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596991717815399</t>
+    <t xml:space="preserve">0.596991777420044</t>
   </si>
   <si>
     <t xml:space="preserve">0.608516693115234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599296748638153</t>
+    <t xml:space="preserve">0.599296808242798</t>
   </si>
   <si>
     <t xml:space="preserve">0.589308559894562</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">0.553965389728546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538598716259003</t>
+    <t xml:space="preserve">0.538598775863647</t>
   </si>
   <si>
     <t xml:space="preserve">0.557038724422455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536293745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524000585079193</t>
+    <t xml:space="preserve">0.536293804645538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524000525474548</t>
   </si>
   <si>
     <t xml:space="preserve">0.537830471992493</t>
@@ -1349,25 +1349,25 @@
     <t xml:space="preserve">0.547818720340729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532452166080475</t>
+    <t xml:space="preserve">0.53245222568512</t>
   </si>
   <si>
     <t xml:space="preserve">0.537062108516693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527073800563812</t>
+    <t xml:space="preserve">0.527073860168457</t>
   </si>
   <si>
     <t xml:space="preserve">0.52092719078064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517853915691376</t>
+    <t xml:space="preserve">0.517853856086731</t>
   </si>
   <si>
     <t xml:space="preserve">0.525537192821503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530147194862366</t>
+    <t xml:space="preserve">0.53014725446701</t>
   </si>
   <si>
     <t xml:space="preserve">0.523232221603394</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">0.524768888950348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549355387687683</t>
+    <t xml:space="preserve">0.549355328083038</t>
   </si>
   <si>
     <t xml:space="preserve">0.501718997955322</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">0.488657355308533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471754193305969</t>
+    <t xml:space="preserve">0.471754163503647</t>
   </si>
   <si>
     <t xml:space="preserve">0.472522437572479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468680858612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487120717763901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481742411851883</t>
+    <t xml:space="preserve">0.468680888414383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487120658159256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481742471456528</t>
   </si>
   <si>
     <t xml:space="preserve">0.480974107980728</t>
@@ -1421,79 +1421,79 @@
     <t xml:space="preserve">0.478669166564941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47021746635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467912524938583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466375797986984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839190244675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461765915155411</t>
+    <t xml:space="preserve">0.470217496156693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467912554740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466375827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839249849319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461765855550766</t>
   </si>
   <si>
     <t xml:space="preserve">0.487889021635056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500182330608368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469449132680893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437179356813431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444862574338913</t>
+    <t xml:space="preserve">0.500182271003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469449102878571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437179386615753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444862604141235</t>
   </si>
   <si>
     <t xml:space="preserve">0.431800991296768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444094300270081</t>
+    <t xml:space="preserve">0.444094270467758</t>
   </si>
   <si>
     <t xml:space="preserve">0.424117684364319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415666133165359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382627964019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379170447587967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382243812084198</t>
+    <t xml:space="preserve">0.415666103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382627993822098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379170477390289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382243782281876</t>
   </si>
   <si>
     <t xml:space="preserve">0.385701268911362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388774573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391847878694534</t>
+    <t xml:space="preserve">0.388774544000626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391847848892212</t>
   </si>
   <si>
     <t xml:space="preserve">0.384164601564407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37648132443428</t>
+    <t xml:space="preserve">0.376481294631958</t>
   </si>
   <si>
     <t xml:space="preserve">0.367261350154877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364956378936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360346436500549</t>
+    <t xml:space="preserve">0.364956349134445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360346406698227</t>
   </si>
   <si>
     <t xml:space="preserve">0.3522789478302</t>
@@ -1502,22 +1502,22 @@
     <t xml:space="preserve">0.356504738330841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371487140655518</t>
+    <t xml:space="preserve">0.37148717045784</t>
   </si>
   <si>
     <t xml:space="preserve">0.368029683828354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37225553393364</t>
+    <t xml:space="preserve">0.372255504131317</t>
   </si>
   <si>
     <t xml:space="preserve">0.365340530872345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374944657087326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3664930164814</t>
+    <t xml:space="preserve">0.374944686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366493046283722</t>
   </si>
   <si>
     <t xml:space="preserve">0.374560534954071</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">0.37878629565239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362267255783081</t>
+    <t xml:space="preserve">0.362267196178436</t>
   </si>
   <si>
     <t xml:space="preserve">0.353815615177155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354583919048309</t>
+    <t xml:space="preserve">0.354583948850632</t>
   </si>
   <si>
     <t xml:space="preserve">0.353047311306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37071880698204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35419973731041</t>
+    <t xml:space="preserve">0.370718866586685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354199767112732</t>
   </si>
   <si>
     <t xml:space="preserve">0.395689517259598</t>
@@ -1553,16 +1553,16 @@
     <t xml:space="preserve">0.411056131124496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407982796430588</t>
+    <t xml:space="preserve">0.40798282623291</t>
   </si>
   <si>
     <t xml:space="preserve">0.384932965040207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39031121134758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378017961978912</t>
+    <t xml:space="preserve">0.390311241149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378017991781235</t>
   </si>
   <si>
     <t xml:space="preserve">0.380707114934921</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">0.353431463241577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349589794874191</t>
+    <t xml:space="preserve">0.349589824676514</t>
   </si>
   <si>
     <t xml:space="preserve">0.344979822635651</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">0.343058973550797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354968100786209</t>
+    <t xml:space="preserve">0.354968130588531</t>
   </si>
   <si>
     <t xml:space="preserve">0.36418804526329</t>
@@ -1598,28 +1598,28 @@
     <t xml:space="preserve">0.349973976612091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339217394590378</t>
+    <t xml:space="preserve">0.339217364788055</t>
   </si>
   <si>
     <t xml:space="preserve">0.323850780725479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361883014440536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350742250680923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38954296708107</t>
+    <t xml:space="preserve">0.361883044242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350742280483246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389542937278748</t>
   </si>
   <si>
     <t xml:space="preserve">0.404141157865524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396457880735397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412592798471451</t>
+    <t xml:space="preserve">0.396457850933075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412592828273773</t>
   </si>
   <si>
     <t xml:space="preserve">0.404909521341324</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">0.401836186647415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394152909517288</t>
+    <t xml:space="preserve">0.394152879714966</t>
   </si>
   <si>
     <t xml:space="preserve">0.399531185626984</t>
@@ -1637,22 +1637,22 @@
     <t xml:space="preserve">0.40260449051857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40106788277626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397994518280029</t>
+    <t xml:space="preserve">0.401067852973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397994548082352</t>
   </si>
   <si>
     <t xml:space="preserve">0.375712960958481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36457222700119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345748096704483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336528241634369</t>
+    <t xml:space="preserve">0.364572167396545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345748126506805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336528182029724</t>
   </si>
   <si>
     <t xml:space="preserve">0.335759878158569</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">0.337296515703201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329613238573074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328076541423798</t>
+    <t xml:space="preserve">0.329613208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32807657122612</t>
   </si>
   <si>
     <t xml:space="preserve">0.331534028053284</t>
@@ -1673,49 +1673,49 @@
     <t xml:space="preserve">0.319240808486938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326924055814743</t>
+    <t xml:space="preserve">0.326924085617065</t>
   </si>
   <si>
     <t xml:space="preserve">0.312709987163544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34113821387291</t>
+    <t xml:space="preserve">0.341138184070587</t>
   </si>
   <si>
     <t xml:space="preserve">0.322698295116425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326155751943588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324619084596634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325771570205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330381542444229</t>
+    <t xml:space="preserve">0.326155781745911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324619114398956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325771600008011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330381572246552</t>
   </si>
   <si>
     <t xml:space="preserve">0.329997390508652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324234932661057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313862472772598</t>
+    <t xml:space="preserve">0.324234902858734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313862502574921</t>
   </si>
   <si>
     <t xml:space="preserve">0.301185011863708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30387419462204</t>
+    <t xml:space="preserve">0.303874164819717</t>
   </si>
   <si>
     <t xml:space="preserve">0.296959221363068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302721738815308</t>
+    <t xml:space="preserve">0.302721709012985</t>
   </si>
   <si>
     <t xml:space="preserve">0.32308241724968</t>
@@ -1736,19 +1736,19 @@
     <t xml:space="preserve">0.305410861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30848416686058</t>
+    <t xml:space="preserve">0.308484196662903</t>
   </si>
   <si>
     <t xml:space="preserve">0.304642498493195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320777416229248</t>
+    <t xml:space="preserve">0.320777475833893</t>
   </si>
   <si>
     <t xml:space="preserve">0.356888920068741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358041405677795</t>
+    <t xml:space="preserve">0.358041375875473</t>
   </si>
   <si>
     <t xml:space="preserve">0.356120586395264</t>
@@ -1775,19 +1775,19 @@
     <t xml:space="preserve">0.370334655046463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383780419826508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376097142696381</t>
+    <t xml:space="preserve">0.38378044962883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376097172498703</t>
   </si>
   <si>
     <t xml:space="preserve">0.376865476369858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377249658107758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398762881755829</t>
+    <t xml:space="preserve">0.37724968791008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398762851953506</t>
   </si>
   <si>
     <t xml:space="preserve">0.403372824192047</t>
@@ -1802,16 +1802,16 @@
     <t xml:space="preserve">0.39107957482338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381475448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407214462757111</t>
+    <t xml:space="preserve">0.381475478410721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407214492559433</t>
   </si>
   <si>
     <t xml:space="preserve">0.387237936258316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394921183586121</t>
+    <t xml:space="preserve">0.394921213388443</t>
   </si>
   <si>
     <t xml:space="preserve">0.411824464797974</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">0.408751159906387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410287767648697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414129376411438</t>
+    <t xml:space="preserve">0.410287797451019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41412940621376</t>
   </si>
   <si>
     <t xml:space="preserve">0.416434437036514</t>
@@ -1844,40 +1844,40 @@
     <t xml:space="preserve">0.420276075601578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421812772750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430264353752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473290771245956</t>
+    <t xml:space="preserve">0.421812742948532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430264383554459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473290801048279</t>
   </si>
   <si>
     <t xml:space="preserve">0.49480402469635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484047412872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267387151718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506328940391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479437410831451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482510715723038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595891475677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070826768875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465607464313507</t>
+    <t xml:space="preserve">0.484047472476959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267327547073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506328999996185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479437470436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48251074552536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595831871033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465607523918152</t>
   </si>
   <si>
     <t xml:space="preserve">0.460997551679611</t>
@@ -1886,55 +1886,55 @@
     <t xml:space="preserve">0.453314214944839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4341059923172</t>
+    <t xml:space="preserve">0.434106022119522</t>
   </si>
   <si>
     <t xml:space="preserve">0.441789239645004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445630937814713</t>
+    <t xml:space="preserve">0.44563090801239</t>
   </si>
   <si>
     <t xml:space="preserve">0.449472546577454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451009303331375</t>
+    <t xml:space="preserve">0.451009273529053</t>
   </si>
   <si>
     <t xml:space="preserve">0.460229218006134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454082608222961</t>
+    <t xml:space="preserve">0.454082578420639</t>
   </si>
   <si>
     <t xml:space="preserve">0.457155913114548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451777577400208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456387490034103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463302463293076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47098582983017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467144191265106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457924216985703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447167605161667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432569354772568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437947660684586</t>
+    <t xml:space="preserve">0.451777547597885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456387549638748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463302493095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470985859632492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467144101858139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457924246788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447167634963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43256938457489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437947630882263</t>
   </si>
   <si>
     <t xml:space="preserve">0.433337688446045</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">0.434874325990677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436411023139954</t>
+    <t xml:space="preserve">0.436410993337631</t>
   </si>
   <si>
     <t xml:space="preserve">0.43948432803154</t>
@@ -1952,43 +1952,43 @@
     <t xml:space="preserve">0.441020995378494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440252631902695</t>
+    <t xml:space="preserve">0.440252691507339</t>
   </si>
   <si>
     <t xml:space="preserve">0.438715934753418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442557543516159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485584110021591</t>
+    <t xml:space="preserve">0.442557603120804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485584050416946</t>
   </si>
   <si>
     <t xml:space="preserve">0.455619186162949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443326026201248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429496079683304</t>
+    <t xml:space="preserve">0.443325966596603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429496049880981</t>
   </si>
   <si>
     <t xml:space="preserve">0.435642659664154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450240910053253</t>
+    <t xml:space="preserve">0.450240939855576</t>
   </si>
   <si>
     <t xml:space="preserve">0.427191078662872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375328809022903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386469602584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393384605646133</t>
+    <t xml:space="preserve">0.375328779220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386469572782516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393384575843811</t>
   </si>
   <si>
     <t xml:space="preserve">0.365724712610245</t>
@@ -1997,16 +1997,16 @@
     <t xml:space="preserve">0.372639685869217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351510614156723</t>
+    <t xml:space="preserve">0.351510643959045</t>
   </si>
   <si>
     <t xml:space="preserve">0.342674821615219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317319959402084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265073597431183</t>
+    <t xml:space="preserve">0.317319989204407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265073627233505</t>
   </si>
   <si>
     <t xml:space="preserve">0.259695291519165</t>
@@ -2015,25 +2015,25 @@
     <t xml:space="preserve">0.239334583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242023706436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234724566340446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245865359902382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258926957845688</t>
+    <t xml:space="preserve">0.24202373623848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234724551439285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24586533010006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258926928043365</t>
   </si>
   <si>
     <t xml:space="preserve">0.251627802848816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266610264778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269299358129501</t>
+    <t xml:space="preserve">0.266610234975815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269299387931824</t>
   </si>
   <si>
     <t xml:space="preserve">0.258158624172211</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">0.245097011327744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254701137542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262000292539597</t>
+    <t xml:space="preserve">0.254701107740402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262000262737274</t>
   </si>
   <si>
     <t xml:space="preserve">0.254316985607147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261231899261475</t>
+    <t xml:space="preserve">0.261231929063797</t>
   </si>
   <si>
     <t xml:space="preserve">0.262768596410751</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">0.264689415693283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271988570690155</t>
+    <t xml:space="preserve">0.271988540887833</t>
   </si>
   <si>
     <t xml:space="preserve">0.273909360170364</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">0.272756844758987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275446057319641</t>
+    <t xml:space="preserve">0.275445997714996</t>
   </si>
   <si>
     <t xml:space="preserve">0.268915235996246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265841841697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258542776107788</t>
+    <t xml:space="preserve">0.265841871500015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25854280591011</t>
   </si>
   <si>
     <t xml:space="preserve">0.265457719564438</t>
@@ -2105,61 +2105,61 @@
     <t xml:space="preserve">0.327692419290543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302337527275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301953345537186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332302391529083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332686543464661</t>
+    <t xml:space="preserve">0.302337497472763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301953375339508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332302361726761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332686573266983</t>
   </si>
   <si>
     <t xml:space="preserve">0.306179195642471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305026739835739</t>
+    <t xml:space="preserve">0.305026710033417</t>
   </si>
   <si>
     <t xml:space="preserve">0.312325805425644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331918239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315399140119553</t>
+    <t xml:space="preserve">0.331918209791183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31539911031723</t>
   </si>
   <si>
     <t xml:space="preserve">0.326539903879166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292349249124527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289275944232941</t>
+    <t xml:space="preserve">0.292349278926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289275974035263</t>
   </si>
   <si>
     <t xml:space="preserve">0.291196793317795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286970943212509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285050123929977</t>
+    <t xml:space="preserve">0.286970973014832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285050094127655</t>
   </si>
   <si>
     <t xml:space="preserve">0.273525178432465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260847747325897</t>
+    <t xml:space="preserve">0.260847806930542</t>
   </si>
   <si>
     <t xml:space="preserve">0.261616110801697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270067691802979</t>
+    <t xml:space="preserve">0.270067721605301</t>
   </si>
   <si>
     <t xml:space="preserve">0.278519362211227</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">0.266994416713715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255469471216202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25316447019577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256621986627579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256237775087357</t>
+    <t xml:space="preserve">0.255469441413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253164499998093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256621927022934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256237804889679</t>
   </si>
   <si>
     <t xml:space="preserve">0.249322816729546</t>
@@ -2201,28 +2201,28 @@
     <t xml:space="preserve">0.283513456583023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27775102853775</t>
+    <t xml:space="preserve">0.277750998735428</t>
   </si>
   <si>
     <t xml:space="preserve">0.294654279947281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319624960422516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343827337026596</t>
+    <t xml:space="preserve">0.319624990224838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343827307224274</t>
   </si>
   <si>
     <t xml:space="preserve">0.338449001312256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340754002332687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338833212852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338064849376678</t>
+    <t xml:space="preserve">0.34075403213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338833183050156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338064879179001</t>
   </si>
   <si>
     <t xml:space="preserve">0.336912333965302</t>
@@ -2234,25 +2234,25 @@
     <t xml:space="preserve">0.330765724182129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328844904899597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339985698461533</t>
+    <t xml:space="preserve">0.328844875097275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33998566865921</t>
   </si>
   <si>
     <t xml:space="preserve">0.34766897559166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35996225476265</t>
+    <t xml:space="preserve">0.359962224960327</t>
   </si>
   <si>
     <t xml:space="preserve">0.351894795894623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369182199239731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357657253742218</t>
+    <t xml:space="preserve">0.369182229042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357657223939896</t>
   </si>
   <si>
     <t xml:space="preserve">0.355352282524109</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">0.346516489982605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347284823656082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363419741392136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373792141675949</t>
+    <t xml:space="preserve">0.34728479385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363419681787491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373792171478271</t>
   </si>
   <si>
     <t xml:space="preserve">0.373023808002472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379554629325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425654411315918</t>
+    <t xml:space="preserve">0.379554659128189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425654381513596</t>
   </si>
   <si>
     <t xml:space="preserve">0.417971104383469</t>
@@ -2288,52 +2288,52 @@
     <t xml:space="preserve">0.381859600543976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38301208615303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377633839845657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37840211391449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381091296672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380322962999344</t>
+    <t xml:space="preserve">0.383012115955353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377633810043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378402143716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381091266870499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380322992801666</t>
   </si>
   <si>
     <t xml:space="preserve">0.348437309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400299549102783</t>
+    <t xml:space="preserve">0.400299578905106</t>
   </si>
   <si>
     <t xml:space="preserve">0.383396297693253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379938840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388006240129471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428727746009827</t>
+    <t xml:space="preserve">0.379938811063766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388006269931793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428727716207504</t>
   </si>
   <si>
     <t xml:space="preserve">0.368413865566254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344595640897751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334223210811615</t>
+    <t xml:space="preserve">0.344595670700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334223181009293</t>
   </si>
   <si>
     <t xml:space="preserve">0.341906487941742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323466569185257</t>
+    <t xml:space="preserve">0.323466598987579</t>
   </si>
   <si>
     <t xml:space="preserve">0.340369820594788</t>
@@ -2348,16 +2348,16 @@
     <t xml:space="preserve">0.322314113378525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285818457603455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337680697441101</t>
+    <t xml:space="preserve">0.285818487405777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337680667638779</t>
   </si>
   <si>
     <t xml:space="preserve">0.345363944768906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341522365808487</t>
+    <t xml:space="preserve">0.341522336006165</t>
   </si>
   <si>
     <t xml:space="preserve">0.329229056835175</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">0.353653132915497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351594626903534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354064851999283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352829724550247</t>
+    <t xml:space="preserve">0.351594597101212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35406482219696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352829694747925</t>
   </si>
   <si>
     <t xml:space="preserve">0.347477555274963</t>
@@ -2390,10 +2390,10 @@
     <t xml:space="preserve">0.348300993442535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35982871055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353241413831711</t>
+    <t xml:space="preserve">0.359828650951385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353241384029388</t>
   </si>
   <si>
     <t xml:space="preserve">0.35488823056221</t>
@@ -2402,13 +2402,13 @@
     <t xml:space="preserve">0.350359499454498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345007359981537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339655190706253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342948824167252</t>
+    <t xml:space="preserve">0.345007330179214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339655220508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342948853969574</t>
   </si>
   <si>
     <t xml:space="preserve">0.341302037239075</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">0.319070041179657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321540266275406</t>
+    <t xml:space="preserve">0.321540296077728</t>
   </si>
   <si>
     <t xml:space="preserve">0.310835957527161</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">0.315776437520981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314129650592804</t>
+    <t xml:space="preserve">0.314129620790482</t>
   </si>
   <si>
     <t xml:space="preserve">0.312894523143768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318246603012085</t>
+    <t xml:space="preserve">0.31824666261673</t>
   </si>
   <si>
     <t xml:space="preserve">0.317834943532944</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">0.319481790065765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312071084976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308365792036057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310012608766556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314541280269623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318658351898193</t>
+    <t xml:space="preserve">0.312071114778519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308365762233734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310012578964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314541310071945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318658322095871</t>
   </si>
   <si>
     <t xml:space="preserve">0.320305168628693</t>
@@ -2468,13 +2468,13 @@
     <t xml:space="preserve">0.322775393724442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30960088968277</t>
+    <t xml:space="preserve">0.309600859880447</t>
   </si>
   <si>
     <t xml:space="preserve">0.309189170598984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32112854719162</t>
+    <t xml:space="preserve">0.321128576993942</t>
   </si>
   <si>
     <t xml:space="preserve">0.32195195555687</t>
@@ -2483,37 +2483,37 @@
     <t xml:space="preserve">0.325245589017868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32689243555069</t>
+    <t xml:space="preserve">0.326892405748367</t>
   </si>
   <si>
     <t xml:space="preserve">0.323187112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323598802089691</t>
+    <t xml:space="preserve">0.323598772287369</t>
   </si>
   <si>
     <t xml:space="preserve">0.315364688634872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31330618262291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310424298048019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314952999353409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311247676610947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317011535167694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31742325425148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311659395694733</t>
+    <t xml:space="preserve">0.313306242227554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310424268245697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314953029155731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311247646808624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317011505365372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317423224449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31165936589241</t>
   </si>
   <si>
     <t xml:space="preserve">0.316188126802444</t>
@@ -2531,25 +2531,25 @@
     <t xml:space="preserve">0.303013622760773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307542324066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302601963281631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307954043149948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306307256221771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301778495311737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303837031126022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30095511674881</t>
+    <t xml:space="preserve">0.307542353868484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302601933479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307954072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306307286024094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301778525114059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3038370013237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300955086946487</t>
   </si>
   <si>
     <t xml:space="preserve">0.301366806030273</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">0.302190214395523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313717901706696</t>
+    <t xml:space="preserve">0.313717931509018</t>
   </si>
   <si>
     <t xml:space="preserve">0.326480716466904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328539192676544</t>
+    <t xml:space="preserve">0.328539222478867</t>
   </si>
   <si>
     <t xml:space="preserve">0.340890347957611</t>
@@ -2573,19 +2573,19 @@
     <t xml:space="preserve">0.356535047292709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343360543251038</t>
+    <t xml:space="preserve">0.343360513448715</t>
   </si>
   <si>
     <t xml:space="preserve">0.336361587047577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339243501424789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335126489400864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358181864023209</t>
+    <t xml:space="preserve">0.339243531227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335126459598541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358181834220886</t>
   </si>
   <si>
     <t xml:space="preserve">0.3470658659935</t>
@@ -2597,46 +2597,46 @@
     <t xml:space="preserve">0.336773276329041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345419049263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349124372005463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338008373975754</t>
+    <t xml:space="preserve">0.345419079065323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349124401807785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338008433580399</t>
   </si>
   <si>
     <t xml:space="preserve">0.335949867963791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343772262334824</t>
+    <t xml:space="preserve">0.343772232532501</t>
   </si>
   <si>
     <t xml:space="preserve">0.337596714496613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340066909790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340478628873825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332244515419006</t>
+    <t xml:space="preserve">0.340066879987717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340478599071503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332244545221329</t>
   </si>
   <si>
     <t xml:space="preserve">0.329362630844116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325657278299332</t>
+    <t xml:space="preserve">0.325657308101654</t>
   </si>
   <si>
     <t xml:space="preserve">0.338420122861862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346654176712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35571163892746</t>
+    <t xml:space="preserve">0.346654146909714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355711668729782</t>
   </si>
   <si>
     <t xml:space="preserve">0.359005272388458</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">0.377943605184555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38164895772934</t>
+    <t xml:space="preserve">0.381648927927017</t>
   </si>
   <si>
     <t xml:space="preserve">0.390294700860977</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">0.395235151052475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399763911962509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389471292495728</t>
+    <t xml:space="preserve">0.399763882160187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38947132229805</t>
   </si>
   <si>
     <t xml:space="preserve">0.401822417974472</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">0.411703288555145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402234137058258</t>
+    <t xml:space="preserve">0.402234107255936</t>
   </si>
   <si>
     <t xml:space="preserve">0.403469234704971</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">0.409644782543182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408409684896469</t>
+    <t xml:space="preserve">0.408409655094147</t>
   </si>
   <si>
     <t xml:space="preserve">0.40593945980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406351119279861</t>
+    <t xml:space="preserve">0.406351149082184</t>
   </si>
   <si>
     <t xml:space="preserve">0.400175601243973</t>
@@ -2693,19 +2693,19 @@
     <t xml:space="preserve">0.397705405950546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403880923986435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403057515621185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394823461771011</t>
+    <t xml:space="preserve">0.403880953788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403057485818863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394823431968689</t>
   </si>
   <si>
     <t xml:space="preserve">0.417467176914215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433111876249313</t>
+    <t xml:space="preserve">0.433111846446991</t>
   </si>
   <si>
     <t xml:space="preserve">0.430641680955887</t>
@@ -2717,22 +2717,22 @@
     <t xml:space="preserve">0.454520434141159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442992717027664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488280087709427</t>
+    <t xml:space="preserve">0.442992746829987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488280028104782</t>
   </si>
   <si>
     <t xml:space="preserve">0.50392484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534390926361084</t>
+    <t xml:space="preserve">0.534390807151794</t>
   </si>
   <si>
     <t xml:space="preserve">0.518746137619019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522039771080017</t>
+    <t xml:space="preserve">0.522039711475372</t>
   </si>
   <si>
     <t xml:space="preserve">0.500631153583527</t>
@@ -2747,13 +2747,13 @@
     <t xml:space="preserve">0.485809803009033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462754458189011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472635388374329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493220508098602</t>
+    <t xml:space="preserve">0.462754487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472635358572006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493220567703247</t>
   </si>
   <si>
     <t xml:space="preserve">0.491573750972748</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">0.467694938182831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459460943937302</t>
+    <t xml:space="preserve">0.459460914134979</t>
   </si>
   <si>
     <t xml:space="preserve">0.461107701063156</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">0.476752400398254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479222595691681</t>
+    <t xml:space="preserve">0.479222655296326</t>
   </si>
   <si>
     <t xml:space="preserve">0.477575838565826</t>
@@ -2786,25 +2786,25 @@
     <t xml:space="preserve">0.504748225212097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501454591751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498984456062317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494043976068497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505571722984314</t>
+    <t xml:space="preserve">0.501454532146454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498984396457672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494044005870819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505571663379669</t>
   </si>
   <si>
     <t xml:space="preserve">0.490750372409821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484986543655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492397129535675</t>
+    <t xml:space="preserve">0.484986424446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49239718914032</t>
   </si>
   <si>
     <t xml:space="preserve">0.482516258955002</t>
@@ -2813,22 +2813,22 @@
     <t xml:space="preserve">0.478399217128754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473458826541901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470988571643829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47016516327858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46522468328476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284262895584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46851834654808</t>
+    <t xml:space="preserve">0.473458737134933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470988541841507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470165133476257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465224713087082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284322500229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468518376350403</t>
   </si>
   <si>
     <t xml:space="preserve">0.466750353574753</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">0.457910388708115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46144637465477</t>
+    <t xml:space="preserve">0.461446404457092</t>
   </si>
   <si>
     <t xml:space="preserve">0.464098334312439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454374402761459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44111442565918</t>
+    <t xml:space="preserve">0.454374372959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441114455461502</t>
   </si>
   <si>
     <t xml:space="preserve">0.420782536268234</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">0.435810476541519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438462466001511</t>
+    <t xml:space="preserve">0.438462436199188</t>
   </si>
   <si>
     <t xml:space="preserve">0.427412509918213</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">0.433158487081528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448186457157135</t>
+    <t xml:space="preserve">0.448186427354813</t>
   </si>
   <si>
     <t xml:space="preserve">0.441998451948166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434484452009201</t>
+    <t xml:space="preserve">0.434484422206879</t>
   </si>
   <si>
     <t xml:space="preserve">0.44465047121048</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">0.430948466062546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4313904941082</t>
+    <t xml:space="preserve">0.431390464305878</t>
   </si>
   <si>
     <t xml:space="preserve">0.434926480054855</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">0.428738474845886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424318492412567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434042453765869</t>
+    <t xml:space="preserve">0.424318462610245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434042483568192</t>
   </si>
   <si>
     <t xml:space="preserve">0.421666502952576</t>
@@ -2930,28 +2930,28 @@
     <t xml:space="preserve">0.411942541599274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414152503013611</t>
+    <t xml:space="preserve">0.414152532815933</t>
   </si>
   <si>
     <t xml:space="preserve">0.41813051700592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422550469636917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413710534572601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425202518701553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423876464366913</t>
+    <t xml:space="preserve">0.42255049943924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413710504770279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425202488899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423876494169235</t>
   </si>
   <si>
     <t xml:space="preserve">0.414594531059265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422992527484894</t>
+    <t xml:space="preserve">0.422992497682571</t>
   </si>
   <si>
     <t xml:space="preserve">0.421224534511566</t>
@@ -2963,13 +2963,13 @@
     <t xml:space="preserve">0.415920525789261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408406555652618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412384539842606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411058515310287</t>
+    <t xml:space="preserve">0.408406585454941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412384569644928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41105854511261</t>
   </si>
   <si>
     <t xml:space="preserve">0.409732550382614</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">0.409290552139282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407964557409286</t>
+    <t xml:space="preserve">0.407964527606964</t>
   </si>
   <si>
     <t xml:space="preserve">0.423434525728226</t>
@@ -2993,16 +2993,16 @@
     <t xml:space="preserve">0.428296476602554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424760490655899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422108501195908</t>
+    <t xml:space="preserve">0.424760520458221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422108471393585</t>
   </si>
   <si>
     <t xml:space="preserve">0.415478527545929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402218610048294</t>
+    <t xml:space="preserve">0.402218580245972</t>
   </si>
   <si>
     <t xml:space="preserve">0.394262611865997</t>
@@ -3020,22 +3020,22 @@
     <t xml:space="preserve">0.396030604839325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405754536390305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403544545173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400450587272644</t>
+    <t xml:space="preserve">0.405754566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403544574975967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400450557470322</t>
   </si>
   <si>
     <t xml:space="preserve">0.389842629432678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388958632946014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395146578550339</t>
+    <t xml:space="preserve">0.388958603143692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395146608352661</t>
   </si>
   <si>
     <t xml:space="preserve">0.386748641729355</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">0.393378585577011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403102576732635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396914571523666</t>
+    <t xml:space="preserve">0.403102546930313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396914601325989</t>
   </si>
   <si>
     <t xml:space="preserve">0.397798597812653</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660548686981</t>
+    <t xml:space="preserve">0.402660578489304</t>
   </si>
   <si>
     <t xml:space="preserve">0.419898509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436694443225861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443766385316849</t>
+    <t xml:space="preserve">0.436694413423538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443766415119171</t>
   </si>
   <si>
     <t xml:space="preserve">0.453789889812469</t>
@@ -3963,6 +3963,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.584999978542328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58899998664856</t>
   </si>
 </sst>
 </file>
@@ -69249,7 +69252,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6909837963</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>115702</v>
@@ -69270,6 +69273,32 @@
         <v>1316</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6909722222</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>294138</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>0.596000015735626</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>0.583999991416931</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>0.586000025272369</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>0.58899998664856</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="1318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="1319">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333736211061478</t>
+    <t xml:space="preserve">0.333736181259155</t>
   </si>
   <si>
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327446281909943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321156322956085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317678391933441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307318449020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288448661565781</t>
+    <t xml:space="preserve">0.32744625210762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321156293153763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317678362131119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307318478822708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288448721170425</t>
   </si>
   <si>
     <t xml:space="preserve">0.289336681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294368624687195</t>
+    <t xml:space="preserve">0.294368594884872</t>
   </si>
   <si>
     <t xml:space="preserve">0.285636752843857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796856403351</t>
+    <t xml:space="preserve">0.273796916007996</t>
   </si>
   <si>
     <t xml:space="preserve">0.258997023105621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258257061243057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243605226278305</t>
+    <t xml:space="preserve">0.258257031440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243605196475983</t>
   </si>
   <si>
     <t xml:space="preserve">0.246417194604874</t>
@@ -89,22 +89,22 @@
     <t xml:space="preserve">0.256407082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.259811013936996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261512994766235</t>
+    <t xml:space="preserve">0.259811043739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261512964963913</t>
   </si>
   <si>
     <t xml:space="preserve">0.253817081451416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25307708978653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286894708871841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284600734710693</t>
+    <t xml:space="preserve">0.253077119588852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286894679069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284600794315338</t>
   </si>
   <si>
     <t xml:space="preserve">0.277496814727783</t>
@@ -119,34 +119,34 @@
     <t xml:space="preserve">0.263806968927383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256777107715607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.250117152929306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277570813894272</t>
+    <t xml:space="preserve">0.256777048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.250117123126984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277570784091949</t>
   </si>
   <si>
     <t xml:space="preserve">0.297994613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310796409845352</t>
+    <t xml:space="preserve">0.310796439647675</t>
   </si>
   <si>
     <t xml:space="preserve">0.303544491529465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304358541965485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318122357130051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309686481952667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301620543003082</t>
+    <t xml:space="preserve">0.304358512163162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318122327327728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309686422348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30162051320076</t>
   </si>
   <si>
     <t xml:space="preserve">0.310352444648743</t>
@@ -164,16 +164,16 @@
     <t xml:space="preserve">0.315236419439316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315606385469437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332996189594269</t>
+    <t xml:space="preserve">0.315606415271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332996219396591</t>
   </si>
   <si>
     <t xml:space="preserve">0.332256197929382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328852236270905</t>
+    <t xml:space="preserve">0.328852266073227</t>
   </si>
   <si>
     <t xml:space="preserve">0.330480217933655</t>
@@ -182,34 +182,34 @@
     <t xml:space="preserve">0.311240434646606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312054395675659</t>
+    <t xml:space="preserve">0.312054455280304</t>
   </si>
   <si>
     <t xml:space="preserve">0.299696564674377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296884566545486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299400568008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297476589679718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295996606349945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293702661991119</t>
+    <t xml:space="preserve">0.296884596347809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299400597810745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29747661948204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295996636152267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293702632188797</t>
   </si>
   <si>
     <t xml:space="preserve">0.298216551542282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286376744508743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276756852865219</t>
+    <t xml:space="preserve">0.286376714706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276756823062897</t>
   </si>
   <si>
     <t xml:space="preserve">0.27453687787056</t>
@@ -218,43 +218,43 @@
     <t xml:space="preserve">0.272316873073578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268542915582657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270466953516006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26506495475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268172919750214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268616944551468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269208878278732</t>
+    <t xml:space="preserve">0.268542945384979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270466893911362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265064984560013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268172949552536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268616914749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269208908081055</t>
   </si>
   <si>
     <t xml:space="preserve">0.275276869535446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284896701574326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290002673864365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308206468820572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309168487787247</t>
+    <t xml:space="preserve">0.284896731376648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290002703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308206498622894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309168457984924</t>
   </si>
   <si>
     <t xml:space="preserve">0.318196356296539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31693834066391</t>
+    <t xml:space="preserve">0.316938370466232</t>
   </si>
   <si>
     <t xml:space="preserve">0.308946460485458</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">0.314200401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321378290653229</t>
+    <t xml:space="preserve">0.321378320455551</t>
   </si>
   <si>
     <t xml:space="preserve">0.319380342960358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310722440481186</t>
+    <t xml:space="preserve">0.310722470283508</t>
   </si>
   <si>
     <t xml:space="preserve">0.313682407140732</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">0.30761444568634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304950505495071</t>
+    <t xml:space="preserve">0.304950475692749</t>
   </si>
   <si>
     <t xml:space="preserve">0.305616468191147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2995485663414</t>
+    <t xml:space="preserve">0.299548596143723</t>
   </si>
   <si>
     <t xml:space="preserve">0.305320501327515</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">0.295626640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300954550504684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314400315284729</t>
+    <t xml:space="preserve">0.300954520702362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314400285482407</t>
   </si>
   <si>
     <t xml:space="preserve">0.318779796361923</t>
@@ -311,64 +311,64 @@
     <t xml:space="preserve">0.318856596946716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318395614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319932252168655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318088293075562</t>
+    <t xml:space="preserve">0.318395644426346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319932281970978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318088263273239</t>
   </si>
   <si>
     <t xml:space="preserve">0.307331681251526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321776270866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320393294095993</t>
+    <t xml:space="preserve">0.321776300668716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320393264293671</t>
   </si>
   <si>
     <t xml:space="preserve">0.311557501554489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305795013904572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301569223403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295806705951691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299648404121399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296575099229813</t>
+    <t xml:space="preserve">0.305795043706894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301569253206253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295806735754013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299648344516754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29657506942749</t>
   </si>
   <si>
     <t xml:space="preserve">0.303490042686462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314246654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318011462688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318702965974808</t>
+    <t xml:space="preserve">0.31424668431282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318011432886124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318702936172485</t>
   </si>
   <si>
     <t xml:space="preserve">0.321161597967148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310020804405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311941653490067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311173319816589</t>
+    <t xml:space="preserve">0.310020834207535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311941623687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311173349618912</t>
   </si>
   <si>
     <t xml:space="preserve">0.307254880666733</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">0.305564552545547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304949879646301</t>
+    <t xml:space="preserve">0.304949849843979</t>
   </si>
   <si>
     <t xml:space="preserve">0.306870698928833</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">0.297727584838867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301799684762955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304027855396271</t>
+    <t xml:space="preserve">0.301799714565277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304027885198593</t>
   </si>
   <si>
     <t xml:space="preserve">0.300032585859299</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">0.312556326389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307869523763657</t>
+    <t xml:space="preserve">0.307869493961334</t>
   </si>
   <si>
     <t xml:space="preserve">0.311480671167374</t>
@@ -419,49 +419,49 @@
     <t xml:space="preserve">0.305257201194763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295576214790344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295960366725922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297650694847107</t>
+    <t xml:space="preserve">0.295576244592667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295960396528244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297650724649429</t>
   </si>
   <si>
     <t xml:space="preserve">0.297881215810776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29373225569725</t>
+    <t xml:space="preserve">0.293732225894928</t>
   </si>
   <si>
     <t xml:space="preserve">0.298803240060806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300416707992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300109356641769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298880070447922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30548769235611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30955982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303105890750885</t>
+    <t xml:space="preserve">0.300416737794876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300109386444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298880040645599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305487722158432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309559881687164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303105860948563</t>
   </si>
   <si>
     <t xml:space="preserve">0.303566873073578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308253675699234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304873049259186</t>
+    <t xml:space="preserve">0.308253705501556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304873019456863</t>
   </si>
   <si>
     <t xml:space="preserve">0.306563347578049</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">0.3006471991539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28297558426857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291965126991272</t>
+    <t xml:space="preserve">0.282975614070892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29196509718895</t>
   </si>
   <si>
     <t xml:space="preserve">0.289736926555634</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">0.292656570672989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292502909898758</t>
+    <t xml:space="preserve">0.29250293970108</t>
   </si>
   <si>
     <t xml:space="preserve">0.289583265781403</t>
@@ -506,61 +506,61 @@
     <t xml:space="preserve">0.288123458623886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284281820058823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287892997264862</t>
+    <t xml:space="preserve">0.284281849861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28789296746254</t>
   </si>
   <si>
     <t xml:space="preserve">0.290044277906418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292887091636658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293117612600327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291888266801834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289813816547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286586791276932</t>
+    <t xml:space="preserve">0.292887061834335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293117582798004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291888236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289813786745071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286586821079254</t>
   </si>
   <si>
     <t xml:space="preserve">0.294270068407059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291811406612396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292579799890518</t>
+    <t xml:space="preserve">0.291811436414719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292579770088196</t>
   </si>
   <si>
     <t xml:space="preserve">0.295729905366898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298419088125229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294731050729752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287355124950409</t>
+    <t xml:space="preserve">0.298419058322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294731080532074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287355095148087</t>
   </si>
   <si>
     <t xml:space="preserve">0.293809115886688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292041927576065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286740481853485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2846659719944</t>
+    <t xml:space="preserve">0.292041957378387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286740452051163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284665942192078</t>
   </si>
   <si>
     <t xml:space="preserve">0.278903514146805</t>
@@ -572,43 +572,43 @@
     <t xml:space="preserve">0.270221382379532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272449523210526</t>
+    <t xml:space="preserve">0.272449553012848</t>
   </si>
   <si>
     <t xml:space="preserve">0.276675373315811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27398619055748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275676548480988</t>
+    <t xml:space="preserve">0.273986160755157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275676518678665</t>
   </si>
   <si>
     <t xml:space="preserve">0.275522828102112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276598483324051</t>
+    <t xml:space="preserve">0.276598542928696</t>
   </si>
   <si>
     <t xml:space="preserve">0.270989716053009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27114337682724</t>
+    <t xml:space="preserve">0.271143406629562</t>
   </si>
   <si>
     <t xml:space="preserve">0.274293541908264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270451933145523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268146902322769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267378598451614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264612585306168</t>
+    <t xml:space="preserve">0.270451873540878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268146872520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267378568649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264612555503845</t>
   </si>
   <si>
     <t xml:space="preserve">0.265765070915222</t>
@@ -617,31 +617,31 @@
     <t xml:space="preserve">0.262384444475174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267532199621201</t>
+    <t xml:space="preserve">0.267532229423523</t>
   </si>
   <si>
     <t xml:space="preserve">0.265304088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271911680698395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272526413202286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283283025026321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279902309179306</t>
+    <t xml:space="preserve">0.271911710500717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272526383399963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283282995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279902338981628</t>
   </si>
   <si>
     <t xml:space="preserve">0.277059525251389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278442531824112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280517011880875</t>
+    <t xml:space="preserve">0.27844250202179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28051695227623</t>
   </si>
   <si>
     <t xml:space="preserve">0.278749823570251</t>
@@ -656,16 +656,16 @@
     <t xml:space="preserve">0.284051299095154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290812641382217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289660155773163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290428400039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294807910919189</t>
+    <t xml:space="preserve">0.290812611579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289660096168518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290428429841995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294807940721512</t>
   </si>
   <si>
     <t xml:space="preserve">0.295422583818436</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.288507610559464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284589141607285</t>
+    <t xml:space="preserve">0.284589171409607</t>
   </si>
   <si>
     <t xml:space="preserve">0.291043102741241</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">0.293885916471481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294884771108627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289890587329865</t>
+    <t xml:space="preserve">0.294884741306305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289890617132187</t>
   </si>
   <si>
     <t xml:space="preserve">0.286125808954239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284358620643616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282745152711868</t>
+    <t xml:space="preserve">0.284358650445938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282745122909546</t>
   </si>
   <si>
     <t xml:space="preserve">0.277290046215057</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">0.269760400056839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275061875581741</t>
+    <t xml:space="preserve">0.275061845779419</t>
   </si>
   <si>
     <t xml:space="preserve">0.271834880113602</t>
@@ -728,49 +728,49 @@
     <t xml:space="preserve">0.276905834674835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274831354618073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282668352127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280440181493759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279595047235489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27736684679985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278135150671005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278672963380814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282591491937637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279364496469498</t>
+    <t xml:space="preserve">0.27483132481575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282668322324753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280440151691437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279595017433167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277366816997528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278135180473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281208485364914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278672993183136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282591462135315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27936452627182</t>
   </si>
   <si>
     <t xml:space="preserve">0.285587966442108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27967181801796</t>
+    <t xml:space="preserve">0.279671788215637</t>
   </si>
   <si>
     <t xml:space="preserve">0.286663621664047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284435510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281899988651276</t>
+    <t xml:space="preserve">0.284435451030731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281899958848953</t>
   </si>
   <si>
     <t xml:space="preserve">0.283897668123245</t>
@@ -779,22 +779,22 @@
     <t xml:space="preserve">0.285280615091324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285434275865555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295038431882858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304258346557617</t>
+    <t xml:space="preserve">0.285434305667877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295038461685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30425837635994</t>
   </si>
   <si>
     <t xml:space="preserve">0.321929961442947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32561793923378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331841379404068</t>
+    <t xml:space="preserve">0.325617909431458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33184140920639</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387418270111</t>
@@ -803,28 +803,28 @@
     <t xml:space="preserve">0.316935807466507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309790313243866</t>
+    <t xml:space="preserve">0.309790343046188</t>
   </si>
   <si>
     <t xml:space="preserve">0.309252500534058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311096519231796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313094168901443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313017308712006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288891762495041</t>
+    <t xml:space="preserve">0.311096489429474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313094139099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313017338514328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288891822099686</t>
   </si>
   <si>
     <t xml:space="preserve">0.293040752410889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295192092657089</t>
+    <t xml:space="preserve">0.295192062854767</t>
   </si>
   <si>
     <t xml:space="preserve">0.296805590391159</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">0.298111766576767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310251295566559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313555121421814</t>
+    <t xml:space="preserve">0.310251355171204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313555151224136</t>
   </si>
   <si>
     <t xml:space="preserve">0.300800889730453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308868318796158</t>
+    <t xml:space="preserve">0.30886834859848</t>
   </si>
   <si>
     <t xml:space="preserve">0.299725204706192</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">0.32185310125351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327308297157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318472474813461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312095314264297</t>
+    <t xml:space="preserve">0.327308267354965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318472445011139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312095284461975</t>
   </si>
   <si>
     <t xml:space="preserve">0.314016163349152</t>
@@ -875,64 +875,64 @@
     <t xml:space="preserve">0.313939303159714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309636682271957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307408541440964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308945178985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313631981611252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30802321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307715833187103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309022039175034</t>
+    <t xml:space="preserve">0.309636652469635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307408511638641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308945119380951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313632011413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308023184537888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307715862989426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309022009372711</t>
   </si>
   <si>
     <t xml:space="preserve">0.309944003820419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317780941724777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316551625728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316474795341492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324388593435287</t>
+    <t xml:space="preserve">0.3177809715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31655165553093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316474825143814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324388563632965</t>
   </si>
   <si>
     <t xml:space="preserve">0.325003296136856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318318754434586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317704111337662</t>
+    <t xml:space="preserve">0.318318784236908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317704141139984</t>
   </si>
   <si>
     <t xml:space="preserve">0.321545779705048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320470094680786</t>
+    <t xml:space="preserve">0.320470154285431</t>
   </si>
   <si>
     <t xml:space="preserve">0.322621405124664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323697090148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333454847335815</t>
+    <t xml:space="preserve">0.323697060346603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333454877138138</t>
   </si>
   <si>
     <t xml:space="preserve">0.327385067939758</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">0.339524686336517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34567129611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340446680784225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333378046751022</t>
+    <t xml:space="preserve">0.345671355724335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340446710586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3333780169487</t>
   </si>
   <si>
     <t xml:space="preserve">0.33499151468277</t>
@@ -959,52 +959,52 @@
     <t xml:space="preserve">0.336144030094147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337757498025894</t>
+    <t xml:space="preserve">0.337757527828217</t>
   </si>
   <si>
     <t xml:space="preserve">0.338910013437271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338141679763794</t>
+    <t xml:space="preserve">0.338141649961472</t>
   </si>
   <si>
     <t xml:space="preserve">0.339678376913071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350358128547668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346593260765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344211488962173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340677201747894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334607362747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338218510150909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346900671720505</t>
+    <t xml:space="preserve">0.350358098745346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34659332036972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344211518764496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340677171945572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33460733294487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338218539953232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346900641918182</t>
   </si>
   <si>
     <t xml:space="preserve">0.346132338047028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339601516723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340907663106918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352663099765778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369950473308563</t>
+    <t xml:space="preserve">0.33960148692131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340907692909241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3526631295681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369950503110886</t>
   </si>
   <si>
     <t xml:space="preserve">0.36541736125946</t>
@@ -1013,19 +1013,19 @@
     <t xml:space="preserve">0.363035529851913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374099493026733</t>
+    <t xml:space="preserve">0.374099522829056</t>
   </si>
   <si>
     <t xml:space="preserve">0.371103018522263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369566380977631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368797987699509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366108864545822</t>
+    <t xml:space="preserve">0.369566351175308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368798017501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366108894348145</t>
   </si>
   <si>
     <t xml:space="preserve">0.363112419843674</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">0.366262555122375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361114740371704</t>
+    <t xml:space="preserve">0.361114770174026</t>
   </si>
   <si>
     <t xml:space="preserve">0.359885394573212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359193861484528</t>
+    <t xml:space="preserve">0.359193921089172</t>
   </si>
   <si>
     <t xml:space="preserve">0.368567526340485</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">0.375559329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380246132612228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392616212368011</t>
+    <t xml:space="preserve">0.380246102809906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392616182565689</t>
   </si>
   <si>
     <t xml:space="preserve">0.405677855014801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421044379472733</t>
+    <t xml:space="preserve">0.421044409275055</t>
   </si>
   <si>
     <t xml:space="preserve">0.419507741928101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396842062473297</t>
+    <t xml:space="preserve">0.396842032670975</t>
   </si>
   <si>
     <t xml:space="preserve">0.413361132144928</t>
@@ -1085,37 +1085,37 @@
     <t xml:space="preserve">0.417586892843246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426422744989395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423349410295486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427959322929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436795175075531</t>
+    <t xml:space="preserve">0.426422715187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423349440097809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427959382534027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436795145273209</t>
   </si>
   <si>
     <t xml:space="preserve">0.432953506708145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452930063009262</t>
+    <t xml:space="preserve">0.452930092811584</t>
   </si>
   <si>
     <t xml:space="preserve">0.459460854530334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465223342180252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296676874161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48135831952095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522463858127594</t>
+    <t xml:space="preserve">0.465223401784897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296647071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481358200311661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522463798522949</t>
   </si>
   <si>
     <t xml:space="preserve">0.515164732933044</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">0.505560636520386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507097244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515548825263977</t>
+    <t xml:space="preserve">0.50709730386734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515548884868622</t>
   </si>
   <si>
     <t xml:space="preserve">0.503255605697632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48980987071991</t>
+    <t xml:space="preserve">0.489809930324554</t>
   </si>
   <si>
     <t xml:space="preserve">0.480205744504929</t>
@@ -1142,64 +1142,64 @@
     <t xml:space="preserve">0.519006371498108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511323094367981</t>
+    <t xml:space="preserve">0.511322975158691</t>
   </si>
   <si>
     <t xml:space="preserve">0.499413967132568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491730660200119</t>
+    <t xml:space="preserve">0.491730719804764</t>
   </si>
   <si>
     <t xml:space="preserve">0.484431564807892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483663260936737</t>
+    <t xml:space="preserve">0.483663201332092</t>
   </si>
   <si>
     <t xml:space="preserve">0.484815716743469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495188236236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490194022655487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553196966648102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542056202888489</t>
+    <t xml:space="preserve">0.495188176631927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490194082260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553197085857391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542056322097778</t>
   </si>
   <si>
     <t xml:space="preserve">0.56280118227005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586235225200653</t>
+    <t xml:space="preserve">0.586235165596008</t>
   </si>
   <si>
     <t xml:space="preserve">0.600065171718597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58239358663559</t>
+    <t xml:space="preserve">0.582393527030945</t>
   </si>
   <si>
     <t xml:space="preserve">0.572021067142487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572789430618286</t>
+    <t xml:space="preserve">0.572789490222931</t>
   </si>
   <si>
     <t xml:space="preserve">0.552428662776947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551276206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545129537582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565874516963959</t>
+    <t xml:space="preserve">0.55127614736557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545129597187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565874457359314</t>
   </si>
   <si>
     <t xml:space="preserve">0.577015221118927</t>
@@ -1208,31 +1208,31 @@
     <t xml:space="preserve">0.596607625484467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584698557853699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608132541179657</t>
+    <t xml:space="preserve">0.584698498249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608132481575012</t>
   </si>
   <si>
     <t xml:space="preserve">0.621962487697601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620425879955292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629645764827728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614279270172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607748329639435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581625282764435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560880362987518</t>
+    <t xml:space="preserve">0.620425820350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629645824432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614279210567474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60774838924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58162522315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560880303382874</t>
   </si>
   <si>
     <t xml:space="preserve">0.598528444766998</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">0.601601779460907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586619317531586</t>
+    <t xml:space="preserve">0.58661937713623</t>
   </si>
   <si>
     <t xml:space="preserve">0.595455169677734</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">0.587771832942963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584314346313477</t>
+    <t xml:space="preserve">0.584314405918121</t>
   </si>
   <si>
     <t xml:space="preserve">0.577399373054504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567026913166046</t>
+    <t xml:space="preserve">0.567026972770691</t>
   </si>
   <si>
     <t xml:space="preserve">0.57432609796524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543592929840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564721941947937</t>
+    <t xml:space="preserve">0.543592870235443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564722001552582</t>
   </si>
   <si>
     <t xml:space="preserve">0.563185334205627</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">0.576246917247772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583930253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580856800079346</t>
+    <t xml:space="preserve">0.583930194377899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58085685968399</t>
   </si>
   <si>
     <t xml:space="preserve">0.587003529071808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604674994945526</t>
+    <t xml:space="preserve">0.604675054550171</t>
   </si>
   <si>
     <t xml:space="preserve">0.629261612892151</t>
@@ -1304,13 +1304,13 @@
     <t xml:space="preserve">0.606980085372925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603138446807861</t>
+    <t xml:space="preserve">0.603138506412506</t>
   </si>
   <si>
     <t xml:space="preserve">0.612358391284943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611590027809143</t>
+    <t xml:space="preserve">0.611590087413788</t>
   </si>
   <si>
     <t xml:space="preserve">0.593918442726135</t>
@@ -1319,25 +1319,25 @@
     <t xml:space="preserve">0.596991777420044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608516693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599296808242798</t>
+    <t xml:space="preserve">0.608516752719879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599296689033508</t>
   </si>
   <si>
     <t xml:space="preserve">0.589308559894562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553965389728546</t>
+    <t xml:space="preserve">0.553965330123901</t>
   </si>
   <si>
     <t xml:space="preserve">0.538598775863647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557038724422455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536293804645538</t>
+    <t xml:space="preserve">0.55703866481781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536293745040894</t>
   </si>
   <si>
     <t xml:space="preserve">0.524000525474548</t>
@@ -1349,25 +1349,25 @@
     <t xml:space="preserve">0.547818720340729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53245222568512</t>
+    <t xml:space="preserve">0.532452166080475</t>
   </si>
   <si>
     <t xml:space="preserve">0.537062108516693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527073860168457</t>
+    <t xml:space="preserve">0.527073800563812</t>
   </si>
   <si>
     <t xml:space="preserve">0.52092719078064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517853856086731</t>
+    <t xml:space="preserve">0.517853915691376</t>
   </si>
   <si>
     <t xml:space="preserve">0.525537192821503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53014725446701</t>
+    <t xml:space="preserve">0.530147194862366</t>
   </si>
   <si>
     <t xml:space="preserve">0.523232221603394</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">0.492499023675919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477900743484497</t>
+    <t xml:space="preserve">0.477900683879852</t>
   </si>
   <si>
     <t xml:space="preserve">0.476364135742188</t>
@@ -1397,16 +1397,16 @@
     <t xml:space="preserve">0.488657355308533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471754163503647</t>
+    <t xml:space="preserve">0.471754193305969</t>
   </si>
   <si>
     <t xml:space="preserve">0.472522437572479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468680888414383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487120658159256</t>
+    <t xml:space="preserve">0.468680799007416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487120717763901</t>
   </si>
   <si>
     <t xml:space="preserve">0.481742471456528</t>
@@ -1415,70 +1415,70 @@
     <t xml:space="preserve">0.480974107980728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483279049396515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478669166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470217496156693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467912554740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466375827789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839249849319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461765855550766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487889021635056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500182271003723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469449102878571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437179386615753</t>
+    <t xml:space="preserve">0.48327910900116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478669106960297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470217406749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467912524938583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466375797986984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839190244675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461765885353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487889051437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500182330608368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469449192285538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437179327011108</t>
   </si>
   <si>
     <t xml:space="preserve">0.444862604141235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431800991296768</t>
+    <t xml:space="preserve">0.431800931692123</t>
   </si>
   <si>
     <t xml:space="preserve">0.444094270467758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424117684364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415666103363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382627993822098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379170477390289</t>
+    <t xml:space="preserve">0.424117714166641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415666133165359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382627964019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379170447587967</t>
   </si>
   <si>
     <t xml:space="preserve">0.382243782281876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385701268911362</t>
+    <t xml:space="preserve">0.385701239109039</t>
   </si>
   <si>
     <t xml:space="preserve">0.388774544000626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391847848892212</t>
+    <t xml:space="preserve">0.391847878694534</t>
   </si>
   <si>
     <t xml:space="preserve">0.384164601564407</t>
@@ -1490,25 +1490,25 @@
     <t xml:space="preserve">0.367261350154877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364956349134445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360346406698227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3522789478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356504738330841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37148717045784</t>
+    <t xml:space="preserve">0.364956378936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360346436500549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352278977632523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356504708528519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371487200260162</t>
   </si>
   <si>
     <t xml:space="preserve">0.368029683828354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372255504131317</t>
+    <t xml:space="preserve">0.372255474328995</t>
   </si>
   <si>
     <t xml:space="preserve">0.365340530872345</t>
@@ -1517,40 +1517,40 @@
     <t xml:space="preserve">0.374944686889648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366493046283722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374560534954071</t>
+    <t xml:space="preserve">0.3664930164814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374560505151749</t>
   </si>
   <si>
     <t xml:space="preserve">0.374176323413849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37878629565239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362267196178436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353815615177155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354583948850632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353047311306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370718866586685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354199767112732</t>
+    <t xml:space="preserve">0.378786265850067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362267255783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353815585374832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354583919048309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353047251701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37071880698204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35419973731041</t>
   </si>
   <si>
     <t xml:space="preserve">0.395689517259598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411056131124496</t>
+    <t xml:space="preserve">0.411056160926819</t>
   </si>
   <si>
     <t xml:space="preserve">0.40798282623291</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">0.390311241149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378017991781235</t>
+    <t xml:space="preserve">0.378017961978912</t>
   </si>
   <si>
     <t xml:space="preserve">0.380707114934921</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">0.362651377916336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35957807302475</t>
+    <t xml:space="preserve">0.359578043222427</t>
   </si>
   <si>
     <t xml:space="preserve">0.353431463241577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349589824676514</t>
+    <t xml:space="preserve">0.349589794874191</t>
   </si>
   <si>
     <t xml:space="preserve">0.344979822635651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343058973550797</t>
+    <t xml:space="preserve">0.343059003353119</t>
   </si>
   <si>
     <t xml:space="preserve">0.354968130588531</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">0.36418804526329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357273101806641</t>
+    <t xml:space="preserve">0.357273072004318</t>
   </si>
   <si>
     <t xml:space="preserve">0.349973976612091</t>
@@ -1607,31 +1607,31 @@
     <t xml:space="preserve">0.361883044242859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350742280483246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389542937278748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404141157865524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396457850933075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412592828273773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404909521341324</t>
+    <t xml:space="preserve">0.350742250680923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38954296708107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404141187667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396457880735397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412592768669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404909551143646</t>
   </si>
   <si>
     <t xml:space="preserve">0.401836186647415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394152879714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399531185626984</t>
+    <t xml:space="preserve">0.394152909517288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399531215429306</t>
   </si>
   <si>
     <t xml:space="preserve">0.40260449051857</t>
@@ -1640,19 +1640,19 @@
     <t xml:space="preserve">0.401067852973938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397994548082352</t>
+    <t xml:space="preserve">0.397994518280029</t>
   </si>
   <si>
     <t xml:space="preserve">0.375712960958481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364572167396545</t>
+    <t xml:space="preserve">0.36457222700119</t>
   </si>
   <si>
     <t xml:space="preserve">0.345748126506805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336528182029724</t>
+    <t xml:space="preserve">0.336528211832047</t>
   </si>
   <si>
     <t xml:space="preserve">0.335759878158569</t>
@@ -1664,40 +1664,40 @@
     <t xml:space="preserve">0.329613208770752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32807657122612</t>
+    <t xml:space="preserve">0.328076541423798</t>
   </si>
   <si>
     <t xml:space="preserve">0.331534028053284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319240808486938</t>
+    <t xml:space="preserve">0.319240778684616</t>
   </si>
   <si>
     <t xml:space="preserve">0.326924085617065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312709987163544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341138184070587</t>
+    <t xml:space="preserve">0.312710016965866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34113821387291</t>
   </si>
   <si>
     <t xml:space="preserve">0.322698295116425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326155781745911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324619114398956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325771600008011</t>
+    <t xml:space="preserve">0.326155751943588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324619084596634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325771570205688</t>
   </si>
   <si>
     <t xml:space="preserve">0.330381572246552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329997390508652</t>
+    <t xml:space="preserve">0.329997420310974</t>
   </si>
   <si>
     <t xml:space="preserve">0.324234902858734</t>
@@ -1709,19 +1709,19 @@
     <t xml:space="preserve">0.301185011863708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303874164819717</t>
+    <t xml:space="preserve">0.30387419462204</t>
   </si>
   <si>
     <t xml:space="preserve">0.296959221363068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302721709012985</t>
+    <t xml:space="preserve">0.302721738815308</t>
   </si>
   <si>
     <t xml:space="preserve">0.32308241724968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308100014925003</t>
+    <t xml:space="preserve">0.308100044727325</t>
   </si>
   <si>
     <t xml:space="preserve">0.310405015945435</t>
@@ -1736,61 +1736,61 @@
     <t xml:space="preserve">0.305410861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308484196662903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304642498493195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320777475833893</t>
+    <t xml:space="preserve">0.30848416686058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304642528295517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32077744603157</t>
   </si>
   <si>
     <t xml:space="preserve">0.356888920068741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358041375875473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356120586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360730588436127</t>
+    <t xml:space="preserve">0.358041405677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356120616197586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360730558633804</t>
   </si>
   <si>
     <t xml:space="preserve">0.358809739351273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351126432418823</t>
+    <t xml:space="preserve">0.351126462221146</t>
   </si>
   <si>
     <t xml:space="preserve">0.355736434459686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342290639877319</t>
+    <t xml:space="preserve">0.342290669679642</t>
   </si>
   <si>
     <t xml:space="preserve">0.37187135219574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370334655046463</t>
+    <t xml:space="preserve">0.370334684848785</t>
   </si>
   <si>
     <t xml:space="preserve">0.38378044962883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376097172498703</t>
+    <t xml:space="preserve">0.376097142696381</t>
   </si>
   <si>
     <t xml:space="preserve">0.376865476369858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37724968791008</t>
+    <t xml:space="preserve">0.377249658107758</t>
   </si>
   <si>
     <t xml:space="preserve">0.398762851953506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403372824192047</t>
+    <t xml:space="preserve">0.40337285399437</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446129083633</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">0.409519463777542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39107957482338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381475478410721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407214492559433</t>
+    <t xml:space="preserve">0.391079604625702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381475448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407214432954788</t>
   </si>
   <si>
     <t xml:space="preserve">0.387237936258316</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">0.411824464797974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41489776968956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417202711105347</t>
+    <t xml:space="preserve">0.414897799491882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417202740907669</t>
   </si>
   <si>
     <t xml:space="preserve">0.397226184606552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408751159906387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410287797451019</t>
+    <t xml:space="preserve">0.408751130104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410287767648697</t>
   </si>
   <si>
     <t xml:space="preserve">0.41412940621376</t>
@@ -1838,28 +1838,28 @@
     <t xml:space="preserve">0.416434437036514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418739438056946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420276075601578</t>
+    <t xml:space="preserve">0.418739408254623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420276015996933</t>
   </si>
   <si>
     <t xml:space="preserve">0.421812742948532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430264383554459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473290801048279</t>
+    <t xml:space="preserve">0.430264353752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473290771245956</t>
   </si>
   <si>
     <t xml:space="preserve">0.49480402469635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484047472476959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267327547073</t>
+    <t xml:space="preserve">0.48404735326767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267416954041</t>
   </si>
   <si>
     <t xml:space="preserve">0.506328999996185</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">0.479437470436096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48251074552536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595831871033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070796966553</t>
+    <t xml:space="preserve">0.482510715723038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595772266388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46407076716423</t>
   </si>
   <si>
     <t xml:space="preserve">0.465607523918152</t>
@@ -1886,31 +1886,31 @@
     <t xml:space="preserve">0.453314214944839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434106022119522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789239645004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44563090801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449472546577454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451009273529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460229218006134</t>
+    <t xml:space="preserve">0.4341059923172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789329051971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445630878210068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449472606182098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451009213924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460229188203812</t>
   </si>
   <si>
     <t xml:space="preserve">0.454082578420639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457155913114548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451777547597885</t>
+    <t xml:space="preserve">0.457155883312225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451777637004852</t>
   </si>
   <si>
     <t xml:space="preserve">0.456387549638748</t>
@@ -1919,22 +1919,22 @@
     <t xml:space="preserve">0.463302493095398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470985859632492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467144101858139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457924246788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447167634963989</t>
+    <t xml:space="preserve">0.470985770225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467144131660461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457924216985703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447167605161667</t>
   </si>
   <si>
     <t xml:space="preserve">0.43256938457489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437947630882263</t>
+    <t xml:space="preserve">0.437947660684586</t>
   </si>
   <si>
     <t xml:space="preserve">0.433337688446045</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">0.434874325990677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436410993337631</t>
+    <t xml:space="preserve">0.436411023139954</t>
   </si>
   <si>
     <t xml:space="preserve">0.43948432803154</t>
@@ -1952,10 +1952,10 @@
     <t xml:space="preserve">0.441020995378494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440252691507339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438715934753418</t>
+    <t xml:space="preserve">0.440252602100372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438715904951096</t>
   </si>
   <si>
     <t xml:space="preserve">0.442557603120804</t>
@@ -1964,82 +1964,82 @@
     <t xml:space="preserve">0.485584050416946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455619186162949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443325966596603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429496049880981</t>
+    <t xml:space="preserve">0.455619215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443325996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429496079683304</t>
   </si>
   <si>
     <t xml:space="preserve">0.435642659664154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450240939855576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427191078662872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375328779220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386469572782516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393384575843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365724712610245</t>
+    <t xml:space="preserve">0.450240910053253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427191019058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375328809022903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386469602584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393384605646133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365724742412567</t>
   </si>
   <si>
     <t xml:space="preserve">0.372639685869217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351510643959045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342674821615219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317319989204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265073627233505</t>
+    <t xml:space="preserve">0.351510614156723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342674851417542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317319959402084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265073597431183</t>
   </si>
   <si>
     <t xml:space="preserve">0.259695291519165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239334583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24202373623848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234724551439285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24586533010006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258926928043365</t>
+    <t xml:space="preserve">0.239334553480148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242023676633835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234724596142769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245865359902382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258926957845688</t>
   </si>
   <si>
     <t xml:space="preserve">0.251627802848816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266610234975815</t>
+    <t xml:space="preserve">0.266610264778137</t>
   </si>
   <si>
     <t xml:space="preserve">0.269299387931824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258158624172211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.251243650913239</t>
+    <t xml:space="preserve">0.258158594369888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.251243621110916</t>
   </si>
   <si>
     <t xml:space="preserve">0.252011984586716</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">0.242407858371735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245097011327744</t>
+    <t xml:space="preserve">0.245097041130066</t>
   </si>
   <si>
     <t xml:space="preserve">0.254701107740402</t>
@@ -2057,10 +2057,10 @@
     <t xml:space="preserve">0.262000262737274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254316985607147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261231929063797</t>
+    <t xml:space="preserve">0.254316955804825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261231899261475</t>
   </si>
   <si>
     <t xml:space="preserve">0.262768596410751</t>
@@ -2075,28 +2075,28 @@
     <t xml:space="preserve">0.273909360170364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276982694864273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272756844758987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275445997714996</t>
+    <t xml:space="preserve">0.276982665061951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27275687456131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275446057319641</t>
   </si>
   <si>
     <t xml:space="preserve">0.268915235996246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265841871500015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25854280591011</t>
+    <t xml:space="preserve">0.265841901302338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258542746305466</t>
   </si>
   <si>
     <t xml:space="preserve">0.265457719564438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263152748346329</t>
+    <t xml:space="preserve">0.263152778148651</t>
   </si>
   <si>
     <t xml:space="preserve">0.292733430862427</t>
@@ -2105,16 +2105,16 @@
     <t xml:space="preserve">0.327692419290543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302337497472763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301953375339508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332302361726761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332686573266983</t>
+    <t xml:space="preserve">0.302337527275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301953345537186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332302391529083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332686543464661</t>
   </si>
   <si>
     <t xml:space="preserve">0.306179195642471</t>
@@ -2126,34 +2126,34 @@
     <t xml:space="preserve">0.312325805425644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331918209791183</t>
+    <t xml:space="preserve">0.331918239593506</t>
   </si>
   <si>
     <t xml:space="preserve">0.31539911031723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326539903879166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292349278926849</t>
+    <t xml:space="preserve">0.326539933681488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292349249124527</t>
   </si>
   <si>
     <t xml:space="preserve">0.289275974035263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291196793317795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286970973014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285050094127655</t>
+    <t xml:space="preserve">0.291196763515472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286970943212509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285050123929977</t>
   </si>
   <si>
     <t xml:space="preserve">0.273525178432465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260847806930542</t>
+    <t xml:space="preserve">0.26084777712822</t>
   </si>
   <si>
     <t xml:space="preserve">0.261616110801697</t>
@@ -2162,28 +2162,28 @@
     <t xml:space="preserve">0.270067721605301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278519362211227</t>
+    <t xml:space="preserve">0.278519332408905</t>
   </si>
   <si>
     <t xml:space="preserve">0.27314105629921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266994416713715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.255469441413879</t>
+    <t xml:space="preserve">0.266994386911392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.255469471216202</t>
   </si>
   <si>
     <t xml:space="preserve">0.253164499998093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256621927022934</t>
+    <t xml:space="preserve">0.256621986627579</t>
   </si>
   <si>
     <t xml:space="preserve">0.256237804889679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249322816729546</t>
+    <t xml:space="preserve">0.249322846531868</t>
   </si>
   <si>
     <t xml:space="preserve">0.23626121878624</t>
@@ -2192,13 +2192,13 @@
     <t xml:space="preserve">0.238182067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253548622131348</t>
+    <t xml:space="preserve">0.25354865193367</t>
   </si>
   <si>
     <t xml:space="preserve">0.267762750387192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283513456583023</t>
+    <t xml:space="preserve">0.283513486385345</t>
   </si>
   <si>
     <t xml:space="preserve">0.277750998735428</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">0.294654279947281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319624990224838</t>
+    <t xml:space="preserve">0.319624960422516</t>
   </si>
   <si>
     <t xml:space="preserve">0.343827307224274</t>
@@ -2216,28 +2216,28 @@
     <t xml:space="preserve">0.338449001312256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34075403213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338833183050156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338064879179001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336912333965302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333839058876038</t>
+    <t xml:space="preserve">0.340754002332687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338833212852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338064819574356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336912363767624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333839029073715</t>
   </si>
   <si>
     <t xml:space="preserve">0.330765724182129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328844875097275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33998566865921</t>
+    <t xml:space="preserve">0.328844904899597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339985698461533</t>
   </si>
   <si>
     <t xml:space="preserve">0.34766897559166</t>
@@ -2246,31 +2246,31 @@
     <t xml:space="preserve">0.359962224960327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351894795894623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369182229042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357657223939896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355352282524109</t>
+    <t xml:space="preserve">0.3518947660923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369182199239731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357657253742218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355352252721786</t>
   </si>
   <si>
     <t xml:space="preserve">0.348053127527237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346516489982605</t>
+    <t xml:space="preserve">0.346516519784927</t>
   </si>
   <si>
     <t xml:space="preserve">0.34728479385376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363419681787491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373792171478271</t>
+    <t xml:space="preserve">0.363419741392136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373792141675949</t>
   </si>
   <si>
     <t xml:space="preserve">0.373023808002472</t>
@@ -2282,31 +2282,31 @@
     <t xml:space="preserve">0.425654381513596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417971104383469</t>
+    <t xml:space="preserve">0.417971134185791</t>
   </si>
   <si>
     <t xml:space="preserve">0.381859600543976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383012115955353</t>
+    <t xml:space="preserve">0.38301208615303</t>
   </si>
   <si>
     <t xml:space="preserve">0.377633810043335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378402143716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381091266870499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380322992801666</t>
+    <t xml:space="preserve">0.378402173519135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381091296672821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380322962999344</t>
   </si>
   <si>
     <t xml:space="preserve">0.348437309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400299578905106</t>
+    <t xml:space="preserve">0.400299519300461</t>
   </si>
   <si>
     <t xml:space="preserve">0.383396297693253</t>
@@ -2315,31 +2315,31 @@
     <t xml:space="preserve">0.379938811063766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388006269931793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428727716207504</t>
+    <t xml:space="preserve">0.388006240129471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428727686405182</t>
   </si>
   <si>
     <t xml:space="preserve">0.368413865566254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344595670700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334223181009293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341906487941742</t>
+    <t xml:space="preserve">0.344595640897751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334223210811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341906517744064</t>
   </si>
   <si>
     <t xml:space="preserve">0.323466598987579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340369820594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331149905920029</t>
+    <t xml:space="preserve">0.340369790792465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331149876117706</t>
   </si>
   <si>
     <t xml:space="preserve">0.348821461200714</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">0.285818487405777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337680667638779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345363944768906</t>
+    <t xml:space="preserve">0.337680697441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345363974571228</t>
   </si>
   <si>
     <t xml:space="preserve">0.341522336006165</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">0.351594597101212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35406482219696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352829694747925</t>
+    <t xml:space="preserve">0.354064851999283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352829724550247</t>
   </si>
   <si>
     <t xml:space="preserve">0.347477555274963</t>
@@ -2384,25 +2384,25 @@
     <t xml:space="preserve">0.341713696718216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34253716468811</t>
+    <t xml:space="preserve">0.342537134885788</t>
   </si>
   <si>
     <t xml:space="preserve">0.348300993442535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359828650951385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353241384029388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35488823056221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350359499454498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345007330179214</t>
+    <t xml:space="preserve">0.35982871055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353241413831711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354888200759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350359529256821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345007389783859</t>
   </si>
   <si>
     <t xml:space="preserve">0.339655220508575</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">0.312894523143768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31824666261673</t>
+    <t xml:space="preserve">0.318246603012085</t>
   </si>
   <si>
     <t xml:space="preserve">0.317834943532944</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">0.319481790065765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312071114778519</t>
+    <t xml:space="preserve">0.312071084976196</t>
   </si>
   <si>
     <t xml:space="preserve">0.308365762233734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310012578964233</t>
+    <t xml:space="preserve">0.310012608766556</t>
   </si>
   <si>
     <t xml:space="preserve">0.314541310071945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318658322095871</t>
+    <t xml:space="preserve">0.318658351898193</t>
   </si>
   <si>
     <t xml:space="preserve">0.320305168628693</t>
@@ -2468,25 +2468,25 @@
     <t xml:space="preserve">0.322775393724442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309600859880447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309189170598984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321128576993942</t>
+    <t xml:space="preserve">0.30960088968277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309189200401306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321128517389297</t>
   </si>
   <si>
     <t xml:space="preserve">0.32195195555687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325245589017868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326892405748367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323187112808228</t>
+    <t xml:space="preserve">0.32524561882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32689243555069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32318714261055</t>
   </si>
   <si>
     <t xml:space="preserve">0.323598772287369</t>
@@ -2495,28 +2495,28 @@
     <t xml:space="preserve">0.315364688634872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313306242227554</t>
+    <t xml:space="preserve">0.31330618262291</t>
   </si>
   <si>
     <t xml:space="preserve">0.310424268245697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314953029155731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311247646808624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317011505365372</t>
+    <t xml:space="preserve">0.314952999353409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311247676610947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317011535167694</t>
   </si>
   <si>
     <t xml:space="preserve">0.317423224449158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31165936589241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316188126802444</t>
+    <t xml:space="preserve">0.311659395694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316188156604767</t>
   </si>
   <si>
     <t xml:space="preserve">0.319893479347229</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">0.30877748131752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303013622760773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307542353868484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302601933479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307954072952271</t>
+    <t xml:space="preserve">0.30301359295845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307542324066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302601963281631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307954043149948</t>
   </si>
   <si>
     <t xml:space="preserve">0.306307286024094</t>
@@ -2546,10 +2546,10 @@
     <t xml:space="preserve">0.301778525114059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3038370013237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300955086946487</t>
+    <t xml:space="preserve">0.303837031126022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30095511674881</t>
   </si>
   <si>
     <t xml:space="preserve">0.301366806030273</t>
@@ -2558,22 +2558,22 @@
     <t xml:space="preserve">0.302190214395523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313717931509018</t>
+    <t xml:space="preserve">0.313717901706696</t>
   </si>
   <si>
     <t xml:space="preserve">0.326480716466904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328539222478867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340890347957611</t>
+    <t xml:space="preserve">0.328539192676544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340890318155289</t>
   </si>
   <si>
     <t xml:space="preserve">0.356535047292709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343360513448715</t>
+    <t xml:space="preserve">0.343360543251038</t>
   </si>
   <si>
     <t xml:space="preserve">0.336361587047577</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">0.339243531227112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335126459598541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358181834220886</t>
+    <t xml:space="preserve">0.335126489400864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358181864023209</t>
   </si>
   <si>
     <t xml:space="preserve">0.3470658659935</t>
@@ -2594,31 +2594,31 @@
     <t xml:space="preserve">0.344183951616287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336773276329041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345419079065323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349124401807785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338008433580399</t>
+    <t xml:space="preserve">0.336773306131363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345419049263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349124372005463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338008373975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.335949867963791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343772232532501</t>
+    <t xml:space="preserve">0.343772262334824</t>
   </si>
   <si>
     <t xml:space="preserve">0.337596714496613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340066879987717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340478599071503</t>
+    <t xml:space="preserve">0.340066909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340478628873825</t>
   </si>
   <si>
     <t xml:space="preserve">0.332244545221329</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">0.329362630844116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325657308101654</t>
+    <t xml:space="preserve">0.325657278299332</t>
   </si>
   <si>
     <t xml:space="preserve">0.338420122861862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346654146909714</t>
+    <t xml:space="preserve">0.346654206514359</t>
   </si>
   <si>
     <t xml:space="preserve">0.355711668729782</t>
@@ -2645,10 +2645,10 @@
     <t xml:space="preserve">0.370121270418167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377943605184555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381648927927017</t>
+    <t xml:space="preserve">0.377943634986877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381648987531662</t>
   </si>
   <si>
     <t xml:space="preserve">0.390294700860977</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">0.399763882160187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38947132229805</t>
+    <t xml:space="preserve">0.389471292495728</t>
   </si>
   <si>
     <t xml:space="preserve">0.401822417974472</t>
@@ -2669,22 +2669,22 @@
     <t xml:space="preserve">0.411703288555145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402234107255936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403469234704971</t>
+    <t xml:space="preserve">0.402234137058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403469204902649</t>
   </si>
   <si>
     <t xml:space="preserve">0.409644782543182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408409655094147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40593945980072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406351149082184</t>
+    <t xml:space="preserve">0.408409684896469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405939429998398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406351119279861</t>
   </si>
   <si>
     <t xml:space="preserve">0.400175601243973</t>
@@ -2696,19 +2696,19 @@
     <t xml:space="preserve">0.403880953788757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403057485818863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394823431968689</t>
+    <t xml:space="preserve">0.403057515621185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394823461771011</t>
   </si>
   <si>
     <t xml:space="preserve">0.417467176914215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433111846446991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430641680955887</t>
+    <t xml:space="preserve">0.433111876249313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430641621351242</t>
   </si>
   <si>
     <t xml:space="preserve">0.44134595990181</t>
@@ -2717,22 +2717,22 @@
     <t xml:space="preserve">0.454520434141159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442992746829987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488280028104782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50392484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534390807151794</t>
+    <t xml:space="preserve">0.442992717027664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488280087709427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503924787044525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534390866756439</t>
   </si>
   <si>
     <t xml:space="preserve">0.518746137619019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522039711475372</t>
+    <t xml:space="preserve">0.522039771080017</t>
   </si>
   <si>
     <t xml:space="preserve">0.500631153583527</t>
@@ -2744,28 +2744,28 @@
     <t xml:space="preserve">0.46934175491333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485809803009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462754487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472635358572006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493220567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573750972748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48169282078743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467694938182831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460914134979</t>
+    <t xml:space="preserve">0.485809862613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462754428386688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472635388374329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493220508098602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491573691368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481692880392075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467694997787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460884332657</t>
   </si>
   <si>
     <t xml:space="preserve">0.461107701063156</t>
@@ -2774,10 +2774,10 @@
     <t xml:space="preserve">0.476752400398254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479222655296326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477575838565826</t>
+    <t xml:space="preserve">0.479222595691681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477575778961182</t>
   </si>
   <si>
     <t xml:space="preserve">0.51545250415802</t>
@@ -2786,25 +2786,25 @@
     <t xml:space="preserve">0.504748225212097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501454532146454</t>
+    <t xml:space="preserve">0.501454591751099</t>
   </si>
   <si>
     <t xml:space="preserve">0.498984396457672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494044005870819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505571663379669</t>
+    <t xml:space="preserve">0.494043976068497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505571722984314</t>
   </si>
   <si>
     <t xml:space="preserve">0.490750372409821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484986424446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49239718914032</t>
+    <t xml:space="preserve">0.484986484050751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492397129535675</t>
   </si>
   <si>
     <t xml:space="preserve">0.482516258955002</t>
@@ -2813,22 +2813,22 @@
     <t xml:space="preserve">0.478399217128754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473458737134933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470988541841507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470165133476257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465224713087082</t>
+    <t xml:space="preserve">0.473458826541901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470988571643829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470165103673935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46522468328476</t>
   </si>
   <si>
     <t xml:space="preserve">0.460284322500229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468518376350403</t>
+    <t xml:space="preserve">0.46851834654808</t>
   </si>
   <si>
     <t xml:space="preserve">0.466750353574753</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">0.457910388708115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461446404457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464098334312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454374372959137</t>
+    <t xml:space="preserve">0.46144637465477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464098364114761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454374402761459</t>
   </si>
   <si>
     <t xml:space="preserve">0.441114455461502</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">0.420782536268234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435810476541519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438462436199188</t>
+    <t xml:space="preserve">0.435810446739197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438462466001511</t>
   </si>
   <si>
     <t xml:space="preserve">0.427412509918213</t>
@@ -2867,34 +2867,34 @@
     <t xml:space="preserve">0.426528483629227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433158487081528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448186427354813</t>
+    <t xml:space="preserve">0.433158457279205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448186457157135</t>
   </si>
   <si>
     <t xml:space="preserve">0.441998451948166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434484422206879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44465047121048</t>
+    <t xml:space="preserve">0.434484452009201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444650441408157</t>
   </si>
   <si>
     <t xml:space="preserve">0.449070423841476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437578439712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433600455522537</t>
+    <t xml:space="preserve">0.437578469514847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43360048532486</t>
   </si>
   <si>
     <t xml:space="preserve">0.430948466062546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431390464305878</t>
+    <t xml:space="preserve">0.4313904941082</t>
   </si>
   <si>
     <t xml:space="preserve">0.434926480054855</t>
@@ -2906,19 +2906,19 @@
     <t xml:space="preserve">0.428738474845886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424318462610245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434042483568192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421666502952576</t>
+    <t xml:space="preserve">0.424318492412567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434042453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421666473150253</t>
   </si>
   <si>
     <t xml:space="preserve">0.430506467819214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427854478359222</t>
+    <t xml:space="preserve">0.427854508161545</t>
   </si>
   <si>
     <t xml:space="preserve">0.419456511735916</t>
@@ -2927,16 +2927,16 @@
     <t xml:space="preserve">0.417246520519257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411942541599274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414152532815933</t>
+    <t xml:space="preserve">0.411942511796951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414152503013611</t>
   </si>
   <si>
     <t xml:space="preserve">0.41813051700592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42255049943924</t>
+    <t xml:space="preserve">0.422550469636917</t>
   </si>
   <si>
     <t xml:space="preserve">0.413710504770279</t>
@@ -2948,10 +2948,10 @@
     <t xml:space="preserve">0.423876494169235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414594531059265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422992497682571</t>
+    <t xml:space="preserve">0.414594560861588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422992527484894</t>
   </si>
   <si>
     <t xml:space="preserve">0.421224534511566</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">0.412384569644928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41105854511261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409732550382614</t>
+    <t xml:space="preserve">0.411058515310287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409732580184937</t>
   </si>
   <si>
     <t xml:space="preserve">0.409290552139282</t>
@@ -2984,25 +2984,25 @@
     <t xml:space="preserve">0.423434525728226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420340478420258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426086455583572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428296476602554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424760520458221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422108471393585</t>
+    <t xml:space="preserve">0.42034050822258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426086485385895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428296446800232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424760490655899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422108501195908</t>
   </si>
   <si>
     <t xml:space="preserve">0.415478527545929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402218580245972</t>
+    <t xml:space="preserve">0.402218610048294</t>
   </si>
   <si>
     <t xml:space="preserve">0.394262611865997</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">0.405754566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403544574975967</t>
+    <t xml:space="preserve">0.403544545173645</t>
   </si>
   <si>
     <t xml:space="preserve">0.400450557470322</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">0.388958603143692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395146608352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386748641729355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393378585577011</t>
+    <t xml:space="preserve">0.395146578550339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386748611927032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393378615379333</t>
   </si>
   <si>
     <t xml:space="preserve">0.403102546930313</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660578489304</t>
+    <t xml:space="preserve">0.402660548686981</t>
   </si>
   <si>
     <t xml:space="preserve">0.419898509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436694413423538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443766415119171</t>
+    <t xml:space="preserve">0.436694443225861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443766385316849</t>
   </si>
   <si>
     <t xml:space="preserve">0.453789889812469</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">0.456523567438126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465635776519775</t>
+    <t xml:space="preserve">0.465635806322098</t>
   </si>
   <si>
     <t xml:space="preserve">0.464724570512772</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">0.468369513750076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480215400457382</t>
+    <t xml:space="preserve">0.480215460062027</t>
   </si>
   <si>
     <t xml:space="preserve">0.482949018478394</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">0.486593961715698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501173555850983</t>
+    <t xml:space="preserve">0.501173615455627</t>
   </si>
   <si>
     <t xml:space="preserve">0.523042976856232</t>
@@ -3158,28 +3158,28 @@
     <t xml:space="preserve">0.519398033618927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513930678367615</t>
+    <t xml:space="preserve">0.51393073797226</t>
   </si>
   <si>
     <t xml:space="preserve">0.524865388870239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509374558925629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526687920093536</t>
+    <t xml:space="preserve">0.509374618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526687860488892</t>
   </si>
   <si>
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267454624176</t>
+    <t xml:space="preserve">0.541267514228821</t>
   </si>
   <si>
     <t xml:space="preserve">0.546734869480133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537622511386871</t>
+    <t xml:space="preserve">0.537622570991516</t>
   </si>
   <si>
     <t xml:space="preserve">0.549468457698822</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">0.564959287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569515407085419</t>
+    <t xml:space="preserve">0.569515466690063</t>
   </si>
   <si>
     <t xml:space="preserve">0.565870463848114</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">0.550379633903503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547646045684814</t>
+    <t xml:space="preserve">0.547646105289459</t>
   </si>
   <si>
     <t xml:space="preserve">0.55584704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553113341331482</t>
+    <t xml:space="preserve">0.553113400936127</t>
   </si>
   <si>
     <t xml:space="preserve">0.564048111438751</t>
@@ -3227,25 +3227,25 @@
     <t xml:space="preserve">0.559491991996765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561314344406128</t>
+    <t xml:space="preserve">0.561314404010773</t>
   </si>
   <si>
     <t xml:space="preserve">0.558580696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556758284568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542178750038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557669520378113</t>
+    <t xml:space="preserve">0.556758344173431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542178690433502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557669460773468</t>
   </si>
   <si>
     <t xml:space="preserve">0.534888863563538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528510332107544</t>
+    <t xml:space="preserve">0.528510272502899</t>
   </si>
   <si>
     <t xml:space="preserve">0.535800099372864</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617496013641</t>
+    <t xml:space="preserve">0.496617436408997</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
@@ -3293,19 +3293,19 @@
     <t xml:space="preserve">0.487505257129669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495706230401993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49388375878334</t>
+    <t xml:space="preserve">0.495706290006638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493883818387985</t>
   </si>
   <si>
     <t xml:space="preserve">0.491150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517575621604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489643424749374</t>
+    <t xml:space="preserve">0.517575681209564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489643454551697</t>
   </si>
   <si>
     <t xml:space="preserve">0.48199275135994</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">0.475776553153992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476732909679413</t>
+    <t xml:space="preserve">0.47673287987709</t>
   </si>
   <si>
     <t xml:space="preserve">0.480080038309097</t>
@@ -3329,31 +3329,31 @@
     <t xml:space="preserve">0.46477872133255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473385721445084</t>
+    <t xml:space="preserve">0.473385751247406</t>
   </si>
   <si>
     <t xml:space="preserve">0.469560384750366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470994889736176</t>
+    <t xml:space="preserve">0.470994919538498</t>
   </si>
   <si>
     <t xml:space="preserve">0.459040701389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453780889511108</t>
+    <t xml:space="preserve">0.453780859708786</t>
   </si>
   <si>
     <t xml:space="preserve">0.451390027999878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447564691305161</t>
+    <t xml:space="preserve">0.447564661502838</t>
   </si>
   <si>
     <t xml:space="preserve">0.45091187953949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441826671361923</t>
+    <t xml:space="preserve">0.441826701164246</t>
   </si>
   <si>
     <t xml:space="preserve">0.438479512929916</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">0.432741492986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436088681221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438001334667206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441348522901535</t>
+    <t xml:space="preserve">0.436088651418686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438001364469528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441348493099213</t>
   </si>
   <si>
     <t xml:space="preserve">0.446608364582062</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">0.436566829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438957661390305</t>
+    <t xml:space="preserve">0.438957691192627</t>
   </si>
   <si>
     <t xml:space="preserve">0.444695681333542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439435869455338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433697819709778</t>
+    <t xml:space="preserve">0.439435839653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4336978495121</t>
   </si>
   <si>
     <t xml:space="preserve">0.434654176235199</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">0.46669140458107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454737186431885</t>
+    <t xml:space="preserve">0.454737216234207</t>
   </si>
   <si>
     <t xml:space="preserve">0.455693542957306</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">0.561368525028229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538416564464569</t>
+    <t xml:space="preserve">0.538416504859924</t>
   </si>
   <si>
     <t xml:space="preserve">0.544154524803162</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">0.540329158306122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525984108448029</t>
+    <t xml:space="preserve">0.525984168052673</t>
   </si>
   <si>
     <t xml:space="preserve">0.517377138137817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525027871131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521202504634857</t>
+    <t xml:space="preserve">0.525027811527252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521202445030212</t>
   </si>
   <si>
     <t xml:space="preserve">0.519289791584015</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">0.531722128391266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518333435058594</t>
+    <t xml:space="preserve">0.518333494663239</t>
   </si>
   <si>
     <t xml:space="preserve">0.514508128166199</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">0.527896821498871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52694046497345</t>
+    <t xml:space="preserve">0.526940524578094</t>
   </si>
   <si>
     <t xml:space="preserve">0.535547494888306</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">0.553717851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568062841892242</t>
+    <t xml:space="preserve">0.568062901496887</t>
   </si>
   <si>
     <t xml:space="preserve">0.55849951505661</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">0.555630505084991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554674208164215</t>
+    <t xml:space="preserve">0.55467414855957</t>
   </si>
   <si>
     <t xml:space="preserve">0.557543218135834</t>
@@ -3491,16 +3491,16 @@
     <t xml:space="preserve">0.54702353477478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537460148334503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551805198192596</t>
+    <t xml:space="preserve">0.537460088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551805257797241</t>
   </si>
   <si>
     <t xml:space="preserve">0.524071455001831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533634901046753</t>
+    <t xml:space="preserve">0.533634841442108</t>
   </si>
   <si>
     <t xml:space="preserve">0.536503851413727</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">0.522158801555634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529809534549713</t>
+    <t xml:space="preserve">0.529809474945068</t>
   </si>
   <si>
     <t xml:space="preserve">0.532678484916687</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">0.499206781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49633777141571</t>
+    <t xml:space="preserve">0.496337741613388</t>
   </si>
   <si>
     <t xml:space="preserve">0.506857395172119</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">0.487730741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483905404806137</t>
+    <t xml:space="preserve">0.483905375003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.461909741163254</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">0.478167414665222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46860408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471473067998886</t>
+    <t xml:space="preserve">0.468604058027267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471473038196564</t>
   </si>
   <si>
     <t xml:space="preserve">0.48260822892189</t>
@@ -3966,6 +3966,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.58899998664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.578999996185303</t>
   </si>
 </sst>
 </file>
@@ -69278,7 +69281,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6909722222</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>294138</v>
@@ -69299,6 +69302,32 @@
         <v>1317</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6909837963</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>244792</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>0.586000025272369</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>0.573000013828278</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>0.583999991416931</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>0.578999996185303</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1318</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="1319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="1320">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,34 +44,34 @@
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32744625210762</t>
+    <t xml:space="preserve">0.327446222305298</t>
   </si>
   <si>
     <t xml:space="preserve">0.321156293153763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317678362131119</t>
+    <t xml:space="preserve">0.317678391933441</t>
   </si>
   <si>
     <t xml:space="preserve">0.307318478822708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288448721170425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289336681365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294368594884872</t>
+    <t xml:space="preserve">0.288448750972748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289336651563644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294368624687195</t>
   </si>
   <si>
     <t xml:space="preserve">0.285636752843857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796916007996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258997023105621</t>
+    <t xml:space="preserve">0.273796856403351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258997082710266</t>
   </si>
   <si>
     <t xml:space="preserve">0.258257031440735</t>
@@ -80,37 +80,37 @@
     <t xml:space="preserve">0.243605196475983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246417194604874</t>
+    <t xml:space="preserve">0.246417164802551</t>
   </si>
   <si>
     <t xml:space="preserve">0.262696981430054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256407082080841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259811043739319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261512964963913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253817081451416</t>
+    <t xml:space="preserve">0.256407052278519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259811013936996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261512994766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253817111253738</t>
   </si>
   <si>
     <t xml:space="preserve">0.253077119588852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286894679069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284600794315338</t>
+    <t xml:space="preserve">0.286894708871841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284600764513016</t>
   </si>
   <si>
     <t xml:space="preserve">0.277496814727783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287116706371307</t>
+    <t xml:space="preserve">0.287116765975952</t>
   </si>
   <si>
     <t xml:space="preserve">0.290742635726929</t>
@@ -119,34 +119,34 @@
     <t xml:space="preserve">0.263806968927383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256777048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.250117123126984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277570784091949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297994613647461</t>
+    <t xml:space="preserve">0.256777077913284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.250117152929306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277570813894272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297994583845139</t>
   </si>
   <si>
     <t xml:space="preserve">0.310796439647675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303544491529465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304358512163162</t>
+    <t xml:space="preserve">0.303544551134109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30435848236084</t>
   </si>
   <si>
     <t xml:space="preserve">0.318122327327728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309686422348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30162051320076</t>
+    <t xml:space="preserve">0.309686452150345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301620543003082</t>
   </si>
   <si>
     <t xml:space="preserve">0.310352444648743</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">0.320046335458755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316716343164444</t>
+    <t xml:space="preserve">0.316716372966766</t>
   </si>
   <si>
     <t xml:space="preserve">0.315236419439316</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">0.315606415271759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332996219396591</t>
+    <t xml:space="preserve">0.332996159791946</t>
   </si>
   <si>
     <t xml:space="preserve">0.332256197929382</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">0.328852266073227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330480217933655</t>
+    <t xml:space="preserve">0.330480188131332</t>
   </si>
   <si>
     <t xml:space="preserve">0.311240434646606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312054455280304</t>
+    <t xml:space="preserve">0.312054395675659</t>
   </si>
   <si>
     <t xml:space="preserve">0.299696564674377</t>
@@ -191,34 +191,34 @@
     <t xml:space="preserve">0.296884596347809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299400597810745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29747661948204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295996636152267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293702632188797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298216551542282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286376714706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276756823062897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27453687787056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272316873073578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268542945384979</t>
+    <t xml:space="preserve">0.299400568008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297476589679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295996576547623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293702602386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298216581344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286376744508743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276756852865219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274536848068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2723169028759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268542915582657</t>
   </si>
   <si>
     <t xml:space="preserve">0.270466893911362</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">0.265064984560013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268172949552536</t>
+    <t xml:space="preserve">0.268172919750214</t>
   </si>
   <si>
     <t xml:space="preserve">0.268616914749146</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">0.275276869535446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284896731376648</t>
+    <t xml:space="preserve">0.284896701574326</t>
   </si>
   <si>
     <t xml:space="preserve">0.290002703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308206498622894</t>
+    <t xml:space="preserve">0.308206468820572</t>
   </si>
   <si>
     <t xml:space="preserve">0.309168457984924</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">0.316938370466232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308946460485458</t>
+    <t xml:space="preserve">0.308946490287781</t>
   </si>
   <si>
     <t xml:space="preserve">0.314200401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321378320455551</t>
+    <t xml:space="preserve">0.321378290653229</t>
   </si>
   <si>
     <t xml:space="preserve">0.319380342960358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310722470283508</t>
+    <t xml:space="preserve">0.310722440481186</t>
   </si>
   <si>
     <t xml:space="preserve">0.313682407140732</t>
@@ -281,76 +281,76 @@
     <t xml:space="preserve">0.307096481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30761444568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304950475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305616468191147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299548596143723</t>
+    <t xml:space="preserve">0.307614475488663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304950505495071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305616497993469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2995485663414</t>
   </si>
   <si>
     <t xml:space="preserve">0.305320501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295626640319824</t>
+    <t xml:space="preserve">0.295626610517502</t>
   </si>
   <si>
     <t xml:space="preserve">0.300954520702362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314400285482407</t>
+    <t xml:space="preserve">0.314400315284729</t>
   </si>
   <si>
     <t xml:space="preserve">0.318779796361923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318856596946716</t>
+    <t xml:space="preserve">0.318856626749039</t>
   </si>
   <si>
     <t xml:space="preserve">0.318395644426346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319932281970978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318088263273239</t>
+    <t xml:space="preserve">0.319932252168655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318088322877884</t>
   </si>
   <si>
     <t xml:space="preserve">0.307331681251526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321776300668716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320393264293671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311557501554489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305795043706894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301569253206253</t>
+    <t xml:space="preserve">0.321776270866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320393294095993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311557471752167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305795013904572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301569223403931</t>
   </si>
   <si>
     <t xml:space="preserve">0.295806735754013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299648344516754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29657506942749</t>
+    <t xml:space="preserve">0.299648374319077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296575099229813</t>
   </si>
   <si>
     <t xml:space="preserve">0.303490042686462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31424668431282</t>
+    <t xml:space="preserve">0.314246654510498</t>
   </si>
   <si>
     <t xml:space="preserve">0.318011432886124</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">0.321161597967148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310020834207535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311941623687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311173349618912</t>
+    <t xml:space="preserve">0.310020804405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311941653490067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311173319816589</t>
   </si>
   <si>
     <t xml:space="preserve">0.307254880666733</t>
@@ -380,34 +380,34 @@
     <t xml:space="preserve">0.305564552545547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304949849843979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306870698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297727584838867</t>
+    <t xml:space="preserve">0.304949820041656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306870669126511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297727555036545</t>
   </si>
   <si>
     <t xml:space="preserve">0.301799714565277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304027885198593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300032585859299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313478291034698</t>
+    <t xml:space="preserve">0.304027855396271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300032556056976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313478320837021</t>
   </si>
   <si>
     <t xml:space="preserve">0.312556326389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307869493961334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311480671167374</t>
+    <t xml:space="preserve">0.307869523763657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311480700969696</t>
   </si>
   <si>
     <t xml:space="preserve">0.298265397548676</t>
@@ -425,31 +425,31 @@
     <t xml:space="preserve">0.295960396528244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297650724649429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297881215810776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293732225894928</t>
+    <t xml:space="preserve">0.297650694847107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297881245613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29373225569725</t>
   </si>
   <si>
     <t xml:space="preserve">0.298803240060806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300416737794876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300109386444092</t>
+    <t xml:space="preserve">0.300416678190231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300109416246414</t>
   </si>
   <si>
     <t xml:space="preserve">0.298880040645599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305487722158432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309559881687164</t>
+    <t xml:space="preserve">0.305487662553787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309559851884842</t>
   </si>
   <si>
     <t xml:space="preserve">0.303105860948563</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">0.303566873073578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308253705501556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304873019456863</t>
+    <t xml:space="preserve">0.308253675699234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304873049259186</t>
   </si>
   <si>
     <t xml:space="preserve">0.306563347578049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30018624663353</t>
+    <t xml:space="preserve">0.300186216831207</t>
   </si>
   <si>
     <t xml:space="preserve">0.298649579286575</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">0.296421378850937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3014155626297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3006471991539</t>
+    <t xml:space="preserve">0.301415592432022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300647228956223</t>
   </si>
   <si>
     <t xml:space="preserve">0.282975614070892</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">0.288123458623886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284281849861145</t>
+    <t xml:space="preserve">0.284281820058823</t>
   </si>
   <si>
     <t xml:space="preserve">0.28789296746254</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">0.290044277906418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292887061834335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293117582798004</t>
+    <t xml:space="preserve">0.292887091636658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293117612600327</t>
   </si>
   <si>
     <t xml:space="preserve">0.291888236999512</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">0.289813786745071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286586821079254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294270068407059</t>
+    <t xml:space="preserve">0.286586791276932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294270098209381</t>
   </si>
   <si>
     <t xml:space="preserve">0.291811436414719</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">0.292579770088196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295729905366898</t>
+    <t xml:space="preserve">0.295729875564575</t>
   </si>
   <si>
     <t xml:space="preserve">0.298419058322906</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">0.294731080532074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287355095148087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293809115886688</t>
+    <t xml:space="preserve">0.287355124950409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293809056282043</t>
   </si>
   <si>
     <t xml:space="preserve">0.292041957378387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286740452051163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284665942192078</t>
+    <t xml:space="preserve">0.286740511655807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2846659719944</t>
   </si>
   <si>
     <t xml:space="preserve">0.278903514146805</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">0.276675373315811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273986160755157</t>
+    <t xml:space="preserve">0.27398619055748</t>
   </si>
   <si>
     <t xml:space="preserve">0.275676518678665</t>
@@ -587,22 +587,22 @@
     <t xml:space="preserve">0.275522828102112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276598542928696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270989716053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271143406629562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274293541908264</t>
+    <t xml:space="preserve">0.276598513126373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270989686250687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27114337682724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274293512105942</t>
   </si>
   <si>
     <t xml:space="preserve">0.270451873540878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268146872520447</t>
+    <t xml:space="preserve">0.268146902322769</t>
   </si>
   <si>
     <t xml:space="preserve">0.267378568649292</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">0.265765070915222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262384444475174</t>
+    <t xml:space="preserve">0.262384414672852</t>
   </si>
   <si>
     <t xml:space="preserve">0.267532229423523</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">0.265304088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271911710500717</t>
+    <t xml:space="preserve">0.271911680698395</t>
   </si>
   <si>
     <t xml:space="preserve">0.272526383399963</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.277059525251389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27844250202179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28051695227623</t>
+    <t xml:space="preserve">0.278442531824112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280517041683197</t>
   </si>
   <si>
     <t xml:space="preserve">0.278749823570251</t>
@@ -650,52 +650,52 @@
     <t xml:space="preserve">0.278980314731598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278212010860443</t>
+    <t xml:space="preserve">0.278212040662766</t>
   </si>
   <si>
     <t xml:space="preserve">0.284051299095154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290812611579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289660096168518</t>
+    <t xml:space="preserve">0.290812641382217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28966012597084</t>
   </si>
   <si>
     <t xml:space="preserve">0.290428429841995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294807940721512</t>
+    <t xml:space="preserve">0.294807910919189</t>
   </si>
   <si>
     <t xml:space="preserve">0.295422583818436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288507610559464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284589171409607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291043102741241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293885916471481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294884741306305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289890617132187</t>
+    <t xml:space="preserve">0.288507580757141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284589141607285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291043132543564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293885946273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294884771108627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289890587329865</t>
   </si>
   <si>
     <t xml:space="preserve">0.286125808954239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284358650445938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282745122909546</t>
+    <t xml:space="preserve">0.284358590841293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282745182514191</t>
   </si>
   <si>
     <t xml:space="preserve">0.277290046215057</t>
@@ -713,28 +713,28 @@
     <t xml:space="preserve">0.269760400056839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275061845779419</t>
+    <t xml:space="preserve">0.275061875581741</t>
   </si>
   <si>
     <t xml:space="preserve">0.271834880113602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273371547460556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275215536355972</t>
+    <t xml:space="preserve">0.273371577262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275215566158295</t>
   </si>
   <si>
     <t xml:space="preserve">0.276905834674835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27483132481575</t>
+    <t xml:space="preserve">0.274831354618073</t>
   </si>
   <si>
     <t xml:space="preserve">0.282668322324753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280440151691437</t>
+    <t xml:space="preserve">0.280440181493759</t>
   </si>
   <si>
     <t xml:space="preserve">0.279595017433167</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">0.277366816997528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278135180473328</t>
+    <t xml:space="preserve">0.278135120868683</t>
   </si>
   <si>
     <t xml:space="preserve">0.281208485364914</t>
@@ -752,25 +752,25 @@
     <t xml:space="preserve">0.278672993183136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282591462135315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27936452627182</t>
+    <t xml:space="preserve">0.282591491937637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279364496469498</t>
   </si>
   <si>
     <t xml:space="preserve">0.285587966442108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279671788215637</t>
+    <t xml:space="preserve">0.27967181801796</t>
   </si>
   <si>
     <t xml:space="preserve">0.286663621664047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284435451030731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281899958848953</t>
+    <t xml:space="preserve">0.284435510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281899988651276</t>
   </si>
   <si>
     <t xml:space="preserve">0.283897668123245</t>
@@ -779,25 +779,25 @@
     <t xml:space="preserve">0.285280615091324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285434305667877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295038461685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30425837635994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321929961442947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325617909431458</t>
+    <t xml:space="preserve">0.285434275865555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295038431882858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304258346557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321929931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32561793923378</t>
   </si>
   <si>
     <t xml:space="preserve">0.33184140920639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325387418270111</t>
+    <t xml:space="preserve">0.325387448072433</t>
   </si>
   <si>
     <t xml:space="preserve">0.316935807466507</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">0.309252500534058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311096489429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313094139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313017338514328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288891822099686</t>
+    <t xml:space="preserve">0.311096549034119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313094168901443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313017308712006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288891762495041</t>
   </si>
   <si>
     <t xml:space="preserve">0.293040752410889</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.295192062854767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296805590391159</t>
+    <t xml:space="preserve">0.296805560588837</t>
   </si>
   <si>
     <t xml:space="preserve">0.297266602516174</t>
@@ -836,43 +836,43 @@
     <t xml:space="preserve">0.298111766576767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310251355171204</t>
+    <t xml:space="preserve">0.310251325368881</t>
   </si>
   <si>
     <t xml:space="preserve">0.313555151224136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300800889730453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30886834859848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299725204706192</t>
+    <t xml:space="preserve">0.300800859928131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308868318796158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299725234508514</t>
   </si>
   <si>
     <t xml:space="preserve">0.32185310125351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327308267354965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318472445011139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312095284461975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314016163349152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315014988183975</t>
+    <t xml:space="preserve">0.327308297157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318472474813461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312095314264297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314016133546829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315014958381653</t>
   </si>
   <si>
     <t xml:space="preserve">0.312249004840851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313939303159714</t>
+    <t xml:space="preserve">0.313939332962036</t>
   </si>
   <si>
     <t xml:space="preserve">0.309636652469635</t>
@@ -881,40 +881,40 @@
     <t xml:space="preserve">0.307408511638641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308945119380951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313632011413574</t>
+    <t xml:space="preserve">0.308945178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313631951808929</t>
   </si>
   <si>
     <t xml:space="preserve">0.308023184537888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307715862989426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309022009372711</t>
+    <t xml:space="preserve">0.307715833187103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309022068977356</t>
   </si>
   <si>
     <t xml:space="preserve">0.309944003820419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3177809715271</t>
+    <t xml:space="preserve">0.317780941724777</t>
   </si>
   <si>
     <t xml:space="preserve">0.31655165553093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316474825143814</t>
+    <t xml:space="preserve">0.316474795341492</t>
   </si>
   <si>
     <t xml:space="preserve">0.324388563632965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325003296136856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318318784236908</t>
+    <t xml:space="preserve">0.325003236532211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318318754434586</t>
   </si>
   <si>
     <t xml:space="preserve">0.317704141139984</t>
@@ -923,67 +923,67 @@
     <t xml:space="preserve">0.321545779705048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320470154285431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621405124664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323697060346603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333454877138138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327385067939758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331764549016953</t>
+    <t xml:space="preserve">0.320470094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621464729309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323697119951248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333454847335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327385038137436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331764578819275</t>
   </si>
   <si>
     <t xml:space="preserve">0.339524686336517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345671355724335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340446710586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3333780169487</t>
+    <t xml:space="preserve">0.34567129611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340446680784225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333378076553345</t>
   </si>
   <si>
     <t xml:space="preserve">0.33499151468277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336144030094147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337757527828217</t>
+    <t xml:space="preserve">0.336144000291824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337757498025894</t>
   </si>
   <si>
     <t xml:space="preserve">0.338910013437271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338141649961472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339678376913071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350358098745346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34659332036972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344211518764496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340677171945572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33460733294487</t>
+    <t xml:space="preserve">0.338141709566116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339678347110748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350358128547668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346593290567398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344211488962173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340677201747894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334607392549515</t>
   </si>
   <si>
     <t xml:space="preserve">0.338218539953232</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">0.346132338047028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33960148692131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340907692909241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3526631295681</t>
+    <t xml:space="preserve">0.339601516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340907663106918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352663099765778</t>
   </si>
   <si>
     <t xml:space="preserve">0.369950503110886</t>
@@ -1016,19 +1016,19 @@
     <t xml:space="preserve">0.374099522829056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371103018522263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369566351175308</t>
+    <t xml:space="preserve">0.371103048324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369566321372986</t>
   </si>
   <si>
     <t xml:space="preserve">0.368798017501831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366108894348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363112419843674</t>
+    <t xml:space="preserve">0.3661088347435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363112390041351</t>
   </si>
   <si>
     <t xml:space="preserve">0.3686443567276</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">0.366262555122375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361114770174026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359885394573212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359193921089172</t>
+    <t xml:space="preserve">0.361114740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359885424375534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35919389128685</t>
   </si>
   <si>
     <t xml:space="preserve">0.368567526340485</t>
@@ -1058,19 +1058,19 @@
     <t xml:space="preserve">0.375559329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380246102809906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392616182565689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405677855014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421044409275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419507741928101</t>
+    <t xml:space="preserve">0.380246132612228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392616212368011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405677825212479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42104434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419507771730423</t>
   </si>
   <si>
     <t xml:space="preserve">0.396842032670975</t>
@@ -1085,37 +1085,37 @@
     <t xml:space="preserve">0.417586892843246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426422715187073</t>
+    <t xml:space="preserve">0.426422774791718</t>
   </si>
   <si>
     <t xml:space="preserve">0.423349440097809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427959382534027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436795145273209</t>
+    <t xml:space="preserve">0.427959322929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436795175075531</t>
   </si>
   <si>
     <t xml:space="preserve">0.432953506708145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452930092811584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460854530334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465223401784897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296647071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481358200311661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522463798522949</t>
+    <t xml:space="preserve">0.452930122613907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460824728012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46522331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296706676483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481358289718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522463858127594</t>
   </si>
   <si>
     <t xml:space="preserve">0.515164732933044</t>
@@ -1127,82 +1127,82 @@
     <t xml:space="preserve">0.50709730386734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515548884868622</t>
+    <t xml:space="preserve">0.515548944473267</t>
   </si>
   <si>
     <t xml:space="preserve">0.503255605697632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489809930324554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480205744504929</t>
+    <t xml:space="preserve">0.48980987071991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480205774307251</t>
   </si>
   <si>
     <t xml:space="preserve">0.519006371498108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511322975158691</t>
+    <t xml:space="preserve">0.511323094367981</t>
   </si>
   <si>
     <t xml:space="preserve">0.499413967132568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491730719804764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484431564807892</t>
+    <t xml:space="preserve">0.491730660200119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484431535005569</t>
   </si>
   <si>
     <t xml:space="preserve">0.483663201332092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484815716743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495188176631927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490194082260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553197085857391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542056322097778</t>
+    <t xml:space="preserve">0.484815776348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49518820643425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490193992853165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553197026252747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542056262493134</t>
   </si>
   <si>
     <t xml:space="preserve">0.56280118227005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586235165596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600065171718597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582393527030945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572021067142487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572789490222931</t>
+    <t xml:space="preserve">0.586235225200653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600065112113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58239358663559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572021126747131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572789371013641</t>
   </si>
   <si>
     <t xml:space="preserve">0.552428662776947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55127614736557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545129597187042</t>
+    <t xml:space="preserve">0.551276206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545129537582397</t>
   </si>
   <si>
     <t xml:space="preserve">0.565874457359314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577015221118927</t>
+    <t xml:space="preserve">0.577015161514282</t>
   </si>
   <si>
     <t xml:space="preserve">0.596607625484467</t>
@@ -1211,34 +1211,34 @@
     <t xml:space="preserve">0.584698498249054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608132481575012</t>
+    <t xml:space="preserve">0.608132541179657</t>
   </si>
   <si>
     <t xml:space="preserve">0.621962487697601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620425820350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629645824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614279210567474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60774838924408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58162522315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560880303382874</t>
+    <t xml:space="preserve">0.620425939559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629645764827728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614279270172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607748329639435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581625282764435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560880362987518</t>
   </si>
   <si>
     <t xml:space="preserve">0.598528444766998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598144292831421</t>
+    <t xml:space="preserve">0.598144352436066</t>
   </si>
   <si>
     <t xml:space="preserve">0.619657516479492</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">0.618120849132538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601601779460907</t>
+    <t xml:space="preserve">0.601601719856262</t>
   </si>
   <si>
     <t xml:space="preserve">0.58661937713623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595455169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587771832942963</t>
+    <t xml:space="preserve">0.59545511007309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587771892547607</t>
   </si>
   <si>
     <t xml:space="preserve">0.584314405918121</t>
@@ -1265,10 +1265,10 @@
     <t xml:space="preserve">0.577399373054504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567026972770691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57432609796524</t>
+    <t xml:space="preserve">0.567026913166046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574326038360596</t>
   </si>
   <si>
     <t xml:space="preserve">0.543592870235443</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">0.564722001552582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.563185334205627</t>
+    <t xml:space="preserve">0.563185214996338</t>
   </si>
   <si>
     <t xml:space="preserve">0.576246917247772</t>
@@ -1304,25 +1304,25 @@
     <t xml:space="preserve">0.606980085372925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603138506412506</t>
+    <t xml:space="preserve">0.603138446807861</t>
   </si>
   <si>
     <t xml:space="preserve">0.612358391284943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611590087413788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593918442726135</t>
+    <t xml:space="preserve">0.611590027809143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59391850233078</t>
   </si>
   <si>
     <t xml:space="preserve">0.596991777420044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608516752719879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599296689033508</t>
+    <t xml:space="preserve">0.608516693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599296748638153</t>
   </si>
   <si>
     <t xml:space="preserve">0.589308559894562</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">0.55703866481781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536293745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524000525474548</t>
+    <t xml:space="preserve">0.536293804645538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524000585079193</t>
   </si>
   <si>
     <t xml:space="preserve">0.537830471992493</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">0.547818720340729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532452166080475</t>
+    <t xml:space="preserve">0.53245210647583</t>
   </si>
   <si>
     <t xml:space="preserve">0.537062108516693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527073800563812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52092719078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517853915691376</t>
+    <t xml:space="preserve">0.527073919773102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520927250385284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517853856086731</t>
   </si>
   <si>
     <t xml:space="preserve">0.525537192821503</t>
@@ -1370,94 +1370,94 @@
     <t xml:space="preserve">0.530147194862366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523232221603394</t>
+    <t xml:space="preserve">0.523232281208038</t>
   </si>
   <si>
     <t xml:space="preserve">0.51939058303833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524768888950348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549355328083038</t>
+    <t xml:space="preserve">0.524768829345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549355387687683</t>
   </si>
   <si>
     <t xml:space="preserve">0.501718997955322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492499023675919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477900683879852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476364135742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488657355308533</t>
+    <t xml:space="preserve">0.492498964071274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477900773286819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476364076137543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48865732550621</t>
   </si>
   <si>
     <t xml:space="preserve">0.471754193305969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472522437572479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468680799007416</t>
+    <t xml:space="preserve">0.472522497177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468680888414383</t>
   </si>
   <si>
     <t xml:space="preserve">0.487120717763901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481742471456528</t>
+    <t xml:space="preserve">0.481742411851883</t>
   </si>
   <si>
     <t xml:space="preserve">0.480974107980728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48327910900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478669106960297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470217406749725</t>
+    <t xml:space="preserve">0.483279079198837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478669196367264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47021746635437</t>
   </si>
   <si>
     <t xml:space="preserve">0.467912524938583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466375797986984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839190244675</t>
+    <t xml:space="preserve">0.466375827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839249849319</t>
   </si>
   <si>
     <t xml:space="preserve">0.461765885353088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487889051437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500182330608368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469449192285538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437179327011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444862604141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431800931692123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444094270467758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424117714166641</t>
+    <t xml:space="preserve">0.487889021635056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500182271003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469449162483215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437179356813431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444862574338913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431800991296768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444094300270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424117654561996</t>
   </si>
   <si>
     <t xml:space="preserve">0.415666133165359</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">0.382627964019775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379170447587967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382243782281876</t>
+    <t xml:space="preserve">0.379170477390289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382243812084198</t>
   </si>
   <si>
     <t xml:space="preserve">0.385701239109039</t>
@@ -1493,28 +1493,28 @@
     <t xml:space="preserve">0.364956378936768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360346436500549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352278977632523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356504708528519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371487200260162</t>
+    <t xml:space="preserve">0.360346406698227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352278918027878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356504738330841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37148717045784</t>
   </si>
   <si>
     <t xml:space="preserve">0.368029683828354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372255474328995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365340530872345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374944686889648</t>
+    <t xml:space="preserve">0.37225553393364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365340501070023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374944657087326</t>
   </si>
   <si>
     <t xml:space="preserve">0.3664930164814</t>
@@ -1526,43 +1526,43 @@
     <t xml:space="preserve">0.374176323413849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378786265850067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362267255783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353815585374832</t>
+    <t xml:space="preserve">0.378786325454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362267225980759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353815644979477</t>
   </si>
   <si>
     <t xml:space="preserve">0.354583919048309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353047251701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37071880698204</t>
+    <t xml:space="preserve">0.353047281503677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370718866586685</t>
   </si>
   <si>
     <t xml:space="preserve">0.35419973731041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395689517259598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411056160926819</t>
+    <t xml:space="preserve">0.395689487457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411056131124496</t>
   </si>
   <si>
     <t xml:space="preserve">0.40798282623291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384932965040207</t>
+    <t xml:space="preserve">0.384932935237885</t>
   </si>
   <si>
     <t xml:space="preserve">0.390311241149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378017961978912</t>
+    <t xml:space="preserve">0.378018021583557</t>
   </si>
   <si>
     <t xml:space="preserve">0.380707114934921</t>
@@ -1571,31 +1571,31 @@
     <t xml:space="preserve">0.362651377916336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359578043222427</t>
+    <t xml:space="preserve">0.35957807302475</t>
   </si>
   <si>
     <t xml:space="preserve">0.353431463241577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349589794874191</t>
+    <t xml:space="preserve">0.349589854478836</t>
   </si>
   <si>
     <t xml:space="preserve">0.344979822635651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343059003353119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354968130588531</t>
+    <t xml:space="preserve">0.343058973550797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354968100786209</t>
   </si>
   <si>
     <t xml:space="preserve">0.36418804526329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357273072004318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349973976612091</t>
+    <t xml:space="preserve">0.357273101806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349974006414413</t>
   </si>
   <si>
     <t xml:space="preserve">0.339217364788055</t>
@@ -1607,82 +1607,82 @@
     <t xml:space="preserve">0.361883044242859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350742250680923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38954296708107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404141187667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396457880735397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412592768669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404909551143646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401836186647415</t>
+    <t xml:space="preserve">0.350742280483246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389542937278748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404141217470169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396457850933075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412592828273773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404909521341324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401836156845093</t>
   </si>
   <si>
     <t xml:space="preserve">0.394152909517288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399531215429306</t>
+    <t xml:space="preserve">0.399531155824661</t>
   </si>
   <si>
     <t xml:space="preserve">0.40260449051857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401067852973938</t>
+    <t xml:space="preserve">0.40106788277626</t>
   </si>
   <si>
     <t xml:space="preserve">0.397994518280029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375712960958481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36457222700119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345748126506805</t>
+    <t xml:space="preserve">0.375712990760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364572197198868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345748156309128</t>
   </si>
   <si>
     <t xml:space="preserve">0.336528211832047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335759878158569</t>
+    <t xml:space="preserve">0.335759848356247</t>
   </si>
   <si>
     <t xml:space="preserve">0.337296515703201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329613208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328076541423798</t>
+    <t xml:space="preserve">0.329613238573074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32807657122612</t>
   </si>
   <si>
     <t xml:space="preserve">0.331534028053284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319240778684616</t>
+    <t xml:space="preserve">0.319240808486938</t>
   </si>
   <si>
     <t xml:space="preserve">0.326924085617065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312710016965866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34113821387291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322698295116425</t>
+    <t xml:space="preserve">0.312709987163544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341138154268265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322698265314102</t>
   </si>
   <si>
     <t xml:space="preserve">0.326155751943588</t>
@@ -1691,37 +1691,37 @@
     <t xml:space="preserve">0.324619084596634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325771570205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330381572246552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329997420310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324234902858734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313862502574921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301185011863708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30387419462204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296959221363068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302721738815308</t>
+    <t xml:space="preserve">0.325771600008011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330381542444229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329997390508652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324234962463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313862472772598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301185041666031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303874164819717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29695925116539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302721679210663</t>
   </si>
   <si>
     <t xml:space="preserve">0.32308241724968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308100044727325</t>
+    <t xml:space="preserve">0.308100014925003</t>
   </si>
   <si>
     <t xml:space="preserve">0.310405015945435</t>
@@ -1748,25 +1748,25 @@
     <t xml:space="preserve">0.356888920068741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358041405677795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356120616197586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360730558633804</t>
+    <t xml:space="preserve">0.358041375875473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356120586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360730588436127</t>
   </si>
   <si>
     <t xml:space="preserve">0.358809739351273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351126462221146</t>
+    <t xml:space="preserve">0.351126432418823</t>
   </si>
   <si>
     <t xml:space="preserve">0.355736434459686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342290669679642</t>
+    <t xml:space="preserve">0.342290639877319</t>
   </si>
   <si>
     <t xml:space="preserve">0.37187135219574</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">0.376865476369858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377249658107758</t>
+    <t xml:space="preserve">0.377249628305435</t>
   </si>
   <si>
     <t xml:space="preserve">0.398762851953506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40337285399437</t>
+    <t xml:space="preserve">0.403372824192047</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446129083633</t>
@@ -1799,37 +1799,37 @@
     <t xml:space="preserve">0.409519463777542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391079604625702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381475448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407214432954788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387237936258316</t>
+    <t xml:space="preserve">0.39107957482338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381475478410721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407214462757111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387237906455994</t>
   </si>
   <si>
     <t xml:space="preserve">0.394921213388443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411824464797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414897799491882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417202740907669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397226184606552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408751130104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410287767648697</t>
+    <t xml:space="preserve">0.411824494600296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41489776968956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417202711105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397226214408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408751159906387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410287797451019</t>
   </si>
   <si>
     <t xml:space="preserve">0.41412940621376</t>
@@ -1841,13 +1841,13 @@
     <t xml:space="preserve">0.418739408254623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420276015996933</t>
+    <t xml:space="preserve">0.420276075601578</t>
   </si>
   <si>
     <t xml:space="preserve">0.421812742948532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430264353752136</t>
+    <t xml:space="preserve">0.430264383554459</t>
   </si>
   <si>
     <t xml:space="preserve">0.473290771245956</t>
@@ -1856,49 +1856,49 @@
     <t xml:space="preserve">0.49480402469635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48404735326767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267416954041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506328999996185</t>
+    <t xml:space="preserve">0.484047383069992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267357349396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506328940391541</t>
   </si>
   <si>
     <t xml:space="preserve">0.479437470436096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482510715723038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595772266388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46407076716423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465607523918152</t>
+    <t xml:space="preserve">0.48251074552536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595831871033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070826768875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465607494115829</t>
   </si>
   <si>
     <t xml:space="preserve">0.460997551679611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453314214944839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4341059923172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789329051971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445630878210068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449472606182098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451009213924408</t>
+    <t xml:space="preserve">0.453314185142517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434106051921844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789299249649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445630937814713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449472546577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451009273529053</t>
   </si>
   <si>
     <t xml:space="preserve">0.460229188203812</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">0.454082578420639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457155883312225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451777637004852</t>
+    <t xml:space="preserve">0.45715594291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451777517795563</t>
   </si>
   <si>
     <t xml:space="preserve">0.456387549638748</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">0.463302493095398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470985770225525</t>
+    <t xml:space="preserve">0.470985800027847</t>
   </si>
   <si>
     <t xml:space="preserve">0.467144131660461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457924216985703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447167605161667</t>
+    <t xml:space="preserve">0.457924276590347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447167634963989</t>
   </si>
   <si>
     <t xml:space="preserve">0.43256938457489</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">0.433337688446045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434874325990677</t>
+    <t xml:space="preserve">0.434874296188354</t>
   </si>
   <si>
     <t xml:space="preserve">0.436411023139954</t>
@@ -1949,28 +1949,28 @@
     <t xml:space="preserve">0.43948432803154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441020995378494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440252602100372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438715904951096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442557603120804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485584050416946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455619215965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443325996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429496079683304</t>
+    <t xml:space="preserve">0.441020965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440252661705017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43871596455574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442557573318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485584110021591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455619186162949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443325966596603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429496049880981</t>
   </si>
   <si>
     <t xml:space="preserve">0.435642659664154</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">0.450240910053253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427191019058228</t>
+    <t xml:space="preserve">0.427191078662872</t>
   </si>
   <si>
     <t xml:space="preserve">0.375328809022903</t>
@@ -1991,13 +1991,13 @@
     <t xml:space="preserve">0.393384605646133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365724742412567</t>
+    <t xml:space="preserve">0.365724712610245</t>
   </si>
   <si>
     <t xml:space="preserve">0.372639685869217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351510614156723</t>
+    <t xml:space="preserve">0.351510643959045</t>
   </si>
   <si>
     <t xml:space="preserve">0.342674851417542</t>
@@ -2012,61 +2012,61 @@
     <t xml:space="preserve">0.259695291519165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239334553480148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242023676633835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234724596142769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245865359902382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258926957845688</t>
+    <t xml:space="preserve">0.239334598183632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242023691534996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234724581241608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24586533010006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258926928043365</t>
   </si>
   <si>
     <t xml:space="preserve">0.251627802848816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266610264778137</t>
+    <t xml:space="preserve">0.266610234975815</t>
   </si>
   <si>
     <t xml:space="preserve">0.269299387931824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258158594369888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.251243621110916</t>
+    <t xml:space="preserve">0.258158624172211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.251243650913239</t>
   </si>
   <si>
     <t xml:space="preserve">0.252011984586716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242407858371735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245097041130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254701107740402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262000262737274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254316955804825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261231899261475</t>
+    <t xml:space="preserve">0.242407888174057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245096996426582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254701137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262000292539597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254316985607147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261231929063797</t>
   </si>
   <si>
     <t xml:space="preserve">0.262768596410751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264689415693283</t>
+    <t xml:space="preserve">0.264689445495605</t>
   </si>
   <si>
     <t xml:space="preserve">0.271988540887833</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">0.27275687456131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275446057319641</t>
+    <t xml:space="preserve">0.275446027517319</t>
   </si>
   <si>
     <t xml:space="preserve">0.268915235996246</t>
@@ -2090,28 +2090,28 @@
     <t xml:space="preserve">0.265841901302338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258542746305466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265457719564438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263152778148651</t>
+    <t xml:space="preserve">0.25854280591011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26545774936676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263152748346329</t>
   </si>
   <si>
     <t xml:space="preserve">0.292733430862427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327692419290543</t>
+    <t xml:space="preserve">0.327692449092865</t>
   </si>
   <si>
     <t xml:space="preserve">0.302337527275085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301953345537186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332302391529083</t>
+    <t xml:space="preserve">0.301953375339508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332302361726761</t>
   </si>
   <si>
     <t xml:space="preserve">0.332686543464661</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">0.306179195642471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305026710033417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312325805425644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331918239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31539911031723</t>
+    <t xml:space="preserve">0.305026739835739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312325835227966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331918209791183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315399140119553</t>
   </si>
   <si>
     <t xml:space="preserve">0.326539933681488</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">0.292349249124527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289275974035263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291196763515472</t>
+    <t xml:space="preserve">0.289275944232941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291196793317795</t>
   </si>
   <si>
     <t xml:space="preserve">0.286970943212509</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">0.26084777712822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261616110801697</t>
+    <t xml:space="preserve">0.261616140604019</t>
   </si>
   <si>
     <t xml:space="preserve">0.270067721605301</t>
@@ -2171,25 +2171,25 @@
     <t xml:space="preserve">0.266994386911392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255469471216202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253164499998093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256621986627579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256237804889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.249322846531868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23626121878624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238182067871094</t>
+    <t xml:space="preserve">0.255469441413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25316447019577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256621956825256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256237775087357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.249322831630707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.236261248588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238182038068771</t>
   </si>
   <si>
     <t xml:space="preserve">0.25354865193367</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">0.267762750387192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283513486385345</t>
+    <t xml:space="preserve">0.283513456583023</t>
   </si>
   <si>
     <t xml:space="preserve">0.277750998735428</t>
@@ -2213,19 +2213,19 @@
     <t xml:space="preserve">0.343827307224274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338449001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340754002332687</t>
+    <t xml:space="preserve">0.338449031114578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34075403213501</t>
   </si>
   <si>
     <t xml:space="preserve">0.338833212852478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338064819574356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336912363767624</t>
+    <t xml:space="preserve">0.338064849376678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336912333965302</t>
   </si>
   <si>
     <t xml:space="preserve">0.333839029073715</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">0.328844904899597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339985698461533</t>
+    <t xml:space="preserve">0.33998566865921</t>
   </si>
   <si>
     <t xml:space="preserve">0.34766897559166</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">0.359962224960327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3518947660923</t>
+    <t xml:space="preserve">0.351894795894623</t>
   </si>
   <si>
     <t xml:space="preserve">0.369182199239731</t>
@@ -2255,46 +2255,46 @@
     <t xml:space="preserve">0.357657253742218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355352252721786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348053127527237</t>
+    <t xml:space="preserve">0.355352282524109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348053157329559</t>
   </si>
   <si>
     <t xml:space="preserve">0.346516519784927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34728479385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363419741392136</t>
+    <t xml:space="preserve">0.347284764051437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363419681787491</t>
   </si>
   <si>
     <t xml:space="preserve">0.373792141675949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373023808002472</t>
+    <t xml:space="preserve">0.373023837804794</t>
   </si>
   <si>
     <t xml:space="preserve">0.379554659128189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425654381513596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417971134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381859600543976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38301208615303</t>
+    <t xml:space="preserve">0.425654411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417971074581146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381859660148621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383012145757675</t>
   </si>
   <si>
     <t xml:space="preserve">0.377633810043335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378402173519135</t>
+    <t xml:space="preserve">0.378402143716812</t>
   </si>
   <si>
     <t xml:space="preserve">0.381091296672821</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">0.348437309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400299519300461</t>
+    <t xml:space="preserve">0.400299578905106</t>
   </si>
   <si>
     <t xml:space="preserve">0.383396297693253</t>
@@ -2318,25 +2318,25 @@
     <t xml:space="preserve">0.388006240129471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428727686405182</t>
+    <t xml:space="preserve">0.428727716207504</t>
   </si>
   <si>
     <t xml:space="preserve">0.368413865566254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344595640897751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334223210811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341906517744064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323466598987579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340369790792465</t>
+    <t xml:space="preserve">0.344595670700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334223181009293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34190645813942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323466628789902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34036985039711</t>
   </si>
   <si>
     <t xml:space="preserve">0.331149876117706</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">0.337680697441101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345363974571228</t>
+    <t xml:space="preserve">0.345363944768906</t>
   </si>
   <si>
     <t xml:space="preserve">0.341522336006165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329229056835175</t>
+    <t xml:space="preserve">0.329229086637497</t>
   </si>
   <si>
     <t xml:space="preserve">0.353653132915497</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">0.351594597101212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354064851999283</t>
+    <t xml:space="preserve">0.35406482219696</t>
   </si>
   <si>
     <t xml:space="preserve">0.352829724550247</t>
@@ -2381,37 +2381,37 @@
     <t xml:space="preserve">0.345830768346786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341713696718216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342537134885788</t>
+    <t xml:space="preserve">0.341713726520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342537194490433</t>
   </si>
   <si>
     <t xml:space="preserve">0.348300993442535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35982871055603</t>
+    <t xml:space="preserve">0.359828680753708</t>
   </si>
   <si>
     <t xml:space="preserve">0.353241413831711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354888200759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350359529256821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345007389783859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339655220508575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342948853969574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341302037239075</t>
+    <t xml:space="preserve">0.35488823056221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350359499454498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345007359981537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339655190706253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342948883771896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341302007436752</t>
   </si>
   <si>
     <t xml:space="preserve">0.333479672670364</t>
@@ -2426,28 +2426,28 @@
     <t xml:space="preserve">0.321540296077728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310835957527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315776437520981</t>
+    <t xml:space="preserve">0.310835987329483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315776407718658</t>
   </si>
   <si>
     <t xml:space="preserve">0.314129620790482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312894523143768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318246603012085</t>
+    <t xml:space="preserve">0.312894493341446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31824666261673</t>
   </si>
   <si>
     <t xml:space="preserve">0.317834943532944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319481790065765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312071084976196</t>
+    <t xml:space="preserve">0.319481760263443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312071114778519</t>
   </si>
   <si>
     <t xml:space="preserve">0.308365762233734</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">0.320305168628693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322775393724442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30960088968277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309189200401306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321128517389297</t>
+    <t xml:space="preserve">0.322775363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309600859880447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309189170598984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32112854719162</t>
   </si>
   <si>
     <t xml:space="preserve">0.32195195555687</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">0.32689243555069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32318714261055</t>
+    <t xml:space="preserve">0.323187083005905</t>
   </si>
   <si>
     <t xml:space="preserve">0.323598772287369</t>
@@ -2495,52 +2495,52 @@
     <t xml:space="preserve">0.315364688634872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31330618262291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310424268245697</t>
+    <t xml:space="preserve">0.313306212425232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310424298048019</t>
   </si>
   <si>
     <t xml:space="preserve">0.314952999353409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311247676610947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317011535167694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317423224449158</t>
+    <t xml:space="preserve">0.311247646808624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317011505365372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31742325425148</t>
   </si>
   <si>
     <t xml:space="preserve">0.311659395694733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316188156604767</t>
+    <t xml:space="preserve">0.316188097000122</t>
   </si>
   <si>
     <t xml:space="preserve">0.319893479347229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304660439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30877748131752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30301359295845</t>
+    <t xml:space="preserve">0.30466040968895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308777451515198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303013622760773</t>
   </si>
   <si>
     <t xml:space="preserve">0.307542324066162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302601963281631</t>
+    <t xml:space="preserve">0.302601933479309</t>
   </si>
   <si>
     <t xml:space="preserve">0.307954043149948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306307286024094</t>
+    <t xml:space="preserve">0.306307256221771</t>
   </si>
   <si>
     <t xml:space="preserve">0.301778525114059</t>
@@ -2549,22 +2549,22 @@
     <t xml:space="preserve">0.303837031126022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30095511674881</t>
+    <t xml:space="preserve">0.300955086946487</t>
   </si>
   <si>
     <t xml:space="preserve">0.301366806030273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302190214395523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313717901706696</t>
+    <t xml:space="preserve">0.302190244197845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313717931509018</t>
   </si>
   <si>
     <t xml:space="preserve">0.326480716466904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328539192676544</t>
+    <t xml:space="preserve">0.328539252281189</t>
   </si>
   <si>
     <t xml:space="preserve">0.340890318155289</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">0.339243531227112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335126489400864</t>
+    <t xml:space="preserve">0.335126519203186</t>
   </si>
   <si>
     <t xml:space="preserve">0.358181864023209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3470658659935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344183951616287</t>
+    <t xml:space="preserve">0.347065836191177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34418398141861</t>
   </si>
   <si>
     <t xml:space="preserve">0.336773306131363</t>
@@ -2600,16 +2600,16 @@
     <t xml:space="preserve">0.345419049263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349124372005463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338008373975754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335949867963791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343772262334824</t>
+    <t xml:space="preserve">0.349124401807785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338008403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335949897766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343772232532501</t>
   </si>
   <si>
     <t xml:space="preserve">0.337596714496613</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">0.340066909790039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340478628873825</t>
+    <t xml:space="preserve">0.340478599071503</t>
   </si>
   <si>
     <t xml:space="preserve">0.332244545221329</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">0.329362630844116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325657278299332</t>
+    <t xml:space="preserve">0.325657308101654</t>
   </si>
   <si>
     <t xml:space="preserve">0.338420122861862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346654206514359</t>
+    <t xml:space="preserve">0.346654146909714</t>
   </si>
   <si>
     <t xml:space="preserve">0.355711668729782</t>
@@ -2642,22 +2642,22 @@
     <t xml:space="preserve">0.359005272388458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370121270418167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377943634986877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381648987531662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390294700860977</t>
+    <t xml:space="preserve">0.370121240615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377943605184555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381648927927017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3902947306633</t>
   </si>
   <si>
     <t xml:space="preserve">0.395235151052475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399763882160187</t>
+    <t xml:space="preserve">0.399763941764832</t>
   </si>
   <si>
     <t xml:space="preserve">0.389471292495728</t>
@@ -2669,34 +2669,34 @@
     <t xml:space="preserve">0.411703288555145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402234137058258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403469204902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409644782543182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408409684896469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405939429998398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406351119279861</t>
+    <t xml:space="preserve">0.402234107255936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403469234704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409644812345505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408409655094147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40593945980072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406351178884506</t>
   </si>
   <si>
     <t xml:space="preserve">0.400175601243973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397705405950546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403880953788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403057515621185</t>
+    <t xml:space="preserve">0.397705376148224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403880923986435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403057545423508</t>
   </si>
   <si>
     <t xml:space="preserve">0.394823461771011</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">0.417467176914215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433111876249313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430641621351242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44134595990181</t>
+    <t xml:space="preserve">0.433111846446991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430641651153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441345930099487</t>
   </si>
   <si>
     <t xml:space="preserve">0.454520434141159</t>
@@ -2720,10 +2720,10 @@
     <t xml:space="preserve">0.442992717027664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488280087709427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503924787044525</t>
+    <t xml:space="preserve">0.488280028104782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50392484664917</t>
   </si>
   <si>
     <t xml:space="preserve">0.534390866756439</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">0.522039771080017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500631153583527</t>
+    <t xml:space="preserve">0.500631213188171</t>
   </si>
   <si>
     <t xml:space="preserve">0.517922759056091</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">0.485809862613678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462754428386688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472635388374329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493220508098602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573691368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481692880392075</t>
+    <t xml:space="preserve">0.462754487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472635418176651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493220597505569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49157378077507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48169282078743</t>
   </si>
   <si>
     <t xml:space="preserve">0.467694997787476</t>
@@ -2768,70 +2768,70 @@
     <t xml:space="preserve">0.459460884332657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461107701063156</t>
+    <t xml:space="preserve">0.461107671260834</t>
   </si>
   <si>
     <t xml:space="preserve">0.476752400398254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479222595691681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477575778961182</t>
+    <t xml:space="preserve">0.47922271490097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477575808763504</t>
   </si>
   <si>
     <t xml:space="preserve">0.51545250415802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504748225212097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501454591751099</t>
+    <t xml:space="preserve">0.504748165607452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501454532146454</t>
   </si>
   <si>
     <t xml:space="preserve">0.498984396457672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494043976068497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505571722984314</t>
+    <t xml:space="preserve">0.494044005870819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505571663379669</t>
   </si>
   <si>
     <t xml:space="preserve">0.490750372409821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484986484050751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492397129535675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482516258955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478399217128754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473458826541901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470988571643829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470165103673935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46522468328476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284322500229</t>
+    <t xml:space="preserve">0.484986454248428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49239718914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482516288757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478399246931076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473458766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470988661050797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470165193080902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465224713087082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284292697906</t>
   </si>
   <si>
     <t xml:space="preserve">0.46851834654808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466750353574753</t>
+    <t xml:space="preserve">0.466750383377075</t>
   </si>
   <si>
     <t xml:space="preserve">0.473822325468063</t>
@@ -2843,13 +2843,13 @@
     <t xml:space="preserve">0.46144637465477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464098364114761</t>
+    <t xml:space="preserve">0.464098334312439</t>
   </si>
   <si>
     <t xml:space="preserve">0.454374402761459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441114455461502</t>
+    <t xml:space="preserve">0.44111442565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.420782536268234</t>
@@ -2858,16 +2858,16 @@
     <t xml:space="preserve">0.435810446739197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438462466001511</t>
+    <t xml:space="preserve">0.438462436199188</t>
   </si>
   <si>
     <t xml:space="preserve">0.427412509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426528483629227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433158457279205</t>
+    <t xml:space="preserve">0.426528453826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433158487081528</t>
   </si>
   <si>
     <t xml:space="preserve">0.448186457157135</t>
@@ -2876,25 +2876,25 @@
     <t xml:space="preserve">0.441998451948166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434484452009201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444650441408157</t>
+    <t xml:space="preserve">0.434484481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44465047121048</t>
   </si>
   <si>
     <t xml:space="preserve">0.449070423841476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437578469514847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43360048532486</t>
+    <t xml:space="preserve">0.437578439712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433600425720215</t>
   </si>
   <si>
     <t xml:space="preserve">0.430948466062546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4313904941082</t>
+    <t xml:space="preserve">0.431390464305878</t>
   </si>
   <si>
     <t xml:space="preserve">0.434926480054855</t>
@@ -2912,49 +2912,49 @@
     <t xml:space="preserve">0.434042453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421666473150253</t>
+    <t xml:space="preserve">0.421666502952576</t>
   </si>
   <si>
     <t xml:space="preserve">0.430506467819214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427854508161545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419456511735916</t>
+    <t xml:space="preserve">0.427854478359222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419456541538239</t>
   </si>
   <si>
     <t xml:space="preserve">0.417246520519257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411942511796951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414152503013611</t>
+    <t xml:space="preserve">0.411942571401596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414152532815933</t>
   </si>
   <si>
     <t xml:space="preserve">0.41813051700592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422550469636917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413710504770279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425202488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423876494169235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414594560861588</t>
+    <t xml:space="preserve">0.42255049943924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413710534572601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425202518701553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423876464366913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414594531059265</t>
   </si>
   <si>
     <t xml:space="preserve">0.422992527484894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421224534511566</t>
+    <t xml:space="preserve">0.421224504709244</t>
   </si>
   <si>
     <t xml:space="preserve">0.413268536329269</t>
@@ -2963,37 +2963,37 @@
     <t xml:space="preserve">0.415920525789261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408406585454941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412384569644928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411058515310287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409732580184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409290552139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407964527606964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423434525728226</t>
+    <t xml:space="preserve">0.408406525850296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412384539842606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41105854511261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409732550382614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409290581941605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407964557409286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423434495925903</t>
   </si>
   <si>
     <t xml:space="preserve">0.42034050822258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426086485385895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428296446800232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424760490655899</t>
+    <t xml:space="preserve">0.426086455583572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428296476602554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424760520458221</t>
   </si>
   <si>
     <t xml:space="preserve">0.422108501195908</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">0.400008589029312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401334583759308</t>
+    <t xml:space="preserve">0.401334553956985</t>
   </si>
   <si>
     <t xml:space="preserve">0.39249461889267</t>
@@ -3020,52 +3020,52 @@
     <t xml:space="preserve">0.396030604839325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405754566192627</t>
+    <t xml:space="preserve">0.405754536390305</t>
   </si>
   <si>
     <t xml:space="preserve">0.403544545173645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400450557470322</t>
+    <t xml:space="preserve">0.400450617074966</t>
   </si>
   <si>
     <t xml:space="preserve">0.389842629432678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388958603143692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395146578550339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386748611927032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393378615379333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403102546930313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396914601325989</t>
+    <t xml:space="preserve">0.388958632946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395146608352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386748641729355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393378585577011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403102576732635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396914571523666</t>
   </si>
   <si>
     <t xml:space="preserve">0.397798597812653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40177658200264</t>
+    <t xml:space="preserve">0.401776552200317</t>
   </si>
   <si>
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660548686981</t>
+    <t xml:space="preserve">0.402660578489304</t>
   </si>
   <si>
     <t xml:space="preserve">0.419898509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436694443225861</t>
+    <t xml:space="preserve">0.436694473028183</t>
   </si>
   <si>
     <t xml:space="preserve">0.443766385316849</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">0.456523567438126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465635806322098</t>
+    <t xml:space="preserve">0.465635776519775</t>
   </si>
   <si>
     <t xml:space="preserve">0.464724570512772</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">0.468369513750076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480215460062027</t>
+    <t xml:space="preserve">0.480215400457382</t>
   </si>
   <si>
     <t xml:space="preserve">0.482949018478394</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">0.486593961715698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501173615455627</t>
+    <t xml:space="preserve">0.501173555850983</t>
   </si>
   <si>
     <t xml:space="preserve">0.523042976856232</t>
@@ -3158,28 +3158,28 @@
     <t xml:space="preserve">0.519398033618927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51393073797226</t>
+    <t xml:space="preserve">0.513930678367615</t>
   </si>
   <si>
     <t xml:space="preserve">0.524865388870239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509374618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526687860488892</t>
+    <t xml:space="preserve">0.509374558925629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526687920093536</t>
   </si>
   <si>
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267514228821</t>
+    <t xml:space="preserve">0.541267454624176</t>
   </si>
   <si>
     <t xml:space="preserve">0.546734869480133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537622570991516</t>
+    <t xml:space="preserve">0.537622511386871</t>
   </si>
   <si>
     <t xml:space="preserve">0.549468457698822</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">0.564959287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569515466690063</t>
+    <t xml:space="preserve">0.569515407085419</t>
   </si>
   <si>
     <t xml:space="preserve">0.565870463848114</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">0.550379633903503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547646105289459</t>
+    <t xml:space="preserve">0.547646045684814</t>
   </si>
   <si>
     <t xml:space="preserve">0.55584704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553113400936127</t>
+    <t xml:space="preserve">0.553113341331482</t>
   </si>
   <si>
     <t xml:space="preserve">0.564048111438751</t>
@@ -3227,25 +3227,25 @@
     <t xml:space="preserve">0.559491991996765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561314404010773</t>
+    <t xml:space="preserve">0.561314344406128</t>
   </si>
   <si>
     <t xml:space="preserve">0.558580696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556758344173431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542178690433502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557669460773468</t>
+    <t xml:space="preserve">0.556758284568787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542178750038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557669520378113</t>
   </si>
   <si>
     <t xml:space="preserve">0.534888863563538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528510272502899</t>
+    <t xml:space="preserve">0.528510332107544</t>
   </si>
   <si>
     <t xml:space="preserve">0.535800099372864</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617436408997</t>
+    <t xml:space="preserve">0.496617496013641</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
@@ -3293,19 +3293,19 @@
     <t xml:space="preserve">0.487505257129669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495706290006638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493883818387985</t>
+    <t xml:space="preserve">0.495706230401993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49388375878334</t>
   </si>
   <si>
     <t xml:space="preserve">0.491150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517575681209564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489643454551697</t>
+    <t xml:space="preserve">0.517575621604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489643424749374</t>
   </si>
   <si>
     <t xml:space="preserve">0.48199275135994</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">0.475776553153992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47673287987709</t>
+    <t xml:space="preserve">0.476732909679413</t>
   </si>
   <si>
     <t xml:space="preserve">0.480080038309097</t>
@@ -3329,31 +3329,31 @@
     <t xml:space="preserve">0.46477872133255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473385751247406</t>
+    <t xml:space="preserve">0.473385721445084</t>
   </si>
   <si>
     <t xml:space="preserve">0.469560384750366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470994919538498</t>
+    <t xml:space="preserve">0.470994889736176</t>
   </si>
   <si>
     <t xml:space="preserve">0.459040701389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453780859708786</t>
+    <t xml:space="preserve">0.453780889511108</t>
   </si>
   <si>
     <t xml:space="preserve">0.451390027999878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447564661502838</t>
+    <t xml:space="preserve">0.447564691305161</t>
   </si>
   <si>
     <t xml:space="preserve">0.45091187953949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441826701164246</t>
+    <t xml:space="preserve">0.441826671361923</t>
   </si>
   <si>
     <t xml:space="preserve">0.438479512929916</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">0.432741492986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436088651418686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438001364469528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441348493099213</t>
+    <t xml:space="preserve">0.436088681221008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438001334667206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441348522901535</t>
   </si>
   <si>
     <t xml:space="preserve">0.446608364582062</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">0.436566829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438957691192627</t>
+    <t xml:space="preserve">0.438957661390305</t>
   </si>
   <si>
     <t xml:space="preserve">0.444695681333542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439435839653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4336978495121</t>
+    <t xml:space="preserve">0.439435869455338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433697819709778</t>
   </si>
   <si>
     <t xml:space="preserve">0.434654176235199</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">0.46669140458107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454737216234207</t>
+    <t xml:space="preserve">0.454737186431885</t>
   </si>
   <si>
     <t xml:space="preserve">0.455693542957306</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">0.561368525028229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538416504859924</t>
+    <t xml:space="preserve">0.538416564464569</t>
   </si>
   <si>
     <t xml:space="preserve">0.544154524803162</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">0.540329158306122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525984168052673</t>
+    <t xml:space="preserve">0.525984108448029</t>
   </si>
   <si>
     <t xml:space="preserve">0.517377138137817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525027811527252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521202445030212</t>
+    <t xml:space="preserve">0.525027871131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521202504634857</t>
   </si>
   <si>
     <t xml:space="preserve">0.519289791584015</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">0.531722128391266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518333494663239</t>
+    <t xml:space="preserve">0.518333435058594</t>
   </si>
   <si>
     <t xml:space="preserve">0.514508128166199</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">0.527896821498871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526940524578094</t>
+    <t xml:space="preserve">0.52694046497345</t>
   </si>
   <si>
     <t xml:space="preserve">0.535547494888306</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">0.553717851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568062901496887</t>
+    <t xml:space="preserve">0.568062841892242</t>
   </si>
   <si>
     <t xml:space="preserve">0.55849951505661</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">0.555630505084991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55467414855957</t>
+    <t xml:space="preserve">0.554674208164215</t>
   </si>
   <si>
     <t xml:space="preserve">0.557543218135834</t>
@@ -3491,16 +3491,16 @@
     <t xml:space="preserve">0.54702353477478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537460088729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551805257797241</t>
+    <t xml:space="preserve">0.537460148334503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551805198192596</t>
   </si>
   <si>
     <t xml:space="preserve">0.524071455001831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533634841442108</t>
+    <t xml:space="preserve">0.533634901046753</t>
   </si>
   <si>
     <t xml:space="preserve">0.536503851413727</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">0.522158801555634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529809474945068</t>
+    <t xml:space="preserve">0.529809534549713</t>
   </si>
   <si>
     <t xml:space="preserve">0.532678484916687</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">0.499206781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496337741613388</t>
+    <t xml:space="preserve">0.49633777141571</t>
   </si>
   <si>
     <t xml:space="preserve">0.506857395172119</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">0.487730741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483905375003815</t>
+    <t xml:space="preserve">0.483905404806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.461909741163254</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">0.478167414665222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468604058027267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471473038196564</t>
+    <t xml:space="preserve">0.46860408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471473067998886</t>
   </si>
   <si>
     <t xml:space="preserve">0.48260822892189</t>
@@ -3969,6 +3969,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.578999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575999975204468</t>
   </si>
 </sst>
 </file>
@@ -69307,7 +69310,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6909837963</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>244792</v>
@@ -69328,6 +69331,32 @@
         <v>1318</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6936226852</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>171378</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>0.583000004291534</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>0.575999975204468</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>0.582000017166138</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>0.575999975204468</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1319</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="1320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="1319">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,91 +38,91 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333736181259155</t>
+    <t xml:space="preserve">0.333736151456833</t>
   </si>
   <si>
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327446222305298</t>
+    <t xml:space="preserve">0.32744625210762</t>
   </si>
   <si>
     <t xml:space="preserve">0.321156293153763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317678391933441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307318478822708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288448750972748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289336651563644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294368624687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285636752843857</t>
+    <t xml:space="preserve">0.317678362131119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307318449020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288448721170425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289336681365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294368594884872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285636723041534</t>
   </si>
   <si>
     <t xml:space="preserve">0.273796856403351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258997082710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258257031440735</t>
+    <t xml:space="preserve">0.258997052907944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258257001638412</t>
   </si>
   <si>
     <t xml:space="preserve">0.243605196475983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246417164802551</t>
+    <t xml:space="preserve">0.246417194604874</t>
   </si>
   <si>
     <t xml:space="preserve">0.262696981430054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256407052278519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259811013936996</t>
+    <t xml:space="preserve">0.256407082080841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259811043739319</t>
   </si>
   <si>
     <t xml:space="preserve">0.261512994766235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253817111253738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253077119588852</t>
+    <t xml:space="preserve">0.253817081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25307708978653</t>
   </si>
   <si>
     <t xml:space="preserve">0.286894708871841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284600764513016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277496814727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287116765975952</t>
+    <t xml:space="preserve">0.284600734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277496784925461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28711673617363</t>
   </si>
   <si>
     <t xml:space="preserve">0.290742635726929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263806968927383</t>
+    <t xml:space="preserve">0.263806939125061</t>
   </si>
   <si>
     <t xml:space="preserve">0.256777077913284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250117152929306</t>
+    <t xml:space="preserve">0.250117123126984</t>
   </si>
   <si>
     <t xml:space="preserve">0.277570813894272</t>
@@ -134,19 +134,19 @@
     <t xml:space="preserve">0.310796439647675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303544551134109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30435848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318122327327728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309686452150345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301620543003082</t>
+    <t xml:space="preserve">0.303544521331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304358512163162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318122297525406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309686481952667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30162051320076</t>
   </si>
   <si>
     <t xml:space="preserve">0.310352444648743</t>
@@ -161,52 +161,52 @@
     <t xml:space="preserve">0.316716372966766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315236419439316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315606415271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332996159791946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332256197929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328852266073227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330480188131332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311240434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312054395675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299696564674377</t>
+    <t xml:space="preserve">0.315236389636993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315606385469437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332996189594269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33225616812706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328852206468582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330480247735977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311240404844284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312054425477982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2996965944767</t>
   </si>
   <si>
     <t xml:space="preserve">0.296884596347809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299400568008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297476589679718</t>
+    <t xml:space="preserve">0.2994005382061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297476649284363</t>
   </si>
   <si>
     <t xml:space="preserve">0.295996576547623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293702602386475</t>
+    <t xml:space="preserve">0.293702632188797</t>
   </si>
   <si>
     <t xml:space="preserve">0.298216581344604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286376744508743</t>
+    <t xml:space="preserve">0.286376714706421</t>
   </si>
   <si>
     <t xml:space="preserve">0.276756852865219</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">0.270466893911362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265064984560013</t>
+    <t xml:space="preserve">0.26506495475769</t>
   </si>
   <si>
     <t xml:space="preserve">0.268172919750214</t>
@@ -236,34 +236,34 @@
     <t xml:space="preserve">0.269208908081055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275276869535446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284896701574326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290002703666687</t>
+    <t xml:space="preserve">0.275276839733124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284896731376648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290002673864365</t>
   </si>
   <si>
     <t xml:space="preserve">0.308206468820572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309168457984924</t>
+    <t xml:space="preserve">0.309168487787247</t>
   </si>
   <si>
     <t xml:space="preserve">0.318196356296539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316938370466232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308946490287781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314200401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321378290653229</t>
+    <t xml:space="preserve">0.31693834066391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308946460485458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314200431108475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321378320455551</t>
   </si>
   <si>
     <t xml:space="preserve">0.319380342960358</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">0.304950505495071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305616497993469</t>
+    <t xml:space="preserve">0.305616438388824</t>
   </si>
   <si>
     <t xml:space="preserve">0.2995485663414</t>
@@ -302,31 +302,31 @@
     <t xml:space="preserve">0.300954520702362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314400315284729</t>
+    <t xml:space="preserve">0.314400345087051</t>
   </si>
   <si>
     <t xml:space="preserve">0.318779796361923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318856626749039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318395644426346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319932252168655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318088322877884</t>
+    <t xml:space="preserve">0.318856596946716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318395614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319932281970978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318088293075562</t>
   </si>
   <si>
     <t xml:space="preserve">0.307331681251526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321776270866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320393294095993</t>
+    <t xml:space="preserve">0.321776300668716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320393264293671</t>
   </si>
   <si>
     <t xml:space="preserve">0.311557471752167</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">0.305795013904572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301569223403931</t>
+    <t xml:space="preserve">0.301569193601608</t>
   </si>
   <si>
     <t xml:space="preserve">0.295806735754013</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">0.299648374319077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296575099229813</t>
+    <t xml:space="preserve">0.29657506942749</t>
   </si>
   <si>
     <t xml:space="preserve">0.303490042686462</t>
@@ -353,16 +353,16 @@
     <t xml:space="preserve">0.314246654510498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318011432886124</t>
+    <t xml:space="preserve">0.318011462688446</t>
   </si>
   <si>
     <t xml:space="preserve">0.318702936172485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321161597967148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310020804405212</t>
+    <t xml:space="preserve">0.32116162776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310020834207535</t>
   </si>
   <si>
     <t xml:space="preserve">0.311941653490067</t>
@@ -371,16 +371,16 @@
     <t xml:space="preserve">0.311173319816589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307254880666733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30671700835228</t>
+    <t xml:space="preserve">0.307254821062088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306717038154602</t>
   </si>
   <si>
     <t xml:space="preserve">0.305564552545547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304949820041656</t>
+    <t xml:space="preserve">0.304949879646301</t>
   </si>
   <si>
     <t xml:space="preserve">0.306870669126511</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">0.301799714565277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304027855396271</t>
+    <t xml:space="preserve">0.304027885198593</t>
   </si>
   <si>
     <t xml:space="preserve">0.300032556056976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313478320837021</t>
+    <t xml:space="preserve">0.313478291034698</t>
   </si>
   <si>
     <t xml:space="preserve">0.312556326389313</t>
@@ -410,25 +410,25 @@
     <t xml:space="preserve">0.311480700969696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298265397548676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299110561609268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305257201194763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295576244592667</t>
+    <t xml:space="preserve">0.298265427350998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299110531806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305257230997086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295576214790344</t>
   </si>
   <si>
     <t xml:space="preserve">0.295960396528244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297650694847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297881245613098</t>
+    <t xml:space="preserve">0.297650724649429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297881275415421</t>
   </si>
   <si>
     <t xml:space="preserve">0.29373225569725</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">0.300416678190231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300109416246414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298880040645599</t>
+    <t xml:space="preserve">0.300109386444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298880070447922</t>
   </si>
   <si>
     <t xml:space="preserve">0.305487662553787</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">0.303566873073578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308253675699234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304873049259186</t>
+    <t xml:space="preserve">0.308253705501556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304873079061508</t>
   </si>
   <si>
     <t xml:space="preserve">0.306563347578049</t>
@@ -476,25 +476,25 @@
     <t xml:space="preserve">0.296421378850937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301415592432022</t>
+    <t xml:space="preserve">0.3014155626297</t>
   </si>
   <si>
     <t xml:space="preserve">0.300647228956223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282975614070892</t>
+    <t xml:space="preserve">0.282975643873215</t>
   </si>
   <si>
     <t xml:space="preserve">0.29196509718895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289736926555634</t>
+    <t xml:space="preserve">0.289736956357956</t>
   </si>
   <si>
     <t xml:space="preserve">0.293501764535904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292656570672989</t>
+    <t xml:space="preserve">0.292656600475311</t>
   </si>
   <si>
     <t xml:space="preserve">0.29250293970108</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">0.289583265781403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288123458623886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284281820058823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28789296746254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290044277906418</t>
+    <t xml:space="preserve">0.288123428821564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2842817902565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287892997264862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290044248104095</t>
   </si>
   <si>
     <t xml:space="preserve">0.292887091636658</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.293117612600327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291888236999512</t>
+    <t xml:space="preserve">0.291888296604156</t>
   </si>
   <si>
     <t xml:space="preserve">0.289813786745071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286586791276932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294270098209381</t>
+    <t xml:space="preserve">0.286586821079254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294270068407059</t>
   </si>
   <si>
     <t xml:space="preserve">0.291811436414719</t>
@@ -539,37 +539,37 @@
     <t xml:space="preserve">0.292579770088196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295729875564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298419058322906</t>
+    <t xml:space="preserve">0.295729905366898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298419088125229</t>
   </si>
   <si>
     <t xml:space="preserve">0.294731080532074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287355124950409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293809056282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292041957378387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286740511655807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2846659719944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278903514146805</t>
+    <t xml:space="preserve">0.287355095148087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293809086084366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29204198718071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286740481853485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284665942192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278903484344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.275599718093872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270221382379532</t>
+    <t xml:space="preserve">0.270221412181854</t>
   </si>
   <si>
     <t xml:space="preserve">0.272449553012848</t>
@@ -578,25 +578,25 @@
     <t xml:space="preserve">0.276675373315811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27398619055748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275676518678665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275522828102112</t>
+    <t xml:space="preserve">0.273986220359802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275676488876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275522857904434</t>
   </si>
   <si>
     <t xml:space="preserve">0.276598513126373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270989686250687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27114337682724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274293512105942</t>
+    <t xml:space="preserve">0.270989716053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271143347024918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274293541908264</t>
   </si>
   <si>
     <t xml:space="preserve">0.270451873540878</t>
@@ -605,40 +605,40 @@
     <t xml:space="preserve">0.268146902322769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267378568649292</t>
+    <t xml:space="preserve">0.26737853884697</t>
   </si>
   <si>
     <t xml:space="preserve">0.264612555503845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265765070915222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262384414672852</t>
+    <t xml:space="preserve">0.265765100717545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262384444475174</t>
   </si>
   <si>
     <t xml:space="preserve">0.267532229423523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265304088592529</t>
+    <t xml:space="preserve">0.265304058790207</t>
   </si>
   <si>
     <t xml:space="preserve">0.271911680698395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272526383399963</t>
+    <t xml:space="preserve">0.272526353597641</t>
   </si>
   <si>
     <t xml:space="preserve">0.283282995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279902338981628</t>
+    <t xml:space="preserve">0.279902368783951</t>
   </si>
   <si>
     <t xml:space="preserve">0.277059525251389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278442531824112</t>
+    <t xml:space="preserve">0.27844250202179</t>
   </si>
   <si>
     <t xml:space="preserve">0.280517041683197</t>
@@ -647,40 +647,40 @@
     <t xml:space="preserve">0.278749823570251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278980314731598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278212040662766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284051299095154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290812641382217</t>
+    <t xml:space="preserve">0.27898034453392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278211981058121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284051328897476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290812581777573</t>
   </si>
   <si>
     <t xml:space="preserve">0.28966012597084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290428429841995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294807910919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295422583818436</t>
+    <t xml:space="preserve">0.290428400039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294807940721512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295422554016113</t>
   </si>
   <si>
     <t xml:space="preserve">0.288507580757141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284589141607285</t>
+    <t xml:space="preserve">0.284589111804962</t>
   </si>
   <si>
     <t xml:space="preserve">0.291043132543564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293885946273804</t>
+    <t xml:space="preserve">0.293885886669159</t>
   </si>
   <si>
     <t xml:space="preserve">0.294884771108627</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">0.286125808954239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284358590841293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282745182514191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277290046215057</t>
+    <t xml:space="preserve">0.284358620643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282745152711868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277290016412735</t>
   </si>
   <si>
     <t xml:space="preserve">0.281976819038391</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">0.276214331388474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273602038621902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269760400056839</t>
+    <t xml:space="preserve">0.27360200881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269760429859161</t>
   </si>
   <si>
     <t xml:space="preserve">0.275061875581741</t>
@@ -719,37 +719,37 @@
     <t xml:space="preserve">0.271834880113602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273371577262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275215566158295</t>
+    <t xml:space="preserve">0.273371547460556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275215536355972</t>
   </si>
   <si>
     <t xml:space="preserve">0.276905834674835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274831354618073</t>
+    <t xml:space="preserve">0.274831384420395</t>
   </si>
   <si>
     <t xml:space="preserve">0.282668322324753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280440181493759</t>
+    <t xml:space="preserve">0.280440151691437</t>
   </si>
   <si>
     <t xml:space="preserve">0.279595017433167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277366816997528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278135120868683</t>
+    <t xml:space="preserve">0.27736684679985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278135150671005</t>
   </si>
   <si>
     <t xml:space="preserve">0.281208485364914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278672993183136</t>
+    <t xml:space="preserve">0.278672963380814</t>
   </si>
   <si>
     <t xml:space="preserve">0.282591491937637</t>
@@ -764,25 +764,25 @@
     <t xml:space="preserve">0.27967181801796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286663621664047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284435510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281899988651276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283897668123245</t>
+    <t xml:space="preserve">0.28666365146637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284435480833054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281899958848953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283897638320923</t>
   </si>
   <si>
     <t xml:space="preserve">0.285280615091324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285434275865555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295038431882858</t>
+    <t xml:space="preserve">0.285434305667877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295038402080536</t>
   </si>
   <si>
     <t xml:space="preserve">0.304258346557617</t>
@@ -797,64 +797,64 @@
     <t xml:space="preserve">0.33184140920639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325387448072433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316935807466507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309790343046188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309252500534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311096549034119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313094168901443</t>
+    <t xml:space="preserve">0.325387418270111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316935777664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309790372848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30925253033638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311096519231796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313094139099121</t>
   </si>
   <si>
     <t xml:space="preserve">0.313017308712006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288891762495041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293040752410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295192062854767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296805560588837</t>
+    <t xml:space="preserve">0.288891732692719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293040722608566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295192092657089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296805590391159</t>
   </si>
   <si>
     <t xml:space="preserve">0.297266602516174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298111766576767</t>
+    <t xml:space="preserve">0.298111736774445</t>
   </si>
   <si>
     <t xml:space="preserve">0.310251325368881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313555151224136</t>
+    <t xml:space="preserve">0.313555181026459</t>
   </si>
   <si>
     <t xml:space="preserve">0.300800859928131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308868318796158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299725234508514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32185310125351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327308297157288</t>
+    <t xml:space="preserve">0.30886834859848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299725204706192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321853131055832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327308237552643</t>
   </si>
   <si>
     <t xml:space="preserve">0.318472474813461</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">0.312095314264297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314016133546829</t>
+    <t xml:space="preserve">0.314016163349152</t>
   </si>
   <si>
     <t xml:space="preserve">0.315014958381653</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">0.309636652469635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307408511638641</t>
+    <t xml:space="preserve">0.307408481836319</t>
   </si>
   <si>
     <t xml:space="preserve">0.308945178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313631951808929</t>
+    <t xml:space="preserve">0.313632011413574</t>
   </si>
   <si>
     <t xml:space="preserve">0.308023184537888</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">0.307715833187103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309022068977356</t>
+    <t xml:space="preserve">0.309022039175034</t>
   </si>
   <si>
     <t xml:space="preserve">0.309944003820419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317780941724777</t>
+    <t xml:space="preserve">0.317780911922455</t>
   </si>
   <si>
     <t xml:space="preserve">0.31655165553093</t>
@@ -908,34 +908,34 @@
     <t xml:space="preserve">0.316474795341492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324388563632965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325003236532211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318318754434586</t>
+    <t xml:space="preserve">0.324388593435287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325003296136856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318318784236908</t>
   </si>
   <si>
     <t xml:space="preserve">0.317704141139984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321545779705048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320470094680786</t>
+    <t xml:space="preserve">0.321545749902725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320470124483109</t>
   </si>
   <si>
     <t xml:space="preserve">0.322621464729309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323697119951248</t>
+    <t xml:space="preserve">0.323697090148926</t>
   </si>
   <si>
     <t xml:space="preserve">0.333454847335815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327385038137436</t>
+    <t xml:space="preserve">0.327385067939758</t>
   </si>
   <si>
     <t xml:space="preserve">0.331764578819275</t>
@@ -944,28 +944,28 @@
     <t xml:space="preserve">0.339524686336517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34567129611969</t>
+    <t xml:space="preserve">0.345671325922012</t>
   </si>
   <si>
     <t xml:space="preserve">0.340446680784225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333378076553345</t>
+    <t xml:space="preserve">0.333378046751022</t>
   </si>
   <si>
     <t xml:space="preserve">0.33499151468277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336144000291824</t>
+    <t xml:space="preserve">0.336144059896469</t>
   </si>
   <si>
     <t xml:space="preserve">0.337757498025894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338910013437271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338141709566116</t>
+    <t xml:space="preserve">0.338909983634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338141679763794</t>
   </si>
   <si>
     <t xml:space="preserve">0.339678347110748</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">0.344211488962173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340677201747894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334607392549515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338218539953232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346900641918182</t>
+    <t xml:space="preserve">0.340677171945572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33460733294487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338218510150909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34690061211586</t>
   </si>
   <si>
     <t xml:space="preserve">0.346132338047028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339601516723633</t>
+    <t xml:space="preserve">0.339601546525955</t>
   </si>
   <si>
     <t xml:space="preserve">0.340907663106918</t>
@@ -1004,34 +1004,34 @@
     <t xml:space="preserve">0.352663099765778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369950503110886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36541736125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363035529851913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374099522829056</t>
+    <t xml:space="preserve">0.369950532913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365417391061783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363035559654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374099493026733</t>
   </si>
   <si>
     <t xml:space="preserve">0.371103048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369566321372986</t>
+    <t xml:space="preserve">0.369566380977631</t>
   </si>
   <si>
     <t xml:space="preserve">0.368798017501831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3661088347435</t>
+    <t xml:space="preserve">0.366108894348145</t>
   </si>
   <si>
     <t xml:space="preserve">0.363112390041351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3686443567276</t>
+    <t xml:space="preserve">0.368644326925278</t>
   </si>
   <si>
     <t xml:space="preserve">0.366877198219299</t>
@@ -1046,19 +1046,19 @@
     <t xml:space="preserve">0.359885424375534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35919389128685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368567526340485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372024983167648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375559329986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380246132612228</t>
+    <t xml:space="preserve">0.359193950891495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368567496538162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372025012969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37555930018425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380246073007584</t>
   </si>
   <si>
     <t xml:space="preserve">0.392616212368011</t>
@@ -1067,28 +1067,28 @@
     <t xml:space="preserve">0.405677825212479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42104434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419507771730423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396842032670975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413361132144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422581076622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417586892843246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426422774791718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423349440097809</t>
+    <t xml:space="preserve">0.421044409275055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419507741928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396842002868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413361102342606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422581017017365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417586922645569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426422744989395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423349350690842</t>
   </si>
   <si>
     <t xml:space="preserve">0.427959322929382</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">0.452930122613907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459460824728012</t>
+    <t xml:space="preserve">0.459460914134979</t>
   </si>
   <si>
     <t xml:space="preserve">0.46522331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468296706676483</t>
+    <t xml:space="preserve">0.468296617269516</t>
   </si>
   <si>
     <t xml:space="preserve">0.481358289718628</t>
@@ -1121,25 +1121,25 @@
     <t xml:space="preserve">0.515164732933044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505560636520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50709730386734</t>
+    <t xml:space="preserve">0.505560696125031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507097363471985</t>
   </si>
   <si>
     <t xml:space="preserve">0.515548944473267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503255605697632</t>
+    <t xml:space="preserve">0.503255665302277</t>
   </si>
   <si>
     <t xml:space="preserve">0.48980987071991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480205774307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519006371498108</t>
+    <t xml:space="preserve">0.480205744504929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519006431102753</t>
   </si>
   <si>
     <t xml:space="preserve">0.511323094367981</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">0.499413967132568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491730660200119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484431535005569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483663201332092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484815776348114</t>
+    <t xml:space="preserve">0.491730779409409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484431624412537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483663231134415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484815746545792</t>
   </si>
   <si>
     <t xml:space="preserve">0.49518820643425</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">0.600065112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58239358663559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572021126747131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572789371013641</t>
+    <t xml:space="preserve">0.582393527030945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572021067142487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572789490222931</t>
   </si>
   <si>
     <t xml:space="preserve">0.552428662776947</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">0.551276206970215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545129537582397</t>
+    <t xml:space="preserve">0.545129597187042</t>
   </si>
   <si>
     <t xml:space="preserve">0.565874457359314</t>
@@ -1208,37 +1208,37 @@
     <t xml:space="preserve">0.596607625484467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584698498249054</t>
+    <t xml:space="preserve">0.584698557853699</t>
   </si>
   <si>
     <t xml:space="preserve">0.608132541179657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621962487697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620425939559937</t>
+    <t xml:space="preserve">0.621962428092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620425820350647</t>
   </si>
   <si>
     <t xml:space="preserve">0.629645764827728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614279270172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607748329639435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581625282764435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560880362987518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598528444766998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598144352436066</t>
+    <t xml:space="preserve">0.614279091358185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60774838924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581625163555145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560880303382874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598528385162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598144292831421</t>
   </si>
   <si>
     <t xml:space="preserve">0.619657516479492</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">0.601601719856262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58661937713623</t>
+    <t xml:space="preserve">0.586619317531586</t>
   </si>
   <si>
     <t xml:space="preserve">0.59545511007309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587771892547607</t>
+    <t xml:space="preserve">0.587771773338318</t>
   </si>
   <si>
     <t xml:space="preserve">0.584314405918121</t>
@@ -1274,37 +1274,37 @@
     <t xml:space="preserve">0.543592870235443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564722001552582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.563185214996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576246917247772</t>
+    <t xml:space="preserve">0.564721941947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.563185274600983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576246857643127</t>
   </si>
   <si>
     <t xml:space="preserve">0.583930194377899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58085685968399</t>
+    <t xml:space="preserve">0.580856800079346</t>
   </si>
   <si>
     <t xml:space="preserve">0.587003529071808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604675054550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629261612892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618505001068115</t>
+    <t xml:space="preserve">0.604675114154816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629261672496796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61850506067276</t>
   </si>
   <si>
     <t xml:space="preserve">0.606980085372925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603138446807861</t>
+    <t xml:space="preserve">0.603138387203217</t>
   </si>
   <si>
     <t xml:space="preserve">0.612358391284943</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">0.599296748638153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589308559894562</t>
+    <t xml:space="preserve">0.589308500289917</t>
   </si>
   <si>
     <t xml:space="preserve">0.553965330123901</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">0.536293804645538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524000585079193</t>
+    <t xml:space="preserve">0.524000525474548</t>
   </si>
   <si>
     <t xml:space="preserve">0.537830471992493</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">0.547818720340729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53245210647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537062108516693</t>
+    <t xml:space="preserve">0.532452166080475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537062168121338</t>
   </si>
   <si>
     <t xml:space="preserve">0.527073919773102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520927250385284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517853856086731</t>
+    <t xml:space="preserve">0.52092719078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517853975296021</t>
   </si>
   <si>
     <t xml:space="preserve">0.525537192821503</t>
@@ -1370,43 +1370,43 @@
     <t xml:space="preserve">0.530147194862366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523232281208038</t>
+    <t xml:space="preserve">0.523232221603394</t>
   </si>
   <si>
     <t xml:space="preserve">0.51939058303833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524768829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549355387687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501718997955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492498964071274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477900773286819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476364076137543</t>
+    <t xml:space="preserve">0.524768888950348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549355447292328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501718938350677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492499053478241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477900743484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476364135742188</t>
   </si>
   <si>
     <t xml:space="preserve">0.48865732550621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471754193305969</t>
+    <t xml:space="preserve">0.471754133701324</t>
   </si>
   <si>
     <t xml:space="preserve">0.472522497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468680888414383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487120717763901</t>
+    <t xml:space="preserve">0.468680828809738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487120777368546</t>
   </si>
   <si>
     <t xml:space="preserve">0.481742411851883</t>
@@ -1418,28 +1418,28 @@
     <t xml:space="preserve">0.483279079198837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478669196367264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47021746635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467912524938583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466375827789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839249849319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461765885353088</t>
+    <t xml:space="preserve">0.478669136762619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470217496156693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467912495136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466375857591629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839190244675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461765825748444</t>
   </si>
   <si>
     <t xml:space="preserve">0.487889021635056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500182271003723</t>
+    <t xml:space="preserve">0.500182390213013</t>
   </si>
   <si>
     <t xml:space="preserve">0.469449162483215</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">0.444862574338913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431800991296768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444094300270081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424117654561996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415666133165359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382627964019775</t>
+    <t xml:space="preserve">0.431800961494446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444094270467758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424117743968964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415666162967682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382627993822098</t>
   </si>
   <si>
     <t xml:space="preserve">0.379170477390289</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">0.382243812084198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385701239109039</t>
+    <t xml:space="preserve">0.385701268911362</t>
   </si>
   <si>
     <t xml:space="preserve">0.388774544000626</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">0.384164601564407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376481294631958</t>
+    <t xml:space="preserve">0.37648132443428</t>
   </si>
   <si>
     <t xml:space="preserve">0.367261350154877</t>
@@ -1493,46 +1493,46 @@
     <t xml:space="preserve">0.364956378936768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360346406698227</t>
+    <t xml:space="preserve">0.360346436500549</t>
   </si>
   <si>
     <t xml:space="preserve">0.352278918027878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356504738330841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37148717045784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368029683828354</t>
+    <t xml:space="preserve">0.356504768133163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371487200260162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368029713630676</t>
   </si>
   <si>
     <t xml:space="preserve">0.37225553393364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365340501070023</t>
+    <t xml:space="preserve">0.365340530872345</t>
   </si>
   <si>
     <t xml:space="preserve">0.374944657087326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3664930164814</t>
+    <t xml:space="preserve">0.366493046283722</t>
   </si>
   <si>
     <t xml:space="preserve">0.374560505151749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374176323413849</t>
+    <t xml:space="preserve">0.374176293611526</t>
   </si>
   <si>
     <t xml:space="preserve">0.378786325454712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362267225980759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353815644979477</t>
+    <t xml:space="preserve">0.362267255783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353815615177155</t>
   </si>
   <si>
     <t xml:space="preserve">0.354583919048309</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">0.35419973731041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395689487457275</t>
+    <t xml:space="preserve">0.395689517259598</t>
   </si>
   <si>
     <t xml:space="preserve">0.411056131124496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40798282623291</t>
+    <t xml:space="preserve">0.407982796430588</t>
   </si>
   <si>
     <t xml:space="preserve">0.384932935237885</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">0.390311241149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378018021583557</t>
+    <t xml:space="preserve">0.378017991781235</t>
   </si>
   <si>
     <t xml:space="preserve">0.380707114934921</t>
@@ -1571,40 +1571,40 @@
     <t xml:space="preserve">0.362651377916336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35957807302475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353431463241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349589854478836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344979822635651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343058973550797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354968100786209</t>
+    <t xml:space="preserve">0.359578102827072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353431433439255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349589824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344979792833328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343059003353119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354968130588531</t>
   </si>
   <si>
     <t xml:space="preserve">0.36418804526329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357273101806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349974006414413</t>
+    <t xml:space="preserve">0.357273072004318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349973976612091</t>
   </si>
   <si>
     <t xml:space="preserve">0.339217364788055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323850780725479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361883044242859</t>
+    <t xml:space="preserve">0.323850750923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361883074045181</t>
   </si>
   <si>
     <t xml:space="preserve">0.350742280483246</t>
@@ -1613,10 +1613,10 @@
     <t xml:space="preserve">0.389542937278748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404141217470169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396457850933075</t>
+    <t xml:space="preserve">0.404141157865524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39645779132843</t>
   </si>
   <si>
     <t xml:space="preserve">0.412592828273773</t>
@@ -1631,13 +1631,13 @@
     <t xml:space="preserve">0.394152909517288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399531155824661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40260449051857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40106788277626</t>
+    <t xml:space="preserve">0.399531185626984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402604520320892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401067852973938</t>
   </si>
   <si>
     <t xml:space="preserve">0.397994518280029</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">0.375712990760803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364572197198868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345748156309128</t>
+    <t xml:space="preserve">0.36457222700119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345748126506805</t>
   </si>
   <si>
     <t xml:space="preserve">0.336528211832047</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">0.335759848356247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337296515703201</t>
+    <t xml:space="preserve">0.337296545505524</t>
   </si>
   <si>
     <t xml:space="preserve">0.329613238573074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32807657122612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331534028053284</t>
+    <t xml:space="preserve">0.328076541423798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331534057855606</t>
   </si>
   <si>
     <t xml:space="preserve">0.319240808486938</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">0.341138154268265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322698265314102</t>
+    <t xml:space="preserve">0.32269823551178</t>
   </si>
   <si>
     <t xml:space="preserve">0.326155751943588</t>
@@ -1697,43 +1697,43 @@
     <t xml:space="preserve">0.330381542444229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329997390508652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324234962463379</t>
+    <t xml:space="preserve">0.329997420310974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324234902858734</t>
   </si>
   <si>
     <t xml:space="preserve">0.313862472772598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301185041666031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303874164819717</t>
+    <t xml:space="preserve">0.301185011863708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30387419462204</t>
   </si>
   <si>
     <t xml:space="preserve">0.29695925116539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302721679210663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32308241724968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308100014925003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310405015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306947529315948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314630806446075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305410861968994</t>
+    <t xml:space="preserve">0.302721738815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323082447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308100044727325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310404986143112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306947499513626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314630836248398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305410891771317</t>
   </si>
   <si>
     <t xml:space="preserve">0.30848416686058</t>
@@ -1742,25 +1742,25 @@
     <t xml:space="preserve">0.304642528295517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32077744603157</t>
+    <t xml:space="preserve">0.320777416229248</t>
   </si>
   <si>
     <t xml:space="preserve">0.356888920068741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358041375875473</t>
+    <t xml:space="preserve">0.358041405677795</t>
   </si>
   <si>
     <t xml:space="preserve">0.356120586395264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360730588436127</t>
+    <t xml:space="preserve">0.360730558633804</t>
   </si>
   <si>
     <t xml:space="preserve">0.358809739351273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351126432418823</t>
+    <t xml:space="preserve">0.351126462221146</t>
   </si>
   <si>
     <t xml:space="preserve">0.355736434459686</t>
@@ -1775,37 +1775,37 @@
     <t xml:space="preserve">0.370334684848785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38378044962883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376097142696381</t>
+    <t xml:space="preserve">0.383780479431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376097172498703</t>
   </si>
   <si>
     <t xml:space="preserve">0.376865476369858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377249628305435</t>
+    <t xml:space="preserve">0.377249658107758</t>
   </si>
   <si>
     <t xml:space="preserve">0.398762851953506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403372824192047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406446129083633</t>
+    <t xml:space="preserve">0.403372794389725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406446099281311</t>
   </si>
   <si>
     <t xml:space="preserve">0.409519463777542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39107957482338</t>
+    <t xml:space="preserve">0.391079545021057</t>
   </si>
   <si>
     <t xml:space="preserve">0.381475478410721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407214462757111</t>
+    <t xml:space="preserve">0.407214432954788</t>
   </si>
   <si>
     <t xml:space="preserve">0.387237906455994</t>
@@ -1817,22 +1817,22 @@
     <t xml:space="preserve">0.411824494600296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41489776968956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417202711105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397226214408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408751159906387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410287797451019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41412940621376</t>
+    <t xml:space="preserve">0.414897799491882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417202740907669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397226184606552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408751130104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410287767648697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414129436016083</t>
   </si>
   <si>
     <t xml:space="preserve">0.416434437036514</t>
@@ -1841,28 +1841,28 @@
     <t xml:space="preserve">0.418739408254623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420276075601578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421812742948532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430264383554459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473290771245956</t>
+    <t xml:space="preserve">0.420276045799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42181271314621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430264353752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473290830850601</t>
   </si>
   <si>
     <t xml:space="preserve">0.49480402469635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484047383069992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267357349396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506328940391541</t>
+    <t xml:space="preserve">0.484047412872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267416954041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506328999996185</t>
   </si>
   <si>
     <t xml:space="preserve">0.479437470436096</t>
@@ -1871,52 +1871,52 @@
     <t xml:space="preserve">0.48251074552536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475595831871033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070826768875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465607494115829</t>
+    <t xml:space="preserve">0.475595772266388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465607523918152</t>
   </si>
   <si>
     <t xml:space="preserve">0.460997551679611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434106051921844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789299249649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445630937814713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449472546577454</t>
+    <t xml:space="preserve">0.453314244747162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434106022119522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789269447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44563090801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449472576379776</t>
   </si>
   <si>
     <t xml:space="preserve">0.451009273529053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460229188203812</t>
+    <t xml:space="preserve">0.460229218006134</t>
   </si>
   <si>
     <t xml:space="preserve">0.454082578420639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45715594291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451777517795563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456387549638748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463302493095398</t>
+    <t xml:space="preserve">0.457155883312225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451777577400208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456387490034103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46330252289772</t>
   </si>
   <si>
     <t xml:space="preserve">0.470985800027847</t>
@@ -1928,19 +1928,19 @@
     <t xml:space="preserve">0.457924276590347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447167634963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43256938457489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437947660684586</t>
+    <t xml:space="preserve">0.447167694568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432569354772568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437947690486908</t>
   </si>
   <si>
     <t xml:space="preserve">0.433337688446045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434874296188354</t>
+    <t xml:space="preserve">0.434874325990677</t>
   </si>
   <si>
     <t xml:space="preserve">0.436411023139954</t>
@@ -1964,19 +1964,19 @@
     <t xml:space="preserve">0.485584110021591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455619186162949</t>
+    <t xml:space="preserve">0.455619215965271</t>
   </si>
   <si>
     <t xml:space="preserve">0.443325966596603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429496049880981</t>
+    <t xml:space="preserve">0.429496020078659</t>
   </si>
   <si>
     <t xml:space="preserve">0.435642659664154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450240910053253</t>
+    <t xml:space="preserve">0.450240939855576</t>
   </si>
   <si>
     <t xml:space="preserve">0.427191078662872</t>
@@ -1988,16 +1988,16 @@
     <t xml:space="preserve">0.386469602584839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393384605646133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365724712610245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372639685869217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351510643959045</t>
+    <t xml:space="preserve">0.393384575843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365724742412567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372639715671539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351510614156723</t>
   </si>
   <si>
     <t xml:space="preserve">0.342674851417542</t>
@@ -2012,22 +2012,22 @@
     <t xml:space="preserve">0.259695291519165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239334598183632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242023691534996</t>
+    <t xml:space="preserve">0.23933456838131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242023706436157</t>
   </si>
   <si>
     <t xml:space="preserve">0.234724581241608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24586533010006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258926928043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.251627802848816</t>
+    <t xml:space="preserve">0.245865389704704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25892698764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.251627832651138</t>
   </si>
   <si>
     <t xml:space="preserve">0.266610234975815</t>
@@ -2042,22 +2042,22 @@
     <t xml:space="preserve">0.251243650913239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252011984586716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242407888174057</t>
+    <t xml:space="preserve">0.252012014389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242407873272896</t>
   </si>
   <si>
     <t xml:space="preserve">0.245096996426582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254701137542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262000292539597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254316985607147</t>
+    <t xml:space="preserve">0.254701107740402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262000262737274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254316955804825</t>
   </si>
   <si>
     <t xml:space="preserve">0.261231929063797</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">0.264689445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271988540887833</t>
+    <t xml:space="preserve">0.271988570690155</t>
   </si>
   <si>
     <t xml:space="preserve">0.273909360170364</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">0.27275687456131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275446027517319</t>
+    <t xml:space="preserve">0.275446057319641</t>
   </si>
   <si>
     <t xml:space="preserve">0.268915235996246</t>
@@ -2090,28 +2090,28 @@
     <t xml:space="preserve">0.265841901302338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25854280591011</t>
+    <t xml:space="preserve">0.258542776107788</t>
   </si>
   <si>
     <t xml:space="preserve">0.26545774936676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263152748346329</t>
+    <t xml:space="preserve">0.263152807950974</t>
   </si>
   <si>
     <t xml:space="preserve">0.292733430862427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327692449092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302337527275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301953375339508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332302361726761</t>
+    <t xml:space="preserve">0.327692419290543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302337557077408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301953345537186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332302391529083</t>
   </si>
   <si>
     <t xml:space="preserve">0.332686543464661</t>
@@ -2120,10 +2120,10 @@
     <t xml:space="preserve">0.306179195642471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305026739835739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312325835227966</t>
+    <t xml:space="preserve">0.305026710033417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312325805425644</t>
   </si>
   <si>
     <t xml:space="preserve">0.331918209791183</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">0.326539933681488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292349249124527</t>
+    <t xml:space="preserve">0.292349278926849</t>
   </si>
   <si>
     <t xml:space="preserve">0.289275944232941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291196793317795</t>
+    <t xml:space="preserve">0.291196763515472</t>
   </si>
   <si>
     <t xml:space="preserve">0.286970943212509</t>
@@ -2150,16 +2150,16 @@
     <t xml:space="preserve">0.285050123929977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273525178432465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26084777712822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261616140604019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270067721605301</t>
+    <t xml:space="preserve">0.273525238037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260847747325897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261616110801697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270067751407623</t>
   </si>
   <si>
     <t xml:space="preserve">0.278519332408905</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">0.27314105629921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266994386911392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.255469441413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25316447019577</t>
+    <t xml:space="preserve">0.266994416713715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.255469471216202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253164499998093</t>
   </si>
   <si>
     <t xml:space="preserve">0.256621956825256</t>
@@ -2189,22 +2189,22 @@
     <t xml:space="preserve">0.236261248588562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.238182038068771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25354865193367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267762750387192</t>
+    <t xml:space="preserve">0.238182067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253548681735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267762720584869</t>
   </si>
   <si>
     <t xml:space="preserve">0.283513456583023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277750998735428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294654279947281</t>
+    <t xml:space="preserve">0.277750968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294654250144958</t>
   </si>
   <si>
     <t xml:space="preserve">0.319624960422516</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">0.343827307224274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338449031114578</t>
+    <t xml:space="preserve">0.338449001312256</t>
   </si>
   <si>
     <t xml:space="preserve">0.34075403213501</t>
@@ -2222,10 +2222,10 @@
     <t xml:space="preserve">0.338833212852478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338064849376678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336912333965302</t>
+    <t xml:space="preserve">0.338064879179001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336912363767624</t>
   </si>
   <si>
     <t xml:space="preserve">0.333839029073715</t>
@@ -2234,19 +2234,19 @@
     <t xml:space="preserve">0.330765724182129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328844904899597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33998566865921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34766897559166</t>
+    <t xml:space="preserve">0.32884493470192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339985698461533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347668945789337</t>
   </si>
   <si>
     <t xml:space="preserve">0.359962224960327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351894795894623</t>
+    <t xml:space="preserve">0.3518947660923</t>
   </si>
   <si>
     <t xml:space="preserve">0.369182199239731</t>
@@ -2261,10 +2261,10 @@
     <t xml:space="preserve">0.348053157329559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346516519784927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347284764051437</t>
+    <t xml:space="preserve">0.346516489982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34728479385376</t>
   </si>
   <si>
     <t xml:space="preserve">0.363419681787491</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">0.373792141675949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373023837804794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379554659128189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425654411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417971074581146</t>
+    <t xml:space="preserve">0.373023867607117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379554629325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42565444111824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417971104383469</t>
   </si>
   <si>
     <t xml:space="preserve">0.381859660148621</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">0.380322962999344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348437309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400299578905106</t>
+    <t xml:space="preserve">0.348437339067459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400299519300461</t>
   </si>
   <si>
     <t xml:space="preserve">0.383396297693253</t>
@@ -2327,22 +2327,22 @@
     <t xml:space="preserve">0.344595670700073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334223181009293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34190645813942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323466628789902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34036985039711</t>
+    <t xml:space="preserve">0.334223210811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341906517744064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323466569185257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340369820594788</t>
   </si>
   <si>
     <t xml:space="preserve">0.331149876117706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348821461200714</t>
+    <t xml:space="preserve">0.348821491003036</t>
   </si>
   <si>
     <t xml:space="preserve">0.322314113378525</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">0.337680697441101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345363944768906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341522336006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329229086637497</t>
+    <t xml:space="preserve">0.345363974571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341522306203842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329229056835175</t>
   </si>
   <si>
     <t xml:space="preserve">0.353653132915497</t>
@@ -2372,10 +2372,10 @@
     <t xml:space="preserve">0.35406482219696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352829724550247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347477555274963</t>
+    <t xml:space="preserve">0.352829694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347477585077286</t>
   </si>
   <si>
     <t xml:space="preserve">0.345830768346786</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">0.341713726520538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342537194490433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348300993442535</t>
+    <t xml:space="preserve">0.34253716468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348301023244858</t>
   </si>
   <si>
     <t xml:space="preserve">0.359828680753708</t>
@@ -2396,19 +2396,19 @@
     <t xml:space="preserve">0.353241413831711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35488823056221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350359499454498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345007359981537</t>
+    <t xml:space="preserve">0.354888260364532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350359469652176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345007389783859</t>
   </si>
   <si>
     <t xml:space="preserve">0.339655190706253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342948883771896</t>
+    <t xml:space="preserve">0.342948853969574</t>
   </si>
   <si>
     <t xml:space="preserve">0.341302007436752</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">0.312894493341446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31824666261673</t>
+    <t xml:space="preserve">0.318246632814407</t>
   </si>
   <si>
     <t xml:space="preserve">0.317834943532944</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">0.319481760263443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312071114778519</t>
+    <t xml:space="preserve">0.312071084976196</t>
   </si>
   <si>
     <t xml:space="preserve">0.308365762233734</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">0.314541310071945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318658351898193</t>
+    <t xml:space="preserve">0.318658322095871</t>
   </si>
   <si>
     <t xml:space="preserve">0.320305168628693</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">0.313306212425232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310424298048019</t>
+    <t xml:space="preserve">0.310424268245697</t>
   </si>
   <si>
     <t xml:space="preserve">0.314952999353409</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">0.31742325425148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311659395694733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316188097000122</t>
+    <t xml:space="preserve">0.31165936589241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316188126802444</t>
   </si>
   <si>
     <t xml:space="preserve">0.319893479347229</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">0.303013622760773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307542324066162</t>
+    <t xml:space="preserve">0.307542353868484</t>
   </si>
   <si>
     <t xml:space="preserve">0.302601933479309</t>
@@ -2540,19 +2540,19 @@
     <t xml:space="preserve">0.307954043149948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306307256221771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301778525114059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303837031126022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300955086946487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301366806030273</t>
+    <t xml:space="preserve">0.306307286024094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301778495311737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3038370013237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30095511674881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301366776227951</t>
   </si>
   <si>
     <t xml:space="preserve">0.302190244197845</t>
@@ -2564,25 +2564,25 @@
     <t xml:space="preserve">0.326480716466904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328539252281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340890318155289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356535047292709</t>
+    <t xml:space="preserve">0.328539222478867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340890347957611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356535077095032</t>
   </si>
   <si>
     <t xml:space="preserve">0.343360543251038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336361587047577</t>
+    <t xml:space="preserve">0.336361557245255</t>
   </si>
   <si>
     <t xml:space="preserve">0.339243531227112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335126519203186</t>
+    <t xml:space="preserve">0.335126489400864</t>
   </si>
   <si>
     <t xml:space="preserve">0.358181864023209</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">0.337596714496613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340066909790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340478599071503</t>
+    <t xml:space="preserve">0.340066879987717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340478628873825</t>
   </si>
   <si>
     <t xml:space="preserve">0.332244545221329</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">0.325657308101654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338420122861862</t>
+    <t xml:space="preserve">0.338420152664185</t>
   </si>
   <si>
     <t xml:space="preserve">0.346654146909714</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">0.381648927927017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3902947306633</t>
+    <t xml:space="preserve">0.390294700860977</t>
   </si>
   <si>
     <t xml:space="preserve">0.395235151052475</t>
@@ -2675,25 +2675,25 @@
     <t xml:space="preserve">0.403469234704971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409644812345505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408409655094147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40593945980072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406351178884506</t>
+    <t xml:space="preserve">0.409644782543182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408409625291824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405939429998398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406351149082184</t>
   </si>
   <si>
     <t xml:space="preserve">0.400175601243973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397705376148224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403880923986435</t>
+    <t xml:space="preserve">0.397705405950546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403880953788757</t>
   </si>
   <si>
     <t xml:space="preserve">0.403057545423508</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">0.433111846446991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430641651153564</t>
+    <t xml:space="preserve">0.430641621351242</t>
   </si>
   <si>
     <t xml:space="preserve">0.441345930099487</t>
@@ -2717,22 +2717,22 @@
     <t xml:space="preserve">0.454520434141159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442992717027664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488280028104782</t>
+    <t xml:space="preserve">0.442992746829987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488280087709427</t>
   </si>
   <si>
     <t xml:space="preserve">0.50392484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534390866756439</t>
+    <t xml:space="preserve">0.534390926361084</t>
   </si>
   <si>
     <t xml:space="preserve">0.518746137619019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522039771080017</t>
+    <t xml:space="preserve">0.522039830684662</t>
   </si>
   <si>
     <t xml:space="preserve">0.500631213188171</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">0.46934175491333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485809862613678</t>
+    <t xml:space="preserve">0.485809922218323</t>
   </si>
   <si>
     <t xml:space="preserve">0.462754487991333</t>
@@ -2756,25 +2756,22 @@
     <t xml:space="preserve">0.493220597505569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49157378077507</t>
+    <t xml:space="preserve">0.491573721170425</t>
   </si>
   <si>
     <t xml:space="preserve">0.48169282078743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467694997787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460884332657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461107671260834</t>
+    <t xml:space="preserve">0.467694967985153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461107701063156</t>
   </si>
   <si>
     <t xml:space="preserve">0.476752400398254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47922271490097</t>
+    <t xml:space="preserve">0.479222685098648</t>
   </si>
   <si>
     <t xml:space="preserve">0.477575808763504</t>
@@ -2786,7 +2783,7 @@
     <t xml:space="preserve">0.504748165607452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501454532146454</t>
+    <t xml:space="preserve">0.501454591751099</t>
   </si>
   <si>
     <t xml:space="preserve">0.498984396457672</t>
@@ -2801,7 +2798,7 @@
     <t xml:space="preserve">0.490750372409821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484986454248428</t>
+    <t xml:space="preserve">0.484986484050751</t>
   </si>
   <si>
     <t xml:space="preserve">0.49239718914032</t>
@@ -2810,13 +2807,13 @@
     <t xml:space="preserve">0.482516288757324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478399246931076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473458766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470988661050797</t>
+    <t xml:space="preserve">0.478399276733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473458796739578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470988631248474</t>
   </si>
   <si>
     <t xml:space="preserve">0.470165193080902</t>
@@ -2828,13 +2825,13 @@
     <t xml:space="preserve">0.460284292697906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46851834654808</t>
+    <t xml:space="preserve">0.468518376350403</t>
   </si>
   <si>
     <t xml:space="preserve">0.466750383377075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473822325468063</t>
+    <t xml:space="preserve">0.473822385072708</t>
   </si>
   <si>
     <t xml:space="preserve">0.457910388708115</t>
@@ -2849,7 +2846,7 @@
     <t xml:space="preserve">0.454374402761459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44111442565918</t>
+    <t xml:space="preserve">0.441114455461502</t>
   </si>
   <si>
     <t xml:space="preserve">0.420782536268234</t>
@@ -2864,22 +2861,22 @@
     <t xml:space="preserve">0.427412509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426528453826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433158487081528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448186457157135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441998451948166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434484481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44465047121048</t>
+    <t xml:space="preserve">0.426528483629227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433158457279205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448186427354813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441998422145844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434484452009201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444650441408157</t>
   </si>
   <si>
     <t xml:space="preserve">0.449070423841476</t>
@@ -2888,31 +2885,31 @@
     <t xml:space="preserve">0.437578439712524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433600425720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430948466062546</t>
+    <t xml:space="preserve">0.433600455522537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430948495864868</t>
   </si>
   <si>
     <t xml:space="preserve">0.431390464305878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434926480054855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429622501134872</t>
+    <t xml:space="preserve">0.434926509857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42962247133255</t>
   </si>
   <si>
     <t xml:space="preserve">0.428738474845886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424318492412567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434042453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421666502952576</t>
+    <t xml:space="preserve">0.424318462610245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434042483568192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421666532754898</t>
   </si>
   <si>
     <t xml:space="preserve">0.430506467819214</t>
@@ -2921,13 +2918,13 @@
     <t xml:space="preserve">0.427854478359222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419456541538239</t>
+    <t xml:space="preserve">0.419456511735916</t>
   </si>
   <si>
     <t xml:space="preserve">0.417246520519257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411942571401596</t>
+    <t xml:space="preserve">0.411942541599274</t>
   </si>
   <si>
     <t xml:space="preserve">0.414152532815933</t>
@@ -2960,10 +2957,10 @@
     <t xml:space="preserve">0.413268536329269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415920525789261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408406525850296</t>
+    <t xml:space="preserve">0.415920555591583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408406555652618</t>
   </si>
   <si>
     <t xml:space="preserve">0.412384539842606</t>
@@ -2975,19 +2972,19 @@
     <t xml:space="preserve">0.409732550382614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409290581941605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407964557409286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423434495925903</t>
+    <t xml:space="preserve">0.409290552139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407964527606964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423434525728226</t>
   </si>
   <si>
     <t xml:space="preserve">0.42034050822258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426086455583572</t>
+    <t xml:space="preserve">0.426086485385895</t>
   </si>
   <si>
     <t xml:space="preserve">0.428296476602554</t>
@@ -2996,13 +2993,13 @@
     <t xml:space="preserve">0.424760520458221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422108501195908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415478527545929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402218610048294</t>
+    <t xml:space="preserve">0.422108471393585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415478497743607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402218580245972</t>
   </si>
   <si>
     <t xml:space="preserve">0.394262611865997</t>
@@ -3020,19 +3017,19 @@
     <t xml:space="preserve">0.396030604839325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405754536390305</t>
+    <t xml:space="preserve">0.405754566192627</t>
   </si>
   <si>
     <t xml:space="preserve">0.403544545173645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400450617074966</t>
+    <t xml:space="preserve">0.400450587272644</t>
   </si>
   <si>
     <t xml:space="preserve">0.389842629432678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388958632946014</t>
+    <t xml:space="preserve">0.388958662748337</t>
   </si>
   <si>
     <t xml:space="preserve">0.395146608352661</t>
@@ -3041,7 +3038,7 @@
     <t xml:space="preserve">0.386748641729355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393378585577011</t>
+    <t xml:space="preserve">0.393378615379333</t>
   </si>
   <si>
     <t xml:space="preserve">0.403102576732635</t>
@@ -3068,7 +3065,7 @@
     <t xml:space="preserve">0.436694473028183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443766385316849</t>
+    <t xml:space="preserve">0.443766415119171</t>
   </si>
   <si>
     <t xml:space="preserve">0.453789889812469</t>
@@ -3098,10 +3095,10 @@
     <t xml:space="preserve">0.468369513750076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480215400457382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482949018478394</t>
+    <t xml:space="preserve">0.480215430259705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482949048280716</t>
   </si>
   <si>
     <t xml:space="preserve">0.481126666069031</t>
@@ -3125,10 +3122,10 @@
     <t xml:space="preserve">0.523042976856232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529421508312225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52577668428421</t>
+    <t xml:space="preserve">0.529421448707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525776624679565</t>
   </si>
   <si>
     <t xml:space="preserve">0.523954212665558</t>
@@ -3143,40 +3140,40 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753209590912</t>
+    <t xml:space="preserve">0.515753149986267</t>
   </si>
   <si>
     <t xml:space="preserve">0.507552146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511197090148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514841914176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519398033618927</t>
+    <t xml:space="preserve">0.511197030544281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514841973781586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519398093223572</t>
   </si>
   <si>
     <t xml:space="preserve">0.513930678367615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524865388870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509374558925629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526687920093536</t>
+    <t xml:space="preserve">0.524865448474884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509374618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526687860488892</t>
   </si>
   <si>
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267454624176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546734869480133</t>
+    <t xml:space="preserve">0.541267395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546734809875488</t>
   </si>
   <si>
     <t xml:space="preserve">0.537622511386871</t>
@@ -3197,10 +3194,10 @@
     <t xml:space="preserve">0.569515407085419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565870463848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562225639820099</t>
+    <t xml:space="preserve">0.565870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562225580215454</t>
   </si>
   <si>
     <t xml:space="preserve">0.551290929317474</t>
@@ -3209,13 +3206,13 @@
     <t xml:space="preserve">0.548557281494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550379633903503</t>
+    <t xml:space="preserve">0.550379693508148</t>
   </si>
   <si>
     <t xml:space="preserve">0.547646045684814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55584704875946</t>
+    <t xml:space="preserve">0.555847108364105</t>
   </si>
   <si>
     <t xml:space="preserve">0.553113341331482</t>
@@ -3227,22 +3224,22 @@
     <t xml:space="preserve">0.559491991996765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561314344406128</t>
+    <t xml:space="preserve">0.561314404010773</t>
   </si>
   <si>
     <t xml:space="preserve">0.558580696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556758284568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542178750038147</t>
+    <t xml:space="preserve">0.556758224964142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542178690433502</t>
   </si>
   <si>
     <t xml:space="preserve">0.557669520378113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534888863563538</t>
+    <t xml:space="preserve">0.534888923168182</t>
   </si>
   <si>
     <t xml:space="preserve">0.528510332107544</t>
@@ -3251,7 +3248,7 @@
     <t xml:space="preserve">0.535800099372864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530332744121552</t>
+    <t xml:space="preserve">0.530332803726196</t>
   </si>
   <si>
     <t xml:space="preserve">0.527599096298218</t>
@@ -3263,7 +3260,7 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617496013641</t>
+    <t xml:space="preserve">0.496617466211319</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
@@ -3272,7 +3269,7 @@
     <t xml:space="preserve">0.505729734897614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494794994592667</t>
+    <t xml:space="preserve">0.494794964790344</t>
   </si>
   <si>
     <t xml:space="preserve">0.499351114034653</t>
@@ -3284,16 +3281,16 @@
     <t xml:space="preserve">0.492061376571655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488416433334351</t>
+    <t xml:space="preserve">0.488416492938995</t>
   </si>
   <si>
     <t xml:space="preserve">0.483860343694687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487505257129669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495706230401993</t>
+    <t xml:space="preserve">0.487505227327347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495706290006638</t>
   </si>
   <si>
     <t xml:space="preserve">0.49388375878334</t>
@@ -52272,7 +52269,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1845" t="s">
-        <v>917</v>
+        <v>363</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52298,7 +52295,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1846" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52324,7 +52321,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52376,7 +52373,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1849" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52402,7 +52399,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1850" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52428,7 +52425,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1851" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52480,7 +52477,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1853" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52506,7 +52503,7 @@
         <v>0.612999975681305</v>
       </c>
       <c r="G1854" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52532,7 +52529,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G1855" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52558,7 +52555,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1856" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52584,7 +52581,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1857" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52610,7 +52607,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1858" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52636,7 +52633,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1859" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52662,7 +52659,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G1860" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52688,7 +52685,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1861" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52714,7 +52711,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1862" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52740,7 +52737,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1863" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52766,7 +52763,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G1864" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52792,7 +52789,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G1865" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52818,7 +52815,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1866" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52870,7 +52867,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1868" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52922,7 +52919,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1870" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -52974,7 +52971,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53026,7 +53023,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1874" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53052,7 +53049,7 @@
         <v>0.570999979972839</v>
       </c>
       <c r="G1875" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53078,7 +53075,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>917</v>
+        <v>363</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53104,7 +53101,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1877" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53130,7 +53127,7 @@
         <v>0.559000015258789</v>
       </c>
       <c r="G1878" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53156,7 +53153,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G1879" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53182,7 +53179,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G1880" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53208,7 +53205,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1881" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53234,7 +53231,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1882" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53260,7 +53257,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G1883" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53286,7 +53283,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1884" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53312,7 +53309,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1885" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53338,7 +53335,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G1886" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53364,7 +53361,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1887" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53390,7 +53387,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1888" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53416,7 +53413,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1889" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53442,7 +53439,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53468,7 +53465,7 @@
         <v>0.482499986886978</v>
       </c>
       <c r="G1891" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -53494,7 +53491,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1892" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -53520,7 +53517,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1893" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -53546,7 +53543,7 @@
         <v>0.5</v>
       </c>
       <c r="G1894" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -53572,7 +53569,7 @@
         <v>0.491499990224838</v>
       </c>
       <c r="G1895" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -53598,7 +53595,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G1896" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53624,7 +53621,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G1897" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53650,7 +53647,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G1898" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53676,7 +53673,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1899" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53702,7 +53699,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G1900" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53728,7 +53725,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1901" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53754,7 +53751,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1902" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53780,7 +53777,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1903" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -53806,7 +53803,7 @@
         <v>0.482499986886978</v>
       </c>
       <c r="G1904" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53832,7 +53829,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53858,7 +53855,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1906" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -53884,7 +53881,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1907" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -53910,7 +53907,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G1908" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -53936,7 +53933,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G1909" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53962,7 +53959,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1910" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53988,7 +53985,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G1911" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -54014,7 +54011,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G1912" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54040,7 +54037,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G1913" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -54066,7 +54063,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1914" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54092,7 +54089,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1915" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54118,7 +54115,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G1916" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -54144,7 +54141,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1917" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54170,7 +54167,7 @@
         <v>0.465999990701675</v>
       </c>
       <c r="G1918" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54196,7 +54193,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G1919" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54222,7 +54219,7 @@
         <v>0.46849998831749</v>
       </c>
       <c r="G1920" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54248,7 +54245,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1921" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54274,7 +54271,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1922" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54300,7 +54297,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G1923" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54326,7 +54323,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1924" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54352,7 +54349,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G1925" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54378,7 +54375,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1926" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54404,7 +54401,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G1927" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54430,7 +54427,7 @@
         <v>0.478500008583069</v>
       </c>
       <c r="G1928" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -54456,7 +54453,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G1929" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54482,7 +54479,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G1930" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54508,7 +54505,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1931" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54534,7 +54531,7 @@
         <v>0.476500004529953</v>
       </c>
       <c r="G1932" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54560,7 +54557,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1933" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54586,7 +54583,7 @@
         <v>0.470499992370605</v>
       </c>
       <c r="G1934" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54612,7 +54609,7 @@
         <v>0.46849998831749</v>
       </c>
       <c r="G1935" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54638,7 +54635,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1936" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54664,7 +54661,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G1937" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54690,7 +54687,7 @@
         <v>0.466500014066696</v>
       </c>
       <c r="G1938" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54716,7 +54713,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1939" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54742,7 +54739,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1940" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54768,7 +54765,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G1941" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54794,7 +54791,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G1942" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54820,7 +54817,7 @@
         <v>0.461499989032745</v>
       </c>
       <c r="G1943" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54846,7 +54843,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G1944" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54872,7 +54869,7 @@
         <v>0.482499986886978</v>
       </c>
       <c r="G1945" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54898,7 +54895,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1946" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54924,7 +54921,7 @@
         <v>0.475499987602234</v>
       </c>
       <c r="G1947" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54950,7 +54947,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1948" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54976,7 +54973,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1949" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -55002,7 +54999,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1950" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -55028,7 +55025,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G1951" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -55054,7 +55051,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G1952" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -55080,7 +55077,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G1953" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -55106,7 +55103,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1954" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -55132,7 +55129,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G1955" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55158,7 +55155,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1956" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55184,7 +55181,7 @@
         <v>0.480500012636185</v>
       </c>
       <c r="G1957" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -55210,7 +55207,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1958" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -55236,7 +55233,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1959" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -55262,7 +55259,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G1960" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -55288,7 +55285,7 @@
         <v>0.47749999165535</v>
       </c>
       <c r="G1961" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55314,7 +55311,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1962" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55340,7 +55337,7 @@
         <v>0.465999990701675</v>
       </c>
       <c r="G1963" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -55366,7 +55363,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G1964" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55392,7 +55389,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1965" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55418,7 +55415,7 @@
         <v>0.452499985694885</v>
       </c>
       <c r="G1966" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55444,7 +55441,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55470,7 +55467,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G1968" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -55496,7 +55493,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G1969" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55522,7 +55519,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1970" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55548,7 +55545,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1971" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -55574,7 +55571,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1972" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55600,7 +55597,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G1973" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55626,7 +55623,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G1974" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55652,7 +55649,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G1975" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55678,7 +55675,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1976" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55704,7 +55701,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1977" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55730,7 +55727,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G1978" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55756,7 +55753,7 @@
         <v>0.4375</v>
       </c>
       <c r="G1979" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55782,7 +55779,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1980" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55808,7 +55805,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1981" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55834,7 +55831,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G1982" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55860,7 +55857,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1983" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55886,7 +55883,7 @@
         <v>0.453999996185303</v>
       </c>
       <c r="G1984" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55912,7 +55909,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1985" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55938,7 +55935,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1986" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55964,7 +55961,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1987" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55990,7 +55987,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1988" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56016,7 +56013,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1989" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56042,7 +56039,7 @@
         <v>0.454499989748001</v>
       </c>
       <c r="G1990" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -56068,7 +56065,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1991" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56094,7 +56091,7 @@
         <v>0.465999990701675</v>
       </c>
       <c r="G1992" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -56120,7 +56117,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1993" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -56146,7 +56143,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G1994" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56172,7 +56169,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1995" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56198,7 +56195,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G1996" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56224,7 +56221,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1997" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56250,7 +56247,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1998" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56276,7 +56273,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1999" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56302,7 +56299,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G2000" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56328,7 +56325,7 @@
         <v>0.476500004529953</v>
       </c>
       <c r="G2001" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56354,7 +56351,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G2002" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56380,7 +56377,7 @@
         <v>0.466500014066696</v>
       </c>
       <c r="G2003" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56406,7 +56403,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2004" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56432,7 +56429,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2005" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56458,7 +56455,7 @@
         <v>0.5</v>
       </c>
       <c r="G2006" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56484,7 +56481,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G2007" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56510,7 +56507,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2008" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56536,7 +56533,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2009" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56562,7 +56559,7 @@
         <v>0.497000008821487</v>
       </c>
       <c r="G2010" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56588,7 +56585,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G2011" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56614,7 +56611,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2012" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56640,7 +56637,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G2013" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56666,7 +56663,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2014" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56692,7 +56689,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G2015" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56718,7 +56715,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G2016" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56744,7 +56741,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2017" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56770,7 +56767,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2018" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -56796,7 +56793,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G2019" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56822,7 +56819,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G2020" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56848,7 +56845,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2021" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56874,7 +56871,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2022" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56900,7 +56897,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G2023" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56926,7 +56923,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G2024" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56952,7 +56949,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2025" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56978,7 +56975,7 @@
         <v>0.521000027656555</v>
       </c>
       <c r="G2026" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57004,7 +57001,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2027" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57030,7 +57027,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2028" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57056,7 +57053,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2029" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -57082,7 +57079,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2030" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57108,7 +57105,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G2031" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57134,7 +57131,7 @@
         <v>0.577000021934509</v>
       </c>
       <c r="G2032" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57160,7 +57157,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G2033" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57186,7 +57183,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2034" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57212,7 +57209,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G2035" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57238,7 +57235,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G2036" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -57264,7 +57261,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2037" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57290,7 +57287,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G2038" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57316,7 +57313,7 @@
         <v>0.560999989509583</v>
       </c>
       <c r="G2039" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57342,7 +57339,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G2040" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57368,7 +57365,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2041" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57394,7 +57391,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2042" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57420,7 +57417,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2043" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57446,7 +57443,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2044" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57472,7 +57469,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2045" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57498,7 +57495,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2046" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -57524,7 +57521,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2047" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -57550,7 +57547,7 @@
         <v>0.560999989509583</v>
       </c>
       <c r="G2048" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -57576,7 +57573,7 @@
         <v>0.559000015258789</v>
       </c>
       <c r="G2049" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -57602,7 +57599,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2050" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -57628,7 +57625,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2051" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -57654,7 +57651,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2052" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57680,7 +57677,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2053" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57706,7 +57703,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2054" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57732,7 +57729,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2055" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -57758,7 +57755,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2056" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -57784,7 +57781,7 @@
         <v>0.602999985218048</v>
       </c>
       <c r="G2057" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57810,7 +57807,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G2058" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57836,7 +57833,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2059" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57862,7 +57859,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2060" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57888,7 +57885,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2061" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -57914,7 +57911,7 @@
         <v>0.625</v>
       </c>
       <c r="G2062" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57940,7 +57937,7 @@
         <v>0.620999991893768</v>
       </c>
       <c r="G2063" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57966,7 +57963,7 @@
         <v>0.616999983787537</v>
       </c>
       <c r="G2064" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57992,7 +57989,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G2065" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58018,7 +58015,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2066" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58044,7 +58041,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2067" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58070,7 +58067,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G2068" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58096,7 +58093,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2069" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58122,7 +58119,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2070" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -58148,7 +58145,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2071" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58174,7 +58171,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2072" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58200,7 +58197,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G2073" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58226,7 +58223,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2074" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -58252,7 +58249,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G2075" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58278,7 +58275,7 @@
         <v>0.619000017642975</v>
       </c>
       <c r="G2076" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -58304,7 +58301,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2077" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -58330,7 +58327,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2078" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -58356,7 +58353,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2079" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -58382,7 +58379,7 @@
         <v>0.612999975681305</v>
       </c>
       <c r="G2080" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58408,7 +58405,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G2081" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -58434,7 +58431,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G2082" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58460,7 +58457,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G2083" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -58486,7 +58483,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2084" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58512,7 +58509,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G2085" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58538,7 +58535,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2086" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58564,7 +58561,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2087" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -58590,7 +58587,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2088" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58616,7 +58613,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G2089" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -58642,7 +58639,7 @@
         <v>0.577000021934509</v>
       </c>
       <c r="G2090" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -58668,7 +58665,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G2091" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58694,7 +58691,7 @@
         <v>0.566999971866608</v>
       </c>
       <c r="G2092" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58720,7 +58717,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2093" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -58746,7 +58743,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G2094" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58772,7 +58769,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G2095" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58798,7 +58795,7 @@
         <v>0.546999990940094</v>
       </c>
       <c r="G2096" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58824,7 +58821,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G2097" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58850,7 +58847,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G2098" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58876,7 +58873,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2099" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -58902,7 +58899,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G2100" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -58928,7 +58925,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G2101" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -58954,7 +58951,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2102" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58980,7 +58977,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2103" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59006,7 +59003,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2104" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59032,7 +59029,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2105" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59058,7 +59055,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G2106" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59084,7 +59081,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2107" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59110,7 +59107,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2108" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59136,7 +59133,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2109" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59162,7 +59159,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G2110" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59188,7 +59185,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2111" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59214,7 +59211,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2112" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59240,7 +59237,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2113" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59266,7 +59263,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G2114" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -59292,7 +59289,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G2115" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -59318,7 +59315,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2116" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -59344,7 +59341,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2117" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -59370,7 +59367,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2118" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59396,7 +59393,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2119" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59422,7 +59419,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G2120" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59448,7 +59445,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2121" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59474,7 +59471,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2122" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59500,7 +59497,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2123" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59526,7 +59523,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2124" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59552,7 +59549,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2125" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59578,7 +59575,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2126" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59604,7 +59601,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2127" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59630,7 +59627,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G2128" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59656,7 +59653,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G2129" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59682,7 +59679,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G2130" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59708,7 +59705,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2131" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59734,7 +59731,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2132" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59760,7 +59757,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2133" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59786,7 +59783,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2134" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59812,7 +59809,7 @@
         <v>0.49549999833107</v>
       </c>
       <c r="G2135" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59838,7 +59835,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G2136" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59864,7 +59861,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G2137" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59890,7 +59887,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G2138" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59916,7 +59913,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2139" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59942,7 +59939,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G2140" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59968,7 +59965,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G2141" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59994,7 +59991,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G2142" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60020,7 +60017,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G2143" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60046,7 +60043,7 @@
         <v>0.492500007152557</v>
       </c>
       <c r="G2144" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60072,7 +60069,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G2145" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60098,7 +60095,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2146" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60124,7 +60121,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G2147" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60150,7 +60147,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G2148" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60176,7 +60173,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G2149" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60202,7 +60199,7 @@
         <v>0.471500009298325</v>
       </c>
       <c r="G2150" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60228,7 +60225,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G2151" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60254,7 +60251,7 @@
         <v>0.458499997854233</v>
       </c>
       <c r="G2152" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60280,7 +60277,7 @@
         <v>0.452499985694885</v>
       </c>
       <c r="G2153" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60306,7 +60303,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2154" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60332,7 +60329,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G2155" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60358,7 +60355,7 @@
         <v>0.461499989032745</v>
       </c>
       <c r="G2156" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60384,7 +60381,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2157" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60410,7 +60407,7 @@
         <v>0.465499997138977</v>
       </c>
       <c r="G2158" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60436,7 +60433,7 @@
         <v>0.462500005960464</v>
       </c>
       <c r="G2159" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60462,7 +60459,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2160" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60488,7 +60485,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G2161" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60514,7 +60511,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G2162" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60540,7 +60537,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2163" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60566,7 +60563,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G2164" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60592,7 +60589,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G2165" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60618,7 +60615,7 @@
         <v>0.462500005960464</v>
       </c>
       <c r="G2166" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60644,7 +60641,7 @@
         <v>0.458499997854233</v>
       </c>
       <c r="G2167" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60670,7 +60667,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G2168" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60696,7 +60693,7 @@
         <v>0.459500014781952</v>
       </c>
       <c r="G2169" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60722,7 +60719,7 @@
         <v>0.453500002622604</v>
       </c>
       <c r="G2170" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60748,7 +60745,7 @@
         <v>0.454499989748001</v>
       </c>
       <c r="G2171" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60774,7 +60771,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G2172" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60800,7 +60797,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G2173" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60826,7 +60823,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G2174" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60852,7 +60849,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G2175" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60878,7 +60875,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2176" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60904,7 +60901,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2177" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60930,7 +60927,7 @@
         <v>0.475499987602234</v>
       </c>
       <c r="G2178" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60956,7 +60953,7 @@
         <v>0.476500004529953</v>
       </c>
       <c r="G2179" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60982,7 +60979,7 @@
         <v>0.46849998831749</v>
       </c>
       <c r="G2180" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61008,7 +61005,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G2181" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61034,7 +61031,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G2182" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61060,7 +61057,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G2183" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61086,7 +61083,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G2184" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61112,7 +61109,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G2185" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61138,7 +61135,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G2186" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61164,7 +61161,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2187" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61190,7 +61187,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G2188" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61216,7 +61213,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G2189" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61242,7 +61239,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G2190" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61268,7 +61265,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G2191" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61294,7 +61291,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2192" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61320,7 +61317,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2193" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61346,7 +61343,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2194" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61372,7 +61369,7 @@
         <v>0.546999990940094</v>
       </c>
       <c r="G2195" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61398,7 +61395,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2196" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61424,7 +61421,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G2197" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61450,7 +61447,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2198" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61476,7 +61473,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2199" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61502,7 +61499,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G2200" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61528,7 +61525,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2201" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61554,7 +61551,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2202" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61580,7 +61577,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G2203" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61606,7 +61603,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2204" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61632,7 +61629,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2205" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61658,7 +61655,7 @@
         <v>0.583000004291534</v>
       </c>
       <c r="G2206" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61684,7 +61681,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G2207" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61710,7 +61707,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2208" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61736,7 +61733,7 @@
         <v>0.577000021934509</v>
       </c>
       <c r="G2209" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61762,7 +61759,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G2210" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61788,7 +61785,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2211" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61814,7 +61811,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2212" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61840,7 +61837,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2213" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61866,7 +61863,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G2214" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61892,7 +61889,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2215" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61918,7 +61915,7 @@
         <v>0.560999989509583</v>
       </c>
       <c r="G2216" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61944,7 +61941,7 @@
         <v>0.560999989509583</v>
       </c>
       <c r="G2217" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61970,7 +61967,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G2218" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61996,7 +61993,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2219" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62022,7 +62019,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G2220" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62048,7 +62045,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G2221" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -62074,7 +62071,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2222" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62100,7 +62097,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2223" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62126,7 +62123,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G2224" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62152,7 +62149,7 @@
         <v>0.560999989509583</v>
       </c>
       <c r="G2225" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62178,7 +62175,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2226" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62204,7 +62201,7 @@
         <v>0.566999971866608</v>
       </c>
       <c r="G2227" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62230,7 +62227,7 @@
         <v>0.573000013828278</v>
       </c>
       <c r="G2228" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62256,7 +62253,7 @@
         <v>0.566999971866608</v>
       </c>
       <c r="G2229" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62282,7 +62279,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2230" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62308,7 +62305,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2231" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62334,7 +62331,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2232" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62360,7 +62357,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2233" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62386,7 +62383,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G2234" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62412,7 +62409,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G2235" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62438,7 +62435,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2236" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62464,7 +62461,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G2237" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62490,7 +62487,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G2238" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62516,7 +62513,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2239" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62542,7 +62539,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G2240" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62568,7 +62565,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2241" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62594,7 +62591,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G2242" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62620,7 +62617,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2243" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62646,7 +62643,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2244" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62672,7 +62669,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2245" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62698,7 +62695,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G2246" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62724,7 +62721,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G2247" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62750,7 +62747,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2248" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62776,7 +62773,7 @@
         <v>0.521000027656555</v>
       </c>
       <c r="G2249" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62802,7 +62799,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2250" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62828,7 +62825,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2251" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62854,7 +62851,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2252" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62880,7 +62877,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2253" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62906,7 +62903,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G2254" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62932,7 +62929,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2255" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62958,7 +62955,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G2256" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62984,7 +62981,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2257" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63010,7 +63007,7 @@
         <v>0.5</v>
       </c>
       <c r="G2258" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63036,7 +63033,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G2259" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63062,7 +63059,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G2260" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63088,7 +63085,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G2261" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63114,7 +63111,7 @@
         <v>0.494500011205673</v>
       </c>
       <c r="G2262" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63140,7 +63137,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G2263" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63166,7 +63163,7 @@
         <v>0.47350001335144</v>
       </c>
       <c r="G2264" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63192,7 +63189,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2265" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63218,7 +63215,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G2266" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63244,7 +63241,7 @@
         <v>0.475499987602234</v>
       </c>
       <c r="G2267" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63270,7 +63267,7 @@
         <v>0.478500008583069</v>
       </c>
       <c r="G2268" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63296,7 +63293,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2269" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63322,7 +63319,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G2270" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63348,7 +63345,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G2271" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63374,7 +63371,7 @@
         <v>0.478500008583069</v>
       </c>
       <c r="G2272" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63400,7 +63397,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2273" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63426,7 +63423,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G2274" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63452,7 +63449,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G2275" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63478,7 +63475,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2276" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63504,7 +63501,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2277" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63530,7 +63527,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2278" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63556,7 +63553,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2279" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63582,7 +63579,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G2280" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63608,7 +63605,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2281" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63634,7 +63631,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G2282" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63660,7 +63657,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G2283" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63686,7 +63683,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G2284" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63712,7 +63709,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G2285" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63738,7 +63735,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G2286" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63764,7 +63761,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G2287" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63790,7 +63787,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2288" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63816,7 +63813,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G2289" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63842,7 +63839,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G2290" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63868,7 +63865,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2291" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63894,7 +63891,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2292" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63920,7 +63917,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G2293" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63946,7 +63943,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2294" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63972,7 +63969,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2295" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63998,7 +63995,7 @@
         <v>0.521000027656555</v>
       </c>
       <c r="G2296" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64024,7 +64021,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2297" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64050,7 +64047,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G2298" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64076,7 +64073,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G2299" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64102,7 +64099,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2300" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64128,7 +64125,7 @@
         <v>0.5</v>
       </c>
       <c r="G2301" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64154,7 +64151,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2302" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64180,7 +64177,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G2303" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64206,7 +64203,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G2304" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64232,7 +64229,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G2305" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64258,7 +64255,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2306" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64284,7 +64281,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G2307" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64310,7 +64307,7 @@
         <v>0.497000008821487</v>
       </c>
       <c r="G2308" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64336,7 +64333,7 @@
         <v>0.5</v>
       </c>
       <c r="G2309" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64362,7 +64359,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G2310" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64388,7 +64385,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2311" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64414,7 +64411,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G2312" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64440,7 +64437,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G2313" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64466,7 +64463,7 @@
         <v>0.5</v>
       </c>
       <c r="G2314" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64492,7 +64489,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G2315" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64518,7 +64515,7 @@
         <v>0.497000008821487</v>
       </c>
       <c r="G2316" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64544,7 +64541,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G2317" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64570,7 +64567,7 @@
         <v>0.488999992609024</v>
       </c>
       <c r="G2318" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64596,7 +64593,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2319" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64622,7 +64619,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G2320" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64648,7 +64645,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G2321" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64674,7 +64671,7 @@
         <v>0.5</v>
       </c>
       <c r="G2322" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64700,7 +64697,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2323" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64726,7 +64723,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G2324" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64752,7 +64749,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2325" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64778,7 +64775,7 @@
         <v>0.573000013828278</v>
       </c>
       <c r="G2326" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64804,7 +64801,7 @@
         <v>0.559000015258789</v>
       </c>
       <c r="G2327" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64830,7 +64827,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2328" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64856,7 +64853,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2329" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64882,7 +64879,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2330" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64908,7 +64905,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2331" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64934,7 +64931,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2332" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64960,7 +64957,7 @@
         <v>0.577000021934509</v>
       </c>
       <c r="G2333" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64986,7 +64983,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G2334" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65012,7 +65009,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2335" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65038,7 +65035,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G2336" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65064,7 +65061,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2337" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65090,7 +65087,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2338" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65116,7 +65113,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2339" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65142,7 +65139,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2340" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65168,7 +65165,7 @@
         <v>0.583000004291534</v>
       </c>
       <c r="G2341" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65194,7 +65191,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2342" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65220,7 +65217,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G2343" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65246,7 +65243,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2344" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65272,7 +65269,7 @@
         <v>0.573000013828278</v>
       </c>
       <c r="G2345" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65298,7 +65295,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G2346" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65324,7 +65321,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2347" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65350,7 +65347,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2348" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65376,7 +65373,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2349" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65402,7 +65399,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G2350" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65428,7 +65425,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G2351" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65454,7 +65451,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G2352" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65480,7 +65477,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2353" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65506,7 +65503,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2354" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65532,7 +65529,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G2355" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65558,7 +65555,7 @@
         <v>0.489499986171722</v>
       </c>
       <c r="G2356" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65584,7 +65581,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2357" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65610,7 +65607,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2358" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65636,7 +65633,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G2359" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65662,7 +65659,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2360" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65688,7 +65685,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G2361" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65714,7 +65711,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2362" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65740,7 +65737,7 @@
         <v>0.494500011205673</v>
       </c>
       <c r="G2363" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65766,7 +65763,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G2364" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65792,7 +65789,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2365" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65818,7 +65815,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G2366" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65844,7 +65841,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G2367" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65870,7 +65867,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G2368" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65896,7 +65893,7 @@
         <v>0.5</v>
       </c>
       <c r="G2369" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65922,7 +65919,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G2370" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65948,7 +65945,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G2371" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65974,7 +65971,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2372" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66000,7 +65997,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2373" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66026,7 +66023,7 @@
         <v>0.5</v>
       </c>
       <c r="G2374" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66052,7 +66049,7 @@
         <v>0.497000008821487</v>
       </c>
       <c r="G2375" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66078,7 +66075,7 @@
         <v>0.5</v>
       </c>
       <c r="G2376" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66104,7 +66101,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G2377" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66130,7 +66127,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G2378" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66156,7 +66153,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2379" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66182,7 +66179,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2380" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66208,7 +66205,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G2381" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66234,7 +66231,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2382" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66260,7 +66257,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2383" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66286,7 +66283,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G2384" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66312,7 +66309,7 @@
         <v>0.496499985456467</v>
       </c>
       <c r="G2385" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66338,7 +66335,7 @@
         <v>0.496499985456467</v>
       </c>
       <c r="G2386" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66364,7 +66361,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2387" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66390,7 +66387,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G2388" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66416,7 +66413,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G2389" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66442,7 +66439,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G2390" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66468,7 +66465,7 @@
         <v>0.5</v>
       </c>
       <c r="G2391" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66494,7 +66491,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G2392" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66520,7 +66517,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G2393" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66546,7 +66543,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G2394" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66572,7 +66569,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G2395" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66598,7 +66595,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2396" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66624,7 +66621,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2397" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66650,7 +66647,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2398" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66676,7 +66673,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2399" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66702,7 +66699,7 @@
         <v>0.5</v>
       </c>
       <c r="G2400" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66728,7 +66725,7 @@
         <v>0.5</v>
       </c>
       <c r="G2401" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66754,7 +66751,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G2402" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66780,7 +66777,7 @@
         <v>0.494500011205673</v>
       </c>
       <c r="G2403" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66806,7 +66803,7 @@
         <v>0.494500011205673</v>
       </c>
       <c r="G2404" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66832,7 +66829,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2405" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66858,7 +66855,7 @@
         <v>0.5</v>
       </c>
       <c r="G2406" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66884,7 +66881,7 @@
         <v>0.492500007152557</v>
       </c>
       <c r="G2407" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66910,7 +66907,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G2408" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66936,7 +66933,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G2409" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66962,7 +66959,7 @@
         <v>0.497000008821487</v>
       </c>
       <c r="G2410" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66988,7 +66985,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G2411" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67014,7 +67011,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G2412" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67040,7 +67037,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G2413" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67066,7 +67063,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G2414" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67092,7 +67089,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2415" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67118,7 +67115,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G2416" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67144,7 +67141,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2417" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67170,7 +67167,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2418" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67196,7 +67193,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2419" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67222,7 +67219,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G2420" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67248,7 +67245,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G2421" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67274,7 +67271,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2422" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67300,7 +67297,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G2423" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67326,7 +67323,7 @@
         <v>0.497000008821487</v>
       </c>
       <c r="G2424" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67352,7 +67349,7 @@
         <v>0.497000008821487</v>
       </c>
       <c r="G2425" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67378,7 +67375,7 @@
         <v>0.491499990224838</v>
       </c>
       <c r="G2426" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67404,7 +67401,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G2427" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67430,7 +67427,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G2428" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67456,7 +67453,7 @@
         <v>0.492500007152557</v>
       </c>
       <c r="G2429" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67482,7 +67479,7 @@
         <v>0.496499985456467</v>
       </c>
       <c r="G2430" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67508,7 +67505,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2431" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67534,7 +67531,7 @@
         <v>0.5</v>
       </c>
       <c r="G2432" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67560,7 +67557,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G2433" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67586,7 +67583,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G2434" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67612,7 +67609,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G2435" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67638,7 +67635,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G2436" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67664,7 +67661,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G2437" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67690,7 +67687,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G2438" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67716,7 +67713,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2439" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67742,7 +67739,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2440" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67768,7 +67765,7 @@
         <v>0.5</v>
       </c>
       <c r="G2441" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67794,7 +67791,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G2442" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67820,7 +67817,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2443" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67846,7 +67843,7 @@
         <v>0.5</v>
       </c>
       <c r="G2444" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67872,7 +67869,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2445" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67898,7 +67895,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G2446" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67924,7 +67921,7 @@
         <v>0.496499985456467</v>
       </c>
       <c r="G2447" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67950,7 +67947,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G2448" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67976,7 +67973,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G2449" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68002,7 +67999,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2450" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68028,7 +68025,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G2451" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68054,7 +68051,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G2452" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68080,7 +68077,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2453" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68106,7 +68103,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G2454" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68132,7 +68129,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2455" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68158,7 +68155,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G2456" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68184,7 +68181,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G2457" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68210,7 +68207,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2458" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68236,7 +68233,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2459" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68262,7 +68259,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G2460" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68288,7 +68285,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G2461" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68314,7 +68311,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G2462" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68340,7 +68337,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2463" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68366,7 +68363,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G2464" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68392,7 +68389,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G2465" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68418,7 +68415,7 @@
         <v>0.50900000333786</v>
       </c>
       <c r="G2466" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68444,7 +68441,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G2467" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68470,7 +68467,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2468" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68496,7 +68493,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2469" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68522,7 +68519,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G2470" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68548,7 +68545,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2471" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68574,7 +68571,7 @@
         <v>0.570999979972839</v>
       </c>
       <c r="G2472" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68600,7 +68597,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2473" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68626,7 +68623,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2474" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68652,7 +68649,7 @@
         <v>0.570999979972839</v>
       </c>
       <c r="G2475" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68678,7 +68675,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G2476" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68704,7 +68701,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2477" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68730,7 +68727,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2478" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68756,7 +68753,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2479" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68782,7 +68779,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2480" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68808,7 +68805,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2481" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68834,7 +68831,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2482" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68860,7 +68857,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2483" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68886,7 +68883,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2484" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68912,7 +68909,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2485" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68938,7 +68935,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2486" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68964,7 +68961,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G2487" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68990,7 +68987,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G2488" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69016,7 +69013,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G2489" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69042,7 +69039,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G2490" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69068,7 +69065,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2491" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69094,7 +69091,7 @@
         <v>0.602999985218048</v>
       </c>
       <c r="G2492" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69120,7 +69117,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G2493" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69146,7 +69143,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2494" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69172,7 +69169,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2495" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69198,7 +69195,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2496" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69224,7 +69221,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2497" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69250,7 +69247,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G2498" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69276,7 +69273,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G2499" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69302,7 +69299,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G2500" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69328,7 +69325,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G2501" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69336,7 +69333,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6936226852</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>171378</v>
@@ -69354,9 +69351,35 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2502" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6910300926</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>577210</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>0.591000020503998</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>0.564000010490417</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>0.568000018596649</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="1322">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333736151456833</t>
+    <t xml:space="preserve">0.333736181259155</t>
   </si>
   <si>
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32744625210762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321156322956085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317678391933441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307318478822708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288448691368103</t>
+    <t xml:space="preserve">0.327446222305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321156293153763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317678362131119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307318449020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288448721170425</t>
   </si>
   <si>
     <t xml:space="preserve">0.289336711168289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294368624687195</t>
+    <t xml:space="preserve">0.294368654489517</t>
   </si>
   <si>
     <t xml:space="preserve">0.285636752843857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796886205673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258996993303299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258257061243057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243605211377144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246417194604874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262697011232376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256407052278519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259811013936996</t>
+    <t xml:space="preserve">0.273796856403351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258997023105621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258257031440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243605226278305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246417179703712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262696981430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256407082080841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259810984134674</t>
   </si>
   <si>
     <t xml:space="preserve">0.261512994766235</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">0.253817081451416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253077119588852</t>
+    <t xml:space="preserve">0.25307708978653</t>
   </si>
   <si>
     <t xml:space="preserve">0.286894679069519</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">0.284600764513016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277496814727783</t>
+    <t xml:space="preserve">0.277496844530106</t>
   </si>
   <si>
     <t xml:space="preserve">0.28711673617363</t>
@@ -119,16 +119,16 @@
     <t xml:space="preserve">0.263806998729706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256777048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.250117123126984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277570813894272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297994613647461</t>
+    <t xml:space="preserve">0.256777077913284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.250117152929306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277570843696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297994583845139</t>
   </si>
   <si>
     <t xml:space="preserve">0.310796439647675</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">0.301620543003082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31035241484642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323376268148422</t>
+    <t xml:space="preserve">0.310352474451065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323376297950745</t>
   </si>
   <si>
     <t xml:space="preserve">0.320046335458755</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">0.315606415271759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332996159791946</t>
+    <t xml:space="preserve">0.332996189594269</t>
   </si>
   <si>
     <t xml:space="preserve">0.332256227731705</t>
@@ -188,52 +188,52 @@
     <t xml:space="preserve">0.299696564674377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296884566545486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2994005382061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29747661948204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295996576547623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293702661991119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298216611146927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286376744508743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276756852865219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27453687787056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272316843271255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268542945384979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270466893911362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265064984560013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268172979354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268616944551468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269208908081055</t>
+    <t xml:space="preserve">0.296884596347809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299400568008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297476589679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295996606349945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293702632188797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298216581344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286376714706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276756823062897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274536848068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272316873073578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268542915582657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270466923713684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26506495475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268172949552536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268616914749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269208878278732</t>
   </si>
   <si>
     <t xml:space="preserve">0.275276839733124</t>
@@ -248,22 +248,22 @@
     <t xml:space="preserve">0.308206468820572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309168457984924</t>
+    <t xml:space="preserve">0.309168517589569</t>
   </si>
   <si>
     <t xml:space="preserve">0.318196386098862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316938400268555</t>
+    <t xml:space="preserve">0.31693834066391</t>
   </si>
   <si>
     <t xml:space="preserve">0.308946460485458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31420037150383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321378320455551</t>
+    <t xml:space="preserve">0.314200401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321378290653229</t>
   </si>
   <si>
     <t xml:space="preserve">0.319380342960358</t>
@@ -278,61 +278,61 @@
     <t xml:space="preserve">0.313312411308289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307096511125565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307614475488663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304950535297394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305616497993469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2995485663414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305320531129837</t>
+    <t xml:space="preserve">0.307096481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30761444568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304950475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305616468191147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299548596143723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305320501327515</t>
   </si>
   <si>
     <t xml:space="preserve">0.295626610517502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300954520702362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314400285482407</t>
+    <t xml:space="preserve">0.300954550504684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314400345087051</t>
   </si>
   <si>
     <t xml:space="preserve">0.318779796361923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318856626749039</t>
+    <t xml:space="preserve">0.318856596946716</t>
   </si>
   <si>
     <t xml:space="preserve">0.318395644426346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319932281970978</t>
+    <t xml:space="preserve">0.319932252168655</t>
   </si>
   <si>
     <t xml:space="preserve">0.318088293075562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307331651449203</t>
+    <t xml:space="preserve">0.307331681251526</t>
   </si>
   <si>
     <t xml:space="preserve">0.321776270866394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320393264293671</t>
+    <t xml:space="preserve">0.320393294095993</t>
   </si>
   <si>
     <t xml:space="preserve">0.311557501554489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305795043706894</t>
+    <t xml:space="preserve">0.305795013904572</t>
   </si>
   <si>
     <t xml:space="preserve">0.301569253206253</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">0.299648374319077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29657506942749</t>
+    <t xml:space="preserve">0.296575099229813</t>
   </si>
   <si>
     <t xml:space="preserve">0.303490042686462</t>
@@ -353,40 +353,40 @@
     <t xml:space="preserve">0.314246654510498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318011462688446</t>
+    <t xml:space="preserve">0.318011432886124</t>
   </si>
   <si>
     <t xml:space="preserve">0.318702936172485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321161597967148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310020864009857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311941653490067</t>
+    <t xml:space="preserve">0.32116162776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310020834207535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311941623687744</t>
   </si>
   <si>
     <t xml:space="preserve">0.311173349618912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30725485086441</t>
+    <t xml:space="preserve">0.307254821062088</t>
   </si>
   <si>
     <t xml:space="preserve">0.30671700835228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305564552545547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304949820041656</t>
+    <t xml:space="preserve">0.305564522743225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304949879646301</t>
   </si>
   <si>
     <t xml:space="preserve">0.306870669126511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297727584838867</t>
+    <t xml:space="preserve">0.297727555036545</t>
   </si>
   <si>
     <t xml:space="preserve">0.301799714565277</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">0.304027885198593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300032556056976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313478291034698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312556326389313</t>
+    <t xml:space="preserve">0.300032526254654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313478320837021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31255629658699</t>
   </si>
   <si>
     <t xml:space="preserve">0.307869493961334</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">0.298265427350998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299110591411591</t>
+    <t xml:space="preserve">0.299110531806946</t>
   </si>
   <si>
     <t xml:space="preserve">0.305257201194763</t>
@@ -425,10 +425,10 @@
     <t xml:space="preserve">0.295960396528244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297650754451752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297881215810776</t>
+    <t xml:space="preserve">0.297650724649429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297881186008453</t>
   </si>
   <si>
     <t xml:space="preserve">0.29373225569725</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">0.298803240060806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300416707992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300109386444092</t>
+    <t xml:space="preserve">0.300416737794876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300109416246414</t>
   </si>
   <si>
     <t xml:space="preserve">0.298880070447922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305487722158432</t>
+    <t xml:space="preserve">0.30548769235611</t>
   </si>
   <si>
     <t xml:space="preserve">0.309559851884842</t>
@@ -455,28 +455,28 @@
     <t xml:space="preserve">0.303105860948563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3035669028759</t>
+    <t xml:space="preserve">0.303566873073578</t>
   </si>
   <si>
     <t xml:space="preserve">0.308253675699234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304873079061508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306563317775726</t>
+    <t xml:space="preserve">0.304873049259186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306563347578049</t>
   </si>
   <si>
     <t xml:space="preserve">0.300186216831207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298649579286575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296421408653259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301415532827377</t>
+    <t xml:space="preserve">0.298649609088898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296421378850937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3014155626297</t>
   </si>
   <si>
     <t xml:space="preserve">0.3006471991539</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">0.282975643873215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291965067386627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289736926555634</t>
+    <t xml:space="preserve">0.29196509718895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289736956357956</t>
   </si>
   <si>
     <t xml:space="preserve">0.293501764535904</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">0.292656600475311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292502969503403</t>
+    <t xml:space="preserve">0.29250293970108</t>
   </si>
   <si>
     <t xml:space="preserve">0.289583295583725</t>
@@ -506,49 +506,49 @@
     <t xml:space="preserve">0.288123458623886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284281849861145</t>
+    <t xml:space="preserve">0.284281820058823</t>
   </si>
   <si>
     <t xml:space="preserve">0.28789296746254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290044277906418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292887061834335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293117612600327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291888266801834</t>
+    <t xml:space="preserve">0.290044248104095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292887091636658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293117582798004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291888296604156</t>
   </si>
   <si>
     <t xml:space="preserve">0.289813756942749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286586761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294270098209381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291811436414719</t>
+    <t xml:space="preserve">0.286586821079254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294270068407059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291811406612396</t>
   </si>
   <si>
     <t xml:space="preserve">0.292579770088196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295729905366898</t>
+    <t xml:space="preserve">0.29572993516922</t>
   </si>
   <si>
     <t xml:space="preserve">0.298419058322906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294731110334396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287355154752731</t>
+    <t xml:space="preserve">0.294731050729752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287355124950409</t>
   </si>
   <si>
     <t xml:space="preserve">0.293809086084366</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">0.292041957378387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28674042224884</t>
+    <t xml:space="preserve">0.286740452051163</t>
   </si>
   <si>
     <t xml:space="preserve">0.2846659719944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278903484344482</t>
+    <t xml:space="preserve">0.278903543949127</t>
   </si>
   <si>
     <t xml:space="preserve">0.27559968829155</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">0.270221382379532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272449553012848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276675373315811</t>
+    <t xml:space="preserve">0.272449523210526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276675343513489</t>
   </si>
   <si>
     <t xml:space="preserve">0.273986160755157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275676488876343</t>
+    <t xml:space="preserve">0.275676518678665</t>
   </si>
   <si>
     <t xml:space="preserve">0.275522857904434</t>
@@ -590,25 +590,25 @@
     <t xml:space="preserve">0.276598513126373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270989716053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27114337682724</t>
+    <t xml:space="preserve">0.270989686250687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271143406629562</t>
   </si>
   <si>
     <t xml:space="preserve">0.274293512105942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270451873540878</t>
+    <t xml:space="preserve">0.270451903343201</t>
   </si>
   <si>
     <t xml:space="preserve">0.268146902322769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267378598451614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264612555503845</t>
+    <t xml:space="preserve">0.267378568649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264612585306168</t>
   </si>
   <si>
     <t xml:space="preserve">0.265765070915222</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">0.262384444475174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267532229423523</t>
+    <t xml:space="preserve">0.267532259225845</t>
   </si>
   <si>
     <t xml:space="preserve">0.265304088592529</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">0.27844250202179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280516982078552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278749823570251</t>
+    <t xml:space="preserve">0.280517011880875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278749853372574</t>
   </si>
   <si>
     <t xml:space="preserve">0.27898034453392</t>
@@ -656,49 +656,49 @@
     <t xml:space="preserve">0.284051328897476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290812611579895</t>
+    <t xml:space="preserve">0.290812641382217</t>
   </si>
   <si>
     <t xml:space="preserve">0.289660096168518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290428429841995</t>
+    <t xml:space="preserve">0.290428459644318</t>
   </si>
   <si>
     <t xml:space="preserve">0.294807910919189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295422554016113</t>
+    <t xml:space="preserve">0.295422583818436</t>
   </si>
   <si>
     <t xml:space="preserve">0.288507610559464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284589141607285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291043102741241</t>
+    <t xml:space="preserve">0.284589171409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291043132543564</t>
   </si>
   <si>
     <t xml:space="preserve">0.293885916471481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294884771108627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289890617132187</t>
+    <t xml:space="preserve">0.294884741306305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289890646934509</t>
   </si>
   <si>
     <t xml:space="preserve">0.286125779151917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284358650445938</t>
+    <t xml:space="preserve">0.284358620643616</t>
   </si>
   <si>
     <t xml:space="preserve">0.282745122909546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277290016412735</t>
+    <t xml:space="preserve">0.27729007601738</t>
   </si>
   <si>
     <t xml:space="preserve">0.281976819038391</t>
@@ -707,16 +707,16 @@
     <t xml:space="preserve">0.276214361190796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273602038621902</t>
+    <t xml:space="preserve">0.27360200881958</t>
   </si>
   <si>
     <t xml:space="preserve">0.269760370254517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275061905384064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271834880113602</t>
+    <t xml:space="preserve">0.275061845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271834850311279</t>
   </si>
   <si>
     <t xml:space="preserve">0.273371547460556</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">0.274831354618073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282668352127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280440151691437</t>
+    <t xml:space="preserve">0.282668322324753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280440181493759</t>
   </si>
   <si>
     <t xml:space="preserve">0.279595017433167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27736684679985</t>
+    <t xml:space="preserve">0.277366816997528</t>
   </si>
   <si>
     <t xml:space="preserve">0.278135180473328</t>
@@ -749,25 +749,25 @@
     <t xml:space="preserve">0.281208485364914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278673022985458</t>
+    <t xml:space="preserve">0.278672963380814</t>
   </si>
   <si>
     <t xml:space="preserve">0.282591491937637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279364496469498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285587966442108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279671788215637</t>
+    <t xml:space="preserve">0.27936452627182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285587936639786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27967181801796</t>
   </si>
   <si>
     <t xml:space="preserve">0.28666365146637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284435451030731</t>
+    <t xml:space="preserve">0.284435480833054</t>
   </si>
   <si>
     <t xml:space="preserve">0.281899988651276</t>
@@ -779,46 +779,46 @@
     <t xml:space="preserve">0.285280644893646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285434305667877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295038431882858</t>
+    <t xml:space="preserve">0.285434275865555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295038402080536</t>
   </si>
   <si>
     <t xml:space="preserve">0.304258346557617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321929931640625</t>
+    <t xml:space="preserve">0.321929901838303</t>
   </si>
   <si>
     <t xml:space="preserve">0.325617909431458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331841379404068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387418270111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316935837268829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309790343046188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309252500534058</t>
+    <t xml:space="preserve">0.33184140920639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387448072433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316935777664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309790313243866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30925253033638</t>
   </si>
   <si>
     <t xml:space="preserve">0.311096489429474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313094139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313017338514328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288891762495041</t>
+    <t xml:space="preserve">0.313094168901443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313017308712006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288891792297363</t>
   </si>
   <si>
     <t xml:space="preserve">0.293040752410889</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.295192092657089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296805590391159</t>
+    <t xml:space="preserve">0.296805560588837</t>
   </si>
   <si>
     <t xml:space="preserve">0.297266602516174</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">0.327308237552643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318472474813461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312095314264297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314016193151474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315015017986298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312248975038528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313939303159714</t>
+    <t xml:space="preserve">0.318472445011139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31209534406662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314016133546829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315014988183975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312249004840851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313939332962036</t>
   </si>
   <si>
     <t xml:space="preserve">0.309636652469635</t>
@@ -893,43 +893,43 @@
     <t xml:space="preserve">0.307715862989426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309022009372711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309944003820419</t>
+    <t xml:space="preserve">0.309022039175034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309943974018097</t>
   </si>
   <si>
     <t xml:space="preserve">0.3177809715271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316551625728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316474825143814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324388563632965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325003266334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318318754434586</t>
+    <t xml:space="preserve">0.31655165553093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316474854946136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32438862323761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325003236532211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31831881403923</t>
   </si>
   <si>
     <t xml:space="preserve">0.317704141139984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321545779705048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320470154285431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621405124664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323697149753571</t>
+    <t xml:space="preserve">0.32154580950737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320470124483109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621464729309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323697090148926</t>
   </si>
   <si>
     <t xml:space="preserve">0.333454877138138</t>
@@ -938,19 +938,19 @@
     <t xml:space="preserve">0.327385067939758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331764549016953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339524686336517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345671325922012</t>
+    <t xml:space="preserve">0.33176451921463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33952471613884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34567129611969</t>
   </si>
   <si>
     <t xml:space="preserve">0.340446680784225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333378046751022</t>
+    <t xml:space="preserve">0.3333780169487</t>
   </si>
   <si>
     <t xml:space="preserve">0.33499151468277</t>
@@ -959,79 +959,79 @@
     <t xml:space="preserve">0.336144030094147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337757527828217</t>
+    <t xml:space="preserve">0.337757498025894</t>
   </si>
   <si>
     <t xml:space="preserve">0.338910013437271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338141709566116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339678317308426</t>
+    <t xml:space="preserve">0.338141679763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339678347110748</t>
   </si>
   <si>
     <t xml:space="preserve">0.350358128547668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34659332036972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344211488962173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340677201747894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334607392549515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338218510150909</t>
+    <t xml:space="preserve">0.346593290567398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344211518764496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340677112340927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334607362747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338218539953232</t>
   </si>
   <si>
     <t xml:space="preserve">0.346900641918182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346132308244705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33960148692131</t>
+    <t xml:space="preserve">0.346132338047028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339601457118988</t>
   </si>
   <si>
     <t xml:space="preserve">0.340907663106918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3526631295681</t>
+    <t xml:space="preserve">0.352663099765778</t>
   </si>
   <si>
     <t xml:space="preserve">0.369950503110886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36541736125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363035529851913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374099493026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371103018522263</t>
+    <t xml:space="preserve">0.365417391061783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363035559654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374099463224411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371103048324585</t>
   </si>
   <si>
     <t xml:space="preserve">0.369566351175308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368798017501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366108864545822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363112419843674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368644326925278</t>
+    <t xml:space="preserve">0.368798047304153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366108894348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363112390041351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3686443567276</t>
   </si>
   <si>
     <t xml:space="preserve">0.366877198219299</t>
@@ -1043,13 +1043,13 @@
     <t xml:space="preserve">0.361114740371704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359885424375534</t>
+    <t xml:space="preserve">0.359885454177856</t>
   </si>
   <si>
     <t xml:space="preserve">0.359193921089172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368567496538162</t>
+    <t xml:space="preserve">0.368567526340485</t>
   </si>
   <si>
     <t xml:space="preserve">0.372024983167648</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">0.421044409275055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419507771730423</t>
+    <t xml:space="preserve">0.419507712125778</t>
   </si>
   <si>
     <t xml:space="preserve">0.396842062473297</t>
@@ -1079,46 +1079,46 @@
     <t xml:space="preserve">0.413361102342606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422581076622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417586863040924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426422744989395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423349440097809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427959352731705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436795175075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432953476905823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452930063009262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460884332657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465223342180252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296676874161</t>
+    <t xml:space="preserve">0.422581106424332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417586892843246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42642268538475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423349380493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427959382534027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436795115470886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432953506708145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45293003320694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460854530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46522331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296617269516</t>
   </si>
   <si>
     <t xml:space="preserve">0.481358289718628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522463798522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5151646733284</t>
+    <t xml:space="preserve">0.522463917732239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515164732933044</t>
   </si>
   <si>
     <t xml:space="preserve">0.505560576915741</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">0.515548884868622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503255665302277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489809840917587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480205774307251</t>
+    <t xml:space="preserve">0.503255605697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48980987071991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480205714702606</t>
   </si>
   <si>
     <t xml:space="preserve">0.519006371498108</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">0.491730690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484431535005569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48366317152977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484815686941147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495188176631927</t>
+    <t xml:space="preserve">0.484431564807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483663231134415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484815776348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49518820643425</t>
   </si>
   <si>
     <t xml:space="preserve">0.490194082260132</t>
@@ -1175,16 +1175,16 @@
     <t xml:space="preserve">0.56280118227005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586235225200653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600065112113953</t>
+    <t xml:space="preserve">0.586235165596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600065052509308</t>
   </si>
   <si>
     <t xml:space="preserve">0.58239358663559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572021126747131</t>
+    <t xml:space="preserve">0.572021067142487</t>
   </si>
   <si>
     <t xml:space="preserve">0.572789430618286</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">0.552428722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551276206970215</t>
+    <t xml:space="preserve">0.55127614736557</t>
   </si>
   <si>
     <t xml:space="preserve">0.545129597187042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565874516963959</t>
+    <t xml:space="preserve">0.565874457359314</t>
   </si>
   <si>
     <t xml:space="preserve">0.577015221118927</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">0.596607625484467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584698557853699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608132481575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621962428092957</t>
+    <t xml:space="preserve">0.584698498249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608132541179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621962487697601</t>
   </si>
   <si>
     <t xml:space="preserve">0.620425879955292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629645884037018</t>
+    <t xml:space="preserve">0.629645824432373</t>
   </si>
   <si>
     <t xml:space="preserve">0.614279210567474</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">0.607748448848724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58162522315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560880303382874</t>
+    <t xml:space="preserve">0.581625282764435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560880362987518</t>
   </si>
   <si>
     <t xml:space="preserve">0.598528444766998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598144292831421</t>
+    <t xml:space="preserve">0.598144233226776</t>
   </si>
   <si>
     <t xml:space="preserve">0.619657516479492</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">0.601601779460907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586619317531586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595455169677734</t>
+    <t xml:space="preserve">0.58661937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59545511007309</t>
   </si>
   <si>
     <t xml:space="preserve">0.587771832942963</t>
@@ -1262,31 +1262,31 @@
     <t xml:space="preserve">0.584314405918121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577399432659149</t>
+    <t xml:space="preserve">0.577399373054504</t>
   </si>
   <si>
     <t xml:space="preserve">0.567026913166046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574326038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543592929840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564722061157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.563185274600983</t>
+    <t xml:space="preserve">0.57432609796524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543592870235443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564721941947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.563185334205627</t>
   </si>
   <si>
     <t xml:space="preserve">0.576246917247772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583930134773254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58085685968399</t>
+    <t xml:space="preserve">0.583930194377899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580856919288635</t>
   </si>
   <si>
     <t xml:space="preserve">0.587003529071808</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">0.604675054550171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629261612892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618505001068115</t>
+    <t xml:space="preserve">0.629261553287506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61850506067276</t>
   </si>
   <si>
     <t xml:space="preserve">0.606980085372925</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">0.603138506412506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612358391284943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611590087413788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593918442726135</t>
+    <t xml:space="preserve">0.612358331680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611590027809143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59391850233078</t>
   </si>
   <si>
     <t xml:space="preserve">0.596991777420044</t>
@@ -1325,37 +1325,37 @@
     <t xml:space="preserve">0.599296748638153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589308500289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553965389728546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538598775863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557038605213165</t>
+    <t xml:space="preserve">0.589308559894562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553965330123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538598656654358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557038724422455</t>
   </si>
   <si>
     <t xml:space="preserve">0.536293804645538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524000406265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537830471992493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547818779945374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532452166080475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537062168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527073800563812</t>
+    <t xml:space="preserve">0.524000465869904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537830412387848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547818720340729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53245210647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537062227725983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527073860168457</t>
   </si>
   <si>
     <t xml:space="preserve">0.52092719078064</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">0.525537192821503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530147194862366</t>
+    <t xml:space="preserve">0.530147075653076</t>
   </si>
   <si>
     <t xml:space="preserve">0.523232221603394</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">0.524768888950348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549355328083038</t>
+    <t xml:space="preserve">0.549355387687683</t>
   </si>
   <si>
     <t xml:space="preserve">0.501718938350677</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">0.492498993873596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477900743484497</t>
+    <t xml:space="preserve">0.477900773286819</t>
   </si>
   <si>
     <t xml:space="preserve">0.476364135742188</t>
@@ -1397,34 +1397,34 @@
     <t xml:space="preserve">0.48865732550621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471754223108292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472522467374802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468680769205093</t>
+    <t xml:space="preserve">0.471754133701324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472522497177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468680799007416</t>
   </si>
   <si>
     <t xml:space="preserve">0.487120717763901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481742441654205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480974078178406</t>
+    <t xml:space="preserve">0.481742411851883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480974018573761</t>
   </si>
   <si>
     <t xml:space="preserve">0.483279079198837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478669106960297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470217436552048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467912524938583</t>
+    <t xml:space="preserve">0.478669136762619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470217496156693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467912554740906</t>
   </si>
   <si>
     <t xml:space="preserve">0.466375797986984</t>
@@ -1433,40 +1433,40 @@
     <t xml:space="preserve">0.464839190244675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461765915155411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487889021635056</t>
+    <t xml:space="preserve">0.461765885353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487889111042023</t>
   </si>
   <si>
     <t xml:space="preserve">0.500182390213013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469449192285538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437179327011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444862604141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431800961494446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444094270467758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424117714166641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415666073560715</t>
+    <t xml:space="preserve">0.469449132680893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437179356813431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444862574338913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431801021099091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444094240665436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424117684364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415666133165359</t>
   </si>
   <si>
     <t xml:space="preserve">0.382627934217453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379170507192612</t>
+    <t xml:space="preserve">0.379170477390289</t>
   </si>
   <si>
     <t xml:space="preserve">0.382243812084198</t>
@@ -1475,31 +1475,31 @@
     <t xml:space="preserve">0.385701239109039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388774573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391847878694534</t>
+    <t xml:space="preserve">0.388774544000626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391847908496857</t>
   </si>
   <si>
     <t xml:space="preserve">0.38416463136673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376481294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367261320352554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.364956349134445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360346466302872</t>
+    <t xml:space="preserve">0.37648132443428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367261350154877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364956378936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360346406698227</t>
   </si>
   <si>
     <t xml:space="preserve">0.3522789478302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356504738330841</t>
+    <t xml:space="preserve">0.356504768133163</t>
   </si>
   <si>
     <t xml:space="preserve">0.37148717045784</t>
@@ -1508,28 +1508,28 @@
     <t xml:space="preserve">0.368029683828354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372255474328995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365340530872345</t>
+    <t xml:space="preserve">0.372255504131317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365340501070023</t>
   </si>
   <si>
     <t xml:space="preserve">0.374944657087326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366493046283722</t>
+    <t xml:space="preserve">0.3664930164814</t>
   </si>
   <si>
     <t xml:space="preserve">0.374560475349426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374176293611526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37878629565239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362267255783081</t>
+    <t xml:space="preserve">0.374176323413849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378786265850067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362267196178436</t>
   </si>
   <si>
     <t xml:space="preserve">0.353815615177155</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">0.354199767112732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395689517259598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411056160926819</t>
+    <t xml:space="preserve">0.395689576864243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411056190729141</t>
   </si>
   <si>
     <t xml:space="preserve">0.407982856035233</t>
@@ -1559,40 +1559,40 @@
     <t xml:space="preserve">0.384932905435562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390311270952225</t>
+    <t xml:space="preserve">0.390311241149902</t>
   </si>
   <si>
     <t xml:space="preserve">0.378017991781235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380707085132599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362651407718658</t>
+    <t xml:space="preserve">0.380707114934921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362651377916336</t>
   </si>
   <si>
     <t xml:space="preserve">0.35957807302475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3534314930439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349589794874191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344979852437973</t>
+    <t xml:space="preserve">0.353431463241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349589765071869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344979822635651</t>
   </si>
   <si>
     <t xml:space="preserve">0.343059003353119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354968070983887</t>
+    <t xml:space="preserve">0.354968100786209</t>
   </si>
   <si>
     <t xml:space="preserve">0.36418804526329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357273072004318</t>
+    <t xml:space="preserve">0.357273101806641</t>
   </si>
   <si>
     <t xml:space="preserve">0.349973946809769</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">0.339217334985733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323850750923157</t>
+    <t xml:space="preserve">0.323850780725479</t>
   </si>
   <si>
     <t xml:space="preserve">0.361883044242859</t>
@@ -1610,28 +1610,28 @@
     <t xml:space="preserve">0.350742280483246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389542907476425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404141187667847</t>
+    <t xml:space="preserve">0.389542937278748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404141157865524</t>
   </si>
   <si>
     <t xml:space="preserve">0.396457880735397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412592798471451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404909521341324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401836156845093</t>
+    <t xml:space="preserve">0.412592828273773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404909491539001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401836186647415</t>
   </si>
   <si>
     <t xml:space="preserve">0.394152909517288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399531185626984</t>
+    <t xml:space="preserve">0.399531126022339</t>
   </si>
   <si>
     <t xml:space="preserve">0.40260449051857</t>
@@ -1640,28 +1640,28 @@
     <t xml:space="preserve">0.40106788277626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397994548082352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375712990760803</t>
+    <t xml:space="preserve">0.397994577884674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375712960958481</t>
   </si>
   <si>
     <t xml:space="preserve">0.36457222700119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345748156309128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336528211832047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335759907960892</t>
+    <t xml:space="preserve">0.345748126506805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336528182029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335759878158569</t>
   </si>
   <si>
     <t xml:space="preserve">0.337296515703201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329613208770752</t>
+    <t xml:space="preserve">0.329613238573074</t>
   </si>
   <si>
     <t xml:space="preserve">0.32807657122612</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">0.319240808486938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326924115419388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312710016965866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341138154268265</t>
+    <t xml:space="preserve">0.326924055814743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312709987163544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341138184070587</t>
   </si>
   <si>
     <t xml:space="preserve">0.322698265314102</t>
@@ -1688,22 +1688,22 @@
     <t xml:space="preserve">0.326155722141266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324619114398956</t>
+    <t xml:space="preserve">0.324619084596634</t>
   </si>
   <si>
     <t xml:space="preserve">0.325771600008011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330381542444229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329997390508652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324234902858734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313862472772598</t>
+    <t xml:space="preserve">0.330381602048874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329997420310974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324234962463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313862502574921</t>
   </si>
   <si>
     <t xml:space="preserve">0.301185041666031</t>
@@ -1712,34 +1712,34 @@
     <t xml:space="preserve">0.303874224424362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296959221363068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302721738815308</t>
+    <t xml:space="preserve">0.29695925116539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302721709012985</t>
   </si>
   <si>
     <t xml:space="preserve">0.32308241724968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308100044727325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310405015945435</t>
+    <t xml:space="preserve">0.308100014925003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310404986143112</t>
   </si>
   <si>
     <t xml:space="preserve">0.306947529315948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314630806446075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305410832166672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30848416686058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304642498493195</t>
+    <t xml:space="preserve">0.314630776643753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305410861968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308484137058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304642528295517</t>
   </si>
   <si>
     <t xml:space="preserve">0.320777416229248</t>
@@ -1748,76 +1748,76 @@
     <t xml:space="preserve">0.356888920068741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358041405677795</t>
+    <t xml:space="preserve">0.358041375875473</t>
   </si>
   <si>
     <t xml:space="preserve">0.356120586395264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360730528831482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35880970954895</t>
+    <t xml:space="preserve">0.360730588436127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358809798955917</t>
   </si>
   <si>
     <t xml:space="preserve">0.351126462221146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355736404657364</t>
+    <t xml:space="preserve">0.355736434459686</t>
   </si>
   <si>
     <t xml:space="preserve">0.342290639877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371871322393417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370334714651108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383780419826508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376097142696381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37686550617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377249628305435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398762822151184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40337285399437</t>
+    <t xml:space="preserve">0.37187135219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370334655046463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38378044962883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376097172498703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376865446567535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377249658107758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398762881755829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403372824192047</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446129083633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409519463777542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39107957482338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381475418806076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407214432954788</t>
+    <t xml:space="preserve">0.40951943397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391079545021057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381475448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407214462757111</t>
   </si>
   <si>
     <t xml:space="preserve">0.387237936258316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394921243190765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411824464797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414897829294205</t>
+    <t xml:space="preserve">0.394921183586121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411824434995651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41489776968956</t>
   </si>
   <si>
     <t xml:space="preserve">0.417202740907669</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">0.397226184606552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408751130104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410287767648697</t>
+    <t xml:space="preserve">0.408751159906387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410287797451019</t>
   </si>
   <si>
     <t xml:space="preserve">0.414129436016083</t>
@@ -1838,58 +1838,58 @@
     <t xml:space="preserve">0.416434437036514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418739438056946</t>
+    <t xml:space="preserve">0.418739408254623</t>
   </si>
   <si>
     <t xml:space="preserve">0.420276045799255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421812772750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430264383554459</t>
+    <t xml:space="preserve">0.421812742948532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430264353752136</t>
   </si>
   <si>
     <t xml:space="preserve">0.473290830850601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494804084300995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484047323465347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267357349396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506328880786896</t>
+    <t xml:space="preserve">0.494804054498672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48404735326767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267387151718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506328999996185</t>
   </si>
   <si>
     <t xml:space="preserve">0.479437470436096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482510775327682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595772266388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070826768875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465607523918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460997581481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4341059923172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789329051971</t>
+    <t xml:space="preserve">0.482510805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595712661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070856571198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465607494115829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460997492074966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453314214944839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434105962514877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789299249649</t>
   </si>
   <si>
     <t xml:space="preserve">0.445630937814713</t>
@@ -1898,127 +1898,127 @@
     <t xml:space="preserve">0.449472546577454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45100924372673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460229128599167</t>
+    <t xml:space="preserve">0.451009213924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460229158401489</t>
   </si>
   <si>
     <t xml:space="preserve">0.454082578420639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457155883312225</t>
+    <t xml:space="preserve">0.457155913114548</t>
   </si>
   <si>
     <t xml:space="preserve">0.45177760720253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456387579441071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463302552700043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470985740423203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467144101858139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457924216985703</t>
+    <t xml:space="preserve">0.456387519836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463302493095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470985770225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467144191265106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457924276590347</t>
   </si>
   <si>
     <t xml:space="preserve">0.447167605161667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43256938457489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437947630882263</t>
+    <t xml:space="preserve">0.432569354772568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43794772028923</t>
   </si>
   <si>
     <t xml:space="preserve">0.433337688446045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434874355792999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436411023139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439484387636185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441020935773849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440252602100372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438715994358063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442557603120804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485584110021591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455619215965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443326026201248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429496079683304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435642600059509</t>
+    <t xml:space="preserve">0.434874325990677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436410993337631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439484298229218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441020965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440252661705017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438715934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442557632923126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485584050416946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455619245767593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443325996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429496020078659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435642629861832</t>
   </si>
   <si>
     <t xml:space="preserve">0.450240910053253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427190989255905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375328838825226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386469602584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393384575843811</t>
+    <t xml:space="preserve">0.42719104886055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375328809022903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386469632387161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393384546041489</t>
   </si>
   <si>
     <t xml:space="preserve">0.365724712610245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372639685869217</t>
+    <t xml:space="preserve">0.372639626264572</t>
   </si>
   <si>
     <t xml:space="preserve">0.351510643959045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342674881219864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317319989204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265073597431183</t>
+    <t xml:space="preserve">0.342674851417542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317319959402084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265073537826538</t>
   </si>
   <si>
     <t xml:space="preserve">0.259695291519165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239334553480148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242023661732674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234724596142769</t>
+    <t xml:space="preserve">0.23933456838131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242023676633835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234724566340446</t>
   </si>
   <si>
     <t xml:space="preserve">0.245865345001221</t>
@@ -2027,25 +2027,25 @@
     <t xml:space="preserve">0.258926928043365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251627832651138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266610264778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269299387931824</t>
+    <t xml:space="preserve">0.251627802848816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266610234975815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269299328327179</t>
   </si>
   <si>
     <t xml:space="preserve">0.258158624172211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251243650913239</t>
+    <t xml:space="preserve">0.251243680715561</t>
   </si>
   <si>
     <t xml:space="preserve">0.252011984586716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242407843470573</t>
+    <t xml:space="preserve">0.242407888174057</t>
   </si>
   <si>
     <t xml:space="preserve">0.245097041130066</t>
@@ -2054,13 +2054,13 @@
     <t xml:space="preserve">0.254701107740402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262000203132629</t>
+    <t xml:space="preserve">0.262000232934952</t>
   </si>
   <si>
     <t xml:space="preserve">0.254316955804825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261231899261475</t>
+    <t xml:space="preserve">0.261231958866119</t>
   </si>
   <si>
     <t xml:space="preserve">0.262768596410751</t>
@@ -2069,40 +2069,40 @@
     <t xml:space="preserve">0.264689415693283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27198851108551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273909389972687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276982694864273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272756844758987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275446027517319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268915235996246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265841901302338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25854280591011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265457719564438</t>
+    <t xml:space="preserve">0.271988540887833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273909360170364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276982665061951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27275687456131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275445997714996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268915206193924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26584193110466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258542776107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26545774936676</t>
   </si>
   <si>
     <t xml:space="preserve">0.263152748346329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292733460664749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327692449092865</t>
+    <t xml:space="preserve">0.292733430862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327692419290543</t>
   </si>
   <si>
     <t xml:space="preserve">0.302337527275085</t>
@@ -2111,31 +2111,31 @@
     <t xml:space="preserve">0.30195340514183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332302391529083</t>
+    <t xml:space="preserve">0.332302361726761</t>
   </si>
   <si>
     <t xml:space="preserve">0.332686573266983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306179195642471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305026739835739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312325805425644</t>
+    <t xml:space="preserve">0.306179165840149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305026710033417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312325835227966</t>
   </si>
   <si>
     <t xml:space="preserve">0.331918209791183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31539911031723</t>
+    <t xml:space="preserve">0.315399169921875</t>
   </si>
   <si>
     <t xml:space="preserve">0.326539933681488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292349278926849</t>
+    <t xml:space="preserve">0.292349249124527</t>
   </si>
   <si>
     <t xml:space="preserve">0.289275974035263</t>
@@ -2147,10 +2147,10 @@
     <t xml:space="preserve">0.286970943212509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2850501537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273525208234787</t>
+    <t xml:space="preserve">0.285050123929977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273525238037109</t>
   </si>
   <si>
     <t xml:space="preserve">0.260847747325897</t>
@@ -2162,31 +2162,31 @@
     <t xml:space="preserve">0.270067721605301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278519302606583</t>
+    <t xml:space="preserve">0.278519362211227</t>
   </si>
   <si>
     <t xml:space="preserve">0.27314105629921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266994416713715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.255469471216202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253164440393448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256621986627579</t>
+    <t xml:space="preserve">0.266994386911392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.255469501018524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253164499998093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256621927022934</t>
   </si>
   <si>
     <t xml:space="preserve">0.256237804889679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249322831630707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236261233687401</t>
+    <t xml:space="preserve">0.249322801828384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.236261248588562</t>
   </si>
   <si>
     <t xml:space="preserve">0.238182067871094</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">0.25354865193367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267762720584869</t>
+    <t xml:space="preserve">0.267762750387192</t>
   </si>
   <si>
     <t xml:space="preserve">0.283513456583023</t>
@@ -2204,31 +2204,31 @@
     <t xml:space="preserve">0.277750998735428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294654250144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319624930620193</t>
+    <t xml:space="preserve">0.294654279947281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319624960422516</t>
   </si>
   <si>
     <t xml:space="preserve">0.343827337026596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338449001312256</t>
+    <t xml:space="preserve">0.338449031114578</t>
   </si>
   <si>
     <t xml:space="preserve">0.34075403213501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338833183050156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338064819574356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336912363767624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33383908867836</t>
+    <t xml:space="preserve">0.338833212852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338064849376678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336912333965302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333839058876038</t>
   </si>
   <si>
     <t xml:space="preserve">0.330765724182129</t>
@@ -2237,16 +2237,16 @@
     <t xml:space="preserve">0.328844904899597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33998566865921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34766897559166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359962224960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351894795894623</t>
+    <t xml:space="preserve">0.339985698461533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347668945789337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359962195158005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351894736289978</t>
   </si>
   <si>
     <t xml:space="preserve">0.369182229042053</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">0.348053127527237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346516460180283</t>
+    <t xml:space="preserve">0.346516489982605</t>
   </si>
   <si>
     <t xml:space="preserve">0.34728479385376</t>
@@ -2270,25 +2270,25 @@
     <t xml:space="preserve">0.363419711589813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373792141675949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373023808002472</t>
+    <t xml:space="preserve">0.373792171478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373023837804794</t>
   </si>
   <si>
     <t xml:space="preserve">0.379554629325867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425654381513596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417971104383469</t>
+    <t xml:space="preserve">0.42565444111824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417971134185791</t>
   </si>
   <si>
     <t xml:space="preserve">0.381859630346298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38301208615303</t>
+    <t xml:space="preserve">0.383012056350708</t>
   </si>
   <si>
     <t xml:space="preserve">0.377633810043335</t>
@@ -2303,270 +2303,273 @@
     <t xml:space="preserve">0.380322962999344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348437279462814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400299519300461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38339626789093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379938811063766</t>
+    <t xml:space="preserve">0.348437309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400299549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383396327495575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379938781261444</t>
   </si>
   <si>
     <t xml:space="preserve">0.388006269931793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428727686405182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368413865566254</t>
+    <t xml:space="preserve">0.428727716207504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368413835763931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344595640897751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334223210811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341906487941742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323466598987579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340369820594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331149876117706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348821491003036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322314113378525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285818457603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337680697441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345363944768906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341522336006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329229027032852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353653162717819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351594626903534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354064851999283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352829694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347477585077286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345830768346786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341713726520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342537134885788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348300993442535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35982871055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353241413831711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35488823056221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350359499454498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345007330179214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339655190706253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342948853969574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341302007436752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333479672670364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320716857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319070041179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321540266275406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310835957527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315776437520981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314129620790482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312894523143768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31824666261673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317834973335266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319481760263443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312071114778519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308365762233734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310012608766556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314541310071945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318658322095871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320305168628693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322775363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30960088968277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309189140796661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32112854719162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321951985359192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32524561882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326892405748367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323187112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323598831892014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315364718437195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31330618262291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310424268245697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314953029155731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311247676610947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317011535167694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31742325425148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311659425497055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316188126802444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319893449544907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304660439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30877748131752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30301359295845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307542324066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302601903676987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307954072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306307256221771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301778554916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303837031126022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30095511674881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301366806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302190214395523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313717901706696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326480686664581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328539252281189</t>
   </si>
   <si>
     <t xml:space="preserve">0.344595670700073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334223210811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341906487941742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323466628789902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340369820594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331149846315384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348821431398392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322314083576202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285818487405777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337680697441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345363974571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341522336006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329229056835175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353653132915497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351594597101212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35406482219696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352829724550247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347477555274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345830768346786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341713726520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342537105083466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348300993442535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35982871055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353241413831711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354888200759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350359529256821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345007359981537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339655250310898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342948853969574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341302037239075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333479672670364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320716857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319070070981979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321540266275406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310835987329483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315776437520981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314129620790482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312894463539124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318246632814407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317834943532944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319481760263443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312071114778519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308365732431412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310012608766556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314541310071945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318658351898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320305168628693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322775363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309600859880447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309189170598984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32112854719162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32195195555687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326892465353012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323187112808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323598802089691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315364718437195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313306212425232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310424268245697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314952999353409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311247676610947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317011535167694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31742325425148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311659395694733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316188156604767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319893449544907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304660469293594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30877748131752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30301359295845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307542353868484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302601963281631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307954102754593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306307256221771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301778495311737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3038370013237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300955086946487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301366806030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302190214395523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313717931509018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326480686664581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328539192676544</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.340890318155289</t>
   </si>
   <si>
@@ -2579,19 +2582,19 @@
     <t xml:space="preserve">0.336361587047577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339243501424789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335126519203186</t>
+    <t xml:space="preserve">0.339243531227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335126489400864</t>
   </si>
   <si>
     <t xml:space="preserve">0.358181864023209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3470658659935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344183951616287</t>
+    <t xml:space="preserve">0.347065895795822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34418398141861</t>
   </si>
   <si>
     <t xml:space="preserve">0.336773306131363</t>
@@ -2603,37 +2606,37 @@
     <t xml:space="preserve">0.349124401807785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338008373975754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335949867963791</t>
+    <t xml:space="preserve">0.338008433580399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335949897766113</t>
   </si>
   <si>
     <t xml:space="preserve">0.343772232532501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337596744298935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340066939592361</t>
+    <t xml:space="preserve">0.337596714496613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340066909790039</t>
   </si>
   <si>
     <t xml:space="preserve">0.340478628873825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332244575023651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329362601041794</t>
+    <t xml:space="preserve">0.332244545221329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329362630844116</t>
   </si>
   <si>
     <t xml:space="preserve">0.325657337903976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338420122861862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346654206514359</t>
+    <t xml:space="preserve">0.33842009305954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346654146909714</t>
   </si>
   <si>
     <t xml:space="preserve">0.35571163892746</t>
@@ -2645,7 +2648,7 @@
     <t xml:space="preserve">0.370121240615845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377943634986877</t>
+    <t xml:space="preserve">0.377943605184555</t>
   </si>
   <si>
     <t xml:space="preserve">0.38164895772934</t>
@@ -2666,19 +2669,19 @@
     <t xml:space="preserve">0.401822417974472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411703318357468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402234137058258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403469204902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409644812345505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408409684896469</t>
+    <t xml:space="preserve">0.411703288555145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402234107255936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403469234704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409644782543182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408409655094147</t>
   </si>
   <si>
     <t xml:space="preserve">0.405939429998398</t>
@@ -2693,19 +2696,19 @@
     <t xml:space="preserve">0.397705405950546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403880953788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403057515621185</t>
+    <t xml:space="preserve">0.403880923986435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403057545423508</t>
   </si>
   <si>
     <t xml:space="preserve">0.394823461771011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417467147111893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433111876249313</t>
+    <t xml:space="preserve">0.417467176914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433111846446991</t>
   </si>
   <si>
     <t xml:space="preserve">0.430641621351242</t>
@@ -2714,58 +2717,55 @@
     <t xml:space="preserve">0.441345930099487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454520434141159</t>
+    <t xml:space="preserve">0.454520404338837</t>
   </si>
   <si>
     <t xml:space="preserve">0.442992717027664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488280087709427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503924787044525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534390866756439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518746078014374</t>
+    <t xml:space="preserve">0.488280147314072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50392484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534390807151794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518746137619019</t>
   </si>
   <si>
     <t xml:space="preserve">0.522039771080017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500631153583527</t>
+    <t xml:space="preserve">0.500631213188171</t>
   </si>
   <si>
     <t xml:space="preserve">0.517922759056091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469341725111008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485809832811356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462754428386688</t>
+    <t xml:space="preserve">0.469341814517975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485809892416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462754487991333</t>
   </si>
   <si>
     <t xml:space="preserve">0.472635358572006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49322047829628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573691368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48169282078743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467694967985153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460854530334</t>
+    <t xml:space="preserve">0.493220508098602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491573721170425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481692790985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467694938182831</t>
   </si>
   <si>
     <t xml:space="preserve">0.461107701063156</t>
@@ -2774,31 +2774,31 @@
     <t xml:space="preserve">0.476752400398254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479222625494003</t>
+    <t xml:space="preserve">0.479222655296326</t>
   </si>
   <si>
     <t xml:space="preserve">0.477575808763504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51545250415802</t>
+    <t xml:space="preserve">0.515452444553375</t>
   </si>
   <si>
     <t xml:space="preserve">0.504748165607452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501454651355743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498984426259995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494044005870819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505571722984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490750342607498</t>
+    <t xml:space="preserve">0.501454710960388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498984396457672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494043916463852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505571663379669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490750372409821</t>
   </si>
   <si>
     <t xml:space="preserve">0.484986513853073</t>
@@ -2813,31 +2813,31 @@
     <t xml:space="preserve">0.478399187326431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473458826541901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470988661050797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47016516327858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465224713087082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284322500229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46851834654808</t>
+    <t xml:space="preserve">0.473458796739578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470988541841507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470165133476257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46522468328476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284292697906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468518376350403</t>
   </si>
   <si>
     <t xml:space="preserve">0.466750353574753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473822295665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457910418510437</t>
+    <t xml:space="preserve">0.473822325468063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457910388708115</t>
   </si>
   <si>
     <t xml:space="preserve">0.461446404457092</t>
@@ -2846,16 +2846,16 @@
     <t xml:space="preserve">0.464098364114761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454374402761459</t>
+    <t xml:space="preserve">0.454374372959137</t>
   </si>
   <si>
     <t xml:space="preserve">0.441114455461502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420782506465912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435810446739197</t>
+    <t xml:space="preserve">0.420782536268234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435810476541519</t>
   </si>
   <si>
     <t xml:space="preserve">0.438462436199188</t>
@@ -2873,22 +2873,22 @@
     <t xml:space="preserve">0.448186427354813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441998451948166</t>
+    <t xml:space="preserve">0.441998422145844</t>
   </si>
   <si>
     <t xml:space="preserve">0.434484452009201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444650441408157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449070453643799</t>
+    <t xml:space="preserve">0.44465047121048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449070423841476</t>
   </si>
   <si>
     <t xml:space="preserve">0.437578469514847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43360048532486</t>
+    <t xml:space="preserve">0.433600455522537</t>
   </si>
   <si>
     <t xml:space="preserve">0.430948466062546</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">0.429622501134872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428738504648209</t>
+    <t xml:space="preserve">0.428738474845886</t>
   </si>
   <si>
     <t xml:space="preserve">0.424318492412567</t>
@@ -2924,37 +2924,37 @@
     <t xml:space="preserve">0.419456511735916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417246550321579</t>
+    <t xml:space="preserve">0.417246490716934</t>
   </si>
   <si>
     <t xml:space="preserve">0.411942541599274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414152532815933</t>
+    <t xml:space="preserve">0.414152503013611</t>
   </si>
   <si>
     <t xml:space="preserve">0.41813051700592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422550469636917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413710504770279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425202459096909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423876494169235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41459459066391</t>
+    <t xml:space="preserve">0.42255049943924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413710534572601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425202488899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423876523971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414594531059265</t>
   </si>
   <si>
     <t xml:space="preserve">0.422992497682571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421224504709244</t>
+    <t xml:space="preserve">0.421224534511566</t>
   </si>
   <si>
     <t xml:space="preserve">0.413268536329269</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">0.412384569644928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411058515310287</t>
+    <t xml:space="preserve">0.41105854511261</t>
   </si>
   <si>
     <t xml:space="preserve">0.409732550382614</t>
@@ -2978,16 +2978,16 @@
     <t xml:space="preserve">0.409290552139282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407964527606964</t>
+    <t xml:space="preserve">0.407964557409286</t>
   </si>
   <si>
     <t xml:space="preserve">0.423434495925903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42034050822258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426086515188217</t>
+    <t xml:space="preserve">0.420340478420258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426086455583572</t>
   </si>
   <si>
     <t xml:space="preserve">0.428296476602554</t>
@@ -2996,43 +2996,43 @@
     <t xml:space="preserve">0.424760520458221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42210853099823</t>
+    <t xml:space="preserve">0.422108471393585</t>
   </si>
   <si>
     <t xml:space="preserve">0.415478527545929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402218580245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39426264166832</t>
+    <t xml:space="preserve">0.402218550443649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394262611865997</t>
   </si>
   <si>
     <t xml:space="preserve">0.400008589029312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401334553956985</t>
+    <t xml:space="preserve">0.401334583759308</t>
   </si>
   <si>
     <t xml:space="preserve">0.39249461889267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396030604839325</t>
+    <t xml:space="preserve">0.396030634641647</t>
   </si>
   <si>
     <t xml:space="preserve">0.405754566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403544545173645</t>
+    <t xml:space="preserve">0.403544574975967</t>
   </si>
   <si>
     <t xml:space="preserve">0.400450587272644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389842629432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388958632946014</t>
+    <t xml:space="preserve">0.389842659235001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388958603143692</t>
   </si>
   <si>
     <t xml:space="preserve">0.395146608352661</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">0.386748641729355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393378585577011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403102546930313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396914631128311</t>
+    <t xml:space="preserve">0.393378555774689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403102576732635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396914601325989</t>
   </si>
   <si>
     <t xml:space="preserve">0.39779856801033</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">0.40177658200264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406638592481613</t>
+    <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
     <t xml:space="preserve">0.402660578489304</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">0.443766415119171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453789919614792</t>
+    <t xml:space="preserve">0.453789889812469</t>
   </si>
   <si>
     <t xml:space="preserve">0.452878683805466</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">0.453334271907806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462902188301086</t>
+    <t xml:space="preserve">0.462902158498764</t>
   </si>
   <si>
     <t xml:space="preserve">0.459257245063782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456523537635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465635806322098</t>
+    <t xml:space="preserve">0.456523567438126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465635776519775</t>
   </si>
   <si>
     <t xml:space="preserve">0.464724570512772</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">0.482949048280716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481126636266708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482037872076035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479304194450378</t>
+    <t xml:space="preserve">0.481126666069031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482037842273712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479304224252701</t>
   </si>
   <si>
     <t xml:space="preserve">0.474748075008392</t>
@@ -3125,10 +3125,10 @@
     <t xml:space="preserve">0.523042976856232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529421508312225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52577668428421</t>
+    <t xml:space="preserve">0.529421448707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525776624679565</t>
   </si>
   <si>
     <t xml:space="preserve">0.523954212665558</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753209590912</t>
+    <t xml:space="preserve">0.515753149986267</t>
   </si>
   <si>
     <t xml:space="preserve">0.507552146911621</t>
@@ -3152,37 +3152,37 @@
     <t xml:space="preserve">0.511197030544281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514841914176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519398033618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51393073797226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524865388870239</t>
+    <t xml:space="preserve">0.514841973781586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519398093223572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513930678367615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524865448474884</t>
   </si>
   <si>
     <t xml:space="preserve">0.509374618530273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526687920093536</t>
+    <t xml:space="preserve">0.526687860488892</t>
   </si>
   <si>
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267454624176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546734869480133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537622570991516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549468517303467</t>
+    <t xml:space="preserve">0.541267395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546734809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537622511386871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549468457698822</t>
   </si>
   <si>
     <t xml:space="preserve">0.554935872554779</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">0.554024577140808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564959347248077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569515466690063</t>
+    <t xml:space="preserve">0.564959287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569515407085419</t>
   </si>
   <si>
     <t xml:space="preserve">0.565870523452759</t>
@@ -3203,25 +3203,25 @@
     <t xml:space="preserve">0.562225580215454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551290988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548557221889496</t>
+    <t xml:space="preserve">0.551290929317474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548557281494141</t>
   </si>
   <si>
     <t xml:space="preserve">0.550379693508148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547646105289459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55584704875946</t>
+    <t xml:space="preserve">0.547646045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555847108364105</t>
   </si>
   <si>
     <t xml:space="preserve">0.553113341331482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564048051834106</t>
+    <t xml:space="preserve">0.564048111438751</t>
   </si>
   <si>
     <t xml:space="preserve">0.559491991996765</t>
@@ -3233,31 +3233,31 @@
     <t xml:space="preserve">0.558580696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556758284568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542178750038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557669460773468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534888863563538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528510272502899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535800158977509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530332744121552</t>
+    <t xml:space="preserve">0.556758224964142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542178690433502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557669520378113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534888923168182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528510332107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535800099372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530332803726196</t>
   </si>
   <si>
     <t xml:space="preserve">0.527599096298218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516664326190948</t>
+    <t xml:space="preserve">0.516664385795593</t>
   </si>
   <si>
     <t xml:space="preserve">0.490238875150681</t>
@@ -3269,43 +3269,43 @@
     <t xml:space="preserve">0.498439848423004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505729675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494794994592667</t>
+    <t xml:space="preserve">0.505729734897614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494794964790344</t>
   </si>
   <si>
     <t xml:space="preserve">0.499351114034653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497528702020645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492061406373978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488416403532028</t>
+    <t xml:space="preserve">0.497528672218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492061376571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488416492938995</t>
   </si>
   <si>
     <t xml:space="preserve">0.483860343694687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487505257129669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495706260204315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493883788585663</t>
+    <t xml:space="preserve">0.487505227327347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495706290006638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49388375878334</t>
   </si>
   <si>
     <t xml:space="preserve">0.491150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517575681209564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489643454551697</t>
+    <t xml:space="preserve">0.517575621604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489643424749374</t>
   </si>
   <si>
     <t xml:space="preserve">0.48199275135994</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">0.475776553153992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47673287987709</t>
+    <t xml:space="preserve">0.476732909679413</t>
   </si>
   <si>
     <t xml:space="preserve">0.480080038309097</t>
@@ -3329,31 +3329,31 @@
     <t xml:space="preserve">0.46477872133255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473385751247406</t>
+    <t xml:space="preserve">0.473385721445084</t>
   </si>
   <si>
     <t xml:space="preserve">0.469560384750366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470994919538498</t>
+    <t xml:space="preserve">0.470994889736176</t>
   </si>
   <si>
     <t xml:space="preserve">0.459040701389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453780859708786</t>
+    <t xml:space="preserve">0.453780889511108</t>
   </si>
   <si>
     <t xml:space="preserve">0.451390027999878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447564661502838</t>
+    <t xml:space="preserve">0.447564691305161</t>
   </si>
   <si>
     <t xml:space="preserve">0.45091187953949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441826701164246</t>
+    <t xml:space="preserve">0.441826671361923</t>
   </si>
   <si>
     <t xml:space="preserve">0.438479512929916</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">0.432741492986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436088651418686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438001364469528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441348493099213</t>
+    <t xml:space="preserve">0.436088681221008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438001334667206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441348522901535</t>
   </si>
   <si>
     <t xml:space="preserve">0.446608364582062</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">0.436566829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438957691192627</t>
+    <t xml:space="preserve">0.438957661390305</t>
   </si>
   <si>
     <t xml:space="preserve">0.444695681333542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439435839653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4336978495121</t>
+    <t xml:space="preserve">0.439435869455338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433697819709778</t>
   </si>
   <si>
     <t xml:space="preserve">0.434654176235199</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">0.46669140458107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454737216234207</t>
+    <t xml:space="preserve">0.454737186431885</t>
   </si>
   <si>
     <t xml:space="preserve">0.455693542957306</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">0.561368525028229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538416504859924</t>
+    <t xml:space="preserve">0.538416564464569</t>
   </si>
   <si>
     <t xml:space="preserve">0.544154524803162</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">0.540329158306122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525984168052673</t>
+    <t xml:space="preserve">0.525984108448029</t>
   </si>
   <si>
     <t xml:space="preserve">0.517377138137817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525027811527252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521202445030212</t>
+    <t xml:space="preserve">0.525027871131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521202504634857</t>
   </si>
   <si>
     <t xml:space="preserve">0.519289791584015</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">0.531722128391266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518333494663239</t>
+    <t xml:space="preserve">0.518333435058594</t>
   </si>
   <si>
     <t xml:space="preserve">0.514508128166199</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">0.527896821498871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526940524578094</t>
+    <t xml:space="preserve">0.52694046497345</t>
   </si>
   <si>
     <t xml:space="preserve">0.535547494888306</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">0.553717851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568062901496887</t>
+    <t xml:space="preserve">0.568062841892242</t>
   </si>
   <si>
     <t xml:space="preserve">0.55849951505661</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">0.555630505084991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55467414855957</t>
+    <t xml:space="preserve">0.554674208164215</t>
   </si>
   <si>
     <t xml:space="preserve">0.557543218135834</t>
@@ -3491,16 +3491,16 @@
     <t xml:space="preserve">0.54702353477478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537460088729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551805257797241</t>
+    <t xml:space="preserve">0.537460148334503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551805198192596</t>
   </si>
   <si>
     <t xml:space="preserve">0.524071455001831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533634841442108</t>
+    <t xml:space="preserve">0.533634901046753</t>
   </si>
   <si>
     <t xml:space="preserve">0.536503851413727</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">0.522158801555634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529809474945068</t>
+    <t xml:space="preserve">0.529809534549713</t>
   </si>
   <si>
     <t xml:space="preserve">0.532678484916687</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">0.499206781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496337741613388</t>
+    <t xml:space="preserve">0.49633777141571</t>
   </si>
   <si>
     <t xml:space="preserve">0.506857395172119</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">0.487730741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483905375003815</t>
+    <t xml:space="preserve">0.483905404806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.461909741163254</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">0.478167414665222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468604058027267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471473038196564</t>
+    <t xml:space="preserve">0.46860408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471473067998886</t>
   </si>
   <si>
     <t xml:space="preserve">0.48260822892189</t>
@@ -3975,6 +3975,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.558000028133392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549000024795532</t>
   </si>
 </sst>
 </file>
@@ -49675,7 +49678,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1745" t="s">
-        <v>770</v>
+        <v>851</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49701,7 +49704,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1746" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49727,7 +49730,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1747" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49805,7 +49808,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1750" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49831,7 +49834,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G1751" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49857,7 +49860,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1752" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49883,7 +49886,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1753" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49909,7 +49912,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1754" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49935,7 +49938,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1755" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49961,7 +49964,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1756" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49987,7 +49990,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1757" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50013,7 +50016,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1758" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -50065,7 +50068,7 @@
         <v>0.41949999332428</v>
       </c>
       <c r="G1760" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50091,7 +50094,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1761" t="s">
-        <v>770</v>
+        <v>851</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50117,7 +50120,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1762" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50169,7 +50172,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1764" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -50195,7 +50198,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1765" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50221,7 +50224,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1766" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -50247,7 +50250,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1767" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50273,7 +50276,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1768" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -50299,7 +50302,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1769" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -50325,7 +50328,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1770" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50351,7 +50354,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1771" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50403,7 +50406,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1773" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50429,7 +50432,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1774" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50455,7 +50458,7 @@
         <v>0.403499990701675</v>
       </c>
       <c r="G1775" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50507,7 +50510,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1777" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50533,7 +50536,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1778" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50585,7 +50588,7 @@
         <v>0.395500004291534</v>
       </c>
       <c r="G1780" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50637,7 +50640,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1782" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50663,7 +50666,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1783" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50689,7 +50692,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1784" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50715,7 +50718,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1785" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50741,7 +50744,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1786" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50767,7 +50770,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1787" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50819,7 +50822,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1789" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50845,7 +50848,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1790" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50871,7 +50874,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1791" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50897,7 +50900,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1792" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50949,7 +50952,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50975,7 +50978,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1795" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -51001,7 +51004,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1796" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -51027,7 +51030,7 @@
         <v>0.449499994516373</v>
       </c>
       <c r="G1797" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51053,7 +51056,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G1798" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51079,7 +51082,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1799" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51105,7 +51108,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G1800" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -51131,7 +51134,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1801" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -51157,7 +51160,7 @@
         <v>0.485500007867813</v>
       </c>
       <c r="G1802" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -51183,7 +51186,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1803" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51209,7 +51212,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1804" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -51235,7 +51238,7 @@
         <v>0.5</v>
       </c>
       <c r="G1805" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -51261,7 +51264,7 @@
         <v>0.488499999046326</v>
       </c>
       <c r="G1806" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51287,7 +51290,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -51313,7 +51316,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G1808" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51339,7 +51342,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1809" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51365,7 +51368,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1810" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51391,7 +51394,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1811" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51417,7 +51420,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1812" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51443,7 +51446,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1813" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51469,7 +51472,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1814" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51495,7 +51498,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1815" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51521,7 +51524,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1816" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51547,7 +51550,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1817" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51573,7 +51576,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1818" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51599,7 +51602,7 @@
         <v>0.489499986171722</v>
       </c>
       <c r="G1819" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51625,7 +51628,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1820" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51651,7 +51654,7 @@
         <v>0.5</v>
       </c>
       <c r="G1821" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51677,7 +51680,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1822" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51703,7 +51706,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1823" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51729,7 +51732,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1824" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51755,7 +51758,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1825" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51781,7 +51784,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1826" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51807,7 +51810,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1827" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51833,7 +51836,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G1828" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51859,7 +51862,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1829" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51885,7 +51888,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G1830" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51911,7 +51914,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1831" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51937,7 +51940,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1832" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51963,7 +51966,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1833" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51989,7 +51992,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G1834" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -52015,7 +52018,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1835" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52041,7 +52044,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1836" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52067,7 +52070,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1837" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52093,7 +52096,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1838" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -52119,7 +52122,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1839" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -52145,7 +52148,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1840" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52171,7 +52174,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G1841" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52197,7 +52200,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1842" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52223,7 +52226,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1843" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52249,7 +52252,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1844" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52275,7 +52278,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1845" t="s">
-        <v>917</v>
+        <v>363</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52353,7 +52356,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1848" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52457,7 +52460,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1852" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52847,7 +52850,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1867" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52899,7 +52902,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1869" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52951,7 +52954,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1871" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53003,7 +53006,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1873" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53081,7 +53084,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>917</v>
+        <v>363</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -69391,7 +69394,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6910300926</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>188368</v>
@@ -69412,6 +69415,32 @@
         <v>1320</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6914814815</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>367143</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>0.560999989509583</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>0.546999990940094</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>0.549000024795532</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1321</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327446222305298</t>
+    <t xml:space="preserve">0.327446281909943</t>
   </si>
   <si>
     <t xml:space="preserve">0.321156293153763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317678362131119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307318449020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288448721170425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289336711168289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294368654489517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285636752843857</t>
+    <t xml:space="preserve">0.317678391933441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307318478822708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288448691368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289336681365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294368624687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285636723041534</t>
   </si>
   <si>
     <t xml:space="preserve">0.273796856403351</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">0.258997023105621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258257031440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243605226278305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246417179703712</t>
+    <t xml:space="preserve">0.258257061243057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243605196475983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246417164802551</t>
   </si>
   <si>
     <t xml:space="preserve">0.262696981430054</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">0.253817081451416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25307708978653</t>
+    <t xml:space="preserve">0.253077119588852</t>
   </si>
   <si>
     <t xml:space="preserve">0.286894679069519</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">0.284600764513016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277496844530106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28711673617363</t>
+    <t xml:space="preserve">0.277496784925461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287116706371307</t>
   </si>
   <si>
     <t xml:space="preserve">0.290742665529251</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">0.263806998729706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256777077913284</t>
+    <t xml:space="preserve">0.256777048110962</t>
   </si>
   <si>
     <t xml:space="preserve">0.250117152929306</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">0.310796439647675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303544491529465</t>
+    <t xml:space="preserve">0.303544521331787</t>
   </si>
   <si>
     <t xml:space="preserve">0.304358512163162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318122357130051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309686452150345</t>
+    <t xml:space="preserve">0.318122327327728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309686481952667</t>
   </si>
   <si>
     <t xml:space="preserve">0.301620543003082</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">0.323376297950745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320046335458755</t>
+    <t xml:space="preserve">0.320046365261078</t>
   </si>
   <si>
     <t xml:space="preserve">0.316716372966766</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">0.315236419439316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315606415271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332996189594269</t>
+    <t xml:space="preserve">0.315606385469437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332996159791946</t>
   </si>
   <si>
     <t xml:space="preserve">0.332256227731705</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">0.330480217933655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311240404844284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312054425477982</t>
+    <t xml:space="preserve">0.311240434646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312054395675659</t>
   </si>
   <si>
     <t xml:space="preserve">0.299696564674377</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">0.296884596347809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299400568008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297476589679718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295996606349945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293702632188797</t>
+    <t xml:space="preserve">0.2994005382061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29747661948204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295996636152267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293702661991119</t>
   </si>
   <si>
     <t xml:space="preserve">0.298216581344604</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">0.276756823062897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274536848068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272316873073578</t>
+    <t xml:space="preserve">0.27453687787056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2723169028759</t>
   </si>
   <si>
     <t xml:space="preserve">0.268542915582657</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">0.270466923713684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26506495475769</t>
+    <t xml:space="preserve">0.265065014362335</t>
   </si>
   <si>
     <t xml:space="preserve">0.268172949552536</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">0.268616914749146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269208878278732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275276839733124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28489676117897</t>
+    <t xml:space="preserve">0.269208908081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275276869535446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284896731376648</t>
   </si>
   <si>
     <t xml:space="preserve">0.290002673864365</t>
@@ -248,22 +248,22 @@
     <t xml:space="preserve">0.308206468820572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309168517589569</t>
+    <t xml:space="preserve">0.309168487787247</t>
   </si>
   <si>
     <t xml:space="preserve">0.318196386098862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31693834066391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308946460485458</t>
+    <t xml:space="preserve">0.316938370466232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308946430683136</t>
   </si>
   <si>
     <t xml:space="preserve">0.314200401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321378290653229</t>
+    <t xml:space="preserve">0.321378320455551</t>
   </si>
   <si>
     <t xml:space="preserve">0.319380342960358</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">0.313682407140732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313312411308289</t>
+    <t xml:space="preserve">0.313312441110611</t>
   </si>
   <si>
     <t xml:space="preserve">0.307096481323242</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">0.30761444568634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304950475692749</t>
+    <t xml:space="preserve">0.304950505495071</t>
   </si>
   <si>
     <t xml:space="preserve">0.305616468191147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299548596143723</t>
+    <t xml:space="preserve">0.2995485663414</t>
   </si>
   <si>
     <t xml:space="preserve">0.305320501327515</t>
@@ -299,85 +299,85 @@
     <t xml:space="preserve">0.295626610517502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300954550504684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314400345087051</t>
+    <t xml:space="preserve">0.300954520702362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314400285482407</t>
   </si>
   <si>
     <t xml:space="preserve">0.318779796361923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318856596946716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318395644426346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319932252168655</t>
+    <t xml:space="preserve">0.318856626749039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318395614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319932281970978</t>
   </si>
   <si>
     <t xml:space="preserve">0.318088293075562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307331681251526</t>
+    <t xml:space="preserve">0.307331711053848</t>
   </si>
   <si>
     <t xml:space="preserve">0.321776270866394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320393294095993</t>
+    <t xml:space="preserve">0.320393264293671</t>
   </si>
   <si>
     <t xml:space="preserve">0.311557501554489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305795013904572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301569253206253</t>
+    <t xml:space="preserve">0.305795043706894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301569193601608</t>
   </si>
   <si>
     <t xml:space="preserve">0.295806735754013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299648374319077</t>
+    <t xml:space="preserve">0.299648404121399</t>
   </si>
   <si>
     <t xml:space="preserve">0.296575099229813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303490042686462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314246654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318011432886124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318702936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32116162776947</t>
+    <t xml:space="preserve">0.303490072488785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31424668431282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318011462688446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318702965974808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321161597967148</t>
   </si>
   <si>
     <t xml:space="preserve">0.310020834207535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311941623687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311173349618912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307254821062088</t>
+    <t xml:space="preserve">0.311941653490067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311173319816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307254880666733</t>
   </si>
   <si>
     <t xml:space="preserve">0.30671700835228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305564522743225</t>
+    <t xml:space="preserve">0.305564552545547</t>
   </si>
   <si>
     <t xml:space="preserve">0.304949879646301</t>
@@ -395,22 +395,22 @@
     <t xml:space="preserve">0.304027885198593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300032526254654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313478320837021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31255629658699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307869493961334</t>
+    <t xml:space="preserve">0.300032585859299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313478350639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312556326389313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307869523763657</t>
   </si>
   <si>
     <t xml:space="preserve">0.311480671167374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298265427350998</t>
+    <t xml:space="preserve">0.298265397548676</t>
   </si>
   <si>
     <t xml:space="preserve">0.299110531806946</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">0.297650724649429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297881186008453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29373225569725</t>
+    <t xml:space="preserve">0.297881215810776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293732225894928</t>
   </si>
   <si>
     <t xml:space="preserve">0.298803240060806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300416737794876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300109416246414</t>
+    <t xml:space="preserve">0.300416707992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300109386444092</t>
   </si>
   <si>
     <t xml:space="preserve">0.298880070447922</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">0.309559851884842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303105860948563</t>
+    <t xml:space="preserve">0.30310583114624</t>
   </si>
   <si>
     <t xml:space="preserve">0.303566873073578</t>
@@ -467,28 +467,28 @@
     <t xml:space="preserve">0.306563347578049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300186216831207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298649609088898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296421378850937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3014155626297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3006471991539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282975643873215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29196509718895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289736956357956</t>
+    <t xml:space="preserve">0.30018624663353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298649579286575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296421408653259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301415532827377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300647228956223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282975614070892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291965126991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289736926555634</t>
   </si>
   <si>
     <t xml:space="preserve">0.293501764535904</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">0.29250293970108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289583295583725</t>
+    <t xml:space="preserve">0.289583265781403</t>
   </si>
   <si>
     <t xml:space="preserve">0.288123458623886</t>
@@ -512,37 +512,37 @@
     <t xml:space="preserve">0.28789296746254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290044248104095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292887091636658</t>
+    <t xml:space="preserve">0.290044277906418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292887061834335</t>
   </si>
   <si>
     <t xml:space="preserve">0.293117582798004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291888296604156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289813756942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286586821079254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294270068407059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291811406612396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292579770088196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29572993516922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298419058322906</t>
+    <t xml:space="preserve">0.291888266801834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289813786745071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286586791276932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294270098209381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291811436414719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292579799890518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295729905366898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298419028520584</t>
   </si>
   <si>
     <t xml:space="preserve">0.294731050729752</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">0.293809086084366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292041957378387</t>
+    <t xml:space="preserve">0.292041927576065</t>
   </si>
   <si>
     <t xml:space="preserve">0.286740452051163</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">0.2846659719944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278903543949127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27559968829155</t>
+    <t xml:space="preserve">0.278903514146805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275599718093872</t>
   </si>
   <si>
     <t xml:space="preserve">0.270221382379532</t>
@@ -578,34 +578,34 @@
     <t xml:space="preserve">0.276675343513489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273986160755157</t>
+    <t xml:space="preserve">0.27398619055748</t>
   </si>
   <si>
     <t xml:space="preserve">0.275676518678665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275522857904434</t>
+    <t xml:space="preserve">0.275522828102112</t>
   </si>
   <si>
     <t xml:space="preserve">0.276598513126373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270989686250687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271143406629562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274293512105942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270451903343201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268146902322769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267378568649292</t>
+    <t xml:space="preserve">0.270989716053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27114337682724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274293541908264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270451873540878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268146872520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26737853884697</t>
   </si>
   <si>
     <t xml:space="preserve">0.264612585306168</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">0.262384444475174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267532259225845</t>
+    <t xml:space="preserve">0.267532199621201</t>
   </si>
   <si>
     <t xml:space="preserve">0.265304088592529</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">0.271911710500717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272526353597641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283282965421677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279902338981628</t>
+    <t xml:space="preserve">0.272526383399963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283283025026321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279902309179306</t>
   </si>
   <si>
     <t xml:space="preserve">0.277059525251389</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">0.27844250202179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280517011880875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278749853372574</t>
+    <t xml:space="preserve">0.280516982078552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278749823570251</t>
   </si>
   <si>
     <t xml:space="preserve">0.27898034453392</t>
@@ -656,16 +656,16 @@
     <t xml:space="preserve">0.284051328897476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290812641382217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289660096168518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290428459644318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294807910919189</t>
+    <t xml:space="preserve">0.290812611579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28966012597084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290428429841995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294807940721512</t>
   </si>
   <si>
     <t xml:space="preserve">0.295422583818436</t>
@@ -677,46 +677,46 @@
     <t xml:space="preserve">0.284589171409607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291043132543564</t>
+    <t xml:space="preserve">0.291043102741241</t>
   </si>
   <si>
     <t xml:space="preserve">0.293885916471481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294884741306305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289890646934509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286125779151917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284358620643616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282745122909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27729007601738</t>
+    <t xml:space="preserve">0.294884771108627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289890617132187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286125808954239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284358650445938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282745152711868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277290046215057</t>
   </si>
   <si>
     <t xml:space="preserve">0.281976819038391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276214361190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27360200881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269760370254517</t>
+    <t xml:space="preserve">0.276214331388474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273602038621902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269760340452194</t>
   </si>
   <si>
     <t xml:space="preserve">0.275061845779419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271834850311279</t>
+    <t xml:space="preserve">0.271834880113602</t>
   </si>
   <si>
     <t xml:space="preserve">0.273371547460556</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">0.275215536355972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276905834674835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274831354618073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282668322324753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280440181493759</t>
+    <t xml:space="preserve">0.276905864477158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274831384420395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282668352127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280440151691437</t>
   </si>
   <si>
     <t xml:space="preserve">0.279595017433167</t>
@@ -743,22 +743,22 @@
     <t xml:space="preserve">0.277366816997528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278135180473328</t>
+    <t xml:space="preserve">0.278135150671005</t>
   </si>
   <si>
     <t xml:space="preserve">0.281208485364914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278672963380814</t>
+    <t xml:space="preserve">0.278672993183136</t>
   </si>
   <si>
     <t xml:space="preserve">0.282591491937637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27936452627182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285587936639786</t>
+    <t xml:space="preserve">0.279364496469498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285587996244431</t>
   </si>
   <si>
     <t xml:space="preserve">0.27967181801796</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">0.28666365146637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284435480833054</t>
+    <t xml:space="preserve">0.284435451030731</t>
   </si>
   <si>
     <t xml:space="preserve">0.281899988651276</t>
@@ -782,40 +782,40 @@
     <t xml:space="preserve">0.285434275865555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295038402080536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304258346557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321929901838303</t>
+    <t xml:space="preserve">0.295038461685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30425837635994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321929961442947</t>
   </si>
   <si>
     <t xml:space="preserve">0.325617909431458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33184140920639</t>
+    <t xml:space="preserve">0.331841379404068</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387448072433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316935777664185</t>
+    <t xml:space="preserve">0.316935807466507</t>
   </si>
   <si>
     <t xml:space="preserve">0.309790313243866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30925253033638</t>
+    <t xml:space="preserve">0.309252500534058</t>
   </si>
   <si>
     <t xml:space="preserve">0.311096489429474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313094168901443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313017308712006</t>
+    <t xml:space="preserve">0.313094139099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31301736831665</t>
   </si>
   <si>
     <t xml:space="preserve">0.288891792297363</t>
@@ -824,16 +824,16 @@
     <t xml:space="preserve">0.293040752410889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295192092657089</t>
+    <t xml:space="preserve">0.295192062854767</t>
   </si>
   <si>
     <t xml:space="preserve">0.296805560588837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297266602516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298111736774445</t>
+    <t xml:space="preserve">0.297266572713852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298111766576767</t>
   </si>
   <si>
     <t xml:space="preserve">0.310251355171204</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">0.300800889730453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30886834859848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299725234508514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321853131055832</t>
+    <t xml:space="preserve">0.308868378400803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299725204706192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32185310125351</t>
   </si>
   <si>
     <t xml:space="preserve">0.327308237552643</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">0.318472445011139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31209534406662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314016133546829</t>
+    <t xml:space="preserve">0.312095284461975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314016193151474</t>
   </si>
   <si>
     <t xml:space="preserve">0.315014988183975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312249004840851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313939332962036</t>
+    <t xml:space="preserve">0.312248975038528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313939303159714</t>
   </si>
   <si>
     <t xml:space="preserve">0.309636652469635</t>
@@ -881,22 +881,22 @@
     <t xml:space="preserve">0.307408511638641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308945149183273</t>
+    <t xml:space="preserve">0.308945178985596</t>
   </si>
   <si>
     <t xml:space="preserve">0.313631981611252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308023184537888</t>
+    <t xml:space="preserve">0.30802321434021</t>
   </si>
   <si>
     <t xml:space="preserve">0.307715862989426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309022039175034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309943974018097</t>
+    <t xml:space="preserve">0.309022009372711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309944003820419</t>
   </si>
   <si>
     <t xml:space="preserve">0.3177809715271</t>
@@ -905,28 +905,28 @@
     <t xml:space="preserve">0.31655165553093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316474854946136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32438862323761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325003236532211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31831881403923</t>
+    <t xml:space="preserve">0.316474795341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324388593435287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325003296136856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318318784236908</t>
   </si>
   <si>
     <t xml:space="preserve">0.317704141139984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32154580950737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320470124483109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621464729309</t>
+    <t xml:space="preserve">0.321545779705048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320470154285431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621434926987</t>
   </si>
   <si>
     <t xml:space="preserve">0.323697090148926</t>
@@ -938,34 +938,34 @@
     <t xml:space="preserve">0.327385067939758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33176451921463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33952471613884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34567129611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340446680784225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3333780169487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33499151468277</t>
+    <t xml:space="preserve">0.331764549016953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339524686336517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345671325922012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340446710586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333378046751022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334991544485092</t>
   </si>
   <si>
     <t xml:space="preserve">0.336144030094147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337757498025894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338910013437271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338141679763794</t>
+    <t xml:space="preserve">0.337757527828217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338910043239594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338141649961472</t>
   </si>
   <si>
     <t xml:space="preserve">0.339678347110748</t>
@@ -980,76 +980,76 @@
     <t xml:space="preserve">0.344211518764496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340677112340927</t>
+    <t xml:space="preserve">0.340677171945572</t>
   </si>
   <si>
     <t xml:space="preserve">0.334607362747192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338218539953232</t>
+    <t xml:space="preserve">0.338218569755554</t>
   </si>
   <si>
     <t xml:space="preserve">0.346900641918182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346132338047028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339601457118988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340907663106918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352663099765778</t>
+    <t xml:space="preserve">0.346132308244705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33960148692131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340907692909241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3526631295681</t>
   </si>
   <si>
     <t xml:space="preserve">0.369950503110886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365417391061783</t>
+    <t xml:space="preserve">0.36541736125946</t>
   </si>
   <si>
     <t xml:space="preserve">0.363035559654236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374099463224411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371103048324585</t>
+    <t xml:space="preserve">0.374099493026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371103018522263</t>
   </si>
   <si>
     <t xml:space="preserve">0.369566351175308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368798047304153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366108894348145</t>
+    <t xml:space="preserve">0.368797987699509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366108864545822</t>
   </si>
   <si>
     <t xml:space="preserve">0.363112390041351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3686443567276</t>
+    <t xml:space="preserve">0.368644326925278</t>
   </si>
   <si>
     <t xml:space="preserve">0.366877198219299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366262525320053</t>
+    <t xml:space="preserve">0.366262555122375</t>
   </si>
   <si>
     <t xml:space="preserve">0.361114740371704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359885454177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359193921089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368567526340485</t>
+    <t xml:space="preserve">0.359885424375534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35919389128685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368567496538162</t>
   </si>
   <si>
     <t xml:space="preserve">0.372024983167648</t>
@@ -1064,28 +1064,28 @@
     <t xml:space="preserve">0.392616212368011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405677825212479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421044409275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419507712125778</t>
+    <t xml:space="preserve">0.405677795410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421044379472733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419507771730423</t>
   </si>
   <si>
     <t xml:space="preserve">0.396842062473297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413361102342606</t>
+    <t xml:space="preserve">0.41336116194725</t>
   </si>
   <si>
     <t xml:space="preserve">0.422581106424332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417586892843246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42642268538475</t>
+    <t xml:space="preserve">0.417586922645569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426422715187073</t>
   </si>
   <si>
     <t xml:space="preserve">0.423349380493164</t>
@@ -1094,28 +1094,28 @@
     <t xml:space="preserve">0.427959382534027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436795115470886</t>
+    <t xml:space="preserve">0.436795145273209</t>
   </si>
   <si>
     <t xml:space="preserve">0.432953506708145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45293003320694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460854530334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46522331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296617269516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481358289718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522463917732239</t>
+    <t xml:space="preserve">0.452930063009262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460824728012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465223342180252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296647071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481358259916306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522463858127594</t>
   </si>
   <si>
     <t xml:space="preserve">0.515164732933044</t>
@@ -1124,43 +1124,43 @@
     <t xml:space="preserve">0.505560576915741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50709730386734</t>
+    <t xml:space="preserve">0.507097244262695</t>
   </si>
   <si>
     <t xml:space="preserve">0.515548884868622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503255605697632</t>
+    <t xml:space="preserve">0.503255665302277</t>
   </si>
   <si>
     <t xml:space="preserve">0.48980987071991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480205714702606</t>
+    <t xml:space="preserve">0.480205744504929</t>
   </si>
   <si>
     <t xml:space="preserve">0.519006371498108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511323034763336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499413996934891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491730690002441</t>
+    <t xml:space="preserve">0.511323094367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499413907527924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491730719804764</t>
   </si>
   <si>
     <t xml:space="preserve">0.484431564807892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483663231134415</t>
+    <t xml:space="preserve">0.483663201332092</t>
   </si>
   <si>
     <t xml:space="preserve">0.484815776348114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49518820643425</t>
+    <t xml:space="preserve">0.495188236236572</t>
   </si>
   <si>
     <t xml:space="preserve">0.490194082260132</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">0.553197026252747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542056262493134</t>
+    <t xml:space="preserve">0.542056202888489</t>
   </si>
   <si>
     <t xml:space="preserve">0.56280118227005</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">0.586235165596008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600065052509308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58239358663559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572021067142487</t>
+    <t xml:space="preserve">0.600065171718597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582393527030945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572021126747131</t>
   </si>
   <si>
     <t xml:space="preserve">0.572789430618286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552428722381592</t>
+    <t xml:space="preserve">0.552428662776947</t>
   </si>
   <si>
     <t xml:space="preserve">0.55127614736557</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">0.545129597187042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565874457359314</t>
+    <t xml:space="preserve">0.565874516963959</t>
   </si>
   <si>
     <t xml:space="preserve">0.577015221118927</t>
@@ -1208,49 +1208,49 @@
     <t xml:space="preserve">0.596607625484467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584698498249054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608132541179657</t>
+    <t xml:space="preserve">0.584698557853699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608132481575012</t>
   </si>
   <si>
     <t xml:space="preserve">0.621962487697601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620425879955292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629645824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614279210567474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607748448848724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581625282764435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560880362987518</t>
+    <t xml:space="preserve">0.620425820350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629645764827728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61427915096283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60774838924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58162522315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560880303382874</t>
   </si>
   <si>
     <t xml:space="preserve">0.598528444766998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598144233226776</t>
+    <t xml:space="preserve">0.598144292831421</t>
   </si>
   <si>
     <t xml:space="preserve">0.619657516479492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618120789527893</t>
+    <t xml:space="preserve">0.618120849132538</t>
   </si>
   <si>
     <t xml:space="preserve">0.601601779460907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58661937713623</t>
+    <t xml:space="preserve">0.586619317531586</t>
   </si>
   <si>
     <t xml:space="preserve">0.59545511007309</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">0.584314405918121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577399373054504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567026913166046</t>
+    <t xml:space="preserve">0.577399432659149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567026972770691</t>
   </si>
   <si>
     <t xml:space="preserve">0.57432609796524</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">0.543592870235443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564721941947937</t>
+    <t xml:space="preserve">0.564722001552582</t>
   </si>
   <si>
     <t xml:space="preserve">0.563185334205627</t>
@@ -1283,64 +1283,64 @@
     <t xml:space="preserve">0.576246917247772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583930194377899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580856919288635</t>
+    <t xml:space="preserve">0.583930253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58085685968399</t>
   </si>
   <si>
     <t xml:space="preserve">0.587003529071808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604675054550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629261553287506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61850506067276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606980085372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603138506412506</t>
+    <t xml:space="preserve">0.604675114154816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629261672496796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618505001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60698014497757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603138387203217</t>
   </si>
   <si>
     <t xml:space="preserve">0.612358331680298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611590027809143</t>
+    <t xml:space="preserve">0.611590087413788</t>
   </si>
   <si>
     <t xml:space="preserve">0.59391850233078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596991777420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608516693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599296748638153</t>
+    <t xml:space="preserve">0.596991837024689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608516752719879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599296808242798</t>
   </si>
   <si>
     <t xml:space="preserve">0.589308559894562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553965330123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538598656654358</t>
+    <t xml:space="preserve">0.553965389728546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538598835468292</t>
   </si>
   <si>
     <t xml:space="preserve">0.557038724422455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536293804645538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524000465869904</t>
+    <t xml:space="preserve">0.536293745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524000525474548</t>
   </si>
   <si>
     <t xml:space="preserve">0.537830412387848</t>
@@ -1349,31 +1349,31 @@
     <t xml:space="preserve">0.547818720340729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53245210647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537062227725983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527073860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52092719078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517853856086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525537192821503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530147075653076</t>
+    <t xml:space="preserve">0.532452166080475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537062048912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527073800563812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520927131175995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517853915691376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525537073612213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530147194862366</t>
   </si>
   <si>
     <t xml:space="preserve">0.523232221603394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51939058303833</t>
+    <t xml:space="preserve">0.519390523433685</t>
   </si>
   <si>
     <t xml:space="preserve">0.524768888950348</t>
@@ -1382,25 +1382,25 @@
     <t xml:space="preserve">0.549355387687683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501718938350677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492498993873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477900773286819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476364135742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48865732550621</t>
+    <t xml:space="preserve">0.501718997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492499023675919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477900743484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47636416554451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488657355308533</t>
   </si>
   <si>
     <t xml:space="preserve">0.471754133701324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472522497177124</t>
+    <t xml:space="preserve">0.472522467374802</t>
   </si>
   <si>
     <t xml:space="preserve">0.468680799007416</t>
@@ -1409,34 +1409,34 @@
     <t xml:space="preserve">0.487120717763901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481742411851883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480974018573761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483279079198837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478669136762619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470217496156693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467912554740906</t>
+    <t xml:space="preserve">0.481742471456528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480974048376083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48327910900116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478669106960297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47021746635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467912524938583</t>
   </si>
   <si>
     <t xml:space="preserve">0.466375797986984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464839190244675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461765885353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487889111042023</t>
+    <t xml:space="preserve">0.464839160442352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461765855550766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487889051437378</t>
   </si>
   <si>
     <t xml:space="preserve">0.500182390213013</t>
@@ -1445,43 +1445,43 @@
     <t xml:space="preserve">0.469449132680893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437179356813431</t>
+    <t xml:space="preserve">0.437179297208786</t>
   </si>
   <si>
     <t xml:space="preserve">0.444862574338913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431801021099091</t>
+    <t xml:space="preserve">0.431800931692123</t>
   </si>
   <si>
     <t xml:space="preserve">0.444094240665436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424117684364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415666133165359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382627934217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379170477390289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382243812084198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385701239109039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388774544000626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391847908496857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38416463136673</t>
+    <t xml:space="preserve">0.424117714166641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415666103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382627964019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379170447587967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382243782281876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385701268911362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38877460360527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391847848892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384164601564407</t>
   </si>
   <si>
     <t xml:space="preserve">0.37648132443428</t>
@@ -1490,16 +1490,16 @@
     <t xml:space="preserve">0.367261350154877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364956378936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360346406698227</t>
+    <t xml:space="preserve">0.364956349134445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360346436500549</t>
   </si>
   <si>
     <t xml:space="preserve">0.3522789478302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356504768133163</t>
+    <t xml:space="preserve">0.356504738330841</t>
   </si>
   <si>
     <t xml:space="preserve">0.37148717045784</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">0.372255504131317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365340501070023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374944657087326</t>
+    <t xml:space="preserve">0.365340530872345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374944686889648</t>
   </si>
   <si>
     <t xml:space="preserve">0.3664930164814</t>
@@ -1523,19 +1523,19 @@
     <t xml:space="preserve">0.374560475349426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374176323413849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378786265850067</t>
+    <t xml:space="preserve">0.374176293611526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37878629565239</t>
   </si>
   <si>
     <t xml:space="preserve">0.362267196178436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353815615177155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354583919048309</t>
+    <t xml:space="preserve">0.353815585374832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354583889245987</t>
   </si>
   <si>
     <t xml:space="preserve">0.353047281503677</t>
@@ -1544,16 +1544,16 @@
     <t xml:space="preserve">0.370718836784363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354199767112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395689576864243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411056190729141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407982856035233</t>
+    <t xml:space="preserve">0.35419973731041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395689517259598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411056131124496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40798282623291</t>
   </si>
   <si>
     <t xml:space="preserve">0.384932905435562</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">0.380707114934921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362651377916336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35957807302475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353431463241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349589765071869</t>
+    <t xml:space="preserve">0.362651407718658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359578043222427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353431433439255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349589824676514</t>
   </si>
   <si>
     <t xml:space="preserve">0.344979822635651</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">0.343059003353119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354968100786209</t>
+    <t xml:space="preserve">0.354968130588531</t>
   </si>
   <si>
     <t xml:space="preserve">0.36418804526329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357273101806641</t>
+    <t xml:space="preserve">0.357273072004318</t>
   </si>
   <si>
     <t xml:space="preserve">0.349973946809769</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">0.339217334985733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323850780725479</t>
+    <t xml:space="preserve">0.323850750923157</t>
   </si>
   <si>
     <t xml:space="preserve">0.361883044242859</t>
@@ -1619,37 +1619,37 @@
     <t xml:space="preserve">0.396457880735397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412592828273773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404909491539001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401836186647415</t>
+    <t xml:space="preserve">0.412592798471451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404909551143646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401836156845093</t>
   </si>
   <si>
     <t xml:space="preserve">0.394152909517288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399531126022339</t>
+    <t xml:space="preserve">0.399531185626984</t>
   </si>
   <si>
     <t xml:space="preserve">0.40260449051857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40106788277626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397994577884674</t>
+    <t xml:space="preserve">0.401067852973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397994548082352</t>
   </si>
   <si>
     <t xml:space="preserve">0.375712960958481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36457222700119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345748126506805</t>
+    <t xml:space="preserve">0.364572197198868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345748156309128</t>
   </si>
   <si>
     <t xml:space="preserve">0.336528182029724</t>
@@ -1658,64 +1658,64 @@
     <t xml:space="preserve">0.335759878158569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337296515703201</t>
+    <t xml:space="preserve">0.337296545505524</t>
   </si>
   <si>
     <t xml:space="preserve">0.329613238573074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32807657122612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331534057855606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319240808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326924055814743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312709987163544</t>
+    <t xml:space="preserve">0.328076601028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331534028053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319240778684616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326924115419388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312710016965866</t>
   </si>
   <si>
     <t xml:space="preserve">0.341138184070587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322698265314102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326155722141266</t>
+    <t xml:space="preserve">0.322698295116425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326155692338943</t>
   </si>
   <si>
     <t xml:space="preserve">0.324619084596634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325771600008011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330381602048874</t>
+    <t xml:space="preserve">0.325771570205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330381572246552</t>
   </si>
   <si>
     <t xml:space="preserve">0.329997420310974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324234962463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313862502574921</t>
+    <t xml:space="preserve">0.324234932661057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313862442970276</t>
   </si>
   <si>
     <t xml:space="preserve">0.301185041666031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303874224424362</t>
+    <t xml:space="preserve">0.30387419462204</t>
   </si>
   <si>
     <t xml:space="preserve">0.29695925116539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302721709012985</t>
+    <t xml:space="preserve">0.302721738815308</t>
   </si>
   <si>
     <t xml:space="preserve">0.32308241724968</t>
@@ -1724,22 +1724,22 @@
     <t xml:space="preserve">0.308100014925003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310404986143112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306947529315948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314630776643753</t>
+    <t xml:space="preserve">0.310405015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306947499513626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314630836248398</t>
   </si>
   <si>
     <t xml:space="preserve">0.305410861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308484137058258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304642528295517</t>
+    <t xml:space="preserve">0.30848416686058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304642498493195</t>
   </si>
   <si>
     <t xml:space="preserve">0.320777416229248</t>
@@ -1748,16 +1748,16 @@
     <t xml:space="preserve">0.356888920068741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358041375875473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356120586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360730588436127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358809798955917</t>
+    <t xml:space="preserve">0.358041405677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356120556592941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360730558633804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35880970954895</t>
   </si>
   <si>
     <t xml:space="preserve">0.351126462221146</t>
@@ -1772,37 +1772,37 @@
     <t xml:space="preserve">0.37187135219574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370334655046463</t>
+    <t xml:space="preserve">0.370334684848785</t>
   </si>
   <si>
     <t xml:space="preserve">0.38378044962883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376097172498703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376865446567535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377249658107758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398762881755829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403372824192047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406446129083633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40951943397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391079545021057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381475448608398</t>
+    <t xml:space="preserve">0.376097142696381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376865476369858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377249628305435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398762851953506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40337285399437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406446158885956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409519463777542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391079604625702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381475418806076</t>
   </si>
   <si>
     <t xml:space="preserve">0.407214462757111</t>
@@ -1811,34 +1811,34 @@
     <t xml:space="preserve">0.387237936258316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394921183586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411824434995651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41489776968956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417202740907669</t>
+    <t xml:space="preserve">0.394921213388443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411824405193329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414897829294205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417202711105347</t>
   </si>
   <si>
     <t xml:space="preserve">0.397226184606552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408751159906387</t>
+    <t xml:space="preserve">0.408751130104065</t>
   </si>
   <si>
     <t xml:space="preserve">0.410287797451019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414129436016083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416434437036514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418739408254623</t>
+    <t xml:space="preserve">0.41412940621376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416434466838837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418739438056946</t>
   </si>
   <si>
     <t xml:space="preserve">0.420276045799255</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">0.421812742948532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430264353752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473290830850601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494804054498672</t>
+    <t xml:space="preserve">0.430264323949814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473290860652924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49480402469635</t>
   </si>
   <si>
     <t xml:space="preserve">0.48404735326767</t>
@@ -1868,61 +1868,61 @@
     <t xml:space="preserve">0.479437470436096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482510805130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595712661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070856571198</t>
+    <t xml:space="preserve">0.48251074552536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595772266388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070796966553</t>
   </si>
   <si>
     <t xml:space="preserve">0.465607494115829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460997492074966</t>
+    <t xml:space="preserve">0.460997521877289</t>
   </si>
   <si>
     <t xml:space="preserve">0.453314214944839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434105962514877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789299249649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445630937814713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449472546577454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451009213924408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460229158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454082578420639</t>
+    <t xml:space="preserve">0.4341059923172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789329051971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44563090801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449472576379776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45100924372673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460229188203812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454082548618317</t>
   </si>
   <si>
     <t xml:space="preserve">0.457155913114548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45177760720253</t>
+    <t xml:space="preserve">0.451777637004852</t>
   </si>
   <si>
     <t xml:space="preserve">0.456387519836426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463302493095398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470985770225525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467144191265106</t>
+    <t xml:space="preserve">0.463302552700043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470985800027847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467144131660461</t>
   </si>
   <si>
     <t xml:space="preserve">0.457924276590347</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">0.432569354772568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43794772028923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433337688446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434874325990677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436410993337631</t>
+    <t xml:space="preserve">0.437947630882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433337718248367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434874296188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436411052942276</t>
   </si>
   <si>
     <t xml:space="preserve">0.439484298229218</t>
@@ -1952,22 +1952,22 @@
     <t xml:space="preserve">0.441020965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440252661705017</t>
+    <t xml:space="preserve">0.440252631902695</t>
   </si>
   <si>
     <t xml:space="preserve">0.438715934753418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442557632923126</t>
+    <t xml:space="preserve">0.442557573318481</t>
   </si>
   <si>
     <t xml:space="preserve">0.485584050416946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455619245767593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443325996398926</t>
+    <t xml:space="preserve">0.455619186162949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443326026201248</t>
   </si>
   <si>
     <t xml:space="preserve">0.429496020078659</t>
@@ -1976,43 +1976,43 @@
     <t xml:space="preserve">0.435642629861832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450240910053253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42719104886055</t>
+    <t xml:space="preserve">0.450240850448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427191019058228</t>
   </si>
   <si>
     <t xml:space="preserve">0.375328809022903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386469632387161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393384546041489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365724712610245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372639626264572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351510643959045</t>
+    <t xml:space="preserve">0.386469572782516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393384575843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365724742412567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372639685869217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351510584354401</t>
   </si>
   <si>
     <t xml:space="preserve">0.342674851417542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317319959402084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265073537826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259695291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23933456838131</t>
+    <t xml:space="preserve">0.317319989204407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265073597431183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259695261716843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239334553480148</t>
   </si>
   <si>
     <t xml:space="preserve">0.242023676633835</t>
@@ -2021,28 +2021,28 @@
     <t xml:space="preserve">0.234724566340446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245865345001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258926928043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.251627802848816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266610234975815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269299328327179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258158624172211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.251243680715561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.252011984586716</t>
+    <t xml:space="preserve">0.245865359902382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258926957845688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.251627832651138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266610264778137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269299417734146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258158594369888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.251243650913239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.252011954784393</t>
   </si>
   <si>
     <t xml:space="preserve">0.242407888174057</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">0.254701107740402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262000232934952</t>
+    <t xml:space="preserve">0.262000262737274</t>
   </si>
   <si>
     <t xml:space="preserve">0.254316955804825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261231958866119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262768596410751</t>
+    <t xml:space="preserve">0.261231929063797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262768536806107</t>
   </si>
   <si>
     <t xml:space="preserve">0.264689415693283</t>
@@ -2075,25 +2075,25 @@
     <t xml:space="preserve">0.273909360170364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276982665061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27275687456131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275445997714996</t>
+    <t xml:space="preserve">0.276982694864273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272756844758987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275446027517319</t>
   </si>
   <si>
     <t xml:space="preserve">0.268915206193924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26584193110466</t>
+    <t xml:space="preserve">0.265841871500015</t>
   </si>
   <si>
     <t xml:space="preserve">0.258542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26545774936676</t>
+    <t xml:space="preserve">0.265457719564438</t>
   </si>
   <si>
     <t xml:space="preserve">0.263152748346329</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">0.327692419290543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302337527275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30195340514183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332302361726761</t>
+    <t xml:space="preserve">0.302337557077408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301953375339508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332302391529083</t>
   </si>
   <si>
     <t xml:space="preserve">0.332686573266983</t>
@@ -2120,28 +2120,28 @@
     <t xml:space="preserve">0.306179165840149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305026710033417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312325835227966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331918209791183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315399169921875</t>
+    <t xml:space="preserve">0.305026739835739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312325805425644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331918239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31539911031723</t>
   </si>
   <si>
     <t xml:space="preserve">0.326539933681488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292349249124527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289275974035263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291196793317795</t>
+    <t xml:space="preserve">0.292349278926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289276003837585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291196763515472</t>
   </si>
   <si>
     <t xml:space="preserve">0.286970943212509</t>
@@ -2150,10 +2150,10 @@
     <t xml:space="preserve">0.285050123929977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273525238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260847747325897</t>
+    <t xml:space="preserve">0.273525178432465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260847806930542</t>
   </si>
   <si>
     <t xml:space="preserve">0.261616110801697</t>
@@ -2171,37 +2171,37 @@
     <t xml:space="preserve">0.266994386911392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255469501018524</t>
+    <t xml:space="preserve">0.255469471216202</t>
   </si>
   <si>
     <t xml:space="preserve">0.253164499998093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256621927022934</t>
+    <t xml:space="preserve">0.256621956825256</t>
   </si>
   <si>
     <t xml:space="preserve">0.256237804889679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249322801828384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236261248588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238182067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25354865193367</t>
+    <t xml:space="preserve">0.249322816729546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.236261233687401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238182082772255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253548622131348</t>
   </si>
   <si>
     <t xml:space="preserve">0.267762750387192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283513456583023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277750998735428</t>
+    <t xml:space="preserve">0.283513486385345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277750968933105</t>
   </si>
   <si>
     <t xml:space="preserve">0.294654279947281</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">0.319624960422516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343827337026596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338449031114578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34075403213501</t>
+    <t xml:space="preserve">0.343827277421951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338449001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340754002332687</t>
   </si>
   <si>
     <t xml:space="preserve">0.338833212852478</t>
@@ -2228,37 +2228,37 @@
     <t xml:space="preserve">0.336912333965302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333839058876038</t>
+    <t xml:space="preserve">0.333839029073715</t>
   </si>
   <si>
     <t xml:space="preserve">0.330765724182129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328844904899597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339985698461533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347668945789337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359962195158005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351894736289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369182229042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357657223939896</t>
+    <t xml:space="preserve">0.328844875097275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33998566865921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34766897559166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359962224960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351894795894623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369182199239731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357657253742218</t>
   </si>
   <si>
     <t xml:space="preserve">0.355352252721786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348053127527237</t>
+    <t xml:space="preserve">0.348053157329559</t>
   </si>
   <si>
     <t xml:space="preserve">0.346516489982605</t>
@@ -2270,58 +2270,58 @@
     <t xml:space="preserve">0.363419711589813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373792171478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373023837804794</t>
+    <t xml:space="preserve">0.373792141675949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373023808002472</t>
   </si>
   <si>
     <t xml:space="preserve">0.379554629325867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42565444111824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417971134185791</t>
+    <t xml:space="preserve">0.425654381513596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417971104383469</t>
   </si>
   <si>
     <t xml:space="preserve">0.381859630346298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383012056350708</t>
+    <t xml:space="preserve">0.383012115955353</t>
   </si>
   <si>
     <t xml:space="preserve">0.377633810043335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378402143716812</t>
+    <t xml:space="preserve">0.37840211391449</t>
   </si>
   <si>
     <t xml:space="preserve">0.381091296672821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380322962999344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348437309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400299549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383396327495575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379938781261444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388006269931793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428727716207504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368413835763931</t>
+    <t xml:space="preserve">0.380322992801666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348437279462814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400299519300461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383396297693253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379938811063766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388006240129471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428727656602859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368413865566254</t>
   </si>
   <si>
     <t xml:space="preserve">0.344595640897751</t>
@@ -2330,19 +2330,19 @@
     <t xml:space="preserve">0.334223210811615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341906487941742</t>
+    <t xml:space="preserve">0.341906517744064</t>
   </si>
   <si>
     <t xml:space="preserve">0.323466598987579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340369820594788</t>
+    <t xml:space="preserve">0.34036985039711</t>
   </si>
   <si>
     <t xml:space="preserve">0.331149876117706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348821491003036</t>
+    <t xml:space="preserve">0.348821431398392</t>
   </si>
   <si>
     <t xml:space="preserve">0.322314113378525</t>
@@ -2360,22 +2360,22 @@
     <t xml:space="preserve">0.341522336006165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329229027032852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353653162717819</t>
+    <t xml:space="preserve">0.329229056835175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353653132915497</t>
   </si>
   <si>
     <t xml:space="preserve">0.351594626903534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354064851999283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352829694747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347477585077286</t>
+    <t xml:space="preserve">0.35406482219696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352829724550247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347477555274963</t>
   </si>
   <si>
     <t xml:space="preserve">0.345830768346786</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">0.342537134885788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348300993442535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35982871055603</t>
+    <t xml:space="preserve">0.348301023244858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359828680753708</t>
   </si>
   <si>
     <t xml:space="preserve">0.353241413831711</t>
@@ -2399,19 +2399,19 @@
     <t xml:space="preserve">0.35488823056221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350359499454498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345007330179214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339655190706253</t>
+    <t xml:space="preserve">0.350359529256821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345007359981537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339655220508575</t>
   </si>
   <si>
     <t xml:space="preserve">0.342948853969574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341302007436752</t>
+    <t xml:space="preserve">0.341302037239075</t>
   </si>
   <si>
     <t xml:space="preserve">0.333479672670364</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">0.321540266275406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310835957527161</t>
+    <t xml:space="preserve">0.310835987329483</t>
   </si>
   <si>
     <t xml:space="preserve">0.315776437520981</t>
@@ -2438,16 +2438,16 @@
     <t xml:space="preserve">0.312894523143768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31824666261673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317834973335266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319481760263443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312071114778519</t>
+    <t xml:space="preserve">0.318246632814407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317834943532944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319481790065765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312071084976196</t>
   </si>
   <si>
     <t xml:space="preserve">0.308365762233734</t>
@@ -2465,43 +2465,43 @@
     <t xml:space="preserve">0.320305168628693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322775363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30960088968277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309189140796661</t>
+    <t xml:space="preserve">0.322775393724442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309600859880447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309189170598984</t>
   </si>
   <si>
     <t xml:space="preserve">0.32112854719162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321951985359192</t>
+    <t xml:space="preserve">0.32195195555687</t>
   </si>
   <si>
     <t xml:space="preserve">0.32524561882019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326892405748367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323187112808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323598831892014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315364718437195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31330618262291</t>
+    <t xml:space="preserve">0.32689243555069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323187083005905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323598772287369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315364688634872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313306212425232</t>
   </si>
   <si>
     <t xml:space="preserve">0.310424268245697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314953029155731</t>
+    <t xml:space="preserve">0.314952999353409</t>
   </si>
   <si>
     <t xml:space="preserve">0.311247676610947</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">0.317011535167694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31742325425148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311659425497055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316188126802444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319893449544907</t>
+    <t xml:space="preserve">0.317423224449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311659395694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316188156604767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319893509149551</t>
   </si>
   <si>
     <t xml:space="preserve">0.304660439491272</t>
@@ -2528,13 +2528,13 @@
     <t xml:space="preserve">0.30877748131752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30301359295845</t>
+    <t xml:space="preserve">0.303013622760773</t>
   </si>
   <si>
     <t xml:space="preserve">0.307542324066162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302601903676987</t>
+    <t xml:space="preserve">0.302601933479309</t>
   </si>
   <si>
     <t xml:space="preserve">0.307954072952271</t>
@@ -2543,19 +2543,19 @@
     <t xml:space="preserve">0.306307256221771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301778554916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303837031126022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30095511674881</t>
+    <t xml:space="preserve">0.301778525114059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3038370013237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300955086946487</t>
   </si>
   <si>
     <t xml:space="preserve">0.301366806030273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302190214395523</t>
+    <t xml:space="preserve">0.302190244197845</t>
   </si>
   <si>
     <t xml:space="preserve">0.313717901706696</t>
@@ -2564,25 +2564,25 @@
     <t xml:space="preserve">0.326480686664581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328539252281189</t>
+    <t xml:space="preserve">0.328539222478867</t>
   </si>
   <si>
     <t xml:space="preserve">0.344595670700073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340890318155289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356535077095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343360543251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336361587047577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339243531227112</t>
+    <t xml:space="preserve">0.340890347957611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356535047292709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343360513448715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336361557245255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339243501424789</t>
   </si>
   <si>
     <t xml:space="preserve">0.335126489400864</t>
@@ -2591,22 +2591,22 @@
     <t xml:space="preserve">0.358181864023209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347065895795822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34418398141861</t>
+    <t xml:space="preserve">0.3470658659935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344183951616287</t>
   </si>
   <si>
     <t xml:space="preserve">0.336773306131363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345419049263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349124401807785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338008433580399</t>
+    <t xml:space="preserve">0.345419079065323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349124372005463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338008373975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.335949897766113</t>
@@ -2630,25 +2630,25 @@
     <t xml:space="preserve">0.329362630844116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325657337903976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33842009305954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346654146909714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35571163892746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359005242586136</t>
+    <t xml:space="preserve">0.325657308101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338420122861862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346654176712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355711668729782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359005272388458</t>
   </si>
   <si>
     <t xml:space="preserve">0.370121240615845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377943605184555</t>
+    <t xml:space="preserve">0.377943634986877</t>
   </si>
   <si>
     <t xml:space="preserve">0.38164895772934</t>
@@ -2663,34 +2663,34 @@
     <t xml:space="preserve">0.399763882160187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38947132229805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401822417974472</t>
+    <t xml:space="preserve">0.389471292495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401822447776794</t>
   </si>
   <si>
     <t xml:space="preserve">0.411703288555145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402234107255936</t>
+    <t xml:space="preserve">0.402234137058258</t>
   </si>
   <si>
     <t xml:space="preserve">0.403469234704971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409644782543182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408409655094147</t>
+    <t xml:space="preserve">0.40964475274086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408409684896469</t>
   </si>
   <si>
     <t xml:space="preserve">0.405939429998398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406351178884506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400175631046295</t>
+    <t xml:space="preserve">0.406351149082184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400175601243973</t>
   </si>
   <si>
     <t xml:space="preserve">0.397705405950546</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">0.403880923986435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403057545423508</t>
+    <t xml:space="preserve">0.403057515621185</t>
   </si>
   <si>
     <t xml:space="preserve">0.394823461771011</t>
@@ -2711,19 +2711,19 @@
     <t xml:space="preserve">0.433111846446991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430641621351242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441345930099487</t>
+    <t xml:space="preserve">0.430641651153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441345900297165</t>
   </si>
   <si>
     <t xml:space="preserve">0.454520404338837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442992717027664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488280147314072</t>
+    <t xml:space="preserve">0.442992776632309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488280087709427</t>
   </si>
   <si>
     <t xml:space="preserve">0.50392484664917</t>
@@ -2738,37 +2738,37 @@
     <t xml:space="preserve">0.522039771080017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500631213188171</t>
+    <t xml:space="preserve">0.500631153583527</t>
   </si>
   <si>
     <t xml:space="preserve">0.517922759056091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469341814517975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485809892416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462754487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472635358572006</t>
+    <t xml:space="preserve">0.46934175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485809862613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462754428386688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472635388374329</t>
   </si>
   <si>
     <t xml:space="preserve">0.493220508098602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491573721170425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481692790985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467694938182831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461107701063156</t>
+    <t xml:space="preserve">0.491573750972748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481692880392075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467694997787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461107671260834</t>
   </si>
   <si>
     <t xml:space="preserve">0.476752400398254</t>
@@ -2777,22 +2777,22 @@
     <t xml:space="preserve">0.479222655296326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477575808763504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515452444553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504748165607452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501454710960388</t>
+    <t xml:space="preserve">0.477575778961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51545250415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504748225212097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501454591751099</t>
   </si>
   <si>
     <t xml:space="preserve">0.498984396457672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494043916463852</t>
+    <t xml:space="preserve">0.494043976068497</t>
   </si>
   <si>
     <t xml:space="preserve">0.505571663379669</t>
@@ -2801,22 +2801,22 @@
     <t xml:space="preserve">0.490750372409821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484986513853073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492397159337997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482516258955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478399187326431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473458796739578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470988541841507</t>
+    <t xml:space="preserve">0.484986484050751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492397129535675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482516199350357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478399217128754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473458826541901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470988571643829</t>
   </si>
   <si>
     <t xml:space="preserve">0.470165133476257</t>
@@ -2828,25 +2828,25 @@
     <t xml:space="preserve">0.460284292697906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468518376350403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466750353574753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473822325468063</t>
+    <t xml:space="preserve">0.468518316745758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46675032377243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473822295665741</t>
   </si>
   <si>
     <t xml:space="preserve">0.457910388708115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461446404457092</t>
+    <t xml:space="preserve">0.46144637465477</t>
   </si>
   <si>
     <t xml:space="preserve">0.464098364114761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454374372959137</t>
+    <t xml:space="preserve">0.454374402761459</t>
   </si>
   <si>
     <t xml:space="preserve">0.441114455461502</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">0.420782536268234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435810476541519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438462436199188</t>
+    <t xml:space="preserve">0.435810446739197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438462466001511</t>
   </si>
   <si>
     <t xml:space="preserve">0.427412480115891</t>
@@ -2867,19 +2867,19 @@
     <t xml:space="preserve">0.426528483629227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433158457279205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448186427354813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441998422145844</t>
+    <t xml:space="preserve">0.433158487081528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448186457157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441998451948166</t>
   </si>
   <si>
     <t xml:space="preserve">0.434484452009201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44465047121048</t>
+    <t xml:space="preserve">0.444650441408157</t>
   </si>
   <si>
     <t xml:space="preserve">0.449070423841476</t>
@@ -2894,64 +2894,64 @@
     <t xml:space="preserve">0.430948466062546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431390464305878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434926450252533</t>
+    <t xml:space="preserve">0.4313904941082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434926480054855</t>
   </si>
   <si>
     <t xml:space="preserve">0.429622501134872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428738474845886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424318492412567</t>
+    <t xml:space="preserve">0.428738504648209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424318462610245</t>
   </si>
   <si>
     <t xml:space="preserve">0.434042453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421666502952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430506467819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427854478359222</t>
+    <t xml:space="preserve">0.421666473150253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430506438016891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427854508161545</t>
   </si>
   <si>
     <t xml:space="preserve">0.419456511735916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417246490716934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411942541599274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414152503013611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41813051700592</t>
+    <t xml:space="preserve">0.417246550321579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411942511796951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414152532815933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418130487203598</t>
   </si>
   <si>
     <t xml:space="preserve">0.42255049943924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413710534572601</t>
+    <t xml:space="preserve">0.413710504770279</t>
   </si>
   <si>
     <t xml:space="preserve">0.425202488899231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423876523971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414594531059265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422992497682571</t>
+    <t xml:space="preserve">0.423876494169235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414594560861588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422992527484894</t>
   </si>
   <si>
     <t xml:space="preserve">0.421224534511566</t>
@@ -2963,31 +2963,31 @@
     <t xml:space="preserve">0.415920525789261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408406555652618</t>
+    <t xml:space="preserve">0.408406585454941</t>
   </si>
   <si>
     <t xml:space="preserve">0.412384569644928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41105854511261</t>
+    <t xml:space="preserve">0.411058515310287</t>
   </si>
   <si>
     <t xml:space="preserve">0.409732550382614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409290552139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407964557409286</t>
+    <t xml:space="preserve">0.40929052233696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407964527606964</t>
   </si>
   <si>
     <t xml:space="preserve">0.423434495925903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420340478420258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426086455583572</t>
+    <t xml:space="preserve">0.42034050822258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426086485385895</t>
   </si>
   <si>
     <t xml:space="preserve">0.428296476602554</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">0.424760520458221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422108471393585</t>
+    <t xml:space="preserve">0.422108501195908</t>
   </si>
   <si>
     <t xml:space="preserve">0.415478527545929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402218550443649</t>
+    <t xml:space="preserve">0.402218610048294</t>
   </si>
   <si>
     <t xml:space="preserve">0.394262611865997</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">0.400008589029312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401334583759308</t>
+    <t xml:space="preserve">0.401334553956985</t>
   </si>
   <si>
     <t xml:space="preserve">0.39249461889267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396030634641647</t>
+    <t xml:space="preserve">0.396030604839325</t>
   </si>
   <si>
     <t xml:space="preserve">0.405754566192627</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">0.400450587272644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389842659235001</t>
+    <t xml:space="preserve">0.389842629432678</t>
   </si>
   <si>
     <t xml:space="preserve">0.388958603143692</t>
@@ -3041,16 +3041,16 @@
     <t xml:space="preserve">0.386748641729355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393378555774689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403102576732635</t>
+    <t xml:space="preserve">0.393378615379333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403102546930313</t>
   </si>
   <si>
     <t xml:space="preserve">0.396914601325989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39779856801033</t>
+    <t xml:space="preserve">0.397798597812653</t>
   </si>
   <si>
     <t xml:space="preserve">0.40177658200264</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660578489304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419898509979248</t>
+    <t xml:space="preserve">0.402660548686981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419898480176926</t>
   </si>
   <si>
     <t xml:space="preserve">0.436694443225861</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">0.456523567438126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465635776519775</t>
+    <t xml:space="preserve">0.465635806322098</t>
   </si>
   <si>
     <t xml:space="preserve">0.464724570512772</t>
@@ -3098,10 +3098,10 @@
     <t xml:space="preserve">0.468369513750076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480215430259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482949048280716</t>
+    <t xml:space="preserve">0.480215460062027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482949018478394</t>
   </si>
   <si>
     <t xml:space="preserve">0.481126666069031</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">0.486593961715698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501173555850983</t>
+    <t xml:space="preserve">0.501173615455627</t>
   </si>
   <si>
     <t xml:space="preserve">0.523042976856232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529421448707581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525776624679565</t>
+    <t xml:space="preserve">0.529421508312225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52577668428421</t>
   </si>
   <si>
     <t xml:space="preserve">0.523954212665558</t>
@@ -3143,25 +3143,25 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753149986267</t>
+    <t xml:space="preserve">0.515753209590912</t>
   </si>
   <si>
     <t xml:space="preserve">0.507552146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511197030544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514841973781586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519398093223572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513930678367615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524865448474884</t>
+    <t xml:space="preserve">0.511197090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514841914176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519398033618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51393073797226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524865388870239</t>
   </si>
   <si>
     <t xml:space="preserve">0.509374618530273</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546734809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537622511386871</t>
+    <t xml:space="preserve">0.541267514228821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546734869480133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537622570991516</t>
   </si>
   <si>
     <t xml:space="preserve">0.549468457698822</t>
@@ -3194,13 +3194,13 @@
     <t xml:space="preserve">0.564959287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569515407085419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562225580215454</t>
+    <t xml:space="preserve">0.569515466690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565870463848114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562225639820099</t>
   </si>
   <si>
     <t xml:space="preserve">0.551290929317474</t>
@@ -3209,16 +3209,16 @@
     <t xml:space="preserve">0.548557281494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550379693508148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547646045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555847108364105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553113341331482</t>
+    <t xml:space="preserve">0.550379633903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547646105289459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55584704875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553113400936127</t>
   </si>
   <si>
     <t xml:space="preserve">0.564048111438751</t>
@@ -3233,25 +3233,25 @@
     <t xml:space="preserve">0.558580696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556758224964142</t>
+    <t xml:space="preserve">0.556758344173431</t>
   </si>
   <si>
     <t xml:space="preserve">0.542178690433502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557669520378113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534888923168182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528510332107544</t>
+    <t xml:space="preserve">0.557669460773468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534888863563538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528510272502899</t>
   </si>
   <si>
     <t xml:space="preserve">0.535800099372864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530332803726196</t>
+    <t xml:space="preserve">0.530332744121552</t>
   </si>
   <si>
     <t xml:space="preserve">0.527599096298218</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617466211319</t>
+    <t xml:space="preserve">0.496617436408997</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">0.505729734897614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494794964790344</t>
+    <t xml:space="preserve">0.494794994592667</t>
   </si>
   <si>
     <t xml:space="preserve">0.499351114034653</t>
@@ -3284,28 +3284,28 @@
     <t xml:space="preserve">0.492061376571655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488416492938995</t>
+    <t xml:space="preserve">0.488416433334351</t>
   </si>
   <si>
     <t xml:space="preserve">0.483860343694687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487505227327347</t>
+    <t xml:space="preserve">0.487505257129669</t>
   </si>
   <si>
     <t xml:space="preserve">0.495706290006638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49388375878334</t>
+    <t xml:space="preserve">0.493883818387985</t>
   </si>
   <si>
     <t xml:space="preserve">0.491150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517575621604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489643424749374</t>
+    <t xml:space="preserve">0.517575681209564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489643454551697</t>
   </si>
   <si>
     <t xml:space="preserve">0.48199275135994</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">0.475776553153992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476732909679413</t>
+    <t xml:space="preserve">0.47673287987709</t>
   </si>
   <si>
     <t xml:space="preserve">0.480080038309097</t>
@@ -3329,31 +3329,31 @@
     <t xml:space="preserve">0.46477872133255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473385721445084</t>
+    <t xml:space="preserve">0.473385751247406</t>
   </si>
   <si>
     <t xml:space="preserve">0.469560384750366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470994889736176</t>
+    <t xml:space="preserve">0.470994919538498</t>
   </si>
   <si>
     <t xml:space="preserve">0.459040701389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453780889511108</t>
+    <t xml:space="preserve">0.453780859708786</t>
   </si>
   <si>
     <t xml:space="preserve">0.451390027999878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447564691305161</t>
+    <t xml:space="preserve">0.447564661502838</t>
   </si>
   <si>
     <t xml:space="preserve">0.45091187953949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441826671361923</t>
+    <t xml:space="preserve">0.441826701164246</t>
   </si>
   <si>
     <t xml:space="preserve">0.438479512929916</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">0.432741492986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436088681221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438001334667206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441348522901535</t>
+    <t xml:space="preserve">0.436088651418686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438001364469528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441348493099213</t>
   </si>
   <si>
     <t xml:space="preserve">0.446608364582062</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">0.436566829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438957661390305</t>
+    <t xml:space="preserve">0.438957691192627</t>
   </si>
   <si>
     <t xml:space="preserve">0.444695681333542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439435869455338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433697819709778</t>
+    <t xml:space="preserve">0.439435839653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4336978495121</t>
   </si>
   <si>
     <t xml:space="preserve">0.434654176235199</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">0.46669140458107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454737186431885</t>
+    <t xml:space="preserve">0.454737216234207</t>
   </si>
   <si>
     <t xml:space="preserve">0.455693542957306</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">0.561368525028229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538416564464569</t>
+    <t xml:space="preserve">0.538416504859924</t>
   </si>
   <si>
     <t xml:space="preserve">0.544154524803162</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">0.540329158306122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525984108448029</t>
+    <t xml:space="preserve">0.525984168052673</t>
   </si>
   <si>
     <t xml:space="preserve">0.517377138137817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525027871131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521202504634857</t>
+    <t xml:space="preserve">0.525027811527252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521202445030212</t>
   </si>
   <si>
     <t xml:space="preserve">0.519289791584015</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">0.531722128391266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518333435058594</t>
+    <t xml:space="preserve">0.518333494663239</t>
   </si>
   <si>
     <t xml:space="preserve">0.514508128166199</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">0.527896821498871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52694046497345</t>
+    <t xml:space="preserve">0.526940524578094</t>
   </si>
   <si>
     <t xml:space="preserve">0.535547494888306</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">0.553717851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568062841892242</t>
+    <t xml:space="preserve">0.568062901496887</t>
   </si>
   <si>
     <t xml:space="preserve">0.55849951505661</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">0.555630505084991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554674208164215</t>
+    <t xml:space="preserve">0.55467414855957</t>
   </si>
   <si>
     <t xml:space="preserve">0.557543218135834</t>
@@ -3491,16 +3491,16 @@
     <t xml:space="preserve">0.54702353477478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537460148334503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551805198192596</t>
+    <t xml:space="preserve">0.537460088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551805257797241</t>
   </si>
   <si>
     <t xml:space="preserve">0.524071455001831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533634901046753</t>
+    <t xml:space="preserve">0.533634841442108</t>
   </si>
   <si>
     <t xml:space="preserve">0.536503851413727</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">0.522158801555634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529809534549713</t>
+    <t xml:space="preserve">0.529809474945068</t>
   </si>
   <si>
     <t xml:space="preserve">0.532678484916687</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">0.499206781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49633777141571</t>
+    <t xml:space="preserve">0.496337741613388</t>
   </si>
   <si>
     <t xml:space="preserve">0.506857395172119</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">0.487730741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483905404806137</t>
+    <t xml:space="preserve">0.483905375003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.461909741163254</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">0.478167414665222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46860408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471473067998886</t>
+    <t xml:space="preserve">0.468604058027267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471473038196564</t>
   </si>
   <si>
     <t xml:space="preserve">0.48260822892189</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">0.558000028133392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549000024795532</t>
+    <t xml:space="preserve">0.533999979496002</t>
   </si>
 </sst>
 </file>
@@ -69420,22 +69420,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6914814815</v>
+        <v>45967.691099537</v>
       </c>
       <c r="B2505" t="n">
-        <v>367143</v>
+        <v>432154</v>
       </c>
       <c r="C2505" t="n">
-        <v>0.560999989509583</v>
+        <v>0.549000024795532</v>
       </c>
       <c r="D2505" t="n">
+        <v>0.531000018119812</v>
+      </c>
+      <c r="E2505" t="n">
         <v>0.546999990940094</v>
       </c>
-      <c r="E2505" t="n">
-        <v>0.560000002384186</v>
-      </c>
       <c r="F2505" t="n">
-        <v>0.549000024795532</v>
+        <v>0.533999979496002</v>
       </c>
       <c r="G2505" t="s">
         <v>1321</v>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="1324">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333736181259155</t>
+    <t xml:space="preserve">0.333736151456833</t>
   </si>
   <si>
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327446281909943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321156322956085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317678362131119</t>
+    <t xml:space="preserve">0.327446222305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321156293153763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317678391933441</t>
   </si>
   <si>
     <t xml:space="preserve">0.307318478822708</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">0.273796856403351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258997082710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25825709104538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243605181574821</t>
+    <t xml:space="preserve">0.258997023105621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258257031440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243605196475983</t>
   </si>
   <si>
     <t xml:space="preserve">0.246417179703712</t>
@@ -89,31 +89,31 @@
     <t xml:space="preserve">0.256407082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.259811043739319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261513024568558</t>
+    <t xml:space="preserve">0.259811013936996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261512994766235</t>
   </si>
   <si>
     <t xml:space="preserve">0.253817081451416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25307708978653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286894708871841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284600764513016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277496844530106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287116676568985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290742635726929</t>
+    <t xml:space="preserve">0.253077119588852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286894679069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284600734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277496814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287116706371307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290742665529251</t>
   </si>
   <si>
     <t xml:space="preserve">0.263806998729706</t>
@@ -125,40 +125,40 @@
     <t xml:space="preserve">0.250117152929306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277570784091949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297994554042816</t>
+    <t xml:space="preserve">0.277570813894272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297994583845139</t>
   </si>
   <si>
     <t xml:space="preserve">0.310796439647675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303544491529465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304358512163162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318122357130051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309686422348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30162051320076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310352444648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323376297950745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320046335458755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316716372966766</t>
+    <t xml:space="preserve">0.303544521331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304358541965485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318122327327728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309686452150345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301620543003082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310352474451065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323376327753067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320046365261078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316716402769089</t>
   </si>
   <si>
     <t xml:space="preserve">0.315236389636993</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">0.315606385469437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332996159791946</t>
+    <t xml:space="preserve">0.332996189594269</t>
   </si>
   <si>
     <t xml:space="preserve">0.332256197929382</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">0.311240434646606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312054425477982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299696534872055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296884596347809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299400568008423</t>
+    <t xml:space="preserve">0.312054395675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299696564674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296884626150131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2994005382061</t>
   </si>
   <si>
     <t xml:space="preserve">0.297476589679718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295996606349945</t>
+    <t xml:space="preserve">0.295996576547623</t>
   </si>
   <si>
     <t xml:space="preserve">0.293702602386475</t>
@@ -209,28 +209,28 @@
     <t xml:space="preserve">0.286376714706421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276756852865219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274536818265915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2723169028759</t>
+    <t xml:space="preserve">0.276756882667542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274536848068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272316873073578</t>
   </si>
   <si>
     <t xml:space="preserve">0.268542915582657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270466923713684</t>
+    <t xml:space="preserve">0.270466953516006</t>
   </si>
   <si>
     <t xml:space="preserve">0.26506495475769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268172949552536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268616914749146</t>
+    <t xml:space="preserve">0.268172919750214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268616944551468</t>
   </si>
   <si>
     <t xml:space="preserve">0.269208908081055</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">0.275276839733124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28489676117897</t>
+    <t xml:space="preserve">0.284896731376648</t>
   </si>
   <si>
     <t xml:space="preserve">0.290002673864365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308206468820572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309168428182602</t>
+    <t xml:space="preserve">0.308206498622894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309168457984924</t>
   </si>
   <si>
     <t xml:space="preserve">0.318196356296539</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">0.314200401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321378290653229</t>
+    <t xml:space="preserve">0.321378320455551</t>
   </si>
   <si>
     <t xml:space="preserve">0.319380342960358</t>
@@ -275,22 +275,22 @@
     <t xml:space="preserve">0.313682407140732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313312411308289</t>
+    <t xml:space="preserve">0.313312441110611</t>
   </si>
   <si>
     <t xml:space="preserve">0.30709645152092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307614475488663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304950505495071</t>
+    <t xml:space="preserve">0.30761444568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304950475692749</t>
   </si>
   <si>
     <t xml:space="preserve">0.305616497993469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299548596143723</t>
+    <t xml:space="preserve">0.2995485663414</t>
   </si>
   <si>
     <t xml:space="preserve">0.305320501327515</t>
@@ -299,16 +299,16 @@
     <t xml:space="preserve">0.295626640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300954520702362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314400285482407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318779796361923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318856596946716</t>
+    <t xml:space="preserve">0.300954550504684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314400315284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318779766559601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318856626749039</t>
   </si>
   <si>
     <t xml:space="preserve">0.318395614624023</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">0.319932281970978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318088263273239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307331681251526</t>
+    <t xml:space="preserve">0.318088293075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307331651449203</t>
   </si>
   <si>
     <t xml:space="preserve">0.321776270866394</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">0.320393294095993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311557501554489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305795013904572</t>
+    <t xml:space="preserve">0.311557471752167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305795043706894</t>
   </si>
   <si>
     <t xml:space="preserve">0.301569223403931</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">0.299648374319077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296575099229813</t>
+    <t xml:space="preserve">0.29657506942749</t>
   </si>
   <si>
     <t xml:space="preserve">0.303490042686462</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">0.318011462688446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318702965974808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32116162776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310020834207535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311941653490067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311173319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307254821062088</t>
+    <t xml:space="preserve">0.318702936172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321161597967148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310020804405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311941623687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311173349618912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30725485086441</t>
   </si>
   <si>
     <t xml:space="preserve">0.30671700835228</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">0.305564522743225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304949849843979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306870698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297727555036545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301799714565277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304027855396271</t>
+    <t xml:space="preserve">0.304949820041656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306870639324188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297727584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301799744367599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304027885198593</t>
   </si>
   <si>
     <t xml:space="preserve">0.300032585859299</t>
@@ -407,16 +407,16 @@
     <t xml:space="preserve">0.307869523763657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311480641365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298265427350998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299110531806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305257171392441</t>
+    <t xml:space="preserve">0.311480671167374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298265397548676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299110561609268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305257201194763</t>
   </si>
   <si>
     <t xml:space="preserve">0.295576244592667</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.297650724649429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297881245613098</t>
+    <t xml:space="preserve">0.297881215810776</t>
   </si>
   <si>
     <t xml:space="preserve">0.29373225569725</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">0.300416707992554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300109356641769</t>
+    <t xml:space="preserve">0.300109386444092</t>
   </si>
   <si>
     <t xml:space="preserve">0.298880040645599</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">0.30548769235611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309559851884842</t>
+    <t xml:space="preserve">0.30955982208252</t>
   </si>
   <si>
     <t xml:space="preserve">0.303105860948563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303566843271255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308253645896912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304873049259186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306563347578049</t>
+    <t xml:space="preserve">0.303566873073578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308253705501556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304873019456863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306563377380371</t>
   </si>
   <si>
     <t xml:space="preserve">0.300186216831207</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">0.298649579286575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296421378850937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301415592432022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300647228956223</t>
+    <t xml:space="preserve">0.296421408653259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301415532827377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3006471991539</t>
   </si>
   <si>
     <t xml:space="preserve">0.282975643873215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291965067386627</t>
+    <t xml:space="preserve">0.29196509718895</t>
   </si>
   <si>
     <t xml:space="preserve">0.289736926555634</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">0.293501764535904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292656570672989</t>
+    <t xml:space="preserve">0.292656600475311</t>
   </si>
   <si>
     <t xml:space="preserve">0.29250293970108</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">0.289583265781403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288123488426208</t>
+    <t xml:space="preserve">0.288123458623886</t>
   </si>
   <si>
     <t xml:space="preserve">0.284281820058823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28789296746254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29004430770874</t>
+    <t xml:space="preserve">0.287892997264862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290044277906418</t>
   </si>
   <si>
     <t xml:space="preserve">0.292887091636658</t>
@@ -521,28 +521,28 @@
     <t xml:space="preserve">0.293117612600327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291888296604156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289813816547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286586821079254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294270098209381</t>
+    <t xml:space="preserve">0.291888266801834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289813786745071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286586791276932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294270068407059</t>
   </si>
   <si>
     <t xml:space="preserve">0.291811436414719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292579770088196</t>
+    <t xml:space="preserve">0.292579799890518</t>
   </si>
   <si>
     <t xml:space="preserve">0.295729905366898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298419058322906</t>
+    <t xml:space="preserve">0.298419028520584</t>
   </si>
   <si>
     <t xml:space="preserve">0.294731080532074</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.27559968829155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270221412181854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272449553012848</t>
+    <t xml:space="preserve">0.270221382379532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272449523210526</t>
   </si>
   <si>
     <t xml:space="preserve">0.276675373315811</t>
@@ -584,37 +584,37 @@
     <t xml:space="preserve">0.275676518678665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275522857904434</t>
+    <t xml:space="preserve">0.275522828102112</t>
   </si>
   <si>
     <t xml:space="preserve">0.276598542928696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270989716053009</t>
+    <t xml:space="preserve">0.270989686250687</t>
   </si>
   <si>
     <t xml:space="preserve">0.27114337682724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274293571710587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270451873540878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268146932125092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267378598451614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264612555503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265765100717545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262384414672852</t>
+    <t xml:space="preserve">0.274293541908264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270451843738556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268146902322769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267378568649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264612585306168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265765070915222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262384444475174</t>
   </si>
   <si>
     <t xml:space="preserve">0.267532229423523</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">0.271911710500717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272526383399963</t>
+    <t xml:space="preserve">0.272526323795319</t>
   </si>
   <si>
     <t xml:space="preserve">0.283282995223999</t>
@@ -635,49 +635,49 @@
     <t xml:space="preserve">0.279902338981628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277059525251389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278442531824112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280517041683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278749883174896</t>
+    <t xml:space="preserve">0.277059495449066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27844250202179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280517011880875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278749853372574</t>
   </si>
   <si>
     <t xml:space="preserve">0.278980314731598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278212040662766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284051299095154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290812641382217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28966012597084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290428429841995</t>
+    <t xml:space="preserve">0.278212010860443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284051328897476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290812611579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289660096168518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290428459644318</t>
   </si>
   <si>
     <t xml:space="preserve">0.294807940721512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295422583818436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288507580757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284589141607285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291043162345886</t>
+    <t xml:space="preserve">0.295422554016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288507640361786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284589171409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291043102741241</t>
   </si>
   <si>
     <t xml:space="preserve">0.293885916471481</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">0.294884741306305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289890587329865</t>
+    <t xml:space="preserve">0.289890617132187</t>
   </si>
   <si>
     <t xml:space="preserve">0.286125779151917</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">0.281976819038391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276214331388474</t>
+    <t xml:space="preserve">0.276214361190796</t>
   </si>
   <si>
     <t xml:space="preserve">0.273602038621902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269760400056839</t>
+    <t xml:space="preserve">0.269760370254517</t>
   </si>
   <si>
     <t xml:space="preserve">0.275061875581741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271834909915924</t>
+    <t xml:space="preserve">0.271834880113602</t>
   </si>
   <si>
     <t xml:space="preserve">0.273371547460556</t>
@@ -725,10 +725,10 @@
     <t xml:space="preserve">0.275215536355972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276905834674835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274831354618073</t>
+    <t xml:space="preserve">0.276905804872513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27483132481575</t>
   </si>
   <si>
     <t xml:space="preserve">0.282668352127075</t>
@@ -737,61 +737,61 @@
     <t xml:space="preserve">0.280440181493759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279595017433167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277366876602173</t>
+    <t xml:space="preserve">0.279594987630844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27736684679985</t>
   </si>
   <si>
     <t xml:space="preserve">0.278135180473328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278672993183136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28259152173996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279364496469498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285587966442108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27967181801796</t>
+    <t xml:space="preserve">0.281208485364914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278673022985458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282591491937637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279364466667175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285587936639786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279671788215637</t>
   </si>
   <si>
     <t xml:space="preserve">0.28666365146637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284435510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281900018453598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283897668123245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285280674695969</t>
+    <t xml:space="preserve">0.284435451030731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281899988651276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283897638320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285280644893646</t>
   </si>
   <si>
     <t xml:space="preserve">0.285434275865555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295038402080536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304258346557617</t>
+    <t xml:space="preserve">0.295038431882858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304258406162262</t>
   </si>
   <si>
     <t xml:space="preserve">0.321929931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32561793923378</t>
+    <t xml:space="preserve">0.325617909431458</t>
   </si>
   <si>
     <t xml:space="preserve">0.331841379404068</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">0.325387418270111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316935777664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309790372848511</t>
+    <t xml:space="preserve">0.316935807466507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309790343046188</t>
   </si>
   <si>
     <t xml:space="preserve">0.309252500534058</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">0.313094139099121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313017308712006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288891792297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293040782213211</t>
+    <t xml:space="preserve">0.313017338514328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288891762495041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293040752410889</t>
   </si>
   <si>
     <t xml:space="preserve">0.295192092657089</t>
@@ -833,22 +833,22 @@
     <t xml:space="preserve">0.297266602516174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298111736774445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310251325368881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313555151224136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300800889730453</t>
+    <t xml:space="preserve">0.298111706972122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310251384973526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313555181026459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300800859928131</t>
   </si>
   <si>
     <t xml:space="preserve">0.308868318796158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299725234508514</t>
+    <t xml:space="preserve">0.299725264310837</t>
   </si>
   <si>
     <t xml:space="preserve">0.32185310125351</t>
@@ -857,28 +857,28 @@
     <t xml:space="preserve">0.327308237552643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318472474813461</t>
+    <t xml:space="preserve">0.318472445011139</t>
   </si>
   <si>
     <t xml:space="preserve">0.312095314264297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314016163349152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315014988183975</t>
+    <t xml:space="preserve">0.314016133546829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315015017986298</t>
   </si>
   <si>
     <t xml:space="preserve">0.312249004840851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313939303159714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309636652469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307408541440964</t>
+    <t xml:space="preserve">0.313939273357391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309636682271957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307408481836319</t>
   </si>
   <si>
     <t xml:space="preserve">0.308945178985596</t>
@@ -887,13 +887,13 @@
     <t xml:space="preserve">0.313631981611252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308023154735565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307715833187103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309022009372711</t>
+    <t xml:space="preserve">0.308023184537888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307715862989426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309022039175034</t>
   </si>
   <si>
     <t xml:space="preserve">0.309944003820419</t>
@@ -902,31 +902,31 @@
     <t xml:space="preserve">0.317780941724777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316551625728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316474795341492</t>
+    <t xml:space="preserve">0.31655165553093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316474825143814</t>
   </si>
   <si>
     <t xml:space="preserve">0.324388563632965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325003236532211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318318784236908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317704141139984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321545779705048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320470094680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621464729309</t>
+    <t xml:space="preserve">0.325003296136856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31831881403923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317704170942307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32154580950737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320470124483109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621434926987</t>
   </si>
   <si>
     <t xml:space="preserve">0.323697090148926</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">0.327385038137436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331764549016953</t>
+    <t xml:space="preserve">0.331764578819275</t>
   </si>
   <si>
     <t xml:space="preserve">0.339524686336517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345671355724335</t>
+    <t xml:space="preserve">0.345671325922012</t>
   </si>
   <si>
     <t xml:space="preserve">0.340446680784225</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">0.339678347110748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350358128547668</t>
+    <t xml:space="preserve">0.350358098745346</t>
   </si>
   <si>
     <t xml:space="preserve">0.34659332036972</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">0.344211518764496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340677171945572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334607362747192</t>
+    <t xml:space="preserve">0.340677231550217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33460733294487</t>
   </si>
   <si>
     <t xml:space="preserve">0.338218539953232</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">0.346900671720505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346132338047028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339601516723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340907692909241</t>
+    <t xml:space="preserve">0.346132308244705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33960148692131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340907663106918</t>
   </si>
   <si>
     <t xml:space="preserve">0.352663099765778</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">0.369950503110886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36541736125946</t>
+    <t xml:space="preserve">0.365417391061783</t>
   </si>
   <si>
     <t xml:space="preserve">0.363035529851913</t>
@@ -1019,22 +1019,22 @@
     <t xml:space="preserve">0.371103048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369566351175308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368798017501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366108864545822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363112419843674</t>
+    <t xml:space="preserve">0.369566321372986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368797987699509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366108894348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363112390041351</t>
   </si>
   <si>
     <t xml:space="preserve">0.3686443567276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366877228021622</t>
+    <t xml:space="preserve">0.366877198219299</t>
   </si>
   <si>
     <t xml:space="preserve">0.366262555122375</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">0.361114740371704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359885394573212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359193921089172</t>
+    <t xml:space="preserve">0.359885454177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359193950891495</t>
   </si>
   <si>
     <t xml:space="preserve">0.368567526340485</t>
@@ -1058,73 +1058,73 @@
     <t xml:space="preserve">0.375559329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380246132612228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392616212368011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405677795410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421044409275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419507801532745</t>
+    <t xml:space="preserve">0.380246102809906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392616182565689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405677825212479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421044379472733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419507771730423</t>
   </si>
   <si>
     <t xml:space="preserve">0.396842032670975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413361102342606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422581106424332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417586892843246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426422744989395</t>
+    <t xml:space="preserve">0.413361132144928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422581076622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417586952447891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42642268538475</t>
   </si>
   <si>
     <t xml:space="preserve">0.423349440097809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427959352731705</t>
+    <t xml:space="preserve">0.427959382534027</t>
   </si>
   <si>
     <t xml:space="preserve">0.436795145273209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432953506708145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452930092811584</t>
+    <t xml:space="preserve">0.4329534471035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45293003320694</t>
   </si>
   <si>
     <t xml:space="preserve">0.459460884332657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465223342180252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296676874161</t>
+    <t xml:space="preserve">0.46522331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296647071838</t>
   </si>
   <si>
     <t xml:space="preserve">0.481358259916306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522463798522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515164732933044</t>
+    <t xml:space="preserve">0.522463858127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5151646733284</t>
   </si>
   <si>
     <t xml:space="preserve">0.505560636520386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507097244262695</t>
+    <t xml:space="preserve">0.50709730386734</t>
   </si>
   <si>
     <t xml:space="preserve">0.515548884868622</t>
@@ -1133,46 +1133,46 @@
     <t xml:space="preserve">0.503255605697632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489809840917587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480205714702606</t>
+    <t xml:space="preserve">0.48980987071991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480205774307251</t>
   </si>
   <si>
     <t xml:space="preserve">0.519006371498108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511323034763336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499413996934891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491730630397797</t>
+    <t xml:space="preserve">0.511323094367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499413967132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491730749607086</t>
   </si>
   <si>
     <t xml:space="preserve">0.484431564807892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483663201332092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484815657138824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495188146829605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490193963050842</t>
+    <t xml:space="preserve">0.483663260936737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484815686941147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495188236236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490194022655487</t>
   </si>
   <si>
     <t xml:space="preserve">0.553197085857391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542056262493134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56280118227005</t>
+    <t xml:space="preserve">0.542056322097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562801122665405</t>
   </si>
   <si>
     <t xml:space="preserve">0.586235225200653</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">0.600065171718597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582393527030945</t>
+    <t xml:space="preserve">0.58239358663559</t>
   </si>
   <si>
     <t xml:space="preserve">0.572021067142487</t>
@@ -1190,46 +1190,46 @@
     <t xml:space="preserve">0.572789430618286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552428662776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55127614736557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545129537582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565874457359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577015161514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596607565879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584698557853699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608132481575012</t>
+    <t xml:space="preserve">0.552428722381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551276206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545129597187042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565874516963959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577015280723572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596607625484467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584698498249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608132541179657</t>
   </si>
   <si>
     <t xml:space="preserve">0.621962487697601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620425879955292</t>
+    <t xml:space="preserve">0.620425820350647</t>
   </si>
   <si>
     <t xml:space="preserve">0.629645824432373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614279270172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60774838924408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581625282764435</t>
+    <t xml:space="preserve">0.61427915096283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607748448848724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58162522315979</t>
   </si>
   <si>
     <t xml:space="preserve">0.560880362987518</t>
@@ -1241,25 +1241,25 @@
     <t xml:space="preserve">0.598144292831421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.619657576084137</t>
+    <t xml:space="preserve">0.619657456874847</t>
   </si>
   <si>
     <t xml:space="preserve">0.618120849132538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601601779460907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586619317531586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59545511007309</t>
+    <t xml:space="preserve">0.601601719856262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586619257926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595455169677734</t>
   </si>
   <si>
     <t xml:space="preserve">0.587771832942963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584314346313477</t>
+    <t xml:space="preserve">0.584314405918121</t>
   </si>
   <si>
     <t xml:space="preserve">0.577399373054504</t>
@@ -1274,19 +1274,19 @@
     <t xml:space="preserve">0.543592929840088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564722001552582</t>
+    <t xml:space="preserve">0.564721941947937</t>
   </si>
   <si>
     <t xml:space="preserve">0.563185274600983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576246976852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583930134773254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58085685968399</t>
+    <t xml:space="preserve">0.576246917247772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583930194377899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580856919288635</t>
   </si>
   <si>
     <t xml:space="preserve">0.587003529071808</t>
@@ -1310,49 +1310,49 @@
     <t xml:space="preserve">0.612358331680298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611590027809143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59391850233078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596991777420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608516693115234</t>
+    <t xml:space="preserve">0.611590087413788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593918442726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596991837024689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608516812324524</t>
   </si>
   <si>
     <t xml:space="preserve">0.599296748638153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589308500289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553965449333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538598716259003</t>
+    <t xml:space="preserve">0.589308559894562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553965270519257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538598835468292</t>
   </si>
   <si>
     <t xml:space="preserve">0.557038724422455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536293864250183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524000525474548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537830531597137</t>
+    <t xml:space="preserve">0.536293804645538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524000465869904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537830412387848</t>
   </si>
   <si>
     <t xml:space="preserve">0.547818779945374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532452166080475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537062168121338</t>
+    <t xml:space="preserve">0.53245210647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537062048912048</t>
   </si>
   <si>
     <t xml:space="preserve">0.527073800563812</t>
@@ -1361,49 +1361,49 @@
     <t xml:space="preserve">0.52092719078064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517853856086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525537133216858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530147194862366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523232161998749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51939058303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524768829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549355387687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501718938350677</t>
+    <t xml:space="preserve">0.517853915691376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525537252426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530147135257721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523232221603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519390523433685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524768888950348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549355328083038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501719057559967</t>
   </si>
   <si>
     <t xml:space="preserve">0.492499023675919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477900743484497</t>
+    <t xml:space="preserve">0.477900773286819</t>
   </si>
   <si>
     <t xml:space="preserve">0.476364076137543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488657355308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471754133701324</t>
+    <t xml:space="preserve">0.488657385110855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471754163503647</t>
   </si>
   <si>
     <t xml:space="preserve">0.472522467374802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468680858612061</t>
+    <t xml:space="preserve">0.468680799007416</t>
   </si>
   <si>
     <t xml:space="preserve">0.487120717763901</t>
@@ -1415,19 +1415,19 @@
     <t xml:space="preserve">0.480974107980728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483279049396515</t>
+    <t xml:space="preserve">0.483279138803482</t>
   </si>
   <si>
     <t xml:space="preserve">0.478669106960297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47021746635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467912554740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466375768184662</t>
+    <t xml:space="preserve">0.470217436552048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467912495136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466375827789307</t>
   </si>
   <si>
     <t xml:space="preserve">0.464839220046997</t>
@@ -1442,25 +1442,25 @@
     <t xml:space="preserve">0.500182330608368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469449102878571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437179356813431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444862604141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431800991296768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444094330072403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424117684364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415666103363037</t>
+    <t xml:space="preserve">0.469449162483215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437179327011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444862633943558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431801021099091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444094270467758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424117714166641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415666073560715</t>
   </si>
   <si>
     <t xml:space="preserve">0.382627964019775</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">0.382243782281876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385701239109039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388774573802948</t>
+    <t xml:space="preserve">0.385701268911362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388774514198303</t>
   </si>
   <si>
     <t xml:space="preserve">0.391847908496857</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">0.367261350154877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364956378936768</t>
+    <t xml:space="preserve">0.364956349134445</t>
   </si>
   <si>
     <t xml:space="preserve">0.360346406698227</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">0.3522789478302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356504738330841</t>
+    <t xml:space="preserve">0.356504768133163</t>
   </si>
   <si>
     <t xml:space="preserve">0.37148717045784</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">0.368029683828354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372255504131317</t>
+    <t xml:space="preserve">0.372255474328995</t>
   </si>
   <si>
     <t xml:space="preserve">0.365340530872345</t>
@@ -1517,22 +1517,22 @@
     <t xml:space="preserve">0.374944657087326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366492986679077</t>
+    <t xml:space="preserve">0.3664930164814</t>
   </si>
   <si>
     <t xml:space="preserve">0.374560505151749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374176323413849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378786265850067</t>
+    <t xml:space="preserve">0.374176293611526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37878629565239</t>
   </si>
   <si>
     <t xml:space="preserve">0.362267225980759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353815615177155</t>
+    <t xml:space="preserve">0.353815585374832</t>
   </si>
   <si>
     <t xml:space="preserve">0.354583919048309</t>
@@ -1544,25 +1544,25 @@
     <t xml:space="preserve">0.370718836784363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354199767112732</t>
+    <t xml:space="preserve">0.35419973731041</t>
   </si>
   <si>
     <t xml:space="preserve">0.395689517259598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411056131124496</t>
+    <t xml:space="preserve">0.411056160926819</t>
   </si>
   <si>
     <t xml:space="preserve">0.40798282623291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384932905435562</t>
+    <t xml:space="preserve">0.384932935237885</t>
   </si>
   <si>
     <t xml:space="preserve">0.390311241149902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378017991781235</t>
+    <t xml:space="preserve">0.378017961978912</t>
   </si>
   <si>
     <t xml:space="preserve">0.380707114934921</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">0.362651377916336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359578043222427</t>
+    <t xml:space="preserve">0.35957807302475</t>
   </si>
   <si>
     <t xml:space="preserve">0.353431463241577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349589824676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344979852437973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343059003353119</t>
+    <t xml:space="preserve">0.349589794874191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344979822635651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343058973550797</t>
   </si>
   <si>
     <t xml:space="preserve">0.354968130588531</t>
@@ -1592,46 +1592,46 @@
     <t xml:space="preserve">0.364188075065613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357273072004318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349973976612091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339217364788055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323850780725479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361883074045181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350742280483246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389542937278748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404141157865524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396457850933075</t>
+    <t xml:space="preserve">0.357273101806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349973946809769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339217334985733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323850721120834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361883103847504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350742310285568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38954296708107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404141187667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396457880735397</t>
   </si>
   <si>
     <t xml:space="preserve">0.412592768669128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404909491539001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401836216449738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394152849912643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399531155824661</t>
+    <t xml:space="preserve">0.404909521341324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401836186647415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394152909517288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399531185626984</t>
   </si>
   <si>
     <t xml:space="preserve">0.40260449051857</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">0.397994548082352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375712960958481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36457222700119</t>
+    <t xml:space="preserve">0.375712990760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364572197198868</t>
   </si>
   <si>
     <t xml:space="preserve">0.345748156309128</t>
@@ -1667,16 +1667,16 @@
     <t xml:space="preserve">0.328076541423798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331534028053284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319240778684616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326924085617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312709957361221</t>
+    <t xml:space="preserve">0.331534057855606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319240808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326924115419388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312709987163544</t>
   </si>
   <si>
     <t xml:space="preserve">0.341138184070587</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">0.324619084596634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325771570205688</t>
+    <t xml:space="preserve">0.325771600008011</t>
   </si>
   <si>
     <t xml:space="preserve">0.330381542444229</t>
@@ -1703,22 +1703,22 @@
     <t xml:space="preserve">0.324234932661057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313862442970276</t>
+    <t xml:space="preserve">0.313862472772598</t>
   </si>
   <si>
     <t xml:space="preserve">0.301185041666031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30387419462204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29695925116539</t>
+    <t xml:space="preserve">0.303874224424362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296959221363068</t>
   </si>
   <si>
     <t xml:space="preserve">0.302721709012985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082387447357</t>
+    <t xml:space="preserve">0.323082447052002</t>
   </si>
   <si>
     <t xml:space="preserve">0.308100014925003</t>
@@ -1736,28 +1736,28 @@
     <t xml:space="preserve">0.305410861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30848416686058</t>
+    <t xml:space="preserve">0.308484226465225</t>
   </si>
   <si>
     <t xml:space="preserve">0.304642498493195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32077744603157</t>
+    <t xml:space="preserve">0.320777416229248</t>
   </si>
   <si>
     <t xml:space="preserve">0.356888920068741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358041405677795</t>
+    <t xml:space="preserve">0.358041375875473</t>
   </si>
   <si>
     <t xml:space="preserve">0.356120586395264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360730588436127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358809769153595</t>
+    <t xml:space="preserve">0.360730558633804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358809739351273</t>
   </si>
   <si>
     <t xml:space="preserve">0.351126462221146</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">0.342290639877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371871322393417</t>
+    <t xml:space="preserve">0.37187135219574</t>
   </si>
   <si>
     <t xml:space="preserve">0.370334684848785</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">0.383780419826508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376097142696381</t>
+    <t xml:space="preserve">0.376097172498703</t>
   </si>
   <si>
     <t xml:space="preserve">0.376865476369858</t>
@@ -1793,31 +1793,31 @@
     <t xml:space="preserve">0.403372824192047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406446099281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40951943397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39107957482338</t>
+    <t xml:space="preserve">0.406446158885956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409519463777542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391079604625702</t>
   </si>
   <si>
     <t xml:space="preserve">0.381475418806076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407214462757111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387237906455994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394921213388443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411824464797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41489776968956</t>
+    <t xml:space="preserve">0.407214432954788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387237936258316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394921243190765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411824434995651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414897829294205</t>
   </si>
   <si>
     <t xml:space="preserve">0.417202740907669</t>
@@ -1826,70 +1826,70 @@
     <t xml:space="preserve">0.397226184606552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408751159906387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410287797451019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414129436016083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416434466838837</t>
+    <t xml:space="preserve">0.408751130104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410287767648697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41412940621376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416434437036514</t>
   </si>
   <si>
     <t xml:space="preserve">0.418739438056946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4202761054039</t>
+    <t xml:space="preserve">0.420276075601578</t>
   </si>
   <si>
     <t xml:space="preserve">0.421812742948532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430264383554459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473290801048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49480402469635</t>
+    <t xml:space="preserve">0.430264323949814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473290830850601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494803994894028</t>
   </si>
   <si>
     <t xml:space="preserve">0.484047383069992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493267357349396</t>
+    <t xml:space="preserve">0.493267387151718</t>
   </si>
   <si>
     <t xml:space="preserve">0.506328940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479437381029129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482510775327682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595861673355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46407076716423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465607523918152</t>
+    <t xml:space="preserve">0.479437410831451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48251074552536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47559580206871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070826768875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465607464313507</t>
   </si>
   <si>
     <t xml:space="preserve">0.460997521877289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453314214944839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434106051921844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789239645004</t>
+    <t xml:space="preserve">0.453314244747162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434106022119522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789329051971</t>
   </si>
   <si>
     <t xml:space="preserve">0.445630937814713</t>
@@ -1904,52 +1904,52 @@
     <t xml:space="preserve">0.460229188203812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454082608222961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457155913114548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451777577400208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456387579441071</t>
+    <t xml:space="preserve">0.454082548618317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457155853509903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45177760720253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456387549638748</t>
   </si>
   <si>
     <t xml:space="preserve">0.463302493095398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470985740423203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467144161462784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457924246788025</t>
+    <t xml:space="preserve">0.470985770225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467144131660461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457924216985703</t>
   </si>
   <si>
     <t xml:space="preserve">0.447167634963989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43256938457489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437947660684586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433337688446045</t>
+    <t xml:space="preserve">0.432569354772568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437947630882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433337718248367</t>
   </si>
   <si>
     <t xml:space="preserve">0.434874296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436410993337631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439484357833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441021025180817</t>
+    <t xml:space="preserve">0.436411023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43948432803154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441020965576172</t>
   </si>
   <si>
     <t xml:space="preserve">0.440252661705017</t>
@@ -1958,22 +1958,22 @@
     <t xml:space="preserve">0.43871596455574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442557603120804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485584050416946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455619156360626</t>
+    <t xml:space="preserve">0.442557632923126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485584080219269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455619245767593</t>
   </si>
   <si>
     <t xml:space="preserve">0.443325966596603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429496079683304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435642659664154</t>
+    <t xml:space="preserve">0.429496049880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435642600059509</t>
   </si>
   <si>
     <t xml:space="preserve">0.450240910053253</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">0.386469602584839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393384546041489</t>
+    <t xml:space="preserve">0.393384575843811</t>
   </si>
   <si>
     <t xml:space="preserve">0.365724712610245</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">0.372639685869217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351510643959045</t>
+    <t xml:space="preserve">0.351510614156723</t>
   </si>
   <si>
     <t xml:space="preserve">0.342674881219864</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">0.317319959402084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265073597431183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259695291519165</t>
+    <t xml:space="preserve">0.26507356762886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259695261716843</t>
   </si>
   <si>
     <t xml:space="preserve">0.239334553480148</t>
@@ -2018,25 +2018,25 @@
     <t xml:space="preserve">0.242023691534996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234724551439285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245865315198898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258926928043365</t>
+    <t xml:space="preserve">0.234724581241608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245865374803543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258926957845688</t>
   </si>
   <si>
     <t xml:space="preserve">0.251627802848816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266610264778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269299358129501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258158594369888</t>
+    <t xml:space="preserve">0.266610234975815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269299417734146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258158624172211</t>
   </si>
   <si>
     <t xml:space="preserve">0.251243650913239</t>
@@ -2045,64 +2045,64 @@
     <t xml:space="preserve">0.252011954784393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242407828569412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245096981525421</t>
+    <t xml:space="preserve">0.242407843470573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245097011327744</t>
   </si>
   <si>
     <t xml:space="preserve">0.254701107740402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262000262737274</t>
+    <t xml:space="preserve">0.262000232934952</t>
   </si>
   <si>
     <t xml:space="preserve">0.254316955804825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261231899261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262768566608429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264689445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271988540887833</t>
+    <t xml:space="preserve">0.261231929063797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262768626213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264689415693283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271988570690155</t>
   </si>
   <si>
     <t xml:space="preserve">0.273909389972687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276982724666595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272756844758987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275446027517319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268915265798569</t>
+    <t xml:space="preserve">0.276982635259628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272756814956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275445997714996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268915206193924</t>
   </si>
   <si>
     <t xml:space="preserve">0.265841901302338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258542776107788</t>
+    <t xml:space="preserve">0.258542746305466</t>
   </si>
   <si>
     <t xml:space="preserve">0.26545774936676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263152778148651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292733460664749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32769238948822</t>
+    <t xml:space="preserve">0.263152748346329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292733430862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327692419290543</t>
   </si>
   <si>
     <t xml:space="preserve">0.302337557077408</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">0.301953375339508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332302361726761</t>
+    <t xml:space="preserve">0.332302391529083</t>
   </si>
   <si>
     <t xml:space="preserve">0.332686543464661</t>
@@ -2120,28 +2120,28 @@
     <t xml:space="preserve">0.306179165840149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305026739835739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312325835227966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331918209791183</t>
+    <t xml:space="preserve">0.305026710033417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312325865030289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331918239593506</t>
   </si>
   <si>
     <t xml:space="preserve">0.31539911031723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326539933681488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292349278926849</t>
+    <t xml:space="preserve">0.326539903879166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292349249124527</t>
   </si>
   <si>
     <t xml:space="preserve">0.289275974035263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291196763515472</t>
+    <t xml:space="preserve">0.291196793317795</t>
   </si>
   <si>
     <t xml:space="preserve">0.286970943212509</t>
@@ -2153,22 +2153,22 @@
     <t xml:space="preserve">0.273525208234787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260847747325897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261616080999374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270067751407623</t>
+    <t xml:space="preserve">0.26084777712822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261616110801697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270067721605301</t>
   </si>
   <si>
     <t xml:space="preserve">0.278519362211227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27314105629921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266994386911392</t>
+    <t xml:space="preserve">0.273141026496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266994416713715</t>
   </si>
   <si>
     <t xml:space="preserve">0.255469471216202</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">0.25316447019577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256621956825256</t>
+    <t xml:space="preserve">0.256621927022934</t>
   </si>
   <si>
     <t xml:space="preserve">0.256237775087357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249322801828384</t>
+    <t xml:space="preserve">0.249322786927223</t>
   </si>
   <si>
     <t xml:space="preserve">0.236261233687401</t>
@@ -2192,28 +2192,28 @@
     <t xml:space="preserve">0.238182038068771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253548622131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267762750387192</t>
+    <t xml:space="preserve">0.25354865193367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267762720584869</t>
   </si>
   <si>
     <t xml:space="preserve">0.283513486385345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27775102853775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294654250144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319624900817871</t>
+    <t xml:space="preserve">0.277750998735428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294654279947281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319624930620193</t>
   </si>
   <si>
     <t xml:space="preserve">0.343827307224274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338449001312256</t>
+    <t xml:space="preserve">0.338449031114578</t>
   </si>
   <si>
     <t xml:space="preserve">0.34075403213501</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">0.338833183050156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338064819574356</t>
+    <t xml:space="preserve">0.338064849376678</t>
   </si>
   <si>
     <t xml:space="preserve">0.336912333965302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333839029073715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330765753984451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328844875097275</t>
+    <t xml:space="preserve">0.333839058876038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330765724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328844904899597</t>
   </si>
   <si>
     <t xml:space="preserve">0.339985698461533</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">0.347668945789337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359962224960327</t>
+    <t xml:space="preserve">0.35996225476265</t>
   </si>
   <si>
     <t xml:space="preserve">0.351894795894623</t>
@@ -2276,85 +2276,85 @@
     <t xml:space="preserve">0.373023837804794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379554629325867</t>
+    <t xml:space="preserve">0.379554599523544</t>
   </si>
   <si>
     <t xml:space="preserve">0.425654411315918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417971134185791</t>
+    <t xml:space="preserve">0.417971104383469</t>
   </si>
   <si>
     <t xml:space="preserve">0.381859630346298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383012115955353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377633839845657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378402143716812</t>
+    <t xml:space="preserve">0.383012145757675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377633810043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378402173519135</t>
   </si>
   <si>
     <t xml:space="preserve">0.381091296672821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380322962999344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348437339067459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400299519300461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383396297693253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379938781261444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388006240129471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428727775812149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368413865566254</t>
+    <t xml:space="preserve">0.380322992801666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348437309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400299549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38339626789093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379938811063766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388006210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428727716207504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368413895368576</t>
   </si>
   <si>
     <t xml:space="preserve">0.344595670700073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334223210811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341906517744064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323466598987579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34036985039711</t>
+    <t xml:space="preserve">0.334223240613937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341906487941742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323466628789902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340369820594788</t>
   </si>
   <si>
     <t xml:space="preserve">0.331149876117706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348821461200714</t>
+    <t xml:space="preserve">0.348821431398392</t>
   </si>
   <si>
     <t xml:space="preserve">0.322314083576202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285818457603455</t>
+    <t xml:space="preserve">0.285818517208099</t>
   </si>
   <si>
     <t xml:space="preserve">0.337680697441101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34536400437355</t>
+    <t xml:space="preserve">0.345363974571228</t>
   </si>
   <si>
     <t xml:space="preserve">0.341522336006165</t>
@@ -2366,61 +2366,61 @@
     <t xml:space="preserve">0.353653132915497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351594626903534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35406482219696</t>
+    <t xml:space="preserve">0.351594597101212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354064851999283</t>
   </si>
   <si>
     <t xml:space="preserve">0.352829694747925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347477555274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345830768346786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341713726520538</t>
+    <t xml:space="preserve">0.347477585077286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345830738544464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341713696718216</t>
   </si>
   <si>
     <t xml:space="preserve">0.342537134885788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348300963640213</t>
+    <t xml:space="preserve">0.348301023244858</t>
   </si>
   <si>
     <t xml:space="preserve">0.359828680753708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241443634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35488823056221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350359499454498</t>
+    <t xml:space="preserve">0.353241413831711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354888200759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350359529256821</t>
   </si>
   <si>
     <t xml:space="preserve">0.345007359981537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339655220508575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342948824167252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341302007436752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333479672670364</t>
+    <t xml:space="preserve">0.339655190706253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342948853969574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341302037239075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333479702472687</t>
   </si>
   <si>
     <t xml:space="preserve">0.320716857910156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319070041179657</t>
+    <t xml:space="preserve">0.319070070981979</t>
   </si>
   <si>
     <t xml:space="preserve">0.321540266275406</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">0.315776437520981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314129650592804</t>
+    <t xml:space="preserve">0.314129620790482</t>
   </si>
   <si>
     <t xml:space="preserve">0.312894493341446</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">0.317834943532944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319481760263443</t>
+    <t xml:space="preserve">0.319481730461121</t>
   </si>
   <si>
     <t xml:space="preserve">0.312071084976196</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">0.308365762233734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310012549161911</t>
+    <t xml:space="preserve">0.310012608766556</t>
   </si>
   <si>
     <t xml:space="preserve">0.314541310071945</t>
@@ -2465,49 +2465,49 @@
     <t xml:space="preserve">0.320305168628693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322775393724442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30960088968277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309189170598984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32112854719162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321951985359192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325245589017868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326892405748367</t>
+    <t xml:space="preserve">0.322775363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309600859880447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309189200401306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321128576993942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32195195555687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32524561882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32689243555069</t>
   </si>
   <si>
     <t xml:space="preserve">0.323187083005905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323598802089691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315364688634872</t>
+    <t xml:space="preserve">0.323598772287369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315364748239517</t>
   </si>
   <si>
     <t xml:space="preserve">0.313306212425232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310424298048019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314953029155731</t>
+    <t xml:space="preserve">0.310424268245697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314952999353409</t>
   </si>
   <si>
     <t xml:space="preserve">0.311247706413269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317011505365372</t>
+    <t xml:space="preserve">0.317011564970016</t>
   </si>
   <si>
     <t xml:space="preserve">0.31742325425148</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">0.311659395694733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316188156604767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319893449544907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304660439491272</t>
+    <t xml:space="preserve">0.316188126802444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319893479347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304660469293594</t>
   </si>
   <si>
     <t xml:space="preserve">0.308777451515198</t>
@@ -2531,25 +2531,25 @@
     <t xml:space="preserve">0.30301359295845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307542383670807</t>
+    <t xml:space="preserve">0.307542324066162</t>
   </si>
   <si>
     <t xml:space="preserve">0.302601933479309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307954043149948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306307256221771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301778525114059</t>
+    <t xml:space="preserve">0.307954102754593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306307286024094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301778495311737</t>
   </si>
   <si>
     <t xml:space="preserve">0.303837031126022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300955086946487</t>
+    <t xml:space="preserve">0.300955146551132</t>
   </si>
   <si>
     <t xml:space="preserve">0.301366776227951</t>
@@ -2558,16 +2558,16 @@
     <t xml:space="preserve">0.302190244197845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313717901706696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326480686664581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328539192676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340890318155289</t>
+    <t xml:space="preserve">0.313717931509018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326480716466904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328539222478867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340890347957611</t>
   </si>
   <si>
     <t xml:space="preserve">0.356535077095032</t>
@@ -2588,10 +2588,10 @@
     <t xml:space="preserve">0.358181864023209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3470658659935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34418398141861</t>
+    <t xml:space="preserve">0.347065836191177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344183951616287</t>
   </si>
   <si>
     <t xml:space="preserve">0.336773306131363</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">0.349124372005463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338008403778076</t>
+    <t xml:space="preserve">0.338008373975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.335949867963791</t>
@@ -2612,28 +2612,28 @@
     <t xml:space="preserve">0.343772232532501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33759668469429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340066939592361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340478628873825</t>
+    <t xml:space="preserve">0.337596714496613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340066909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340478658676147</t>
   </si>
   <si>
     <t xml:space="preserve">0.332244545221329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329362660646439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325657337903976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33842009305954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346654176712036</t>
+    <t xml:space="preserve">0.329362630844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325657308101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338420122861862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346654206514359</t>
   </si>
   <si>
     <t xml:space="preserve">0.35571163892746</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">0.399763911962509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389471292495728</t>
+    <t xml:space="preserve">0.38947132229805</t>
   </si>
   <si>
     <t xml:space="preserve">0.401822417974472</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">0.411703318357468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402234137058258</t>
+    <t xml:space="preserve">0.402234107255936</t>
   </si>
   <si>
     <t xml:space="preserve">0.403469234704971</t>
@@ -2678,55 +2678,55 @@
     <t xml:space="preserve">0.409644782543182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408409655094147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405939429998398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406351178884506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400175631046295</t>
+    <t xml:space="preserve">0.408409684896469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40593945980072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406351149082184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40017557144165</t>
   </si>
   <si>
     <t xml:space="preserve">0.397705405950546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403880923986435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403057485818863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394823491573334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417467147111893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433111876249313</t>
+    <t xml:space="preserve">0.403880953788757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403057515621185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394823461771011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417467176914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433111846446991</t>
   </si>
   <si>
     <t xml:space="preserve">0.430641621351242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441345900297165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454520374536514</t>
+    <t xml:space="preserve">0.441345930099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454520404338837</t>
   </si>
   <si>
     <t xml:space="preserve">0.442992746829987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488280117511749</t>
+    <t xml:space="preserve">0.488280057907104</t>
   </si>
   <si>
     <t xml:space="preserve">0.50392484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534390926361084</t>
+    <t xml:space="preserve">0.534390807151794</t>
   </si>
   <si>
     <t xml:space="preserve">0.518746137619019</t>
@@ -2738,43 +2738,43 @@
     <t xml:space="preserve">0.500631153583527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517922699451447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469341814517975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485809832811356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462754487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472635388374329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493220567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573691368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48169282078743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467694908380508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461107701063156</t>
+    <t xml:space="preserve">0.517922759056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46934175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485809922218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462754458189011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472635358572006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49322047829628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491573750972748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481692850589752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467694967985153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461107671260834</t>
   </si>
   <si>
     <t xml:space="preserve">0.476752430200577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479222655296326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477575778961182</t>
+    <t xml:space="preserve">0.479222625494003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477575838565826</t>
   </si>
   <si>
     <t xml:space="preserve">0.51545250415802</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">0.498984396457672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494044005870819</t>
+    <t xml:space="preserve">0.494043946266174</t>
   </si>
   <si>
     <t xml:space="preserve">0.505571722984314</t>
@@ -2798,19 +2798,19 @@
     <t xml:space="preserve">0.490750342607498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484986424446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492397159337997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482516258955002</t>
+    <t xml:space="preserve">0.484986454248428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492397099733353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482516229152679</t>
   </si>
   <si>
     <t xml:space="preserve">0.478399187326431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473458737134933</t>
+    <t xml:space="preserve">0.473458796739578</t>
   </si>
   <si>
     <t xml:space="preserve">0.470988631248474</t>
@@ -2819,31 +2819,31 @@
     <t xml:space="preserve">0.470165133476257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465224713087082</t>
+    <t xml:space="preserve">0.465224742889404</t>
   </si>
   <si>
     <t xml:space="preserve">0.460284292697906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468518376350403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46675032377243</t>
+    <t xml:space="preserve">0.46851834654808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466750353574753</t>
   </si>
   <si>
     <t xml:space="preserve">0.473822295665741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.457910388708115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46144637465477</t>
+    <t xml:space="preserve">0.457910418510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461446404457092</t>
   </si>
   <si>
     <t xml:space="preserve">0.464098364114761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454374372959137</t>
+    <t xml:space="preserve">0.454374402761459</t>
   </si>
   <si>
     <t xml:space="preserve">0.441114455461502</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">0.426528483629227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433158487081528</t>
+    <t xml:space="preserve">0.433158457279205</t>
   </si>
   <si>
     <t xml:space="preserve">0.448186427354813</t>
@@ -2876,16 +2876,16 @@
     <t xml:space="preserve">0.434484452009201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44465047121048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449070423841476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437578439712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433600455522537</t>
+    <t xml:space="preserve">0.444650441408157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449070453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437578469514847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43360048532486</t>
   </si>
   <si>
     <t xml:space="preserve">0.430948466062546</t>
@@ -2900,13 +2900,13 @@
     <t xml:space="preserve">0.429622501134872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428738474845886</t>
+    <t xml:space="preserve">0.428738504648209</t>
   </si>
   <si>
     <t xml:space="preserve">0.424318492412567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434042483568192</t>
+    <t xml:space="preserve">0.434042453765869</t>
   </si>
   <si>
     <t xml:space="preserve">0.421666502952576</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">0.419456511735916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417246520519257</t>
+    <t xml:space="preserve">0.417246550321579</t>
   </si>
   <si>
     <t xml:space="preserve">0.411942541599274</t>
@@ -2930,22 +2930,22 @@
     <t xml:space="preserve">0.414152532815933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418130487203598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42255049943924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413710534572601</t>
+    <t xml:space="preserve">0.41813051700592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422550469636917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413710504770279</t>
   </si>
   <si>
     <t xml:space="preserve">0.425202459096909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423876523971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414594560861588</t>
+    <t xml:space="preserve">0.423876494169235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41459459066391</t>
   </si>
   <si>
     <t xml:space="preserve">0.422992497682571</t>
@@ -2957,10 +2957,10 @@
     <t xml:space="preserve">0.413268536329269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415920495986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408406585454941</t>
+    <t xml:space="preserve">0.415920525789261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408406555652618</t>
   </si>
   <si>
     <t xml:space="preserve">0.412384569644928</t>
@@ -2993,22 +2993,22 @@
     <t xml:space="preserve">0.424760520458221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422108501195908</t>
+    <t xml:space="preserve">0.42210853099823</t>
   </si>
   <si>
     <t xml:space="preserve">0.415478527545929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402218610048294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394262611865997</t>
+    <t xml:space="preserve">0.402218580245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39426264166832</t>
   </si>
   <si>
     <t xml:space="preserve">0.400008589029312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401334583759308</t>
+    <t xml:space="preserve">0.401334553956985</t>
   </si>
   <si>
     <t xml:space="preserve">0.39249461889267</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">0.396030604839325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405754536390305</t>
+    <t xml:space="preserve">0.405754566192627</t>
   </si>
   <si>
     <t xml:space="preserve">0.403544545173645</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">0.400450587272644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389842659235001</t>
+    <t xml:space="preserve">0.389842629432678</t>
   </si>
   <si>
     <t xml:space="preserve">0.388958632946014</t>
@@ -3050,16 +3050,16 @@
     <t xml:space="preserve">0.39779856801033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401776552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406638562679291</t>
+    <t xml:space="preserve">0.40177658200264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406638592481613</t>
   </si>
   <si>
     <t xml:space="preserve">0.402660578489304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41989853978157</t>
+    <t xml:space="preserve">0.419898509979248</t>
   </si>
   <si>
     <t xml:space="preserve">0.436694443225861</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">0.453334271907806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462902158498764</t>
+    <t xml:space="preserve">0.462902188301086</t>
   </si>
   <si>
     <t xml:space="preserve">0.459257245063782</t>
@@ -3092,19 +3092,19 @@
     <t xml:space="preserve">0.464724570512772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468369483947754</t>
+    <t xml:space="preserve">0.468369513750076</t>
   </si>
   <si>
     <t xml:space="preserve">0.480215430259705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482949078083038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481126606464386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482037842273712</t>
+    <t xml:space="preserve">0.482949048280716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481126636266708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482037872076035</t>
   </si>
   <si>
     <t xml:space="preserve">0.479304194450378</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">0.52577668428421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523954153060913</t>
+    <t xml:space="preserve">0.523954212665558</t>
   </si>
   <si>
     <t xml:space="preserve">0.510285794734955</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753149986267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507552087306976</t>
+    <t xml:space="preserve">0.515753209590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507552146911621</t>
   </si>
   <si>
     <t xml:space="preserve">0.511197030544281</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">0.514841914176941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519398093223572</t>
+    <t xml:space="preserve">0.519398033618927</t>
   </si>
   <si>
     <t xml:space="preserve">0.51393073797226</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267395019531</t>
+    <t xml:space="preserve">0.541267454624176</t>
   </si>
   <si>
     <t xml:space="preserve">0.546734869480133</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">0.537622570991516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549468457698822</t>
+    <t xml:space="preserve">0.549468517303467</t>
   </si>
   <si>
     <t xml:space="preserve">0.554935872554779</t>
@@ -3209,16 +3209,16 @@
     <t xml:space="preserve">0.550379693508148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547646045684814</t>
+    <t xml:space="preserve">0.547646105289459</t>
   </si>
   <si>
     <t xml:space="preserve">0.55584704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553113400936127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564048111438751</t>
+    <t xml:space="preserve">0.553113341331482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564048051834106</t>
   </si>
   <si>
     <t xml:space="preserve">0.559491991996765</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">0.542178750038147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557669520378113</t>
+    <t xml:space="preserve">0.557669460773468</t>
   </si>
   <si>
     <t xml:space="preserve">0.534888863563538</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">0.527599096298218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516664385795593</t>
+    <t xml:space="preserve">0.516664326190948</t>
   </si>
   <si>
     <t xml:space="preserve">0.490238875150681</t>
@@ -3278,13 +3278,13 @@
     <t xml:space="preserve">0.497528702020645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492061346769333</t>
+    <t xml:space="preserve">0.492061406373978</t>
   </si>
   <si>
     <t xml:space="preserve">0.488416403532028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483860313892365</t>
+    <t xml:space="preserve">0.483860343694687</t>
   </si>
   <si>
     <t xml:space="preserve">0.487505257129669</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">0.491150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517575621604919</t>
+    <t xml:space="preserve">0.517575681209564</t>
   </si>
   <si>
     <t xml:space="preserve">0.489643454551697</t>
@@ -3974,7 +3974,16 @@
     <t xml:space="preserve">0.558000028133392</t>
   </si>
   <si>
+    <t xml:space="preserve">0.549000024795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533999979496002</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.521000027656555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52700001001358</t>
   </si>
 </sst>
 </file>
@@ -69417,27 +69426,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6909722222</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>1446006</v>
+        <v>367143</v>
       </c>
       <c r="C2505" t="n">
-        <v>0.541999995708466</v>
+        <v>0.560999989509583</v>
       </c>
       <c r="D2505" t="n">
-        <v>0.513999998569489</v>
+        <v>0.546999990940094</v>
       </c>
       <c r="E2505" t="n">
-        <v>0.53600001335144</v>
+        <v>0.560000002384186</v>
       </c>
       <c r="F2505" t="n">
-        <v>0.521000027656555</v>
+        <v>0.549000024795532</v>
       </c>
       <c r="G2505" t="s">
         <v>1320</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>432154</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>0.549000024795532</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>0.531000018119812</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>0.546999990940094</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>0.533999979496002</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1321</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>1446006</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>0.541999995708466</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>0.513999998569489</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>0.53600001335144</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>0.521000027656555</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6917708333</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>577724</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>0.546999990940094</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>0.518999993801117</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>0.527999997138977</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>0.52700001001358</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1323</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="1325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="1326">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333736181259155</t>
+    <t xml:space="preserve">0.33373612165451</t>
   </si>
   <si>
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327446222305298</t>
+    <t xml:space="preserve">0.327446281909943</t>
   </si>
   <si>
     <t xml:space="preserve">0.321156293153763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317678362131119</t>
+    <t xml:space="preserve">0.317678332328796</t>
   </si>
   <si>
     <t xml:space="preserve">0.307318478822708</t>
@@ -59,28 +59,28 @@
     <t xml:space="preserve">0.288448721170425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289336651563644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294368654489517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285636752843857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273796856403351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258997052907944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258257031440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243605226278305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246417179703712</t>
+    <t xml:space="preserve">0.289336711168289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294368624687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285636723041534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273796886205673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258997023105621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258257061243057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243605181574821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246417194604874</t>
   </si>
   <si>
     <t xml:space="preserve">0.262696981430054</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">0.256407082080841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.259811013936996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261513024568558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253817051649094</t>
+    <t xml:space="preserve">0.259810984134674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261512964963913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253817111253738</t>
   </si>
   <si>
     <t xml:space="preserve">0.253077119588852</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">0.286894708871841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284600734710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277496874332428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287116706371307</t>
+    <t xml:space="preserve">0.284600764513016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277496814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28711673617363</t>
   </si>
   <si>
     <t xml:space="preserve">0.290742665529251</t>
@@ -119,31 +119,31 @@
     <t xml:space="preserve">0.263806968927383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256777077913284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.250117123126984</t>
+    <t xml:space="preserve">0.256777048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.250117152929306</t>
   </si>
   <si>
     <t xml:space="preserve">0.277570813894272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297994613647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310796439647675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303544521331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304358541965485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318122357130051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309686422348022</t>
+    <t xml:space="preserve">0.297994583845139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310796409845352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303544491529465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304358512163162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318122327327728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309686452150345</t>
   </si>
   <si>
     <t xml:space="preserve">0.30162051320076</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">0.323376297950745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320046365261078</t>
+    <t xml:space="preserve">0.320046335458755</t>
   </si>
   <si>
     <t xml:space="preserve">0.316716402769089</t>
@@ -164,25 +164,25 @@
     <t xml:space="preserve">0.315236389636993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315606385469437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332996189594269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332256227731705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328852236270905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330480188131332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311240404844284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312054395675659</t>
+    <t xml:space="preserve">0.315606415271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332996159791946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332256197929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328852266073227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330480247735977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311240434646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312054425477982</t>
   </si>
   <si>
     <t xml:space="preserve">0.299696564674377</t>
@@ -194,28 +194,28 @@
     <t xml:space="preserve">0.299400568008423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297476559877396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295996636152267</t>
+    <t xml:space="preserve">0.29747661948204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295996606349945</t>
   </si>
   <si>
     <t xml:space="preserve">0.293702632188797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298216640949249</t>
+    <t xml:space="preserve">0.298216581344604</t>
   </si>
   <si>
     <t xml:space="preserve">0.286376714706421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276756852865219</t>
+    <t xml:space="preserve">0.276756823062897</t>
   </si>
   <si>
     <t xml:space="preserve">0.274536848068237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2723169028759</t>
+    <t xml:space="preserve">0.272316843271255</t>
   </si>
   <si>
     <t xml:space="preserve">0.268542915582657</t>
@@ -224,25 +224,25 @@
     <t xml:space="preserve">0.270466923713684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26506495475769</t>
+    <t xml:space="preserve">0.265065014362335</t>
   </si>
   <si>
     <t xml:space="preserve">0.268172919750214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268616914749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269208878278732</t>
+    <t xml:space="preserve">0.268616944551468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269208908081055</t>
   </si>
   <si>
     <t xml:space="preserve">0.275276869535446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284896731376648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290002673864365</t>
+    <t xml:space="preserve">0.28489676117897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290002644062042</t>
   </si>
   <si>
     <t xml:space="preserve">0.308206468820572</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">0.309168487787247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318196386098862</t>
+    <t xml:space="preserve">0.318196356296539</t>
   </si>
   <si>
     <t xml:space="preserve">0.316938370466232</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">0.308946460485458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314200401306152</t>
+    <t xml:space="preserve">0.31420037150383</t>
   </si>
   <si>
     <t xml:space="preserve">0.321378320455551</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">0.319380342960358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310722410678864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313682407140732</t>
+    <t xml:space="preserve">0.310722440481186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313682436943054</t>
   </si>
   <si>
     <t xml:space="preserve">0.313312441110611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30709645152092</t>
+    <t xml:space="preserve">0.307096481323242</t>
   </si>
   <si>
     <t xml:space="preserve">0.307614475488663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304950535297394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305616468191147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299548536539078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305320501327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295626640319824</t>
+    <t xml:space="preserve">0.304950475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305616497993469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299548596143723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305320531129837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295626610517502</t>
   </si>
   <si>
     <t xml:space="preserve">0.300954550504684</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">0.314400345087051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318779826164246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318856596946716</t>
+    <t xml:space="preserve">0.318779796361923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318856626749039</t>
   </si>
   <si>
     <t xml:space="preserve">0.318395644426346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319932281970978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318088322877884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307331711053848</t>
+    <t xml:space="preserve">0.319932252168655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318088293075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307331651449203</t>
   </si>
   <si>
     <t xml:space="preserve">0.321776270866394</t>
@@ -329,22 +329,22 @@
     <t xml:space="preserve">0.320393264293671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311557471752167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305795043706894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301569193601608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295806735754013</t>
+    <t xml:space="preserve">0.311557501554489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305795013904572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301569253206253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295806765556335</t>
   </si>
   <si>
     <t xml:space="preserve">0.299648374319077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296575099229813</t>
+    <t xml:space="preserve">0.29657506942749</t>
   </si>
   <si>
     <t xml:space="preserve">0.303490042686462</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">0.318011432886124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318702936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32116162776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310020804405212</t>
+    <t xml:space="preserve">0.318702906370163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321161597967148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310020834207535</t>
   </si>
   <si>
     <t xml:space="preserve">0.311941653490067</t>
@@ -371,22 +371,22 @@
     <t xml:space="preserve">0.311173349618912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307254821062088</t>
+    <t xml:space="preserve">0.30725485086441</t>
   </si>
   <si>
     <t xml:space="preserve">0.30671700835228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305564492940903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304949879646301</t>
+    <t xml:space="preserve">0.305564552545547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304949849843979</t>
   </si>
   <si>
     <t xml:space="preserve">0.306870669126511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297727584838867</t>
+    <t xml:space="preserve">0.297727555036545</t>
   </si>
   <si>
     <t xml:space="preserve">0.301799714565277</t>
@@ -398,31 +398,31 @@
     <t xml:space="preserve">0.300032556056976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313478320837021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31255629658699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307869523763657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311480671167374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298265427350998</t>
+    <t xml:space="preserve">0.313478291034698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312556326389313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307869493961334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311480641365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298265397548676</t>
   </si>
   <si>
     <t xml:space="preserve">0.299110561609268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305257201194763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295576274394989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295960426330566</t>
+    <t xml:space="preserve">0.305257171392441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295576214790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295960396528244</t>
   </si>
   <si>
     <t xml:space="preserve">0.297650724649429</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">0.297881245613098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293732225894928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298803210258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300416707992554</t>
+    <t xml:space="preserve">0.29373225569725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298803240060806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300416737794876</t>
   </si>
   <si>
     <t xml:space="preserve">0.300109386444092</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">0.298880070447922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30548769235611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30955982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303105860948563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303566873073578</t>
+    <t xml:space="preserve">0.305487662553787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309559851884842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303105890750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303566843271255</t>
   </si>
   <si>
     <t xml:space="preserve">0.308253675699234</t>
@@ -467,25 +467,25 @@
     <t xml:space="preserve">0.306563347578049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30018624663353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298649579286575</t>
+    <t xml:space="preserve">0.300186276435852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298649549484253</t>
   </si>
   <si>
     <t xml:space="preserve">0.296421408653259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3014155626297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300647228956223</t>
+    <t xml:space="preserve">0.301415532827377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3006471991539</t>
   </si>
   <si>
     <t xml:space="preserve">0.282975643873215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291965067386627</t>
+    <t xml:space="preserve">0.291965126991272</t>
   </si>
   <si>
     <t xml:space="preserve">0.289736926555634</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">0.292656600475311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292502909898758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289583295583725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288123488426208</t>
+    <t xml:space="preserve">0.29250293970108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289583265781403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288123458623886</t>
   </si>
   <si>
     <t xml:space="preserve">0.284281820058823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28789296746254</t>
+    <t xml:space="preserve">0.287892997264862</t>
   </si>
   <si>
     <t xml:space="preserve">0.290044277906418</t>
@@ -518,37 +518,37 @@
     <t xml:space="preserve">0.292887061834335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293117582798004</t>
+    <t xml:space="preserve">0.293117612600327</t>
   </si>
   <si>
     <t xml:space="preserve">0.291888296604156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289813786745071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286586761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294270128011703</t>
+    <t xml:space="preserve">0.289813756942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286586791276932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294270068407059</t>
   </si>
   <si>
     <t xml:space="preserve">0.291811406612396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292579799890518</t>
+    <t xml:space="preserve">0.292579770088196</t>
   </si>
   <si>
     <t xml:space="preserve">0.29572993516922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298419028520584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294731080532074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287355124950409</t>
+    <t xml:space="preserve">0.298419058322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294731110334396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287355095148087</t>
   </si>
   <si>
     <t xml:space="preserve">0.293809086084366</t>
@@ -560,34 +560,34 @@
     <t xml:space="preserve">0.286740481853485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284665942192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278903514146805</t>
+    <t xml:space="preserve">0.284666001796722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278903484344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.275599658489227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270221382379532</t>
+    <t xml:space="preserve">0.270221412181854</t>
   </si>
   <si>
     <t xml:space="preserve">0.272449523210526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276675373315811</t>
+    <t xml:space="preserve">0.276675343513489</t>
   </si>
   <si>
     <t xml:space="preserve">0.27398619055748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275676548480988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275522887706757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276598513126373</t>
+    <t xml:space="preserve">0.275676488876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275522857904434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276598542928696</t>
   </si>
   <si>
     <t xml:space="preserve">0.270989716053009</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">0.270451873540878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268146872520447</t>
+    <t xml:space="preserve">0.268146932125092</t>
   </si>
   <si>
     <t xml:space="preserve">0.267378568649292</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">0.265765070915222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262384444475174</t>
+    <t xml:space="preserve">0.262384474277496</t>
   </si>
   <si>
     <t xml:space="preserve">0.267532229423523</t>
@@ -623,25 +623,25 @@
     <t xml:space="preserve">0.265304088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27191174030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272526353597641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283283025026321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279902338981628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277059495449066</t>
+    <t xml:space="preserve">0.271911710500717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272526383399963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283282995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279902368783951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277059525251389</t>
   </si>
   <si>
     <t xml:space="preserve">0.27844250202179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280517041683197</t>
+    <t xml:space="preserve">0.280516982078552</t>
   </si>
   <si>
     <t xml:space="preserve">0.278749823570251</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">0.27898034453392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278212010860443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284051328897476</t>
+    <t xml:space="preserve">0.278212040662766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284051358699799</t>
   </si>
   <si>
     <t xml:space="preserve">0.290812611579895</t>
@@ -662,22 +662,22 @@
     <t xml:space="preserve">0.28966012597084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290428459644318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294807910919189</t>
+    <t xml:space="preserve">0.290428429841995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294807940721512</t>
   </si>
   <si>
     <t xml:space="preserve">0.295422583818436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288507610559464</t>
+    <t xml:space="preserve">0.288507580757141</t>
   </si>
   <si>
     <t xml:space="preserve">0.284589141607285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291043132543564</t>
+    <t xml:space="preserve">0.291043102741241</t>
   </si>
   <si>
     <t xml:space="preserve">0.293885916471481</t>
@@ -686,16 +686,16 @@
     <t xml:space="preserve">0.294884741306305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289890617132187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286125779151917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284358590841293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282745122909546</t>
+    <t xml:space="preserve">0.289890646934509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286125808954239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284358650445938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282745152711868</t>
   </si>
   <si>
     <t xml:space="preserve">0.277290016412735</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">0.281976848840714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276214361190796</t>
+    <t xml:space="preserve">0.276214331388474</t>
   </si>
   <si>
     <t xml:space="preserve">0.27360200881958</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">0.269760370254517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275061875581741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271834880113602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273371547460556</t>
+    <t xml:space="preserve">0.275061845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271834850311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273371577262878</t>
   </si>
   <si>
     <t xml:space="preserve">0.275215536355972</t>
@@ -728,19 +728,19 @@
     <t xml:space="preserve">0.276905834674835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274831384420395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282668322324753</t>
+    <t xml:space="preserve">0.27483132481575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282668352127075</t>
   </si>
   <si>
     <t xml:space="preserve">0.280440151691437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279594987630844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277366876602173</t>
+    <t xml:space="preserve">0.279595017433167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27736684679985</t>
   </si>
   <si>
     <t xml:space="preserve">0.278135150671005</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">0.279364496469498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285587966442108</t>
+    <t xml:space="preserve">0.285587936639786</t>
   </si>
   <si>
     <t xml:space="preserve">0.279671847820282</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">0.284435480833054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281899958848953</t>
+    <t xml:space="preserve">0.281899988651276</t>
   </si>
   <si>
     <t xml:space="preserve">0.283897668123245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285280644893646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285434275865555</t>
+    <t xml:space="preserve">0.285280615091324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2854343354702</t>
   </si>
   <si>
     <t xml:space="preserve">0.295038402080536</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">0.304258346557617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321929931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325617879629135</t>
+    <t xml:space="preserve">0.321929901838303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325617909431458</t>
   </si>
   <si>
     <t xml:space="preserve">0.33184140920639</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">0.325387448072433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316935807466507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309790313243866</t>
+    <t xml:space="preserve">0.316935777664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309790343046188</t>
   </si>
   <si>
     <t xml:space="preserve">0.30925253033638</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">0.311096489429474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313094168901443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313017308712006</t>
+    <t xml:space="preserve">0.313094139099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31301736831665</t>
   </si>
   <si>
     <t xml:space="preserve">0.288891762495041</t>
@@ -824,58 +824,58 @@
     <t xml:space="preserve">0.293040752410889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295192092657089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296805560588837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29726654291153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298111736774445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310251325368881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313555181026459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300800889730453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30886834859848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299725234508514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321853131055832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327308237552643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318472415208817</t>
+    <t xml:space="preserve">0.295192122459412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296805590391159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297266572713852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298111766576767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310251355171204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313555151224136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300800859928131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308868378400803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299725204706192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32185310125351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32730820775032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318472474813461</t>
   </si>
   <si>
     <t xml:space="preserve">0.312095314264297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314016133546829</t>
+    <t xml:space="preserve">0.314016163349152</t>
   </si>
   <si>
     <t xml:space="preserve">0.315014958381653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312249004840851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313939332962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309636682271957</t>
+    <t xml:space="preserve">0.312248945236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313939303159714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309636652469635</t>
   </si>
   <si>
     <t xml:space="preserve">0.307408511638641</t>
@@ -884,16 +884,16 @@
     <t xml:space="preserve">0.308945178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313631981611252</t>
+    <t xml:space="preserve">0.313632011413574</t>
   </si>
   <si>
     <t xml:space="preserve">0.308023184537888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307715862989426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309022009372711</t>
+    <t xml:space="preserve">0.307715833187103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309021979570389</t>
   </si>
   <si>
     <t xml:space="preserve">0.309944003820419</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">0.3177809715271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316551595926285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316474795341492</t>
+    <t xml:space="preserve">0.316551625728607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316474825143814</t>
   </si>
   <si>
     <t xml:space="preserve">0.324388593435287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325003236532211</t>
+    <t xml:space="preserve">0.325003296136856</t>
   </si>
   <si>
     <t xml:space="preserve">0.318318784236908</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">0.320470124483109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322621434926987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323697090148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333454847335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327385097742081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331764549016953</t>
+    <t xml:space="preserve">0.322621464729309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323697119951248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333454877138138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327385067939758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331764578819275</t>
   </si>
   <si>
     <t xml:space="preserve">0.339524686336517</t>
@@ -950,22 +950,22 @@
     <t xml:space="preserve">0.340446680784225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3333780169487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33499151468277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336144030094147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337757498025894</t>
+    <t xml:space="preserve">0.333378046751022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334991544485092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336144059896469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337757527828217</t>
   </si>
   <si>
     <t xml:space="preserve">0.338910013437271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338141679763794</t>
+    <t xml:space="preserve">0.338141709566116</t>
   </si>
   <si>
     <t xml:space="preserve">0.339678317308426</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">0.350358098745346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34659332036972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344211488962173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34067714214325</t>
+    <t xml:space="preserve">0.346593290567398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344211518764496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340677171945572</t>
   </si>
   <si>
     <t xml:space="preserve">0.334607392549515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338218539953232</t>
+    <t xml:space="preserve">0.338218569755554</t>
   </si>
   <si>
     <t xml:space="preserve">0.346900641918182</t>
@@ -995,31 +995,31 @@
     <t xml:space="preserve">0.346132308244705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339601516723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340907663106918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352663069963455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369950532913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365417391061783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363035529851913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374099493026733</t>
+    <t xml:space="preserve">0.33960148692131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340907692909241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3526631295681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36995056271553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36541736125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363035559654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374099463224411</t>
   </si>
   <si>
     <t xml:space="preserve">0.371103018522263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369566321372986</t>
+    <t xml:space="preserve">0.369566380977631</t>
   </si>
   <si>
     <t xml:space="preserve">0.368798017501831</t>
@@ -1031,19 +1031,19 @@
     <t xml:space="preserve">0.363112419843674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368644386529922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366877168416977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366262555122375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361114710569382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359885394573212</t>
+    <t xml:space="preserve">0.368644326925278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366877198219299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366262525320053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361114740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359885424375534</t>
   </si>
   <si>
     <t xml:space="preserve">0.359193921089172</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.368567526340485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372025012969971</t>
+    <t xml:space="preserve">0.372024983167648</t>
   </si>
   <si>
     <t xml:space="preserve">0.37555930018425</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">0.380246102809906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392616182565689</t>
+    <t xml:space="preserve">0.392616212368011</t>
   </si>
   <si>
     <t xml:space="preserve">0.405677825212479</t>
@@ -1073,1726 +1073,1726 @@
     <t xml:space="preserve">0.419507741928101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396842032670975</t>
+    <t xml:space="preserve">0.396842062473297</t>
   </si>
   <si>
     <t xml:space="preserve">0.413361102342606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422581046819687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417586892843246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42642268538475</t>
+    <t xml:space="preserve">0.422581106424332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417586922645569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426422715187073</t>
   </si>
   <si>
     <t xml:space="preserve">0.423349350690842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427959352731705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436795145273209</t>
+    <t xml:space="preserve">0.427959412336349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436795175075531</t>
   </si>
   <si>
     <t xml:space="preserve">0.432953476905823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452930092811584</t>
+    <t xml:space="preserve">0.452930063009262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460854530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46522331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296617269516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481358230113983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522463858127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5151646733284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505560576915741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507097244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515548884868622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503255665302277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489809900522232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480205774307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519006311893463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511323094367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499413967132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491730690002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484431594610214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483663231134415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484815746545792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495188176631927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490194082260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553197085857391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542056202888489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56280118227005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586235225200653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600065112113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582393527030945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572021126747131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572789430618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552428662776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55127614736557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545129656791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565874516963959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577015161514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596607565879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584698498249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608132481575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621962487697601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620425879955292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629645824432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614279210567474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60774838924408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58162522315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560880303382874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598528444766998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598144352436066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619657516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618120789527893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601601719856262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58661937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59545511007309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587771832942963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584314405918121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577399492263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567026913166046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574326038360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543592870235443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564722001552582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.563185334205627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576246917247772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583930253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58085685968399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587003529071808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604675114154816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629261672496796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61850506067276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606980085372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603138506412506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612358391284943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611590027809143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593918442726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596991837024689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608516693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599296748638153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589308500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553965389728546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538598775863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5570387840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536293864250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524000525474548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537830471992493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547818720340729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532452166080475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537062168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527073860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52092719078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517853856086731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525537133216858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530147194862366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523232161998749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519390642642975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524768948554993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549355447292328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501718997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492499053478241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477900743484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476364135742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48865732550621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471754163503647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472522467374802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468680769205093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487120777368546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481742382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480974078178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483279079198837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478669106960297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470217496156693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467912524938583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466375797986984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839190244675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461765855550766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487889021635056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500182390213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469449192285538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437179297208786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444862604141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431800991296768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444094270467758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424117684364319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415666103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382627934217453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379170477390289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382243782281876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385701268911362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388774573802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391847878694534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384164601564407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37648132443428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367261350154877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364956378936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360346406698227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3522789478302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356504738330841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37148717045784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368029713630676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372255504131317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365340501070023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374944657087326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3664930164814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374560534954071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374176293611526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37878629565239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362267255783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353815644979477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354583919048309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353047281503677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370718836784363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35419973731041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395689517259598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411056190729141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40798282623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384932905435562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39031121134758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378018021583557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380707114934921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362651377916336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359578043222427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353431463241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349589794874191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344979852437973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343059003353119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354968100786209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36418804526329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357273072004318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349973976612091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339217334985733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323850750923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361883074045181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350742280483246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389542937278748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404141157865524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39645791053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412592798471451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404909521341324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401836186647415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394152909517288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399531155824661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40260449051857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401067852973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397994548082352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375712960958481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36457222700119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345748156309128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336528211832047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335759878158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337296515703201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329613208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328076601028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331534057855606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319240778684616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326924085617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312709987163544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341138184070587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322698265314102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326155751943588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324619084596634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325771570205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330381542444229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329997390508652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324234932661057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313862472772598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301185071468353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30387419462204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296959221363068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302721709012985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32308241724968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308100044727325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310405015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306947499513626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314630836248398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305410861968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30848416686058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304642498493195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320777416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356888890266418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358041405677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356120586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360730558633804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358809769153595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351126462221146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355736434459686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342290669679642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37187135219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370334655046463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383780419826508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376097142696381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376865476369858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377249658107758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398762851953506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403372824192047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406446099281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40951943397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39107957482338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381475418806076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407214462757111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387237936258316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394921213388443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411824434995651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414897829294205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417202711105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397226184606552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40875118970871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410287797451019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414129436016083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416434407234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418739438056946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4202761054039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421812772750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430264413356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473290771245956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49480402469635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484047383069992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267297744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506328880786896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479437470436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48251074552536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595772266388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070826768875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465607553720474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460997492074966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453314214944839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434105962514877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789269447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44563090801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449472546577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45100924372673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460229218006134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454082578420639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457155853509903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451777547597885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456387519836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46330252289772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470985800027847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467144101858139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457924246788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447167634963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432569354772568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437947660684586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433337718248367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434874325990677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436410993337631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43948432803154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441020965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440252631902695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43871596455574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442557603120804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485584050416946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455619215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443326026201248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429496049880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435642689466476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450240910053253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427191019058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375328838825226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386469602584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393384575843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365724712610245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372639685869217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351510614156723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342674851417542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317319959402084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265073597431183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259695321321487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239334553480148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242023691534996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234724596142769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245865345001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258926928043365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.251627832651138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266610234975815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269299387931824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258158624172211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.251243680715561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.252011984586716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242407873272896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245097041130066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254701137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262000262737274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254316955804825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261231929063797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262768566608429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264689445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271988570690155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273909360170364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276982694864273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27275687456131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275446027517319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268915235996246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265841901302338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25854280591011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26545774936676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263152748346329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292733460664749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327692419290543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302337557077408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30195340514183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332302391529083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332686543464661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306179195642471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305026710033417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312325805425644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331918239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315399140119553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326539933681488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292349249124527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289275944232941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291196763515472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286970943212509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2850501537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273525208234787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260847747325897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261616080999374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270067721605301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27851939201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27314105629921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266994386911392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.255469471216202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253164440393448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256621956825256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256237775087357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.249322831630707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.236261233687401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238182067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253548622131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267762750387192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283513456583023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277750998735428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294654250144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319624990224838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343827307224274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338449001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340753972530365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338833212852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338064819574356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336912333965302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333839058876038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330765724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328844904899597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33998566865921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347668945789337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359962224960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351894795894623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369182199239731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357657223939896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355352252721786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348053157329559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34651643037796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347284764051437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363419681787491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373792141675949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373023808002472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379554629325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42565444111824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417971104383469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381859630346298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383012115955353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377633810043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378402173519135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381091266870499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380322962999344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348437309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400299549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383396297693253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379938811063766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388006269931793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428727656602859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368413865566254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344595670700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334223181009293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341906487941742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323466569185257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340369820594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331149876117706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348821461200714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322314113378525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285818487405777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337680667638779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345363974571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341522365808487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329229056835175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353653132915497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351594626903534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35406482219696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352829694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347477585077286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345830768346786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341713726520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34253716468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348301023244858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359828680753708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353241413831711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35488823056221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350359499454498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345007330179214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339655190706253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342948853969574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341302037239075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333479672670364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320716857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319070041179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321540266275406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310835987329483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315776437520981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314129620790482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312894523143768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318246632814407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317834943532944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319481790065765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312071084976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308365762233734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310012578964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314541310071945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318658322095871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320305168628693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322775393724442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309600859880447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309189140796661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32112854719162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321951985359192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32524561882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32689243555069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323187112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323598802089691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315364688634872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31330618262291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310424298048019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314952999353409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311247676610947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317011564970016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317423224449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311659395694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316188126802444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319893479347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304660439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30877748131752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303013622760773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307542353868484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302601933479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307954043149948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306307256221771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301778525114059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3038370013237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300955086946487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301366806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302190244197845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313717931509018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326480686664581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328539222478867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340890318155289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356535047292709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343360543251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336361587047577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339243501424789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335126489400864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358181834220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3470658659935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344183951616287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336773306131363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345419079065323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349124372005463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338008403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335949867963791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343772202730179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33759668469429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340066909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340478628873825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332244545221329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329362601041794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325657308101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338420122861862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346654146909714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355711668729782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359005272388458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370121240615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377943634986877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38164895772934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3902947306633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395235151052475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399763882160187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389471292495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401822417974472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411703288555145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402234137058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403469234704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409644782543182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408409655094147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405939429998398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406351149082184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400175601243973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397705405950546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403880923986435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403057515621185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394823461771011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417467176914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433111846446991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430641651153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441345900297165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454520404338837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442992717027664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488280087709427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50392484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534390866756439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518746137619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522039830684662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500631153583527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517922759056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46934175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485809862613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462754487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472635388374329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493220567703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491573750972748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48169282078743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467694938182831</t>
   </si>
   <si>
     <t xml:space="preserve">0.459460824728012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465223342180252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296617269516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481358289718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522463917732239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515164732933044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505560576915741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507097244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515548944473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503255546092987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489809930324554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480205804109573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519006371498108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511323094367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499413996934891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491730749607086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484431594610214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483663231134415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484815776348114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495188146829605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490194022655487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553197026252747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542056202888489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562801122665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586235165596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600065112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58239358663559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572021067142487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572789430618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552428722381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551276206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545129597187042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565874516963959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577015221118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596607625484467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584698557853699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608132541179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621962487697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620425879955292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629645764827728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614279210567474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60774838924408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58162522315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560880303382874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598528385162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598144292831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619657576084137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618120789527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601601779460907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58661937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595455169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587771832942963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584314405918121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577399432659149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567026913166046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57432609796524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543592929840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564721941947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.563185274600983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576246976852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583930134773254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580856919288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587003529071808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604675054550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629261612892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61850506067276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606980085372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603138387203217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612358391284943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611590087413788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593918442726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596991837024689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608516693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599296748638153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589308559894562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553965389728546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538598716259003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55703866481781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536293745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524000465869904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537830471992493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547818720340729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532452166080475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537062108516693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527073800563812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520927250385284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517853915691376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525537252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530147135257721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523232161998749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51939058303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524768888950348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549355447292328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501718997955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492498993873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477900803089142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476364076137543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488657385110855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471754193305969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472522526979446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468680799007416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487120777368546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481742411851883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480974078178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483279079198837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478669136762619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470217496156693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467912524938583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466375797986984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839190244675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461765855550766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487889051437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500182330608368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469449132680893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437179327011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444862574338913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431800991296768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444094300270081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424117743968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415666133165359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382627934217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379170477390289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382243752479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385701239109039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388774544000626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391847878694534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384164601564407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37648132443428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367261320352554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.364956378936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360346406698227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352278918027878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356504768133163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37148717045784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368029683828354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37225553393364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365340501070023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374944686889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366493046283722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374560534954071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374176323413849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37878629565239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362267225980759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353815585374832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354583919048309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353047281503677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370718866586685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354199767112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395689576864243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411056160926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407982856035233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384932935237885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390311241149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378017991781235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380707144737244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362651407718658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359578102827072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353431433439255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349589824676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344979822635651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343059033155441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354968100786209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36418804526329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357273101806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349973917007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339217364788055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323850780725479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361883044242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350742280483246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38954296708107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404141187667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396457821130753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412592768669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404909521341324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401836216449738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394152909517288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399531155824661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402604460716248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401067852973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397994548082352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375712960958481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36457222700119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345748126506805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336528182029724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335759848356247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337296515703201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329613238573074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32807657122612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331534057855606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319240778684616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326924055814743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312709987163544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34113821387291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322698265314102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326155751943588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324619114398956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325771570205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330381602048874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329997390508652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324234962463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313862472772598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301185041666031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30387419462204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296959221363068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302721709012985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082447052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308100014925003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310404986143112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306947559118271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314630806446075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305410861968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30848416686058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304642558097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320777416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356888920068741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358041435480118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356120586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360730558633804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358809739351273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351126462221146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355736434459686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342290669679642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37187135219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370334655046463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383780419826508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376097142696381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376865476369858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377249658107758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398762881755829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403372794389725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406446129083633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40951943397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39107957482338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381475448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407214462757111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387237936258316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394921213388443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411824464797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414897799491882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417202740907669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397226184606552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408751159906387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410287797451019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41412940621376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416434437036514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418739438056946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420276045799255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421812772750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430264353752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473290741443634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494803994894028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484047412872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267327547073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506328940391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479437470436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482510834932327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595772266388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465607523918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460997581481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453314214944839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4341059923172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789269447327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445630967617035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449472546577454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451009273529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460229158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454082578420639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457155883312225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451777547597885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456387460231781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46330252289772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470985800027847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467144131660461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457924276590347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447167575359344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432569414377213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437947690486908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433337688446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434874325990677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436410963535309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439484298229218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441020995378494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440252631902695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438715994358063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442557632923126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485584110021591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455619275569916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443325966596603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429496020078659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435642629861832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450240910053253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427191019058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375328809022903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386469602584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393384575843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365724712610245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372639685869217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351510643959045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342674821615219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317319959402084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26507356762886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259695291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23933456838131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242023706436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234724566340446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245865374803543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258926957845688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.251627773046494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266610234975815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269299358129501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258158624172211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.251243650913239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.252011984586716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242407888174057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245097011327744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254701107740402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262000232934952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254316985607147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261231958866119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262768626213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264689415693283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271988540887833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273909360170364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276982694864273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27275687456131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275446027517319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268915235996246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265841871500015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258542776107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265457719564438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263152748346329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292733460664749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327692419290543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302337527275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301953375339508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332302391529083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332686573266983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306179195642471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305026710033417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312325835227966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331918209791183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315399140119553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326539933681488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292349278926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289275974035263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291196793317795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286970943212509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285050123929977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273525238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26084777712822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261616080999374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270067691802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278519332408905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27314105629921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266994386911392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.255469471216202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25316447019577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256621956825256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256237804889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.249322831630707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236261263489723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238182038068771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253548622131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267762750387192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283513456583023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27775102853775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294654279947281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319624960422516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343827307224274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338449031114578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340754061937332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338833212852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338064879179001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336912333965302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333839058876038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330765724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328844904899597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33998566865921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347668945789337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359962224960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3518947660923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369182169437408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35765728354454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355352312326431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348053157329559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346516489982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34728479385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363419681787491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373792141675949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373023867607117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379554629325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42565444111824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417971104383469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381859600543976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383012115955353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377633780241013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378402143716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381091296672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380322962999344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348437279462814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400299519300461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38339626789093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379938781261444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388006269931793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428727775812149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368413835763931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344595670700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334223181009293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341906487941742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323466598987579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340369820594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331149876117706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348821431398392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322314113378525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285818487405777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337680697441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345363974571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341522336006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329229027032852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353653132915497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351594626903534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354064851999283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352829694747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347477585077286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345830768346786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341713726520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34253716468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348300993442535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359828680753708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353241413831711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35488823056221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350359499454498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345007389783859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339655190706253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342948853969574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34130197763443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333479672670364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320716857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319070041179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321540296077728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310835987329483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315776437520981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314129620790482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312894463539124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318246632814407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317834943532944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319481760263443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312071114778519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308365762233734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310012608766556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314541280269623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318658322095871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320305198431015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322775393724442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309600859880447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309189140796661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321128576993942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32195195555687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32689243555069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323187083005905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323598802089691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315364718437195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31330618262291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310424268245697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314952999353409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311247676610947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317011505365372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31742325425148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311659395694733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316188126802444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319893449544907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304660469293594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308777511119843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303013622760773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307542353868484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302601933479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307954072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306307286024094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301778525114059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303837031126022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30095511674881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301366806030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302190244197845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313717931509018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326480716466904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328539192676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340890347957611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356535077095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343360543251038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336361557245255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339243471622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335126459598541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358181834220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347065895795822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34418398141861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336773306131363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345419049263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349124372005463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338008403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335949897766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343772262334824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337596654891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340066909790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340478628873825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332244515419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329362660646439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325657337903976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338420122861862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346654146909714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35571163892746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359005242586136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370121270418167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377943605184555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381648927927017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3902947306633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395235151052475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399763911962509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389471292495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401822417974472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411703288555145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402234107255936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403469204902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40964475274086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408409684896469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405939429998398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406351149082184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400175601243973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397705405950546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403880923986435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403057515621185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394823461771011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417467176914215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433111906051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430641651153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44134595990181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454520463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442992717027664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488280147314072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50392484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534390866756439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518746197223663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522039830684662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500631153583527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517922759056091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46934175491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485809892416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462754458189011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472635418176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493220508098602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573721170425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48169282078743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467694878578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460943937302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461107701063156</t>
+    <t xml:space="preserve">0.461107730865479</t>
   </si>
   <si>
     <t xml:space="preserve">0.476752400398254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479222625494003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477575868368149</t>
+    <t xml:space="preserve">0.479222655296326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477575778961182</t>
   </si>
   <si>
     <t xml:space="preserve">0.51545250415802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504748165607452</t>
+    <t xml:space="preserve">0.504748225212097</t>
   </si>
   <si>
     <t xml:space="preserve">0.501454651355743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498984396457672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.494043976068497</t>
+    <t xml:space="preserve">0.498984456062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494043916463852</t>
   </si>
   <si>
     <t xml:space="preserve">0.505571663379669</t>
@@ -2804,82 +2804,82 @@
     <t xml:space="preserve">0.484986484050751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492397099733353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482516288757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478399217128754</t>
+    <t xml:space="preserve">0.492397129535675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482516258955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478399157524109</t>
   </si>
   <si>
     <t xml:space="preserve">0.473458766937256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470988541841507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47016516327858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465224713087082</t>
+    <t xml:space="preserve">0.470988571643829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470165133476257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46522468328476</t>
   </si>
   <si>
     <t xml:space="preserve">0.460284292697906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468518376350403</t>
+    <t xml:space="preserve">0.468518316745758</t>
   </si>
   <si>
     <t xml:space="preserve">0.466750353574753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473822355270386</t>
+    <t xml:space="preserve">0.473822295665741</t>
   </si>
   <si>
     <t xml:space="preserve">0.457910388708115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46144637465477</t>
+    <t xml:space="preserve">0.461446404457092</t>
   </si>
   <si>
     <t xml:space="preserve">0.464098334312439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454374402761459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44111442565918</t>
+    <t xml:space="preserve">0.454374372959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441114455461502</t>
   </si>
   <si>
     <t xml:space="preserve">0.420782536268234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435810476541519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438462466001511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427412509918213</t>
+    <t xml:space="preserve">0.435810446739197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438462436199188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427412480115891</t>
   </si>
   <si>
     <t xml:space="preserve">0.426528483629227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433158457279205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448186427354813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441998422145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434484452009201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44465047121048</t>
+    <t xml:space="preserve">0.433158487081528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448186457157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441998451948166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434484422206879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444650441408157</t>
   </si>
   <si>
     <t xml:space="preserve">0.449070423841476</t>
@@ -2894,31 +2894,31 @@
     <t xml:space="preserve">0.430948495864868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4313904941082</t>
+    <t xml:space="preserve">0.431390464305878</t>
   </si>
   <si>
     <t xml:space="preserve">0.434926480054855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42962247133255</t>
+    <t xml:space="preserve">0.429622501134872</t>
   </si>
   <si>
     <t xml:space="preserve">0.428738504648209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424318492412567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434042453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421666532754898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430506467819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427854478359222</t>
+    <t xml:space="preserve">0.424318462610245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434042483568192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421666473150253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430506438016891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427854508161545</t>
   </si>
   <si>
     <t xml:space="preserve">0.419456511735916</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">0.417246520519257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411942541599274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414152503013611</t>
+    <t xml:space="preserve">0.411942511796951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414152532815933</t>
   </si>
   <si>
     <t xml:space="preserve">0.418130487203598</t>
@@ -2939,34 +2939,34 @@
     <t xml:space="preserve">0.42255049943924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413710534572601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425202488899231</t>
+    <t xml:space="preserve">0.413710504770279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425202518701553</t>
   </si>
   <si>
     <t xml:space="preserve">0.423876494169235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414594531059265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422992527484894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421224504709244</t>
+    <t xml:space="preserve">0.414594560861588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422992497682571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421224534511566</t>
   </si>
   <si>
     <t xml:space="preserve">0.413268536329269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415920555591583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408406555652618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412384539842606</t>
+    <t xml:space="preserve">0.415920495986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408406585454941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412384569644928</t>
   </si>
   <si>
     <t xml:space="preserve">0.41105854511261</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">0.424760490655899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422108471393585</t>
+    <t xml:space="preserve">0.422108501195908</t>
   </si>
   <si>
     <t xml:space="preserve">0.415478527545929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402218580245972</t>
+    <t xml:space="preserve">0.402218610048294</t>
   </si>
   <si>
     <t xml:space="preserve">0.394262611865997</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">0.400008589029312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401334553956985</t>
+    <t xml:space="preserve">0.401334583759308</t>
   </si>
   <si>
     <t xml:space="preserve">0.39249461889267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396030634641647</t>
+    <t xml:space="preserve">0.396030604839325</t>
   </si>
   <si>
     <t xml:space="preserve">0.405754566192627</t>
@@ -3032,10 +3032,10 @@
     <t xml:space="preserve">0.389842629432678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388958662748337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395146608352661</t>
+    <t xml:space="preserve">0.388958603143692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395146578550339</t>
   </si>
   <si>
     <t xml:space="preserve">0.386748641729355</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">0.393378585577011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403102606534958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396914571523666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39779856801033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40177658200264</t>
+    <t xml:space="preserve">0.403102546930313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396914601325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397798597812653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401776552200317</t>
   </si>
   <si>
     <t xml:space="preserve">0.406638562679291</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">0.402660578489304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41989853978157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436694473028183</t>
+    <t xml:space="preserve">0.419898509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436694413423538</t>
   </si>
   <si>
     <t xml:space="preserve">0.443766415119171</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">0.456523567438126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465635776519775</t>
+    <t xml:space="preserve">0.465635806322098</t>
   </si>
   <si>
     <t xml:space="preserve">0.464724570512772</t>
@@ -3098,10 +3098,10 @@
     <t xml:space="preserve">0.468369513750076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480215430259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482949048280716</t>
+    <t xml:space="preserve">0.480215460062027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482949018478394</t>
   </si>
   <si>
     <t xml:space="preserve">0.481126666069031</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">0.486593961715698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501173555850983</t>
+    <t xml:space="preserve">0.501173615455627</t>
   </si>
   <si>
     <t xml:space="preserve">0.523042976856232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529421448707581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525776624679565</t>
+    <t xml:space="preserve">0.529421508312225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52577668428421</t>
   </si>
   <si>
     <t xml:space="preserve">0.523954212665558</t>
@@ -3143,25 +3143,25 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753149986267</t>
+    <t xml:space="preserve">0.515753209590912</t>
   </si>
   <si>
     <t xml:space="preserve">0.507552146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511197030544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514841973781586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519398093223572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513930678367615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524865448474884</t>
+    <t xml:space="preserve">0.511197090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514841914176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519398033618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51393073797226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524865388870239</t>
   </si>
   <si>
     <t xml:space="preserve">0.509374618530273</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546734809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537622511386871</t>
+    <t xml:space="preserve">0.541267514228821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546734869480133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537622570991516</t>
   </si>
   <si>
     <t xml:space="preserve">0.549468457698822</t>
@@ -3194,13 +3194,13 @@
     <t xml:space="preserve">0.564959287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569515407085419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562225580215454</t>
+    <t xml:space="preserve">0.569515466690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565870463848114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562225639820099</t>
   </si>
   <si>
     <t xml:space="preserve">0.551290929317474</t>
@@ -3209,16 +3209,16 @@
     <t xml:space="preserve">0.548557281494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550379693508148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547646045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555847108364105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553113341331482</t>
+    <t xml:space="preserve">0.550379633903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547646105289459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55584704875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553113400936127</t>
   </si>
   <si>
     <t xml:space="preserve">0.564048111438751</t>
@@ -3233,25 +3233,25 @@
     <t xml:space="preserve">0.558580696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556758224964142</t>
+    <t xml:space="preserve">0.556758344173431</t>
   </si>
   <si>
     <t xml:space="preserve">0.542178690433502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557669520378113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534888923168182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528510332107544</t>
+    <t xml:space="preserve">0.557669460773468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534888863563538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528510272502899</t>
   </si>
   <si>
     <t xml:space="preserve">0.535800099372864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530332803726196</t>
+    <t xml:space="preserve">0.530332744121552</t>
   </si>
   <si>
     <t xml:space="preserve">0.527599096298218</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617466211319</t>
+    <t xml:space="preserve">0.496617436408997</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">0.505729734897614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494794964790344</t>
+    <t xml:space="preserve">0.494794994592667</t>
   </si>
   <si>
     <t xml:space="preserve">0.499351114034653</t>
@@ -3284,28 +3284,28 @@
     <t xml:space="preserve">0.492061376571655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488416492938995</t>
+    <t xml:space="preserve">0.488416433334351</t>
   </si>
   <si>
     <t xml:space="preserve">0.483860343694687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487505227327347</t>
+    <t xml:space="preserve">0.487505257129669</t>
   </si>
   <si>
     <t xml:space="preserve">0.495706290006638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49388375878334</t>
+    <t xml:space="preserve">0.493883818387985</t>
   </si>
   <si>
     <t xml:space="preserve">0.491150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517575621604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489643424749374</t>
+    <t xml:space="preserve">0.517575681209564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489643454551697</t>
   </si>
   <si>
     <t xml:space="preserve">0.48199275135994</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">0.475776553153992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476732909679413</t>
+    <t xml:space="preserve">0.47673287987709</t>
   </si>
   <si>
     <t xml:space="preserve">0.480080038309097</t>
@@ -3329,31 +3329,31 @@
     <t xml:space="preserve">0.46477872133255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473385721445084</t>
+    <t xml:space="preserve">0.473385751247406</t>
   </si>
   <si>
     <t xml:space="preserve">0.469560384750366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470994889736176</t>
+    <t xml:space="preserve">0.470994919538498</t>
   </si>
   <si>
     <t xml:space="preserve">0.459040701389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453780889511108</t>
+    <t xml:space="preserve">0.453780859708786</t>
   </si>
   <si>
     <t xml:space="preserve">0.451390027999878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447564691305161</t>
+    <t xml:space="preserve">0.447564661502838</t>
   </si>
   <si>
     <t xml:space="preserve">0.45091187953949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441826671361923</t>
+    <t xml:space="preserve">0.441826701164246</t>
   </si>
   <si>
     <t xml:space="preserve">0.438479512929916</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">0.432741492986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436088681221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438001334667206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441348522901535</t>
+    <t xml:space="preserve">0.436088651418686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438001364469528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441348493099213</t>
   </si>
   <si>
     <t xml:space="preserve">0.446608364582062</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">0.436566829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438957661390305</t>
+    <t xml:space="preserve">0.438957691192627</t>
   </si>
   <si>
     <t xml:space="preserve">0.444695681333542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439435869455338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433697819709778</t>
+    <t xml:space="preserve">0.439435839653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4336978495121</t>
   </si>
   <si>
     <t xml:space="preserve">0.434654176235199</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">0.46669140458107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454737186431885</t>
+    <t xml:space="preserve">0.454737216234207</t>
   </si>
   <si>
     <t xml:space="preserve">0.455693542957306</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">0.561368525028229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538416564464569</t>
+    <t xml:space="preserve">0.538416504859924</t>
   </si>
   <si>
     <t xml:space="preserve">0.544154524803162</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">0.540329158306122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525984108448029</t>
+    <t xml:space="preserve">0.525984168052673</t>
   </si>
   <si>
     <t xml:space="preserve">0.517377138137817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525027871131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521202504634857</t>
+    <t xml:space="preserve">0.525027811527252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521202445030212</t>
   </si>
   <si>
     <t xml:space="preserve">0.519289791584015</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">0.531722128391266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518333435058594</t>
+    <t xml:space="preserve">0.518333494663239</t>
   </si>
   <si>
     <t xml:space="preserve">0.514508128166199</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">0.527896821498871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52694046497345</t>
+    <t xml:space="preserve">0.526940524578094</t>
   </si>
   <si>
     <t xml:space="preserve">0.535547494888306</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">0.553717851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568062841892242</t>
+    <t xml:space="preserve">0.568062901496887</t>
   </si>
   <si>
     <t xml:space="preserve">0.55849951505661</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">0.555630505084991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554674208164215</t>
+    <t xml:space="preserve">0.55467414855957</t>
   </si>
   <si>
     <t xml:space="preserve">0.557543218135834</t>
@@ -3491,16 +3491,16 @@
     <t xml:space="preserve">0.54702353477478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537460148334503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551805198192596</t>
+    <t xml:space="preserve">0.537460088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551805257797241</t>
   </si>
   <si>
     <t xml:space="preserve">0.524071455001831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533634901046753</t>
+    <t xml:space="preserve">0.533634841442108</t>
   </si>
   <si>
     <t xml:space="preserve">0.536503851413727</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">0.522158801555634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529809534549713</t>
+    <t xml:space="preserve">0.529809474945068</t>
   </si>
   <si>
     <t xml:space="preserve">0.532678484916687</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">0.499206781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49633777141571</t>
+    <t xml:space="preserve">0.496337741613388</t>
   </si>
   <si>
     <t xml:space="preserve">0.506857395172119</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">0.487730741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483905404806137</t>
+    <t xml:space="preserve">0.483905375003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.461909741163254</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">0.478167414665222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46860408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471473067998886</t>
+    <t xml:space="preserve">0.468604058027267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471473038196564</t>
   </si>
   <si>
     <t xml:space="preserve">0.48260822892189</t>
@@ -3987,6 +3987,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.52700001001358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531000018119812</t>
   </si>
 </sst>
 </file>
@@ -69533,7 +69536,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6912384259</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>231340</v>
@@ -69554,6 +69557,32 @@
         <v>1265</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6911574074</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>770182</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>0.541000008583069</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>0.532000005245209</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>0.538999974727631</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>0.531000018119812</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33373612165451</t>
+    <t xml:space="preserve">0.333736211061478</t>
   </si>
   <si>
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327446281909943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321156293153763</t>
+    <t xml:space="preserve">0.32744625210762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321156322956085</t>
   </si>
   <si>
     <t xml:space="preserve">0.317678332328796</t>
@@ -62,40 +62,40 @@
     <t xml:space="preserve">0.289336711168289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294368624687195</t>
+    <t xml:space="preserve">0.294368654489517</t>
   </si>
   <si>
     <t xml:space="preserve">0.285636723041534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796886205673</t>
+    <t xml:space="preserve">0.273796916007996</t>
   </si>
   <si>
     <t xml:space="preserve">0.258997023105621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258257061243057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243605181574821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246417194604874</t>
+    <t xml:space="preserve">0.258257031440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243605211377144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246417179703712</t>
   </si>
   <si>
     <t xml:space="preserve">0.262696981430054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256407082080841</t>
+    <t xml:space="preserve">0.256407111883163</t>
   </si>
   <si>
     <t xml:space="preserve">0.259810984134674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261512964963913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253817111253738</t>
+    <t xml:space="preserve">0.261513024568558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253817081451416</t>
   </si>
   <si>
     <t xml:space="preserve">0.253077119588852</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">0.286894708871841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284600764513016</t>
+    <t xml:space="preserve">0.284600734710693</t>
   </si>
   <si>
     <t xml:space="preserve">0.277496814727783</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">0.28711673617363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290742665529251</t>
+    <t xml:space="preserve">0.290742695331573</t>
   </si>
   <si>
     <t xml:space="preserve">0.263806968927383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256777048110962</t>
+    <t xml:space="preserve">0.25677701830864</t>
   </si>
   <si>
     <t xml:space="preserve">0.250117152929306</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">0.297994583845139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310796409845352</t>
+    <t xml:space="preserve">0.310796469449997</t>
   </si>
   <si>
     <t xml:space="preserve">0.303544491529465</t>
@@ -140,43 +140,43 @@
     <t xml:space="preserve">0.304358512163162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318122327327728</t>
+    <t xml:space="preserve">0.318122357130051</t>
   </si>
   <si>
     <t xml:space="preserve">0.309686452150345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30162051320076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310352444648743</t>
+    <t xml:space="preserve">0.301620543003082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31035241484642</t>
   </si>
   <si>
     <t xml:space="preserve">0.323376297950745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320046335458755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316716402769089</t>
+    <t xml:space="preserve">0.320046305656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316716343164444</t>
   </si>
   <si>
     <t xml:space="preserve">0.315236389636993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315606415271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332996159791946</t>
+    <t xml:space="preserve">0.315606385469437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332996189594269</t>
   </si>
   <si>
     <t xml:space="preserve">0.332256197929382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328852266073227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330480247735977</t>
+    <t xml:space="preserve">0.328852206468582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330480188131332</t>
   </si>
   <si>
     <t xml:space="preserve">0.311240434646606</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">0.312054425477982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299696564674377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296884596347809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299400568008423</t>
+    <t xml:space="preserve">0.2996965944767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296884626150131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2994005382061</t>
   </si>
   <si>
     <t xml:space="preserve">0.29747661948204</t>
@@ -200,13 +200,13 @@
     <t xml:space="preserve">0.295996606349945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293702632188797</t>
+    <t xml:space="preserve">0.293702661991119</t>
   </si>
   <si>
     <t xml:space="preserve">0.298216581344604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286376714706421</t>
+    <t xml:space="preserve">0.286376744508743</t>
   </si>
   <si>
     <t xml:space="preserve">0.276756823062897</t>
@@ -215,19 +215,19 @@
     <t xml:space="preserve">0.274536848068237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272316843271255</t>
+    <t xml:space="preserve">0.272316873073578</t>
   </si>
   <si>
     <t xml:space="preserve">0.268542915582657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270466923713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265065014362335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268172919750214</t>
+    <t xml:space="preserve">0.270466893911362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265064984560013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268172889947891</t>
   </si>
   <si>
     <t xml:space="preserve">0.268616944551468</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">0.269208908081055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275276869535446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28489676117897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290002644062042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308206468820572</t>
+    <t xml:space="preserve">0.275276839733124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284896731376648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290002673864365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308206498622894</t>
   </si>
   <si>
     <t xml:space="preserve">0.309168487787247</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">0.316938370466232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308946460485458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31420037150383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321378320455551</t>
+    <t xml:space="preserve">0.308946430683136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314200401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321378350257874</t>
   </si>
   <si>
     <t xml:space="preserve">0.319380342960358</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">0.310722440481186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313682436943054</t>
+    <t xml:space="preserve">0.313682407140732</t>
   </si>
   <si>
     <t xml:space="preserve">0.313312441110611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307096481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307614475488663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304950475692749</t>
+    <t xml:space="preserve">0.30709645152092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307614505290985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304950535297394</t>
   </si>
   <si>
     <t xml:space="preserve">0.305616497993469</t>
@@ -293,22 +293,22 @@
     <t xml:space="preserve">0.299548596143723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305320531129837</t>
+    <t xml:space="preserve">0.305320501327515</t>
   </si>
   <si>
     <t xml:space="preserve">0.295626610517502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300954550504684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314400345087051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318779796361923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318856626749039</t>
+    <t xml:space="preserve">0.300954520702362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314400285482407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318779826164246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318856596946716</t>
   </si>
   <si>
     <t xml:space="preserve">0.318395644426346</t>
@@ -320,46 +320,46 @@
     <t xml:space="preserve">0.318088293075562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307331651449203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321776270866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320393264293671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311557501554489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305795013904572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301569253206253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295806765556335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299648374319077</t>
+    <t xml:space="preserve">0.307331681251526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321776241064072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320393294095993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311557471752167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305795043706894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301569193601608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295806735754013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299648404121399</t>
   </si>
   <si>
     <t xml:space="preserve">0.29657506942749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303490042686462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314246654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318011432886124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318702906370163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321161597967148</t>
+    <t xml:space="preserve">0.303490072488785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31424668431282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318011462688446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318702965974808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32116162776947</t>
   </si>
   <si>
     <t xml:space="preserve">0.310020834207535</t>
@@ -380,58 +380,58 @@
     <t xml:space="preserve">0.305564552545547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304949849843979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306870669126511</t>
+    <t xml:space="preserve">0.304949879646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306870698928833</t>
   </si>
   <si>
     <t xml:space="preserve">0.297727555036545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301799714565277</t>
+    <t xml:space="preserve">0.301799684762955</t>
   </si>
   <si>
     <t xml:space="preserve">0.304027885198593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300032556056976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313478291034698</t>
+    <t xml:space="preserve">0.300032585859299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313478320837021</t>
   </si>
   <si>
     <t xml:space="preserve">0.312556326389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307869493961334</t>
+    <t xml:space="preserve">0.307869523763657</t>
   </si>
   <si>
     <t xml:space="preserve">0.311480641365051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298265397548676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299110561609268</t>
+    <t xml:space="preserve">0.298265427350998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299110531806946</t>
   </si>
   <si>
     <t xml:space="preserve">0.305257171392441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295576214790344</t>
+    <t xml:space="preserve">0.295576244592667</t>
   </si>
   <si>
     <t xml:space="preserve">0.295960396528244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297650724649429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297881245613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29373225569725</t>
+    <t xml:space="preserve">0.297650754451752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297881215810776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293732225894928</t>
   </si>
   <si>
     <t xml:space="preserve">0.298803240060806</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">0.309559851884842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303105890750885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303566843271255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308253675699234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304873049259186</t>
+    <t xml:space="preserve">0.303105860948563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303566873073578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308253705501556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304873019456863</t>
   </si>
   <si>
     <t xml:space="preserve">0.306563347578049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300186276435852</t>
+    <t xml:space="preserve">0.300186216831207</t>
   </si>
   <si>
     <t xml:space="preserve">0.298649549484253</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">0.301415532827377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3006471991539</t>
+    <t xml:space="preserve">0.300647228956223</t>
   </si>
   <si>
     <t xml:space="preserve">0.282975643873215</t>
@@ -494,22 +494,22 @@
     <t xml:space="preserve">0.293501764535904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292656600475311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29250293970108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289583265781403</t>
+    <t xml:space="preserve">0.292656630277634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292502909898758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289583295583725</t>
   </si>
   <si>
     <t xml:space="preserve">0.288123458623886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284281820058823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287892997264862</t>
+    <t xml:space="preserve">0.284281849861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28789296746254</t>
   </si>
   <si>
     <t xml:space="preserve">0.290044277906418</t>
@@ -518,37 +518,37 @@
     <t xml:space="preserve">0.292887061834335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293117612600327</t>
+    <t xml:space="preserve">0.293117582798004</t>
   </si>
   <si>
     <t xml:space="preserve">0.291888296604156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289813756942749</t>
+    <t xml:space="preserve">0.289813786745071</t>
   </si>
   <si>
     <t xml:space="preserve">0.286586791276932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294270068407059</t>
+    <t xml:space="preserve">0.294270098209381</t>
   </si>
   <si>
     <t xml:space="preserve">0.291811406612396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292579770088196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29572993516922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298419058322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294731110334396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287355095148087</t>
+    <t xml:space="preserve">0.292579799890518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295729905366898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298419028520584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294731050729752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287355124950409</t>
   </si>
   <si>
     <t xml:space="preserve">0.293809086084366</t>
@@ -557,37 +557,37 @@
     <t xml:space="preserve">0.292041927576065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286740481853485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284666001796722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278903484344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275599658489227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270221412181854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272449523210526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276675343513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27398619055748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275676488876343</t>
+    <t xml:space="preserve">0.286740452051163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2846659719944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278903514146805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275599718093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270221382379532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272449553012848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276675373315811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273986220359802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275676548480988</t>
   </si>
   <si>
     <t xml:space="preserve">0.275522857904434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276598542928696</t>
+    <t xml:space="preserve">0.276598483324051</t>
   </si>
   <si>
     <t xml:space="preserve">0.270989716053009</t>
@@ -596,16 +596,16 @@
     <t xml:space="preserve">0.27114337682724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274293512105942</t>
+    <t xml:space="preserve">0.274293541908264</t>
   </si>
   <si>
     <t xml:space="preserve">0.270451873540878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268146932125092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267378568649292</t>
+    <t xml:space="preserve">0.268146872520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26737853884697</t>
   </si>
   <si>
     <t xml:space="preserve">0.264612585306168</t>
@@ -614,46 +614,46 @@
     <t xml:space="preserve">0.265765070915222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262384474277496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267532229423523</t>
+    <t xml:space="preserve">0.262384444475174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267532199621201</t>
   </si>
   <si>
     <t xml:space="preserve">0.265304088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271911710500717</t>
+    <t xml:space="preserve">0.27191174030304</t>
   </si>
   <si>
     <t xml:space="preserve">0.272526383399963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283282995223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279902368783951</t>
+    <t xml:space="preserve">0.283283025026321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279902338981628</t>
   </si>
   <si>
     <t xml:space="preserve">0.277059525251389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27844250202179</t>
+    <t xml:space="preserve">0.278442472219467</t>
   </si>
   <si>
     <t xml:space="preserve">0.280516982078552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278749823570251</t>
+    <t xml:space="preserve">0.278749853372574</t>
   </si>
   <si>
     <t xml:space="preserve">0.27898034453392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278212040662766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284051358699799</t>
+    <t xml:space="preserve">0.278211981058121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284051299095154</t>
   </si>
   <si>
     <t xml:space="preserve">0.290812611579895</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">0.295422583818436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288507580757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284589141607285</t>
+    <t xml:space="preserve">0.288507610559464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284589171409607</t>
   </si>
   <si>
     <t xml:space="preserve">0.291043102741241</t>
@@ -686,49 +686,49 @@
     <t xml:space="preserve">0.294884741306305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289890646934509</t>
+    <t xml:space="preserve">0.289890617132187</t>
   </si>
   <si>
     <t xml:space="preserve">0.286125808954239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284358650445938</t>
+    <t xml:space="preserve">0.284358620643616</t>
   </si>
   <si>
     <t xml:space="preserve">0.282745152711868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277290016412735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281976848840714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276214331388474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27360200881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269760370254517</t>
+    <t xml:space="preserve">0.277290046215057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281976819038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276214361190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273602038621902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269760340452194</t>
   </si>
   <si>
     <t xml:space="preserve">0.275061845779419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271834850311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273371577262878</t>
+    <t xml:space="preserve">0.271834880113602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273371547460556</t>
   </si>
   <si>
     <t xml:space="preserve">0.275215536355972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276905834674835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27483132481575</t>
+    <t xml:space="preserve">0.276905864477158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274831384420395</t>
   </si>
   <si>
     <t xml:space="preserve">0.282668352127075</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">0.279595017433167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27736684679985</t>
+    <t xml:space="preserve">0.277366816997528</t>
   </si>
   <si>
     <t xml:space="preserve">0.278135150671005</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">0.279364496469498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285587936639786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279671847820282</t>
+    <t xml:space="preserve">0.285587966442108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27967181801796</t>
   </si>
   <si>
     <t xml:space="preserve">0.28666365146637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284435480833054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281899988651276</t>
+    <t xml:space="preserve">0.284435451030731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281900018453598</t>
   </si>
   <si>
     <t xml:space="preserve">0.283897668123245</t>
@@ -779,34 +779,34 @@
     <t xml:space="preserve">0.285280615091324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2854343354702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295038402080536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304258346557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321929901838303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325617909431458</t>
+    <t xml:space="preserve">0.285434275865555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295038461685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30425837635994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321929961442947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32561793923378</t>
   </si>
   <si>
     <t xml:space="preserve">0.33184140920639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325387448072433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316935777664185</t>
+    <t xml:space="preserve">0.325387418270111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316935807466507</t>
   </si>
   <si>
     <t xml:space="preserve">0.309790343046188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30925253033638</t>
+    <t xml:space="preserve">0.309252500534058</t>
   </si>
   <si>
     <t xml:space="preserve">0.311096489429474</t>
@@ -815,19 +815,19 @@
     <t xml:space="preserve">0.313094139099121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31301736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288891762495041</t>
+    <t xml:space="preserve">0.313017338514328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288891792297363</t>
   </si>
   <si>
     <t xml:space="preserve">0.293040752410889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295192122459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296805590391159</t>
+    <t xml:space="preserve">0.295192033052444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296805530786514</t>
   </si>
   <si>
     <t xml:space="preserve">0.297266572713852</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">0.313555151224136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300800859928131</t>
+    <t xml:space="preserve">0.300800889730453</t>
   </si>
   <si>
     <t xml:space="preserve">0.308868378400803</t>
@@ -851,61 +851,61 @@
     <t xml:space="preserve">0.299725204706192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32185310125351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32730820775032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318472474813461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312095314264297</t>
+    <t xml:space="preserve">0.321853131055832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327308237552643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318472445011139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312095284461975</t>
   </si>
   <si>
     <t xml:space="preserve">0.314016163349152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315014958381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312248945236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313939303159714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309636652469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307408511638641</t>
+    <t xml:space="preserve">0.315014988183975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312248975038528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313939332962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309636682271957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307408541440964</t>
   </si>
   <si>
     <t xml:space="preserve">0.308945178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313632011413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308023184537888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307715833187103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309021979570389</t>
+    <t xml:space="preserve">0.313631981611252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30802321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307715862989426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309022009372711</t>
   </si>
   <si>
     <t xml:space="preserve">0.309944003820419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3177809715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316551625728607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316474825143814</t>
+    <t xml:space="preserve">0.317780941724777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31655165553093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316474795341492</t>
   </si>
   <si>
     <t xml:space="preserve">0.324388593435287</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">0.325003296136856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318318784236908</t>
+    <t xml:space="preserve">0.318318754434586</t>
   </si>
   <si>
     <t xml:space="preserve">0.317704141139984</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">0.320470124483109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322621464729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323697119951248</t>
+    <t xml:space="preserve">0.322621434926987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323697090148926</t>
   </si>
   <si>
     <t xml:space="preserve">0.333454877138138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327385067939758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331764578819275</t>
+    <t xml:space="preserve">0.327385097742081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331764549016953</t>
   </si>
   <si>
     <t xml:space="preserve">0.339524686336517</t>
@@ -950,28 +950,28 @@
     <t xml:space="preserve">0.340446680784225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333378046751022</t>
+    <t xml:space="preserve">0.333378076553345</t>
   </si>
   <si>
     <t xml:space="preserve">0.334991544485092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336144059896469</t>
+    <t xml:space="preserve">0.336144030094147</t>
   </si>
   <si>
     <t xml:space="preserve">0.337757527828217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338910013437271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338141709566116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339678317308426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350358098745346</t>
+    <t xml:space="preserve">0.338910043239594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338141679763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339678376913071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350358128547668</t>
   </si>
   <si>
     <t xml:space="preserve">0.346593290567398</t>
@@ -980,31 +980,31 @@
     <t xml:space="preserve">0.344211518764496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340677171945572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334607392549515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338218569755554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346900641918182</t>
+    <t xml:space="preserve">0.34067714214325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334607362747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338218539953232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34690061211586</t>
   </si>
   <si>
     <t xml:space="preserve">0.346132308244705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33960148692131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340907692909241</t>
+    <t xml:space="preserve">0.339601516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340907663106918</t>
   </si>
   <si>
     <t xml:space="preserve">0.3526631295681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36995056271553</t>
+    <t xml:space="preserve">0.369950503110886</t>
   </si>
   <si>
     <t xml:space="preserve">0.36541736125946</t>
@@ -1013,31 +1013,31 @@
     <t xml:space="preserve">0.363035559654236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374099463224411</t>
+    <t xml:space="preserve">0.374099493026733</t>
   </si>
   <si>
     <t xml:space="preserve">0.371103018522263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369566380977631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368798017501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366108894348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363112419843674</t>
+    <t xml:space="preserve">0.369566351175308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368797987699509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366108864545822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363112360239029</t>
   </si>
   <si>
     <t xml:space="preserve">0.368644326925278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366877198219299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366262525320053</t>
+    <t xml:space="preserve">0.366877168416977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366262555122375</t>
   </si>
   <si>
     <t xml:space="preserve">0.361114740371704</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">0.359885424375534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359193921089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368567526340485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372024983167648</t>
+    <t xml:space="preserve">0.35919389128685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368567556142807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372025012969971</t>
   </si>
   <si>
     <t xml:space="preserve">0.37555930018425</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">0.380246102809906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392616212368011</t>
+    <t xml:space="preserve">0.392616152763367</t>
   </si>
   <si>
     <t xml:space="preserve">0.405677825212479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421044409275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419507741928101</t>
+    <t xml:space="preserve">0.421044439077377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419507712125778</t>
   </si>
   <si>
     <t xml:space="preserve">0.396842062473297</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">0.413361102342606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422581106424332</t>
+    <t xml:space="preserve">0.422581046819687</t>
   </si>
   <si>
     <t xml:space="preserve">0.417586922645569</t>
@@ -1088,58 +1088,58 @@
     <t xml:space="preserve">0.426422715187073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423349350690842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427959412336349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436795175075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432953476905823</t>
+    <t xml:space="preserve">0.423349380493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427959322929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436795145273209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432953506708145</t>
   </si>
   <si>
     <t xml:space="preserve">0.452930063009262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459460854530334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46522331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296617269516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481358230113983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522463858127594</t>
+    <t xml:space="preserve">0.459460824728012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465223342180252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296647071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481358259916306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522463917732239</t>
   </si>
   <si>
     <t xml:space="preserve">0.5151646733284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505560576915741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507097244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515548884868622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503255665302277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489809900522232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480205774307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519006311893463</t>
+    <t xml:space="preserve">0.505560636520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50709730386734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515548944473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503255605697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48980987071991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480205744504929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519006371498108</t>
   </si>
   <si>
     <t xml:space="preserve">0.511323094367981</t>
@@ -1148,25 +1148,25 @@
     <t xml:space="preserve">0.499413967132568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491730690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484431594610214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483663231134415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484815746545792</t>
+    <t xml:space="preserve">0.491730660200119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484431564807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483663201332092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484815716743469</t>
   </si>
   <si>
     <t xml:space="preserve">0.495188176631927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490194082260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553197085857391</t>
+    <t xml:space="preserve">0.490193963050842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553196966648102</t>
   </si>
   <si>
     <t xml:space="preserve">0.542056202888489</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">0.56280118227005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586235225200653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600065112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582393527030945</t>
+    <t xml:space="preserve">0.586235165596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600065171718597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58239358663559</t>
   </si>
   <si>
     <t xml:space="preserve">0.572021126747131</t>
@@ -1190,25 +1190,25 @@
     <t xml:space="preserve">0.572789430618286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552428662776947</t>
+    <t xml:space="preserve">0.552428722381592</t>
   </si>
   <si>
     <t xml:space="preserve">0.55127614736557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545129656791687</t>
+    <t xml:space="preserve">0.545129537582397</t>
   </si>
   <si>
     <t xml:space="preserve">0.565874516963959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577015161514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596607565879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584698498249054</t>
+    <t xml:space="preserve">0.577015221118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596607625484467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584698557853699</t>
   </si>
   <si>
     <t xml:space="preserve">0.608132481575012</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">0.621962487697601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620425879955292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629645824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614279210567474</t>
+    <t xml:space="preserve">0.620425820350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629645764827728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61427915096283</t>
   </si>
   <si>
     <t xml:space="preserve">0.60774838924408</t>
@@ -1238,19 +1238,19 @@
     <t xml:space="preserve">0.598528444766998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598144352436066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619657516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618120789527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601601719856262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58661937713623</t>
+    <t xml:space="preserve">0.598144233226776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619657456874847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618120849132538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601601779460907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586619317531586</t>
   </si>
   <si>
     <t xml:space="preserve">0.59545511007309</t>
@@ -1262,22 +1262,22 @@
     <t xml:space="preserve">0.584314405918121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577399492263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567026913166046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574326038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543592870235443</t>
+    <t xml:space="preserve">0.577399432659149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567026972770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57432609796524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543592929840088</t>
   </si>
   <si>
     <t xml:space="preserve">0.564722001552582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.563185334205627</t>
+    <t xml:space="preserve">0.563185274600983</t>
   </si>
   <si>
     <t xml:space="preserve">0.576246917247772</t>
@@ -1298,94 +1298,94 @@
     <t xml:space="preserve">0.629261672496796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61850506067276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606980085372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603138506412506</t>
+    <t xml:space="preserve">0.618505001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60698014497757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603138387203217</t>
   </si>
   <si>
     <t xml:space="preserve">0.612358391284943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611590027809143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593918442726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596991837024689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608516693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599296748638153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589308500289917</t>
+    <t xml:space="preserve">0.611590087413788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59391850233078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596991777420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608516752719879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599296808242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589308559894562</t>
   </si>
   <si>
     <t xml:space="preserve">0.553965389728546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538598775863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5570387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536293864250183</t>
+    <t xml:space="preserve">0.538598835468292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557038724422455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536293745040894</t>
   </si>
   <si>
     <t xml:space="preserve">0.524000525474548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537830471992493</t>
+    <t xml:space="preserve">0.537830412387848</t>
   </si>
   <si>
     <t xml:space="preserve">0.547818720340729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532452166080475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537062168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527073860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52092719078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517853856086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525537133216858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530147194862366</t>
+    <t xml:space="preserve">0.53245222568512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537062108516693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527073800563812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520927131175995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517853915691376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525537192821503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530147075653076</t>
   </si>
   <si>
     <t xml:space="preserve">0.523232161998749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519390642642975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524768948554993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549355447292328</t>
+    <t xml:space="preserve">0.51939058303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524768888950348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549355387687683</t>
   </si>
   <si>
     <t xml:space="preserve">0.501718997955322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492499053478241</t>
+    <t xml:space="preserve">0.492499083280563</t>
   </si>
   <si>
     <t xml:space="preserve">0.477900743484497</t>
@@ -1394,34 +1394,34 @@
     <t xml:space="preserve">0.476364135742188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48865732550621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471754163503647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472522467374802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468680769205093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487120777368546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481742382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480974078178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483279079198837</t>
+    <t xml:space="preserve">0.488657355308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471754133701324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472522526979446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468680799007416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487120717763901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481742411851883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480974048376083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48327910900116</t>
   </si>
   <si>
     <t xml:space="preserve">0.478669106960297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470217496156693</t>
+    <t xml:space="preserve">0.47021746635437</t>
   </si>
   <si>
     <t xml:space="preserve">0.467912524938583</t>
@@ -1430,43 +1430,43 @@
     <t xml:space="preserve">0.466375797986984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464839190244675</t>
+    <t xml:space="preserve">0.464839160442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.461765855550766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487889021635056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500182390213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469449192285538</t>
+    <t xml:space="preserve">0.487889051437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500182271003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469449132680893</t>
   </si>
   <si>
     <t xml:space="preserve">0.437179297208786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444862604141235</t>
+    <t xml:space="preserve">0.444862574338913</t>
   </si>
   <si>
     <t xml:space="preserve">0.431800991296768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444094270467758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424117684364319</t>
+    <t xml:space="preserve">0.444094300270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424117743968964</t>
   </si>
   <si>
     <t xml:space="preserve">0.415666103363037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382627934217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379170477390289</t>
+    <t xml:space="preserve">0.382627964019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379170447587967</t>
   </si>
   <si>
     <t xml:space="preserve">0.382243782281876</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">0.385701268911362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388774573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391847878694534</t>
+    <t xml:space="preserve">0.38877460360527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391847848892212</t>
   </si>
   <si>
     <t xml:space="preserve">0.384164601564407</t>
@@ -1514,73 +1514,73 @@
     <t xml:space="preserve">0.365340501070023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374944657087326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3664930164814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374560534954071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374176293611526</t>
+    <t xml:space="preserve">0.374944686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366493046283722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374560475349426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374176323413849</t>
   </si>
   <si>
     <t xml:space="preserve">0.37878629565239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362267255783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353815644979477</t>
+    <t xml:space="preserve">0.362267225980759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35381555557251</t>
   </si>
   <si>
     <t xml:space="preserve">0.354583919048309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353047281503677</t>
+    <t xml:space="preserve">0.353047311306</t>
   </si>
   <si>
     <t xml:space="preserve">0.370718836784363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35419973731041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395689517259598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411056190729141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40798282623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384932905435562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39031121134758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378018021583557</t>
+    <t xml:space="preserve">0.354199767112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395689576864243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411056160926819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407982856035233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384932935237885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390311241149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378017991781235</t>
   </si>
   <si>
     <t xml:space="preserve">0.380707114934921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362651377916336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359578043222427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353431463241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349589794874191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344979852437973</t>
+    <t xml:space="preserve">0.362651407718658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35957807302475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353431433439255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349589824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344979822635651</t>
   </si>
   <si>
     <t xml:space="preserve">0.343059003353119</t>
@@ -1592,49 +1592,49 @@
     <t xml:space="preserve">0.36418804526329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357273072004318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349973976612091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339217334985733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323850750923157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361883074045181</t>
+    <t xml:space="preserve">0.357273101806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349973946809769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339217364788055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323850721120834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361883014440536</t>
   </si>
   <si>
     <t xml:space="preserve">0.350742280483246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389542937278748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404141157865524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39645791053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412592798471451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404909521341324</t>
+    <t xml:space="preserve">0.389542907476425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404141187667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396457850933075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412592738866806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404909491539001</t>
   </si>
   <si>
     <t xml:space="preserve">0.401836186647415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394152909517288</t>
+    <t xml:space="preserve">0.394152879714966</t>
   </si>
   <si>
     <t xml:space="preserve">0.399531155824661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40260449051857</t>
+    <t xml:space="preserve">0.402604460716248</t>
   </si>
   <si>
     <t xml:space="preserve">0.401067852973938</t>
@@ -1643,16 +1643,16 @@
     <t xml:space="preserve">0.397994548082352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375712960958481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36457222700119</t>
+    <t xml:space="preserve">0.375712990760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364572197198868</t>
   </si>
   <si>
     <t xml:space="preserve">0.345748156309128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336528211832047</t>
+    <t xml:space="preserve">0.336528241634369</t>
   </si>
   <si>
     <t xml:space="preserve">0.335759878158569</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">0.337296515703201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329613208770752</t>
+    <t xml:space="preserve">0.329613238573074</t>
   </si>
   <si>
     <t xml:space="preserve">0.328076601028442</t>
@@ -1676,28 +1676,28 @@
     <t xml:space="preserve">0.326924085617065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312709987163544</t>
+    <t xml:space="preserve">0.312710016965866</t>
   </si>
   <si>
     <t xml:space="preserve">0.341138184070587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322698265314102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326155751943588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324619084596634</t>
+    <t xml:space="preserve">0.322698295116425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326155722141266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324619114398956</t>
   </si>
   <si>
     <t xml:space="preserve">0.325771570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330381542444229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329997390508652</t>
+    <t xml:space="preserve">0.330381572246552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329997420310974</t>
   </si>
   <si>
     <t xml:space="preserve">0.324234932661057</t>
@@ -1706,28 +1706,28 @@
     <t xml:space="preserve">0.313862472772598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301185071468353</t>
+    <t xml:space="preserve">0.301185041666031</t>
   </si>
   <si>
     <t xml:space="preserve">0.30387419462204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296959221363068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302721709012985</t>
+    <t xml:space="preserve">0.29695925116539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302721738815308</t>
   </si>
   <si>
     <t xml:space="preserve">0.32308241724968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308100044727325</t>
+    <t xml:space="preserve">0.308100014925003</t>
   </si>
   <si>
     <t xml:space="preserve">0.310405015945435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306947499513626</t>
+    <t xml:space="preserve">0.306947529315948</t>
   </si>
   <si>
     <t xml:space="preserve">0.314630836248398</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">0.30848416686058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304642498493195</t>
+    <t xml:space="preserve">0.304642528295517</t>
   </si>
   <si>
     <t xml:space="preserve">0.320777416229248</t>
@@ -1748,34 +1748,34 @@
     <t xml:space="preserve">0.356888890266418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358041405677795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356120586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360730558633804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358809769153595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351126462221146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355736434459686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342290669679642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37187135219574</t>
+    <t xml:space="preserve">0.358041435480118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356120556592941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360730588436127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35880970954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351126432418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355736464262009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342290639877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371871322393417</t>
   </si>
   <si>
     <t xml:space="preserve">0.370334655046463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383780419826508</t>
+    <t xml:space="preserve">0.38378044962883</t>
   </si>
   <si>
     <t xml:space="preserve">0.376097142696381</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">0.377249658107758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398762851953506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403372824192047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406446099281311</t>
+    <t xml:space="preserve">0.398762881755829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403372794389725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406446129083633</t>
   </si>
   <si>
     <t xml:space="preserve">0.40951943397522</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">0.39107957482338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381475418806076</t>
+    <t xml:space="preserve">0.381475448608398</t>
   </si>
   <si>
     <t xml:space="preserve">0.407214462757111</t>
@@ -1817,82 +1817,82 @@
     <t xml:space="preserve">0.411824434995651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414897829294205</t>
+    <t xml:space="preserve">0.41489776968956</t>
   </si>
   <si>
     <t xml:space="preserve">0.417202711105347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397226184606552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40875118970871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410287797451019</t>
+    <t xml:space="preserve">0.397226214408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408751159906387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410287767648697</t>
   </si>
   <si>
     <t xml:space="preserve">0.414129436016083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416434407234192</t>
+    <t xml:space="preserve">0.416434437036514</t>
   </si>
   <si>
     <t xml:space="preserve">0.418739438056946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4202761054039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421812772750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430264413356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473290771245956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49480402469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484047383069992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267297744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506328880786896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479437470436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48251074552536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595772266388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070826768875</t>
+    <t xml:space="preserve">0.420276045799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421812742948532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430264323949814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473290801048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494803965091705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48404735326767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267387151718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506328940391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479437410831451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482510805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595831871033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070796966553</t>
   </si>
   <si>
     <t xml:space="preserve">0.465607553720474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460997492074966</t>
+    <t xml:space="preserve">0.460997521877289</t>
   </si>
   <si>
     <t xml:space="preserve">0.453314214944839</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434105962514877</t>
+    <t xml:space="preserve">0.434106051921844</t>
   </si>
   <si>
     <t xml:space="preserve">0.441789269447327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44563090801239</t>
+    <t xml:space="preserve">0.445630967617035</t>
   </si>
   <si>
     <t xml:space="preserve">0.449472546577454</t>
@@ -1901,52 +1901,52 @@
     <t xml:space="preserve">0.45100924372673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460229218006134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454082578420639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457155853509903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451777547597885</t>
+    <t xml:space="preserve">0.460229188203812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454082548618317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457155913114548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451777577400208</t>
   </si>
   <si>
     <t xml:space="preserve">0.456387519836426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46330252289772</t>
+    <t xml:space="preserve">0.463302493095398</t>
   </si>
   <si>
     <t xml:space="preserve">0.470985800027847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467144101858139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457924246788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447167634963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432569354772568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437947660684586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433337718248367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434874325990677</t>
+    <t xml:space="preserve">0.467144131660461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457924216985703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447167605161667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432569414377213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437947630882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433337658643723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434874296188354</t>
   </si>
   <si>
     <t xml:space="preserve">0.436410993337631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43948432803154</t>
+    <t xml:space="preserve">0.439484298229218</t>
   </si>
   <si>
     <t xml:space="preserve">0.441020965576172</t>
@@ -1955,25 +1955,25 @@
     <t xml:space="preserve">0.440252631902695</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43871596455574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442557603120804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485584050416946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455619215965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443326026201248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429496049880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435642689466476</t>
+    <t xml:space="preserve">0.438715934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442557632923126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485584110021591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455619245767593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443325966596603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429496020078659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435642659664154</t>
   </si>
   <si>
     <t xml:space="preserve">0.450240910053253</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">0.427191019058228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375328838825226</t>
+    <t xml:space="preserve">0.375328809022903</t>
   </si>
   <si>
     <t xml:space="preserve">0.386469602584839</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">0.393384575843811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365724712610245</t>
+    <t xml:space="preserve">0.365724742412567</t>
   </si>
   <si>
     <t xml:space="preserve">0.372639685869217</t>
@@ -2006,49 +2006,49 @@
     <t xml:space="preserve">0.317319959402084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265073597431183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259695321321487</t>
+    <t xml:space="preserve">0.265073537826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259695291519165</t>
   </si>
   <si>
     <t xml:space="preserve">0.239334553480148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242023691534996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234724596142769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245865345001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258926928043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.251627832651138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266610234975815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269299387931824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258158624172211</t>
+    <t xml:space="preserve">0.242023676633835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234724566340446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24586533010006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258926957845688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.251627802848816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266610205173492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269299417734146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258158564567566</t>
   </si>
   <si>
     <t xml:space="preserve">0.251243680715561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252011984586716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242407873272896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245097041130066</t>
+    <t xml:space="preserve">0.252011954784393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242407858371735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245096981525421</t>
   </si>
   <si>
     <t xml:space="preserve">0.254701137542725</t>
@@ -2060,16 +2060,16 @@
     <t xml:space="preserve">0.254316955804825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261231929063797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262768566608429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264689445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271988570690155</t>
+    <t xml:space="preserve">0.261231958866119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262768596410751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264689415693283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271988540887833</t>
   </si>
   <si>
     <t xml:space="preserve">0.273909360170364</t>
@@ -2084,22 +2084,22 @@
     <t xml:space="preserve">0.275446027517319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268915235996246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265841901302338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25854280591011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26545774936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263152748346329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292733460664749</t>
+    <t xml:space="preserve">0.268915206193924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265841871500015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258542776107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265457719564438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263152718544006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292733430862427</t>
   </si>
   <si>
     <t xml:space="preserve">0.327692419290543</t>
@@ -2111,22 +2111,22 @@
     <t xml:space="preserve">0.30195340514183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332302391529083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332686543464661</t>
+    <t xml:space="preserve">0.332302361726761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332686573266983</t>
   </si>
   <si>
     <t xml:space="preserve">0.306179195642471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305026710033417</t>
+    <t xml:space="preserve">0.305026739835739</t>
   </si>
   <si>
     <t xml:space="preserve">0.312325805425644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331918239593506</t>
+    <t xml:space="preserve">0.331918209791183</t>
   </si>
   <si>
     <t xml:space="preserve">0.315399140119553</t>
@@ -2135,124 +2135,124 @@
     <t xml:space="preserve">0.326539933681488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292349249124527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289275944232941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291196763515472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286970943212509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2850501537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273525208234787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260847747325897</t>
+    <t xml:space="preserve">0.292349278926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289275974035263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291196793317795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286970973014832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285050123929977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273525178432465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26084777712822</t>
   </si>
   <si>
     <t xml:space="preserve">0.261616080999374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270067721605301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27851939201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27314105629921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266994386911392</t>
+    <t xml:space="preserve">0.270067691802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278519362211227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273141026496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266994416713715</t>
   </si>
   <si>
     <t xml:space="preserve">0.255469471216202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253164440393448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256621956825256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256237775087357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.249322831630707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236261233687401</t>
+    <t xml:space="preserve">0.25316447019577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256621927022934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256237834692001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.249322846531868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.236261263489723</t>
   </si>
   <si>
     <t xml:space="preserve">0.238182067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253548622131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267762750387192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283513456583023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277750998735428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294654250144958</t>
+    <t xml:space="preserve">0.25354865193367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267762780189514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283513486385345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27775102853775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294654279947281</t>
   </si>
   <si>
     <t xml:space="preserve">0.319624990224838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343827307224274</t>
+    <t xml:space="preserve">0.343827277421951</t>
   </si>
   <si>
     <t xml:space="preserve">0.338449001312256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340753972530365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338833212852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338064819574356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336912333965302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333839058876038</t>
+    <t xml:space="preserve">0.340754002332687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338833183050156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338064879179001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336912304162979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333839029073715</t>
   </si>
   <si>
     <t xml:space="preserve">0.330765724182129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328844904899597</t>
+    <t xml:space="preserve">0.328844875097275</t>
   </si>
   <si>
     <t xml:space="preserve">0.33998566865921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347668945789337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359962224960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351894795894623</t>
+    <t xml:space="preserve">0.34766897559166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359962195158005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3518947660923</t>
   </si>
   <si>
     <t xml:space="preserve">0.369182199239731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357657223939896</t>
+    <t xml:space="preserve">0.357657253742218</t>
   </si>
   <si>
     <t xml:space="preserve">0.355352252721786</t>
@@ -2261,31 +2261,31 @@
     <t xml:space="preserve">0.348053157329559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34651643037796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347284764051437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363419681787491</t>
+    <t xml:space="preserve">0.346516519784927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347284823656082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363419711589813</t>
   </si>
   <si>
     <t xml:space="preserve">0.373792141675949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373023808002472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379554629325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42565444111824</t>
+    <t xml:space="preserve">0.373023837804794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379554599523544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425654381513596</t>
   </si>
   <si>
     <t xml:space="preserve">0.417971104383469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381859630346298</t>
+    <t xml:space="preserve">0.381859600543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.383012115955353</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">0.377633810043335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378402173519135</t>
+    <t xml:space="preserve">0.37840211391449</t>
   </si>
   <si>
     <t xml:space="preserve">0.381091266870499</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">0.380322962999344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348437309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400299549102783</t>
+    <t xml:space="preserve">0.348437249660492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400299519300461</t>
   </si>
   <si>
     <t xml:space="preserve">0.383396297693253</t>
@@ -2318,43 +2318,43 @@
     <t xml:space="preserve">0.388006269931793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428727656602859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368413865566254</t>
+    <t xml:space="preserve">0.428727716207504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368413835763931</t>
   </si>
   <si>
     <t xml:space="preserve">0.344595670700073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334223181009293</t>
+    <t xml:space="preserve">0.334223210811615</t>
   </si>
   <si>
     <t xml:space="preserve">0.341906487941742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323466569185257</t>
+    <t xml:space="preserve">0.323466598987579</t>
   </si>
   <si>
     <t xml:space="preserve">0.340369820594788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331149876117706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348821461200714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322314113378525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285818487405777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337680667638779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345363974571228</t>
+    <t xml:space="preserve">0.331149905920029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348821431398392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322314083576202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285818457603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337680697441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345363944768906</t>
   </si>
   <si>
     <t xml:space="preserve">0.341522365808487</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">0.35406482219696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352829694747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347477585077286</t>
+    <t xml:space="preserve">0.352829724550247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347477555274963</t>
   </si>
   <si>
     <t xml:space="preserve">0.345830768346786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341713726520538</t>
+    <t xml:space="preserve">0.341713696718216</t>
   </si>
   <si>
     <t xml:space="preserve">0.34253716468811</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">0.350359499454498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345007330179214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339655190706253</t>
+    <t xml:space="preserve">0.345007359981537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339655220508575</t>
   </si>
   <si>
     <t xml:space="preserve">0.342948853969574</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">0.318246632814407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317834943532944</t>
+    <t xml:space="preserve">0.317834913730621</t>
   </si>
   <si>
     <t xml:space="preserve">0.319481790065765</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">0.309600859880447</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309189140796661</t>
+    <t xml:space="preserve">0.309189170598984</t>
   </si>
   <si>
     <t xml:space="preserve">0.32112854719162</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">0.32689243555069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323187112808228</t>
+    <t xml:space="preserve">0.323187083005905</t>
   </si>
   <si>
     <t xml:space="preserve">0.323598802089691</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">0.315364688634872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31330618262291</t>
+    <t xml:space="preserve">0.313306212425232</t>
   </si>
   <si>
     <t xml:space="preserve">0.310424298048019</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">0.311247676610947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317011564970016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317423224449158</t>
+    <t xml:space="preserve">0.317011535167694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31742325425148</t>
   </si>
   <si>
     <t xml:space="preserve">0.311659395694733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316188126802444</t>
+    <t xml:space="preserve">0.316188156604767</t>
   </si>
   <si>
     <t xml:space="preserve">0.319893479347229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304660439491272</t>
+    <t xml:space="preserve">0.304660469293594</t>
   </si>
   <si>
     <t xml:space="preserve">0.30877748131752</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">0.302601933479309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307954043149948</t>
+    <t xml:space="preserve">0.307954072952271</t>
   </si>
   <si>
     <t xml:space="preserve">0.306307256221771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301778525114059</t>
+    <t xml:space="preserve">0.301778495311737</t>
   </si>
   <si>
     <t xml:space="preserve">0.3038370013237</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">0.313717931509018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326480686664581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328539222478867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340890318155289</t>
+    <t xml:space="preserve">0.326480716466904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328539192676544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340890347957611</t>
   </si>
   <si>
     <t xml:space="preserve">0.356535047292709</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">0.335126489400864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358181834220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3470658659935</t>
+    <t xml:space="preserve">0.358181864023209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347065836191177</t>
   </si>
   <si>
     <t xml:space="preserve">0.344183951616287</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">0.336773306131363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345419079065323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349124372005463</t>
+    <t xml:space="preserve">0.345419049263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349124401807785</t>
   </si>
   <si>
     <t xml:space="preserve">0.338008403778076</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">0.335949867963791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343772202730179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33759668469429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340066909790039</t>
+    <t xml:space="preserve">0.343772232532501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337596714496613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340066879987717</t>
   </si>
   <si>
     <t xml:space="preserve">0.340478628873825</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">0.338420122861862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346654146909714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355711668729782</t>
+    <t xml:space="preserve">0.346654176712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35571163892746</t>
   </si>
   <si>
     <t xml:space="preserve">0.359005272388458</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">0.395235151052475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399763882160187</t>
+    <t xml:space="preserve">0.399763911962509</t>
   </si>
   <si>
     <t xml:space="preserve">0.389471292495728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401822417974472</t>
+    <t xml:space="preserve">0.401822447776794</t>
   </si>
   <si>
     <t xml:space="preserve">0.411703288555145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402234137058258</t>
+    <t xml:space="preserve">0.402234107255936</t>
   </si>
   <si>
     <t xml:space="preserve">0.403469234704971</t>
@@ -2681,13 +2681,13 @@
     <t xml:space="preserve">0.408409655094147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405939429998398</t>
+    <t xml:space="preserve">0.40593945980072</t>
   </si>
   <si>
     <t xml:space="preserve">0.406351149082184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400175601243973</t>
+    <t xml:space="preserve">0.40017557144165</t>
   </si>
   <si>
     <t xml:space="preserve">0.397705405950546</t>
@@ -2699,28 +2699,28 @@
     <t xml:space="preserve">0.403057515621185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394823461771011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417467176914215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433111846446991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430641651153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441345900297165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454520404338837</t>
+    <t xml:space="preserve">0.394823431968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417467147111893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433111876249313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430641680955887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441345930099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454520463943481</t>
   </si>
   <si>
     <t xml:space="preserve">0.442992717027664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488280087709427</t>
+    <t xml:space="preserve">0.488280147314072</t>
   </si>
   <si>
     <t xml:space="preserve">0.50392484664917</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">0.518746137619019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522039830684662</t>
+    <t xml:space="preserve">0.522039771080017</t>
   </si>
   <si>
     <t xml:space="preserve">0.500631153583527</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">0.472635388374329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493220567703247</t>
+    <t xml:space="preserve">0.493220508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.491573750972748</t>
@@ -2765,10 +2765,10 @@
     <t xml:space="preserve">0.467694938182831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459460824728012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461107730865479</t>
+    <t xml:space="preserve">0.459460884332657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461107671260834</t>
   </si>
   <si>
     <t xml:space="preserve">0.476752400398254</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">0.479222655296326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477575778961182</t>
+    <t xml:space="preserve">0.477575838565826</t>
   </si>
   <si>
     <t xml:space="preserve">0.51545250415802</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">0.504748225212097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501454651355743</t>
+    <t xml:space="preserve">0.501454591751099</t>
   </si>
   <si>
     <t xml:space="preserve">0.498984456062317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494043916463852</t>
+    <t xml:space="preserve">0.494043976068497</t>
   </si>
   <si>
     <t xml:space="preserve">0.505571663379669</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">0.470165133476257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46522468328476</t>
+    <t xml:space="preserve">0.465224742889404</t>
   </si>
   <si>
     <t xml:space="preserve">0.460284292697906</t>
@@ -2834,34 +2834,34 @@
     <t xml:space="preserve">0.466750353574753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473822295665741</t>
+    <t xml:space="preserve">0.473822325468063</t>
   </si>
   <si>
     <t xml:space="preserve">0.457910388708115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461446404457092</t>
+    <t xml:space="preserve">0.46144637465477</t>
   </si>
   <si>
     <t xml:space="preserve">0.464098334312439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454374372959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441114455461502</t>
+    <t xml:space="preserve">0.454374402761459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44111442565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.420782536268234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435810446739197</t>
+    <t xml:space="preserve">0.435810476541519</t>
   </si>
   <si>
     <t xml:space="preserve">0.438462436199188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427412480115891</t>
+    <t xml:space="preserve">0.427412509918213</t>
   </si>
   <si>
     <t xml:space="preserve">0.426528483629227</t>
@@ -2870,37 +2870,37 @@
     <t xml:space="preserve">0.433158487081528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448186457157135</t>
+    <t xml:space="preserve">0.448186427354813</t>
   </si>
   <si>
     <t xml:space="preserve">0.441998451948166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434484422206879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444650441408157</t>
+    <t xml:space="preserve">0.434484452009201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44465047121048</t>
   </si>
   <si>
     <t xml:space="preserve">0.449070423841476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437578469514847</t>
+    <t xml:space="preserve">0.437578439712524</t>
   </si>
   <si>
     <t xml:space="preserve">0.433600455522537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430948495864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431390464305878</t>
+    <t xml:space="preserve">0.430948466062546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4313904941082</t>
   </si>
   <si>
     <t xml:space="preserve">0.434926480054855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429622501134872</t>
+    <t xml:space="preserve">0.42962247133255</t>
   </si>
   <si>
     <t xml:space="preserve">0.428738504648209</t>
@@ -2912,25 +2912,25 @@
     <t xml:space="preserve">0.434042483568192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421666473150253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430506438016891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427854508161545</t>
+    <t xml:space="preserve">0.421666502952576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430506467819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427854478359222</t>
   </si>
   <si>
     <t xml:space="preserve">0.419456511735916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417246520519257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411942511796951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414152532815933</t>
+    <t xml:space="preserve">0.417246550321579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411942541599274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414152503013611</t>
   </si>
   <si>
     <t xml:space="preserve">0.418130487203598</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">0.42255049943924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413710504770279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.425202518701553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423876494169235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414594560861588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422992497682571</t>
+    <t xml:space="preserve">0.413710534572601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.425202488899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423876464366913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414594531059265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422992527484894</t>
   </si>
   <si>
     <t xml:space="preserve">0.421224534511566</t>
@@ -2960,13 +2960,13 @@
     <t xml:space="preserve">0.413268536329269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415920495986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408406585454941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412384569644928</t>
+    <t xml:space="preserve">0.415920525789261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408406555652618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412384539842606</t>
   </si>
   <si>
     <t xml:space="preserve">0.41105854511261</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">0.428296476602554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424760490655899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422108501195908</t>
+    <t xml:space="preserve">0.424760520458221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422108471393585</t>
   </si>
   <si>
     <t xml:space="preserve">0.415478527545929</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">0.400008589029312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401334583759308</t>
+    <t xml:space="preserve">0.401334553956985</t>
   </si>
   <si>
     <t xml:space="preserve">0.39249461889267</t>
@@ -3029,10 +3029,10 @@
     <t xml:space="preserve">0.400450587272644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389842629432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388958603143692</t>
+    <t xml:space="preserve">0.389842599630356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388958632946014</t>
   </si>
   <si>
     <t xml:space="preserve">0.395146578550339</t>
@@ -3053,13 +3053,13 @@
     <t xml:space="preserve">0.397798597812653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401776552200317</t>
+    <t xml:space="preserve">0.40177658200264</t>
   </si>
   <si>
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660578489304</t>
+    <t xml:space="preserve">0.402660548686981</t>
   </si>
   <si>
     <t xml:space="preserve">0.419898509979248</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">0.456523567438126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465635806322098</t>
+    <t xml:space="preserve">0.465635776519775</t>
   </si>
   <si>
     <t xml:space="preserve">0.464724570512772</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">0.468369513750076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480215460062027</t>
+    <t xml:space="preserve">0.480215400457382</t>
   </si>
   <si>
     <t xml:space="preserve">0.482949018478394</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">0.486593961715698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501173615455627</t>
+    <t xml:space="preserve">0.501173555850983</t>
   </si>
   <si>
     <t xml:space="preserve">0.523042976856232</t>
@@ -3158,28 +3158,28 @@
     <t xml:space="preserve">0.519398033618927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51393073797226</t>
+    <t xml:space="preserve">0.513930678367615</t>
   </si>
   <si>
     <t xml:space="preserve">0.524865388870239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509374618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526687860488892</t>
+    <t xml:space="preserve">0.509374558925629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526687920093536</t>
   </si>
   <si>
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267514228821</t>
+    <t xml:space="preserve">0.541267454624176</t>
   </si>
   <si>
     <t xml:space="preserve">0.546734869480133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537622570991516</t>
+    <t xml:space="preserve">0.537622511386871</t>
   </si>
   <si>
     <t xml:space="preserve">0.549468457698822</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">0.564959287643433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569515466690063</t>
+    <t xml:space="preserve">0.569515407085419</t>
   </si>
   <si>
     <t xml:space="preserve">0.565870463848114</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">0.550379633903503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547646105289459</t>
+    <t xml:space="preserve">0.547646045684814</t>
   </si>
   <si>
     <t xml:space="preserve">0.55584704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553113400936127</t>
+    <t xml:space="preserve">0.553113341331482</t>
   </si>
   <si>
     <t xml:space="preserve">0.564048111438751</t>
@@ -3227,25 +3227,25 @@
     <t xml:space="preserve">0.559491991996765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561314404010773</t>
+    <t xml:space="preserve">0.561314344406128</t>
   </si>
   <si>
     <t xml:space="preserve">0.558580696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556758344173431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542178690433502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557669460773468</t>
+    <t xml:space="preserve">0.556758284568787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542178750038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557669520378113</t>
   </si>
   <si>
     <t xml:space="preserve">0.534888863563538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528510272502899</t>
+    <t xml:space="preserve">0.528510332107544</t>
   </si>
   <si>
     <t xml:space="preserve">0.535800099372864</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617436408997</t>
+    <t xml:space="preserve">0.496617496013641</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
@@ -3293,19 +3293,19 @@
     <t xml:space="preserve">0.487505257129669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495706290006638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493883818387985</t>
+    <t xml:space="preserve">0.495706230401993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49388375878334</t>
   </si>
   <si>
     <t xml:space="preserve">0.491150081157684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517575681209564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489643454551697</t>
+    <t xml:space="preserve">0.517575621604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489643424749374</t>
   </si>
   <si>
     <t xml:space="preserve">0.48199275135994</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">0.475776553153992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47673287987709</t>
+    <t xml:space="preserve">0.476732909679413</t>
   </si>
   <si>
     <t xml:space="preserve">0.480080038309097</t>
@@ -3329,31 +3329,31 @@
     <t xml:space="preserve">0.46477872133255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473385751247406</t>
+    <t xml:space="preserve">0.473385721445084</t>
   </si>
   <si>
     <t xml:space="preserve">0.469560384750366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470994919538498</t>
+    <t xml:space="preserve">0.470994889736176</t>
   </si>
   <si>
     <t xml:space="preserve">0.459040701389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453780859708786</t>
+    <t xml:space="preserve">0.453780889511108</t>
   </si>
   <si>
     <t xml:space="preserve">0.451390027999878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447564661502838</t>
+    <t xml:space="preserve">0.447564691305161</t>
   </si>
   <si>
     <t xml:space="preserve">0.45091187953949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441826701164246</t>
+    <t xml:space="preserve">0.441826671361923</t>
   </si>
   <si>
     <t xml:space="preserve">0.438479512929916</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">0.432741492986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436088651418686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438001364469528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441348493099213</t>
+    <t xml:space="preserve">0.436088681221008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438001334667206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441348522901535</t>
   </si>
   <si>
     <t xml:space="preserve">0.446608364582062</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">0.436566829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438957691192627</t>
+    <t xml:space="preserve">0.438957661390305</t>
   </si>
   <si>
     <t xml:space="preserve">0.444695681333542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439435839653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4336978495121</t>
+    <t xml:space="preserve">0.439435869455338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433697819709778</t>
   </si>
   <si>
     <t xml:space="preserve">0.434654176235199</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">0.46669140458107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454737216234207</t>
+    <t xml:space="preserve">0.454737186431885</t>
   </si>
   <si>
     <t xml:space="preserve">0.455693542957306</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">0.561368525028229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538416504859924</t>
+    <t xml:space="preserve">0.538416564464569</t>
   </si>
   <si>
     <t xml:space="preserve">0.544154524803162</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">0.540329158306122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525984168052673</t>
+    <t xml:space="preserve">0.525984108448029</t>
   </si>
   <si>
     <t xml:space="preserve">0.517377138137817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525027811527252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521202445030212</t>
+    <t xml:space="preserve">0.525027871131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521202504634857</t>
   </si>
   <si>
     <t xml:space="preserve">0.519289791584015</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">0.531722128391266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518333494663239</t>
+    <t xml:space="preserve">0.518333435058594</t>
   </si>
   <si>
     <t xml:space="preserve">0.514508128166199</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">0.527896821498871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526940524578094</t>
+    <t xml:space="preserve">0.52694046497345</t>
   </si>
   <si>
     <t xml:space="preserve">0.535547494888306</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">0.553717851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568062901496887</t>
+    <t xml:space="preserve">0.568062841892242</t>
   </si>
   <si>
     <t xml:space="preserve">0.55849951505661</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">0.555630505084991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55467414855957</t>
+    <t xml:space="preserve">0.554674208164215</t>
   </si>
   <si>
     <t xml:space="preserve">0.557543218135834</t>
@@ -3491,16 +3491,16 @@
     <t xml:space="preserve">0.54702353477478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537460088729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551805257797241</t>
+    <t xml:space="preserve">0.537460148334503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551805198192596</t>
   </si>
   <si>
     <t xml:space="preserve">0.524071455001831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533634841442108</t>
+    <t xml:space="preserve">0.533634901046753</t>
   </si>
   <si>
     <t xml:space="preserve">0.536503851413727</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">0.522158801555634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529809474945068</t>
+    <t xml:space="preserve">0.529809534549713</t>
   </si>
   <si>
     <t xml:space="preserve">0.532678484916687</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">0.499206781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496337741613388</t>
+    <t xml:space="preserve">0.49633777141571</t>
   </si>
   <si>
     <t xml:space="preserve">0.506857395172119</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">0.487730741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483905375003815</t>
+    <t xml:space="preserve">0.483905404806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.461909741163254</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">0.478167414665222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468604058027267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471473038196564</t>
+    <t xml:space="preserve">0.46860408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471473067998886</t>
   </si>
   <si>
     <t xml:space="preserve">0.48260822892189</t>
@@ -69562,7 +69562,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6911574074</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>770182</v>
@@ -69571,7 +69571,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="D2510" t="n">
-        <v>0.532000005245209</v>
+        <v>0.531000018119812</v>
       </c>
       <c r="E2510" t="n">
         <v>0.538999974727631</v>
@@ -69583,6 +69583,32 @@
         <v>1325</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6911689815</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>399205</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>0.532000005245209</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>0.532000005245209</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>0.533999979496002</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="1329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="1330">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,16 +44,16 @@
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32744625210762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32115626335144</t>
+    <t xml:space="preserve">0.327446281909943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321156322956085</t>
   </si>
   <si>
     <t xml:space="preserve">0.317678362131119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307318449020386</t>
+    <t xml:space="preserve">0.307318478822708</t>
   </si>
   <si>
     <t xml:space="preserve">0.288448721170425</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">0.289336681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294368624687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285636723041534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273796826601028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258997082710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258257031440735</t>
+    <t xml:space="preserve">0.294368594884872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285636752843857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273796856403351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258997023105621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258257061243057</t>
   </si>
   <si>
     <t xml:space="preserve">0.243605196475983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.246417194604874</t>
+    <t xml:space="preserve">0.246417164802551</t>
   </si>
   <si>
     <t xml:space="preserve">0.262696951627731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.256407052278519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259810984134674</t>
+    <t xml:space="preserve">0.256407082080841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259811013936996</t>
   </si>
   <si>
     <t xml:space="preserve">0.261512994766235</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">0.253077119588852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286894679069519</t>
+    <t xml:space="preserve">0.286894708871841</t>
   </si>
   <si>
     <t xml:space="preserve">0.284600764513016</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">0.277496844530106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287116765975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290742635726929</t>
+    <t xml:space="preserve">0.287116706371307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290742665529251</t>
   </si>
   <si>
     <t xml:space="preserve">0.263806998729706</t>
@@ -122,34 +122,34 @@
     <t xml:space="preserve">0.256777077913284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.250117123126984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277570813894272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297994583845139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310796439647675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303544551134109</t>
+    <t xml:space="preserve">0.250117152929306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277570754289627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297994613647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310796409845352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303544491529465</t>
   </si>
   <si>
     <t xml:space="preserve">0.304358512163162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318122327327728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309686452150345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301620543003082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310352444648743</t>
+    <t xml:space="preserve">0.318122357130051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309686481952667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301620572805405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31035241484642</t>
   </si>
   <si>
     <t xml:space="preserve">0.323376268148422</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">0.320046335458755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316716372966766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315236389636993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315606415271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332996159791946</t>
+    <t xml:space="preserve">0.316716343164444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315236419439316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315606385469437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332996189594269</t>
   </si>
   <si>
     <t xml:space="preserve">0.332256197929382</t>
@@ -176,34 +176,34 @@
     <t xml:space="preserve">0.328852236270905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330480217933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311240434646606</t>
+    <t xml:space="preserve">0.330480188131332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311240404844284</t>
   </si>
   <si>
     <t xml:space="preserve">0.312054425477982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299696534872055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296884626150131</t>
+    <t xml:space="preserve">0.299696564674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296884596347809</t>
   </si>
   <si>
     <t xml:space="preserve">0.299400568008423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297476559877396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295996606349945</t>
+    <t xml:space="preserve">0.297476589679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295996636152267</t>
   </si>
   <si>
     <t xml:space="preserve">0.293702632188797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298216581344604</t>
+    <t xml:space="preserve">0.298216551542282</t>
   </si>
   <si>
     <t xml:space="preserve">0.286376714706421</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">0.276756852865219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274536818265915</t>
+    <t xml:space="preserve">0.274536848068237</t>
   </si>
   <si>
     <t xml:space="preserve">0.2723169028759</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">0.268172919750214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268616884946823</t>
+    <t xml:space="preserve">0.26861697435379</t>
   </si>
   <si>
     <t xml:space="preserve">0.269208908081055</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">0.275276839733124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28489676117897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290002673864365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308206468820572</t>
+    <t xml:space="preserve">0.284896731376648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290002703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308206498622894</t>
   </si>
   <si>
     <t xml:space="preserve">0.309168457984924</t>
@@ -254,61 +254,61 @@
     <t xml:space="preserve">0.318196356296539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316938400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308946490287781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314200431108475</t>
+    <t xml:space="preserve">0.31693834066391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308946460485458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314200401306152</t>
   </si>
   <si>
     <t xml:space="preserve">0.321378320455551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31938037276268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722410678864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313682377338409</t>
+    <t xml:space="preserve">0.319380313158035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722470283508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313682407140732</t>
   </si>
   <si>
     <t xml:space="preserve">0.313312411308289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307096511125565</t>
+    <t xml:space="preserve">0.307096481323242</t>
   </si>
   <si>
     <t xml:space="preserve">0.307614475488663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304950505495071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305616468191147</t>
+    <t xml:space="preserve">0.304950535297394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305616497993469</t>
   </si>
   <si>
     <t xml:space="preserve">0.2995485663414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305320471525192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295626610517502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300954520702362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314400345087051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318779766559601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318856656551361</t>
+    <t xml:space="preserve">0.305320501327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295626640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300954550504684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314400285482407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318779826164246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318856626749039</t>
   </si>
   <si>
     <t xml:space="preserve">0.318395614624023</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">0.318088293075562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307331711053848</t>
+    <t xml:space="preserve">0.307331681251526</t>
   </si>
   <si>
     <t xml:space="preserve">0.321776270866394</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">0.320393264293671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311557471752167</t>
+    <t xml:space="preserve">0.311557501554489</t>
   </si>
   <si>
     <t xml:space="preserve">0.305795013904572</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">0.301569223403931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295806795358658</t>
+    <t xml:space="preserve">0.295806735754013</t>
   </si>
   <si>
     <t xml:space="preserve">0.299648374319077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296575099229813</t>
+    <t xml:space="preserve">0.296575129032135</t>
   </si>
   <si>
     <t xml:space="preserve">0.303490042686462</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">0.314246654510498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318011432886124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318702965974808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321161597967148</t>
+    <t xml:space="preserve">0.318011462688446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318702936172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32116162776947</t>
   </si>
   <si>
     <t xml:space="preserve">0.310020834207535</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">0.311941653490067</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311173290014267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30725485086441</t>
+    <t xml:space="preserve">0.311173349618912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307254880666733</t>
   </si>
   <si>
     <t xml:space="preserve">0.30671700835228</t>
@@ -380,25 +380,25 @@
     <t xml:space="preserve">0.305564552545547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304949849843979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306870698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297727555036545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301799714565277</t>
+    <t xml:space="preserve">0.304949879646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306870669126511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29772761464119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301799684762955</t>
   </si>
   <si>
     <t xml:space="preserve">0.304027855396271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300032526254654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313478320837021</t>
+    <t xml:space="preserve">0.300032585859299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313478291034698</t>
   </si>
   <si>
     <t xml:space="preserve">0.312556326389313</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">0.299110561609268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305257230997086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295576214790344</t>
+    <t xml:space="preserve">0.305257201194763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295576244592667</t>
   </si>
   <si>
     <t xml:space="preserve">0.295960396528244</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">0.29373225569725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298803240060806</t>
+    <t xml:space="preserve">0.298803210258484</t>
   </si>
   <si>
     <t xml:space="preserve">0.300416707992554</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">0.298880070447922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30548769235611</t>
+    <t xml:space="preserve">0.305487662553787</t>
   </si>
   <si>
     <t xml:space="preserve">0.309559851884842</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">0.306563347578049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300186216831207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298649609088898</t>
+    <t xml:space="preserve">0.30018624663353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298649579286575</t>
   </si>
   <si>
     <t xml:space="preserve">0.296421378850937</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">0.3014155626297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300647228956223</t>
+    <t xml:space="preserve">0.3006471991539</t>
   </si>
   <si>
     <t xml:space="preserve">0.282975614070892</t>
@@ -497,34 +497,34 @@
     <t xml:space="preserve">0.292656570672989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29250293970108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28958323597908</t>
+    <t xml:space="preserve">0.292502909898758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289583265781403</t>
   </si>
   <si>
     <t xml:space="preserve">0.288123458623886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2842817902565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287892997264862</t>
+    <t xml:space="preserve">0.284281820058823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28789296746254</t>
   </si>
   <si>
     <t xml:space="preserve">0.290044277906418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292887091636658</t>
+    <t xml:space="preserve">0.292887061834335</t>
   </si>
   <si>
     <t xml:space="preserve">0.293117612600327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291888266801834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289813816547394</t>
+    <t xml:space="preserve">0.291888296604156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289813786745071</t>
   </si>
   <si>
     <t xml:space="preserve">0.286586791276932</t>
@@ -536,61 +536,61 @@
     <t xml:space="preserve">0.291811436414719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292579770088196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295729875564575</t>
+    <t xml:space="preserve">0.292579799890518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295729905366898</t>
   </si>
   <si>
     <t xml:space="preserve">0.298419058322906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294731050729752</t>
+    <t xml:space="preserve">0.294731080532074</t>
   </si>
   <si>
     <t xml:space="preserve">0.287355124950409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293809086084366</t>
+    <t xml:space="preserve">0.293809115886688</t>
   </si>
   <si>
     <t xml:space="preserve">0.292041957378387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286740481853485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284666001796722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278903484344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27559968829155</t>
+    <t xml:space="preserve">0.286740452051163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2846659719944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278903514146805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275599718093872</t>
   </si>
   <si>
     <t xml:space="preserve">0.270221382379532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272449553012848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276675343513489</t>
+    <t xml:space="preserve">0.272449523210526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276675373315811</t>
   </si>
   <si>
     <t xml:space="preserve">0.273986160755157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275676548480988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275522857904434</t>
+    <t xml:space="preserve">0.275676518678665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275522828102112</t>
   </si>
   <si>
     <t xml:space="preserve">0.276598513126373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270989686250687</t>
+    <t xml:space="preserve">0.270989716053009</t>
   </si>
   <si>
     <t xml:space="preserve">0.27114337682724</t>
@@ -605,43 +605,43 @@
     <t xml:space="preserve">0.268146902322769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267378568649292</t>
+    <t xml:space="preserve">0.267378598451614</t>
   </si>
   <si>
     <t xml:space="preserve">0.264612585306168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265765070915222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262384474277496</t>
+    <t xml:space="preserve">0.265765100717545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262384414672852</t>
   </si>
   <si>
     <t xml:space="preserve">0.267532229423523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265304058790207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271911680698395</t>
+    <t xml:space="preserve">0.265304118394852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271911710500717</t>
   </si>
   <si>
     <t xml:space="preserve">0.272526383399963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283282995223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279902338981628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277059555053711</t>
+    <t xml:space="preserve">0.283283025026321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279902309179306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277059525251389</t>
   </si>
   <si>
     <t xml:space="preserve">0.27844250202179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280517041683197</t>
+    <t xml:space="preserve">0.280517011880875</t>
   </si>
   <si>
     <t xml:space="preserve">0.278749823570251</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">0.278980314731598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278212040662766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284051328897476</t>
+    <t xml:space="preserve">0.278212010860443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284051299095154</t>
   </si>
   <si>
     <t xml:space="preserve">0.290812611579895</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">0.290428400039673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294807910919189</t>
+    <t xml:space="preserve">0.294807940721512</t>
   </si>
   <si>
     <t xml:space="preserve">0.295422583818436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288507580757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284589141607285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291043132543564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293885916471481</t>
+    <t xml:space="preserve">0.288507610559464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284589111804962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291043102741241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293885886669159</t>
   </si>
   <si>
     <t xml:space="preserve">0.294884771108627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289890587329865</t>
+    <t xml:space="preserve">0.289890617132187</t>
   </si>
   <si>
     <t xml:space="preserve">0.286125808954239</t>
@@ -695,10 +695,10 @@
     <t xml:space="preserve">0.284358620643616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282745182514191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277290046215057</t>
+    <t xml:space="preserve">0.282745152711868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277290016412735</t>
   </si>
   <si>
     <t xml:space="preserve">0.281976819038391</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">0.273602038621902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269760370254517</t>
+    <t xml:space="preserve">0.269760400056839</t>
   </si>
   <si>
     <t xml:space="preserve">0.275061875581741</t>
@@ -719,37 +719,37 @@
     <t xml:space="preserve">0.271834880113602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273371577262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275215536355972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276905864477158</t>
+    <t xml:space="preserve">0.273371547460556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27521550655365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276905834674835</t>
   </si>
   <si>
     <t xml:space="preserve">0.274831354618073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282668322324753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280440181493759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279595047235489</t>
+    <t xml:space="preserve">0.282668352127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280440211296082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279595017433167</t>
   </si>
   <si>
     <t xml:space="preserve">0.27736684679985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278135120868683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281208485364914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278672993183136</t>
+    <t xml:space="preserve">0.278135180473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281208515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278672963380814</t>
   </si>
   <si>
     <t xml:space="preserve">0.28259152173996</t>
@@ -758,31 +758,31 @@
     <t xml:space="preserve">0.279364496469498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285587966442108</t>
+    <t xml:space="preserve">0.285587936639786</t>
   </si>
   <si>
     <t xml:space="preserve">0.279671788215637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28666365146637</t>
+    <t xml:space="preserve">0.286663621664047</t>
   </si>
   <si>
     <t xml:space="preserve">0.284435480833054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281899988651276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283897668123245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285280644893646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285434305667877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295038431882858</t>
+    <t xml:space="preserve">0.281900018453598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283897638320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285280615091324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285434275865555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295038402080536</t>
   </si>
   <si>
     <t xml:space="preserve">0.304258346557617</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">0.32561793923378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331841379404068</t>
+    <t xml:space="preserve">0.33184140920639</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387448072433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316935837268829</t>
+    <t xml:space="preserve">0.316935807466507</t>
   </si>
   <si>
     <t xml:space="preserve">0.309790343046188</t>
@@ -809,76 +809,76 @@
     <t xml:space="preserve">0.309252500534058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311096549034119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313094139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313017338514328</t>
+    <t xml:space="preserve">0.311096519231796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313094168901443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313017308712006</t>
   </si>
   <si>
     <t xml:space="preserve">0.288891762495041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293040722608566</t>
+    <t xml:space="preserve">0.293040782213211</t>
   </si>
   <si>
     <t xml:space="preserve">0.295192092657089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296805560588837</t>
+    <t xml:space="preserve">0.296805590391159</t>
   </si>
   <si>
     <t xml:space="preserve">0.297266602516174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298111766576767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310251295566559</t>
+    <t xml:space="preserve">0.298111736774445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310251325368881</t>
   </si>
   <si>
     <t xml:space="preserve">0.313555151224136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300800859928131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308868318796158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299725204706192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321853131055832</t>
+    <t xml:space="preserve">0.300800889730453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30886834859848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29972517490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32185310125351</t>
   </si>
   <si>
     <t xml:space="preserve">0.327308267354965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318472474813461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31209534406662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314016133546829</t>
+    <t xml:space="preserve">0.318472445011139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312095314264297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314016163349152</t>
   </si>
   <si>
     <t xml:space="preserve">0.315014958381653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312249004840851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313939332962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309636652469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307408511638641</t>
+    <t xml:space="preserve">0.312248975038528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313939273357391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309636682271957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307408541440964</t>
   </si>
   <si>
     <t xml:space="preserve">0.308945178985596</t>
@@ -893,25 +893,25 @@
     <t xml:space="preserve">0.307715862989426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309022039175034</t>
+    <t xml:space="preserve">0.309022009372711</t>
   </si>
   <si>
     <t xml:space="preserve">0.309944003820419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317780941724777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31655165553093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316474825143814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324388563632965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325003266334534</t>
+    <t xml:space="preserve">0.3177809715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316551625728607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316474795341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324388593435287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325003296136856</t>
   </si>
   <si>
     <t xml:space="preserve">0.318318784236908</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">0.323697090148926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333454817533493</t>
+    <t xml:space="preserve">0.333454877138138</t>
   </si>
   <si>
     <t xml:space="preserve">0.327385038137436</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">0.331764578819275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33952471613884</t>
+    <t xml:space="preserve">0.339524686336517</t>
   </si>
   <si>
     <t xml:space="preserve">0.34567129611969</t>
@@ -950,31 +950,31 @@
     <t xml:space="preserve">0.340446680784225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333378076553345</t>
+    <t xml:space="preserve">0.333378046751022</t>
   </si>
   <si>
     <t xml:space="preserve">0.33499151468277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336144000291824</t>
+    <t xml:space="preserve">0.336144030094147</t>
   </si>
   <si>
     <t xml:space="preserve">0.337757527828217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338910013437271</t>
+    <t xml:space="preserve">0.338910043239594</t>
   </si>
   <si>
     <t xml:space="preserve">0.338141709566116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339678317308426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350358158349991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34659332036972</t>
+    <t xml:space="preserve">0.339678347110748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350358128547668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346593260765076</t>
   </si>
   <si>
     <t xml:space="preserve">0.344211488962173</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">0.346900671720505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346132338047028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339601516723633</t>
+    <t xml:space="preserve">0.346132308244705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33960148692131</t>
   </si>
   <si>
     <t xml:space="preserve">0.340907663106918</t>
@@ -1004,61 +1004,61 @@
     <t xml:space="preserve">0.352663099765778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369950532913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365417391061783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363035529851913</t>
+    <t xml:space="preserve">0.369950473308563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36541736125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363035559654236</t>
   </si>
   <si>
     <t xml:space="preserve">0.374099493026733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371103048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369566321372986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368798017501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366108864545822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363112419843674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3686443567276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366877168416977</t>
+    <t xml:space="preserve">0.371103018522263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369566351175308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368797987699509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366108894348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363112390041351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368644326925278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366877198219299</t>
   </si>
   <si>
     <t xml:space="preserve">0.366262555122375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361114740371704</t>
+    <t xml:space="preserve">0.361114770174026</t>
   </si>
   <si>
     <t xml:space="preserve">0.359885394573212</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359193921089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368567526340485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372025012969971</t>
+    <t xml:space="preserve">0.35919389128685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368567496538162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372024983167648</t>
   </si>
   <si>
     <t xml:space="preserve">0.375559329986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380246102809906</t>
+    <t xml:space="preserve">0.380246162414551</t>
   </si>
   <si>
     <t xml:space="preserve">0.392616212368011</t>
@@ -1067,58 +1067,58 @@
     <t xml:space="preserve">0.405677855014801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42104434967041</t>
+    <t xml:space="preserve">0.421044379472733</t>
   </si>
   <si>
     <t xml:space="preserve">0.419507741928101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396842032670975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413361102342606</t>
+    <t xml:space="preserve">0.396842062473297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41336116194725</t>
   </si>
   <si>
     <t xml:space="preserve">0.422581076622009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417586892843246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426422744989395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423349410295486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427959322929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436795175075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432953536510468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452930063009262</t>
+    <t xml:space="preserve">0.417586922645569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426422774791718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423349380493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42795929312706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436795145273209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432953506708145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452930003404617</t>
   </si>
   <si>
     <t xml:space="preserve">0.459460854530334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465223282575607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296647071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481358289718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522463858127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515164792537689</t>
+    <t xml:space="preserve">0.465223342180252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296676874161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481358259916306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522463798522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5151646733284</t>
   </si>
   <si>
     <t xml:space="preserve">0.505560636520386</t>
@@ -1133,10 +1133,10 @@
     <t xml:space="preserve">0.503255605697632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48980987071991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480205774307251</t>
+    <t xml:space="preserve">0.489809811115265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480205804109573</t>
   </si>
   <si>
     <t xml:space="preserve">0.519006371498108</t>
@@ -1145,31 +1145,31 @@
     <t xml:space="preserve">0.511323094367981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499413967132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491730660200119</t>
+    <t xml:space="preserve">0.499414026737213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491730600595474</t>
   </si>
   <si>
     <t xml:space="preserve">0.484431564807892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483663231134415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484815746545792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49518820643425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490193992853165</t>
+    <t xml:space="preserve">0.483663201332092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484815716743469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495188176631927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490194022655487</t>
   </si>
   <si>
     <t xml:space="preserve">0.553197026252747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542056262493134</t>
+    <t xml:space="preserve">0.542056202888489</t>
   </si>
   <si>
     <t xml:space="preserve">0.56280118227005</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">0.586235225200653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600065052509308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582393527030945</t>
+    <t xml:space="preserve">0.600065171718597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58239358663559</t>
   </si>
   <si>
     <t xml:space="preserve">0.572021067142487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572789371013641</t>
+    <t xml:space="preserve">0.572789430618286</t>
   </si>
   <si>
     <t xml:space="preserve">0.552428662776947</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">0.565874457359314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577015161514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596607685089111</t>
+    <t xml:space="preserve">0.577015221118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596607625484467</t>
   </si>
   <si>
     <t xml:space="preserve">0.584698557853699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608132481575012</t>
+    <t xml:space="preserve">0.608132421970367</t>
   </si>
   <si>
     <t xml:space="preserve">0.621962487697601</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">0.629645764827728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614279270172119</t>
+    <t xml:space="preserve">0.614279210567474</t>
   </si>
   <si>
     <t xml:space="preserve">0.60774838924408</t>
@@ -1232,34 +1232,34 @@
     <t xml:space="preserve">0.58162522315979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560880362987518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598528444766998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598144352436066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619657576084137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618120789527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601601719856262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586619257926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59545511007309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587771832942963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584314405918121</t>
+    <t xml:space="preserve">0.560880422592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598528385162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598144233226776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619657516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618120908737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601601779460907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586619317531586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595455229282379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587771773338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584314346313477</t>
   </si>
   <si>
     <t xml:space="preserve">0.577399373054504</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">0.567026972770691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574326038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543592929840088</t>
+    <t xml:space="preserve">0.57432609796524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543592870235443</t>
   </si>
   <si>
     <t xml:space="preserve">0.564722001552582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.563185214996338</t>
+    <t xml:space="preserve">0.563185334205627</t>
   </si>
   <si>
     <t xml:space="preserve">0.576246917247772</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">0.587003529071808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604674994945526</t>
+    <t xml:space="preserve">0.604675054550171</t>
   </si>
   <si>
     <t xml:space="preserve">0.629261612892151</t>
@@ -1307,16 +1307,16 @@
     <t xml:space="preserve">0.603138446807861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612358331680298</t>
+    <t xml:space="preserve">0.612358391284943</t>
   </si>
   <si>
     <t xml:space="preserve">0.611590027809143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.59391850233078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596991837024689</t>
+    <t xml:space="preserve">0.593918442726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596991777420044</t>
   </si>
   <si>
     <t xml:space="preserve">0.608516693115234</t>
@@ -1328,10 +1328,10 @@
     <t xml:space="preserve">0.589308559894562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553965330123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538598716259003</t>
+    <t xml:space="preserve">0.553965389728546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538598775863647</t>
   </si>
   <si>
     <t xml:space="preserve">0.55703866481781</t>
@@ -1343,19 +1343,19 @@
     <t xml:space="preserve">0.524000525474548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537830531597137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547818779945374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53245210647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537062168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527073860168457</t>
+    <t xml:space="preserve">0.537830471992493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547818720340729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532452166080475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537062108516693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527073800563812</t>
   </si>
   <si>
     <t xml:space="preserve">0.52092719078064</t>
@@ -1364,25 +1364,25 @@
     <t xml:space="preserve">0.517853915691376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525537252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530147194862366</t>
+    <t xml:space="preserve">0.525537192821503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53014725446701</t>
   </si>
   <si>
     <t xml:space="preserve">0.523232221603394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519390523433685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524768948554993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549355387687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501718997955322</t>
+    <t xml:space="preserve">0.51939058303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524768829345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549355328083038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501719057559967</t>
   </si>
   <si>
     <t xml:space="preserve">0.492499023675919</t>
@@ -1394,16 +1394,16 @@
     <t xml:space="preserve">0.476364135742188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488657385110855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471754193305969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472522467374802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468680858612061</t>
+    <t xml:space="preserve">0.488657355308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471754163503647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472522437572479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468680888414383</t>
   </si>
   <si>
     <t xml:space="preserve">0.487120658159256</t>
@@ -1415,52 +1415,52 @@
     <t xml:space="preserve">0.480974107980728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483279079198837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478669136762619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470217525959015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467912524938583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466375857591629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839190244675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461765855550766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4878890812397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500182330608368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469449132680893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437179356813431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444862574338913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431800961494446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444094270467758</t>
+    <t xml:space="preserve">0.48327910900116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478669166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470217436552048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467912495136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466375827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839220046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461765915155411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487889021635056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500182271003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469449102878571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437179327011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444862544536591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431801021099091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444094300270081</t>
   </si>
   <si>
     <t xml:space="preserve">0.424117714166641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415666133165359</t>
+    <t xml:space="preserve">0.415666103363037</t>
   </si>
   <si>
     <t xml:space="preserve">0.382627964019775</t>
@@ -1469,28 +1469,28 @@
     <t xml:space="preserve">0.379170477390289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382243812084198</t>
+    <t xml:space="preserve">0.382243782281876</t>
   </si>
   <si>
     <t xml:space="preserve">0.385701268911362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388774544000626</t>
+    <t xml:space="preserve">0.388774573802948</t>
   </si>
   <si>
     <t xml:space="preserve">0.391847908496857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384164601564407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376481294631958</t>
+    <t xml:space="preserve">0.384164571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37648132443428</t>
   </si>
   <si>
     <t xml:space="preserve">0.367261350154877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364956349134445</t>
+    <t xml:space="preserve">0.364956378936768</t>
   </si>
   <si>
     <t xml:space="preserve">0.360346406698227</t>
@@ -1499,31 +1499,31 @@
     <t xml:space="preserve">0.3522789478302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356504768133163</t>
+    <t xml:space="preserve">0.356504738330841</t>
   </si>
   <si>
     <t xml:space="preserve">0.37148717045784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368029713630676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37225553393364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365340501070023</t>
+    <t xml:space="preserve">0.368029683828354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372255504131317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365340560674667</t>
   </si>
   <si>
     <t xml:space="preserve">0.374944657087326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3664930164814</t>
+    <t xml:space="preserve">0.366493046283722</t>
   </si>
   <si>
     <t xml:space="preserve">0.374560505151749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374176323413849</t>
+    <t xml:space="preserve">0.374176353216171</t>
   </si>
   <si>
     <t xml:space="preserve">0.37878629565239</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">0.362267225980759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353815615177155</t>
+    <t xml:space="preserve">0.353815585374832</t>
   </si>
   <si>
     <t xml:space="preserve">0.354583919048309</t>
@@ -1541,19 +1541,19 @@
     <t xml:space="preserve">0.353047311306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370718866586685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354199767112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395689487457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411056160926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407982796430588</t>
+    <t xml:space="preserve">0.370718836784363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35419973731041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39568954706192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411056131124496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40798282623291</t>
   </si>
   <si>
     <t xml:space="preserve">0.384932935237885</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">0.344979822635651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343059003353119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354968130588531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36418804526329</t>
+    <t xml:space="preserve">0.343058973550797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354968100786209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364188075065613</t>
   </si>
   <si>
     <t xml:space="preserve">0.357273072004318</t>
@@ -1598,28 +1598,28 @@
     <t xml:space="preserve">0.349974006414413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339217364788055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323850750923157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361883074045181</t>
+    <t xml:space="preserve">0.339217394590378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323850780725479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361883044242859</t>
   </si>
   <si>
     <t xml:space="preserve">0.350742280483246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389542907476425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404141217470169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396457821130753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412592798471451</t>
+    <t xml:space="preserve">0.389542937278748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404141187667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396457850933075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412592768669128</t>
   </si>
   <si>
     <t xml:space="preserve">0.404909521341324</t>
@@ -1628,16 +1628,16 @@
     <t xml:space="preserve">0.401836186647415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394152879714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399531185626984</t>
+    <t xml:space="preserve">0.394152909517288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399531155824661</t>
   </si>
   <si>
     <t xml:space="preserve">0.40260449051857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401067852973938</t>
+    <t xml:space="preserve">0.40106788277626</t>
   </si>
   <si>
     <t xml:space="preserve">0.397994548082352</t>
@@ -1652,37 +1652,37 @@
     <t xml:space="preserve">0.345748126506805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336528211832047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335759848356247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337296545505524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329613238573074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32807657122612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331533998250961</t>
+    <t xml:space="preserve">0.336528241634369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335759878158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337296515703201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329613208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328076541423798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331534028053284</t>
   </si>
   <si>
     <t xml:space="preserve">0.319240808486938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326924085617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312709987163544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341138154268265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322698265314102</t>
+    <t xml:space="preserve">0.326924055814743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312709957361221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341138184070587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322698295116425</t>
   </si>
   <si>
     <t xml:space="preserve">0.326155751943588</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">0.324619084596634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325771629810333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330381542444229</t>
+    <t xml:space="preserve">0.325771570205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330381572246552</t>
   </si>
   <si>
     <t xml:space="preserve">0.329997390508652</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">0.324234932661057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313862502574921</t>
+    <t xml:space="preserve">0.313862472772598</t>
   </si>
   <si>
     <t xml:space="preserve">0.301185041666031</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">0.30387419462204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29695925116539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302721679210663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082476854324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308100044727325</t>
+    <t xml:space="preserve">0.296959221363068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302721709012985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32308241724968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308100014925003</t>
   </si>
   <si>
     <t xml:space="preserve">0.310405015945435</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">0.305410861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30848416686058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304642528295517</t>
+    <t xml:space="preserve">0.308484196662903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304642498493195</t>
   </si>
   <si>
     <t xml:space="preserve">0.32077744603157</t>
@@ -1748,46 +1748,46 @@
     <t xml:space="preserve">0.356888920068741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358041375875473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356120586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360730558633804</t>
+    <t xml:space="preserve">0.358041405677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356120556592941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360730588436127</t>
   </si>
   <si>
     <t xml:space="preserve">0.358809769153595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351126462221146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355736434459686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342290610074997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371871322393417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370334684848785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383780479431152</t>
+    <t xml:space="preserve">0.351126432418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355736404657364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342290639877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37187135219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370334655046463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383780419826508</t>
   </si>
   <si>
     <t xml:space="preserve">0.376097142696381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37686550617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377249628305435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398762851953506</t>
+    <t xml:space="preserve">0.376865476369858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377249658107758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398762881755829</t>
   </si>
   <si>
     <t xml:space="preserve">0.403372824192047</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">0.39107957482338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381475478410721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407214462757111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387237906455994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394921243190765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411824494600296</t>
+    <t xml:space="preserve">0.381475448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407214492559433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387237936258316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394921213388443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411824464797974</t>
   </si>
   <si>
     <t xml:space="preserve">0.41489776968956</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">0.417202711105347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397226214408875</t>
+    <t xml:space="preserve">0.397226184606552</t>
   </si>
   <si>
     <t xml:space="preserve">0.408751159906387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410287797451019</t>
+    <t xml:space="preserve">0.410287767648697</t>
   </si>
   <si>
     <t xml:space="preserve">0.41412940621376</t>
@@ -1838,73 +1838,73 @@
     <t xml:space="preserve">0.416434437036514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418739408254623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420276075601578</t>
+    <t xml:space="preserve">0.418739467859268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4202761054039</t>
   </si>
   <si>
     <t xml:space="preserve">0.421812772750854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430264383554459</t>
+    <t xml:space="preserve">0.430264353752136</t>
   </si>
   <si>
     <t xml:space="preserve">0.473290801048279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494803965091705</t>
+    <t xml:space="preserve">0.49480402469635</t>
   </si>
   <si>
     <t xml:space="preserve">0.484047412872314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493267357349396</t>
+    <t xml:space="preserve">0.493267387151718</t>
   </si>
   <si>
     <t xml:space="preserve">0.506328999996185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479437440633774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48251074552536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595861673355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070826768875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465607523918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460997551679611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453314214944839</t>
+    <t xml:space="preserve">0.479437410831451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482510805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595831871033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070856571198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465607464313507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460997521877289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453314185142517</t>
   </si>
   <si>
     <t xml:space="preserve">0.434106051921844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441789269447327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44563090801239</t>
+    <t xml:space="preserve">0.441789239645004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445630937814713</t>
   </si>
   <si>
     <t xml:space="preserve">0.449472546577454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451009273529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460229188203812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454082608222961</t>
+    <t xml:space="preserve">0.45100924372673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460229218006134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454082578420639</t>
   </si>
   <si>
     <t xml:space="preserve">0.457155913114548</t>
@@ -1919,22 +1919,22 @@
     <t xml:space="preserve">0.463302493095398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470985800027847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467144161462784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457924276590347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447167634963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432569354772568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437947630882263</t>
+    <t xml:space="preserve">0.470985859632492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467144101858139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457924246788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447167605161667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43256938457489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437947660684586</t>
   </si>
   <si>
     <t xml:space="preserve">0.433337718248367</t>
@@ -1943,19 +1943,19 @@
     <t xml:space="preserve">0.434874296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436411052942276</t>
+    <t xml:space="preserve">0.436410993337631</t>
   </si>
   <si>
     <t xml:space="preserve">0.43948432803154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441020965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440252691507339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43871596455574</t>
+    <t xml:space="preserve">0.441020995378494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440252661705017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438715904951096</t>
   </si>
   <si>
     <t xml:space="preserve">0.442557603120804</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">0.455619186162949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443325966596603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429496049880981</t>
+    <t xml:space="preserve">0.443325996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429496079683304</t>
   </si>
   <si>
     <t xml:space="preserve">0.435642659664154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450240910053253</t>
+    <t xml:space="preserve">0.450240969657898</t>
   </si>
   <si>
     <t xml:space="preserve">0.427191078662872</t>
@@ -1994,34 +1994,34 @@
     <t xml:space="preserve">0.365724712610245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372639715671539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351510643959045</t>
+    <t xml:space="preserve">0.372639656066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351510614156723</t>
   </si>
   <si>
     <t xml:space="preserve">0.342674821615219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317319959402084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265073597431183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259695261716843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23933456838131</t>
+    <t xml:space="preserve">0.317319989204407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265073627233505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259695291519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.239334583282471</t>
   </si>
   <si>
     <t xml:space="preserve">0.242023706436157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234724566340446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24586533010006</t>
+    <t xml:space="preserve">0.234724551439285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245865300297737</t>
   </si>
   <si>
     <t xml:space="preserve">0.258926957845688</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">0.266610234975815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269299358129501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258158624172211</t>
+    <t xml:space="preserve">0.269299387931824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258158594369888</t>
   </si>
   <si>
     <t xml:space="preserve">0.251243650913239</t>
@@ -2045,46 +2045,46 @@
     <t xml:space="preserve">0.252011984586716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242407873272896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245096996426582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254701107740402</t>
+    <t xml:space="preserve">0.242407858371735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245097011327744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254701137542725</t>
   </si>
   <si>
     <t xml:space="preserve">0.262000262737274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.254316955804825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261231929063797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262768626213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264689445495605</t>
+    <t xml:space="preserve">0.254316985607147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261231899261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262768596410751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264689415693283</t>
   </si>
   <si>
     <t xml:space="preserve">0.271988540887833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273909389972687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276982665061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272756814956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275445997714996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268915265798569</t>
+    <t xml:space="preserve">0.273909360170364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276982694864273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272756844758987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275446027517319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268915235996246</t>
   </si>
   <si>
     <t xml:space="preserve">0.265841871500015</t>
@@ -2093,64 +2093,64 @@
     <t xml:space="preserve">0.258542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26545774936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263152748346329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292733460664749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327692449092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302337497472763</t>
+    <t xml:space="preserve">0.265457719564438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263152718544006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292733430862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32769238948822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302337527275085</t>
   </si>
   <si>
     <t xml:space="preserve">0.301953375339508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332302361726761</t>
+    <t xml:space="preserve">0.332302391529083</t>
   </si>
   <si>
     <t xml:space="preserve">0.332686543464661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306179165840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305026739835739</t>
+    <t xml:space="preserve">0.306179195642471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305026710033417</t>
   </si>
   <si>
     <t xml:space="preserve">0.312325805425644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331918239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315399140119553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326539933681488</t>
+    <t xml:space="preserve">0.331918209791183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31539911031723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326539874076843</t>
   </si>
   <si>
     <t xml:space="preserve">0.292349278926849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289275974035263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291196763515472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286970973014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285050123929977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273525208234787</t>
+    <t xml:space="preserve">0.289275944232941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291196793317795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286970943212509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285050094127655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273525178432465</t>
   </si>
   <si>
     <t xml:space="preserve">0.26084777712822</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">0.278519332408905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273141026496887</t>
+    <t xml:space="preserve">0.27314105629921</t>
   </si>
   <si>
     <t xml:space="preserve">0.266994416713715</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">0.256237804889679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249322831630707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236261233687401</t>
+    <t xml:space="preserve">0.249322816729546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23626121878624</t>
   </si>
   <si>
     <t xml:space="preserve">0.238182067871094</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">0.338449001312256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34075403213501</t>
+    <t xml:space="preserve">0.340754002332687</t>
   </si>
   <si>
     <t xml:space="preserve">0.338833212852478</t>
@@ -2228,46 +2228,46 @@
     <t xml:space="preserve">0.336912333965302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333839029073715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330765694379807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328844904899597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339985698461533</t>
+    <t xml:space="preserve">0.333839058876038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330765724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328844875097275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33998566865921</t>
   </si>
   <si>
     <t xml:space="preserve">0.34766897559166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359962224960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3518947660923</t>
+    <t xml:space="preserve">0.35996225476265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351894825696945</t>
   </si>
   <si>
     <t xml:space="preserve">0.369182199239731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357657223939896</t>
+    <t xml:space="preserve">0.357657253742218</t>
   </si>
   <si>
     <t xml:space="preserve">0.355352282524109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348053157329559</t>
+    <t xml:space="preserve">0.348053127527237</t>
   </si>
   <si>
     <t xml:space="preserve">0.346516489982605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347284764051437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363419681787491</t>
+    <t xml:space="preserve">0.34728479385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363419711589813</t>
   </si>
   <si>
     <t xml:space="preserve">0.373792141675949</t>
@@ -2279,16 +2279,16 @@
     <t xml:space="preserve">0.379554659128189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425654381513596</t>
+    <t xml:space="preserve">0.425654351711273</t>
   </si>
   <si>
     <t xml:space="preserve">0.417971104383469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381859630346298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383012145757675</t>
+    <t xml:space="preserve">0.381859600543976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38301208615303</t>
   </si>
   <si>
     <t xml:space="preserve">0.377633810043335</t>
@@ -2297,10 +2297,10 @@
     <t xml:space="preserve">0.378402143716812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381091296672821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380322962999344</t>
+    <t xml:space="preserve">0.381091266870499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380322992801666</t>
   </si>
   <si>
     <t xml:space="preserve">0.348437309265137</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">0.400299549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38339626789093</t>
+    <t xml:space="preserve">0.383396297693253</t>
   </si>
   <si>
     <t xml:space="preserve">0.379938811063766</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">0.368413835763931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344595640897751</t>
+    <t xml:space="preserve">0.344595670700073</t>
   </si>
   <si>
     <t xml:space="preserve">0.334223210811615</t>
@@ -2333,28 +2333,28 @@
     <t xml:space="preserve">0.34190645813942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323466598987579</t>
+    <t xml:space="preserve">0.323466569185257</t>
   </si>
   <si>
     <t xml:space="preserve">0.340369820594788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331149876117706</t>
+    <t xml:space="preserve">0.331149905920029</t>
   </si>
   <si>
     <t xml:space="preserve">0.348821461200714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322314113378525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285818487405777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337680697441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345363974571228</t>
+    <t xml:space="preserve">0.322314143180847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285818457603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337680727243423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345363944768906</t>
   </si>
   <si>
     <t xml:space="preserve">0.341522336006165</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">0.353653132915497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351594597101212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354064851999283</t>
+    <t xml:space="preserve">0.351594626903534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35406482219696</t>
   </si>
   <si>
     <t xml:space="preserve">0.352829724550247</t>
@@ -2381,22 +2381,22 @@
     <t xml:space="preserve">0.345830768346786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341713726520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342537194490433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348301023244858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359828650951385</t>
+    <t xml:space="preserve">0.341713696718216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34253716468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348300993442535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359828680753708</t>
   </si>
   <si>
     <t xml:space="preserve">0.353241413831711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354888260364532</t>
+    <t xml:space="preserve">0.35488823056221</t>
   </si>
   <si>
     <t xml:space="preserve">0.350359499454498</t>
@@ -2405,16 +2405,16 @@
     <t xml:space="preserve">0.345007359981537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339655190706253</t>
+    <t xml:space="preserve">0.339655220508575</t>
   </si>
   <si>
     <t xml:space="preserve">0.342948853969574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341302007436752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333479702472687</t>
+    <t xml:space="preserve">0.341302037239075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333479672670364</t>
   </si>
   <si>
     <t xml:space="preserve">0.320716857910156</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">0.319070041179657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321540296077728</t>
+    <t xml:space="preserve">0.321540266275406</t>
   </si>
   <si>
     <t xml:space="preserve">0.310835957527161</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">0.314129620790482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312894493341446</t>
+    <t xml:space="preserve">0.312894523143768</t>
   </si>
   <si>
     <t xml:space="preserve">0.31824666261673</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">0.317834943532944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319481730461121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312071114778519</t>
+    <t xml:space="preserve">0.319481790065765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312071084976196</t>
   </si>
   <si>
     <t xml:space="preserve">0.308365762233734</t>
@@ -2456,40 +2456,40 @@
     <t xml:space="preserve">0.310012608766556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314541280269623</t>
+    <t xml:space="preserve">0.314541310071945</t>
   </si>
   <si>
     <t xml:space="preserve">0.318658322095871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32030513882637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322775363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309600859880447</t>
+    <t xml:space="preserve">0.320305168628693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322775393724442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30960088968277</t>
   </si>
   <si>
     <t xml:space="preserve">0.309189170598984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32112854719162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321951985359192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32689243555069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323187083005905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323598772287369</t>
+    <t xml:space="preserve">0.321128576993942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32195195555687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325245589017868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326892405748367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323187112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323598802089691</t>
   </si>
   <si>
     <t xml:space="preserve">0.315364688634872</t>
@@ -2501,46 +2501,46 @@
     <t xml:space="preserve">0.310424268245697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314952999353409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311247646808624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317011505365372</t>
+    <t xml:space="preserve">0.314953029155731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311247676610947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317011535167694</t>
   </si>
   <si>
     <t xml:space="preserve">0.31742325425148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311659395694733</t>
+    <t xml:space="preserve">0.311659425497055</t>
   </si>
   <si>
     <t xml:space="preserve">0.316188126802444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319893449544907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30466040968895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308777451515198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30301359295845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307542353868484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302601903676987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307954043149948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306307256221771</t>
+    <t xml:space="preserve">0.319893479347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304660439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30877748131752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303013622760773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307542324066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302601933479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307954072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306307286024094</t>
   </si>
   <si>
     <t xml:space="preserve">0.301778525114059</t>
@@ -2549,31 +2549,31 @@
     <t xml:space="preserve">0.3038370013237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300955146551132</t>
+    <t xml:space="preserve">0.30095511674881</t>
   </si>
   <si>
     <t xml:space="preserve">0.301366806030273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302190244197845</t>
+    <t xml:space="preserve">0.302190214395523</t>
   </si>
   <si>
     <t xml:space="preserve">0.313717901706696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326480716466904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328539222478867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340890318155289</t>
+    <t xml:space="preserve">0.326480746269226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328539192676544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340890347957611</t>
   </si>
   <si>
     <t xml:space="preserve">0.356535047292709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34336057305336</t>
+    <t xml:space="preserve">0.343360543251038</t>
   </si>
   <si>
     <t xml:space="preserve">0.336361587047577</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">0.339243501424789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335126459598541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358181893825531</t>
+    <t xml:space="preserve">0.335126489400864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358181834220886</t>
   </si>
   <si>
     <t xml:space="preserve">0.347065836191177</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">0.344183951616287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336773335933685</t>
+    <t xml:space="preserve">0.336773276329041</t>
   </si>
   <si>
     <t xml:space="preserve">0.345419049263</t>
@@ -2603,19 +2603,19 @@
     <t xml:space="preserve">0.349124401807785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338008403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335949897766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343772262334824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337596744298935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340066909790039</t>
+    <t xml:space="preserve">0.338008433580399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335949867963791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343772202730179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337596714496613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340066879987717</t>
   </si>
   <si>
     <t xml:space="preserve">0.340478628873825</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">0.325657308101654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338420152664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346654206514359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355711668729782</t>
+    <t xml:space="preserve">0.33842009305954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346654146909714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35571163892746</t>
   </si>
   <si>
     <t xml:space="preserve">0.359005272388458</t>
@@ -2645,25 +2645,25 @@
     <t xml:space="preserve">0.370121240615845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377943605184555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381648927927017</t>
+    <t xml:space="preserve">0.377943634986877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38164895772934</t>
   </si>
   <si>
     <t xml:space="preserve">0.3902947306633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395235180854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399763911962509</t>
+    <t xml:space="preserve">0.395235151052475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399763882160187</t>
   </si>
   <si>
     <t xml:space="preserve">0.389471292495728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40182238817215</t>
+    <t xml:space="preserve">0.401822447776794</t>
   </si>
   <si>
     <t xml:space="preserve">0.411703288555145</t>
@@ -2672,43 +2672,43 @@
     <t xml:space="preserve">0.402234107255936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403469264507294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409644812345505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408409625291824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405939429998398</t>
+    <t xml:space="preserve">0.403469234704971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409644782543182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408409655094147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40593945980072</t>
   </si>
   <si>
     <t xml:space="preserve">0.406351149082184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400175601243973</t>
+    <t xml:space="preserve">0.40017557144165</t>
   </si>
   <si>
     <t xml:space="preserve">0.397705405950546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403880953788757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403057545423508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394823491573334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417467147111893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433111846446991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430641651153564</t>
+    <t xml:space="preserve">0.403880923986435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403057515621185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394823431968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417467176914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433111876249313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430641680955887</t>
   </si>
   <si>
     <t xml:space="preserve">0.441345930099487</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">0.454520434141159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442992746829987</t>
+    <t xml:space="preserve">0.442992717027664</t>
   </si>
   <si>
     <t xml:space="preserve">0.488280087709427</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">0.518746137619019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522039830684662</t>
+    <t xml:space="preserve">0.522039711475372</t>
   </si>
   <si>
     <t xml:space="preserve">0.500631153583527</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">0.517922759056091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469341784715652</t>
+    <t xml:space="preserve">0.46934175491333</t>
   </si>
   <si>
     <t xml:space="preserve">0.485809862613678</t>
@@ -2750,40 +2750,40 @@
     <t xml:space="preserve">0.462754487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472635418176651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493220537900925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573721170425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481692790985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467695027589798</t>
+    <t xml:space="preserve">0.472635358572006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493220508098602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491573750972748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481692761182785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467694938182831</t>
   </si>
   <si>
     <t xml:space="preserve">0.459460914134979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461107701063156</t>
+    <t xml:space="preserve">0.461107671260834</t>
   </si>
   <si>
     <t xml:space="preserve">0.476752400398254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47922271490097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477575778961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51545250415802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504748225212097</t>
+    <t xml:space="preserve">0.479222655296326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477575838565826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515452444553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504748165607452</t>
   </si>
   <si>
     <t xml:space="preserve">0.501454591751099</t>
@@ -2792,16 +2792,16 @@
     <t xml:space="preserve">0.498984396457672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494043946266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505571722984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490750432014465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484986454248428</t>
+    <t xml:space="preserve">0.494043976068497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505571663379669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490750372409821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484986484050751</t>
   </si>
   <si>
     <t xml:space="preserve">0.492397129535675</t>
@@ -2810,31 +2810,31 @@
     <t xml:space="preserve">0.482516258955002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478399246931076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473458766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470988601446152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470165133476257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46522468328476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284322500229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468518406152725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46675032377243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473822295665741</t>
+    <t xml:space="preserve">0.478399157524109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473458796739578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470988541841507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470165193080902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465224713087082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284292697906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468518376350403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466750353574753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473822325468063</t>
   </si>
   <si>
     <t xml:space="preserve">0.457910388708115</t>
@@ -2843,40 +2843,40 @@
     <t xml:space="preserve">0.46144637465477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464098364114761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454374372959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441114455461502</t>
+    <t xml:space="preserve">0.464098334312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454374402761459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44111442565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.420782536268234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.435810446739197</t>
+    <t xml:space="preserve">0.435810476541519</t>
   </si>
   <si>
     <t xml:space="preserve">0.438462436199188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427412480115891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426528453826904</t>
+    <t xml:space="preserve">0.427412509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426528483629227</t>
   </si>
   <si>
     <t xml:space="preserve">0.433158487081528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448186457157135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441998422145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434484422206879</t>
+    <t xml:space="preserve">0.448186427354813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441998451948166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434484452009201</t>
   </si>
   <si>
     <t xml:space="preserve">0.44465047121048</t>
@@ -2894,16 +2894,16 @@
     <t xml:space="preserve">0.430948466062546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431390464305878</t>
+    <t xml:space="preserve">0.4313904941082</t>
   </si>
   <si>
     <t xml:space="preserve">0.434926480054855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429622501134872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428738474845886</t>
+    <t xml:space="preserve">0.42962247133255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428738504648209</t>
   </si>
   <si>
     <t xml:space="preserve">0.424318462610245</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">0.419456511735916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417246520519257</t>
+    <t xml:space="preserve">0.417246550321579</t>
   </si>
   <si>
     <t xml:space="preserve">0.411942541599274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414152532815933</t>
+    <t xml:space="preserve">0.414152503013611</t>
   </si>
   <si>
     <t xml:space="preserve">0.418130487203598</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">0.425202488899231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423876523971558</t>
+    <t xml:space="preserve">0.423876464366913</t>
   </si>
   <si>
     <t xml:space="preserve">0.414594531059265</t>
@@ -2954,16 +2954,16 @@
     <t xml:space="preserve">0.422992527484894</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421224504709244</t>
+    <t xml:space="preserve">0.421224534511566</t>
   </si>
   <si>
     <t xml:space="preserve">0.413268536329269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415920495986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408406585454941</t>
+    <t xml:space="preserve">0.415920525789261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408406555652618</t>
   </si>
   <si>
     <t xml:space="preserve">0.412384539842606</t>
@@ -2978,16 +2978,16 @@
     <t xml:space="preserve">0.409290552139282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407964527606964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423434495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42034050822258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426086515188217</t>
+    <t xml:space="preserve">0.407964557409286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423434525728226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420340478420258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426086455583572</t>
   </si>
   <si>
     <t xml:space="preserve">0.428296476602554</t>
@@ -3011,40 +3011,40 @@
     <t xml:space="preserve">0.400008589029312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401334583759308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392494589090347</t>
+    <t xml:space="preserve">0.401334553956985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39249461889267</t>
   </si>
   <si>
     <t xml:space="preserve">0.396030604839325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405754536390305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403544545173645</t>
+    <t xml:space="preserve">0.405754566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403544574975967</t>
   </si>
   <si>
     <t xml:space="preserve">0.400450587272644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389842659235001</t>
+    <t xml:space="preserve">0.389842599630356</t>
   </si>
   <si>
     <t xml:space="preserve">0.388958632946014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395146608352661</t>
+    <t xml:space="preserve">0.395146578550339</t>
   </si>
   <si>
     <t xml:space="preserve">0.386748641729355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393378615379333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403102576732635</t>
+    <t xml:space="preserve">0.393378585577011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403102546930313</t>
   </si>
   <si>
     <t xml:space="preserve">0.396914601325989</t>
@@ -3053,25 +3053,25 @@
     <t xml:space="preserve">0.397798597812653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401776552200317</t>
+    <t xml:space="preserve">0.40177658200264</t>
   </si>
   <si>
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660578489304</t>
+    <t xml:space="preserve">0.402660548686981</t>
   </si>
   <si>
     <t xml:space="preserve">0.419898509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436694443225861</t>
+    <t xml:space="preserve">0.436694413423538</t>
   </si>
   <si>
     <t xml:space="preserve">0.443766415119171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453789919614792</t>
+    <t xml:space="preserve">0.453789889812469</t>
   </si>
   <si>
     <t xml:space="preserve">0.452878683805466</t>
@@ -3086,31 +3086,31 @@
     <t xml:space="preserve">0.459257245063782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456523537635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465635806322098</t>
+    <t xml:space="preserve">0.456523567438126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465635776519775</t>
   </si>
   <si>
     <t xml:space="preserve">0.464724570512772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468369483947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480215430259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482949078083038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481126606464386</t>
+    <t xml:space="preserve">0.468369513750076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480215400457382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482949018478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481126666069031</t>
   </si>
   <si>
     <t xml:space="preserve">0.482037842273712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479304194450378</t>
+    <t xml:space="preserve">0.479304224252701</t>
   </si>
   <si>
     <t xml:space="preserve">0.474748075008392</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">0.52577668428421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523954153060913</t>
+    <t xml:space="preserve">0.523954212665558</t>
   </si>
   <si>
     <t xml:space="preserve">0.510285794734955</t>
@@ -3143,28 +3143,28 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753149986267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507552087306976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511197030544281</t>
+    <t xml:space="preserve">0.515753209590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507552146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511197090148926</t>
   </si>
   <si>
     <t xml:space="preserve">0.514841914176941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519398093223572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51393073797226</t>
+    <t xml:space="preserve">0.519398033618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513930678367615</t>
   </si>
   <si>
     <t xml:space="preserve">0.524865388870239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509374618530273</t>
+    <t xml:space="preserve">0.509374558925629</t>
   </si>
   <si>
     <t xml:space="preserve">0.526687920093536</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267395019531</t>
+    <t xml:space="preserve">0.541267454624176</t>
   </si>
   <si>
     <t xml:space="preserve">0.546734869480133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537622570991516</t>
+    <t xml:space="preserve">0.537622511386871</t>
   </si>
   <si>
     <t xml:space="preserve">0.549468457698822</t>
@@ -3191,25 +3191,25 @@
     <t xml:space="preserve">0.554024577140808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564959347248077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569515466690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562225580215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551290988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548557221889496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550379693508148</t>
+    <t xml:space="preserve">0.564959287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569515407085419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565870463848114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562225639820099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551290929317474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548557281494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550379633903503</t>
   </si>
   <si>
     <t xml:space="preserve">0.547646045684814</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">0.55584704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553113400936127</t>
+    <t xml:space="preserve">0.553113341331482</t>
   </si>
   <si>
     <t xml:space="preserve">0.564048111438751</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">0.559491991996765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561314404010773</t>
+    <t xml:space="preserve">0.561314344406128</t>
   </si>
   <si>
     <t xml:space="preserve">0.558580696582794</t>
@@ -3245,10 +3245,10 @@
     <t xml:space="preserve">0.534888863563538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528510272502899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535800158977509</t>
+    <t xml:space="preserve">0.528510332107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535800099372864</t>
   </si>
   <si>
     <t xml:space="preserve">0.530332744121552</t>
@@ -3263,13 +3263,13 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617466211319</t>
+    <t xml:space="preserve">0.496617496013641</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505729675292969</t>
+    <t xml:space="preserve">0.505729734897614</t>
   </si>
   <si>
     <t xml:space="preserve">0.494794994592667</t>
@@ -3278,25 +3278,25 @@
     <t xml:space="preserve">0.499351114034653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497528702020645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492061346769333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488416403532028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483860313892365</t>
+    <t xml:space="preserve">0.497528672218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492061376571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488416433334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483860343694687</t>
   </si>
   <si>
     <t xml:space="preserve">0.487505257129669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495706260204315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493883788585663</t>
+    <t xml:space="preserve">0.495706230401993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49388375878334</t>
   </si>
   <si>
     <t xml:space="preserve">0.491150081157684</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">0.517575621604919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489643454551697</t>
+    <t xml:space="preserve">0.489643424749374</t>
   </si>
   <si>
     <t xml:space="preserve">0.48199275135994</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">0.475776553153992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47673287987709</t>
+    <t xml:space="preserve">0.476732909679413</t>
   </si>
   <si>
     <t xml:space="preserve">0.480080038309097</t>
@@ -3329,31 +3329,31 @@
     <t xml:space="preserve">0.46477872133255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473385751247406</t>
+    <t xml:space="preserve">0.473385721445084</t>
   </si>
   <si>
     <t xml:space="preserve">0.469560384750366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470994919538498</t>
+    <t xml:space="preserve">0.470994889736176</t>
   </si>
   <si>
     <t xml:space="preserve">0.459040701389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453780859708786</t>
+    <t xml:space="preserve">0.453780889511108</t>
   </si>
   <si>
     <t xml:space="preserve">0.451390027999878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447564661502838</t>
+    <t xml:space="preserve">0.447564691305161</t>
   </si>
   <si>
     <t xml:space="preserve">0.45091187953949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441826701164246</t>
+    <t xml:space="preserve">0.441826671361923</t>
   </si>
   <si>
     <t xml:space="preserve">0.438479512929916</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">0.432741492986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436088651418686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438001364469528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441348493099213</t>
+    <t xml:space="preserve">0.436088681221008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438001334667206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441348522901535</t>
   </si>
   <si>
     <t xml:space="preserve">0.446608364582062</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">0.436566829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438957691192627</t>
+    <t xml:space="preserve">0.438957661390305</t>
   </si>
   <si>
     <t xml:space="preserve">0.444695681333542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439435839653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4336978495121</t>
+    <t xml:space="preserve">0.439435869455338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433697819709778</t>
   </si>
   <si>
     <t xml:space="preserve">0.434654176235199</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">0.46669140458107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454737216234207</t>
+    <t xml:space="preserve">0.454737186431885</t>
   </si>
   <si>
     <t xml:space="preserve">0.455693542957306</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">0.561368525028229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538416504859924</t>
+    <t xml:space="preserve">0.538416564464569</t>
   </si>
   <si>
     <t xml:space="preserve">0.544154524803162</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">0.540329158306122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525984168052673</t>
+    <t xml:space="preserve">0.525984108448029</t>
   </si>
   <si>
     <t xml:space="preserve">0.517377138137817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525027811527252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521202445030212</t>
+    <t xml:space="preserve">0.525027871131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521202504634857</t>
   </si>
   <si>
     <t xml:space="preserve">0.519289791584015</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">0.531722128391266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518333494663239</t>
+    <t xml:space="preserve">0.518333435058594</t>
   </si>
   <si>
     <t xml:space="preserve">0.514508128166199</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">0.527896821498871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526940524578094</t>
+    <t xml:space="preserve">0.52694046497345</t>
   </si>
   <si>
     <t xml:space="preserve">0.535547494888306</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">0.553717851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568062901496887</t>
+    <t xml:space="preserve">0.568062841892242</t>
   </si>
   <si>
     <t xml:space="preserve">0.55849951505661</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">0.555630505084991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55467414855957</t>
+    <t xml:space="preserve">0.554674208164215</t>
   </si>
   <si>
     <t xml:space="preserve">0.557543218135834</t>
@@ -3491,16 +3491,16 @@
     <t xml:space="preserve">0.54702353477478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537460088729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551805257797241</t>
+    <t xml:space="preserve">0.537460148334503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551805198192596</t>
   </si>
   <si>
     <t xml:space="preserve">0.524071455001831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533634841442108</t>
+    <t xml:space="preserve">0.533634901046753</t>
   </si>
   <si>
     <t xml:space="preserve">0.536503851413727</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">0.522158801555634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529809474945068</t>
+    <t xml:space="preserve">0.529809534549713</t>
   </si>
   <si>
     <t xml:space="preserve">0.532678484916687</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">0.499206781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496337741613388</t>
+    <t xml:space="preserve">0.49633777141571</t>
   </si>
   <si>
     <t xml:space="preserve">0.506857395172119</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">0.487730741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483905375003815</t>
+    <t xml:space="preserve">0.483905404806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.461909741163254</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">0.478167414665222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468604058027267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471473038196564</t>
+    <t xml:space="preserve">0.46860408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471473067998886</t>
   </si>
   <si>
     <t xml:space="preserve">0.48260822892189</t>
@@ -3999,6 +3999,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.51800000667572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.541999995708466</t>
   </si>
 </sst>
 </file>
@@ -69779,7 +69782,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6909722222</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>390727</v>
@@ -69800,6 +69803,32 @@
         <v>1322</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6912847222</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>837800</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>0.546000003814697</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>0.533999979496002</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>0.537000000476837</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>0.541999995708466</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>1329</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32744625210762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321156322956085</t>
+    <t xml:space="preserve">0.327446222305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32115626335144</t>
   </si>
   <si>
     <t xml:space="preserve">0.317678362131119</t>
@@ -62,28 +62,28 @@
     <t xml:space="preserve">0.289336681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294368654489517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285636752843857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273796826601028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258997052907944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258257061243057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243605181574821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246417179703712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262696981430054</t>
+    <t xml:space="preserve">0.294368624687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285636723041534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273796886205673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258996993303299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258257031440735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243605226278305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246417164802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262696951627731</t>
   </si>
   <si>
     <t xml:space="preserve">0.256407082080841</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">0.261512994766235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.253817111253738</t>
+    <t xml:space="preserve">0.253817081451416</t>
   </si>
   <si>
     <t xml:space="preserve">0.253077119588852</t>
@@ -107,67 +107,67 @@
     <t xml:space="preserve">0.284600764513016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277496814727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28711673617363</t>
+    <t xml:space="preserve">0.277496844530106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287116706371307</t>
   </si>
   <si>
     <t xml:space="preserve">0.290742665529251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263806968927383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256777077913284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.250117152929306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277570843696594</t>
+    <t xml:space="preserve">0.263806998729706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25677701830864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.250117123126984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277570813894272</t>
   </si>
   <si>
     <t xml:space="preserve">0.297994613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310796469449997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303544491529465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304358541965485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318122327327728</t>
+    <t xml:space="preserve">0.310796409845352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303544521331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304358512163162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318122357130051</t>
   </si>
   <si>
     <t xml:space="preserve">0.309686452150345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301620572805405</t>
+    <t xml:space="preserve">0.30162051320076</t>
   </si>
   <si>
     <t xml:space="preserve">0.310352444648743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323376297950745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320046365261078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316716402769089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315236389636993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315606385469437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332996129989624</t>
+    <t xml:space="preserve">0.323376268148422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320046335458755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316716372966766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315236359834671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315606355667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332996189594269</t>
   </si>
   <si>
     <t xml:space="preserve">0.332256197929382</t>
@@ -176,43 +176,43 @@
     <t xml:space="preserve">0.328852266073227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330480217933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311240464448929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312054425477982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299696534872055</t>
+    <t xml:space="preserve">0.330480188131332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311240434646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312054455280304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2996965944767</t>
   </si>
   <si>
     <t xml:space="preserve">0.296884596347809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2994005382061</t>
+    <t xml:space="preserve">0.299400568008423</t>
   </si>
   <si>
     <t xml:space="preserve">0.29747661948204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295996606349945</t>
+    <t xml:space="preserve">0.295996636152267</t>
   </si>
   <si>
     <t xml:space="preserve">0.293702661991119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298216551542282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286376714706421</t>
+    <t xml:space="preserve">0.298216581344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286376744508743</t>
   </si>
   <si>
     <t xml:space="preserve">0.276756823062897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274536818265915</t>
+    <t xml:space="preserve">0.274536848068237</t>
   </si>
   <si>
     <t xml:space="preserve">0.2723169028759</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">0.268542915582657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270466923713684</t>
+    <t xml:space="preserve">0.270466893911362</t>
   </si>
   <si>
     <t xml:space="preserve">0.265064984560013</t>
@@ -233,28 +233,28 @@
     <t xml:space="preserve">0.268616944551468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269208908081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275276839733124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28489676117897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290002673864365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308206468820572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309168517589569</t>
+    <t xml:space="preserve">0.269208878278732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275276869535446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284896731376648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290002703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30820643901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309168457984924</t>
   </si>
   <si>
     <t xml:space="preserve">0.318196386098862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316938370466232</t>
+    <t xml:space="preserve">0.31693834066391</t>
   </si>
   <si>
     <t xml:space="preserve">0.308946460485458</t>
@@ -263,28 +263,28 @@
     <t xml:space="preserve">0.314200401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321378350257874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319380313158035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722410678864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313682436943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313312411308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307096481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30761444568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304950475692749</t>
+    <t xml:space="preserve">0.321378320455551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31938037276268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722440481186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313682407140732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313312441110611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30709645152092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307614475488663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304950505495071</t>
   </si>
   <si>
     <t xml:space="preserve">0.305616497993469</t>
@@ -293,40 +293,40 @@
     <t xml:space="preserve">0.299548596143723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305320471525192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295626610517502</t>
+    <t xml:space="preserve">0.305320531129837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295626670122147</t>
   </si>
   <si>
     <t xml:space="preserve">0.300954550504684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314400345087051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318779766559601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318856626749039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318395614624023</t>
+    <t xml:space="preserve">0.314400285482407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318779826164246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318856596946716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318395644426346</t>
   </si>
   <si>
     <t xml:space="preserve">0.319932252168655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318088263273239</t>
+    <t xml:space="preserve">0.318088293075562</t>
   </si>
   <si>
     <t xml:space="preserve">0.307331681251526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321776241064072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320393294095993</t>
+    <t xml:space="preserve">0.321776270866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320393264293671</t>
   </si>
   <si>
     <t xml:space="preserve">0.311557501554489</t>
@@ -335,91 +335,91 @@
     <t xml:space="preserve">0.305795013904572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301569253206253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295806765556335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299648344516754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296575099229813</t>
+    <t xml:space="preserve">0.301569193601608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295806705951691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299648374319077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29657506942749</t>
   </si>
   <si>
     <t xml:space="preserve">0.303490042686462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314246654510498</t>
+    <t xml:space="preserve">0.31424668431282</t>
   </si>
   <si>
     <t xml:space="preserve">0.318011432886124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318702965974808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32116162776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310020804405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311941623687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311173319816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307254821062088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30671700835228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305564522743225</t>
+    <t xml:space="preserve">0.318702936172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321161657571793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310020834207535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311941653490067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311173349618912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30725485086441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306717038154602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305564552545547</t>
   </si>
   <si>
     <t xml:space="preserve">0.304949879646301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306870698928833</t>
+    <t xml:space="preserve">0.306870669126511</t>
   </si>
   <si>
     <t xml:space="preserve">0.297727555036545</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301799744367599</t>
+    <t xml:space="preserve">0.301799714565277</t>
   </si>
   <si>
     <t xml:space="preserve">0.304027855396271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300032556056976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313478320837021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31255629658699</t>
+    <t xml:space="preserve">0.300032585859299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313478291034698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312556326389313</t>
   </si>
   <si>
     <t xml:space="preserve">0.307869523763657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311480641365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298265427350998</t>
+    <t xml:space="preserve">0.311480671167374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298265397548676</t>
   </si>
   <si>
     <t xml:space="preserve">0.299110561609268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305257230997086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295576244592667</t>
+    <t xml:space="preserve">0.305257201194763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295576214790344</t>
   </si>
   <si>
     <t xml:space="preserve">0.295960396528244</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">0.297881215810776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293732285499573</t>
+    <t xml:space="preserve">0.293732225894928</t>
   </si>
   <si>
     <t xml:space="preserve">0.298803210258484</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">0.298880070447922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305487722158432</t>
+    <t xml:space="preserve">0.30548769235611</t>
   </si>
   <si>
     <t xml:space="preserve">0.309559851884842</t>
@@ -461,16 +461,16 @@
     <t xml:space="preserve">0.308253675699234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304873049259186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306563377380371</t>
+    <t xml:space="preserve">0.304873019456863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306563347578049</t>
   </si>
   <si>
     <t xml:space="preserve">0.30018624663353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298649609088898</t>
+    <t xml:space="preserve">0.298649579286575</t>
   </si>
   <si>
     <t xml:space="preserve">0.296421378850937</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">0.300647228956223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282975643873215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291965067386627</t>
+    <t xml:space="preserve">0.282975614070892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29196509718895</t>
   </si>
   <si>
     <t xml:space="preserve">0.289736956357956</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">0.293501734733582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292656600475311</t>
+    <t xml:space="preserve">0.292656570672989</t>
   </si>
   <si>
     <t xml:space="preserve">0.29250293970108</t>
@@ -503,70 +503,70 @@
     <t xml:space="preserve">0.289583265781403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288123458623886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2842817902565</t>
+    <t xml:space="preserve">0.288123488426208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284281849861145</t>
   </si>
   <si>
     <t xml:space="preserve">0.28789296746254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290044248104095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29288712143898</t>
+    <t xml:space="preserve">0.290044277906418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292887091636658</t>
   </si>
   <si>
     <t xml:space="preserve">0.293117612600327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291888296604156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289813756942749</t>
+    <t xml:space="preserve">0.291888266801834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289813786745071</t>
   </si>
   <si>
     <t xml:space="preserve">0.286586791276932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294270068407059</t>
+    <t xml:space="preserve">0.294270098209381</t>
   </si>
   <si>
     <t xml:space="preserve">0.291811436414719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292579770088196</t>
+    <t xml:space="preserve">0.292579799890518</t>
   </si>
   <si>
     <t xml:space="preserve">0.295729905366898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298419058322906</t>
+    <t xml:space="preserve">0.298419088125229</t>
   </si>
   <si>
     <t xml:space="preserve">0.294731080532074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287355124950409</t>
+    <t xml:space="preserve">0.287355095148087</t>
   </si>
   <si>
     <t xml:space="preserve">0.293809086084366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292041927576065</t>
+    <t xml:space="preserve">0.292041957378387</t>
   </si>
   <si>
     <t xml:space="preserve">0.286740452051163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2846659719944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278903543949127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27559968829155</t>
+    <t xml:space="preserve">0.284665942192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278903514146805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275599718093872</t>
   </si>
   <si>
     <t xml:space="preserve">0.270221382379532</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">0.272449553012848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276675343513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27398619055748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275676518678665</t>
+    <t xml:space="preserve">0.276675373315811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273986220359802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275676548480988</t>
   </si>
   <si>
     <t xml:space="preserve">0.275522857904434</t>
@@ -590,46 +590,46 @@
     <t xml:space="preserve">0.276598513126373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270989716053009</t>
+    <t xml:space="preserve">0.270989686250687</t>
   </si>
   <si>
     <t xml:space="preserve">0.27114337682724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.274293482303619</t>
+    <t xml:space="preserve">0.274293512105942</t>
   </si>
   <si>
     <t xml:space="preserve">0.270451873540878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268146902322769</t>
+    <t xml:space="preserve">0.268146872520447</t>
   </si>
   <si>
     <t xml:space="preserve">0.267378568649292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264612555503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2657650411129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262384444475174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267532199621201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265304118394852</t>
+    <t xml:space="preserve">0.264612525701523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265765070915222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262384414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267532229423523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265304088592529</t>
   </si>
   <si>
     <t xml:space="preserve">0.271911710500717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272526353597641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283282965421677</t>
+    <t xml:space="preserve">0.272526383399963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283282995223999</t>
   </si>
   <si>
     <t xml:space="preserve">0.279902338981628</t>
@@ -647,22 +647,22 @@
     <t xml:space="preserve">0.278749823570251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278980314731598</t>
+    <t xml:space="preserve">0.27898034453392</t>
   </si>
   <si>
     <t xml:space="preserve">0.278212010860443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284051328897476</t>
+    <t xml:space="preserve">0.284051299095154</t>
   </si>
   <si>
     <t xml:space="preserve">0.290812641382217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289660096168518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290428400039673</t>
+    <t xml:space="preserve">0.28966012597084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290428429841995</t>
   </si>
   <si>
     <t xml:space="preserve">0.294807940721512</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">0.284589141607285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291043132543564</t>
+    <t xml:space="preserve">0.291043102741241</t>
   </si>
   <si>
     <t xml:space="preserve">0.293885916471481</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">0.294884741306305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289890617132187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286125779151917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284358650445938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282745152711868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277290016412735</t>
+    <t xml:space="preserve">0.289890587329865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286125808954239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284358620643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282745182514191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277290046215057</t>
   </si>
   <si>
     <t xml:space="preserve">0.281976819038391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276214331388474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27360200881958</t>
+    <t xml:space="preserve">0.276214361190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273602038621902</t>
   </si>
   <si>
     <t xml:space="preserve">0.269760400056839</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">0.273371547460556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275215536355972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276905834674835</t>
+    <t xml:space="preserve">0.275215566158295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276905864477158</t>
   </si>
   <si>
     <t xml:space="preserve">0.274831354618073</t>
@@ -734,49 +734,49 @@
     <t xml:space="preserve">0.282668322324753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280440151691437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279594987630844</t>
+    <t xml:space="preserve">0.280440181493759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279595017433167</t>
   </si>
   <si>
     <t xml:space="preserve">0.27736684679985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278135180473328</t>
+    <t xml:space="preserve">0.278135150671005</t>
   </si>
   <si>
     <t xml:space="preserve">0.281208485364914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278673022985458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28259152173996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279364466667175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285587936639786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27967181801796</t>
+    <t xml:space="preserve">0.278672963380814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282591491937637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279364496469498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285587966442108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279671847820282</t>
   </si>
   <si>
     <t xml:space="preserve">0.28666365146637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284435510635376</t>
+    <t xml:space="preserve">0.284435480833054</t>
   </si>
   <si>
     <t xml:space="preserve">0.281899988651276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283897668123245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285280674695969</t>
+    <t xml:space="preserve">0.283897697925568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285280615091324</t>
   </si>
   <si>
     <t xml:space="preserve">0.285434275865555</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">0.304258346557617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321929901838303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325617909431458</t>
+    <t xml:space="preserve">0.321929931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32561793923378</t>
   </si>
   <si>
     <t xml:space="preserve">0.33184140920639</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">0.316935777664185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309790343046188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309252500534058</t>
+    <t xml:space="preserve">0.309790372848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30925253033638</t>
   </si>
   <si>
     <t xml:space="preserve">0.311096489429474</t>
@@ -815,28 +815,28 @@
     <t xml:space="preserve">0.313094168901443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313017308712006</t>
+    <t xml:space="preserve">0.313017338514328</t>
   </si>
   <si>
     <t xml:space="preserve">0.288891792297363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293040722608566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295192092657089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296805560588837</t>
+    <t xml:space="preserve">0.293040752410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295192062854767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296805590391159</t>
   </si>
   <si>
     <t xml:space="preserve">0.297266572713852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298111736774445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310251355171204</t>
+    <t xml:space="preserve">0.298111766576767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310251325368881</t>
   </si>
   <si>
     <t xml:space="preserve">0.313555151224136</t>
@@ -851,34 +851,34 @@
     <t xml:space="preserve">0.299725234508514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321853131055832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327308237552643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318472474813461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312095373868942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314016163349152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315014988183975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312248975038528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313939332962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309636622667313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307408541440964</t>
+    <t xml:space="preserve">0.32185310125351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327308267354965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318472445011139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312095284461975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314016133546829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31501492857933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312249004840851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313939303159714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309636652469635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307408511638641</t>
   </si>
   <si>
     <t xml:space="preserve">0.308945178985596</t>
@@ -887,22 +887,22 @@
     <t xml:space="preserve">0.313631981611252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308023184537888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307715833187103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309022039175034</t>
+    <t xml:space="preserve">0.308023154735565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307715862989426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309022009372711</t>
   </si>
   <si>
     <t xml:space="preserve">0.309944003820419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3177809715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316551685333252</t>
+    <t xml:space="preserve">0.317780911922455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316551625728607</t>
   </si>
   <si>
     <t xml:space="preserve">0.316474795341492</t>
@@ -914,46 +914,46 @@
     <t xml:space="preserve">0.325003266334534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318318784236908</t>
+    <t xml:space="preserve">0.318318754434586</t>
   </si>
   <si>
     <t xml:space="preserve">0.317704141139984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32154580950737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320470124483109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621434926987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323697090148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333454877138138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327385097742081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33176451921463</t>
+    <t xml:space="preserve">0.321545779705048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320470154285431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621405124664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323697060346603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333454847335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327385067939758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331764549016953</t>
   </si>
   <si>
     <t xml:space="preserve">0.339524686336517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34567129611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340446680784225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333378046751022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334991544485092</t>
+    <t xml:space="preserve">0.345671325922012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340446710586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3333780169487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33499151468277</t>
   </si>
   <si>
     <t xml:space="preserve">0.336144030094147</t>
@@ -962,25 +962,25 @@
     <t xml:space="preserve">0.337757527828217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338910043239594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338141739368439</t>
+    <t xml:space="preserve">0.338909983634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338141709566116</t>
   </si>
   <si>
     <t xml:space="preserve">0.339678347110748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350358128547668</t>
+    <t xml:space="preserve">0.350358098745346</t>
   </si>
   <si>
     <t xml:space="preserve">0.346593290567398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344211518764496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34067714214325</t>
+    <t xml:space="preserve">0.344211488962173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340677201747894</t>
   </si>
   <si>
     <t xml:space="preserve">0.334607362747192</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">0.338218539953232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34690061211586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346132308244705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33960148692131</t>
+    <t xml:space="preserve">0.346900641918182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346132338047028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339601516723633</t>
   </si>
   <si>
     <t xml:space="preserve">0.340907663106918</t>
@@ -1004,22 +1004,22 @@
     <t xml:space="preserve">0.3526631295681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369950532913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365417391061783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363035529851913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374099463224411</t>
+    <t xml:space="preserve">0.369950503110886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36541736125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363035559654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374099493026733</t>
   </si>
   <si>
     <t xml:space="preserve">0.371103048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369566351175308</t>
+    <t xml:space="preserve">0.369566380977631</t>
   </si>
   <si>
     <t xml:space="preserve">0.368798017501831</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">0.366108894348145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363112419843674</t>
+    <t xml:space="preserve">0.363112390041351</t>
   </si>
   <si>
     <t xml:space="preserve">0.3686443567276</t>
@@ -1046,40 +1046,40 @@
     <t xml:space="preserve">0.359885424375534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359193921089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368567526340485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372025012969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37555930018425</t>
+    <t xml:space="preserve">0.35919389128685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368567556142807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372024983167648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375559329986572</t>
   </si>
   <si>
     <t xml:space="preserve">0.380246132612228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392616212368011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405677855014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421044439077377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419507771730423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396842062473297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413361072540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422581106424332</t>
+    <t xml:space="preserve">0.392616152763367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405677825212479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421044409275055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419507741928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396842032670975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413361102342606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422581017017365</t>
   </si>
   <si>
     <t xml:space="preserve">0.417586892843246</t>
@@ -1091,79 +1091,79 @@
     <t xml:space="preserve">0.423349380493164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427959412336349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436795145273209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432953476905823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452930092811584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460884332657</t>
+    <t xml:space="preserve">0.427959322929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436795175075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432953506708145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452930122613907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460824728012</t>
   </si>
   <si>
     <t xml:space="preserve">0.465223342180252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468296676874161</t>
+    <t xml:space="preserve">0.468296706676483</t>
   </si>
   <si>
     <t xml:space="preserve">0.481358259916306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522463917732239</t>
+    <t xml:space="preserve">0.522463858127594</t>
   </si>
   <si>
     <t xml:space="preserve">0.515164732933044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505560517311096</t>
+    <t xml:space="preserve">0.505560636520386</t>
   </si>
   <si>
     <t xml:space="preserve">0.50709730386734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515548825263977</t>
+    <t xml:space="preserve">0.515548944473267</t>
   </si>
   <si>
     <t xml:space="preserve">0.503255605697632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489809900522232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480205714702606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519006371498108</t>
+    <t xml:space="preserve">0.489809930324554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480205684900284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519006431102753</t>
   </si>
   <si>
     <t xml:space="preserve">0.511323034763336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499413937330246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491730690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484431624412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483663231134415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484815716743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49518820643425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490194082260132</t>
+    <t xml:space="preserve">0.499413967132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491730719804764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484431564807892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483663201332092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484815776348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495188236236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490193963050842</t>
   </si>
   <si>
     <t xml:space="preserve">0.553197026252747</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">0.586235225200653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600065112113953</t>
+    <t xml:space="preserve">0.600065171718597</t>
   </si>
   <si>
     <t xml:space="preserve">0.582393527030945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572021126747131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572789490222931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552428662776947</t>
+    <t xml:space="preserve">0.572021067142487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572789430618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552428722381592</t>
   </si>
   <si>
     <t xml:space="preserve">0.55127614736557</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">0.596607625484467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584698438644409</t>
+    <t xml:space="preserve">0.584698557853699</t>
   </si>
   <si>
     <t xml:space="preserve">0.608132541179657</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">0.620425879955292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629645884037018</t>
+    <t xml:space="preserve">0.629645764827728</t>
   </si>
   <si>
     <t xml:space="preserve">0.614279210567474</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">0.581625282764435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560880303382874</t>
+    <t xml:space="preserve">0.560880362987518</t>
   </si>
   <si>
     <t xml:space="preserve">0.598528444766998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598144292831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619657576084137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618120789527893</t>
+    <t xml:space="preserve">0.598144233226776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619657456874847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618120849132538</t>
   </si>
   <si>
     <t xml:space="preserve">0.601601779460907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586619317531586</t>
+    <t xml:space="preserve">0.58661937713623</t>
   </si>
   <si>
     <t xml:space="preserve">0.59545511007309</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">0.587771832942963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584314405918121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577399432659149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567026913166046</t>
+    <t xml:space="preserve">0.584314465522766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577399373054504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567026853561401</t>
   </si>
   <si>
     <t xml:space="preserve">0.57432609796524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543592929840088</t>
+    <t xml:space="preserve">0.543592870235443</t>
   </si>
   <si>
     <t xml:space="preserve">0.564721941947937</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">0.563185334205627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576246917247772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583930134773254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580856800079346</t>
+    <t xml:space="preserve">0.576246976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583930194377899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58085685968399</t>
   </si>
   <si>
     <t xml:space="preserve">0.587003469467163</t>
@@ -1295,19 +1295,19 @@
     <t xml:space="preserve">0.604675054550171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629261612892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618505001068115</t>
+    <t xml:space="preserve">0.629261672496796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61850506067276</t>
   </si>
   <si>
     <t xml:space="preserve">0.606980085372925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603138506412506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612358331680298</t>
+    <t xml:space="preserve">0.603138387203217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612358391284943</t>
   </si>
   <si>
     <t xml:space="preserve">0.611590027809143</t>
@@ -1322,31 +1322,31 @@
     <t xml:space="preserve">0.608516693115234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599296689033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589308500289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553965389728546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538598716259003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557038724422455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536293804645538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524000465869904</t>
+    <t xml:space="preserve">0.599296748638153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589308559894562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553965330123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538598775863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55703866481781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536293745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524000525474548</t>
   </si>
   <si>
     <t xml:space="preserve">0.537830471992493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547818720340729</t>
+    <t xml:space="preserve">0.547818779945374</t>
   </si>
   <si>
     <t xml:space="preserve">0.53245210647583</t>
@@ -1355,16 +1355,16 @@
     <t xml:space="preserve">0.537062108516693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527073860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52092719078064</t>
+    <t xml:space="preserve">0.527073800563812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520927250385284</t>
   </si>
   <si>
     <t xml:space="preserve">0.517853915691376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525537133216858</t>
+    <t xml:space="preserve">0.525537252426147</t>
   </si>
   <si>
     <t xml:space="preserve">0.530147135257721</t>
@@ -1376,58 +1376,58 @@
     <t xml:space="preserve">0.51939058303833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524768888950348</t>
+    <t xml:space="preserve">0.524768829345703</t>
   </si>
   <si>
     <t xml:space="preserve">0.549355387687683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501718938350677</t>
+    <t xml:space="preserve">0.501718997955322</t>
   </si>
   <si>
     <t xml:space="preserve">0.492499023675919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477900743484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476364076137543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48865732550621</t>
+    <t xml:space="preserve">0.477900683879852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476364105939865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488657414913177</t>
   </si>
   <si>
     <t xml:space="preserve">0.471754133701324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472522467374802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468680769205093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487120747566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481742382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480974048376083</t>
+    <t xml:space="preserve">0.472522497177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468680858612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487120777368546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481742411851883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480974107980728</t>
   </si>
   <si>
     <t xml:space="preserve">0.48327910900116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478669077157974</t>
+    <t xml:space="preserve">0.478669166564941</t>
   </si>
   <si>
     <t xml:space="preserve">0.47021746635437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467912554740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466375827789307</t>
+    <t xml:space="preserve">0.467912524938583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466375857591629</t>
   </si>
   <si>
     <t xml:space="preserve">0.464839190244675</t>
@@ -1436,19 +1436,19 @@
     <t xml:space="preserve">0.461765855550766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4878890812397</t>
+    <t xml:space="preserve">0.487889021635056</t>
   </si>
   <si>
     <t xml:space="preserve">0.500182330608368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469449102878571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437179356813431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444862604141235</t>
+    <t xml:space="preserve">0.469449073076248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437179327011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444862574338913</t>
   </si>
   <si>
     <t xml:space="preserve">0.431800991296768</t>
@@ -1457,10 +1457,10 @@
     <t xml:space="preserve">0.444094270467758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424117684364319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415666133165359</t>
+    <t xml:space="preserve">0.424117714166641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415666162967682</t>
   </si>
   <si>
     <t xml:space="preserve">0.382627934217453</t>
@@ -1475,16 +1475,16 @@
     <t xml:space="preserve">0.385701268911362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388774573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391847938299179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38416463136673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37648132443428</t>
+    <t xml:space="preserve">0.388774544000626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391847848892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384164601564407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376481294631958</t>
   </si>
   <si>
     <t xml:space="preserve">0.367261350154877</t>
@@ -1505,28 +1505,28 @@
     <t xml:space="preserve">0.37148717045784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368029713630676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372255504131317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365340530872345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374944627285004</t>
+    <t xml:space="preserve">0.368029683828354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37225553393364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365340501070023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374944716691971</t>
   </si>
   <si>
     <t xml:space="preserve">0.366493046283722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374560505151749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374176323413849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37878629565239</t>
+    <t xml:space="preserve">0.374560534954071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374176293611526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378786325454712</t>
   </si>
   <si>
     <t xml:space="preserve">0.362267225980759</t>
@@ -1544,52 +1544,52 @@
     <t xml:space="preserve">0.370718836784363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354199796915054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39568954706192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411056190729141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407982885837555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384932905435562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390311270952225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378017991781235</t>
+    <t xml:space="preserve">0.35419973731041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395689576864243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411056131124496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407982796430588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384932965040207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390311241149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378017961978912</t>
   </si>
   <si>
     <t xml:space="preserve">0.380707114934921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362651377916336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359578043222427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353431463241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349589794874191</t>
+    <t xml:space="preserve">0.362651407718658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35957807302475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353431433439255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349589824676514</t>
   </si>
   <si>
     <t xml:space="preserve">0.344979822635651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343058973550797</t>
+    <t xml:space="preserve">0.343059003353119</t>
   </si>
   <si>
     <t xml:space="preserve">0.354968100786209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364188075065613</t>
+    <t xml:space="preserve">0.36418804526329</t>
   </si>
   <si>
     <t xml:space="preserve">0.357273072004318</t>
@@ -1601,61 +1601,61 @@
     <t xml:space="preserve">0.339217364788055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323850750923157</t>
+    <t xml:space="preserve">0.323850780725479</t>
   </si>
   <si>
     <t xml:space="preserve">0.361883044242859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350742280483246</t>
+    <t xml:space="preserve">0.350742250680923</t>
   </si>
   <si>
     <t xml:space="preserve">0.389542937278748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404141157865524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396457880735397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412592798471451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404909491539001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401836216449738</t>
+    <t xml:space="preserve">0.404141187667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396457821130753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412592768669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404909521341324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401836186647415</t>
   </si>
   <si>
     <t xml:space="preserve">0.394152909517288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399531155824661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402604520320892</t>
+    <t xml:space="preserve">0.399531185626984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40260449051857</t>
   </si>
   <si>
     <t xml:space="preserve">0.40106788277626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397994548082352</t>
+    <t xml:space="preserve">0.397994518280029</t>
   </si>
   <si>
     <t xml:space="preserve">0.375712960958481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364572197198868</t>
+    <t xml:space="preserve">0.36457222700119</t>
   </si>
   <si>
     <t xml:space="preserve">0.345748126506805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336528211832047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335759878158569</t>
+    <t xml:space="preserve">0.336528241634369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335759848356247</t>
   </si>
   <si>
     <t xml:space="preserve">0.337296515703201</t>
@@ -1664,19 +1664,19 @@
     <t xml:space="preserve">0.329613208770752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328076511621475</t>
+    <t xml:space="preserve">0.32807657122612</t>
   </si>
   <si>
     <t xml:space="preserve">0.331534057855606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319240808486938</t>
+    <t xml:space="preserve">0.319240778684616</t>
   </si>
   <si>
     <t xml:space="preserve">0.326924055814743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312710016965866</t>
+    <t xml:space="preserve">0.312709987163544</t>
   </si>
   <si>
     <t xml:space="preserve">0.341138184070587</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">0.322698265314102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326155722141266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324619084596634</t>
+    <t xml:space="preserve">0.326155751943588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324619114398956</t>
   </si>
   <si>
     <t xml:space="preserve">0.325771570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330381572246552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329997420310974</t>
+    <t xml:space="preserve">0.330381602048874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329997390508652</t>
   </si>
   <si>
     <t xml:space="preserve">0.324234932661057</t>
@@ -1715,94 +1715,94 @@
     <t xml:space="preserve">0.29695925116539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302721709012985</t>
+    <t xml:space="preserve">0.302721738815308</t>
   </si>
   <si>
     <t xml:space="preserve">0.32308241724968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308100014925003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310404986143112</t>
+    <t xml:space="preserve">0.308100044727325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310405015945435</t>
   </si>
   <si>
     <t xml:space="preserve">0.306947499513626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314630806446075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305410861968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30848416686058</t>
+    <t xml:space="preserve">0.314630836248398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305410891771317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308484137058258</t>
   </si>
   <si>
     <t xml:space="preserve">0.304642498493195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32077744603157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356888920068741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358041405677795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356120616197586</t>
+    <t xml:space="preserve">0.320777416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356888890266418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358041435480118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356120586395264</t>
   </si>
   <si>
     <t xml:space="preserve">0.360730558633804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358809769153595</t>
+    <t xml:space="preserve">0.358809739351273</t>
   </si>
   <si>
     <t xml:space="preserve">0.351126462221146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355736404657364</t>
+    <t xml:space="preserve">0.355736434459686</t>
   </si>
   <si>
     <t xml:space="preserve">0.342290639877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37187135219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370334684848785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38378044962883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376097172498703</t>
+    <t xml:space="preserve">0.371871322393417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370334655046463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383780419826508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376097142696381</t>
   </si>
   <si>
     <t xml:space="preserve">0.376865476369858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377249628305435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398762881755829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403372824192047</t>
+    <t xml:space="preserve">0.377249658107758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398762851953506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403372794389725</t>
   </si>
   <si>
     <t xml:space="preserve">0.406446129083633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409519463777542</t>
+    <t xml:space="preserve">0.40951943397522</t>
   </si>
   <si>
     <t xml:space="preserve">0.39107957482338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381475418806076</t>
+    <t xml:space="preserve">0.381475448608398</t>
   </si>
   <si>
     <t xml:space="preserve">0.407214462757111</t>
@@ -1814,16 +1814,16 @@
     <t xml:space="preserve">0.394921183586121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411824464797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41489776968956</t>
+    <t xml:space="preserve">0.411824494600296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414897799491882</t>
   </si>
   <si>
     <t xml:space="preserve">0.417202740907669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397226184606552</t>
+    <t xml:space="preserve">0.397226214408875</t>
   </si>
   <si>
     <t xml:space="preserve">0.408751159906387</t>
@@ -1835,103 +1835,103 @@
     <t xml:space="preserve">0.414129376411438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416434407234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418739408254623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4202761054039</t>
+    <t xml:space="preserve">0.416434437036514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418739438056946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420276045799255</t>
   </si>
   <si>
     <t xml:space="preserve">0.421812772750854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430264383554459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473290741443634</t>
+    <t xml:space="preserve">0.430264323949814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473290771245956</t>
   </si>
   <si>
     <t xml:space="preserve">0.49480402469635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484047383069992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267357349396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506328940391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479437381029129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482510775327682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595742464066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464070796966553</t>
+    <t xml:space="preserve">0.484047412872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267387151718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506328880786896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479437470436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48251074552536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475595831871033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46407076716423</t>
   </si>
   <si>
     <t xml:space="preserve">0.465607523918152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460997521877289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434105932712555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789269447327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445630937814713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449472546577454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45100924372673</t>
+    <t xml:space="preserve">0.460997551679611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453314244747162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4341059923172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789329051971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445630997419357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449472576379776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451009273529053</t>
   </si>
   <si>
     <t xml:space="preserve">0.460229188203812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454082548618317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45715594291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451777577400208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456387549638748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46330252289772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470985740423203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467144161462784</t>
+    <t xml:space="preserve">0.454082608222961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457155883312225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45177760720253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456387490034103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463302493095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47098582983017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467144131660461</t>
   </si>
   <si>
     <t xml:space="preserve">0.457924276590347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447167664766312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43256938457489</t>
+    <t xml:space="preserve">0.447167605161667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432569414377213</t>
   </si>
   <si>
     <t xml:space="preserve">0.437947690486908</t>
@@ -1943,31 +1943,31 @@
     <t xml:space="preserve">0.434874325990677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436410993337631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439484357833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441020965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440252661705017</t>
+    <t xml:space="preserve">0.436410963535309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43948432803154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441020995378494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440252602100372</t>
   </si>
   <si>
     <t xml:space="preserve">0.43871596455574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442557662725449</t>
+    <t xml:space="preserve">0.442557632923126</t>
   </si>
   <si>
     <t xml:space="preserve">0.485584050416946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455619275569916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443325996398926</t>
+    <t xml:space="preserve">0.455619245767593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443325966596603</t>
   </si>
   <si>
     <t xml:space="preserve">0.429496049880981</t>
@@ -1979,31 +1979,31 @@
     <t xml:space="preserve">0.450240910053253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42719104886055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375328809022903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386469632387161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393384575843811</t>
+    <t xml:space="preserve">0.427191019058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375328779220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386469602584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393384605646133</t>
   </si>
   <si>
     <t xml:space="preserve">0.365724712610245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372639685869217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351510614156723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342674851417542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317319959402084</t>
+    <t xml:space="preserve">0.372639656066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351510643959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342674821615219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317319989204407</t>
   </si>
   <si>
     <t xml:space="preserve">0.26507356762886</t>
@@ -2012,16 +2012,16 @@
     <t xml:space="preserve">0.259695291519165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239334538578987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242023691534996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234724551439285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245865345001221</t>
+    <t xml:space="preserve">0.239334583282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242023706436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234724536538124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245865359902382</t>
   </si>
   <si>
     <t xml:space="preserve">0.258926957845688</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">0.266610234975815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269299358129501</t>
+    <t xml:space="preserve">0.269299387931824</t>
   </si>
   <si>
     <t xml:space="preserve">0.258158594369888</t>
@@ -2045,43 +2045,43 @@
     <t xml:space="preserve">0.252011954784393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.242407858371735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245097041130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254701107740402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262000232934952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254316926002502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261231958866119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262768566608429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264689415693283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27198851108551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273909360170364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276982694864273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272756844758987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275445997714996</t>
+    <t xml:space="preserve">0.242407888174057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245096981525421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254701137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262000262737274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254316955804825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261231929063797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262768626213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264689445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271988540887833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273909389972687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276982665061951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27275687456131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275446027517319</t>
   </si>
   <si>
     <t xml:space="preserve">0.268915235996246</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">0.258542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26545774936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263152778148651</t>
+    <t xml:space="preserve">0.265457719564438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263152748346329</t>
   </si>
   <si>
     <t xml:space="preserve">0.292733430862427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32769238948822</t>
+    <t xml:space="preserve">0.327692419290543</t>
   </si>
   <si>
     <t xml:space="preserve">0.302337527275085</t>
@@ -2111,46 +2111,46 @@
     <t xml:space="preserve">0.301953375339508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332302391529083</t>
+    <t xml:space="preserve">0.332302421331406</t>
   </si>
   <si>
     <t xml:space="preserve">0.332686573266983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306179165840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305026710033417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312325835227966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331918209791183</t>
+    <t xml:space="preserve">0.306179195642471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305026739835739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312325805425644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331918179988861</t>
   </si>
   <si>
     <t xml:space="preserve">0.315399140119553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326539933681488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292349219322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289275944232941</t>
+    <t xml:space="preserve">0.326539903879166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292349278926849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289275974035263</t>
   </si>
   <si>
     <t xml:space="preserve">0.291196763515472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286970943212509</t>
+    <t xml:space="preserve">0.286970973014832</t>
   </si>
   <si>
     <t xml:space="preserve">0.285050123929977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273525208234787</t>
+    <t xml:space="preserve">0.273525178432465</t>
   </si>
   <si>
     <t xml:space="preserve">0.26084777712822</t>
@@ -2162,58 +2162,58 @@
     <t xml:space="preserve">0.270067691802979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278519362211227</t>
+    <t xml:space="preserve">0.278519332408905</t>
   </si>
   <si>
     <t xml:space="preserve">0.27314105629921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266994386911392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.255469471216202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25316447019577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256621927022934</t>
+    <t xml:space="preserve">0.266994416713715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.255469501018524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253164440393448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256621986627579</t>
   </si>
   <si>
     <t xml:space="preserve">0.256237775087357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.249322801828384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236261233687401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238182038068771</t>
+    <t xml:space="preserve">0.249322846531868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.236261248588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238182052969933</t>
   </si>
   <si>
     <t xml:space="preserve">0.25354865193367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267762720584869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283513456583023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277750998735428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294654250144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319624930620193</t>
+    <t xml:space="preserve">0.267762780189514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283513426780701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277751058340073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294654279947281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319624990224838</t>
   </si>
   <si>
     <t xml:space="preserve">0.343827307224274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338449031114578</t>
+    <t xml:space="preserve">0.338449001312256</t>
   </si>
   <si>
     <t xml:space="preserve">0.34075403213501</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">0.338833212852478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338064819574356</t>
+    <t xml:space="preserve">0.338064849376678</t>
   </si>
   <si>
     <t xml:space="preserve">0.336912333965302</t>
@@ -2231,19 +2231,19 @@
     <t xml:space="preserve">0.333839058876038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330765753984451</t>
+    <t xml:space="preserve">0.330765724182129</t>
   </si>
   <si>
     <t xml:space="preserve">0.328844904899597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33998566865921</t>
+    <t xml:space="preserve">0.339985638856888</t>
   </si>
   <si>
     <t xml:space="preserve">0.34766897559166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35996225476265</t>
+    <t xml:space="preserve">0.359962224960327</t>
   </si>
   <si>
     <t xml:space="preserve">0.3518947660923</t>
@@ -2252,88 +2252,88 @@
     <t xml:space="preserve">0.369182199239731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357657223939896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355352252721786</t>
+    <t xml:space="preserve">0.35765728354454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355352282524109</t>
   </si>
   <si>
     <t xml:space="preserve">0.348053127527237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346516460180283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34728479385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363419711589813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373792141675949</t>
+    <t xml:space="preserve">0.346516489982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347284823656082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363419681787491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373792171478271</t>
   </si>
   <si>
     <t xml:space="preserve">0.373023837804794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379554599523544</t>
+    <t xml:space="preserve">0.379554629325867</t>
   </si>
   <si>
     <t xml:space="preserve">0.42565444111824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417971163988113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381859630346298</t>
+    <t xml:space="preserve">0.417971104383469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381859600543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.383012115955353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377633780241013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378402173519135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381091266870499</t>
+    <t xml:space="preserve">0.377633810043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37840211391449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381091296672821</t>
   </si>
   <si>
     <t xml:space="preserve">0.380322962999344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348437339067459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400299549102783</t>
+    <t xml:space="preserve">0.348437309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400299519300461</t>
   </si>
   <si>
     <t xml:space="preserve">0.383396297693253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379938781261444</t>
+    <t xml:space="preserve">0.379938840866089</t>
   </si>
   <si>
     <t xml:space="preserve">0.388006269931793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428727686405182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368413895368576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344595640897751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334223240613937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34190645813942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323466598987579</t>
+    <t xml:space="preserve">0.428727775812149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368413865566254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344595670700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334223181009293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341906487941742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323466569185257</t>
   </si>
   <si>
     <t xml:space="preserve">0.340369820594788</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">0.331149905920029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348821491003036</t>
+    <t xml:space="preserve">0.348821461200714</t>
   </si>
   <si>
     <t xml:space="preserve">0.322314113378525</t>
@@ -2357,37 +2357,37 @@
     <t xml:space="preserve">0.345363944768906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341522336006165</t>
+    <t xml:space="preserve">0.341522365808487</t>
   </si>
   <si>
     <t xml:space="preserve">0.329229056835175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353653132915497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351594567298889</t>
+    <t xml:space="preserve">0.353653103113174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351594626903534</t>
   </si>
   <si>
     <t xml:space="preserve">0.354064851999283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352829694747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347477585077286</t>
+    <t xml:space="preserve">0.352829724550247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347477555274963</t>
   </si>
   <si>
     <t xml:space="preserve">0.345830768346786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341713726520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342537134885788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348300993442535</t>
+    <t xml:space="preserve">0.341713696718216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34253716468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348300963640213</t>
   </si>
   <si>
     <t xml:space="preserve">0.359828680753708</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">0.353241413831711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354888260364532</t>
+    <t xml:space="preserve">0.35488823056221</t>
   </si>
   <si>
     <t xml:space="preserve">0.350359499454498</t>
@@ -2426,64 +2426,64 @@
     <t xml:space="preserve">0.321540266275406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310835987329483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315776407718658</t>
+    <t xml:space="preserve">0.310835957527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315776437520981</t>
   </si>
   <si>
     <t xml:space="preserve">0.314129620790482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312894463539124</t>
+    <t xml:space="preserve">0.312894493341446</t>
   </si>
   <si>
     <t xml:space="preserve">0.318246632814407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317834973335266</t>
+    <t xml:space="preserve">0.317834943532944</t>
   </si>
   <si>
     <t xml:space="preserve">0.319481790065765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312071084976196</t>
+    <t xml:space="preserve">0.312071114778519</t>
   </si>
   <si>
     <t xml:space="preserve">0.308365762233734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310012549161911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314541310071945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318658322095871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320305168628693</t>
+    <t xml:space="preserve">0.310012608766556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314541280269623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318658351898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320305198431015</t>
   </si>
   <si>
     <t xml:space="preserve">0.322775393724442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30960088968277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309189140796661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321128517389297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321951985359192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325245589017868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326892405748367</t>
+    <t xml:space="preserve">0.309600859880447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309189170598984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32112854719162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32195195555687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32524561882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326892465353012</t>
   </si>
   <si>
     <t xml:space="preserve">0.323187112808228</t>
@@ -2495,37 +2495,37 @@
     <t xml:space="preserve">0.315364718437195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31330618262291</t>
+    <t xml:space="preserve">0.313306212425232</t>
   </si>
   <si>
     <t xml:space="preserve">0.310424298048019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314953029155731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311247706413269</t>
+    <t xml:space="preserve">0.314952999353409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311247676610947</t>
   </si>
   <si>
     <t xml:space="preserve">0.317011535167694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31742325425148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311659425497055</t>
+    <t xml:space="preserve">0.317423224449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311659395694733</t>
   </si>
   <si>
     <t xml:space="preserve">0.316188126802444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319893449544907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30466040968895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30877748131752</t>
+    <t xml:space="preserve">0.319893479347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304660439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308777511119843</t>
   </si>
   <si>
     <t xml:space="preserve">0.303013622760773</t>
@@ -2534,67 +2534,64 @@
     <t xml:space="preserve">0.307542324066162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302601903676987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307954072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306307256221771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301778495311737</t>
+    <t xml:space="preserve">0.302601933479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307954043149948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306307286024094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301778525114059</t>
   </si>
   <si>
     <t xml:space="preserve">0.3038370013237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30095511674881</t>
+    <t xml:space="preserve">0.300955086946487</t>
   </si>
   <si>
     <t xml:space="preserve">0.301366806030273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302190214395523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313717901706696</t>
+    <t xml:space="preserve">0.302190244197845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313717931509018</t>
   </si>
   <si>
     <t xml:space="preserve">0.326480716466904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328539222478867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344595670700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340890318155289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356535077095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343360543251038</t>
+    <t xml:space="preserve">0.328539192676544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340890347957611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356535047292709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343360513448715</t>
   </si>
   <si>
     <t xml:space="preserve">0.336361587047577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339243531227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335126459598541</t>
+    <t xml:space="preserve">0.339243501424789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335126489400864</t>
   </si>
   <si>
     <t xml:space="preserve">0.358181834220886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347065895795822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34418398141861</t>
+    <t xml:space="preserve">0.3470658659935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344183951616287</t>
   </si>
   <si>
     <t xml:space="preserve">0.336773276329041</t>
@@ -2627,46 +2624,46 @@
     <t xml:space="preserve">0.332244515419006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329362601041794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325657308101654</t>
+    <t xml:space="preserve">0.329362630844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325657278299332</t>
   </si>
   <si>
     <t xml:space="preserve">0.338420122861862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346654176712036</t>
+    <t xml:space="preserve">0.346654146909714</t>
   </si>
   <si>
     <t xml:space="preserve">0.35571163892746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359005242586136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370121240615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377943634986877</t>
+    <t xml:space="preserve">0.359005272388458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370121270418167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377943605184555</t>
   </si>
   <si>
     <t xml:space="preserve">0.38164895772934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390294760465622</t>
+    <t xml:space="preserve">0.3902947306633</t>
   </si>
   <si>
     <t xml:space="preserve">0.395235151052475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399763882160187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38947132229805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401822417974472</t>
+    <t xml:space="preserve">0.399763911962509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389471262693405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401822447776794</t>
   </si>
   <si>
     <t xml:space="preserve">0.411703288555145</t>
@@ -2675,13 +2672,13 @@
     <t xml:space="preserve">0.402234107255936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403469204902649</t>
+    <t xml:space="preserve">0.403469234704971</t>
   </si>
   <si>
     <t xml:space="preserve">0.409644782543182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408409655094147</t>
+    <t xml:space="preserve">0.408409684896469</t>
   </si>
   <si>
     <t xml:space="preserve">0.40593945980072</t>
@@ -2690,7 +2687,7 @@
     <t xml:space="preserve">0.406351149082184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400175631046295</t>
+    <t xml:space="preserve">0.400175601243973</t>
   </si>
   <si>
     <t xml:space="preserve">0.397705405950546</t>
@@ -2699,40 +2696,40 @@
     <t xml:space="preserve">0.403880923986435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403057545423508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394823491573334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417467147111893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433111846446991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430641651153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441345930099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454520374536514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442992717027664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488280117511749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50392484664917</t>
+    <t xml:space="preserve">0.403057515621185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394823461771011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417467176914215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433111876249313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430641680955887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44134595990181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454520434141159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442992687225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488280087709427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503924906253815</t>
   </si>
   <si>
     <t xml:space="preserve">0.534390866756439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518746078014374</t>
+    <t xml:space="preserve">0.518746197223663</t>
   </si>
   <si>
     <t xml:space="preserve">0.522039771080017</t>
@@ -2741,85 +2738,88 @@
     <t xml:space="preserve">0.500631213188171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517922818660736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469341784715652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485809832811356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462754487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472635328769684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493220567703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573691368103</t>
+    <t xml:space="preserve">0.517922759056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46934175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485809862613678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462754458189011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472635388374329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493220508098602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491573750972748</t>
   </si>
   <si>
     <t xml:space="preserve">0.48169282078743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467694967985153</t>
+    <t xml:space="preserve">0.467694938182831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460943937302</t>
   </si>
   <si>
     <t xml:space="preserve">0.461107671260834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476752430200577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47922271490097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477575838565826</t>
+    <t xml:space="preserve">0.476752400398254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479222595691681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477575898170471</t>
   </si>
   <si>
     <t xml:space="preserve">0.51545250415802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504748165607452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.501454710960388</t>
+    <t xml:space="preserve">0.504748225212097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.501454591751099</t>
   </si>
   <si>
     <t xml:space="preserve">0.498984396457672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494043946266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505571663379669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490750342607498</t>
+    <t xml:space="preserve">0.494043976068497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505571722984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490750402212143</t>
   </si>
   <si>
     <t xml:space="preserve">0.484986484050751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492397159337997</t>
+    <t xml:space="preserve">0.492397129535675</t>
   </si>
   <si>
     <t xml:space="preserve">0.482516258955002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478399187326431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473458796739578</t>
+    <t xml:space="preserve">0.478399157524109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473458826541901</t>
   </si>
   <si>
     <t xml:space="preserve">0.470988571643829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470165133476257</t>
+    <t xml:space="preserve">0.47016516327858</t>
   </si>
   <si>
     <t xml:space="preserve">0.46522468328476</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">0.460284292697906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468518376350403</t>
+    <t xml:space="preserve">0.46851834654808</t>
   </si>
   <si>
     <t xml:space="preserve">0.466750353574753</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">0.457910388708115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461446404457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464098364114761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454374372959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441114455461502</t>
+    <t xml:space="preserve">0.46144637465477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464098334312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454374402761459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44111442565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.420782536268234</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">0.435810476541519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438462436199188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427412480115891</t>
+    <t xml:space="preserve">0.438462466001511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427412509918213</t>
   </si>
   <si>
     <t xml:space="preserve">0.426528483629227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433158457279205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448186427354813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441998422145844</t>
+    <t xml:space="preserve">0.433158487081528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448186457157135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441998451948166</t>
   </si>
   <si>
     <t xml:space="preserve">0.434484452009201</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">0.449070423841476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437578469514847</t>
+    <t xml:space="preserve">0.437578439712524</t>
   </si>
   <si>
     <t xml:space="preserve">0.433600455522537</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">0.430948466062546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431390464305878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434926450252533</t>
+    <t xml:space="preserve">0.4313904941082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434926480054855</t>
   </si>
   <si>
     <t xml:space="preserve">0.429622501134872</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">0.419456511735916</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417246490716934</t>
+    <t xml:space="preserve">0.417246520519257</t>
   </si>
   <si>
     <t xml:space="preserve">0.411942541599274</t>
@@ -2936,22 +2936,22 @@
     <t xml:space="preserve">0.41813051700592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42255049943924</t>
+    <t xml:space="preserve">0.422550469636917</t>
   </si>
   <si>
     <t xml:space="preserve">0.413710534572601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.425202488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423876523971558</t>
+    <t xml:space="preserve">0.425202518701553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423876464366913</t>
   </si>
   <si>
     <t xml:space="preserve">0.414594531059265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422992497682571</t>
+    <t xml:space="preserve">0.422992527484894</t>
   </si>
   <si>
     <t xml:space="preserve">0.421224534511566</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">0.408406555652618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412384569644928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41105854511261</t>
+    <t xml:space="preserve">0.412384539842606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411058515310287</t>
   </si>
   <si>
     <t xml:space="preserve">0.409732550382614</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">0.407964557409286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423434495925903</t>
+    <t xml:space="preserve">0.423434525728226</t>
   </si>
   <si>
     <t xml:space="preserve">0.420340478420258</t>
@@ -2993,16 +2993,16 @@
     <t xml:space="preserve">0.428296476602554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424760520458221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422108471393585</t>
+    <t xml:space="preserve">0.424760490655899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422108501195908</t>
   </si>
   <si>
     <t xml:space="preserve">0.415478527545929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402218550443649</t>
+    <t xml:space="preserve">0.402218610048294</t>
   </si>
   <si>
     <t xml:space="preserve">0.394262611865997</t>
@@ -3017,40 +3017,40 @@
     <t xml:space="preserve">0.39249461889267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396030634641647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405754566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403544574975967</t>
+    <t xml:space="preserve">0.396030604839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405754536390305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403544545173645</t>
   </si>
   <si>
     <t xml:space="preserve">0.400450587272644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389842659235001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388958603143692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395146608352661</t>
+    <t xml:space="preserve">0.389842629432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388958632946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395146578550339</t>
   </si>
   <si>
     <t xml:space="preserve">0.386748641729355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393378555774689</t>
+    <t xml:space="preserve">0.393378585577011</t>
   </si>
   <si>
     <t xml:space="preserve">0.403102576732635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396914601325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39779856801033</t>
+    <t xml:space="preserve">0.396914571523666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397798597812653</t>
   </si>
   <si>
     <t xml:space="preserve">0.40177658200264</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660578489304</t>
+    <t xml:space="preserve">0.402660548686981</t>
   </si>
   <si>
     <t xml:space="preserve">0.419898509979248</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">0.436694443225861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443766415119171</t>
+    <t xml:space="preserve">0.443766385316849</t>
   </si>
   <si>
     <t xml:space="preserve">0.453789889812469</t>
@@ -3098,10 +3098,10 @@
     <t xml:space="preserve">0.468369513750076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480215430259705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482949048280716</t>
+    <t xml:space="preserve">0.480215400457382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482949018478394</t>
   </si>
   <si>
     <t xml:space="preserve">0.481126666069031</t>
@@ -3125,10 +3125,10 @@
     <t xml:space="preserve">0.523042976856232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529421448707581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525776624679565</t>
+    <t xml:space="preserve">0.529421508312225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52577668428421</t>
   </si>
   <si>
     <t xml:space="preserve">0.523954212665558</t>
@@ -3143,40 +3143,40 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753149986267</t>
+    <t xml:space="preserve">0.515753209590912</t>
   </si>
   <si>
     <t xml:space="preserve">0.507552146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511197030544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514841973781586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519398093223572</t>
+    <t xml:space="preserve">0.511197090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514841914176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519398033618927</t>
   </si>
   <si>
     <t xml:space="preserve">0.513930678367615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524865448474884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509374618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526687860488892</t>
+    <t xml:space="preserve">0.524865388870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509374558925629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526687920093536</t>
   </si>
   <si>
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546734809875488</t>
+    <t xml:space="preserve">0.541267454624176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546734869480133</t>
   </si>
   <si>
     <t xml:space="preserve">0.537622511386871</t>
@@ -3197,10 +3197,10 @@
     <t xml:space="preserve">0.569515407085419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562225580215454</t>
+    <t xml:space="preserve">0.565870463848114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562225639820099</t>
   </si>
   <si>
     <t xml:space="preserve">0.551290929317474</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">0.548557281494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550379693508148</t>
+    <t xml:space="preserve">0.550379633903503</t>
   </si>
   <si>
     <t xml:space="preserve">0.547646045684814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555847108364105</t>
+    <t xml:space="preserve">0.55584704875946</t>
   </si>
   <si>
     <t xml:space="preserve">0.553113341331482</t>
@@ -3227,22 +3227,22 @@
     <t xml:space="preserve">0.559491991996765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561314404010773</t>
+    <t xml:space="preserve">0.561314344406128</t>
   </si>
   <si>
     <t xml:space="preserve">0.558580696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556758224964142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542178690433502</t>
+    <t xml:space="preserve">0.556758284568787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542178750038147</t>
   </si>
   <si>
     <t xml:space="preserve">0.557669520378113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534888923168182</t>
+    <t xml:space="preserve">0.534888863563538</t>
   </si>
   <si>
     <t xml:space="preserve">0.528510332107544</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">0.535800099372864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530332803726196</t>
+    <t xml:space="preserve">0.530332744121552</t>
   </si>
   <si>
     <t xml:space="preserve">0.527599096298218</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617466211319</t>
+    <t xml:space="preserve">0.496617496013641</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">0.505729734897614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494794964790344</t>
+    <t xml:space="preserve">0.494794994592667</t>
   </si>
   <si>
     <t xml:space="preserve">0.499351114034653</t>
@@ -3284,16 +3284,16 @@
     <t xml:space="preserve">0.492061376571655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488416492938995</t>
+    <t xml:space="preserve">0.488416433334351</t>
   </si>
   <si>
     <t xml:space="preserve">0.483860343694687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487505227327347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495706290006638</t>
+    <t xml:space="preserve">0.487505257129669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495706230401993</t>
   </si>
   <si>
     <t xml:space="preserve">0.49388375878334</t>
@@ -49708,7 +49708,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1745" t="s">
-        <v>851</v>
+        <v>770</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49734,7 +49734,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1746" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49760,7 +49760,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1747" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49838,7 +49838,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1750" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49864,7 +49864,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G1751" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49890,7 +49890,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1752" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49916,7 +49916,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1753" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49942,7 +49942,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1754" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49968,7 +49968,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1755" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49994,7 +49994,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1756" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -50020,7 +50020,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1757" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50046,7 +50046,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1758" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -50098,7 +50098,7 @@
         <v>0.41949999332428</v>
       </c>
       <c r="G1760" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50124,7 +50124,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1761" t="s">
-        <v>851</v>
+        <v>770</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50150,7 +50150,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1762" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50202,7 +50202,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1764" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -50228,7 +50228,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1765" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50254,7 +50254,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1766" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -50280,7 +50280,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1767" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50306,7 +50306,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1768" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -50332,7 +50332,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1769" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -50358,7 +50358,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1770" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50384,7 +50384,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1771" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50436,7 +50436,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1773" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50462,7 +50462,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1774" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50488,7 +50488,7 @@
         <v>0.403499990701675</v>
       </c>
       <c r="G1775" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50540,7 +50540,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1777" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50566,7 +50566,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1778" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50618,7 +50618,7 @@
         <v>0.395500004291534</v>
       </c>
       <c r="G1780" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50670,7 +50670,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1782" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50696,7 +50696,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1783" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50722,7 +50722,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1784" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50748,7 +50748,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1785" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50774,7 +50774,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1786" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50800,7 +50800,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1787" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50852,7 +50852,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1789" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50878,7 +50878,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1790" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50904,7 +50904,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1791" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50930,7 +50930,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1792" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50982,7 +50982,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51008,7 +51008,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1795" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -51034,7 +51034,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1796" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -51060,7 +51060,7 @@
         <v>0.449499994516373</v>
       </c>
       <c r="G1797" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51086,7 +51086,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G1798" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51112,7 +51112,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1799" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51138,7 +51138,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G1800" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -51164,7 +51164,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1801" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -51190,7 +51190,7 @@
         <v>0.485500007867813</v>
       </c>
       <c r="G1802" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -51216,7 +51216,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1803" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51242,7 +51242,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1804" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -51268,7 +51268,7 @@
         <v>0.5</v>
       </c>
       <c r="G1805" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -51294,7 +51294,7 @@
         <v>0.488499999046326</v>
       </c>
       <c r="G1806" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51320,7 +51320,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -51346,7 +51346,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G1808" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51372,7 +51372,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1809" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51398,7 +51398,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1810" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51424,7 +51424,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1811" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51450,7 +51450,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1812" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51476,7 +51476,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1813" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51502,7 +51502,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1814" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51528,7 +51528,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1815" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51554,7 +51554,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1816" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51580,7 +51580,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1817" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51606,7 +51606,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1818" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51632,7 +51632,7 @@
         <v>0.489499986171722</v>
       </c>
       <c r="G1819" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51658,7 +51658,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1820" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51684,7 +51684,7 @@
         <v>0.5</v>
       </c>
       <c r="G1821" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51710,7 +51710,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1822" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51736,7 +51736,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1823" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51762,7 +51762,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1824" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51788,7 +51788,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1825" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51814,7 +51814,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1826" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51840,7 +51840,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1827" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51866,7 +51866,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G1828" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51892,7 +51892,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1829" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51918,7 +51918,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G1830" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51944,7 +51944,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1831" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51970,7 +51970,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1832" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51996,7 +51996,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1833" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52022,7 +52022,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G1834" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -52048,7 +52048,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1835" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52074,7 +52074,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1836" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52100,7 +52100,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1837" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52126,7 +52126,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1838" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -52152,7 +52152,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1839" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -52178,7 +52178,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1840" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52204,7 +52204,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G1841" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52230,7 +52230,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1842" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52256,7 +52256,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1843" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52282,7 +52282,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1844" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52308,7 +52308,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1845" t="s">
-        <v>363</v>
+        <v>917</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52386,7 +52386,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1848" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52490,7 +52490,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1852" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52880,7 +52880,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1867" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52932,7 +52932,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1869" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52984,7 +52984,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1871" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53036,7 +53036,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1873" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53114,7 +53114,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>363</v>
+        <v>917</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -69866,7 +69866,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6910763889</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>458431</v>
@@ -69887,6 +69887,32 @@
         <v>1331</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.6912847222</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>233981</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>0.555999994277954</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>0.564000010490417</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>0.564000010490417</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="1332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="1333">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333736151456833</t>
+    <t xml:space="preserve">0.333736181259155</t>
   </si>
   <si>
     <t xml:space="preserve">IMS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327446222305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32115626335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317678362131119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307318508625031</t>
+    <t xml:space="preserve">0.32744625210762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321156322956085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317678391933441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307318449020386</t>
   </si>
   <si>
     <t xml:space="preserve">0.288448721170425</t>
@@ -65,25 +65,25 @@
     <t xml:space="preserve">0.294368624687195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285636723041534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273796886205673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258996993303299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258257031440735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243605226278305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.246417164802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262696951627731</t>
+    <t xml:space="preserve">0.285636752843857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273796826601028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258997052907944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258257061243057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243605211377144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.246417179703712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262697011232376</t>
   </si>
   <si>
     <t xml:space="preserve">0.256407082080841</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">0.284600764513016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277496844530106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.287116706371307</t>
+    <t xml:space="preserve">0.277496814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287116676568985</t>
   </si>
   <si>
     <t xml:space="preserve">0.290742665529251</t>
@@ -119,40 +119,40 @@
     <t xml:space="preserve">0.263806998729706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25677701830864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.250117123126984</t>
+    <t xml:space="preserve">0.256777077913284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.250117152929306</t>
   </si>
   <si>
     <t xml:space="preserve">0.277570813894272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297994613647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310796409845352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303544521331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304358512163162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318122357130051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309686452150345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30162051320076</t>
+    <t xml:space="preserve">0.297994643449783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310796439647675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303544491529465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304358541965485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318122297525406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309686422348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301620543003082</t>
   </si>
   <si>
     <t xml:space="preserve">0.310352444648743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323376268148422</t>
+    <t xml:space="preserve">0.323376327753067</t>
   </si>
   <si>
     <t xml:space="preserve">0.320046335458755</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">0.316716372966766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315236359834671</t>
+    <t xml:space="preserve">0.315236419439316</t>
   </si>
   <si>
     <t xml:space="preserve">0.315606355667114</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">0.332256197929382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328852266073227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330480188131332</t>
+    <t xml:space="preserve">0.328852206468582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330480217933655</t>
   </si>
   <si>
     <t xml:space="preserve">0.311240434646606</t>
@@ -185,28 +185,28 @@
     <t xml:space="preserve">0.312054455280304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2996965944767</t>
+    <t xml:space="preserve">0.299696564674377</t>
   </si>
   <si>
     <t xml:space="preserve">0.296884596347809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299400568008423</t>
+    <t xml:space="preserve">0.2994005382061</t>
   </si>
   <si>
     <t xml:space="preserve">0.29747661948204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295996636152267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293702661991119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298216581344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286376744508743</t>
+    <t xml:space="preserve">0.295996576547623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293702632188797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298216611146927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286376714706421</t>
   </si>
   <si>
     <t xml:space="preserve">0.276756823062897</t>
@@ -215,25 +215,25 @@
     <t xml:space="preserve">0.274536848068237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2723169028759</t>
+    <t xml:space="preserve">0.272316843271255</t>
   </si>
   <si>
     <t xml:space="preserve">0.268542915582657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270466893911362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265064984560013</t>
+    <t xml:space="preserve">0.270466864109039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26506495475769</t>
   </si>
   <si>
     <t xml:space="preserve">0.268172919750214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268616944551468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269208878278732</t>
+    <t xml:space="preserve">0.268616914749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269208908081055</t>
   </si>
   <si>
     <t xml:space="preserve">0.275276869535446</t>
@@ -242,31 +242,31 @@
     <t xml:space="preserve">0.284896731376648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290002703666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30820643901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309168457984924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318196386098862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31693834066391</t>
+    <t xml:space="preserve">0.290002673864365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308206468820572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309168428182602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318196356296539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316938370466232</t>
   </si>
   <si>
     <t xml:space="preserve">0.308946460485458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314200401306152</t>
+    <t xml:space="preserve">0.31420037150383</t>
   </si>
   <si>
     <t xml:space="preserve">0.321378320455551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31938037276268</t>
+    <t xml:space="preserve">0.319380313158035</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722440481186</t>
@@ -278,31 +278,31 @@
     <t xml:space="preserve">0.313312441110611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30709645152092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307614475488663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304950505495071</t>
+    <t xml:space="preserve">0.307096481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30761444568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304950475692749</t>
   </si>
   <si>
     <t xml:space="preserve">0.305616497993469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299548596143723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305320531129837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295626670122147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300954550504684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314400285482407</t>
+    <t xml:space="preserve">0.2995485663414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305320501327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295626640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300954520702362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314400315284729</t>
   </si>
   <si>
     <t xml:space="preserve">0.318779826164246</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.319932252168655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318088293075562</t>
+    <t xml:space="preserve">0.318088263273239</t>
   </si>
   <si>
     <t xml:space="preserve">0.307331681251526</t>
@@ -332,19 +332,19 @@
     <t xml:space="preserve">0.311557501554489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305795013904572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301569193601608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295806705951691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299648374319077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29657506942749</t>
+    <t xml:space="preserve">0.305795043706894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301569253206253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295806765556335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299648344516754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296575099229813</t>
   </si>
   <si>
     <t xml:space="preserve">0.303490042686462</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">0.31424668431282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318011432886124</t>
+    <t xml:space="preserve">0.318011462688446</t>
   </si>
   <si>
     <t xml:space="preserve">0.318702936172485</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">0.310020834207535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311941653490067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311173349618912</t>
+    <t xml:space="preserve">0.311941623687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311173319816589</t>
   </si>
   <si>
     <t xml:space="preserve">0.30725485086441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306717038154602</t>
+    <t xml:space="preserve">0.30671700835228</t>
   </si>
   <si>
     <t xml:space="preserve">0.305564552545547</t>
@@ -383,58 +383,58 @@
     <t xml:space="preserve">0.304949879646301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306870669126511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297727555036545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301799714565277</t>
+    <t xml:space="preserve">0.306870698928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297727525234222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301799744367599</t>
   </si>
   <si>
     <t xml:space="preserve">0.304027855396271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300032585859299</t>
+    <t xml:space="preserve">0.300032556056976</t>
   </si>
   <si>
     <t xml:space="preserve">0.313478291034698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312556326389313</t>
+    <t xml:space="preserve">0.31255629658699</t>
   </si>
   <si>
     <t xml:space="preserve">0.307869523763657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311480671167374</t>
+    <t xml:space="preserve">0.311480641365051</t>
   </si>
   <si>
     <t xml:space="preserve">0.298265397548676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299110561609268</t>
+    <t xml:space="preserve">0.299110502004623</t>
   </si>
   <si>
     <t xml:space="preserve">0.305257201194763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295576214790344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295960396528244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297650724649429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297881215810776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293732225894928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298803210258484</t>
+    <t xml:space="preserve">0.295576244592667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295960426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297650754451752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297881245613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293732285499573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298803269863129</t>
   </si>
   <si>
     <t xml:space="preserve">0.300416707992554</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">0.300109386444092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298880070447922</t>
+    <t xml:space="preserve">0.298880040645599</t>
   </si>
   <si>
     <t xml:space="preserve">0.30548769235611</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">0.303105890750885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303566873073578</t>
+    <t xml:space="preserve">0.303566843271255</t>
   </si>
   <si>
     <t xml:space="preserve">0.308253675699234</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">0.306563347578049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30018624663353</t>
+    <t xml:space="preserve">0.300186216831207</t>
   </si>
   <si>
     <t xml:space="preserve">0.298649579286575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296421378850937</t>
+    <t xml:space="preserve">0.296421408653259</t>
   </si>
   <si>
     <t xml:space="preserve">0.3014155626297</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">0.300647228956223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282975614070892</t>
+    <t xml:space="preserve">0.282975643873215</t>
   </si>
   <si>
     <t xml:space="preserve">0.29196509718895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289736956357956</t>
+    <t xml:space="preserve">0.289736926555634</t>
   </si>
   <si>
     <t xml:space="preserve">0.293501734733582</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">0.292656570672989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29250293970108</t>
+    <t xml:space="preserve">0.292502909898758</t>
   </si>
   <si>
     <t xml:space="preserve">0.289583265781403</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">0.288123488426208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284281849861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28789296746254</t>
+    <t xml:space="preserve">0.284281820058823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.287892997264862</t>
   </si>
   <si>
     <t xml:space="preserve">0.290044277906418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292887091636658</t>
+    <t xml:space="preserve">0.29288712143898</t>
   </si>
   <si>
     <t xml:space="preserve">0.293117612600327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291888266801834</t>
+    <t xml:space="preserve">0.291888296604156</t>
   </si>
   <si>
     <t xml:space="preserve">0.289813786745071</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">0.286586791276932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294270098209381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291811436414719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292579799890518</t>
+    <t xml:space="preserve">0.294270068407059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291811406612396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292579770088196</t>
   </si>
   <si>
     <t xml:space="preserve">0.295729905366898</t>
@@ -548,52 +548,52 @@
     <t xml:space="preserve">0.294731080532074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287355095148087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293809086084366</t>
+    <t xml:space="preserve">0.287355124950409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293809056282043</t>
   </si>
   <si>
     <t xml:space="preserve">0.292041957378387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.286740452051163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284665942192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278903514146805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275599718093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270221382379532</t>
+    <t xml:space="preserve">0.28674042224884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2846659719944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278903484344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27559968829155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270221412181854</t>
   </si>
   <si>
     <t xml:space="preserve">0.272449553012848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276675373315811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273986220359802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275676548480988</t>
+    <t xml:space="preserve">0.276675343513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27398619055748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275676518678665</t>
   </si>
   <si>
     <t xml:space="preserve">0.275522857904434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276598513126373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270989686250687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27114337682724</t>
+    <t xml:space="preserve">0.276598542928696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270989716053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271143406629562</t>
   </si>
   <si>
     <t xml:space="preserve">0.274293512105942</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">0.270451873540878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268146872520447</t>
+    <t xml:space="preserve">0.268146932125092</t>
   </si>
   <si>
     <t xml:space="preserve">0.267378568649292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.264612525701523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265765070915222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262384414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267532229423523</t>
+    <t xml:space="preserve">0.264612585306168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265765100717545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262384474277496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267532199621201</t>
   </si>
   <si>
     <t xml:space="preserve">0.265304088592529</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">0.271911710500717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272526383399963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283282995223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279902338981628</t>
+    <t xml:space="preserve">0.272526353597641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283282965421677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279902309179306</t>
   </si>
   <si>
     <t xml:space="preserve">0.277059525251389</t>
@@ -641,22 +641,22 @@
     <t xml:space="preserve">0.27844250202179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.280517011880875</t>
+    <t xml:space="preserve">0.280517041683197</t>
   </si>
   <si>
     <t xml:space="preserve">0.278749823570251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27898034453392</t>
+    <t xml:space="preserve">0.278980374336243</t>
   </si>
   <si>
     <t xml:space="preserve">0.278212010860443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284051299095154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290812641382217</t>
+    <t xml:space="preserve">0.284051328897476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290812611579895</t>
   </si>
   <si>
     <t xml:space="preserve">0.28966012597084</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">0.290428429841995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294807940721512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295422583818436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288507580757141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284589141607285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291043102741241</t>
+    <t xml:space="preserve">0.294807910919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295422613620758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288507610559464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284589171409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291043132543564</t>
   </si>
   <si>
     <t xml:space="preserve">0.293885916471481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294884741306305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289890587329865</t>
+    <t xml:space="preserve">0.294884771108627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289890617132187</t>
   </si>
   <si>
     <t xml:space="preserve">0.286125808954239</t>
@@ -695,46 +695,46 @@
     <t xml:space="preserve">0.284358620643616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282745182514191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277290046215057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281976819038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276214361190796</t>
+    <t xml:space="preserve">0.282745152711868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277290016412735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281976848840714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276214331388474</t>
   </si>
   <si>
     <t xml:space="preserve">0.273602038621902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269760400056839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275061845779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271834880113602</t>
+    <t xml:space="preserve">0.269760370254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275061875581741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271834850311279</t>
   </si>
   <si>
     <t xml:space="preserve">0.273371547460556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275215566158295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276905864477158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274831354618073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282668322324753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280440181493759</t>
+    <t xml:space="preserve">0.275215536355972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276905804872513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27483132481575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28266829252243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280440151691437</t>
   </si>
   <si>
     <t xml:space="preserve">0.279595017433167</t>
@@ -743,16 +743,16 @@
     <t xml:space="preserve">0.27736684679985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278135150671005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281208485364914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278672963380814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282591491937637</t>
+    <t xml:space="preserve">0.278135180473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281208455562592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278673022985458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28259152173996</t>
   </si>
   <si>
     <t xml:space="preserve">0.279364496469498</t>
@@ -761,37 +761,37 @@
     <t xml:space="preserve">0.285587966442108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279671847820282</t>
+    <t xml:space="preserve">0.27967181801796</t>
   </si>
   <si>
     <t xml:space="preserve">0.28666365146637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284435480833054</t>
+    <t xml:space="preserve">0.284435510635376</t>
   </si>
   <si>
     <t xml:space="preserve">0.281899988651276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283897697925568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285280615091324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285434275865555</t>
+    <t xml:space="preserve">0.283897668123245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285280644893646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285434305667877</t>
   </si>
   <si>
     <t xml:space="preserve">0.295038431882858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304258346557617</t>
+    <t xml:space="preserve">0.304258406162262</t>
   </si>
   <si>
     <t xml:space="preserve">0.321929931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32561793923378</t>
+    <t xml:space="preserve">0.325617909431458</t>
   </si>
   <si>
     <t xml:space="preserve">0.33184140920639</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">0.311096489429474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313094168901443</t>
+    <t xml:space="preserve">0.313094139099121</t>
   </si>
   <si>
     <t xml:space="preserve">0.313017338514328</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">0.297266572713852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298111766576767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310251325368881</t>
+    <t xml:space="preserve">0.298111736774445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310251355171204</t>
   </si>
   <si>
     <t xml:space="preserve">0.313555151224136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300800889730453</t>
+    <t xml:space="preserve">0.300800859928131</t>
   </si>
   <si>
     <t xml:space="preserve">0.30886834859848</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">0.299725234508514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32185310125351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327308267354965</t>
+    <t xml:space="preserve">0.321853131055832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327308237552643</t>
   </si>
   <si>
     <t xml:space="preserve">0.318472445011139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312095284461975</t>
+    <t xml:space="preserve">0.312095314264297</t>
   </si>
   <si>
     <t xml:space="preserve">0.314016133546829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31501492857933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312249004840851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313939303159714</t>
+    <t xml:space="preserve">0.315014988183975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312248975038528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313939332962036</t>
   </si>
   <si>
     <t xml:space="preserve">0.309636652469635</t>
@@ -881,25 +881,25 @@
     <t xml:space="preserve">0.307408511638641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308945178985596</t>
+    <t xml:space="preserve">0.308945208787918</t>
   </si>
   <si>
     <t xml:space="preserve">0.313631981611252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308023154735565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307715862989426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309022009372711</t>
+    <t xml:space="preserve">0.308023184537888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307715833187103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309021979570389</t>
   </si>
   <si>
     <t xml:space="preserve">0.309944003820419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317780911922455</t>
+    <t xml:space="preserve">0.3177809715271</t>
   </si>
   <si>
     <t xml:space="preserve">0.316551625728607</t>
@@ -914,22 +914,22 @@
     <t xml:space="preserve">0.325003266334534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318318754434586</t>
+    <t xml:space="preserve">0.318318784236908</t>
   </si>
   <si>
     <t xml:space="preserve">0.317704141139984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321545779705048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320470154285431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621405124664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323697060346603</t>
+    <t xml:space="preserve">0.32154580950737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320470124483109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621434926987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323697090148926</t>
   </si>
   <si>
     <t xml:space="preserve">0.333454847335815</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">0.339524686336517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345671325922012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340446710586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3333780169487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33499151468277</t>
+    <t xml:space="preserve">0.34567129611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340446650981903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333378046751022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334991544485092</t>
   </si>
   <si>
     <t xml:space="preserve">0.336144030094147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337757527828217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338909983634949</t>
+    <t xml:space="preserve">0.337757498025894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338910043239594</t>
   </si>
   <si>
     <t xml:space="preserve">0.338141709566116</t>
@@ -974,46 +974,46 @@
     <t xml:space="preserve">0.350358098745346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346593290567398</t>
+    <t xml:space="preserve">0.34659332036972</t>
   </si>
   <si>
     <t xml:space="preserve">0.344211488962173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340677201747894</t>
+    <t xml:space="preserve">0.34067714214325</t>
   </si>
   <si>
     <t xml:space="preserve">0.334607362747192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338218539953232</t>
+    <t xml:space="preserve">0.338218510150909</t>
   </si>
   <si>
     <t xml:space="preserve">0.346900641918182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346132338047028</t>
+    <t xml:space="preserve">0.346132308244705</t>
   </si>
   <si>
     <t xml:space="preserve">0.339601516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340907663106918</t>
+    <t xml:space="preserve">0.340907633304596</t>
   </si>
   <si>
     <t xml:space="preserve">0.3526631295681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369950503110886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36541736125946</t>
+    <t xml:space="preserve">0.369950532913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365417391061783</t>
   </si>
   <si>
     <t xml:space="preserve">0.363035559654236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374099493026733</t>
+    <t xml:space="preserve">0.374099463224411</t>
   </si>
   <si>
     <t xml:space="preserve">0.371103048324585</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">0.368798017501831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366108894348145</t>
+    <t xml:space="preserve">0.366108864545822</t>
   </si>
   <si>
     <t xml:space="preserve">0.363112390041351</t>
@@ -1037,31 +1037,31 @@
     <t xml:space="preserve">0.366877198219299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366262555122375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361114740371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359885424375534</t>
+    <t xml:space="preserve">0.366262525320053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361114770174026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359885394573212</t>
   </si>
   <si>
     <t xml:space="preserve">0.35919389128685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368567556142807</t>
+    <t xml:space="preserve">0.368567496538162</t>
   </si>
   <si>
     <t xml:space="preserve">0.372024983167648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375559329986572</t>
+    <t xml:space="preserve">0.37555930018425</t>
   </si>
   <si>
     <t xml:space="preserve">0.380246132612228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392616152763367</t>
+    <t xml:space="preserve">0.392616212368011</t>
   </si>
   <si>
     <t xml:space="preserve">0.405677825212479</t>
@@ -1070,46 +1070,46 @@
     <t xml:space="preserve">0.421044409275055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419507741928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396842032670975</t>
+    <t xml:space="preserve">0.419507771730423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396842062473297</t>
   </si>
   <si>
     <t xml:space="preserve">0.413361102342606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422581017017365</t>
+    <t xml:space="preserve">0.422581076622009</t>
   </si>
   <si>
     <t xml:space="preserve">0.417586892843246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426422715187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423349380493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427959322929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436795175075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432953506708145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452930122613907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460824728012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465223342180252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468296706676483</t>
+    <t xml:space="preserve">0.42642268538475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423349410295486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427959382534027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436795145273209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4329534471035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452930063009262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459460884332657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465223371982574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468296676874161</t>
   </si>
   <si>
     <t xml:space="preserve">0.481358259916306</t>
@@ -1121,37 +1121,37 @@
     <t xml:space="preserve">0.515164732933044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505560636520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50709730386734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515548944473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503255605697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489809930324554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480205684900284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519006431102753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511323034763336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499413967132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491730719804764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484431564807892</t>
+    <t xml:space="preserve">0.505560576915741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507097244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515548884868622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503255546092987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489809840917587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480205774307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519006371498108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511323094367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499413996934891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491730690002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484431535005569</t>
   </si>
   <si>
     <t xml:space="preserve">0.483663201332092</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">0.484815776348114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495188236236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490193963050842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553197026252747</t>
+    <t xml:space="preserve">0.49518820643425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490194022655487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553197085857391</t>
   </si>
   <si>
     <t xml:space="preserve">0.542056262493134</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">0.586235225200653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600065171718597</t>
+    <t xml:space="preserve">0.600065112113953</t>
   </si>
   <si>
     <t xml:space="preserve">0.582393527030945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572021067142487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572789430618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552428722381592</t>
+    <t xml:space="preserve">0.572021126747131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572789490222931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552428662776947</t>
   </si>
   <si>
     <t xml:space="preserve">0.55127614736557</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">0.545129597187042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565874516963959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577015161514282</t>
+    <t xml:space="preserve">0.565874457359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577015221118927</t>
   </si>
   <si>
     <t xml:space="preserve">0.596607625484467</t>
@@ -1214,67 +1214,67 @@
     <t xml:space="preserve">0.608132541179657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621962428092957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620425879955292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629645764827728</t>
+    <t xml:space="preserve">0.621962487697601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620425820350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629645824432373</t>
   </si>
   <si>
     <t xml:space="preserve">0.614279210567474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60774838924408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581625282764435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560880362987518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598528444766998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598144233226776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619657456874847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618120849132538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601601779460907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58661937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59545511007309</t>
+    <t xml:space="preserve">0.607748448848724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58162522315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560880303382874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598528385162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598144292831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619657516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618120789527893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601601719856262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586619317531586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595455050468445</t>
   </si>
   <si>
     <t xml:space="preserve">0.587771832942963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584314465522766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577399373054504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567026853561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57432609796524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543592870235443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564721941947937</t>
+    <t xml:space="preserve">0.584314405918121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577399432659149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567026913166046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574326157569885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543592929840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564722001552582</t>
   </si>
   <si>
     <t xml:space="preserve">0.563185334205627</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">0.587003469467163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604675054550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629261672496796</t>
+    <t xml:space="preserve">0.60467517375946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629261612892151</t>
   </si>
   <si>
     <t xml:space="preserve">0.61850506067276</t>
@@ -1304,13 +1304,13 @@
     <t xml:space="preserve">0.606980085372925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603138387203217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612358391284943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611590027809143</t>
+    <t xml:space="preserve">0.603138506412506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612358331680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611590087413788</t>
   </si>
   <si>
     <t xml:space="preserve">0.59391850233078</t>
@@ -1319,34 +1319,34 @@
     <t xml:space="preserve">0.596991777420044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608516693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599296748638153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589308559894562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553965330123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538598775863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55703866481781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536293745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524000525474548</t>
+    <t xml:space="preserve">0.608516812324524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599296689033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589308500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553965449333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538598716259003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557038724422455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536293864250183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524000465869904</t>
   </si>
   <si>
     <t xml:space="preserve">0.537830471992493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547818779945374</t>
+    <t xml:space="preserve">0.547818720340729</t>
   </si>
   <si>
     <t xml:space="preserve">0.53245210647583</t>
@@ -1358,13 +1358,13 @@
     <t xml:space="preserve">0.527073800563812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520927250385284</t>
+    <t xml:space="preserve">0.520927131175995</t>
   </si>
   <si>
     <t xml:space="preserve">0.517853915691376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525537252426147</t>
+    <t xml:space="preserve">0.525537192821503</t>
   </si>
   <si>
     <t xml:space="preserve">0.530147135257721</t>
@@ -1376,94 +1376,94 @@
     <t xml:space="preserve">0.51939058303833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524768829345703</t>
+    <t xml:space="preserve">0.524768948554993</t>
   </si>
   <si>
     <t xml:space="preserve">0.549355387687683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501718997955322</t>
+    <t xml:space="preserve">0.501718938350677</t>
   </si>
   <si>
     <t xml:space="preserve">0.492499023675919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477900683879852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476364105939865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488657414913177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471754133701324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472522497177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468680858612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487120777368546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481742411851883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480974107980728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48327910900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478669166564941</t>
+    <t xml:space="preserve">0.477900803089142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476364135742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488657355308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471754193305969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472522467374802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468680828809738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487120717763901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481742382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480974048376083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483279049396515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478669106960297</t>
   </si>
   <si>
     <t xml:space="preserve">0.47021746635437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467912524938583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466375857591629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839190244675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461765855550766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487889021635056</t>
+    <t xml:space="preserve">0.467912554740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466375768184662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839249849319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461765915155411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4878890812397</t>
   </si>
   <si>
     <t xml:space="preserve">0.500182330608368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469449073076248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437179327011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444862574338913</t>
+    <t xml:space="preserve">0.469449102878571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437179356813431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444862693548203</t>
   </si>
   <si>
     <t xml:space="preserve">0.431800991296768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444094270467758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424117714166641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415666162967682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382627934217453</t>
+    <t xml:space="preserve">0.444094300270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424117654561996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415666103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382627964019775</t>
   </si>
   <si>
     <t xml:space="preserve">0.379170447587967</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">0.382243782281876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385701268911362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388774544000626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391847848892212</t>
+    <t xml:space="preserve">0.385701239109039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388774573802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391847878694534</t>
   </si>
   <si>
     <t xml:space="preserve">0.384164601564407</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">0.360346406698227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3522789478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356504738330841</t>
+    <t xml:space="preserve">0.352278918027878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356504708528519</t>
   </si>
   <si>
     <t xml:space="preserve">0.37148717045784</t>
@@ -1508,31 +1508,31 @@
     <t xml:space="preserve">0.368029683828354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37225553393364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365340501070023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374944716691971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366493046283722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374560534954071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374176293611526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378786325454712</t>
+    <t xml:space="preserve">0.372255504131317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365340530872345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374944627285004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366492986679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374560505151749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374176323413849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37878629565239</t>
   </si>
   <si>
     <t xml:space="preserve">0.362267225980759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353815615177155</t>
+    <t xml:space="preserve">0.353815585374832</t>
   </si>
   <si>
     <t xml:space="preserve">0.354583919048309</t>
@@ -1544,28 +1544,28 @@
     <t xml:space="preserve">0.370718836784363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35419973731041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395689576864243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411056131124496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407982796430588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384932965040207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390311241149902</t>
+    <t xml:space="preserve">0.354199767112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39568954706192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411056160926819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407982856035233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38493287563324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390311270952225</t>
   </si>
   <si>
     <t xml:space="preserve">0.378017961978912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380707114934921</t>
+    <t xml:space="preserve">0.380707144737244</t>
   </si>
   <si>
     <t xml:space="preserve">0.362651407718658</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">0.35957807302475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353431433439255</t>
+    <t xml:space="preserve">0.353431463241577</t>
   </si>
   <si>
     <t xml:space="preserve">0.349589824676514</t>
@@ -1598,34 +1598,34 @@
     <t xml:space="preserve">0.349973976612091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339217364788055</t>
+    <t xml:space="preserve">0.339217334985733</t>
   </si>
   <si>
     <t xml:space="preserve">0.323850780725479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361883044242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350742250680923</t>
+    <t xml:space="preserve">0.361883074045181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350742280483246</t>
   </si>
   <si>
     <t xml:space="preserve">0.389542937278748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404141187667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396457821130753</t>
+    <t xml:space="preserve">0.404141157865524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396457850933075</t>
   </si>
   <si>
     <t xml:space="preserve">0.412592768669128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404909521341324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401836186647415</t>
+    <t xml:space="preserve">0.404909461736679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401836156845093</t>
   </si>
   <si>
     <t xml:space="preserve">0.394152909517288</t>
@@ -1634,34 +1634,34 @@
     <t xml:space="preserve">0.399531185626984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40260449051857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40106788277626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397994518280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375712960958481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36457222700119</t>
+    <t xml:space="preserve">0.402604520320892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401067912578583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397994548082352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375712990760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364572197198868</t>
   </si>
   <si>
     <t xml:space="preserve">0.345748126506805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336528241634369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335759848356247</t>
+    <t xml:space="preserve">0.336528182029724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335759878158569</t>
   </si>
   <si>
     <t xml:space="preserve">0.337296515703201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329613208770752</t>
+    <t xml:space="preserve">0.329613238573074</t>
   </si>
   <si>
     <t xml:space="preserve">0.32807657122612</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">0.326924055814743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312709987163544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341138184070587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322698265314102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326155751943588</t>
+    <t xml:space="preserve">0.312710016965866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34113821387291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322698295116425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326155722141266</t>
   </si>
   <si>
     <t xml:space="preserve">0.324619114398956</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">0.325771570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330381602048874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329997390508652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324234932661057</t>
+    <t xml:space="preserve">0.330381572246552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329997420310974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324234962463379</t>
   </si>
   <si>
     <t xml:space="preserve">0.313862472772598</t>
@@ -1709,19 +1709,19 @@
     <t xml:space="preserve">0.301185041666031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30387419462204</t>
+    <t xml:space="preserve">0.303874224424362</t>
   </si>
   <si>
     <t xml:space="preserve">0.29695925116539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302721738815308</t>
+    <t xml:space="preserve">0.302721709012985</t>
   </si>
   <si>
     <t xml:space="preserve">0.32308241724968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308100044727325</t>
+    <t xml:space="preserve">0.308100014925003</t>
   </si>
   <si>
     <t xml:space="preserve">0.310405015945435</t>
@@ -1730,13 +1730,13 @@
     <t xml:space="preserve">0.306947499513626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314630836248398</t>
+    <t xml:space="preserve">0.314630806446075</t>
   </si>
   <si>
     <t xml:space="preserve">0.305410891771317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308484137058258</t>
+    <t xml:space="preserve">0.30848416686058</t>
   </si>
   <si>
     <t xml:space="preserve">0.304642498493195</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">0.320777416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356888890266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358041435480118</t>
+    <t xml:space="preserve">0.356888949871063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358041375875473</t>
   </si>
   <si>
     <t xml:space="preserve">0.356120586395264</t>
@@ -1757,22 +1757,22 @@
     <t xml:space="preserve">0.360730558633804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358809739351273</t>
+    <t xml:space="preserve">0.358809769153595</t>
   </si>
   <si>
     <t xml:space="preserve">0.351126462221146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355736434459686</t>
+    <t xml:space="preserve">0.355736404657364</t>
   </si>
   <si>
     <t xml:space="preserve">0.342290639877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371871322393417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370334655046463</t>
+    <t xml:space="preserve">0.37187135219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370334684848785</t>
   </si>
   <si>
     <t xml:space="preserve">0.383780419826508</t>
@@ -1781,25 +1781,25 @@
     <t xml:space="preserve">0.376097142696381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376865476369858</t>
+    <t xml:space="preserve">0.37686550617218</t>
   </si>
   <si>
     <t xml:space="preserve">0.377249658107758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398762851953506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403372794389725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406446129083633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40951943397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39107957482338</t>
+    <t xml:space="preserve">0.398762881755829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403372824192047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406446099281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409519493579865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391079604625702</t>
   </si>
   <si>
     <t xml:space="preserve">0.381475448608398</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">0.394921183586121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411824494600296</t>
+    <t xml:space="preserve">0.411824434995651</t>
   </si>
   <si>
     <t xml:space="preserve">0.414897799491882</t>
@@ -1826,61 +1826,61 @@
     <t xml:space="preserve">0.397226214408875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408751159906387</t>
+    <t xml:space="preserve">0.40875118970871</t>
   </si>
   <si>
     <t xml:space="preserve">0.410287797451019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414129376411438</t>
+    <t xml:space="preserve">0.41412940621376</t>
   </si>
   <si>
     <t xml:space="preserve">0.416434437036514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418739438056946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420276045799255</t>
+    <t xml:space="preserve">0.418739378452301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420276075601578</t>
   </si>
   <si>
     <t xml:space="preserve">0.421812772750854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430264323949814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473290771245956</t>
+    <t xml:space="preserve">0.430264383554459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473290801048279</t>
   </si>
   <si>
     <t xml:space="preserve">0.49480402469635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484047412872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267387151718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506328880786896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479437470436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48251074552536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475595831871033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46407076716423</t>
+    <t xml:space="preserve">0.484047383069992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267357349396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506328940391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479437440633774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482510715723038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47559580206871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464070796966553</t>
   </si>
   <si>
     <t xml:space="preserve">0.465607523918152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460997551679611</t>
+    <t xml:space="preserve">0.460997521877289</t>
   </si>
   <si>
     <t xml:space="preserve">0.453314244747162</t>
@@ -1889,121 +1889,121 @@
     <t xml:space="preserve">0.4341059923172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441789329051971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445630997419357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449472576379776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451009273529053</t>
+    <t xml:space="preserve">0.441789239645004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445630967617035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449472546577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45100924372673</t>
   </si>
   <si>
     <t xml:space="preserve">0.460229188203812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454082608222961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457155883312225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45177760720253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456387490034103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463302493095398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47098582983017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467144131660461</t>
+    <t xml:space="preserve">0.454082578420639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45715594291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451777577400208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456387519836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463302463293076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470985800027847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467144101858139</t>
   </si>
   <si>
     <t xml:space="preserve">0.457924276590347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447167605161667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432569414377213</t>
+    <t xml:space="preserve">0.447167634963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432569354772568</t>
   </si>
   <si>
     <t xml:space="preserve">0.437947690486908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433337658643723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434874325990677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436410963535309</t>
+    <t xml:space="preserve">0.43333774805069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434874296188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436411023139954</t>
   </si>
   <si>
     <t xml:space="preserve">0.43948432803154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441020995378494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440252602100372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43871596455574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442557632923126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485584050416946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455619245767593</t>
+    <t xml:space="preserve">0.441020935773849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440252661705017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438715904951096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442557573318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485584110021591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455619186162949</t>
   </si>
   <si>
     <t xml:space="preserve">0.443325966596603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429496049880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435642659664154</t>
+    <t xml:space="preserve">0.429496020078659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435642629861832</t>
   </si>
   <si>
     <t xml:space="preserve">0.450240910053253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427191019058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375328779220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386469602584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393384605646133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365724712610245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372639656066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351510643959045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342674821615219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317319989204407</t>
+    <t xml:space="preserve">0.427190989255905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375328838825226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386469572782516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393384546041489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365724682807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372639685869217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351510614156723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342674881219864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317319959402084</t>
   </si>
   <si>
     <t xml:space="preserve">0.26507356762886</t>
@@ -2012,31 +2012,31 @@
     <t xml:space="preserve">0.259695291519165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239334583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242023706436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234724536538124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.245865359902382</t>
+    <t xml:space="preserve">0.239334553480148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.242023691534996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234724551439285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.245865345001221</t>
   </si>
   <si>
     <t xml:space="preserve">0.258926957845688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251627802848816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266610234975815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269299387931824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258158594369888</t>
+    <t xml:space="preserve">0.251627773046494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266610264778137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269299358129501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258158653974533</t>
   </si>
   <si>
     <t xml:space="preserve">0.251243650913239</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">0.242407888174057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245096981525421</t>
+    <t xml:space="preserve">0.245097011327744</t>
   </si>
   <si>
     <t xml:space="preserve">0.254701137542725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262000262737274</t>
+    <t xml:space="preserve">0.262000232934952</t>
   </si>
   <si>
     <t xml:space="preserve">0.254316955804825</t>
@@ -2063,22 +2063,22 @@
     <t xml:space="preserve">0.261231929063797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262768626213074</t>
+    <t xml:space="preserve">0.262768596410751</t>
   </si>
   <si>
     <t xml:space="preserve">0.264689445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271988540887833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273909389972687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276982665061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27275687456131</t>
+    <t xml:space="preserve">0.27198851108551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.273909360170364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276982724666595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272756844758987</t>
   </si>
   <si>
     <t xml:space="preserve">0.275446027517319</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">0.258542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265457719564438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263152748346329</t>
+    <t xml:space="preserve">0.26545774936676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263152778148651</t>
   </si>
   <si>
     <t xml:space="preserve">0.292733430862427</t>
@@ -2105,31 +2105,31 @@
     <t xml:space="preserve">0.327692419290543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302337527275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301953375339508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332302421331406</t>
+    <t xml:space="preserve">0.30233758687973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30195340514183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332302361726761</t>
   </si>
   <si>
     <t xml:space="preserve">0.332686573266983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306179195642471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.305026739835739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312325805425644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331918179988861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315399140119553</t>
+    <t xml:space="preserve">0.306179165840149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.305026710033417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312325835227966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331918209791183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315399169921875</t>
   </si>
   <si>
     <t xml:space="preserve">0.326539903879166</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">0.292349278926849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289275974035263</t>
+    <t xml:space="preserve">0.289275944232941</t>
   </si>
   <si>
     <t xml:space="preserve">0.291196763515472</t>
@@ -2150,76 +2150,76 @@
     <t xml:space="preserve">0.285050123929977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273525178432465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26084777712822</t>
+    <t xml:space="preserve">0.273525208234787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260847747325897</t>
   </si>
   <si>
     <t xml:space="preserve">0.261616110801697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270067691802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278519332408905</t>
+    <t xml:space="preserve">0.270067721605301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278519362211227</t>
   </si>
   <si>
     <t xml:space="preserve">0.27314105629921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.266994416713715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.255469501018524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253164440393448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256621986627579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256237775087357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.249322846531868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.236261248588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238182052969933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25354865193367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267762780189514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.283513426780701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277751058340073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294654279947281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319624990224838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343827307224274</t>
+    <t xml:space="preserve">0.266994386911392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.255469471216202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25316447019577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256621956825256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256237804889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.249322831630707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.236261233687401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238182067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253548622131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267762720584869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.283513456583023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277750998735428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294654250144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319624960422516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343827337026596</t>
   </si>
   <si>
     <t xml:space="preserve">0.338449001312256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34075403213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338833212852478</t>
+    <t xml:space="preserve">0.340754002332687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338833183050156</t>
   </si>
   <si>
     <t xml:space="preserve">0.338064849376678</t>
@@ -2237,22 +2237,22 @@
     <t xml:space="preserve">0.328844904899597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339985638856888</t>
+    <t xml:space="preserve">0.339985698461533</t>
   </si>
   <si>
     <t xml:space="preserve">0.34766897559166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359962224960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3518947660923</t>
+    <t xml:space="preserve">0.35996225476265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351894795894623</t>
   </si>
   <si>
     <t xml:space="preserve">0.369182199239731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35765728354454</t>
+    <t xml:space="preserve">0.357657223939896</t>
   </si>
   <si>
     <t xml:space="preserve">0.355352282524109</t>
@@ -2261,40 +2261,40 @@
     <t xml:space="preserve">0.348053127527237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346516489982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347284823656082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363419681787491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373792171478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373023837804794</t>
+    <t xml:space="preserve">0.346516460180283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347284764051437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363419711589813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373792141675949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373023808002472</t>
   </si>
   <si>
     <t xml:space="preserve">0.379554629325867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42565444111824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417971104383469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381859600543976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383012115955353</t>
+    <t xml:space="preserve">0.425654411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417971134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381859630346298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38301208615303</t>
   </si>
   <si>
     <t xml:space="preserve">0.377633810043335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37840211391449</t>
+    <t xml:space="preserve">0.378402173519135</t>
   </si>
   <si>
     <t xml:space="preserve">0.381091296672821</t>
@@ -2303,277 +2303,280 @@
     <t xml:space="preserve">0.380322962999344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348437309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400299519300461</t>
+    <t xml:space="preserve">0.348437339067459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400299549102783</t>
   </si>
   <si>
     <t xml:space="preserve">0.383396297693253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379938840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388006269931793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428727775812149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368413865566254</t>
+    <t xml:space="preserve">0.379938781261444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388006240129471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428727716207504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368413895368576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344595640897751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334223240613937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341906487941742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323466598987579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340369790792465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331149905920029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348821461200714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322314113378525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285818487405777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337680697441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345363944768906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341522365808487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329229056835175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353653132915497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351594626903534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354064851999283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352829694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347477585077286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345830768346786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341713726520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34253716468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348300963640213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359828680753708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353241443634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354888260364532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350359499454498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345007359981537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339655220508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342948824167252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341302007436752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333479672670364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320716828107834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319070011377335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321540266275406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310835987329483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315776437520981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314129620790482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312894493341446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31824666261673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317834943532944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319481790065765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312071084976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308365732431412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310012578964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314541280269623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318658351898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320305168628693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322775393724442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30960088968277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309189170598984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32112854719162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321951985359192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325245589017868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326892405748367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323187112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323598802089691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315364688634872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313306212425232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310424327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314953029155731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311247706413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317011535167694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31742325425148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311659395694733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316188126802444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319893449544907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304660439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308777511119843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303013622760773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307542353868484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302601933479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307954043149948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306307256221771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301778525114059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3038370013237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300955086946487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301366776227951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302190244197845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313717901706696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326480686664581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328539192676544</t>
   </si>
   <si>
     <t xml:space="preserve">0.344595670700073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334223181009293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341906487941742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323466569185257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340369820594788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331149905920029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348821461200714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322314113378525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285818487405777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337680697441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345363944768906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341522365808487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329229056835175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353653103113174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351594626903534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354064851999283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352829724550247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347477555274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345830768346786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341713696718216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34253716468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348300963640213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359828680753708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353241413831711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35488823056221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350359499454498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345007359981537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339655190706253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342948853969574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341302037239075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333479672670364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320716857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319070041179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321540266275406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310835957527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315776437520981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314129620790482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312894493341446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318246632814407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317834943532944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319481790065765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312071114778519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308365762233734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310012608766556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314541280269623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318658351898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320305198431015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322775393724442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309600859880447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309189170598984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32112854719162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32195195555687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32524561882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326892465353012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323187112808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323598802089691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315364718437195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313306212425232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310424298048019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314952999353409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311247676610947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317011535167694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317423224449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311659395694733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316188126802444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319893479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304660439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308777511119843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303013622760773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307542324066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302601933479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307954043149948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306307286024094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301778525114059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3038370013237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300955086946487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301366806030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302190244197845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313717931509018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326480716466904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328539192676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340890347957611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356535047292709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343360513448715</t>
+    <t xml:space="preserve">0.340890318155289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356535077095032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343360543251038</t>
   </si>
   <si>
     <t xml:space="preserve">0.336361587047577</t>
@@ -2585,16 +2588,16 @@
     <t xml:space="preserve">0.335126489400864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358181834220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3470658659935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344183951616287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.336773276329041</t>
+    <t xml:space="preserve">0.358181864023209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347065895795822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344184011220932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.336773306131363</t>
   </si>
   <si>
     <t xml:space="preserve">0.345419049263</t>
@@ -2603,13 +2606,13 @@
     <t xml:space="preserve">0.349124372005463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338008403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335949867963791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343772232532501</t>
+    <t xml:space="preserve">0.338008433580399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335949838161469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343772202730179</t>
   </si>
   <si>
     <t xml:space="preserve">0.33759668469429</t>
@@ -2621,13 +2624,13 @@
     <t xml:space="preserve">0.340478628873825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332244515419006</t>
+    <t xml:space="preserve">0.332244545221329</t>
   </si>
   <si>
     <t xml:space="preserve">0.329362630844116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325657278299332</t>
+    <t xml:space="preserve">0.325657337903976</t>
   </si>
   <si>
     <t xml:space="preserve">0.338420122861862</t>
@@ -2642,10 +2645,10 @@
     <t xml:space="preserve">0.359005272388458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370121270418167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377943605184555</t>
+    <t xml:space="preserve">0.370121240615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377943634986877</t>
   </si>
   <si>
     <t xml:space="preserve">0.38164895772934</t>
@@ -2657,31 +2660,31 @@
     <t xml:space="preserve">0.395235151052475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399763911962509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389471262693405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401822447776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411703288555145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402234107255936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403469234704971</t>
+    <t xml:space="preserve">0.399763882160187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38947132229805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401822417974472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411703318357468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402234137058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403469204902649</t>
   </si>
   <si>
     <t xml:space="preserve">0.409644782543182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408409684896469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40593945980072</t>
+    <t xml:space="preserve">0.408409655094147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405939429998398</t>
   </si>
   <si>
     <t xml:space="preserve">0.406351149082184</t>
@@ -2693,106 +2696,103 @@
     <t xml:space="preserve">0.397705405950546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403880923986435</t>
+    <t xml:space="preserve">0.403880953788757</t>
   </si>
   <si>
     <t xml:space="preserve">0.403057515621185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394823461771011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417467176914215</t>
+    <t xml:space="preserve">0.394823491573334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417467147111893</t>
   </si>
   <si>
     <t xml:space="preserve">0.433111876249313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430641680955887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44134595990181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454520434141159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442992687225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488280087709427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503924906253815</t>
+    <t xml:space="preserve">0.430641621351242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441345900297165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454520374536514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442992746829987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488280057907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50392484664917</t>
   </si>
   <si>
     <t xml:space="preserve">0.534390866756439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518746197223663</t>
+    <t xml:space="preserve">0.518746137619019</t>
   </si>
   <si>
     <t xml:space="preserve">0.522039771080017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500631213188171</t>
+    <t xml:space="preserve">0.500631153583527</t>
   </si>
   <si>
     <t xml:space="preserve">0.517922759056091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46934175491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485809862613678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.462754458189011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472635388374329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493220508098602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491573750972748</t>
+    <t xml:space="preserve">0.469341784715652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485809892416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.462754487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472635328769684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493220567703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491573691368103</t>
   </si>
   <si>
     <t xml:space="preserve">0.48169282078743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467694938182831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459460943937302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461107671260834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476752400398254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479222595691681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477575898170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51545250415802</t>
+    <t xml:space="preserve">0.467694967985153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461107701063156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476752489805222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479222655296326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477575838565826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515452444553375</t>
   </si>
   <si>
     <t xml:space="preserve">0.504748225212097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501454591751099</t>
+    <t xml:space="preserve">0.501454651355743</t>
   </si>
   <si>
     <t xml:space="preserve">0.498984396457672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494043976068497</t>
+    <t xml:space="preserve">0.494043946266174</t>
   </si>
   <si>
     <t xml:space="preserve">0.505571722984314</t>
@@ -2801,76 +2801,76 @@
     <t xml:space="preserve">0.490750402212143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484986484050751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492397129535675</t>
+    <t xml:space="preserve">0.484986424446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492397159337997</t>
   </si>
   <si>
     <t xml:space="preserve">0.482516258955002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478399157524109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473458826541901</t>
+    <t xml:space="preserve">0.478399187326431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473458737134933</t>
   </si>
   <si>
     <t xml:space="preserve">0.470988571643829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47016516327858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46522468328476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460284292697906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46851834654808</t>
+    <t xml:space="preserve">0.470165073871613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465224713087082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460284262895584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468518376350403</t>
   </si>
   <si>
     <t xml:space="preserve">0.466750353574753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473822325468063</t>
+    <t xml:space="preserve">0.473822295665741</t>
   </si>
   <si>
     <t xml:space="preserve">0.457910388708115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46144637465477</t>
+    <t xml:space="preserve">0.461446434259415</t>
   </si>
   <si>
     <t xml:space="preserve">0.464098334312439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454374402761459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44111442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420782536268234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435810476541519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438462466001511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427412509918213</t>
+    <t xml:space="preserve">0.454374372959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441114455461502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420782506465912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.435810446739197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438462436199188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427412480115891</t>
   </si>
   <si>
     <t xml:space="preserve">0.426528483629227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433158487081528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448186457157135</t>
+    <t xml:space="preserve">0.433158457279205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448186427354813</t>
   </si>
   <si>
     <t xml:space="preserve">0.441998451948166</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">0.434484452009201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44465047121048</t>
+    <t xml:space="preserve">0.444650411605835</t>
   </si>
   <si>
     <t xml:space="preserve">0.449070423841476</t>
@@ -2888,19 +2888,19 @@
     <t xml:space="preserve">0.437578439712524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433600455522537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430948466062546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4313904941082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434926480054855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429622501134872</t>
+    <t xml:space="preserve">0.43360048532486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430948495864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431390464305878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434926450252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42962247133255</t>
   </si>
   <si>
     <t xml:space="preserve">0.428738474845886</t>
@@ -2909,13 +2909,13 @@
     <t xml:space="preserve">0.424318492412567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434042453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421666502952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430506467819214</t>
+    <t xml:space="preserve">0.434042483568192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421666473150253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430506497621536</t>
   </si>
   <si>
     <t xml:space="preserve">0.427854478359222</t>
@@ -2927,16 +2927,16 @@
     <t xml:space="preserve">0.417246520519257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411942541599274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414152503013611</t>
+    <t xml:space="preserve">0.411942511796951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414152532815933</t>
   </si>
   <si>
     <t xml:space="preserve">0.41813051700592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422550469636917</t>
+    <t xml:space="preserve">0.42255049943924</t>
   </si>
   <si>
     <t xml:space="preserve">0.413710534572601</t>
@@ -2945,31 +2945,31 @@
     <t xml:space="preserve">0.425202518701553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423876464366913</t>
+    <t xml:space="preserve">0.423876523971558</t>
   </si>
   <si>
     <t xml:space="preserve">0.414594531059265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422992527484894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421224534511566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413268536329269</t>
+    <t xml:space="preserve">0.422992497682571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421224504709244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413268506526947</t>
   </si>
   <si>
     <t xml:space="preserve">0.415920525789261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408406555652618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412384539842606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411058515310287</t>
+    <t xml:space="preserve">0.408406585454941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412384569644928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41105854511261</t>
   </si>
   <si>
     <t xml:space="preserve">0.409732550382614</t>
@@ -2981,13 +2981,13 @@
     <t xml:space="preserve">0.407964557409286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423434525728226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420340478420258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426086455583572</t>
+    <t xml:space="preserve">0.423434495925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42034050822258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.426086485385895</t>
   </si>
   <si>
     <t xml:space="preserve">0.428296476602554</t>
@@ -2999,13 +2999,13 @@
     <t xml:space="preserve">0.422108501195908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415478527545929</t>
+    <t xml:space="preserve">0.415478557348251</t>
   </si>
   <si>
     <t xml:space="preserve">0.402218610048294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394262611865997</t>
+    <t xml:space="preserve">0.39426264166832</t>
   </si>
   <si>
     <t xml:space="preserve">0.400008589029312</t>
@@ -3014,13 +3014,13 @@
     <t xml:space="preserve">0.401334583759308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39249461889267</t>
+    <t xml:space="preserve">0.392494648694992</t>
   </si>
   <si>
     <t xml:space="preserve">0.396030604839325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405754536390305</t>
+    <t xml:space="preserve">0.405754566192627</t>
   </si>
   <si>
     <t xml:space="preserve">0.403544545173645</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">0.388958632946014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395146578550339</t>
+    <t xml:space="preserve">0.395146608352661</t>
   </si>
   <si>
     <t xml:space="preserve">0.386748641729355</t>
@@ -3044,22 +3044,22 @@
     <t xml:space="preserve">0.393378585577011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403102576732635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396914571523666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397798597812653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40177658200264</t>
+    <t xml:space="preserve">0.403102546930313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396914601325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39779856801033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401776552200317</t>
   </si>
   <si>
     <t xml:space="preserve">0.406638562679291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402660548686981</t>
+    <t xml:space="preserve">0.402660608291626</t>
   </si>
   <si>
     <t xml:space="preserve">0.419898509979248</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">0.436694443225861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443766385316849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453789889812469</t>
+    <t xml:space="preserve">0.443766415119171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453789919614792</t>
   </si>
   <si>
     <t xml:space="preserve">0.452878683805466</t>
@@ -3086,31 +3086,31 @@
     <t xml:space="preserve">0.459257245063782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456523567438126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465635776519775</t>
+    <t xml:space="preserve">0.456523537635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465635806322098</t>
   </si>
   <si>
     <t xml:space="preserve">0.464724570512772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468369513750076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480215400457382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482949018478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481126666069031</t>
+    <t xml:space="preserve">0.468369483947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480215430259705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482949078083038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481126606464386</t>
   </si>
   <si>
     <t xml:space="preserve">0.482037842273712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479304224252701</t>
+    <t xml:space="preserve">0.479304194450378</t>
   </si>
   <si>
     <t xml:space="preserve">0.474748075008392</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">0.52577668428421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523954212665558</t>
+    <t xml:space="preserve">0.523954153060913</t>
   </si>
   <si>
     <t xml:space="preserve">0.510285794734955</t>
@@ -3143,28 +3143,28 @@
     <t xml:space="preserve">0.518486857414246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515753209590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507552146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511197090148926</t>
+    <t xml:space="preserve">0.515753149986267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507552087306976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511197030544281</t>
   </si>
   <si>
     <t xml:space="preserve">0.514841914176941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519398033618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513930678367615</t>
+    <t xml:space="preserve">0.519398093223572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51393073797226</t>
   </si>
   <si>
     <t xml:space="preserve">0.524865388870239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509374558925629</t>
+    <t xml:space="preserve">0.509374618530273</t>
   </si>
   <si>
     <t xml:space="preserve">0.526687920093536</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">0.533977687358856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541267454624176</t>
+    <t xml:space="preserve">0.541267395019531</t>
   </si>
   <si>
     <t xml:space="preserve">0.546734869480133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537622511386871</t>
+    <t xml:space="preserve">0.537622570991516</t>
   </si>
   <si>
     <t xml:space="preserve">0.549468457698822</t>
@@ -3191,25 +3191,25 @@
     <t xml:space="preserve">0.554024577140808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564959287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569515407085419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565870463848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562225639820099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551290929317474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548557281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550379633903503</t>
+    <t xml:space="preserve">0.564959347248077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569515466690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562225580215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551290988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548557221889496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550379693508148</t>
   </si>
   <si>
     <t xml:space="preserve">0.547646045684814</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">0.55584704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553113341331482</t>
+    <t xml:space="preserve">0.553113400936127</t>
   </si>
   <si>
     <t xml:space="preserve">0.564048111438751</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">0.559491991996765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561314344406128</t>
+    <t xml:space="preserve">0.561314404010773</t>
   </si>
   <si>
     <t xml:space="preserve">0.558580696582794</t>
@@ -3245,10 +3245,10 @@
     <t xml:space="preserve">0.534888863563538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528510332107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535800099372864</t>
+    <t xml:space="preserve">0.528510272502899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535800158977509</t>
   </si>
   <si>
     <t xml:space="preserve">0.530332744121552</t>
@@ -3263,13 +3263,13 @@
     <t xml:space="preserve">0.490238875150681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496617496013641</t>
+    <t xml:space="preserve">0.496617466211319</t>
   </si>
   <si>
     <t xml:space="preserve">0.498439848423004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505729734897614</t>
+    <t xml:space="preserve">0.505729675292969</t>
   </si>
   <si>
     <t xml:space="preserve">0.494794994592667</t>
@@ -3278,25 +3278,25 @@
     <t xml:space="preserve">0.499351114034653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497528672218323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492061376571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488416433334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483860343694687</t>
+    <t xml:space="preserve">0.497528702020645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492061346769333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488416403532028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483860313892365</t>
   </si>
   <si>
     <t xml:space="preserve">0.487505257129669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495706230401993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49388375878334</t>
+    <t xml:space="preserve">0.495706260204315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493883788585663</t>
   </si>
   <si>
     <t xml:space="preserve">0.491150081157684</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">0.517575621604919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489643424749374</t>
+    <t xml:space="preserve">0.489643454551697</t>
   </si>
   <si>
     <t xml:space="preserve">0.48199275135994</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">0.475776553153992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476732909679413</t>
+    <t xml:space="preserve">0.47673287987709</t>
   </si>
   <si>
     <t xml:space="preserve">0.480080038309097</t>
@@ -3329,31 +3329,31 @@
     <t xml:space="preserve">0.46477872133255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473385721445084</t>
+    <t xml:space="preserve">0.473385751247406</t>
   </si>
   <si>
     <t xml:space="preserve">0.469560384750366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.470994889736176</t>
+    <t xml:space="preserve">0.470994919538498</t>
   </si>
   <si>
     <t xml:space="preserve">0.459040701389313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453780889511108</t>
+    <t xml:space="preserve">0.453780859708786</t>
   </si>
   <si>
     <t xml:space="preserve">0.451390027999878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447564691305161</t>
+    <t xml:space="preserve">0.447564661502838</t>
   </si>
   <si>
     <t xml:space="preserve">0.45091187953949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441826671361923</t>
+    <t xml:space="preserve">0.441826701164246</t>
   </si>
   <si>
     <t xml:space="preserve">0.438479512929916</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">0.432741492986679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436088681221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438001334667206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441348522901535</t>
+    <t xml:space="preserve">0.436088651418686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438001364469528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441348493099213</t>
   </si>
   <si>
     <t xml:space="preserve">0.446608364582062</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">0.436566829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438957661390305</t>
+    <t xml:space="preserve">0.438957691192627</t>
   </si>
   <si>
     <t xml:space="preserve">0.444695681333542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439435869455338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433697819709778</t>
+    <t xml:space="preserve">0.439435839653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4336978495121</t>
   </si>
   <si>
     <t xml:space="preserve">0.434654176235199</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">0.46669140458107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454737186431885</t>
+    <t xml:space="preserve">0.454737216234207</t>
   </si>
   <si>
     <t xml:space="preserve">0.455693542957306</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">0.561368525028229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538416564464569</t>
+    <t xml:space="preserve">0.538416504859924</t>
   </si>
   <si>
     <t xml:space="preserve">0.544154524803162</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">0.540329158306122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525984108448029</t>
+    <t xml:space="preserve">0.525984168052673</t>
   </si>
   <si>
     <t xml:space="preserve">0.517377138137817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525027871131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521202504634857</t>
+    <t xml:space="preserve">0.525027811527252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521202445030212</t>
   </si>
   <si>
     <t xml:space="preserve">0.519289791584015</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">0.531722128391266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518333435058594</t>
+    <t xml:space="preserve">0.518333494663239</t>
   </si>
   <si>
     <t xml:space="preserve">0.514508128166199</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">0.527896821498871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52694046497345</t>
+    <t xml:space="preserve">0.526940524578094</t>
   </si>
   <si>
     <t xml:space="preserve">0.535547494888306</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">0.553717851638794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568062841892242</t>
+    <t xml:space="preserve">0.568062901496887</t>
   </si>
   <si>
     <t xml:space="preserve">0.55849951505661</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">0.555630505084991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554674208164215</t>
+    <t xml:space="preserve">0.55467414855957</t>
   </si>
   <si>
     <t xml:space="preserve">0.557543218135834</t>
@@ -3491,16 +3491,16 @@
     <t xml:space="preserve">0.54702353477478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537460148334503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551805198192596</t>
+    <t xml:space="preserve">0.537460088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551805257797241</t>
   </si>
   <si>
     <t xml:space="preserve">0.524071455001831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533634901046753</t>
+    <t xml:space="preserve">0.533634841442108</t>
   </si>
   <si>
     <t xml:space="preserve">0.536503851413727</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">0.522158801555634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529809534549713</t>
+    <t xml:space="preserve">0.529809474945068</t>
   </si>
   <si>
     <t xml:space="preserve">0.532678484916687</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">0.499206781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49633777141571</t>
+    <t xml:space="preserve">0.496337741613388</t>
   </si>
   <si>
     <t xml:space="preserve">0.506857395172119</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">0.487730741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483905404806137</t>
+    <t xml:space="preserve">0.483905375003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.461909741163254</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">0.478167414665222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46860408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471473067998886</t>
+    <t xml:space="preserve">0.468604058027267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471473038196564</t>
   </si>
   <si>
     <t xml:space="preserve">0.48260822892189</t>
@@ -4008,6 +4008,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.564000010490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554000020027161</t>
   </si>
 </sst>
 </file>
@@ -49708,7 +49711,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1745" t="s">
-        <v>770</v>
+        <v>851</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49734,7 +49737,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1746" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49760,7 +49763,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1747" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49838,7 +49841,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1750" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49864,7 +49867,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G1751" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49890,7 +49893,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1752" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49916,7 +49919,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1753" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49942,7 +49945,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1754" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49968,7 +49971,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1755" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49994,7 +49997,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1756" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -50020,7 +50023,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1757" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50046,7 +50049,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1758" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -50098,7 +50101,7 @@
         <v>0.41949999332428</v>
       </c>
       <c r="G1760" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50124,7 +50127,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1761" t="s">
-        <v>770</v>
+        <v>851</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50150,7 +50153,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1762" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50202,7 +50205,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1764" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -50228,7 +50231,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1765" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50254,7 +50257,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1766" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -50280,7 +50283,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1767" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50306,7 +50309,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1768" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -50332,7 +50335,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1769" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -50358,7 +50361,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1770" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50384,7 +50387,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1771" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50436,7 +50439,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1773" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50462,7 +50465,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1774" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50488,7 +50491,7 @@
         <v>0.403499990701675</v>
       </c>
       <c r="G1775" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50540,7 +50543,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1777" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50566,7 +50569,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1778" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50618,7 +50621,7 @@
         <v>0.395500004291534</v>
       </c>
       <c r="G1780" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50670,7 +50673,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1782" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50696,7 +50699,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1783" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50722,7 +50725,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1784" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50748,7 +50751,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1785" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50774,7 +50777,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1786" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50800,7 +50803,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1787" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50852,7 +50855,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1789" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50878,7 +50881,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1790" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50904,7 +50907,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1791" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50930,7 +50933,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1792" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50982,7 +50985,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51008,7 +51011,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1795" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -51034,7 +51037,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1796" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -51060,7 +51063,7 @@
         <v>0.449499994516373</v>
       </c>
       <c r="G1797" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51086,7 +51089,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G1798" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51112,7 +51115,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1799" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51138,7 +51141,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G1800" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -51164,7 +51167,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1801" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -51190,7 +51193,7 @@
         <v>0.485500007867813</v>
       </c>
       <c r="G1802" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -51216,7 +51219,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1803" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51242,7 +51245,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1804" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -51268,7 +51271,7 @@
         <v>0.5</v>
       </c>
       <c r="G1805" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -51294,7 +51297,7 @@
         <v>0.488499999046326</v>
       </c>
       <c r="G1806" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51320,7 +51323,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -51346,7 +51349,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G1808" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51372,7 +51375,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1809" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51398,7 +51401,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1810" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51424,7 +51427,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1811" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51450,7 +51453,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1812" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51476,7 +51479,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1813" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51502,7 +51505,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1814" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51528,7 +51531,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1815" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51554,7 +51557,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1816" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51580,7 +51583,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1817" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51606,7 +51609,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1818" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51632,7 +51635,7 @@
         <v>0.489499986171722</v>
       </c>
       <c r="G1819" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51658,7 +51661,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1820" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51684,7 +51687,7 @@
         <v>0.5</v>
       </c>
       <c r="G1821" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51710,7 +51713,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1822" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51736,7 +51739,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1823" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51762,7 +51765,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1824" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51788,7 +51791,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1825" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51814,7 +51817,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1826" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51840,7 +51843,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1827" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51866,7 +51869,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G1828" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51892,7 +51895,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1829" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51918,7 +51921,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G1830" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51944,7 +51947,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1831" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51970,7 +51973,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1832" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51996,7 +51999,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1833" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52022,7 +52025,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G1834" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -52048,7 +52051,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1835" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52074,7 +52077,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1836" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52100,7 +52103,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1837" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52126,7 +52129,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1838" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -52152,7 +52155,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1839" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -52178,7 +52181,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1840" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52204,7 +52207,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G1841" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52230,7 +52233,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1842" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52256,7 +52259,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1843" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52282,7 +52285,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1844" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52308,7 +52311,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1845" t="s">
-        <v>917</v>
+        <v>363</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52386,7 +52389,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1848" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52490,7 +52493,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1852" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52880,7 +52883,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1867" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52932,7 +52935,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1869" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52984,7 +52987,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1871" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53036,7 +53039,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1873" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53114,7 +53117,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>917</v>
+        <v>363</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -69892,7 +69895,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6912847222</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>233981</v>
@@ -69913,6 +69916,32 @@
         <v>1331</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.6912847222</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>412257</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>0.565999984741211</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>0.546000003814697</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>0.554000020027161</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>1332</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="1333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="1334">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,28 +53,28 @@
     <t xml:space="preserve">0.317678391933441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307318449020386</t>
+    <t xml:space="preserve">0.307318478822708</t>
   </si>
   <si>
     <t xml:space="preserve">0.288448721170425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289336681365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294368624687195</t>
+    <t xml:space="preserve">0.289336651563644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294368654489517</t>
   </si>
   <si>
     <t xml:space="preserve">0.285636752843857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273796826601028</t>
+    <t xml:space="preserve">0.273796886205673</t>
   </si>
   <si>
     <t xml:space="preserve">0.258997052907944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258257061243057</t>
+    <t xml:space="preserve">0.258257031440735</t>
   </si>
   <si>
     <t xml:space="preserve">0.243605211377144</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">0.246417179703712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262697011232376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256407082080841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259811043739319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261512994766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253817081451416</t>
+    <t xml:space="preserve">0.262696951627731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256407052278519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259811013936996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261513024568558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.253817111253738</t>
   </si>
   <si>
     <t xml:space="preserve">0.253077119588852</t>
@@ -104,31 +104,31 @@
     <t xml:space="preserve">0.286894708871841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.284600764513016</t>
+    <t xml:space="preserve">0.284600734710693</t>
   </si>
   <si>
     <t xml:space="preserve">0.277496814727783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.287116676568985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290742665529251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263806998729706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256777077913284</t>
+    <t xml:space="preserve">0.28711673617363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290742635726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263806939125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256777107715607</t>
   </si>
   <si>
     <t xml:space="preserve">0.250117152929306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277570813894272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297994643449783</t>
+    <t xml:space="preserve">0.277570784091949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297994583845139</t>
   </si>
   <si>
     <t xml:space="preserve">0.310796439647675</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">0.304358541965485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318122297525406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309686422348022</t>
+    <t xml:space="preserve">0.318122357130051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309686452150345</t>
   </si>
   <si>
     <t xml:space="preserve">0.301620543003082</t>
@@ -152,88 +152,88 @@
     <t xml:space="preserve">0.310352444648743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323376327753067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320046335458755</t>
+    <t xml:space="preserve">0.323376297950745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320046365261078</t>
   </si>
   <si>
     <t xml:space="preserve">0.316716372966766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315236419439316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315606355667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332996189594269</t>
+    <t xml:space="preserve">0.315236389636993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315606415271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332996159791946</t>
   </si>
   <si>
     <t xml:space="preserve">0.332256197929382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328852206468582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330480217933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311240434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312054455280304</t>
+    <t xml:space="preserve">0.328852266073227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330480188131332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311240464448929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312054395675659</t>
   </si>
   <si>
     <t xml:space="preserve">0.299696564674377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.296884596347809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2994005382061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29747661948204</t>
+    <t xml:space="preserve">0.296884626150131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299400568008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297476589679718</t>
   </si>
   <si>
     <t xml:space="preserve">0.295996576547623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293702632188797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298216611146927</t>
+    <t xml:space="preserve">0.293702661991119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298216581344604</t>
   </si>
   <si>
     <t xml:space="preserve">0.286376714706421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276756823062897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274536848068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272316843271255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268542915582657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270466864109039</t>
+    <t xml:space="preserve">0.276756882667542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27453687787056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272316873073578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268542885780334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270466923713684</t>
   </si>
   <si>
     <t xml:space="preserve">0.26506495475769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268172919750214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268616914749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269208908081055</t>
+    <t xml:space="preserve">0.268172949552536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.268616944551468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269208878278732</t>
   </si>
   <si>
     <t xml:space="preserve">0.275276869535446</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">0.308206468820572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309168428182602</t>
+    <t xml:space="preserve">0.309168457984924</t>
   </si>
   <si>
     <t xml:space="preserve">0.318196356296539</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">0.31420037150383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321378320455551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319380313158035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722440481186</t>
+    <t xml:space="preserve">0.321378290653229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319380342960358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722410678864</t>
   </si>
   <si>
     <t xml:space="preserve">0.313682407140732</t>
@@ -284,40 +284,40 @@
     <t xml:space="preserve">0.30761444568634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304950475692749</t>
+    <t xml:space="preserve">0.304950505495071</t>
   </si>
   <si>
     <t xml:space="preserve">0.305616497993469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2995485663414</t>
+    <t xml:space="preserve">0.299548536539078</t>
   </si>
   <si>
     <t xml:space="preserve">0.305320501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295626640319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300954520702362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314400315284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318779826164246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318856596946716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318395644426346</t>
+    <t xml:space="preserve">0.295626670122147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300954550504684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314400345087051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318779766559601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318856656551361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318395614624023</t>
   </si>
   <si>
     <t xml:space="preserve">0.319932252168655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318088263273239</t>
+    <t xml:space="preserve">0.318088293075562</t>
   </si>
   <si>
     <t xml:space="preserve">0.307331681251526</t>
@@ -326,22 +326,22 @@
     <t xml:space="preserve">0.321776270866394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320393264293671</t>
+    <t xml:space="preserve">0.320393294095993</t>
   </si>
   <si>
     <t xml:space="preserve">0.311557501554489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305795043706894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301569253206253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295806765556335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299648344516754</t>
+    <t xml:space="preserve">0.305795013904572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301569223403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295806735754013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.299648374319077</t>
   </si>
   <si>
     <t xml:space="preserve">0.296575099229813</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">0.303490042686462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31424668431282</t>
+    <t xml:space="preserve">0.314246654510498</t>
   </si>
   <si>
     <t xml:space="preserve">0.318011462688446</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.318702936172485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321161657571793</t>
+    <t xml:space="preserve">0.32116162776947</t>
   </si>
   <si>
     <t xml:space="preserve">0.310020834207535</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">0.30671700835228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305564552545547</t>
+    <t xml:space="preserve">0.305564522743225</t>
   </si>
   <si>
     <t xml:space="preserve">0.304949879646301</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">0.306870698928833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297727525234222</t>
+    <t xml:space="preserve">0.297727584838867</t>
   </si>
   <si>
     <t xml:space="preserve">0.301799744367599</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">0.304027855396271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300032556056976</t>
+    <t xml:space="preserve">0.300032585859299</t>
   </si>
   <si>
     <t xml:space="preserve">0.313478291034698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31255629658699</t>
+    <t xml:space="preserve">0.312556326389313</t>
   </si>
   <si>
     <t xml:space="preserve">0.307869523763657</t>
@@ -413,28 +413,28 @@
     <t xml:space="preserve">0.298265397548676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.299110502004623</t>
+    <t xml:space="preserve">0.299110591411591</t>
   </si>
   <si>
     <t xml:space="preserve">0.305257201194763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295576244592667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295960426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297650754451752</t>
+    <t xml:space="preserve">0.295576214790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295960396528244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297650694847107</t>
   </si>
   <si>
     <t xml:space="preserve">0.297881245613098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293732285499573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298803269863129</t>
+    <t xml:space="preserve">0.29373225569725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298803240060806</t>
   </si>
   <si>
     <t xml:space="preserve">0.300416707992554</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">0.300109386444092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298880040645599</t>
+    <t xml:space="preserve">0.298880070447922</t>
   </si>
   <si>
     <t xml:space="preserve">0.30548769235611</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">0.309559851884842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303105890750885</t>
+    <t xml:space="preserve">0.303105860948563</t>
   </si>
   <si>
     <t xml:space="preserve">0.303566843271255</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">0.304873019456863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306563347578049</t>
+    <t xml:space="preserve">0.306563317775726</t>
   </si>
   <si>
     <t xml:space="preserve">0.300186216831207</t>
@@ -476,31 +476,31 @@
     <t xml:space="preserve">0.296421408653259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3014155626297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300647228956223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282975643873215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29196509718895</t>
+    <t xml:space="preserve">0.301415592432022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3006471991539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282975614070892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291965126991272</t>
   </si>
   <si>
     <t xml:space="preserve">0.289736926555634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293501734733582</t>
+    <t xml:space="preserve">0.293501764535904</t>
   </si>
   <si>
     <t xml:space="preserve">0.292656570672989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292502909898758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289583265781403</t>
+    <t xml:space="preserve">0.292502969503403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28958323597908</t>
   </si>
   <si>
     <t xml:space="preserve">0.288123488426208</t>
@@ -512,70 +512,70 @@
     <t xml:space="preserve">0.287892997264862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290044277906418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29288712143898</t>
+    <t xml:space="preserve">0.290044248104095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292887091636658</t>
   </si>
   <si>
     <t xml:space="preserve">0.293117612600327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291888296604156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289813786745071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286586791276932</t>
+    <t xml:space="preserve">0.291888266801834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289813846349716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286586821079254</t>
   </si>
   <si>
     <t xml:space="preserve">0.294270068407059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291811406612396</t>
+    <t xml:space="preserve">0.291811436414719</t>
   </si>
   <si>
     <t xml:space="preserve">0.292579770088196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295729905366898</t>
+    <t xml:space="preserve">0.29572993516922</t>
   </si>
   <si>
     <t xml:space="preserve">0.298419088125229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294731080532074</t>
+    <t xml:space="preserve">0.294731050729752</t>
   </si>
   <si>
     <t xml:space="preserve">0.287355124950409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293809056282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292041957378387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28674042224884</t>
+    <t xml:space="preserve">0.293809115886688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292041927576065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286740481853485</t>
   </si>
   <si>
     <t xml:space="preserve">0.2846659719944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278903484344482</t>
+    <t xml:space="preserve">0.278903514146805</t>
   </si>
   <si>
     <t xml:space="preserve">0.27559968829155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270221412181854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272449553012848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276675343513489</t>
+    <t xml:space="preserve">0.270221382379532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272449523210526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276675373315811</t>
   </si>
   <si>
     <t xml:space="preserve">0.27398619055748</t>
@@ -584,40 +584,40 @@
     <t xml:space="preserve">0.275676518678665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275522857904434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276598542928696</t>
+    <t xml:space="preserve">0.275522828102112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276598513126373</t>
   </si>
   <si>
     <t xml:space="preserve">0.270989716053009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.271143406629562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274293512105942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.270451873540878</t>
+    <t xml:space="preserve">0.271143347024918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274293541908264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270451903343201</t>
   </si>
   <si>
     <t xml:space="preserve">0.268146932125092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267378568649292</t>
+    <t xml:space="preserve">0.267378598451614</t>
   </si>
   <si>
     <t xml:space="preserve">0.264612585306168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265765100717545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262384474277496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267532199621201</t>
+    <t xml:space="preserve">0.2657650411129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.262384444475174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267532229423523</t>
   </si>
   <si>
     <t xml:space="preserve">0.265304088592529</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">0.272526353597641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283282965421677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279902309179306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277059525251389</t>
+    <t xml:space="preserve">0.283282995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279902338981628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277059495449066</t>
   </si>
   <si>
     <t xml:space="preserve">0.27844250202179</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">0.278749823570251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278980374336243</t>
+    <t xml:space="preserve">0.27898034453392</t>
   </si>
   <si>
     <t xml:space="preserve">0.278212010860443</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">0.284051328897476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290812611579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28966012597084</t>
+    <t xml:space="preserve">0.290812641382217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289660096168518</t>
   </si>
   <si>
     <t xml:space="preserve">0.290428429841995</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">0.294807910919189</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295422613620758</t>
+    <t xml:space="preserve">0.295422554016113</t>
   </si>
   <si>
     <t xml:space="preserve">0.288507610559464</t>
@@ -677,19 +677,19 @@
     <t xml:space="preserve">0.284589171409607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291043132543564</t>
+    <t xml:space="preserve">0.291043102741241</t>
   </si>
   <si>
     <t xml:space="preserve">0.293885916471481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294884771108627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289890617132187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286125808954239</t>
+    <t xml:space="preserve">0.294884741306305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289890587329865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.286125779151917</t>
   </si>
   <si>
     <t xml:space="preserve">0.284358620643616</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">0.282745152711868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.277290016412735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281976848840714</t>
+    <t xml:space="preserve">0.277290046215057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281976819038391</t>
   </si>
   <si>
     <t xml:space="preserve">0.276214331388474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273602038621902</t>
+    <t xml:space="preserve">0.273602068424225</t>
   </si>
   <si>
     <t xml:space="preserve">0.269760370254517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275061875581741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271834850311279</t>
+    <t xml:space="preserve">0.275061845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271834880113602</t>
   </si>
   <si>
     <t xml:space="preserve">0.273371547460556</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">0.275215536355972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276905804872513</t>
+    <t xml:space="preserve">0.276905834674835</t>
   </si>
   <si>
     <t xml:space="preserve">0.27483132481575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28266829252243</t>
+    <t xml:space="preserve">0.282668352127075</t>
   </si>
   <si>
     <t xml:space="preserve">0.280440151691437</t>
@@ -743,37 +743,37 @@
     <t xml:space="preserve">0.27736684679985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.278135180473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281208455562592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.278673022985458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28259152173996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279364496469498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285587966442108</t>
+    <t xml:space="preserve">0.278135150671005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281208544969559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.278672993183136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282591491937637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27936452627182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285587936639786</t>
   </si>
   <si>
     <t xml:space="preserve">0.27967181801796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28666365146637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.284435510635376</t>
+    <t xml:space="preserve">0.286663621664047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284435480833054</t>
   </si>
   <si>
     <t xml:space="preserve">0.281899988651276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.283897668123245</t>
+    <t xml:space="preserve">0.283897697925568</t>
   </si>
   <si>
     <t xml:space="preserve">0.285280644893646</t>
@@ -785,49 +785,49 @@
     <t xml:space="preserve">0.295038431882858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304258406162262</t>
+    <t xml:space="preserve">0.304258346557617</t>
   </si>
   <si>
     <t xml:space="preserve">0.321929931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325617909431458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33184140920639</t>
+    <t xml:space="preserve">0.32561793923378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331841379404068</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387418270111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316935777664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309790372848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30925253033638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311096489429474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313094139099121</t>
+    <t xml:space="preserve">0.316935807466507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309790313243866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309252470731735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311096519231796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313094168901443</t>
   </si>
   <si>
     <t xml:space="preserve">0.313017338514328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288891792297363</t>
+    <t xml:space="preserve">0.288891762495041</t>
   </si>
   <si>
     <t xml:space="preserve">0.293040752410889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295192062854767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296805590391159</t>
+    <t xml:space="preserve">0.295192122459412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296805560588837</t>
   </si>
   <si>
     <t xml:space="preserve">0.297266572713852</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">0.298111736774445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310251355171204</t>
+    <t xml:space="preserve">0.310251325368881</t>
   </si>
   <si>
     <t xml:space="preserve">0.313555151224136</t>
@@ -845,19 +845,19 @@
     <t xml:space="preserve">0.300800859928131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30886834859848</t>
+    <t xml:space="preserve">0.308868318796158</t>
   </si>
   <si>
     <t xml:space="preserve">0.299725234508514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321853131055832</t>
+    <t xml:space="preserve">0.32185310125351</t>
   </si>
   <si>
     <t xml:space="preserve">0.327308237552643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318472445011139</t>
+    <t xml:space="preserve">0.318472474813461</t>
   </si>
   <si>
     <t xml:space="preserve">0.312095314264297</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">0.315014988183975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312248975038528</t>
+    <t xml:space="preserve">0.312249034643173</t>
   </si>
   <si>
     <t xml:space="preserve">0.313939332962036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309636652469635</t>
+    <t xml:space="preserve">0.309636682271957</t>
   </si>
   <si>
     <t xml:space="preserve">0.307408511638641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308945208787918</t>
+    <t xml:space="preserve">0.308945178985596</t>
   </si>
   <si>
     <t xml:space="preserve">0.313631981611252</t>
@@ -890,22 +890,22 @@
     <t xml:space="preserve">0.308023184537888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307715833187103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309021979570389</t>
+    <t xml:space="preserve">0.307715862989426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309022068977356</t>
   </si>
   <si>
     <t xml:space="preserve">0.309944003820419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3177809715271</t>
+    <t xml:space="preserve">0.317780941724777</t>
   </si>
   <si>
     <t xml:space="preserve">0.316551625728607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316474795341492</t>
+    <t xml:space="preserve">0.316474825143814</t>
   </si>
   <si>
     <t xml:space="preserve">0.324388593435287</t>
@@ -923,10 +923,10 @@
     <t xml:space="preserve">0.32154580950737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320470124483109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322621434926987</t>
+    <t xml:space="preserve">0.320470094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322621405124664</t>
   </si>
   <si>
     <t xml:space="preserve">0.323697090148926</t>
@@ -941,25 +941,25 @@
     <t xml:space="preserve">0.331764549016953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339524686336517</t>
+    <t xml:space="preserve">0.33952471613884</t>
   </si>
   <si>
     <t xml:space="preserve">0.34567129611969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340446650981903</t>
+    <t xml:space="preserve">0.340446680784225</t>
   </si>
   <si>
     <t xml:space="preserve">0.333378046751022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334991544485092</t>
+    <t xml:space="preserve">0.33499151468277</t>
   </si>
   <si>
     <t xml:space="preserve">0.336144030094147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337757498025894</t>
+    <t xml:space="preserve">0.337757527828217</t>
   </si>
   <si>
     <t xml:space="preserve">0.338910043239594</t>
@@ -971,55 +971,55 @@
     <t xml:space="preserve">0.339678347110748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350358098745346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34659332036972</t>
+    <t xml:space="preserve">0.350358158349991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346593290567398</t>
   </si>
   <si>
     <t xml:space="preserve">0.344211488962173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34067714214325</t>
+    <t xml:space="preserve">0.340677201747894</t>
   </si>
   <si>
     <t xml:space="preserve">0.334607362747192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338218510150909</t>
+    <t xml:space="preserve">0.338218539953232</t>
   </si>
   <si>
     <t xml:space="preserve">0.346900641918182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.346132308244705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.339601516723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340907633304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3526631295681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369950532913208</t>
+    <t xml:space="preserve">0.346132338047028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.339601546525955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340907663106918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352663099765778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369950503110886</t>
   </si>
   <si>
     <t xml:space="preserve">0.365417391061783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363035559654236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374099463224411</t>
+    <t xml:space="preserve">0.363035529851913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374099493026733</t>
   </si>
   <si>
     <t xml:space="preserve">0.371103048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369566380977631</t>
+    <t xml:space="preserve">0.369566351175308</t>
   </si>
   <si>
     <t xml:space="preserve">0.368798017501831</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">0.366108864545822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363112390041351</t>
+    <t xml:space="preserve">0.363112419843674</t>
   </si>
   <si>
     <t xml:space="preserve">0.3686443567276</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">0.366877198219299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366262525320053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361114770174026</t>
+    <t xml:space="preserve">0.366262555122375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361114740371704</t>
   </si>
   <si>
     <t xml:space="preserve">0.359885394573212</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">0.35919389128685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368567496538162</t>
+    <t xml:space="preserve">0.368567526340485</t>
   </si>
   <si>
     <t xml:space="preserve">0.372024983167648</t>
@@ -1058,55 +1058,55 @@
     <t xml:space="preserve">0.37555930018425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380246132612228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.392616212368011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405677825212479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421044409275055</t>
+    <t xml:space="preserve">0.380246102809906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392616182565689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405677855014801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42104434967041</t>
   </si>
   <si>
     <t xml:space="preserve">0.419507771730423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396842062473297</t>
+    <t xml:space="preserve">0.396842032670975</t>
   </si>
   <si>
     <t xml:space="preserve">0.413361102342606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422581076622009</t>
+    <t xml:space="preserve">0.422581106424332</t>
   </si>
   <si>
     <t xml:space="preserve">0.417586892843246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42642268538475</t>
+    <t xml:space="preserve">0.426422715187073</t>
   </si>
   <si>
     <t xml:space="preserve">0.423349410295486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427959382534027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436795145273209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4329534471035</t>
+    <t xml:space="preserve">0.427959352731705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436795175075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432953506708145</t>
   </si>
   <si>
     <t xml:space="preserve">0.452930063009262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459460884332657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465223371982574</t>
+    <t xml:space="preserve">0.459460854530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465223342180252</t>
   </si>
   <si>
     <t xml:space="preserve">0.468296676874161</t>
@@ -1121,37 +1121,37 @@
     <t xml:space="preserve">0.515164732933044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505560576915741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507097244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515548884868622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.503255546092987</t>
+    <t xml:space="preserve">0.505560636520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50709730386734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515548825263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.503255665302277</t>
   </si>
   <si>
     <t xml:space="preserve">0.489809840917587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480205774307251</t>
+    <t xml:space="preserve">0.480205744504929</t>
   </si>
   <si>
     <t xml:space="preserve">0.519006371498108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511323094367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499413996934891</t>
+    <t xml:space="preserve">0.511323034763336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499413907527924</t>
   </si>
   <si>
     <t xml:space="preserve">0.491730690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484431535005569</t>
+    <t xml:space="preserve">0.484431594610214</t>
   </si>
   <si>
     <t xml:space="preserve">0.483663201332092</t>
@@ -1160,16 +1160,16 @@
     <t xml:space="preserve">0.484815776348114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49518820643425</t>
+    <t xml:space="preserve">0.495188176631927</t>
   </si>
   <si>
     <t xml:space="preserve">0.490194022655487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553197085857391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542056262493134</t>
+    <t xml:space="preserve">0.553197026252747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542056202888489</t>
   </si>
   <si>
     <t xml:space="preserve">0.56280118227005</t>
@@ -1178,28 +1178,28 @@
     <t xml:space="preserve">0.586235225200653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600065112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582393527030945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572021126747131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572789490222931</t>
+    <t xml:space="preserve">0.600065171718597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58239358663559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572021067142487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572789371013641</t>
   </si>
   <si>
     <t xml:space="preserve">0.552428662776947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55127614736557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545129597187042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565874457359314</t>
+    <t xml:space="preserve">0.55127626657486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545129537582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565874516963959</t>
   </si>
   <si>
     <t xml:space="preserve">0.577015221118927</t>
@@ -1208,34 +1208,34 @@
     <t xml:space="preserve">0.596607625484467</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584698557853699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608132541179657</t>
+    <t xml:space="preserve">0.584698498249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608132600784302</t>
   </si>
   <si>
     <t xml:space="preserve">0.621962487697601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620425820350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629645824432373</t>
+    <t xml:space="preserve">0.620425879955292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629645764827728</t>
   </si>
   <si>
     <t xml:space="preserve">0.614279210567474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607748448848724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58162522315979</t>
+    <t xml:space="preserve">0.607748329639435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581625282764435</t>
   </si>
   <si>
     <t xml:space="preserve">0.560880303382874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598528385162354</t>
+    <t xml:space="preserve">0.598528504371643</t>
   </si>
   <si>
     <t xml:space="preserve">0.598144292831421</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">0.586619317531586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595455050468445</t>
+    <t xml:space="preserve">0.595455169677734</t>
   </si>
   <si>
     <t xml:space="preserve">0.587771832942963</t>
@@ -1262,76 +1262,76 @@
     <t xml:space="preserve">0.584314405918121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577399432659149</t>
+    <t xml:space="preserve">0.577399373054504</t>
   </si>
   <si>
     <t xml:space="preserve">0.567026913166046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574326157569885</t>
+    <t xml:space="preserve">0.574326038360596</t>
   </si>
   <si>
     <t xml:space="preserve">0.543592929840088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564722001552582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.563185334205627</t>
+    <t xml:space="preserve">0.564721941947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.563185274600983</t>
   </si>
   <si>
     <t xml:space="preserve">0.576246976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583930194377899</t>
+    <t xml:space="preserve">0.583930253982544</t>
   </si>
   <si>
     <t xml:space="preserve">0.58085685968399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587003469467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60467517375946</t>
+    <t xml:space="preserve">0.587003529071808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604675054550171</t>
   </si>
   <si>
     <t xml:space="preserve">0.629261612892151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61850506067276</t>
+    <t xml:space="preserve">0.61850494146347</t>
   </si>
   <si>
     <t xml:space="preserve">0.606980085372925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603138506412506</t>
+    <t xml:space="preserve">0.603138446807861</t>
   </si>
   <si>
     <t xml:space="preserve">0.612358331680298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611590087413788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59391850233078</t>
+    <t xml:space="preserve">0.611590027809143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593918442726135</t>
   </si>
   <si>
     <t xml:space="preserve">0.596991777420044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608516812324524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599296689033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589308500289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553965449333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538598716259003</t>
+    <t xml:space="preserve">0.608516693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599296748638153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589308619499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553965389728546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538598775863647</t>
   </si>
   <si>
     <t xml:space="preserve">0.557038724422455</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">0.536293864250183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524000465869904</t>
+    <t xml:space="preserve">0.524000525474548</t>
   </si>
   <si>
     <t xml:space="preserve">0.537830471992493</t>
@@ -1349,25 +1349,25 @@
     <t xml:space="preserve">0.547818720340729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53245210647583</t>
+    <t xml:space="preserve">0.532452166080475</t>
   </si>
   <si>
     <t xml:space="preserve">0.537062108516693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527073800563812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520927131175995</t>
+    <t xml:space="preserve">0.527073860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52092719078064</t>
   </si>
   <si>
     <t xml:space="preserve">0.517853915691376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525537192821503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530147135257721</t>
+    <t xml:space="preserve">0.525537252426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530147194862366</t>
   </si>
   <si>
     <t xml:space="preserve">0.523232221603394</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">0.51939058303833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524768948554993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549355387687683</t>
+    <t xml:space="preserve">0.524768888950348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549355328083038</t>
   </si>
   <si>
     <t xml:space="preserve">0.501718938350677</t>
@@ -1388,58 +1388,58 @@
     <t xml:space="preserve">0.492499023675919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477900803089142</t>
+    <t xml:space="preserve">0.477900743484497</t>
   </si>
   <si>
     <t xml:space="preserve">0.476364135742188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488657355308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471754193305969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472522467374802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468680828809738</t>
+    <t xml:space="preserve">0.48865732550621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471754163503647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472522437572479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468680858612061</t>
   </si>
   <si>
     <t xml:space="preserve">0.487120717763901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481742382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480974048376083</t>
+    <t xml:space="preserve">0.481742471456528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480974137783051</t>
   </si>
   <si>
     <t xml:space="preserve">0.483279049396515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478669106960297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47021746635437</t>
+    <t xml:space="preserve">0.478669196367264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470217525959015</t>
   </si>
   <si>
     <t xml:space="preserve">0.467912554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466375768184662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839249849319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461765915155411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4878890812397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500182330608368</t>
+    <t xml:space="preserve">0.466375797986984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839220046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461765885353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487888962030411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500182271003723</t>
   </si>
   <si>
     <t xml:space="preserve">0.469449102878571</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">0.437179356813431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444862693548203</t>
+    <t xml:space="preserve">0.444862574338913</t>
   </si>
   <si>
     <t xml:space="preserve">0.431800991296768</t>
@@ -1457,25 +1457,25 @@
     <t xml:space="preserve">0.444094300270081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424117654561996</t>
+    <t xml:space="preserve">0.424117684364319</t>
   </si>
   <si>
     <t xml:space="preserve">0.415666103363037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382627964019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379170447587967</t>
+    <t xml:space="preserve">0.382627993822098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379170477390289</t>
   </si>
   <si>
     <t xml:space="preserve">0.382243782281876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385701239109039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388774573802948</t>
+    <t xml:space="preserve">0.385701268911362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388774514198303</t>
   </si>
   <si>
     <t xml:space="preserve">0.391847878694534</t>
@@ -1484,13 +1484,13 @@
     <t xml:space="preserve">0.384164601564407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376481294631958</t>
+    <t xml:space="preserve">0.37648132443428</t>
   </si>
   <si>
     <t xml:space="preserve">0.367261350154877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364956378936768</t>
+    <t xml:space="preserve">0.364956319332123</t>
   </si>
   <si>
     <t xml:space="preserve">0.360346406698227</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">0.352278918027878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356504708528519</t>
+    <t xml:space="preserve">0.356504738330841</t>
   </si>
   <si>
     <t xml:space="preserve">0.37148717045784</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">0.365340530872345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374944627285004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366492986679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374560505151749</t>
+    <t xml:space="preserve">0.374944657087326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366493046283722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374560534954071</t>
   </si>
   <si>
     <t xml:space="preserve">0.374176323413849</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">0.37878629565239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362267225980759</t>
+    <t xml:space="preserve">0.362267196178436</t>
   </si>
   <si>
     <t xml:space="preserve">0.353815585374832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354583919048309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353047281503677</t>
+    <t xml:space="preserve">0.354583948850632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353047311306</t>
   </si>
   <si>
     <t xml:space="preserve">0.370718836784363</t>
@@ -1547,52 +1547,52 @@
     <t xml:space="preserve">0.354199767112732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39568954706192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411056160926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407982856035233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38493287563324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390311270952225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378017961978912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380707144737244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362651407718658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35957807302475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353431463241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349589824676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344979822635651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343059003353119</t>
+    <t xml:space="preserve">0.395689517259598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411056131124496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407982796430588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384932965040207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390311241149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378017991781235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380707114934921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362651377916336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359578043222427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3534314930439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349589794874191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344979852437973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343058973550797</t>
   </si>
   <si>
     <t xml:space="preserve">0.354968100786209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36418804526329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357273072004318</t>
+    <t xml:space="preserve">0.364188075065613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357273101806641</t>
   </si>
   <si>
     <t xml:space="preserve">0.349973976612091</t>
@@ -1604,40 +1604,40 @@
     <t xml:space="preserve">0.323850780725479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361883074045181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350742280483246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389542937278748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404141157865524</t>
+    <t xml:space="preserve">0.361883044242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350742310285568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38954296708107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404141187667847</t>
   </si>
   <si>
     <t xml:space="preserve">0.396457850933075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412592768669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404909461736679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401836156845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394152909517288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399531185626984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402604520320892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401067912578583</t>
+    <t xml:space="preserve">0.412592798471451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404909521341324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401836186647415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394152879714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399531155824661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402604460716248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401067852973938</t>
   </si>
   <si>
     <t xml:space="preserve">0.397994548082352</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">0.336528182029724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335759878158569</t>
+    <t xml:space="preserve">0.335759848356247</t>
   </si>
   <si>
     <t xml:space="preserve">0.337296515703201</t>
@@ -1667,37 +1667,37 @@
     <t xml:space="preserve">0.32807657122612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331534057855606</t>
+    <t xml:space="preserve">0.331534028053284</t>
   </si>
   <si>
     <t xml:space="preserve">0.319240778684616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326924055814743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312710016965866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34113821387291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322698295116425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326155722141266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324619114398956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325771570205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330381572246552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329997420310974</t>
+    <t xml:space="preserve">0.326924115419388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312709987163544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341138154268265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322698265314102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326155781745911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324619084596634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325771600008011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330381542444229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329997360706329</t>
   </si>
   <si>
     <t xml:space="preserve">0.324234962463379</t>
@@ -1706,52 +1706,52 @@
     <t xml:space="preserve">0.313862472772598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301185041666031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303874224424362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29695925116539</t>
+    <t xml:space="preserve">0.301185011863708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303874164819717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.296959221363068</t>
   </si>
   <si>
     <t xml:space="preserve">0.302721709012985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32308241724968</t>
+    <t xml:space="preserve">0.323082447052002</t>
   </si>
   <si>
     <t xml:space="preserve">0.308100014925003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310405015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306947499513626</t>
+    <t xml:space="preserve">0.310405045747757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306947559118271</t>
   </si>
   <si>
     <t xml:space="preserve">0.314630806446075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.305410891771317</t>
+    <t xml:space="preserve">0.305410861968994</t>
   </si>
   <si>
     <t xml:space="preserve">0.30848416686058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304642498493195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320777416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356888949871063</t>
+    <t xml:space="preserve">0.304642528295517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32077744603157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356888920068741</t>
   </si>
   <si>
     <t xml:space="preserve">0.358041375875473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356120586395264</t>
+    <t xml:space="preserve">0.356120616197586</t>
   </si>
   <si>
     <t xml:space="preserve">0.360730558633804</t>
@@ -1760,46 +1760,46 @@
     <t xml:space="preserve">0.358809769153595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351126462221146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355736404657364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342290639877319</t>
+    <t xml:space="preserve">0.351126402616501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355736434459686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342290669679642</t>
   </si>
   <si>
     <t xml:space="preserve">0.37187135219574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370334684848785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383780419826508</t>
+    <t xml:space="preserve">0.370334625244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38378044962883</t>
   </si>
   <si>
     <t xml:space="preserve">0.376097142696381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37686550617218</t>
+    <t xml:space="preserve">0.376865476369858</t>
   </si>
   <si>
     <t xml:space="preserve">0.377249658107758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398762881755829</t>
+    <t xml:space="preserve">0.398762851953506</t>
   </si>
   <si>
     <t xml:space="preserve">0.403372824192047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406446099281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409519493579865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391079604625702</t>
+    <t xml:space="preserve">0.406446129083633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409519463777542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39107957482338</t>
   </si>
   <si>
     <t xml:space="preserve">0.381475448608398</t>
@@ -1808,22 +1808,22 @@
     <t xml:space="preserve">0.407214462757111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387237936258316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394921183586121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411824434995651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414897799491882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417202740907669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397226214408875</t>
+    <t xml:space="preserve">0.387237906455994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394921243190765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.411824494600296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41489776968956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417202711105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397226184606552</t>
   </si>
   <si>
     <t xml:space="preserve">0.40875118970871</t>
@@ -1832,19 +1832,19 @@
     <t xml:space="preserve">0.410287797451019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41412940621376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416434437036514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418739378452301</t>
+    <t xml:space="preserve">0.414129436016083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416434407234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418739438056946</t>
   </si>
   <si>
     <t xml:space="preserve">0.420276075601578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421812772750854</t>
+    <t xml:space="preserve">0.42181271314621</t>
   </si>
   <si>
     <t xml:space="preserve">0.430264383554459</t>
@@ -1853,25 +1853,25 @@
     <t xml:space="preserve">0.473290801048279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49480402469635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484047383069992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493267357349396</t>
+    <t xml:space="preserve">0.494803994894028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484047472476959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493267387151718</t>
   </si>
   <si>
     <t xml:space="preserve">0.506328940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479437440633774</t>
+    <t xml:space="preserve">0.479437410831451</t>
   </si>
   <si>
     <t xml:space="preserve">0.482510715723038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47559580206871</t>
+    <t xml:space="preserve">0.475595891475677</t>
   </si>
   <si>
     <t xml:space="preserve">0.464070796966553</t>
@@ -1880,28 +1880,28 @@
     <t xml:space="preserve">0.465607523918152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.460997521877289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453314244747162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4341059923172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441789239645004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445630967617035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449472546577454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45100924372673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460229188203812</t>
+    <t xml:space="preserve">0.460997551679611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453314214944839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434106022119522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441789299249649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445630878210068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449472576379776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451009273529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460229218006134</t>
   </si>
   <si>
     <t xml:space="preserve">0.454082578420639</t>
@@ -1913,55 +1913,55 @@
     <t xml:space="preserve">0.451777577400208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456387519836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463302463293076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.470985800027847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467144101858139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.457924276590347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447167634963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432569354772568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437947690486908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43333774805069</t>
+    <t xml:space="preserve">0.456387549638748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463302493095398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47098582983017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.467144131660461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.457924216985703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447167605161667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43256938457489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437947630882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433337718248367</t>
   </si>
   <si>
     <t xml:space="preserve">0.434874296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436411023139954</t>
+    <t xml:space="preserve">0.436410993337631</t>
   </si>
   <si>
     <t xml:space="preserve">0.43948432803154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441020935773849</t>
+    <t xml:space="preserve">0.441020995378494</t>
   </si>
   <si>
     <t xml:space="preserve">0.440252661705017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438715904951096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442557573318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485584110021591</t>
+    <t xml:space="preserve">0.43871596455574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442557603120804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485584050416946</t>
   </si>
   <si>
     <t xml:space="preserve">0.455619186162949</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">0.443325966596603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429496020078659</t>
+    <t xml:space="preserve">0.429496049880981</t>
   </si>
   <si>
     <t xml:space="preserve">0.435642629861832</t>
@@ -1979,43 +1979,43 @@
     <t xml:space="preserve">0.450240910053253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427190989255905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375328838825226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386469572782516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393384546041489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365724682807922</t>
+    <t xml:space="preserve">0.427191078662872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375328809022903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386469602584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393384575843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365724712610245</t>
   </si>
   <si>
     <t xml:space="preserve">0.372639685869217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351510614156723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342674881219864</t>
+    <t xml:space="preserve">0.351510643959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342674851417542</t>
   </si>
   <si>
     <t xml:space="preserve">0.317319959402084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26507356762886</t>
+    <t xml:space="preserve">0.265073597431183</t>
   </si>
   <si>
     <t xml:space="preserve">0.259695291519165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239334553480148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.242023691534996</t>
+    <t xml:space="preserve">0.239334598183632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24202373623848</t>
   </si>
   <si>
     <t xml:space="preserve">0.234724551439285</t>
@@ -2027,22 +2027,22 @@
     <t xml:space="preserve">0.258926957845688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251627773046494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266610264778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.269299358129501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258158653974533</t>
+    <t xml:space="preserve">0.251627832651138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266610234975815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.269299387931824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258158624172211</t>
   </si>
   <si>
     <t xml:space="preserve">0.251243650913239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252011954784393</t>
+    <t xml:space="preserve">0.252011984586716</t>
   </si>
   <si>
     <t xml:space="preserve">0.242407888174057</t>
@@ -2054,28 +2054,28 @@
     <t xml:space="preserve">0.254701137542725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262000232934952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254316955804825</t>
+    <t xml:space="preserve">0.262000262737274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.254316985607147</t>
   </si>
   <si>
     <t xml:space="preserve">0.261231929063797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.262768596410751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264689445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27198851108551</t>
+    <t xml:space="preserve">0.262768626213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.264689415693283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.271988540887833</t>
   </si>
   <si>
     <t xml:space="preserve">0.273909360170364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276982724666595</t>
+    <t xml:space="preserve">0.276982694864273</t>
   </si>
   <si>
     <t xml:space="preserve">0.272756844758987</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">0.268915235996246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265841901302338</t>
+    <t xml:space="preserve">0.265841871500015</t>
   </si>
   <si>
     <t xml:space="preserve">0.258542776107788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26545774936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263152778148651</t>
+    <t xml:space="preserve">0.265457779169083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263152748346329</t>
   </si>
   <si>
     <t xml:space="preserve">0.292733430862427</t>
@@ -2105,16 +2105,16 @@
     <t xml:space="preserve">0.327692419290543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30233758687973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30195340514183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332302361726761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332686573266983</t>
+    <t xml:space="preserve">0.302337527275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301953375339508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332302391529083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332686543464661</t>
   </si>
   <si>
     <t xml:space="preserve">0.306179165840149</t>
@@ -2129,46 +2129,46 @@
     <t xml:space="preserve">0.331918209791183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315399169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326539903879166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292349278926849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289275944232941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291196763515472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.286970973014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285050123929977</t>
+    <t xml:space="preserve">0.315399140119553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326539933681488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292349249124527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28927600383758